--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BEFC8CE-02EC-4BCA-9BBE-361E44A19E76}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0848C664-5BE7-4485-8A94-2FD7068D4FF8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucoes" sheetId="1" r:id="rId1"/>
@@ -427,6 +427,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -437,9 +440,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -767,44 +767,50 @@
       </c>
       <c r="B5" s="21">
         <f>SUM(B6:B7)</f>
-        <v>0</v>
+        <v>1250</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G5" s="14">
         <f>SUM(G6:G7)</f>
-        <v>1300</v>
+        <v>1800</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="L5" s="14">
         <f>SUM(L6:L7)</f>
-        <v>0</v>
+        <v>700</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
       <c r="A6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="14"/>
+      <c r="B6" s="14">
+        <v>750</v>
+      </c>
       <c r="F6" s="7" t="s">
         <v>21</v>
       </c>
       <c r="G6" s="14">
-        <v>1300</v>
+        <v>1800</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="L6" s="14"/>
+      <c r="L6" s="14">
+        <v>700</v>
+      </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="14"/>
+      <c r="B7" s="14">
+        <v>500</v>
+      </c>
       <c r="F7" s="7" t="s">
         <v>22</v>
       </c>
@@ -834,7 +840,7 @@
       </c>
       <c r="L8" s="15">
         <f>SUM(L9:L10)</f>
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1">
@@ -850,7 +856,7 @@
         <v>21</v>
       </c>
       <c r="L9" s="15">
-        <v>800</v>
+        <v>900</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
@@ -938,7 +944,7 @@
       </c>
       <c r="L14" s="15">
         <f>SUM(L15:L16)</f>
-        <v>120</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1">
@@ -954,7 +960,7 @@
         <v>21</v>
       </c>
       <c r="L15" s="15">
-        <v>120</v>
+        <v>220</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1">
@@ -977,7 +983,7 @@
       </c>
       <c r="B17" s="14">
         <f>SUM(B18:B19)</f>
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>26</v>
@@ -999,7 +1005,7 @@
         <v>21</v>
       </c>
       <c r="B18" s="14">
-        <v>120</v>
+        <v>170</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>21</v>
@@ -1132,7 +1138,7 @@
       </c>
       <c r="B26" s="15">
         <f>SUM(B27:B28)</f>
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>29</v>
@@ -1154,7 +1160,7 @@
         <v>21</v>
       </c>
       <c r="B27" s="15">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>21</v>
@@ -1185,7 +1191,7 @@
       </c>
       <c r="B29" s="14">
         <f>SUM(B30:B31)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>30</v>
@@ -1206,7 +1212,9 @@
       <c r="A30" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B30" s="14"/>
+      <c r="B30" s="14">
+        <v>20</v>
+      </c>
       <c r="F30" s="7" t="s">
         <v>21</v>
       </c>
@@ -1240,7 +1248,7 @@
       </c>
       <c r="B32" s="15">
         <f>SUM(B33:B34)</f>
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>31</v>
@@ -1262,7 +1270,7 @@
         <v>21</v>
       </c>
       <c r="B33" s="15">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>21</v>
@@ -1399,21 +1407,21 @@
       </c>
       <c r="B41" s="13">
         <f>SUM(B5,B8,B11,B14,B17,B20,B23,B26,B29,B32,B35,B38)</f>
-        <v>970</v>
+        <v>2840</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G41" s="13">
         <f>SUM(G5,G8,G11,G14,G17,G20,G23,G26,G29,G32,G35,G38)</f>
-        <v>1350</v>
+        <v>1850</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="L41" s="13">
         <f>SUM(L5,L8,L11,L14,L17,L20,L23,L26,L29,L32,L35,L38)</f>
-        <v>3720</v>
+        <v>4620</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1">
@@ -1509,7 +1517,7 @@
       </c>
       <c r="B53" s="14">
         <f>SUM(B54:B55)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F53" s="7" t="s">
         <v>20</v>
@@ -1530,7 +1538,9 @@
       <c r="A54" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B54" s="14"/>
+      <c r="B54" s="14">
+        <v>50</v>
+      </c>
       <c r="F54" s="7" t="s">
         <v>21</v>
       </c>
@@ -1662,7 +1672,7 @@
       </c>
       <c r="B62" s="15">
         <f>SUM(B63:B64)</f>
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>25</v>
@@ -1684,7 +1694,7 @@
         <v>21</v>
       </c>
       <c r="B63" s="15">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>21</v>
@@ -2127,7 +2137,7 @@
       </c>
       <c r="B89" s="13">
         <f>SUM(B53,B56,B59,B62,B65,B68,B71,B74,B77,B80,B83,B86)</f>
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>34</v>
@@ -2191,19 +2201,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="25"/>
       <c r="H1" s="25"/>
       <c r="I1" s="25"/>
-      <c r="K1" s="30" t="s">
+      <c r="K1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="25"/>
@@ -2211,19 +2221,19 @@
       <c r="N1" s="25"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
-      <c r="F2" s="30" t="s">
+      <c r="F2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
       <c r="I2" s="25"/>
-      <c r="K2" s="30" t="s">
+      <c r="K2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="25"/>
@@ -2245,27 +2255,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="29" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="25"/>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="25"/>
-      <c r="H4" s="28" t="s">
+      <c r="H4" s="29" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="25"/>
-      <c r="K4" s="28" t="s">
+      <c r="K4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="25"/>
-      <c r="M4" s="28" t="s">
+      <c r="M4" s="29" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="25"/>
@@ -2274,7 +2284,7 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="28">
         <v>352</v>
       </c>
       <c r="C5" s="25"/>
@@ -2282,13 +2292,13 @@
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="27"/>
+      <c r="G5" s="28"/>
       <c r="H5" s="25"/>
       <c r="I5" s="25"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="27"/>
+      <c r="L5" s="28"/>
       <c r="M5" s="25"/>
       <c r="N5" s="25"/>
     </row>
@@ -2296,7 +2306,7 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="27">
         <v>376</v>
       </c>
       <c r="C6" s="25"/>
@@ -2304,13 +2314,13 @@
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="26"/>
+      <c r="G6" s="27"/>
       <c r="H6" s="25"/>
       <c r="I6" s="25"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="26"/>
+      <c r="L6" s="27"/>
       <c r="M6" s="25"/>
       <c r="N6" s="25"/>
     </row>
@@ -2318,7 +2328,7 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="28">
         <v>0</v>
       </c>
       <c r="C7" s="25"/>
@@ -2326,13 +2336,13 @@
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="27"/>
+      <c r="G7" s="28"/>
       <c r="H7" s="25"/>
       <c r="I7" s="25"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="27"/>
+      <c r="L7" s="28"/>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
     </row>
@@ -2340,7 +2350,7 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="27">
         <v>724</v>
       </c>
       <c r="C8" s="25"/>
@@ -2348,13 +2358,13 @@
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="26"/>
+      <c r="G8" s="27"/>
       <c r="H8" s="25"/>
       <c r="I8" s="25"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="26"/>
+      <c r="L8" s="27"/>
       <c r="M8" s="25"/>
       <c r="N8" s="25"/>
     </row>
@@ -2362,7 +2372,7 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="27">
+      <c r="B9" s="28">
         <v>411</v>
       </c>
       <c r="C9" s="25"/>
@@ -2370,13 +2380,13 @@
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="27"/>
+      <c r="G9" s="28"/>
       <c r="H9" s="25"/>
       <c r="I9" s="25"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="27"/>
+      <c r="L9" s="28"/>
       <c r="M9" s="25"/>
       <c r="N9" s="25"/>
     </row>
@@ -2384,7 +2394,7 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="27">
         <v>0</v>
       </c>
       <c r="C10" s="25"/>
@@ -2392,13 +2402,13 @@
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="26"/>
+      <c r="G10" s="27"/>
       <c r="H10" s="25"/>
       <c r="I10" s="25"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="26"/>
+      <c r="L10" s="27"/>
       <c r="M10" s="25"/>
       <c r="N10" s="25"/>
     </row>
@@ -2406,7 +2416,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="30">
         <f>SUM(B5:B10)</f>
         <v>1863</v>
       </c>
@@ -2415,7 +2425,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="29">
+      <c r="G11" s="30">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -2424,7 +2434,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="29">
+      <c r="L11" s="30">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -2460,19 +2470,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
-      <c r="F25" s="30" t="s">
+      <c r="F25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
       <c r="I25" s="25"/>
-      <c r="K25" s="30" t="s">
+      <c r="K25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="25"/>
@@ -2480,19 +2490,19 @@
       <c r="N25" s="25"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
-      <c r="F26" s="30" t="s">
+      <c r="F26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="25"/>
       <c r="H26" s="25"/>
       <c r="I26" s="25"/>
-      <c r="K26" s="30" t="s">
+      <c r="K26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="25"/>
@@ -2514,27 +2524,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="25"/>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="29" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="25"/>
-      <c r="F28" s="28" t="s">
+      <c r="F28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="25"/>
-      <c r="H28" s="28" t="s">
+      <c r="H28" s="29" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="25"/>
-      <c r="K28" s="28" t="s">
+      <c r="K28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="25"/>
-      <c r="M28" s="28" t="s">
+      <c r="M28" s="29" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="25"/>
@@ -2543,7 +2553,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="27">
+      <c r="B29" s="28">
         <v>0</v>
       </c>
       <c r="C29" s="25"/>
@@ -2551,13 +2561,13 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="27"/>
+      <c r="G29" s="28"/>
       <c r="H29" s="25"/>
       <c r="I29" s="25"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="27">
+      <c r="L29" s="28">
         <v>14</v>
       </c>
       <c r="M29" s="25"/>
@@ -2567,7 +2577,7 @@
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="26">
+      <c r="B30" s="27">
         <v>0</v>
       </c>
       <c r="C30" s="25"/>
@@ -2575,13 +2585,13 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="26"/>
+      <c r="G30" s="27"/>
       <c r="H30" s="25"/>
       <c r="I30" s="25"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="26">
+      <c r="L30" s="27">
         <v>605</v>
       </c>
       <c r="M30" s="25"/>
@@ -2591,7 +2601,7 @@
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="27">
+      <c r="B31" s="28">
         <v>0</v>
       </c>
       <c r="C31" s="25"/>
@@ -2599,13 +2609,13 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="27"/>
+      <c r="G31" s="28"/>
       <c r="H31" s="25"/>
       <c r="I31" s="25"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="27">
+      <c r="L31" s="28">
         <v>1708</v>
       </c>
       <c r="M31" s="25"/>
@@ -2615,7 +2625,7 @@
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="26">
+      <c r="B32" s="27">
         <v>0</v>
       </c>
       <c r="C32" s="25"/>
@@ -2623,13 +2633,13 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="26"/>
+      <c r="G32" s="27"/>
       <c r="H32" s="25"/>
       <c r="I32" s="25"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="26">
+      <c r="L32" s="27">
         <v>1395</v>
       </c>
       <c r="M32" s="25"/>
@@ -2639,7 +2649,7 @@
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="27">
+      <c r="B33" s="28">
         <v>0</v>
       </c>
       <c r="C33" s="25"/>
@@ -2647,13 +2657,13 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="27"/>
+      <c r="G33" s="28"/>
       <c r="H33" s="25"/>
       <c r="I33" s="25"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="27">
+      <c r="L33" s="28">
         <v>0</v>
       </c>
       <c r="M33" s="25"/>
@@ -2663,7 +2673,7 @@
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="26">
+      <c r="B34" s="27">
         <v>0</v>
       </c>
       <c r="C34" s="25"/>
@@ -2671,13 +2681,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="26"/>
+      <c r="G34" s="27"/>
       <c r="H34" s="25"/>
       <c r="I34" s="25"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="26">
+      <c r="L34" s="27">
         <v>0</v>
       </c>
       <c r="M34" s="25"/>
@@ -2687,7 +2697,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="29">
+      <c r="B35" s="30">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -2696,7 +2706,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="29">
+      <c r="G35" s="30">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -2705,7 +2715,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="29">
+      <c r="L35" s="30">
         <f>SUM(L29:L34)</f>
         <v>3722</v>
       </c>
@@ -2742,13 +2752,49 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="L11:N11"/>
@@ -2765,49 +2811,13 @@
     <mergeCell ref="K2:N2"/>
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2823,7 +2833,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
@@ -2831,7 +2841,7 @@
       <c r="D1" s="25"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
@@ -2845,11 +2855,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="29" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="29" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="25"/>
@@ -2858,7 +2868,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="27"/>
+      <c r="B5" s="28"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
     </row>
@@ -2866,7 +2876,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="26"/>
+      <c r="B6" s="27"/>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
     </row>
@@ -2874,7 +2884,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="27"/>
+      <c r="B7" s="28"/>
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
     </row>
@@ -2882,7 +2892,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="26"/>
+      <c r="B8" s="27"/>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
     </row>
@@ -2890,7 +2900,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="30">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -2939,19 +2949,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="25"/>
       <c r="H1" s="25"/>
       <c r="I1" s="25"/>
-      <c r="K1" s="30" t="s">
+      <c r="K1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="25"/>
@@ -2959,19 +2969,19 @@
       <c r="N1" s="25"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
-      <c r="F2" s="30" t="s">
+      <c r="F2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
       <c r="I2" s="25"/>
-      <c r="K2" s="30" t="s">
+      <c r="K2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="25"/>
@@ -2993,27 +3003,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="29" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="25"/>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="25"/>
-      <c r="H4" s="28" t="s">
+      <c r="H4" s="29" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="25"/>
-      <c r="K4" s="28" t="s">
+      <c r="K4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="25"/>
-      <c r="M4" s="28" t="s">
+      <c r="M4" s="29" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="25"/>
@@ -3022,19 +3032,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="27"/>
+      <c r="B5" s="28"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="27"/>
+      <c r="G5" s="28"/>
       <c r="H5" s="25"/>
       <c r="I5" s="25"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="27"/>
+      <c r="L5" s="28"/>
       <c r="M5" s="25"/>
       <c r="N5" s="25"/>
     </row>
@@ -3042,19 +3052,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="26"/>
+      <c r="B6" s="27"/>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="26"/>
+      <c r="G6" s="27"/>
       <c r="H6" s="25"/>
       <c r="I6" s="25"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="26"/>
+      <c r="L6" s="27"/>
       <c r="M6" s="25"/>
       <c r="N6" s="25"/>
     </row>
@@ -3062,19 +3072,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="27"/>
+      <c r="B7" s="28"/>
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="27"/>
+      <c r="G7" s="28"/>
       <c r="H7" s="25"/>
       <c r="I7" s="25"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="27"/>
+      <c r="L7" s="28"/>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
     </row>
@@ -3082,19 +3092,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="26"/>
+      <c r="B8" s="27"/>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="26"/>
+      <c r="G8" s="27"/>
       <c r="H8" s="25"/>
       <c r="I8" s="25"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="26"/>
+      <c r="L8" s="27"/>
       <c r="M8" s="25"/>
       <c r="N8" s="25"/>
     </row>
@@ -3102,19 +3112,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="27"/>
+      <c r="B9" s="28"/>
       <c r="C9" s="25"/>
       <c r="D9" s="25"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="27"/>
+      <c r="G9" s="28"/>
       <c r="H9" s="25"/>
       <c r="I9" s="25"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="27"/>
+      <c r="L9" s="28"/>
       <c r="M9" s="25"/>
       <c r="N9" s="25"/>
     </row>
@@ -3122,19 +3132,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="26"/>
+      <c r="B10" s="27"/>
       <c r="C10" s="25"/>
       <c r="D10" s="25"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="26"/>
+      <c r="G10" s="27"/>
       <c r="H10" s="25"/>
       <c r="I10" s="25"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="26"/>
+      <c r="L10" s="27"/>
       <c r="M10" s="25"/>
       <c r="N10" s="25"/>
     </row>
@@ -3142,19 +3152,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="27"/>
+      <c r="B11" s="28"/>
       <c r="C11" s="25"/>
       <c r="D11" s="25"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="27"/>
+      <c r="G11" s="28"/>
       <c r="H11" s="25"/>
       <c r="I11" s="25"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="27"/>
+      <c r="L11" s="28"/>
       <c r="M11" s="25"/>
       <c r="N11" s="25"/>
     </row>
@@ -3162,19 +3172,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="26"/>
+      <c r="B12" s="27"/>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="26"/>
+      <c r="G12" s="27"/>
       <c r="H12" s="25"/>
       <c r="I12" s="25"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="26"/>
+      <c r="L12" s="27"/>
       <c r="M12" s="25"/>
       <c r="N12" s="25"/>
     </row>
@@ -3182,7 +3192,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="30">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3191,7 +3201,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="29">
+      <c r="G13" s="30">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3200,7 +3210,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="29">
+      <c r="L13" s="30">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3236,19 +3246,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
-      <c r="F25" s="30" t="s">
+      <c r="F25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
       <c r="I25" s="25"/>
-      <c r="K25" s="30" t="s">
+      <c r="K25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="25"/>
@@ -3256,19 +3266,19 @@
       <c r="N25" s="25"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
-      <c r="F26" s="30" t="s">
+      <c r="F26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="25"/>
       <c r="H26" s="25"/>
       <c r="I26" s="25"/>
-      <c r="K26" s="30" t="s">
+      <c r="K26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="25"/>
@@ -3290,27 +3300,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="25"/>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="29" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="25"/>
-      <c r="F28" s="28" t="s">
+      <c r="F28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="25"/>
-      <c r="H28" s="28" t="s">
+      <c r="H28" s="29" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="25"/>
-      <c r="K28" s="28" t="s">
+      <c r="K28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="25"/>
-      <c r="M28" s="28" t="s">
+      <c r="M28" s="29" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="25"/>
@@ -3319,19 +3329,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="27"/>
+      <c r="B29" s="28"/>
       <c r="C29" s="25"/>
       <c r="D29" s="25"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="27"/>
+      <c r="G29" s="28"/>
       <c r="H29" s="25"/>
       <c r="I29" s="25"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="27"/>
+      <c r="L29" s="28"/>
       <c r="M29" s="25"/>
       <c r="N29" s="25"/>
     </row>
@@ -3339,19 +3349,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="26"/>
+      <c r="B30" s="27"/>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="26"/>
+      <c r="G30" s="27"/>
       <c r="H30" s="25"/>
       <c r="I30" s="25"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="26"/>
+      <c r="L30" s="27"/>
       <c r="M30" s="25"/>
       <c r="N30" s="25"/>
     </row>
@@ -3359,19 +3369,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="27"/>
+      <c r="B31" s="28"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="27"/>
+      <c r="G31" s="28"/>
       <c r="H31" s="25"/>
       <c r="I31" s="25"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="27"/>
+      <c r="L31" s="28"/>
       <c r="M31" s="25"/>
       <c r="N31" s="25"/>
     </row>
@@ -3379,19 +3389,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="26"/>
+      <c r="B32" s="27"/>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="26"/>
+      <c r="G32" s="27"/>
       <c r="H32" s="25"/>
       <c r="I32" s="25"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="26"/>
+      <c r="L32" s="27"/>
       <c r="M32" s="25"/>
       <c r="N32" s="25"/>
     </row>
@@ -3399,19 +3409,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="27"/>
+      <c r="B33" s="28"/>
       <c r="C33" s="25"/>
       <c r="D33" s="25"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="27"/>
+      <c r="G33" s="28"/>
       <c r="H33" s="25"/>
       <c r="I33" s="25"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="27"/>
+      <c r="L33" s="28"/>
       <c r="M33" s="25"/>
       <c r="N33" s="25"/>
     </row>
@@ -3419,19 +3429,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="26"/>
+      <c r="B34" s="27"/>
       <c r="C34" s="25"/>
       <c r="D34" s="25"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="26"/>
+      <c r="G34" s="27"/>
       <c r="H34" s="25"/>
       <c r="I34" s="25"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="26"/>
+      <c r="L34" s="27"/>
       <c r="M34" s="25"/>
       <c r="N34" s="25"/>
     </row>
@@ -3439,19 +3449,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="27"/>
+      <c r="B35" s="28"/>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="27"/>
+      <c r="G35" s="28"/>
       <c r="H35" s="25"/>
       <c r="I35" s="25"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="27"/>
+      <c r="L35" s="28"/>
       <c r="M35" s="25"/>
       <c r="N35" s="25"/>
     </row>
@@ -3459,19 +3469,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="26"/>
+      <c r="B36" s="27"/>
       <c r="C36" s="25"/>
       <c r="D36" s="25"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="26"/>
+      <c r="G36" s="27"/>
       <c r="H36" s="25"/>
       <c r="I36" s="25"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="26"/>
+      <c r="L36" s="27"/>
       <c r="M36" s="25"/>
       <c r="N36" s="25"/>
     </row>
@@ -3479,7 +3489,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="29">
+      <c r="B37" s="30">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -3488,7 +3498,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="29">
+      <c r="G37" s="30">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -3497,7 +3507,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="29">
+      <c r="L37" s="30">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -3534,6 +3544,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
     <mergeCell ref="L34:N34"/>
     <mergeCell ref="L6:N6"/>
     <mergeCell ref="B33:D33"/>
@@ -3550,68 +3622,6 @@
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0848C664-5BE7-4485-8A94-2FD7068D4FF8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6EB9C1-E04F-4146-A556-603D86653650}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -427,9 +427,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -440,6 +437,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -767,21 +767,21 @@
       </c>
       <c r="B5" s="21">
         <f>SUM(B6:B7)</f>
-        <v>1250</v>
+        <v>2300</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G5" s="14">
         <f>SUM(G6:G7)</f>
-        <v>1800</v>
+        <v>1700</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="L5" s="14">
         <f>SUM(L6:L7)</f>
-        <v>700</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
@@ -789,19 +789,19 @@
         <v>21</v>
       </c>
       <c r="B6" s="14">
-        <v>750</v>
+        <v>1300</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>21</v>
       </c>
       <c r="G6" s="14">
-        <v>1800</v>
+        <v>1300</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>21</v>
       </c>
       <c r="L6" s="14">
-        <v>700</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
@@ -809,12 +809,14 @@
         <v>22</v>
       </c>
       <c r="B7" s="14">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="14"/>
+      <c r="G7" s="14">
+        <v>400</v>
+      </c>
       <c r="K7" s="7" t="s">
         <v>22</v>
       </c>
@@ -833,14 +835,14 @@
       </c>
       <c r="G8" s="15">
         <f>SUM(G9:G10)</f>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="K8" s="9" t="s">
         <v>23</v>
       </c>
       <c r="L8" s="15">
         <f>SUM(L9:L10)</f>
-        <v>900</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1">
@@ -851,12 +853,14 @@
       <c r="F9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="15"/>
+      <c r="G9" s="15">
+        <v>600</v>
+      </c>
       <c r="K9" s="9" t="s">
         <v>21</v>
       </c>
       <c r="L9" s="15">
-        <v>900</v>
+        <v>350</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
@@ -944,7 +948,7 @@
       </c>
       <c r="L14" s="15">
         <f>SUM(L15:L16)</f>
-        <v>220</v>
+        <v>300</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1">
@@ -960,7 +964,7 @@
         <v>21</v>
       </c>
       <c r="L15" s="15">
-        <v>220</v>
+        <v>300</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1">
@@ -1138,7 +1142,7 @@
       </c>
       <c r="B26" s="15">
         <f>SUM(B27:B28)</f>
-        <v>450</v>
+        <v>0</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>29</v>
@@ -1159,9 +1163,7 @@
       <c r="A27" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="15">
-        <v>450</v>
-      </c>
+      <c r="B27" s="15"/>
       <c r="F27" s="9" t="s">
         <v>21</v>
       </c>
@@ -1191,7 +1193,7 @@
       </c>
       <c r="B29" s="14">
         <f>SUM(B30:B31)</f>
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>30</v>
@@ -1205,7 +1207,7 @@
       </c>
       <c r="L29" s="14">
         <f>SUM(L30:L31)</f>
-        <v>1400</v>
+        <v>540</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1">
@@ -1213,7 +1215,7 @@
         <v>21</v>
       </c>
       <c r="B30" s="14">
-        <v>20</v>
+        <v>800</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>21</v>
@@ -1225,7 +1227,7 @@
         <v>21</v>
       </c>
       <c r="L30" s="14">
-        <v>1400</v>
+        <v>540</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1">
@@ -1248,7 +1250,7 @@
       </c>
       <c r="B32" s="15">
         <f>SUM(B33:B34)</f>
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>31</v>
@@ -1262,16 +1264,14 @@
       </c>
       <c r="L32" s="15">
         <f>SUM(L33:L34)</f>
-        <v>1400</v>
+        <v>400</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="15">
-        <v>800</v>
-      </c>
+      <c r="B33" s="15"/>
       <c r="F33" s="9" t="s">
         <v>21</v>
       </c>
@@ -1280,7 +1280,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="15">
-        <v>1400</v>
+        <v>400</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="B38" s="22">
         <f>SUM(B39:B40)</f>
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>72</v>
@@ -1375,9 +1375,7 @@
       <c r="A39" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B39" s="15">
-        <v>150</v>
-      </c>
+      <c r="B39" s="15"/>
       <c r="F39" s="9" t="s">
         <v>21</v>
       </c>
@@ -1407,21 +1405,21 @@
       </c>
       <c r="B41" s="13">
         <f>SUM(B5,B8,B11,B14,B17,B20,B23,B26,B29,B32,B35,B38)</f>
-        <v>2840</v>
+        <v>3270</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G41" s="13">
         <f>SUM(G5,G8,G11,G14,G17,G20,G23,G26,G29,G32,G35,G38)</f>
-        <v>1850</v>
+        <v>2350</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="L41" s="13">
         <f>SUM(L5,L8,L11,L14,L17,L20,L23,L26,L29,L32,L35,L38)</f>
-        <v>4620</v>
+        <v>4090</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1">
@@ -1517,7 +1515,7 @@
       </c>
       <c r="B53" s="14">
         <f>SUM(B54:B55)</f>
-        <v>50</v>
+        <v>380</v>
       </c>
       <c r="F53" s="7" t="s">
         <v>20</v>
@@ -1539,7 +1537,7 @@
         <v>21</v>
       </c>
       <c r="B54" s="14">
-        <v>50</v>
+        <v>380</v>
       </c>
       <c r="F54" s="7" t="s">
         <v>21</v>
@@ -1672,7 +1670,7 @@
       </c>
       <c r="B62" s="15">
         <f>SUM(B63:B64)</f>
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>25</v>
@@ -1694,7 +1692,7 @@
         <v>21</v>
       </c>
       <c r="B63" s="15">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>21</v>
@@ -1996,7 +1994,7 @@
       </c>
       <c r="L80" s="15">
         <f>SUM(L81:L82)</f>
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:14" ht="15" customHeight="1">
@@ -2011,9 +2009,7 @@
       <c r="K81" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L81" s="15">
-        <v>9</v>
-      </c>
+      <c r="L81" s="15"/>
     </row>
     <row r="82" spans="1:14" ht="15" customHeight="1">
       <c r="A82" s="9" t="s">
@@ -2137,7 +2133,7 @@
       </c>
       <c r="B89" s="13">
         <f>SUM(B53,B56,B59,B62,B65,B68,B71,B74,B77,B80,B83,B86)</f>
-        <v>110</v>
+        <v>386</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>34</v>
@@ -2151,7 +2147,7 @@
       </c>
       <c r="L89" s="13">
         <f>SUM(L53,L56,L59,L62,L65,L68,L71,L74,L77,L80,L83,L86)</f>
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:14" ht="15" customHeight="1">
@@ -2201,19 +2197,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="25"/>
       <c r="H1" s="25"/>
       <c r="I1" s="25"/>
-      <c r="K1" s="26" t="s">
+      <c r="K1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="25"/>
@@ -2221,19 +2217,19 @@
       <c r="N1" s="25"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
       <c r="I2" s="25"/>
-      <c r="K2" s="26" t="s">
+      <c r="K2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="25"/>
@@ -2255,27 +2251,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="28" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="25"/>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="25"/>
-      <c r="H4" s="29" t="s">
+      <c r="H4" s="28" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="25"/>
-      <c r="K4" s="29" t="s">
+      <c r="K4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="25"/>
-      <c r="M4" s="29" t="s">
+      <c r="M4" s="28" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="25"/>
@@ -2284,7 +2280,7 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="28">
+      <c r="B5" s="27">
         <v>352</v>
       </c>
       <c r="C5" s="25"/>
@@ -2292,13 +2288,13 @@
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="28"/>
+      <c r="G5" s="27"/>
       <c r="H5" s="25"/>
       <c r="I5" s="25"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="28"/>
+      <c r="L5" s="27"/>
       <c r="M5" s="25"/>
       <c r="N5" s="25"/>
     </row>
@@ -2306,7 +2302,7 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="26">
         <v>376</v>
       </c>
       <c r="C6" s="25"/>
@@ -2314,13 +2310,13 @@
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="27"/>
+      <c r="G6" s="26"/>
       <c r="H6" s="25"/>
       <c r="I6" s="25"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="27"/>
+      <c r="L6" s="26"/>
       <c r="M6" s="25"/>
       <c r="N6" s="25"/>
     </row>
@@ -2328,7 +2324,7 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="27">
         <v>0</v>
       </c>
       <c r="C7" s="25"/>
@@ -2336,13 +2332,13 @@
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="28"/>
+      <c r="G7" s="27"/>
       <c r="H7" s="25"/>
       <c r="I7" s="25"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="28"/>
+      <c r="L7" s="27"/>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
     </row>
@@ -2350,7 +2346,7 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="26">
         <v>724</v>
       </c>
       <c r="C8" s="25"/>
@@ -2358,13 +2354,13 @@
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="27"/>
+      <c r="G8" s="26"/>
       <c r="H8" s="25"/>
       <c r="I8" s="25"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="27"/>
+      <c r="L8" s="26"/>
       <c r="M8" s="25"/>
       <c r="N8" s="25"/>
     </row>
@@ -2372,7 +2368,7 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="28">
+      <c r="B9" s="27">
         <v>411</v>
       </c>
       <c r="C9" s="25"/>
@@ -2380,13 +2376,13 @@
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="28"/>
+      <c r="G9" s="27"/>
       <c r="H9" s="25"/>
       <c r="I9" s="25"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="28"/>
+      <c r="L9" s="27"/>
       <c r="M9" s="25"/>
       <c r="N9" s="25"/>
     </row>
@@ -2394,7 +2390,7 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="27">
+      <c r="B10" s="26">
         <v>0</v>
       </c>
       <c r="C10" s="25"/>
@@ -2402,13 +2398,13 @@
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="27"/>
+      <c r="G10" s="26"/>
       <c r="H10" s="25"/>
       <c r="I10" s="25"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="27"/>
+      <c r="L10" s="26"/>
       <c r="M10" s="25"/>
       <c r="N10" s="25"/>
     </row>
@@ -2416,7 +2412,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="29">
         <f>SUM(B5:B10)</f>
         <v>1863</v>
       </c>
@@ -2425,7 +2421,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="30">
+      <c r="G11" s="29">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -2434,7 +2430,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="30">
+      <c r="L11" s="29">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -2470,19 +2466,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
-      <c r="F25" s="26" t="s">
+      <c r="F25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
       <c r="I25" s="25"/>
-      <c r="K25" s="26" t="s">
+      <c r="K25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="25"/>
@@ -2490,19 +2486,19 @@
       <c r="N25" s="25"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
-      <c r="F26" s="26" t="s">
+      <c r="F26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="25"/>
       <c r="H26" s="25"/>
       <c r="I26" s="25"/>
-      <c r="K26" s="26" t="s">
+      <c r="K26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="25"/>
@@ -2524,27 +2520,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="25"/>
-      <c r="C28" s="29" t="s">
+      <c r="C28" s="28" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="25"/>
-      <c r="F28" s="29" t="s">
+      <c r="F28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="25"/>
-      <c r="H28" s="29" t="s">
+      <c r="H28" s="28" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="25"/>
-      <c r="K28" s="29" t="s">
+      <c r="K28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="25"/>
-      <c r="M28" s="29" t="s">
+      <c r="M28" s="28" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="25"/>
@@ -2553,7 +2549,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="28">
+      <c r="B29" s="27">
         <v>0</v>
       </c>
       <c r="C29" s="25"/>
@@ -2561,13 +2557,13 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="28"/>
+      <c r="G29" s="27"/>
       <c r="H29" s="25"/>
       <c r="I29" s="25"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="28">
+      <c r="L29" s="27">
         <v>14</v>
       </c>
       <c r="M29" s="25"/>
@@ -2577,7 +2573,7 @@
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="27">
+      <c r="B30" s="26">
         <v>0</v>
       </c>
       <c r="C30" s="25"/>
@@ -2585,13 +2581,13 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="27"/>
+      <c r="G30" s="26"/>
       <c r="H30" s="25"/>
       <c r="I30" s="25"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="27">
+      <c r="L30" s="26">
         <v>605</v>
       </c>
       <c r="M30" s="25"/>
@@ -2601,7 +2597,7 @@
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="28">
+      <c r="B31" s="27">
         <v>0</v>
       </c>
       <c r="C31" s="25"/>
@@ -2609,13 +2605,13 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="28"/>
+      <c r="G31" s="27"/>
       <c r="H31" s="25"/>
       <c r="I31" s="25"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="28">
+      <c r="L31" s="27">
         <v>1708</v>
       </c>
       <c r="M31" s="25"/>
@@ -2625,7 +2621,7 @@
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="27">
+      <c r="B32" s="26">
         <v>0</v>
       </c>
       <c r="C32" s="25"/>
@@ -2633,13 +2629,13 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="27"/>
+      <c r="G32" s="26"/>
       <c r="H32" s="25"/>
       <c r="I32" s="25"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="27">
+      <c r="L32" s="26">
         <v>1395</v>
       </c>
       <c r="M32" s="25"/>
@@ -2649,7 +2645,7 @@
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="28">
+      <c r="B33" s="27">
         <v>0</v>
       </c>
       <c r="C33" s="25"/>
@@ -2657,13 +2653,13 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="28"/>
+      <c r="G33" s="27"/>
       <c r="H33" s="25"/>
       <c r="I33" s="25"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="28">
+      <c r="L33" s="27">
         <v>0</v>
       </c>
       <c r="M33" s="25"/>
@@ -2673,7 +2669,7 @@
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="27">
+      <c r="B34" s="26">
         <v>0</v>
       </c>
       <c r="C34" s="25"/>
@@ -2681,13 +2677,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="27"/>
+      <c r="G34" s="26"/>
       <c r="H34" s="25"/>
       <c r="I34" s="25"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="27">
+      <c r="L34" s="26">
         <v>0</v>
       </c>
       <c r="M34" s="25"/>
@@ -2697,7 +2693,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="30">
+      <c r="B35" s="29">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -2706,7 +2702,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="30">
+      <c r="G35" s="29">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -2715,7 +2711,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="30">
+      <c r="L35" s="29">
         <f>SUM(L29:L34)</f>
         <v>3722</v>
       </c>
@@ -2752,6 +2748,56 @@
     </row>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B10:D10"/>
@@ -2768,56 +2814,6 @@
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="H28:I28"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2833,7 +2829,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
@@ -2841,7 +2837,7 @@
       <c r="D1" s="25"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
@@ -2855,11 +2851,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="28" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="28" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="25"/>
@@ -2868,7 +2864,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="28"/>
+      <c r="B5" s="27"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
     </row>
@@ -2876,7 +2872,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="27"/>
+      <c r="B6" s="26"/>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
     </row>
@@ -2884,7 +2880,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="28"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
     </row>
@@ -2892,7 +2888,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="27"/>
+      <c r="B8" s="26"/>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
     </row>
@@ -2900,7 +2896,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="29">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -2949,19 +2945,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="25"/>
       <c r="H1" s="25"/>
       <c r="I1" s="25"/>
-      <c r="K1" s="26" t="s">
+      <c r="K1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="25"/>
@@ -2969,19 +2965,19 @@
       <c r="N1" s="25"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
       <c r="I2" s="25"/>
-      <c r="K2" s="26" t="s">
+      <c r="K2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="25"/>
@@ -3003,27 +2999,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="28" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="25"/>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="25"/>
-      <c r="H4" s="29" t="s">
+      <c r="H4" s="28" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="25"/>
-      <c r="K4" s="29" t="s">
+      <c r="K4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="25"/>
-      <c r="M4" s="29" t="s">
+      <c r="M4" s="28" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="25"/>
@@ -3032,19 +3028,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="28"/>
+      <c r="B5" s="27"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="28"/>
+      <c r="G5" s="27"/>
       <c r="H5" s="25"/>
       <c r="I5" s="25"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="28"/>
+      <c r="L5" s="27"/>
       <c r="M5" s="25"/>
       <c r="N5" s="25"/>
     </row>
@@ -3052,19 +3048,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="27"/>
+      <c r="B6" s="26"/>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="27"/>
+      <c r="G6" s="26"/>
       <c r="H6" s="25"/>
       <c r="I6" s="25"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="27"/>
+      <c r="L6" s="26"/>
       <c r="M6" s="25"/>
       <c r="N6" s="25"/>
     </row>
@@ -3072,19 +3068,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="28"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="28"/>
+      <c r="G7" s="27"/>
       <c r="H7" s="25"/>
       <c r="I7" s="25"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="28"/>
+      <c r="L7" s="27"/>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
     </row>
@@ -3092,19 +3088,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="27"/>
+      <c r="B8" s="26"/>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="27"/>
+      <c r="G8" s="26"/>
       <c r="H8" s="25"/>
       <c r="I8" s="25"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="27"/>
+      <c r="L8" s="26"/>
       <c r="M8" s="25"/>
       <c r="N8" s="25"/>
     </row>
@@ -3112,19 +3108,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="28"/>
+      <c r="B9" s="27"/>
       <c r="C9" s="25"/>
       <c r="D9" s="25"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="28"/>
+      <c r="G9" s="27"/>
       <c r="H9" s="25"/>
       <c r="I9" s="25"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="28"/>
+      <c r="L9" s="27"/>
       <c r="M9" s="25"/>
       <c r="N9" s="25"/>
     </row>
@@ -3132,19 +3128,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="27"/>
+      <c r="B10" s="26"/>
       <c r="C10" s="25"/>
       <c r="D10" s="25"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="27"/>
+      <c r="G10" s="26"/>
       <c r="H10" s="25"/>
       <c r="I10" s="25"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="27"/>
+      <c r="L10" s="26"/>
       <c r="M10" s="25"/>
       <c r="N10" s="25"/>
     </row>
@@ -3152,19 +3148,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="28"/>
+      <c r="B11" s="27"/>
       <c r="C11" s="25"/>
       <c r="D11" s="25"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="28"/>
+      <c r="G11" s="27"/>
       <c r="H11" s="25"/>
       <c r="I11" s="25"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="28"/>
+      <c r="L11" s="27"/>
       <c r="M11" s="25"/>
       <c r="N11" s="25"/>
     </row>
@@ -3172,19 +3168,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="27"/>
+      <c r="B12" s="26"/>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="27"/>
+      <c r="G12" s="26"/>
       <c r="H12" s="25"/>
       <c r="I12" s="25"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="27"/>
+      <c r="L12" s="26"/>
       <c r="M12" s="25"/>
       <c r="N12" s="25"/>
     </row>
@@ -3192,7 +3188,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="29">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3201,7 +3197,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="30">
+      <c r="G13" s="29">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3210,7 +3206,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="30">
+      <c r="L13" s="29">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3246,19 +3242,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
-      <c r="F25" s="26" t="s">
+      <c r="F25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
       <c r="I25" s="25"/>
-      <c r="K25" s="26" t="s">
+      <c r="K25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="25"/>
@@ -3266,19 +3262,19 @@
       <c r="N25" s="25"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
-      <c r="F26" s="26" t="s">
+      <c r="F26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="25"/>
       <c r="H26" s="25"/>
       <c r="I26" s="25"/>
-      <c r="K26" s="26" t="s">
+      <c r="K26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="25"/>
@@ -3300,27 +3296,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="25"/>
-      <c r="C28" s="29" t="s">
+      <c r="C28" s="28" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="25"/>
-      <c r="F28" s="29" t="s">
+      <c r="F28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="25"/>
-      <c r="H28" s="29" t="s">
+      <c r="H28" s="28" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="25"/>
-      <c r="K28" s="29" t="s">
+      <c r="K28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="25"/>
-      <c r="M28" s="29" t="s">
+      <c r="M28" s="28" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="25"/>
@@ -3329,19 +3325,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="28"/>
+      <c r="B29" s="27"/>
       <c r="C29" s="25"/>
       <c r="D29" s="25"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="28"/>
+      <c r="G29" s="27"/>
       <c r="H29" s="25"/>
       <c r="I29" s="25"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="28"/>
+      <c r="L29" s="27"/>
       <c r="M29" s="25"/>
       <c r="N29" s="25"/>
     </row>
@@ -3349,19 +3345,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="27"/>
+      <c r="B30" s="26"/>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="27"/>
+      <c r="G30" s="26"/>
       <c r="H30" s="25"/>
       <c r="I30" s="25"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="27"/>
+      <c r="L30" s="26"/>
       <c r="M30" s="25"/>
       <c r="N30" s="25"/>
     </row>
@@ -3369,19 +3365,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="28"/>
+      <c r="B31" s="27"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="28"/>
+      <c r="G31" s="27"/>
       <c r="H31" s="25"/>
       <c r="I31" s="25"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="28"/>
+      <c r="L31" s="27"/>
       <c r="M31" s="25"/>
       <c r="N31" s="25"/>
     </row>
@@ -3389,19 +3385,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="27"/>
+      <c r="B32" s="26"/>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="27"/>
+      <c r="G32" s="26"/>
       <c r="H32" s="25"/>
       <c r="I32" s="25"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="27"/>
+      <c r="L32" s="26"/>
       <c r="M32" s="25"/>
       <c r="N32" s="25"/>
     </row>
@@ -3409,19 +3405,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="28"/>
+      <c r="B33" s="27"/>
       <c r="C33" s="25"/>
       <c r="D33" s="25"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="28"/>
+      <c r="G33" s="27"/>
       <c r="H33" s="25"/>
       <c r="I33" s="25"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="28"/>
+      <c r="L33" s="27"/>
       <c r="M33" s="25"/>
       <c r="N33" s="25"/>
     </row>
@@ -3429,19 +3425,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="27"/>
+      <c r="B34" s="26"/>
       <c r="C34" s="25"/>
       <c r="D34" s="25"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="27"/>
+      <c r="G34" s="26"/>
       <c r="H34" s="25"/>
       <c r="I34" s="25"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="27"/>
+      <c r="L34" s="26"/>
       <c r="M34" s="25"/>
       <c r="N34" s="25"/>
     </row>
@@ -3449,19 +3445,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="28"/>
+      <c r="B35" s="27"/>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="28"/>
+      <c r="G35" s="27"/>
       <c r="H35" s="25"/>
       <c r="I35" s="25"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="28"/>
+      <c r="L35" s="27"/>
       <c r="M35" s="25"/>
       <c r="N35" s="25"/>
     </row>
@@ -3469,19 +3465,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="27"/>
+      <c r="B36" s="26"/>
       <c r="C36" s="25"/>
       <c r="D36" s="25"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="27"/>
+      <c r="G36" s="26"/>
       <c r="H36" s="25"/>
       <c r="I36" s="25"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="27"/>
+      <c r="L36" s="26"/>
       <c r="M36" s="25"/>
       <c r="N36" s="25"/>
     </row>
@@ -3489,7 +3485,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="30">
+      <c r="B37" s="29">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -3498,7 +3494,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="30">
+      <c r="G37" s="29">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -3507,7 +3503,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="30">
+      <c r="L37" s="29">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -3544,6 +3540,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
     <mergeCell ref="G36:I36"/>
     <mergeCell ref="L32:N32"/>
     <mergeCell ref="L13:N13"/>
@@ -3560,68 +3618,6 @@
     <mergeCell ref="L33:N33"/>
     <mergeCell ref="L35:N35"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="L9:N9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6EB9C1-E04F-4146-A556-603D86653650}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F61A9F-8E2D-46CE-9A2F-E5BFBA3D43ED}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -427,6 +427,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -437,9 +440,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -767,50 +767,46 @@
       </c>
       <c r="B5" s="21">
         <f>SUM(B6:B7)</f>
-        <v>2300</v>
+        <v>0</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G5" s="14">
         <f>SUM(G6:G7)</f>
-        <v>1700</v>
+        <v>1500</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="L5" s="14">
         <f>SUM(L6:L7)</f>
-        <v>2500</v>
+        <v>500</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
       <c r="A6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="14">
-        <v>1300</v>
-      </c>
+      <c r="B6" s="14"/>
       <c r="F6" s="7" t="s">
         <v>21</v>
       </c>
       <c r="G6" s="14">
-        <v>1300</v>
+        <v>1100</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>21</v>
       </c>
       <c r="L6" s="14">
-        <v>2500</v>
+        <v>500</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="14">
-        <v>1000</v>
-      </c>
+      <c r="B7" s="14"/>
       <c r="F7" s="7" t="s">
         <v>22</v>
       </c>
@@ -1405,21 +1401,21 @@
       </c>
       <c r="B41" s="13">
         <f>SUM(B5,B8,B11,B14,B17,B20,B23,B26,B29,B32,B35,B38)</f>
-        <v>3270</v>
+        <v>970</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G41" s="13">
         <f>SUM(G5,G8,G11,G14,G17,G20,G23,G26,G29,G32,G35,G38)</f>
-        <v>2350</v>
+        <v>2150</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="L41" s="13">
         <f>SUM(L5,L8,L11,L14,L17,L20,L23,L26,L29,L32,L35,L38)</f>
-        <v>4090</v>
+        <v>2090</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1">
@@ -1515,7 +1511,7 @@
       </c>
       <c r="B53" s="14">
         <f>SUM(B54:B55)</f>
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="F53" s="7" t="s">
         <v>20</v>
@@ -1536,9 +1532,7 @@
       <c r="A54" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B54" s="14">
-        <v>380</v>
-      </c>
+      <c r="B54" s="14"/>
       <c r="F54" s="7" t="s">
         <v>21</v>
       </c>
@@ -2133,7 +2127,7 @@
       </c>
       <c r="B89" s="13">
         <f>SUM(B53,B56,B59,B62,B65,B68,B71,B74,B77,B80,B83,B86)</f>
-        <v>386</v>
+        <v>6</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>34</v>
@@ -2197,19 +2191,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="25"/>
       <c r="H1" s="25"/>
       <c r="I1" s="25"/>
-      <c r="K1" s="30" t="s">
+      <c r="K1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="25"/>
@@ -2217,19 +2211,19 @@
       <c r="N1" s="25"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
-      <c r="F2" s="30" t="s">
+      <c r="F2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
       <c r="I2" s="25"/>
-      <c r="K2" s="30" t="s">
+      <c r="K2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="25"/>
@@ -2251,27 +2245,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="29" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="25"/>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="25"/>
-      <c r="H4" s="28" t="s">
+      <c r="H4" s="29" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="25"/>
-      <c r="K4" s="28" t="s">
+      <c r="K4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="25"/>
-      <c r="M4" s="28" t="s">
+      <c r="M4" s="29" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="25"/>
@@ -2280,7 +2274,7 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="28">
         <v>352</v>
       </c>
       <c r="C5" s="25"/>
@@ -2288,13 +2282,13 @@
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="27"/>
+      <c r="G5" s="28"/>
       <c r="H5" s="25"/>
       <c r="I5" s="25"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="27"/>
+      <c r="L5" s="28"/>
       <c r="M5" s="25"/>
       <c r="N5" s="25"/>
     </row>
@@ -2302,7 +2296,7 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="27">
         <v>376</v>
       </c>
       <c r="C6" s="25"/>
@@ -2310,13 +2304,13 @@
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="26"/>
+      <c r="G6" s="27"/>
       <c r="H6" s="25"/>
       <c r="I6" s="25"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="26"/>
+      <c r="L6" s="27"/>
       <c r="M6" s="25"/>
       <c r="N6" s="25"/>
     </row>
@@ -2324,7 +2318,7 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="28">
         <v>0</v>
       </c>
       <c r="C7" s="25"/>
@@ -2332,13 +2326,13 @@
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="27"/>
+      <c r="G7" s="28"/>
       <c r="H7" s="25"/>
       <c r="I7" s="25"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="27"/>
+      <c r="L7" s="28"/>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
     </row>
@@ -2346,7 +2340,7 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="27">
         <v>724</v>
       </c>
       <c r="C8" s="25"/>
@@ -2354,13 +2348,13 @@
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="26"/>
+      <c r="G8" s="27"/>
       <c r="H8" s="25"/>
       <c r="I8" s="25"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="26"/>
+      <c r="L8" s="27"/>
       <c r="M8" s="25"/>
       <c r="N8" s="25"/>
     </row>
@@ -2368,7 +2362,7 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="27">
+      <c r="B9" s="28">
         <v>411</v>
       </c>
       <c r="C9" s="25"/>
@@ -2376,13 +2370,13 @@
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="27"/>
+      <c r="G9" s="28"/>
       <c r="H9" s="25"/>
       <c r="I9" s="25"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="27"/>
+      <c r="L9" s="28"/>
       <c r="M9" s="25"/>
       <c r="N9" s="25"/>
     </row>
@@ -2390,7 +2384,7 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="27">
         <v>0</v>
       </c>
       <c r="C10" s="25"/>
@@ -2398,13 +2392,13 @@
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="26"/>
+      <c r="G10" s="27"/>
       <c r="H10" s="25"/>
       <c r="I10" s="25"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="26"/>
+      <c r="L10" s="27"/>
       <c r="M10" s="25"/>
       <c r="N10" s="25"/>
     </row>
@@ -2412,7 +2406,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="30">
         <f>SUM(B5:B10)</f>
         <v>1863</v>
       </c>
@@ -2421,7 +2415,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="29">
+      <c r="G11" s="30">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -2430,7 +2424,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="29">
+      <c r="L11" s="30">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -2466,19 +2460,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
-      <c r="F25" s="30" t="s">
+      <c r="F25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
       <c r="I25" s="25"/>
-      <c r="K25" s="30" t="s">
+      <c r="K25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="25"/>
@@ -2486,19 +2480,19 @@
       <c r="N25" s="25"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
-      <c r="F26" s="30" t="s">
+      <c r="F26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="25"/>
       <c r="H26" s="25"/>
       <c r="I26" s="25"/>
-      <c r="K26" s="30" t="s">
+      <c r="K26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="25"/>
@@ -2520,27 +2514,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="25"/>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="29" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="25"/>
-      <c r="F28" s="28" t="s">
+      <c r="F28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="25"/>
-      <c r="H28" s="28" t="s">
+      <c r="H28" s="29" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="25"/>
-      <c r="K28" s="28" t="s">
+      <c r="K28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="25"/>
-      <c r="M28" s="28" t="s">
+      <c r="M28" s="29" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="25"/>
@@ -2549,7 +2543,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="27">
+      <c r="B29" s="28">
         <v>0</v>
       </c>
       <c r="C29" s="25"/>
@@ -2557,13 +2551,13 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="27"/>
+      <c r="G29" s="28"/>
       <c r="H29" s="25"/>
       <c r="I29" s="25"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="27">
+      <c r="L29" s="28">
         <v>14</v>
       </c>
       <c r="M29" s="25"/>
@@ -2573,7 +2567,7 @@
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="26">
+      <c r="B30" s="27">
         <v>0</v>
       </c>
       <c r="C30" s="25"/>
@@ -2581,13 +2575,13 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="26"/>
+      <c r="G30" s="27"/>
       <c r="H30" s="25"/>
       <c r="I30" s="25"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="26">
+      <c r="L30" s="27">
         <v>605</v>
       </c>
       <c r="M30" s="25"/>
@@ -2597,7 +2591,7 @@
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="27">
+      <c r="B31" s="28">
         <v>0</v>
       </c>
       <c r="C31" s="25"/>
@@ -2605,13 +2599,13 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="27"/>
+      <c r="G31" s="28"/>
       <c r="H31" s="25"/>
       <c r="I31" s="25"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="27">
+      <c r="L31" s="28">
         <v>1708</v>
       </c>
       <c r="M31" s="25"/>
@@ -2621,7 +2615,7 @@
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="26">
+      <c r="B32" s="27">
         <v>0</v>
       </c>
       <c r="C32" s="25"/>
@@ -2629,13 +2623,13 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="26"/>
+      <c r="G32" s="27"/>
       <c r="H32" s="25"/>
       <c r="I32" s="25"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="26">
+      <c r="L32" s="27">
         <v>1395</v>
       </c>
       <c r="M32" s="25"/>
@@ -2645,7 +2639,7 @@
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="27">
+      <c r="B33" s="28">
         <v>0</v>
       </c>
       <c r="C33" s="25"/>
@@ -2653,13 +2647,13 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="27"/>
+      <c r="G33" s="28"/>
       <c r="H33" s="25"/>
       <c r="I33" s="25"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="27">
+      <c r="L33" s="28">
         <v>0</v>
       </c>
       <c r="M33" s="25"/>
@@ -2669,7 +2663,7 @@
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="26">
+      <c r="B34" s="27">
         <v>0</v>
       </c>
       <c r="C34" s="25"/>
@@ -2677,13 +2671,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="26"/>
+      <c r="G34" s="27"/>
       <c r="H34" s="25"/>
       <c r="I34" s="25"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="26">
+      <c r="L34" s="27">
         <v>0</v>
       </c>
       <c r="M34" s="25"/>
@@ -2693,7 +2687,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="29">
+      <c r="B35" s="30">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -2702,7 +2696,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="29">
+      <c r="G35" s="30">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -2711,7 +2705,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="29">
+      <c r="L35" s="30">
         <f>SUM(L29:L34)</f>
         <v>3722</v>
       </c>
@@ -2748,13 +2742,49 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="L11:N11"/>
@@ -2771,49 +2801,13 @@
     <mergeCell ref="K2:N2"/>
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2829,7 +2823,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
@@ -2837,7 +2831,7 @@
       <c r="D1" s="25"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
@@ -2851,11 +2845,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="29" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="29" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="25"/>
@@ -2864,7 +2858,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="27"/>
+      <c r="B5" s="28"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
     </row>
@@ -2872,7 +2866,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="26"/>
+      <c r="B6" s="27"/>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
     </row>
@@ -2880,7 +2874,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="27"/>
+      <c r="B7" s="28"/>
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
     </row>
@@ -2888,7 +2882,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="26"/>
+      <c r="B8" s="27"/>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
     </row>
@@ -2896,7 +2890,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="30">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -2945,19 +2939,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="25"/>
       <c r="H1" s="25"/>
       <c r="I1" s="25"/>
-      <c r="K1" s="30" t="s">
+      <c r="K1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="25"/>
@@ -2965,19 +2959,19 @@
       <c r="N1" s="25"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
-      <c r="F2" s="30" t="s">
+      <c r="F2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
       <c r="I2" s="25"/>
-      <c r="K2" s="30" t="s">
+      <c r="K2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="25"/>
@@ -2999,27 +2993,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="29" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="25"/>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="25"/>
-      <c r="H4" s="28" t="s">
+      <c r="H4" s="29" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="25"/>
-      <c r="K4" s="28" t="s">
+      <c r="K4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="25"/>
-      <c r="M4" s="28" t="s">
+      <c r="M4" s="29" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="25"/>
@@ -3028,19 +3022,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="27"/>
+      <c r="B5" s="28"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="27"/>
+      <c r="G5" s="28"/>
       <c r="H5" s="25"/>
       <c r="I5" s="25"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="27"/>
+      <c r="L5" s="28"/>
       <c r="M5" s="25"/>
       <c r="N5" s="25"/>
     </row>
@@ -3048,19 +3042,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="26"/>
+      <c r="B6" s="27"/>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="26"/>
+      <c r="G6" s="27"/>
       <c r="H6" s="25"/>
       <c r="I6" s="25"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="26"/>
+      <c r="L6" s="27"/>
       <c r="M6" s="25"/>
       <c r="N6" s="25"/>
     </row>
@@ -3068,19 +3062,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="27"/>
+      <c r="B7" s="28"/>
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="27"/>
+      <c r="G7" s="28"/>
       <c r="H7" s="25"/>
       <c r="I7" s="25"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="27"/>
+      <c r="L7" s="28"/>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
     </row>
@@ -3088,19 +3082,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="26"/>
+      <c r="B8" s="27"/>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="26"/>
+      <c r="G8" s="27"/>
       <c r="H8" s="25"/>
       <c r="I8" s="25"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="26"/>
+      <c r="L8" s="27"/>
       <c r="M8" s="25"/>
       <c r="N8" s="25"/>
     </row>
@@ -3108,19 +3102,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="27"/>
+      <c r="B9" s="28"/>
       <c r="C9" s="25"/>
       <c r="D9" s="25"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="27"/>
+      <c r="G9" s="28"/>
       <c r="H9" s="25"/>
       <c r="I9" s="25"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="27"/>
+      <c r="L9" s="28"/>
       <c r="M9" s="25"/>
       <c r="N9" s="25"/>
     </row>
@@ -3128,19 +3122,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="26"/>
+      <c r="B10" s="27"/>
       <c r="C10" s="25"/>
       <c r="D10" s="25"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="26"/>
+      <c r="G10" s="27"/>
       <c r="H10" s="25"/>
       <c r="I10" s="25"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="26"/>
+      <c r="L10" s="27"/>
       <c r="M10" s="25"/>
       <c r="N10" s="25"/>
     </row>
@@ -3148,19 +3142,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="27"/>
+      <c r="B11" s="28"/>
       <c r="C11" s="25"/>
       <c r="D11" s="25"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="27"/>
+      <c r="G11" s="28"/>
       <c r="H11" s="25"/>
       <c r="I11" s="25"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="27"/>
+      <c r="L11" s="28"/>
       <c r="M11" s="25"/>
       <c r="N11" s="25"/>
     </row>
@@ -3168,19 +3162,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="26"/>
+      <c r="B12" s="27"/>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="26"/>
+      <c r="G12" s="27"/>
       <c r="H12" s="25"/>
       <c r="I12" s="25"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="26"/>
+      <c r="L12" s="27"/>
       <c r="M12" s="25"/>
       <c r="N12" s="25"/>
     </row>
@@ -3188,7 +3182,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="30">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3197,7 +3191,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="29">
+      <c r="G13" s="30">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3206,7 +3200,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="29">
+      <c r="L13" s="30">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3242,19 +3236,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
-      <c r="F25" s="30" t="s">
+      <c r="F25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
       <c r="I25" s="25"/>
-      <c r="K25" s="30" t="s">
+      <c r="K25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="25"/>
@@ -3262,19 +3256,19 @@
       <c r="N25" s="25"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
-      <c r="F26" s="30" t="s">
+      <c r="F26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="25"/>
       <c r="H26" s="25"/>
       <c r="I26" s="25"/>
-      <c r="K26" s="30" t="s">
+      <c r="K26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="25"/>
@@ -3296,27 +3290,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="25"/>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="29" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="25"/>
-      <c r="F28" s="28" t="s">
+      <c r="F28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="25"/>
-      <c r="H28" s="28" t="s">
+      <c r="H28" s="29" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="25"/>
-      <c r="K28" s="28" t="s">
+      <c r="K28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="25"/>
-      <c r="M28" s="28" t="s">
+      <c r="M28" s="29" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="25"/>
@@ -3325,19 +3319,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="27"/>
+      <c r="B29" s="28"/>
       <c r="C29" s="25"/>
       <c r="D29" s="25"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="27"/>
+      <c r="G29" s="28"/>
       <c r="H29" s="25"/>
       <c r="I29" s="25"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="27"/>
+      <c r="L29" s="28"/>
       <c r="M29" s="25"/>
       <c r="N29" s="25"/>
     </row>
@@ -3345,19 +3339,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="26"/>
+      <c r="B30" s="27"/>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="26"/>
+      <c r="G30" s="27"/>
       <c r="H30" s="25"/>
       <c r="I30" s="25"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="26"/>
+      <c r="L30" s="27"/>
       <c r="M30" s="25"/>
       <c r="N30" s="25"/>
     </row>
@@ -3365,19 +3359,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="27"/>
+      <c r="B31" s="28"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="27"/>
+      <c r="G31" s="28"/>
       <c r="H31" s="25"/>
       <c r="I31" s="25"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="27"/>
+      <c r="L31" s="28"/>
       <c r="M31" s="25"/>
       <c r="N31" s="25"/>
     </row>
@@ -3385,19 +3379,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="26"/>
+      <c r="B32" s="27"/>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="26"/>
+      <c r="G32" s="27"/>
       <c r="H32" s="25"/>
       <c r="I32" s="25"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="26"/>
+      <c r="L32" s="27"/>
       <c r="M32" s="25"/>
       <c r="N32" s="25"/>
     </row>
@@ -3405,19 +3399,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="27"/>
+      <c r="B33" s="28"/>
       <c r="C33" s="25"/>
       <c r="D33" s="25"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="27"/>
+      <c r="G33" s="28"/>
       <c r="H33" s="25"/>
       <c r="I33" s="25"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="27"/>
+      <c r="L33" s="28"/>
       <c r="M33" s="25"/>
       <c r="N33" s="25"/>
     </row>
@@ -3425,19 +3419,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="26"/>
+      <c r="B34" s="27"/>
       <c r="C34" s="25"/>
       <c r="D34" s="25"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="26"/>
+      <c r="G34" s="27"/>
       <c r="H34" s="25"/>
       <c r="I34" s="25"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="26"/>
+      <c r="L34" s="27"/>
       <c r="M34" s="25"/>
       <c r="N34" s="25"/>
     </row>
@@ -3445,19 +3439,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="27"/>
+      <c r="B35" s="28"/>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="27"/>
+      <c r="G35" s="28"/>
       <c r="H35" s="25"/>
       <c r="I35" s="25"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="27"/>
+      <c r="L35" s="28"/>
       <c r="M35" s="25"/>
       <c r="N35" s="25"/>
     </row>
@@ -3465,19 +3459,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="26"/>
+      <c r="B36" s="27"/>
       <c r="C36" s="25"/>
       <c r="D36" s="25"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="26"/>
+      <c r="G36" s="27"/>
       <c r="H36" s="25"/>
       <c r="I36" s="25"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="26"/>
+      <c r="L36" s="27"/>
       <c r="M36" s="25"/>
       <c r="N36" s="25"/>
     </row>
@@ -3485,7 +3479,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="29">
+      <c r="B37" s="30">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -3494,7 +3488,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="29">
+      <c r="G37" s="30">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -3503,7 +3497,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="29">
+      <c r="L37" s="30">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -3540,6 +3534,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
     <mergeCell ref="L34:N34"/>
     <mergeCell ref="L6:N6"/>
     <mergeCell ref="B33:D33"/>
@@ -3556,68 +3612,6 @@
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F61A9F-8E2D-46CE-9A2F-E5BFBA3D43ED}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{950121FF-97F3-440D-94C7-EF17BBE9EA92}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -427,9 +427,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -440,6 +437,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -767,7 +767,7 @@
       </c>
       <c r="B5" s="21">
         <f>SUM(B6:B7)</f>
-        <v>0</v>
+        <v>4600</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>20</v>
@@ -781,37 +781,41 @@
       </c>
       <c r="L5" s="14">
         <f>SUM(L6:L7)</f>
-        <v>500</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
       <c r="A6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="14"/>
+      <c r="B6" s="14">
+        <v>3900</v>
+      </c>
       <c r="F6" s="7" t="s">
         <v>21</v>
       </c>
       <c r="G6" s="14">
-        <v>1100</v>
+        <v>800</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>21</v>
       </c>
       <c r="L6" s="14">
-        <v>500</v>
+        <v>2900</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="14"/>
+      <c r="B7" s="14">
+        <v>700</v>
+      </c>
       <c r="F7" s="7" t="s">
         <v>22</v>
       </c>
       <c r="G7" s="14">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="K7" s="7" t="s">
         <v>22</v>
@@ -831,14 +835,14 @@
       </c>
       <c r="G8" s="15">
         <f>SUM(G9:G10)</f>
-        <v>600</v>
+        <v>360</v>
       </c>
       <c r="K8" s="9" t="s">
         <v>23</v>
       </c>
       <c r="L8" s="15">
         <f>SUM(L9:L10)</f>
-        <v>350</v>
+        <v>780</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1">
@@ -850,13 +854,13 @@
         <v>21</v>
       </c>
       <c r="G9" s="15">
-        <v>600</v>
+        <v>360</v>
       </c>
       <c r="K9" s="9" t="s">
         <v>21</v>
       </c>
       <c r="L9" s="15">
-        <v>350</v>
+        <v>780</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
@@ -930,7 +934,7 @@
       </c>
       <c r="B14" s="15">
         <f>SUM(B15:B16)</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>25</v>
@@ -944,14 +948,16 @@
       </c>
       <c r="L14" s="15">
         <f>SUM(L15:L16)</f>
-        <v>300</v>
+        <v>190</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1">
       <c r="A15" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="15"/>
+      <c r="B15" s="15">
+        <v>300</v>
+      </c>
       <c r="F15" s="9" t="s">
         <v>21</v>
       </c>
@@ -960,7 +966,7 @@
         <v>21</v>
       </c>
       <c r="L15" s="15">
-        <v>300</v>
+        <v>190</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1">
@@ -1189,21 +1195,21 @@
       </c>
       <c r="B29" s="14">
         <f>SUM(B30:B31)</f>
-        <v>800</v>
+        <v>70</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>30</v>
       </c>
       <c r="G29" s="14">
         <f>SUM(G30:G31)</f>
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="K29" s="7" t="s">
         <v>30</v>
       </c>
       <c r="L29" s="14">
         <f>SUM(L30:L31)</f>
-        <v>540</v>
+        <v>160</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1">
@@ -1211,19 +1217,19 @@
         <v>21</v>
       </c>
       <c r="B30" s="14">
-        <v>800</v>
+        <v>70</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>21</v>
       </c>
       <c r="G30" s="14">
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="K30" s="7" t="s">
         <v>21</v>
       </c>
       <c r="L30" s="14">
-        <v>540</v>
+        <v>160</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1">
@@ -1246,37 +1252,41 @@
       </c>
       <c r="B32" s="15">
         <f>SUM(B33:B34)</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>31</v>
       </c>
       <c r="G32" s="15">
         <f>SUM(G33:G34)</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="K32" s="9" t="s">
         <v>31</v>
       </c>
       <c r="L32" s="15">
         <f>SUM(L33:L34)</f>
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="15"/>
+      <c r="B33" s="15">
+        <v>300</v>
+      </c>
       <c r="F33" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G33" s="15"/>
+      <c r="G33" s="15">
+        <v>14</v>
+      </c>
       <c r="K33" s="9" t="s">
         <v>21</v>
       </c>
       <c r="L33" s="15">
-        <v>400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
@@ -1401,21 +1411,21 @@
       </c>
       <c r="B41" s="13">
         <f>SUM(B5,B8,B11,B14,B17,B20,B23,B26,B29,B32,B35,B38)</f>
-        <v>970</v>
+        <v>5440</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G41" s="13">
         <f>SUM(G5,G8,G11,G14,G17,G20,G23,G26,G29,G32,G35,G38)</f>
-        <v>2150</v>
+        <v>1968</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="L41" s="13">
         <f>SUM(L5,L8,L11,L14,L17,L20,L23,L26,L29,L32,L35,L38)</f>
-        <v>2090</v>
+        <v>4530</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1">
@@ -1664,7 +1674,7 @@
       </c>
       <c r="B62" s="15">
         <f>SUM(B63:B64)</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>25</v>
@@ -1686,7 +1696,7 @@
         <v>21</v>
       </c>
       <c r="B63" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>21</v>
@@ -1923,7 +1933,7 @@
       </c>
       <c r="B77" s="14">
         <f>SUM(B78:B79)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F77" s="7" t="s">
         <v>30</v>
@@ -1944,7 +1954,9 @@
       <c r="A78" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B78" s="14"/>
+      <c r="B78" s="14">
+        <v>5</v>
+      </c>
       <c r="F78" s="7" t="s">
         <v>21</v>
       </c>
@@ -2076,7 +2088,7 @@
       </c>
       <c r="B86" s="15">
         <f>SUM(B87:B88)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F86" s="9" t="s">
         <v>72</v>
@@ -2097,7 +2109,9 @@
       <c r="A87" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B87" s="15"/>
+      <c r="B87" s="15">
+        <v>5</v>
+      </c>
       <c r="F87" s="9" t="s">
         <v>21</v>
       </c>
@@ -2127,7 +2141,7 @@
       </c>
       <c r="B89" s="13">
         <f>SUM(B53,B56,B59,B62,B65,B68,B71,B74,B77,B80,B83,B86)</f>
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>34</v>
@@ -2191,19 +2205,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="25"/>
       <c r="H1" s="25"/>
       <c r="I1" s="25"/>
-      <c r="K1" s="26" t="s">
+      <c r="K1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="25"/>
@@ -2211,19 +2225,19 @@
       <c r="N1" s="25"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
       <c r="I2" s="25"/>
-      <c r="K2" s="26" t="s">
+      <c r="K2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="25"/>
@@ -2245,27 +2259,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="28" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="25"/>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="25"/>
-      <c r="H4" s="29" t="s">
+      <c r="H4" s="28" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="25"/>
-      <c r="K4" s="29" t="s">
+      <c r="K4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="25"/>
-      <c r="M4" s="29" t="s">
+      <c r="M4" s="28" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="25"/>
@@ -2274,7 +2288,7 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="28">
+      <c r="B5" s="27">
         <v>352</v>
       </c>
       <c r="C5" s="25"/>
@@ -2282,13 +2296,13 @@
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="28"/>
+      <c r="G5" s="27"/>
       <c r="H5" s="25"/>
       <c r="I5" s="25"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="28"/>
+      <c r="L5" s="27"/>
       <c r="M5" s="25"/>
       <c r="N5" s="25"/>
     </row>
@@ -2296,7 +2310,7 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="26">
         <v>376</v>
       </c>
       <c r="C6" s="25"/>
@@ -2304,13 +2318,13 @@
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="27"/>
+      <c r="G6" s="26"/>
       <c r="H6" s="25"/>
       <c r="I6" s="25"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="27"/>
+      <c r="L6" s="26"/>
       <c r="M6" s="25"/>
       <c r="N6" s="25"/>
     </row>
@@ -2318,7 +2332,7 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="27">
         <v>0</v>
       </c>
       <c r="C7" s="25"/>
@@ -2326,13 +2340,13 @@
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="28"/>
+      <c r="G7" s="27"/>
       <c r="H7" s="25"/>
       <c r="I7" s="25"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="28"/>
+      <c r="L7" s="27"/>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
     </row>
@@ -2340,7 +2354,7 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="26">
         <v>724</v>
       </c>
       <c r="C8" s="25"/>
@@ -2348,13 +2362,13 @@
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="27"/>
+      <c r="G8" s="26"/>
       <c r="H8" s="25"/>
       <c r="I8" s="25"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="27"/>
+      <c r="L8" s="26"/>
       <c r="M8" s="25"/>
       <c r="N8" s="25"/>
     </row>
@@ -2362,7 +2376,7 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="28">
+      <c r="B9" s="27">
         <v>411</v>
       </c>
       <c r="C9" s="25"/>
@@ -2370,13 +2384,13 @@
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="28"/>
+      <c r="G9" s="27"/>
       <c r="H9" s="25"/>
       <c r="I9" s="25"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="28"/>
+      <c r="L9" s="27"/>
       <c r="M9" s="25"/>
       <c r="N9" s="25"/>
     </row>
@@ -2384,7 +2398,7 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="27">
+      <c r="B10" s="26">
         <v>0</v>
       </c>
       <c r="C10" s="25"/>
@@ -2392,13 +2406,13 @@
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="27"/>
+      <c r="G10" s="26"/>
       <c r="H10" s="25"/>
       <c r="I10" s="25"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="27"/>
+      <c r="L10" s="26"/>
       <c r="M10" s="25"/>
       <c r="N10" s="25"/>
     </row>
@@ -2406,7 +2420,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="29">
         <f>SUM(B5:B10)</f>
         <v>1863</v>
       </c>
@@ -2415,7 +2429,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="30">
+      <c r="G11" s="29">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -2424,7 +2438,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="30">
+      <c r="L11" s="29">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -2460,19 +2474,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
-      <c r="F25" s="26" t="s">
+      <c r="F25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
       <c r="I25" s="25"/>
-      <c r="K25" s="26" t="s">
+      <c r="K25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="25"/>
@@ -2480,19 +2494,19 @@
       <c r="N25" s="25"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
-      <c r="F26" s="26" t="s">
+      <c r="F26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="25"/>
       <c r="H26" s="25"/>
       <c r="I26" s="25"/>
-      <c r="K26" s="26" t="s">
+      <c r="K26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="25"/>
@@ -2514,27 +2528,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="25"/>
-      <c r="C28" s="29" t="s">
+      <c r="C28" s="28" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="25"/>
-      <c r="F28" s="29" t="s">
+      <c r="F28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="25"/>
-      <c r="H28" s="29" t="s">
+      <c r="H28" s="28" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="25"/>
-      <c r="K28" s="29" t="s">
+      <c r="K28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="25"/>
-      <c r="M28" s="29" t="s">
+      <c r="M28" s="28" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="25"/>
@@ -2543,7 +2557,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="28">
+      <c r="B29" s="27">
         <v>0</v>
       </c>
       <c r="C29" s="25"/>
@@ -2551,13 +2565,13 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="28"/>
+      <c r="G29" s="27"/>
       <c r="H29" s="25"/>
       <c r="I29" s="25"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="28">
+      <c r="L29" s="27">
         <v>14</v>
       </c>
       <c r="M29" s="25"/>
@@ -2567,7 +2581,7 @@
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="27">
+      <c r="B30" s="26">
         <v>0</v>
       </c>
       <c r="C30" s="25"/>
@@ -2575,13 +2589,13 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="27"/>
+      <c r="G30" s="26"/>
       <c r="H30" s="25"/>
       <c r="I30" s="25"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="27">
+      <c r="L30" s="26">
         <v>605</v>
       </c>
       <c r="M30" s="25"/>
@@ -2591,7 +2605,7 @@
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="28">
+      <c r="B31" s="27">
         <v>0</v>
       </c>
       <c r="C31" s="25"/>
@@ -2599,13 +2613,13 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="28"/>
+      <c r="G31" s="27"/>
       <c r="H31" s="25"/>
       <c r="I31" s="25"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="28">
+      <c r="L31" s="27">
         <v>1708</v>
       </c>
       <c r="M31" s="25"/>
@@ -2615,7 +2629,7 @@
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="27">
+      <c r="B32" s="26">
         <v>0</v>
       </c>
       <c r="C32" s="25"/>
@@ -2623,13 +2637,13 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="27"/>
+      <c r="G32" s="26"/>
       <c r="H32" s="25"/>
       <c r="I32" s="25"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="27">
+      <c r="L32" s="26">
         <v>1395</v>
       </c>
       <c r="M32" s="25"/>
@@ -2639,7 +2653,7 @@
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="28">
+      <c r="B33" s="27">
         <v>0</v>
       </c>
       <c r="C33" s="25"/>
@@ -2647,13 +2661,13 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="28"/>
+      <c r="G33" s="27"/>
       <c r="H33" s="25"/>
       <c r="I33" s="25"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="28">
+      <c r="L33" s="27">
         <v>0</v>
       </c>
       <c r="M33" s="25"/>
@@ -2663,7 +2677,7 @@
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="27">
+      <c r="B34" s="26">
         <v>0</v>
       </c>
       <c r="C34" s="25"/>
@@ -2671,13 +2685,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="27"/>
+      <c r="G34" s="26"/>
       <c r="H34" s="25"/>
       <c r="I34" s="25"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="27">
+      <c r="L34" s="26">
         <v>0</v>
       </c>
       <c r="M34" s="25"/>
@@ -2687,7 +2701,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="30">
+      <c r="B35" s="29">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -2696,7 +2710,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="30">
+      <c r="G35" s="29">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -2705,7 +2719,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="30">
+      <c r="L35" s="29">
         <f>SUM(L29:L34)</f>
         <v>3722</v>
       </c>
@@ -2742,6 +2756,56 @@
     </row>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B10:D10"/>
@@ -2758,56 +2822,6 @@
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="H28:I28"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2823,7 +2837,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
@@ -2831,7 +2845,7 @@
       <c r="D1" s="25"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
@@ -2845,11 +2859,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="28" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="28" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="25"/>
@@ -2858,7 +2872,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="28"/>
+      <c r="B5" s="27"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
     </row>
@@ -2866,7 +2880,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="27"/>
+      <c r="B6" s="26"/>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
     </row>
@@ -2874,7 +2888,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="28"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
     </row>
@@ -2882,7 +2896,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="27"/>
+      <c r="B8" s="26"/>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
     </row>
@@ -2890,7 +2904,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="29">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -2939,19 +2953,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="25"/>
       <c r="H1" s="25"/>
       <c r="I1" s="25"/>
-      <c r="K1" s="26" t="s">
+      <c r="K1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="25"/>
@@ -2959,19 +2973,19 @@
       <c r="N1" s="25"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
       <c r="I2" s="25"/>
-      <c r="K2" s="26" t="s">
+      <c r="K2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="25"/>
@@ -2993,27 +3007,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="28" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="25"/>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="25"/>
-      <c r="H4" s="29" t="s">
+      <c r="H4" s="28" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="25"/>
-      <c r="K4" s="29" t="s">
+      <c r="K4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="25"/>
-      <c r="M4" s="29" t="s">
+      <c r="M4" s="28" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="25"/>
@@ -3022,19 +3036,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="28"/>
+      <c r="B5" s="27"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="28"/>
+      <c r="G5" s="27"/>
       <c r="H5" s="25"/>
       <c r="I5" s="25"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="28"/>
+      <c r="L5" s="27"/>
       <c r="M5" s="25"/>
       <c r="N5" s="25"/>
     </row>
@@ -3042,19 +3056,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="27"/>
+      <c r="B6" s="26"/>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="27"/>
+      <c r="G6" s="26"/>
       <c r="H6" s="25"/>
       <c r="I6" s="25"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="27"/>
+      <c r="L6" s="26"/>
       <c r="M6" s="25"/>
       <c r="N6" s="25"/>
     </row>
@@ -3062,19 +3076,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="28"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="28"/>
+      <c r="G7" s="27"/>
       <c r="H7" s="25"/>
       <c r="I7" s="25"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="28"/>
+      <c r="L7" s="27"/>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
     </row>
@@ -3082,19 +3096,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="27"/>
+      <c r="B8" s="26"/>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="27"/>
+      <c r="G8" s="26"/>
       <c r="H8" s="25"/>
       <c r="I8" s="25"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="27"/>
+      <c r="L8" s="26"/>
       <c r="M8" s="25"/>
       <c r="N8" s="25"/>
     </row>
@@ -3102,19 +3116,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="28"/>
+      <c r="B9" s="27"/>
       <c r="C9" s="25"/>
       <c r="D9" s="25"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="28"/>
+      <c r="G9" s="27"/>
       <c r="H9" s="25"/>
       <c r="I9" s="25"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="28"/>
+      <c r="L9" s="27"/>
       <c r="M9" s="25"/>
       <c r="N9" s="25"/>
     </row>
@@ -3122,19 +3136,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="27"/>
+      <c r="B10" s="26"/>
       <c r="C10" s="25"/>
       <c r="D10" s="25"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="27"/>
+      <c r="G10" s="26"/>
       <c r="H10" s="25"/>
       <c r="I10" s="25"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="27"/>
+      <c r="L10" s="26"/>
       <c r="M10" s="25"/>
       <c r="N10" s="25"/>
     </row>
@@ -3142,19 +3156,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="28"/>
+      <c r="B11" s="27"/>
       <c r="C11" s="25"/>
       <c r="D11" s="25"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="28"/>
+      <c r="G11" s="27"/>
       <c r="H11" s="25"/>
       <c r="I11" s="25"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="28"/>
+      <c r="L11" s="27"/>
       <c r="M11" s="25"/>
       <c r="N11" s="25"/>
     </row>
@@ -3162,19 +3176,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="27"/>
+      <c r="B12" s="26"/>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="27"/>
+      <c r="G12" s="26"/>
       <c r="H12" s="25"/>
       <c r="I12" s="25"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="27"/>
+      <c r="L12" s="26"/>
       <c r="M12" s="25"/>
       <c r="N12" s="25"/>
     </row>
@@ -3182,7 +3196,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="29">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3191,7 +3205,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="30">
+      <c r="G13" s="29">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3200,7 +3214,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="30">
+      <c r="L13" s="29">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3236,19 +3250,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
-      <c r="F25" s="26" t="s">
+      <c r="F25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
       <c r="I25" s="25"/>
-      <c r="K25" s="26" t="s">
+      <c r="K25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="25"/>
@@ -3256,19 +3270,19 @@
       <c r="N25" s="25"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
-      <c r="F26" s="26" t="s">
+      <c r="F26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="25"/>
       <c r="H26" s="25"/>
       <c r="I26" s="25"/>
-      <c r="K26" s="26" t="s">
+      <c r="K26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="25"/>
@@ -3290,27 +3304,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="25"/>
-      <c r="C28" s="29" t="s">
+      <c r="C28" s="28" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="25"/>
-      <c r="F28" s="29" t="s">
+      <c r="F28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="25"/>
-      <c r="H28" s="29" t="s">
+      <c r="H28" s="28" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="25"/>
-      <c r="K28" s="29" t="s">
+      <c r="K28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="25"/>
-      <c r="M28" s="29" t="s">
+      <c r="M28" s="28" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="25"/>
@@ -3319,19 +3333,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="28"/>
+      <c r="B29" s="27"/>
       <c r="C29" s="25"/>
       <c r="D29" s="25"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="28"/>
+      <c r="G29" s="27"/>
       <c r="H29" s="25"/>
       <c r="I29" s="25"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="28"/>
+      <c r="L29" s="27"/>
       <c r="M29" s="25"/>
       <c r="N29" s="25"/>
     </row>
@@ -3339,19 +3353,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="27"/>
+      <c r="B30" s="26"/>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="27"/>
+      <c r="G30" s="26"/>
       <c r="H30" s="25"/>
       <c r="I30" s="25"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="27"/>
+      <c r="L30" s="26"/>
       <c r="M30" s="25"/>
       <c r="N30" s="25"/>
     </row>
@@ -3359,19 +3373,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="28"/>
+      <c r="B31" s="27"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="28"/>
+      <c r="G31" s="27"/>
       <c r="H31" s="25"/>
       <c r="I31" s="25"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="28"/>
+      <c r="L31" s="27"/>
       <c r="M31" s="25"/>
       <c r="N31" s="25"/>
     </row>
@@ -3379,19 +3393,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="27"/>
+      <c r="B32" s="26"/>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="27"/>
+      <c r="G32" s="26"/>
       <c r="H32" s="25"/>
       <c r="I32" s="25"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="27"/>
+      <c r="L32" s="26"/>
       <c r="M32" s="25"/>
       <c r="N32" s="25"/>
     </row>
@@ -3399,19 +3413,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="28"/>
+      <c r="B33" s="27"/>
       <c r="C33" s="25"/>
       <c r="D33" s="25"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="28"/>
+      <c r="G33" s="27"/>
       <c r="H33" s="25"/>
       <c r="I33" s="25"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="28"/>
+      <c r="L33" s="27"/>
       <c r="M33" s="25"/>
       <c r="N33" s="25"/>
     </row>
@@ -3419,19 +3433,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="27"/>
+      <c r="B34" s="26"/>
       <c r="C34" s="25"/>
       <c r="D34" s="25"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="27"/>
+      <c r="G34" s="26"/>
       <c r="H34" s="25"/>
       <c r="I34" s="25"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="27"/>
+      <c r="L34" s="26"/>
       <c r="M34" s="25"/>
       <c r="N34" s="25"/>
     </row>
@@ -3439,19 +3453,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="28"/>
+      <c r="B35" s="27"/>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="28"/>
+      <c r="G35" s="27"/>
       <c r="H35" s="25"/>
       <c r="I35" s="25"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="28"/>
+      <c r="L35" s="27"/>
       <c r="M35" s="25"/>
       <c r="N35" s="25"/>
     </row>
@@ -3459,19 +3473,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="27"/>
+      <c r="B36" s="26"/>
       <c r="C36" s="25"/>
       <c r="D36" s="25"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="27"/>
+      <c r="G36" s="26"/>
       <c r="H36" s="25"/>
       <c r="I36" s="25"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="27"/>
+      <c r="L36" s="26"/>
       <c r="M36" s="25"/>
       <c r="N36" s="25"/>
     </row>
@@ -3479,7 +3493,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="30">
+      <c r="B37" s="29">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -3488,7 +3502,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="30">
+      <c r="G37" s="29">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -3497,7 +3511,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="30">
+      <c r="L37" s="29">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -3534,6 +3548,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
     <mergeCell ref="G36:I36"/>
     <mergeCell ref="L32:N32"/>
     <mergeCell ref="L13:N13"/>
@@ -3550,68 +3626,6 @@
     <mergeCell ref="L33:N33"/>
     <mergeCell ref="L35:N35"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="L9:N9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{950121FF-97F3-440D-94C7-EF17BBE9EA92}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35DA87A2-2316-441B-A5E1-C5A5C4AB2C73}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -427,6 +427,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -437,9 +440,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -781,7 +781,7 @@
       </c>
       <c r="L5" s="14">
         <f>SUM(L6:L7)</f>
-        <v>2900</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
@@ -801,7 +801,7 @@
         <v>21</v>
       </c>
       <c r="L6" s="14">
-        <v>2900</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
@@ -842,7 +842,7 @@
       </c>
       <c r="L8" s="15">
         <f>SUM(L9:L10)</f>
-        <v>780</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1">
@@ -860,7 +860,7 @@
         <v>21</v>
       </c>
       <c r="L9" s="15">
-        <v>780</v>
+        <v>500</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
@@ -1425,7 +1425,7 @@
       </c>
       <c r="L41" s="13">
         <f>SUM(L5,L8,L11,L14,L17,L20,L23,L26,L29,L32,L35,L38)</f>
-        <v>4530</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1">
@@ -2205,19 +2205,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="25"/>
       <c r="H1" s="25"/>
       <c r="I1" s="25"/>
-      <c r="K1" s="30" t="s">
+      <c r="K1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="25"/>
@@ -2225,19 +2225,19 @@
       <c r="N1" s="25"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
-      <c r="F2" s="30" t="s">
+      <c r="F2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
       <c r="I2" s="25"/>
-      <c r="K2" s="30" t="s">
+      <c r="K2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="25"/>
@@ -2259,27 +2259,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="29" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="25"/>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="25"/>
-      <c r="H4" s="28" t="s">
+      <c r="H4" s="29" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="25"/>
-      <c r="K4" s="28" t="s">
+      <c r="K4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="25"/>
-      <c r="M4" s="28" t="s">
+      <c r="M4" s="29" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="25"/>
@@ -2288,7 +2288,7 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="28">
         <v>352</v>
       </c>
       <c r="C5" s="25"/>
@@ -2296,13 +2296,13 @@
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="27"/>
+      <c r="G5" s="28"/>
       <c r="H5" s="25"/>
       <c r="I5" s="25"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="27"/>
+      <c r="L5" s="28"/>
       <c r="M5" s="25"/>
       <c r="N5" s="25"/>
     </row>
@@ -2310,7 +2310,7 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="27">
         <v>376</v>
       </c>
       <c r="C6" s="25"/>
@@ -2318,13 +2318,13 @@
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="26"/>
+      <c r="G6" s="27"/>
       <c r="H6" s="25"/>
       <c r="I6" s="25"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="26"/>
+      <c r="L6" s="27"/>
       <c r="M6" s="25"/>
       <c r="N6" s="25"/>
     </row>
@@ -2332,7 +2332,7 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="28">
         <v>0</v>
       </c>
       <c r="C7" s="25"/>
@@ -2340,13 +2340,13 @@
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="27"/>
+      <c r="G7" s="28"/>
       <c r="H7" s="25"/>
       <c r="I7" s="25"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="27"/>
+      <c r="L7" s="28"/>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
     </row>
@@ -2354,7 +2354,7 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="27">
         <v>724</v>
       </c>
       <c r="C8" s="25"/>
@@ -2362,13 +2362,13 @@
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="26"/>
+      <c r="G8" s="27"/>
       <c r="H8" s="25"/>
       <c r="I8" s="25"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="26"/>
+      <c r="L8" s="27"/>
       <c r="M8" s="25"/>
       <c r="N8" s="25"/>
     </row>
@@ -2376,7 +2376,7 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="27">
+      <c r="B9" s="28">
         <v>411</v>
       </c>
       <c r="C9" s="25"/>
@@ -2384,13 +2384,13 @@
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="27"/>
+      <c r="G9" s="28"/>
       <c r="H9" s="25"/>
       <c r="I9" s="25"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="27"/>
+      <c r="L9" s="28"/>
       <c r="M9" s="25"/>
       <c r="N9" s="25"/>
     </row>
@@ -2398,7 +2398,7 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="27">
         <v>0</v>
       </c>
       <c r="C10" s="25"/>
@@ -2406,13 +2406,13 @@
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="26"/>
+      <c r="G10" s="27"/>
       <c r="H10" s="25"/>
       <c r="I10" s="25"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="26"/>
+      <c r="L10" s="27"/>
       <c r="M10" s="25"/>
       <c r="N10" s="25"/>
     </row>
@@ -2420,7 +2420,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="30">
         <f>SUM(B5:B10)</f>
         <v>1863</v>
       </c>
@@ -2429,7 +2429,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="29">
+      <c r="G11" s="30">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -2438,7 +2438,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="29">
+      <c r="L11" s="30">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -2474,19 +2474,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
-      <c r="F25" s="30" t="s">
+      <c r="F25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
       <c r="I25" s="25"/>
-      <c r="K25" s="30" t="s">
+      <c r="K25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="25"/>
@@ -2494,19 +2494,19 @@
       <c r="N25" s="25"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
-      <c r="F26" s="30" t="s">
+      <c r="F26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="25"/>
       <c r="H26" s="25"/>
       <c r="I26" s="25"/>
-      <c r="K26" s="30" t="s">
+      <c r="K26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="25"/>
@@ -2528,27 +2528,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="25"/>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="29" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="25"/>
-      <c r="F28" s="28" t="s">
+      <c r="F28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="25"/>
-      <c r="H28" s="28" t="s">
+      <c r="H28" s="29" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="25"/>
-      <c r="K28" s="28" t="s">
+      <c r="K28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="25"/>
-      <c r="M28" s="28" t="s">
+      <c r="M28" s="29" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="25"/>
@@ -2557,7 +2557,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="27">
+      <c r="B29" s="28">
         <v>0</v>
       </c>
       <c r="C29" s="25"/>
@@ -2565,13 +2565,13 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="27"/>
+      <c r="G29" s="28"/>
       <c r="H29" s="25"/>
       <c r="I29" s="25"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="27">
+      <c r="L29" s="28">
         <v>14</v>
       </c>
       <c r="M29" s="25"/>
@@ -2581,7 +2581,7 @@
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="26">
+      <c r="B30" s="27">
         <v>0</v>
       </c>
       <c r="C30" s="25"/>
@@ -2589,13 +2589,13 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="26"/>
+      <c r="G30" s="27"/>
       <c r="H30" s="25"/>
       <c r="I30" s="25"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="26">
+      <c r="L30" s="27">
         <v>605</v>
       </c>
       <c r="M30" s="25"/>
@@ -2605,7 +2605,7 @@
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="27">
+      <c r="B31" s="28">
         <v>0</v>
       </c>
       <c r="C31" s="25"/>
@@ -2613,13 +2613,13 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="27"/>
+      <c r="G31" s="28"/>
       <c r="H31" s="25"/>
       <c r="I31" s="25"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="27">
+      <c r="L31" s="28">
         <v>1708</v>
       </c>
       <c r="M31" s="25"/>
@@ -2629,7 +2629,7 @@
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="26">
+      <c r="B32" s="27">
         <v>0</v>
       </c>
       <c r="C32" s="25"/>
@@ -2637,13 +2637,13 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="26"/>
+      <c r="G32" s="27"/>
       <c r="H32" s="25"/>
       <c r="I32" s="25"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="26">
+      <c r="L32" s="27">
         <v>1395</v>
       </c>
       <c r="M32" s="25"/>
@@ -2653,7 +2653,7 @@
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="27">
+      <c r="B33" s="28">
         <v>0</v>
       </c>
       <c r="C33" s="25"/>
@@ -2661,13 +2661,13 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="27"/>
+      <c r="G33" s="28"/>
       <c r="H33" s="25"/>
       <c r="I33" s="25"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="27">
+      <c r="L33" s="28">
         <v>0</v>
       </c>
       <c r="M33" s="25"/>
@@ -2677,7 +2677,7 @@
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="26">
+      <c r="B34" s="27">
         <v>0</v>
       </c>
       <c r="C34" s="25"/>
@@ -2685,13 +2685,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="26"/>
+      <c r="G34" s="27"/>
       <c r="H34" s="25"/>
       <c r="I34" s="25"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="26">
+      <c r="L34" s="27">
         <v>0</v>
       </c>
       <c r="M34" s="25"/>
@@ -2701,7 +2701,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="29">
+      <c r="B35" s="30">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -2710,7 +2710,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="29">
+      <c r="G35" s="30">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -2719,7 +2719,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="29">
+      <c r="L35" s="30">
         <f>SUM(L29:L34)</f>
         <v>3722</v>
       </c>
@@ -2756,13 +2756,49 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="L11:N11"/>
@@ -2779,49 +2815,13 @@
     <mergeCell ref="K2:N2"/>
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2837,7 +2837,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
@@ -2845,7 +2845,7 @@
       <c r="D1" s="25"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
@@ -2859,11 +2859,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="29" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="29" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="25"/>
@@ -2872,7 +2872,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="27"/>
+      <c r="B5" s="28"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
     </row>
@@ -2880,7 +2880,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="26"/>
+      <c r="B6" s="27"/>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
     </row>
@@ -2888,7 +2888,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="27"/>
+      <c r="B7" s="28"/>
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
     </row>
@@ -2896,7 +2896,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="26"/>
+      <c r="B8" s="27"/>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
     </row>
@@ -2904,7 +2904,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="30">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -2953,19 +2953,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="25"/>
       <c r="H1" s="25"/>
       <c r="I1" s="25"/>
-      <c r="K1" s="30" t="s">
+      <c r="K1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="25"/>
@@ -2973,19 +2973,19 @@
       <c r="N1" s="25"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
-      <c r="F2" s="30" t="s">
+      <c r="F2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
       <c r="I2" s="25"/>
-      <c r="K2" s="30" t="s">
+      <c r="K2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="25"/>
@@ -3007,27 +3007,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="29" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="25"/>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="25"/>
-      <c r="H4" s="28" t="s">
+      <c r="H4" s="29" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="25"/>
-      <c r="K4" s="28" t="s">
+      <c r="K4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="25"/>
-      <c r="M4" s="28" t="s">
+      <c r="M4" s="29" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="25"/>
@@ -3036,19 +3036,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="27"/>
+      <c r="B5" s="28"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="27"/>
+      <c r="G5" s="28"/>
       <c r="H5" s="25"/>
       <c r="I5" s="25"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="27"/>
+      <c r="L5" s="28"/>
       <c r="M5" s="25"/>
       <c r="N5" s="25"/>
     </row>
@@ -3056,19 +3056,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="26"/>
+      <c r="B6" s="27"/>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="26"/>
+      <c r="G6" s="27"/>
       <c r="H6" s="25"/>
       <c r="I6" s="25"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="26"/>
+      <c r="L6" s="27"/>
       <c r="M6" s="25"/>
       <c r="N6" s="25"/>
     </row>
@@ -3076,19 +3076,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="27"/>
+      <c r="B7" s="28"/>
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="27"/>
+      <c r="G7" s="28"/>
       <c r="H7" s="25"/>
       <c r="I7" s="25"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="27"/>
+      <c r="L7" s="28"/>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
     </row>
@@ -3096,19 +3096,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="26"/>
+      <c r="B8" s="27"/>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="26"/>
+      <c r="G8" s="27"/>
       <c r="H8" s="25"/>
       <c r="I8" s="25"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="26"/>
+      <c r="L8" s="27"/>
       <c r="M8" s="25"/>
       <c r="N8" s="25"/>
     </row>
@@ -3116,19 +3116,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="27"/>
+      <c r="B9" s="28"/>
       <c r="C9" s="25"/>
       <c r="D9" s="25"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="27"/>
+      <c r="G9" s="28"/>
       <c r="H9" s="25"/>
       <c r="I9" s="25"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="27"/>
+      <c r="L9" s="28"/>
       <c r="M9" s="25"/>
       <c r="N9" s="25"/>
     </row>
@@ -3136,19 +3136,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="26"/>
+      <c r="B10" s="27"/>
       <c r="C10" s="25"/>
       <c r="D10" s="25"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="26"/>
+      <c r="G10" s="27"/>
       <c r="H10" s="25"/>
       <c r="I10" s="25"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="26"/>
+      <c r="L10" s="27"/>
       <c r="M10" s="25"/>
       <c r="N10" s="25"/>
     </row>
@@ -3156,19 +3156,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="27"/>
+      <c r="B11" s="28"/>
       <c r="C11" s="25"/>
       <c r="D11" s="25"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="27"/>
+      <c r="G11" s="28"/>
       <c r="H11" s="25"/>
       <c r="I11" s="25"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="27"/>
+      <c r="L11" s="28"/>
       <c r="M11" s="25"/>
       <c r="N11" s="25"/>
     </row>
@@ -3176,19 +3176,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="26"/>
+      <c r="B12" s="27"/>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="26"/>
+      <c r="G12" s="27"/>
       <c r="H12" s="25"/>
       <c r="I12" s="25"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="26"/>
+      <c r="L12" s="27"/>
       <c r="M12" s="25"/>
       <c r="N12" s="25"/>
     </row>
@@ -3196,7 +3196,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="30">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3205,7 +3205,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="29">
+      <c r="G13" s="30">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3214,7 +3214,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="29">
+      <c r="L13" s="30">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3250,19 +3250,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
-      <c r="F25" s="30" t="s">
+      <c r="F25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
       <c r="I25" s="25"/>
-      <c r="K25" s="30" t="s">
+      <c r="K25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="25"/>
@@ -3270,19 +3270,19 @@
       <c r="N25" s="25"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
-      <c r="F26" s="30" t="s">
+      <c r="F26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="25"/>
       <c r="H26" s="25"/>
       <c r="I26" s="25"/>
-      <c r="K26" s="30" t="s">
+      <c r="K26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="25"/>
@@ -3304,27 +3304,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="25"/>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="29" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="25"/>
-      <c r="F28" s="28" t="s">
+      <c r="F28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="25"/>
-      <c r="H28" s="28" t="s">
+      <c r="H28" s="29" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="25"/>
-      <c r="K28" s="28" t="s">
+      <c r="K28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="25"/>
-      <c r="M28" s="28" t="s">
+      <c r="M28" s="29" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="25"/>
@@ -3333,19 +3333,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="27"/>
+      <c r="B29" s="28"/>
       <c r="C29" s="25"/>
       <c r="D29" s="25"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="27"/>
+      <c r="G29" s="28"/>
       <c r="H29" s="25"/>
       <c r="I29" s="25"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="27"/>
+      <c r="L29" s="28"/>
       <c r="M29" s="25"/>
       <c r="N29" s="25"/>
     </row>
@@ -3353,19 +3353,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="26"/>
+      <c r="B30" s="27"/>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="26"/>
+      <c r="G30" s="27"/>
       <c r="H30" s="25"/>
       <c r="I30" s="25"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="26"/>
+      <c r="L30" s="27"/>
       <c r="M30" s="25"/>
       <c r="N30" s="25"/>
     </row>
@@ -3373,19 +3373,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="27"/>
+      <c r="B31" s="28"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="27"/>
+      <c r="G31" s="28"/>
       <c r="H31" s="25"/>
       <c r="I31" s="25"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="27"/>
+      <c r="L31" s="28"/>
       <c r="M31" s="25"/>
       <c r="N31" s="25"/>
     </row>
@@ -3393,19 +3393,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="26"/>
+      <c r="B32" s="27"/>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="26"/>
+      <c r="G32" s="27"/>
       <c r="H32" s="25"/>
       <c r="I32" s="25"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="26"/>
+      <c r="L32" s="27"/>
       <c r="M32" s="25"/>
       <c r="N32" s="25"/>
     </row>
@@ -3413,19 +3413,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="27"/>
+      <c r="B33" s="28"/>
       <c r="C33" s="25"/>
       <c r="D33" s="25"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="27"/>
+      <c r="G33" s="28"/>
       <c r="H33" s="25"/>
       <c r="I33" s="25"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="27"/>
+      <c r="L33" s="28"/>
       <c r="M33" s="25"/>
       <c r="N33" s="25"/>
     </row>
@@ -3433,19 +3433,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="26"/>
+      <c r="B34" s="27"/>
       <c r="C34" s="25"/>
       <c r="D34" s="25"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="26"/>
+      <c r="G34" s="27"/>
       <c r="H34" s="25"/>
       <c r="I34" s="25"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="26"/>
+      <c r="L34" s="27"/>
       <c r="M34" s="25"/>
       <c r="N34" s="25"/>
     </row>
@@ -3453,19 +3453,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="27"/>
+      <c r="B35" s="28"/>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="27"/>
+      <c r="G35" s="28"/>
       <c r="H35" s="25"/>
       <c r="I35" s="25"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="27"/>
+      <c r="L35" s="28"/>
       <c r="M35" s="25"/>
       <c r="N35" s="25"/>
     </row>
@@ -3473,19 +3473,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="26"/>
+      <c r="B36" s="27"/>
       <c r="C36" s="25"/>
       <c r="D36" s="25"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="26"/>
+      <c r="G36" s="27"/>
       <c r="H36" s="25"/>
       <c r="I36" s="25"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="26"/>
+      <c r="L36" s="27"/>
       <c r="M36" s="25"/>
       <c r="N36" s="25"/>
     </row>
@@ -3493,7 +3493,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="29">
+      <c r="B37" s="30">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -3502,7 +3502,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="29">
+      <c r="G37" s="30">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -3511,7 +3511,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="29">
+      <c r="L37" s="30">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -3548,6 +3548,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
     <mergeCell ref="L34:N34"/>
     <mergeCell ref="L6:N6"/>
     <mergeCell ref="B33:D33"/>
@@ -3564,68 +3626,6 @@
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35DA87A2-2316-441B-A5E1-C5A5C4AB2C73}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C2F7A9C-4047-4411-997C-35253AECDA43}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -427,9 +427,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -440,6 +437,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -767,21 +767,21 @@
       </c>
       <c r="B5" s="21">
         <f>SUM(B6:B7)</f>
-        <v>4600</v>
+        <v>1200</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G5" s="14">
         <f>SUM(G6:G7)</f>
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="L5" s="14">
         <f>SUM(L6:L7)</f>
-        <v>1700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
@@ -789,19 +789,19 @@
         <v>21</v>
       </c>
       <c r="B6" s="14">
-        <v>3900</v>
+        <v>500</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>21</v>
       </c>
       <c r="G6" s="14">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>21</v>
       </c>
       <c r="L6" s="14">
-        <v>1700</v>
+        <v>600</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
@@ -835,7 +835,7 @@
       </c>
       <c r="G8" s="15">
         <f>SUM(G9:G10)</f>
-        <v>360</v>
+        <v>0</v>
       </c>
       <c r="K8" s="9" t="s">
         <v>23</v>
@@ -853,9 +853,7 @@
       <c r="F9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="15">
-        <v>360</v>
-      </c>
+      <c r="G9" s="15"/>
       <c r="K9" s="9" t="s">
         <v>21</v>
       </c>
@@ -1411,21 +1409,21 @@
       </c>
       <c r="B41" s="13">
         <f>SUM(B5,B8,B11,B14,B17,B20,B23,B26,B29,B32,B35,B38)</f>
-        <v>5440</v>
+        <v>2040</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G41" s="13">
         <f>SUM(G5,G8,G11,G14,G17,G20,G23,G26,G29,G32,G35,G38)</f>
-        <v>1968</v>
+        <v>1508</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="L41" s="13">
         <f>SUM(L5,L8,L11,L14,L17,L20,L23,L26,L29,L32,L35,L38)</f>
-        <v>3050</v>
+        <v>1950</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1">
@@ -2205,19 +2203,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="25"/>
       <c r="H1" s="25"/>
       <c r="I1" s="25"/>
-      <c r="K1" s="26" t="s">
+      <c r="K1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="25"/>
@@ -2225,19 +2223,19 @@
       <c r="N1" s="25"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
       <c r="I2" s="25"/>
-      <c r="K2" s="26" t="s">
+      <c r="K2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="25"/>
@@ -2259,27 +2257,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="28" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="25"/>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="25"/>
-      <c r="H4" s="29" t="s">
+      <c r="H4" s="28" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="25"/>
-      <c r="K4" s="29" t="s">
+      <c r="K4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="25"/>
-      <c r="M4" s="29" t="s">
+      <c r="M4" s="28" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="25"/>
@@ -2288,7 +2286,7 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="28">
+      <c r="B5" s="27">
         <v>352</v>
       </c>
       <c r="C5" s="25"/>
@@ -2296,13 +2294,13 @@
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="28"/>
+      <c r="G5" s="27"/>
       <c r="H5" s="25"/>
       <c r="I5" s="25"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="28"/>
+      <c r="L5" s="27"/>
       <c r="M5" s="25"/>
       <c r="N5" s="25"/>
     </row>
@@ -2310,7 +2308,7 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="26">
         <v>376</v>
       </c>
       <c r="C6" s="25"/>
@@ -2318,13 +2316,13 @@
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="27"/>
+      <c r="G6" s="26"/>
       <c r="H6" s="25"/>
       <c r="I6" s="25"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="27"/>
+      <c r="L6" s="26"/>
       <c r="M6" s="25"/>
       <c r="N6" s="25"/>
     </row>
@@ -2332,7 +2330,7 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="27">
         <v>0</v>
       </c>
       <c r="C7" s="25"/>
@@ -2340,13 +2338,13 @@
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="28"/>
+      <c r="G7" s="27"/>
       <c r="H7" s="25"/>
       <c r="I7" s="25"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="28"/>
+      <c r="L7" s="27"/>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
     </row>
@@ -2354,7 +2352,7 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="26">
         <v>724</v>
       </c>
       <c r="C8" s="25"/>
@@ -2362,13 +2360,13 @@
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="27"/>
+      <c r="G8" s="26"/>
       <c r="H8" s="25"/>
       <c r="I8" s="25"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="27"/>
+      <c r="L8" s="26"/>
       <c r="M8" s="25"/>
       <c r="N8" s="25"/>
     </row>
@@ -2376,7 +2374,7 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="28">
+      <c r="B9" s="27">
         <v>411</v>
       </c>
       <c r="C9" s="25"/>
@@ -2384,13 +2382,13 @@
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="28"/>
+      <c r="G9" s="27"/>
       <c r="H9" s="25"/>
       <c r="I9" s="25"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="28"/>
+      <c r="L9" s="27"/>
       <c r="M9" s="25"/>
       <c r="N9" s="25"/>
     </row>
@@ -2398,7 +2396,7 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="27">
+      <c r="B10" s="26">
         <v>0</v>
       </c>
       <c r="C10" s="25"/>
@@ -2406,13 +2404,13 @@
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="27"/>
+      <c r="G10" s="26"/>
       <c r="H10" s="25"/>
       <c r="I10" s="25"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="27"/>
+      <c r="L10" s="26"/>
       <c r="M10" s="25"/>
       <c r="N10" s="25"/>
     </row>
@@ -2420,7 +2418,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="29">
         <f>SUM(B5:B10)</f>
         <v>1863</v>
       </c>
@@ -2429,7 +2427,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="30">
+      <c r="G11" s="29">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -2438,7 +2436,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="30">
+      <c r="L11" s="29">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -2474,19 +2472,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
-      <c r="F25" s="26" t="s">
+      <c r="F25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
       <c r="I25" s="25"/>
-      <c r="K25" s="26" t="s">
+      <c r="K25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="25"/>
@@ -2494,19 +2492,19 @@
       <c r="N25" s="25"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
-      <c r="F26" s="26" t="s">
+      <c r="F26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="25"/>
       <c r="H26" s="25"/>
       <c r="I26" s="25"/>
-      <c r="K26" s="26" t="s">
+      <c r="K26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="25"/>
@@ -2528,27 +2526,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="25"/>
-      <c r="C28" s="29" t="s">
+      <c r="C28" s="28" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="25"/>
-      <c r="F28" s="29" t="s">
+      <c r="F28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="25"/>
-      <c r="H28" s="29" t="s">
+      <c r="H28" s="28" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="25"/>
-      <c r="K28" s="29" t="s">
+      <c r="K28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="25"/>
-      <c r="M28" s="29" t="s">
+      <c r="M28" s="28" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="25"/>
@@ -2557,7 +2555,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="28">
+      <c r="B29" s="27">
         <v>0</v>
       </c>
       <c r="C29" s="25"/>
@@ -2565,13 +2563,13 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="28"/>
+      <c r="G29" s="27"/>
       <c r="H29" s="25"/>
       <c r="I29" s="25"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="28">
+      <c r="L29" s="27">
         <v>14</v>
       </c>
       <c r="M29" s="25"/>
@@ -2581,7 +2579,7 @@
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="27">
+      <c r="B30" s="26">
         <v>0</v>
       </c>
       <c r="C30" s="25"/>
@@ -2589,13 +2587,13 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="27"/>
+      <c r="G30" s="26"/>
       <c r="H30" s="25"/>
       <c r="I30" s="25"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="27">
+      <c r="L30" s="26">
         <v>605</v>
       </c>
       <c r="M30" s="25"/>
@@ -2605,7 +2603,7 @@
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="28">
+      <c r="B31" s="27">
         <v>0</v>
       </c>
       <c r="C31" s="25"/>
@@ -2613,13 +2611,13 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="28"/>
+      <c r="G31" s="27"/>
       <c r="H31" s="25"/>
       <c r="I31" s="25"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="28">
+      <c r="L31" s="27">
         <v>1708</v>
       </c>
       <c r="M31" s="25"/>
@@ -2629,7 +2627,7 @@
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="27">
+      <c r="B32" s="26">
         <v>0</v>
       </c>
       <c r="C32" s="25"/>
@@ -2637,13 +2635,13 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="27"/>
+      <c r="G32" s="26"/>
       <c r="H32" s="25"/>
       <c r="I32" s="25"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="27">
+      <c r="L32" s="26">
         <v>1395</v>
       </c>
       <c r="M32" s="25"/>
@@ -2653,7 +2651,7 @@
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="28">
+      <c r="B33" s="27">
         <v>0</v>
       </c>
       <c r="C33" s="25"/>
@@ -2661,13 +2659,13 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="28"/>
+      <c r="G33" s="27"/>
       <c r="H33" s="25"/>
       <c r="I33" s="25"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="28">
+      <c r="L33" s="27">
         <v>0</v>
       </c>
       <c r="M33" s="25"/>
@@ -2677,7 +2675,7 @@
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="27">
+      <c r="B34" s="26">
         <v>0</v>
       </c>
       <c r="C34" s="25"/>
@@ -2685,13 +2683,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="27"/>
+      <c r="G34" s="26"/>
       <c r="H34" s="25"/>
       <c r="I34" s="25"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="27">
+      <c r="L34" s="26">
         <v>0</v>
       </c>
       <c r="M34" s="25"/>
@@ -2701,7 +2699,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="30">
+      <c r="B35" s="29">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -2710,7 +2708,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="30">
+      <c r="G35" s="29">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -2719,7 +2717,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="30">
+      <c r="L35" s="29">
         <f>SUM(L29:L34)</f>
         <v>3722</v>
       </c>
@@ -2756,6 +2754,56 @@
     </row>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B10:D10"/>
@@ -2772,56 +2820,6 @@
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="H28:I28"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2837,7 +2835,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
@@ -2845,7 +2843,7 @@
       <c r="D1" s="25"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
@@ -2859,11 +2857,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="28" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="28" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="25"/>
@@ -2872,7 +2870,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="28"/>
+      <c r="B5" s="27"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
     </row>
@@ -2880,7 +2878,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="27"/>
+      <c r="B6" s="26"/>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
     </row>
@@ -2888,7 +2886,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="28"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
     </row>
@@ -2896,7 +2894,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="27"/>
+      <c r="B8" s="26"/>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
     </row>
@@ -2904,7 +2902,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="29">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -2953,19 +2951,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="25"/>
       <c r="H1" s="25"/>
       <c r="I1" s="25"/>
-      <c r="K1" s="26" t="s">
+      <c r="K1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="25"/>
@@ -2973,19 +2971,19 @@
       <c r="N1" s="25"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
       <c r="I2" s="25"/>
-      <c r="K2" s="26" t="s">
+      <c r="K2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="25"/>
@@ -3007,27 +3005,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="28" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="25"/>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="25"/>
-      <c r="H4" s="29" t="s">
+      <c r="H4" s="28" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="25"/>
-      <c r="K4" s="29" t="s">
+      <c r="K4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="25"/>
-      <c r="M4" s="29" t="s">
+      <c r="M4" s="28" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="25"/>
@@ -3036,19 +3034,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="28"/>
+      <c r="B5" s="27"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="28"/>
+      <c r="G5" s="27"/>
       <c r="H5" s="25"/>
       <c r="I5" s="25"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="28"/>
+      <c r="L5" s="27"/>
       <c r="M5" s="25"/>
       <c r="N5" s="25"/>
     </row>
@@ -3056,19 +3054,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="27"/>
+      <c r="B6" s="26"/>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="27"/>
+      <c r="G6" s="26"/>
       <c r="H6" s="25"/>
       <c r="I6" s="25"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="27"/>
+      <c r="L6" s="26"/>
       <c r="M6" s="25"/>
       <c r="N6" s="25"/>
     </row>
@@ -3076,19 +3074,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="28"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="28"/>
+      <c r="G7" s="27"/>
       <c r="H7" s="25"/>
       <c r="I7" s="25"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="28"/>
+      <c r="L7" s="27"/>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
     </row>
@@ -3096,19 +3094,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="27"/>
+      <c r="B8" s="26"/>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="27"/>
+      <c r="G8" s="26"/>
       <c r="H8" s="25"/>
       <c r="I8" s="25"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="27"/>
+      <c r="L8" s="26"/>
       <c r="M8" s="25"/>
       <c r="N8" s="25"/>
     </row>
@@ -3116,19 +3114,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="28"/>
+      <c r="B9" s="27"/>
       <c r="C9" s="25"/>
       <c r="D9" s="25"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="28"/>
+      <c r="G9" s="27"/>
       <c r="H9" s="25"/>
       <c r="I9" s="25"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="28"/>
+      <c r="L9" s="27"/>
       <c r="M9" s="25"/>
       <c r="N9" s="25"/>
     </row>
@@ -3136,19 +3134,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="27"/>
+      <c r="B10" s="26"/>
       <c r="C10" s="25"/>
       <c r="D10" s="25"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="27"/>
+      <c r="G10" s="26"/>
       <c r="H10" s="25"/>
       <c r="I10" s="25"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="27"/>
+      <c r="L10" s="26"/>
       <c r="M10" s="25"/>
       <c r="N10" s="25"/>
     </row>
@@ -3156,19 +3154,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="28"/>
+      <c r="B11" s="27"/>
       <c r="C11" s="25"/>
       <c r="D11" s="25"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="28"/>
+      <c r="G11" s="27"/>
       <c r="H11" s="25"/>
       <c r="I11" s="25"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="28"/>
+      <c r="L11" s="27"/>
       <c r="M11" s="25"/>
       <c r="N11" s="25"/>
     </row>
@@ -3176,19 +3174,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="27"/>
+      <c r="B12" s="26"/>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="27"/>
+      <c r="G12" s="26"/>
       <c r="H12" s="25"/>
       <c r="I12" s="25"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="27"/>
+      <c r="L12" s="26"/>
       <c r="M12" s="25"/>
       <c r="N12" s="25"/>
     </row>
@@ -3196,7 +3194,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="29">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3205,7 +3203,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="30">
+      <c r="G13" s="29">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3214,7 +3212,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="30">
+      <c r="L13" s="29">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3250,19 +3248,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
-      <c r="F25" s="26" t="s">
+      <c r="F25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
       <c r="I25" s="25"/>
-      <c r="K25" s="26" t="s">
+      <c r="K25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="25"/>
@@ -3270,19 +3268,19 @@
       <c r="N25" s="25"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
-      <c r="F26" s="26" t="s">
+      <c r="F26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="25"/>
       <c r="H26" s="25"/>
       <c r="I26" s="25"/>
-      <c r="K26" s="26" t="s">
+      <c r="K26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="25"/>
@@ -3304,27 +3302,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="25"/>
-      <c r="C28" s="29" t="s">
+      <c r="C28" s="28" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="25"/>
-      <c r="F28" s="29" t="s">
+      <c r="F28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="25"/>
-      <c r="H28" s="29" t="s">
+      <c r="H28" s="28" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="25"/>
-      <c r="K28" s="29" t="s">
+      <c r="K28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="25"/>
-      <c r="M28" s="29" t="s">
+      <c r="M28" s="28" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="25"/>
@@ -3333,19 +3331,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="28"/>
+      <c r="B29" s="27"/>
       <c r="C29" s="25"/>
       <c r="D29" s="25"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="28"/>
+      <c r="G29" s="27"/>
       <c r="H29" s="25"/>
       <c r="I29" s="25"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="28"/>
+      <c r="L29" s="27"/>
       <c r="M29" s="25"/>
       <c r="N29" s="25"/>
     </row>
@@ -3353,19 +3351,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="27"/>
+      <c r="B30" s="26"/>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="27"/>
+      <c r="G30" s="26"/>
       <c r="H30" s="25"/>
       <c r="I30" s="25"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="27"/>
+      <c r="L30" s="26"/>
       <c r="M30" s="25"/>
       <c r="N30" s="25"/>
     </row>
@@ -3373,19 +3371,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="28"/>
+      <c r="B31" s="27"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="28"/>
+      <c r="G31" s="27"/>
       <c r="H31" s="25"/>
       <c r="I31" s="25"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="28"/>
+      <c r="L31" s="27"/>
       <c r="M31" s="25"/>
       <c r="N31" s="25"/>
     </row>
@@ -3393,19 +3391,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="27"/>
+      <c r="B32" s="26"/>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="27"/>
+      <c r="G32" s="26"/>
       <c r="H32" s="25"/>
       <c r="I32" s="25"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="27"/>
+      <c r="L32" s="26"/>
       <c r="M32" s="25"/>
       <c r="N32" s="25"/>
     </row>
@@ -3413,19 +3411,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="28"/>
+      <c r="B33" s="27"/>
       <c r="C33" s="25"/>
       <c r="D33" s="25"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="28"/>
+      <c r="G33" s="27"/>
       <c r="H33" s="25"/>
       <c r="I33" s="25"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="28"/>
+      <c r="L33" s="27"/>
       <c r="M33" s="25"/>
       <c r="N33" s="25"/>
     </row>
@@ -3433,19 +3431,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="27"/>
+      <c r="B34" s="26"/>
       <c r="C34" s="25"/>
       <c r="D34" s="25"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="27"/>
+      <c r="G34" s="26"/>
       <c r="H34" s="25"/>
       <c r="I34" s="25"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="27"/>
+      <c r="L34" s="26"/>
       <c r="M34" s="25"/>
       <c r="N34" s="25"/>
     </row>
@@ -3453,19 +3451,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="28"/>
+      <c r="B35" s="27"/>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="28"/>
+      <c r="G35" s="27"/>
       <c r="H35" s="25"/>
       <c r="I35" s="25"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="28"/>
+      <c r="L35" s="27"/>
       <c r="M35" s="25"/>
       <c r="N35" s="25"/>
     </row>
@@ -3473,19 +3471,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="27"/>
+      <c r="B36" s="26"/>
       <c r="C36" s="25"/>
       <c r="D36" s="25"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="27"/>
+      <c r="G36" s="26"/>
       <c r="H36" s="25"/>
       <c r="I36" s="25"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="27"/>
+      <c r="L36" s="26"/>
       <c r="M36" s="25"/>
       <c r="N36" s="25"/>
     </row>
@@ -3493,7 +3491,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="30">
+      <c r="B37" s="29">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -3502,7 +3500,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="30">
+      <c r="G37" s="29">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -3511,7 +3509,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="30">
+      <c r="L37" s="29">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -3548,6 +3546,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
     <mergeCell ref="G36:I36"/>
     <mergeCell ref="L32:N32"/>
     <mergeCell ref="L13:N13"/>
@@ -3564,68 +3624,6 @@
     <mergeCell ref="L33:N33"/>
     <mergeCell ref="L35:N35"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="L9:N9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C2F7A9C-4047-4411-997C-35253AECDA43}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0171458E-BD2B-430A-96F0-D19DC6DB2EB3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucoes" sheetId="1" r:id="rId1"/>
@@ -767,21 +767,21 @@
       </c>
       <c r="B5" s="21">
         <f>SUM(B6:B7)</f>
-        <v>1200</v>
+        <v>2100</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G5" s="14">
         <f>SUM(G6:G7)</f>
-        <v>1400</v>
+        <v>600</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="L5" s="14">
         <f>SUM(L6:L7)</f>
-        <v>600</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
@@ -789,19 +789,19 @@
         <v>21</v>
       </c>
       <c r="B6" s="14">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>21</v>
       </c>
       <c r="G6" s="14">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>21</v>
       </c>
       <c r="L6" s="14">
-        <v>600</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
@@ -809,14 +809,12 @@
         <v>22</v>
       </c>
       <c r="B7" s="14">
-        <v>700</v>
+        <v>1400</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="14">
-        <v>700</v>
-      </c>
+      <c r="G7" s="14"/>
       <c r="K7" s="7" t="s">
         <v>22</v>
       </c>
@@ -842,7 +840,7 @@
       </c>
       <c r="L8" s="15">
         <f>SUM(L9:L10)</f>
-        <v>500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1">
@@ -857,9 +855,7 @@
       <c r="K9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L9" s="15">
-        <v>500</v>
-      </c>
+      <c r="L9" s="15"/>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
       <c r="A10" s="9" t="s">
@@ -932,7 +928,7 @@
       </c>
       <c r="B14" s="15">
         <f>SUM(B15:B16)</f>
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>25</v>
@@ -946,7 +942,7 @@
       </c>
       <c r="L14" s="15">
         <f>SUM(L15:L16)</f>
-        <v>190</v>
+        <v>400</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1">
@@ -954,7 +950,7 @@
         <v>21</v>
       </c>
       <c r="B15" s="15">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>21</v>
@@ -964,7 +960,7 @@
         <v>21</v>
       </c>
       <c r="L15" s="15">
-        <v>190</v>
+        <v>400</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1">
@@ -1250,7 +1246,7 @@
       </c>
       <c r="B32" s="15">
         <f>SUM(B33:B34)</f>
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>31</v>
@@ -1272,7 +1268,7 @@
         <v>21</v>
       </c>
       <c r="B33" s="15">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>21</v>
@@ -1409,21 +1405,21 @@
       </c>
       <c r="B41" s="13">
         <f>SUM(B5,B8,B11,B14,B17,B20,B23,B26,B29,B32,B35,B38)</f>
-        <v>2040</v>
+        <v>2990</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G41" s="13">
         <f>SUM(G5,G8,G11,G14,G17,G20,G23,G26,G29,G32,G35,G38)</f>
-        <v>1508</v>
+        <v>708</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="L41" s="13">
         <f>SUM(L5,L8,L11,L14,L17,L20,L23,L26,L29,L32,L35,L38)</f>
-        <v>1950</v>
+        <v>2760</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1">
@@ -3671,7 +3667,7 @@
         <v>49</v>
       </c>
       <c r="E2" s="18">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3705,7 +3701,7 @@
         <v>49</v>
       </c>
       <c r="E4" s="18">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3739,7 +3735,7 @@
         <v>49</v>
       </c>
       <c r="E6" s="18">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:5">

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0171458E-BD2B-430A-96F0-D19DC6DB2EB3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3672347-E002-43E2-B475-5ECC9954BB5F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucoes" sheetId="1" r:id="rId1"/>
@@ -427,6 +427,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -437,9 +440,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -774,14 +774,14 @@
       </c>
       <c r="G5" s="14">
         <f>SUM(G6:G7)</f>
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="L5" s="14">
         <f>SUM(L6:L7)</f>
-        <v>1700</v>
+        <v>700</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
@@ -794,14 +794,12 @@
       <c r="F6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="14">
-        <v>600</v>
-      </c>
+      <c r="G6" s="14"/>
       <c r="K6" s="7" t="s">
         <v>21</v>
       </c>
       <c r="L6" s="14">
-        <v>1700</v>
+        <v>700</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
@@ -1412,14 +1410,14 @@
       </c>
       <c r="G41" s="13">
         <f>SUM(G5,G8,G11,G14,G17,G20,G23,G26,G29,G32,G35,G38)</f>
-        <v>708</v>
+        <v>108</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="L41" s="13">
         <f>SUM(L5,L8,L11,L14,L17,L20,L23,L26,L29,L32,L35,L38)</f>
-        <v>2760</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1">
@@ -2199,19 +2197,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="25"/>
       <c r="H1" s="25"/>
       <c r="I1" s="25"/>
-      <c r="K1" s="30" t="s">
+      <c r="K1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="25"/>
@@ -2219,19 +2217,19 @@
       <c r="N1" s="25"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
-      <c r="F2" s="30" t="s">
+      <c r="F2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
       <c r="I2" s="25"/>
-      <c r="K2" s="30" t="s">
+      <c r="K2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="25"/>
@@ -2253,27 +2251,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="29" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="25"/>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="25"/>
-      <c r="H4" s="28" t="s">
+      <c r="H4" s="29" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="25"/>
-      <c r="K4" s="28" t="s">
+      <c r="K4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="25"/>
-      <c r="M4" s="28" t="s">
+      <c r="M4" s="29" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="25"/>
@@ -2282,7 +2280,7 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="28">
         <v>352</v>
       </c>
       <c r="C5" s="25"/>
@@ -2290,13 +2288,13 @@
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="27"/>
+      <c r="G5" s="28"/>
       <c r="H5" s="25"/>
       <c r="I5" s="25"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="27"/>
+      <c r="L5" s="28"/>
       <c r="M5" s="25"/>
       <c r="N5" s="25"/>
     </row>
@@ -2304,7 +2302,7 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="27">
         <v>376</v>
       </c>
       <c r="C6" s="25"/>
@@ -2312,13 +2310,13 @@
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="26"/>
+      <c r="G6" s="27"/>
       <c r="H6" s="25"/>
       <c r="I6" s="25"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="26"/>
+      <c r="L6" s="27"/>
       <c r="M6" s="25"/>
       <c r="N6" s="25"/>
     </row>
@@ -2326,7 +2324,7 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="28">
         <v>0</v>
       </c>
       <c r="C7" s="25"/>
@@ -2334,13 +2332,13 @@
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="27"/>
+      <c r="G7" s="28"/>
       <c r="H7" s="25"/>
       <c r="I7" s="25"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="27"/>
+      <c r="L7" s="28"/>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
     </row>
@@ -2348,7 +2346,7 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="27">
         <v>724</v>
       </c>
       <c r="C8" s="25"/>
@@ -2356,13 +2354,13 @@
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="26"/>
+      <c r="G8" s="27"/>
       <c r="H8" s="25"/>
       <c r="I8" s="25"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="26"/>
+      <c r="L8" s="27"/>
       <c r="M8" s="25"/>
       <c r="N8" s="25"/>
     </row>
@@ -2370,7 +2368,7 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="27">
+      <c r="B9" s="28">
         <v>411</v>
       </c>
       <c r="C9" s="25"/>
@@ -2378,13 +2376,13 @@
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="27"/>
+      <c r="G9" s="28"/>
       <c r="H9" s="25"/>
       <c r="I9" s="25"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="27"/>
+      <c r="L9" s="28"/>
       <c r="M9" s="25"/>
       <c r="N9" s="25"/>
     </row>
@@ -2392,7 +2390,7 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="27">
         <v>0</v>
       </c>
       <c r="C10" s="25"/>
@@ -2400,13 +2398,13 @@
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="26"/>
+      <c r="G10" s="27"/>
       <c r="H10" s="25"/>
       <c r="I10" s="25"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="26"/>
+      <c r="L10" s="27"/>
       <c r="M10" s="25"/>
       <c r="N10" s="25"/>
     </row>
@@ -2414,7 +2412,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="30">
         <f>SUM(B5:B10)</f>
         <v>1863</v>
       </c>
@@ -2423,7 +2421,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="29">
+      <c r="G11" s="30">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -2432,7 +2430,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="29">
+      <c r="L11" s="30">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -2468,19 +2466,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
-      <c r="F25" s="30" t="s">
+      <c r="F25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
       <c r="I25" s="25"/>
-      <c r="K25" s="30" t="s">
+      <c r="K25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="25"/>
@@ -2488,19 +2486,19 @@
       <c r="N25" s="25"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
-      <c r="F26" s="30" t="s">
+      <c r="F26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="25"/>
       <c r="H26" s="25"/>
       <c r="I26" s="25"/>
-      <c r="K26" s="30" t="s">
+      <c r="K26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="25"/>
@@ -2522,27 +2520,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="25"/>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="29" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="25"/>
-      <c r="F28" s="28" t="s">
+      <c r="F28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="25"/>
-      <c r="H28" s="28" t="s">
+      <c r="H28" s="29" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="25"/>
-      <c r="K28" s="28" t="s">
+      <c r="K28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="25"/>
-      <c r="M28" s="28" t="s">
+      <c r="M28" s="29" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="25"/>
@@ -2551,7 +2549,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="27">
+      <c r="B29" s="28">
         <v>0</v>
       </c>
       <c r="C29" s="25"/>
@@ -2559,13 +2557,13 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="27"/>
+      <c r="G29" s="28"/>
       <c r="H29" s="25"/>
       <c r="I29" s="25"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="27">
+      <c r="L29" s="28">
         <v>14</v>
       </c>
       <c r="M29" s="25"/>
@@ -2575,7 +2573,7 @@
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="26">
+      <c r="B30" s="27">
         <v>0</v>
       </c>
       <c r="C30" s="25"/>
@@ -2583,13 +2581,13 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="26"/>
+      <c r="G30" s="27"/>
       <c r="H30" s="25"/>
       <c r="I30" s="25"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="26">
+      <c r="L30" s="27">
         <v>605</v>
       </c>
       <c r="M30" s="25"/>
@@ -2599,7 +2597,7 @@
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="27">
+      <c r="B31" s="28">
         <v>0</v>
       </c>
       <c r="C31" s="25"/>
@@ -2607,13 +2605,13 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="27"/>
+      <c r="G31" s="28"/>
       <c r="H31" s="25"/>
       <c r="I31" s="25"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="27">
+      <c r="L31" s="28">
         <v>1708</v>
       </c>
       <c r="M31" s="25"/>
@@ -2623,7 +2621,7 @@
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="26">
+      <c r="B32" s="27">
         <v>0</v>
       </c>
       <c r="C32" s="25"/>
@@ -2631,13 +2629,13 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="26"/>
+      <c r="G32" s="27"/>
       <c r="H32" s="25"/>
       <c r="I32" s="25"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="26">
+      <c r="L32" s="27">
         <v>1395</v>
       </c>
       <c r="M32" s="25"/>
@@ -2647,7 +2645,7 @@
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="27">
+      <c r="B33" s="28">
         <v>0</v>
       </c>
       <c r="C33" s="25"/>
@@ -2655,13 +2653,13 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="27"/>
+      <c r="G33" s="28"/>
       <c r="H33" s="25"/>
       <c r="I33" s="25"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="27">
+      <c r="L33" s="28">
         <v>0</v>
       </c>
       <c r="M33" s="25"/>
@@ -2671,7 +2669,7 @@
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="26">
+      <c r="B34" s="27">
         <v>0</v>
       </c>
       <c r="C34" s="25"/>
@@ -2679,13 +2677,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="26"/>
+      <c r="G34" s="27"/>
       <c r="H34" s="25"/>
       <c r="I34" s="25"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="26">
+      <c r="L34" s="27">
         <v>0</v>
       </c>
       <c r="M34" s="25"/>
@@ -2695,7 +2693,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="29">
+      <c r="B35" s="30">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -2704,7 +2702,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="29">
+      <c r="G35" s="30">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -2713,7 +2711,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="29">
+      <c r="L35" s="30">
         <f>SUM(L29:L34)</f>
         <v>3722</v>
       </c>
@@ -2750,13 +2748,49 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="L11:N11"/>
@@ -2773,49 +2807,13 @@
     <mergeCell ref="K2:N2"/>
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2831,7 +2829,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
@@ -2839,7 +2837,7 @@
       <c r="D1" s="25"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
@@ -2853,11 +2851,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="29" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="29" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="25"/>
@@ -2866,7 +2864,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="27"/>
+      <c r="B5" s="28"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
     </row>
@@ -2874,7 +2872,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="26"/>
+      <c r="B6" s="27"/>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
     </row>
@@ -2882,7 +2880,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="27"/>
+      <c r="B7" s="28"/>
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
     </row>
@@ -2890,7 +2888,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="26"/>
+      <c r="B8" s="27"/>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
     </row>
@@ -2898,7 +2896,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="30">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -2947,19 +2945,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="25"/>
       <c r="H1" s="25"/>
       <c r="I1" s="25"/>
-      <c r="K1" s="30" t="s">
+      <c r="K1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="25"/>
@@ -2967,19 +2965,19 @@
       <c r="N1" s="25"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
-      <c r="F2" s="30" t="s">
+      <c r="F2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
       <c r="I2" s="25"/>
-      <c r="K2" s="30" t="s">
+      <c r="K2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="25"/>
@@ -3001,27 +2999,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="29" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="25"/>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="25"/>
-      <c r="H4" s="28" t="s">
+      <c r="H4" s="29" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="25"/>
-      <c r="K4" s="28" t="s">
+      <c r="K4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="25"/>
-      <c r="M4" s="28" t="s">
+      <c r="M4" s="29" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="25"/>
@@ -3030,19 +3028,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="27"/>
+      <c r="B5" s="28"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="27"/>
+      <c r="G5" s="28"/>
       <c r="H5" s="25"/>
       <c r="I5" s="25"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="27"/>
+      <c r="L5" s="28"/>
       <c r="M5" s="25"/>
       <c r="N5" s="25"/>
     </row>
@@ -3050,19 +3048,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="26"/>
+      <c r="B6" s="27"/>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="26"/>
+      <c r="G6" s="27"/>
       <c r="H6" s="25"/>
       <c r="I6" s="25"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="26"/>
+      <c r="L6" s="27"/>
       <c r="M6" s="25"/>
       <c r="N6" s="25"/>
     </row>
@@ -3070,19 +3068,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="27"/>
+      <c r="B7" s="28"/>
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="27"/>
+      <c r="G7" s="28"/>
       <c r="H7" s="25"/>
       <c r="I7" s="25"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="27"/>
+      <c r="L7" s="28"/>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
     </row>
@@ -3090,19 +3088,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="26"/>
+      <c r="B8" s="27"/>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="26"/>
+      <c r="G8" s="27"/>
       <c r="H8" s="25"/>
       <c r="I8" s="25"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="26"/>
+      <c r="L8" s="27"/>
       <c r="M8" s="25"/>
       <c r="N8" s="25"/>
     </row>
@@ -3110,19 +3108,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="27"/>
+      <c r="B9" s="28"/>
       <c r="C9" s="25"/>
       <c r="D9" s="25"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="27"/>
+      <c r="G9" s="28"/>
       <c r="H9" s="25"/>
       <c r="I9" s="25"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="27"/>
+      <c r="L9" s="28"/>
       <c r="M9" s="25"/>
       <c r="N9" s="25"/>
     </row>
@@ -3130,19 +3128,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="26"/>
+      <c r="B10" s="27"/>
       <c r="C10" s="25"/>
       <c r="D10" s="25"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="26"/>
+      <c r="G10" s="27"/>
       <c r="H10" s="25"/>
       <c r="I10" s="25"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="26"/>
+      <c r="L10" s="27"/>
       <c r="M10" s="25"/>
       <c r="N10" s="25"/>
     </row>
@@ -3150,19 +3148,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="27"/>
+      <c r="B11" s="28"/>
       <c r="C11" s="25"/>
       <c r="D11" s="25"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="27"/>
+      <c r="G11" s="28"/>
       <c r="H11" s="25"/>
       <c r="I11" s="25"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="27"/>
+      <c r="L11" s="28"/>
       <c r="M11" s="25"/>
       <c r="N11" s="25"/>
     </row>
@@ -3170,19 +3168,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="26"/>
+      <c r="B12" s="27"/>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="26"/>
+      <c r="G12" s="27"/>
       <c r="H12" s="25"/>
       <c r="I12" s="25"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="26"/>
+      <c r="L12" s="27"/>
       <c r="M12" s="25"/>
       <c r="N12" s="25"/>
     </row>
@@ -3190,7 +3188,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="30">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3199,7 +3197,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="29">
+      <c r="G13" s="30">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3208,7 +3206,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="29">
+      <c r="L13" s="30">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3244,19 +3242,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
-      <c r="F25" s="30" t="s">
+      <c r="F25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
       <c r="I25" s="25"/>
-      <c r="K25" s="30" t="s">
+      <c r="K25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="25"/>
@@ -3264,19 +3262,19 @@
       <c r="N25" s="25"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
-      <c r="F26" s="30" t="s">
+      <c r="F26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="25"/>
       <c r="H26" s="25"/>
       <c r="I26" s="25"/>
-      <c r="K26" s="30" t="s">
+      <c r="K26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="25"/>
@@ -3298,27 +3296,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="25"/>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="29" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="25"/>
-      <c r="F28" s="28" t="s">
+      <c r="F28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="25"/>
-      <c r="H28" s="28" t="s">
+      <c r="H28" s="29" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="25"/>
-      <c r="K28" s="28" t="s">
+      <c r="K28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="25"/>
-      <c r="M28" s="28" t="s">
+      <c r="M28" s="29" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="25"/>
@@ -3327,19 +3325,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="27"/>
+      <c r="B29" s="28"/>
       <c r="C29" s="25"/>
       <c r="D29" s="25"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="27"/>
+      <c r="G29" s="28"/>
       <c r="H29" s="25"/>
       <c r="I29" s="25"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="27"/>
+      <c r="L29" s="28"/>
       <c r="M29" s="25"/>
       <c r="N29" s="25"/>
     </row>
@@ -3347,19 +3345,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="26"/>
+      <c r="B30" s="27"/>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="26"/>
+      <c r="G30" s="27"/>
       <c r="H30" s="25"/>
       <c r="I30" s="25"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="26"/>
+      <c r="L30" s="27"/>
       <c r="M30" s="25"/>
       <c r="N30" s="25"/>
     </row>
@@ -3367,19 +3365,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="27"/>
+      <c r="B31" s="28"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="27"/>
+      <c r="G31" s="28"/>
       <c r="H31" s="25"/>
       <c r="I31" s="25"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="27"/>
+      <c r="L31" s="28"/>
       <c r="M31" s="25"/>
       <c r="N31" s="25"/>
     </row>
@@ -3387,19 +3385,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="26"/>
+      <c r="B32" s="27"/>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="26"/>
+      <c r="G32" s="27"/>
       <c r="H32" s="25"/>
       <c r="I32" s="25"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="26"/>
+      <c r="L32" s="27"/>
       <c r="M32" s="25"/>
       <c r="N32" s="25"/>
     </row>
@@ -3407,19 +3405,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="27"/>
+      <c r="B33" s="28"/>
       <c r="C33" s="25"/>
       <c r="D33" s="25"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="27"/>
+      <c r="G33" s="28"/>
       <c r="H33" s="25"/>
       <c r="I33" s="25"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="27"/>
+      <c r="L33" s="28"/>
       <c r="M33" s="25"/>
       <c r="N33" s="25"/>
     </row>
@@ -3427,19 +3425,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="26"/>
+      <c r="B34" s="27"/>
       <c r="C34" s="25"/>
       <c r="D34" s="25"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="26"/>
+      <c r="G34" s="27"/>
       <c r="H34" s="25"/>
       <c r="I34" s="25"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="26"/>
+      <c r="L34" s="27"/>
       <c r="M34" s="25"/>
       <c r="N34" s="25"/>
     </row>
@@ -3447,19 +3445,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="27"/>
+      <c r="B35" s="28"/>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="27"/>
+      <c r="G35" s="28"/>
       <c r="H35" s="25"/>
       <c r="I35" s="25"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="27"/>
+      <c r="L35" s="28"/>
       <c r="M35" s="25"/>
       <c r="N35" s="25"/>
     </row>
@@ -3467,19 +3465,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="26"/>
+      <c r="B36" s="27"/>
       <c r="C36" s="25"/>
       <c r="D36" s="25"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="26"/>
+      <c r="G36" s="27"/>
       <c r="H36" s="25"/>
       <c r="I36" s="25"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="26"/>
+      <c r="L36" s="27"/>
       <c r="M36" s="25"/>
       <c r="N36" s="25"/>
     </row>
@@ -3487,7 +3485,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="29">
+      <c r="B37" s="30">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -3496,7 +3494,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="29">
+      <c r="G37" s="30">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -3505,7 +3503,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="29">
+      <c r="L37" s="30">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -3542,6 +3540,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
     <mergeCell ref="L34:N34"/>
     <mergeCell ref="L6:N6"/>
     <mergeCell ref="B33:D33"/>
@@ -3558,68 +3618,6 @@
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3672347-E002-43E2-B475-5ECC9954BB5F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25EA17D5-9DDE-4CD8-A13C-03A64CE64AC0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -427,9 +427,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -440,6 +437,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -774,14 +774,14 @@
       </c>
       <c r="G5" s="14">
         <f>SUM(G6:G7)</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="L5" s="14">
         <f>SUM(L6:L7)</f>
-        <v>700</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
@@ -789,25 +789,25 @@
         <v>21</v>
       </c>
       <c r="B6" s="14">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="14"/>
+      <c r="G6" s="14">
+        <v>800</v>
+      </c>
       <c r="K6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="L6" s="14">
-        <v>700</v>
-      </c>
+      <c r="L6" s="14"/>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
         <v>22</v>
       </c>
       <c r="B7" s="14">
-        <v>1400</v>
+        <v>1800</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>22</v>
@@ -838,7 +838,7 @@
       </c>
       <c r="L8" s="15">
         <f>SUM(L9:L10)</f>
-        <v>0</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1">
@@ -853,7 +853,10 @@
       <c r="K9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L9" s="15"/>
+      <c r="L9" s="15">
+        <f>540-391</f>
+        <v>149</v>
+      </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
       <c r="A10" s="9" t="s">
@@ -926,7 +929,7 @@
       </c>
       <c r="B14" s="15">
         <f>SUM(B15:B16)</f>
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>25</v>
@@ -940,7 +943,7 @@
       </c>
       <c r="L14" s="15">
         <f>SUM(L15:L16)</f>
-        <v>400</v>
+        <v>220</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1">
@@ -948,7 +951,7 @@
         <v>21</v>
       </c>
       <c r="B15" s="15">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>21</v>
@@ -958,7 +961,7 @@
         <v>21</v>
       </c>
       <c r="L15" s="15">
-        <v>400</v>
+        <v>220</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1">
@@ -981,7 +984,7 @@
       </c>
       <c r="B17" s="14">
         <f>SUM(B18:B19)</f>
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>26</v>
@@ -1003,7 +1006,7 @@
         <v>21</v>
       </c>
       <c r="B18" s="14">
-        <v>170</v>
+        <v>80</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>21</v>
@@ -1201,7 +1204,7 @@
       </c>
       <c r="L29" s="14">
         <f>SUM(L30:L31)</f>
-        <v>160</v>
+        <v>360</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1">
@@ -1221,7 +1224,7 @@
         <v>21</v>
       </c>
       <c r="L30" s="14">
-        <v>160</v>
+        <v>360</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1">
@@ -1244,7 +1247,7 @@
       </c>
       <c r="B32" s="15">
         <f>SUM(B33:B34)</f>
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>31</v>
@@ -1258,7 +1261,7 @@
       </c>
       <c r="L32" s="15">
         <f>SUM(L33:L34)</f>
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
@@ -1266,7 +1269,7 @@
         <v>21</v>
       </c>
       <c r="B33" s="15">
-        <v>500</v>
+        <v>140</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>21</v>
@@ -1278,7 +1281,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="15">
-        <v>500</v>
+        <v>600</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
@@ -1403,21 +1406,21 @@
       </c>
       <c r="B41" s="13">
         <f>SUM(B5,B8,B11,B14,B17,B20,B23,B26,B29,B32,B35,B38)</f>
-        <v>2990</v>
+        <v>2590</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G41" s="13">
         <f>SUM(G5,G8,G11,G14,G17,G20,G23,G26,G29,G32,G35,G38)</f>
-        <v>108</v>
+        <v>908</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="L41" s="13">
         <f>SUM(L5,L8,L11,L14,L17,L20,L23,L26,L29,L32,L35,L38)</f>
-        <v>1760</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1">
@@ -2197,19 +2200,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="25"/>
       <c r="H1" s="25"/>
       <c r="I1" s="25"/>
-      <c r="K1" s="26" t="s">
+      <c r="K1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="25"/>
@@ -2217,19 +2220,19 @@
       <c r="N1" s="25"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
       <c r="I2" s="25"/>
-      <c r="K2" s="26" t="s">
+      <c r="K2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="25"/>
@@ -2251,27 +2254,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="28" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="25"/>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="25"/>
-      <c r="H4" s="29" t="s">
+      <c r="H4" s="28" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="25"/>
-      <c r="K4" s="29" t="s">
+      <c r="K4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="25"/>
-      <c r="M4" s="29" t="s">
+      <c r="M4" s="28" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="25"/>
@@ -2280,7 +2283,7 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="28">
+      <c r="B5" s="27">
         <v>352</v>
       </c>
       <c r="C5" s="25"/>
@@ -2288,13 +2291,13 @@
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="28"/>
+      <c r="G5" s="27"/>
       <c r="H5" s="25"/>
       <c r="I5" s="25"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="28"/>
+      <c r="L5" s="27"/>
       <c r="M5" s="25"/>
       <c r="N5" s="25"/>
     </row>
@@ -2302,7 +2305,7 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="26">
         <v>376</v>
       </c>
       <c r="C6" s="25"/>
@@ -2310,13 +2313,13 @@
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="27"/>
+      <c r="G6" s="26"/>
       <c r="H6" s="25"/>
       <c r="I6" s="25"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="27"/>
+      <c r="L6" s="26"/>
       <c r="M6" s="25"/>
       <c r="N6" s="25"/>
     </row>
@@ -2324,7 +2327,7 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="27">
         <v>0</v>
       </c>
       <c r="C7" s="25"/>
@@ -2332,13 +2335,13 @@
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="28"/>
+      <c r="G7" s="27"/>
       <c r="H7" s="25"/>
       <c r="I7" s="25"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="28"/>
+      <c r="L7" s="27"/>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
     </row>
@@ -2346,7 +2349,7 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="26">
         <v>724</v>
       </c>
       <c r="C8" s="25"/>
@@ -2354,13 +2357,13 @@
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="27"/>
+      <c r="G8" s="26"/>
       <c r="H8" s="25"/>
       <c r="I8" s="25"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="27"/>
+      <c r="L8" s="26"/>
       <c r="M8" s="25"/>
       <c r="N8" s="25"/>
     </row>
@@ -2368,7 +2371,7 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="28">
+      <c r="B9" s="27">
         <v>411</v>
       </c>
       <c r="C9" s="25"/>
@@ -2376,13 +2379,13 @@
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="28"/>
+      <c r="G9" s="27"/>
       <c r="H9" s="25"/>
       <c r="I9" s="25"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="28"/>
+      <c r="L9" s="27"/>
       <c r="M9" s="25"/>
       <c r="N9" s="25"/>
     </row>
@@ -2390,7 +2393,7 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="27">
+      <c r="B10" s="26">
         <v>0</v>
       </c>
       <c r="C10" s="25"/>
@@ -2398,13 +2401,13 @@
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="27"/>
+      <c r="G10" s="26"/>
       <c r="H10" s="25"/>
       <c r="I10" s="25"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="27"/>
+      <c r="L10" s="26"/>
       <c r="M10" s="25"/>
       <c r="N10" s="25"/>
     </row>
@@ -2412,7 +2415,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="29">
         <f>SUM(B5:B10)</f>
         <v>1863</v>
       </c>
@@ -2421,7 +2424,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="30">
+      <c r="G11" s="29">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -2430,7 +2433,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="30">
+      <c r="L11" s="29">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -2466,19 +2469,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
-      <c r="F25" s="26" t="s">
+      <c r="F25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
       <c r="I25" s="25"/>
-      <c r="K25" s="26" t="s">
+      <c r="K25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="25"/>
@@ -2486,19 +2489,19 @@
       <c r="N25" s="25"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
-      <c r="F26" s="26" t="s">
+      <c r="F26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="25"/>
       <c r="H26" s="25"/>
       <c r="I26" s="25"/>
-      <c r="K26" s="26" t="s">
+      <c r="K26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="25"/>
@@ -2520,27 +2523,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="25"/>
-      <c r="C28" s="29" t="s">
+      <c r="C28" s="28" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="25"/>
-      <c r="F28" s="29" t="s">
+      <c r="F28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="25"/>
-      <c r="H28" s="29" t="s">
+      <c r="H28" s="28" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="25"/>
-      <c r="K28" s="29" t="s">
+      <c r="K28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="25"/>
-      <c r="M28" s="29" t="s">
+      <c r="M28" s="28" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="25"/>
@@ -2549,7 +2552,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="28">
+      <c r="B29" s="27">
         <v>0</v>
       </c>
       <c r="C29" s="25"/>
@@ -2557,13 +2560,13 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="28"/>
+      <c r="G29" s="27"/>
       <c r="H29" s="25"/>
       <c r="I29" s="25"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="28">
+      <c r="L29" s="27">
         <v>14</v>
       </c>
       <c r="M29" s="25"/>
@@ -2573,7 +2576,7 @@
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="27">
+      <c r="B30" s="26">
         <v>0</v>
       </c>
       <c r="C30" s="25"/>
@@ -2581,13 +2584,13 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="27"/>
+      <c r="G30" s="26"/>
       <c r="H30" s="25"/>
       <c r="I30" s="25"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="27">
+      <c r="L30" s="26">
         <v>605</v>
       </c>
       <c r="M30" s="25"/>
@@ -2597,7 +2600,7 @@
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="28">
+      <c r="B31" s="27">
         <v>0</v>
       </c>
       <c r="C31" s="25"/>
@@ -2605,13 +2608,13 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="28"/>
+      <c r="G31" s="27"/>
       <c r="H31" s="25"/>
       <c r="I31" s="25"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="28">
+      <c r="L31" s="27">
         <v>1708</v>
       </c>
       <c r="M31" s="25"/>
@@ -2621,7 +2624,7 @@
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="27">
+      <c r="B32" s="26">
         <v>0</v>
       </c>
       <c r="C32" s="25"/>
@@ -2629,13 +2632,13 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="27"/>
+      <c r="G32" s="26"/>
       <c r="H32" s="25"/>
       <c r="I32" s="25"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="27">
+      <c r="L32" s="26">
         <v>1395</v>
       </c>
       <c r="M32" s="25"/>
@@ -2645,7 +2648,7 @@
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="28">
+      <c r="B33" s="27">
         <v>0</v>
       </c>
       <c r="C33" s="25"/>
@@ -2653,13 +2656,13 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="28"/>
+      <c r="G33" s="27"/>
       <c r="H33" s="25"/>
       <c r="I33" s="25"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="28">
+      <c r="L33" s="27">
         <v>0</v>
       </c>
       <c r="M33" s="25"/>
@@ -2669,7 +2672,7 @@
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="27">
+      <c r="B34" s="26">
         <v>0</v>
       </c>
       <c r="C34" s="25"/>
@@ -2677,13 +2680,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="27"/>
+      <c r="G34" s="26"/>
       <c r="H34" s="25"/>
       <c r="I34" s="25"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="27">
+      <c r="L34" s="26">
         <v>0</v>
       </c>
       <c r="M34" s="25"/>
@@ -2693,7 +2696,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="30">
+      <c r="B35" s="29">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -2702,7 +2705,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="30">
+      <c r="G35" s="29">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -2711,7 +2714,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="30">
+      <c r="L35" s="29">
         <f>SUM(L29:L34)</f>
         <v>3722</v>
       </c>
@@ -2748,6 +2751,56 @@
     </row>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B10:D10"/>
@@ -2764,56 +2817,6 @@
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="H28:I28"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2829,7 +2832,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
@@ -2837,7 +2840,7 @@
       <c r="D1" s="25"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
@@ -2851,11 +2854,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="28" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="28" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="25"/>
@@ -2864,7 +2867,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="28"/>
+      <c r="B5" s="27"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
     </row>
@@ -2872,7 +2875,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="27"/>
+      <c r="B6" s="26"/>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
     </row>
@@ -2880,7 +2883,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="28"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
     </row>
@@ -2888,7 +2891,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="27"/>
+      <c r="B8" s="26"/>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
     </row>
@@ -2896,7 +2899,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="29">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -2945,19 +2948,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="25"/>
       <c r="H1" s="25"/>
       <c r="I1" s="25"/>
-      <c r="K1" s="26" t="s">
+      <c r="K1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="25"/>
@@ -2965,19 +2968,19 @@
       <c r="N1" s="25"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
       <c r="I2" s="25"/>
-      <c r="K2" s="26" t="s">
+      <c r="K2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="25"/>
@@ -2999,27 +3002,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="28" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="25"/>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="25"/>
-      <c r="H4" s="29" t="s">
+      <c r="H4" s="28" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="25"/>
-      <c r="K4" s="29" t="s">
+      <c r="K4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="25"/>
-      <c r="M4" s="29" t="s">
+      <c r="M4" s="28" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="25"/>
@@ -3028,19 +3031,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="28"/>
+      <c r="B5" s="27"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="28"/>
+      <c r="G5" s="27"/>
       <c r="H5" s="25"/>
       <c r="I5" s="25"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="28"/>
+      <c r="L5" s="27"/>
       <c r="M5" s="25"/>
       <c r="N5" s="25"/>
     </row>
@@ -3048,19 +3051,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="27"/>
+      <c r="B6" s="26"/>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="27"/>
+      <c r="G6" s="26"/>
       <c r="H6" s="25"/>
       <c r="I6" s="25"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="27"/>
+      <c r="L6" s="26"/>
       <c r="M6" s="25"/>
       <c r="N6" s="25"/>
     </row>
@@ -3068,19 +3071,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="28"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="28"/>
+      <c r="G7" s="27"/>
       <c r="H7" s="25"/>
       <c r="I7" s="25"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="28"/>
+      <c r="L7" s="27"/>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
     </row>
@@ -3088,19 +3091,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="27"/>
+      <c r="B8" s="26"/>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="27"/>
+      <c r="G8" s="26"/>
       <c r="H8" s="25"/>
       <c r="I8" s="25"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="27"/>
+      <c r="L8" s="26"/>
       <c r="M8" s="25"/>
       <c r="N8" s="25"/>
     </row>
@@ -3108,19 +3111,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="28"/>
+      <c r="B9" s="27"/>
       <c r="C9" s="25"/>
       <c r="D9" s="25"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="28"/>
+      <c r="G9" s="27"/>
       <c r="H9" s="25"/>
       <c r="I9" s="25"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="28"/>
+      <c r="L9" s="27"/>
       <c r="M9" s="25"/>
       <c r="N9" s="25"/>
     </row>
@@ -3128,19 +3131,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="27"/>
+      <c r="B10" s="26"/>
       <c r="C10" s="25"/>
       <c r="D10" s="25"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="27"/>
+      <c r="G10" s="26"/>
       <c r="H10" s="25"/>
       <c r="I10" s="25"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="27"/>
+      <c r="L10" s="26"/>
       <c r="M10" s="25"/>
       <c r="N10" s="25"/>
     </row>
@@ -3148,19 +3151,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="28"/>
+      <c r="B11" s="27"/>
       <c r="C11" s="25"/>
       <c r="D11" s="25"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="28"/>
+      <c r="G11" s="27"/>
       <c r="H11" s="25"/>
       <c r="I11" s="25"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="28"/>
+      <c r="L11" s="27"/>
       <c r="M11" s="25"/>
       <c r="N11" s="25"/>
     </row>
@@ -3168,19 +3171,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="27"/>
+      <c r="B12" s="26"/>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="27"/>
+      <c r="G12" s="26"/>
       <c r="H12" s="25"/>
       <c r="I12" s="25"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="27"/>
+      <c r="L12" s="26"/>
       <c r="M12" s="25"/>
       <c r="N12" s="25"/>
     </row>
@@ -3188,7 +3191,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="29">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3197,7 +3200,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="30">
+      <c r="G13" s="29">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3206,7 +3209,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="30">
+      <c r="L13" s="29">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3242,19 +3245,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
-      <c r="F25" s="26" t="s">
+      <c r="F25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
       <c r="I25" s="25"/>
-      <c r="K25" s="26" t="s">
+      <c r="K25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="25"/>
@@ -3262,19 +3265,19 @@
       <c r="N25" s="25"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
-      <c r="F26" s="26" t="s">
+      <c r="F26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="25"/>
       <c r="H26" s="25"/>
       <c r="I26" s="25"/>
-      <c r="K26" s="26" t="s">
+      <c r="K26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="25"/>
@@ -3296,27 +3299,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="25"/>
-      <c r="C28" s="29" t="s">
+      <c r="C28" s="28" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="25"/>
-      <c r="F28" s="29" t="s">
+      <c r="F28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="25"/>
-      <c r="H28" s="29" t="s">
+      <c r="H28" s="28" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="25"/>
-      <c r="K28" s="29" t="s">
+      <c r="K28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="25"/>
-      <c r="M28" s="29" t="s">
+      <c r="M28" s="28" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="25"/>
@@ -3325,19 +3328,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="28"/>
+      <c r="B29" s="27"/>
       <c r="C29" s="25"/>
       <c r="D29" s="25"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="28"/>
+      <c r="G29" s="27"/>
       <c r="H29" s="25"/>
       <c r="I29" s="25"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="28"/>
+      <c r="L29" s="27"/>
       <c r="M29" s="25"/>
       <c r="N29" s="25"/>
     </row>
@@ -3345,19 +3348,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="27"/>
+      <c r="B30" s="26"/>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="27"/>
+      <c r="G30" s="26"/>
       <c r="H30" s="25"/>
       <c r="I30" s="25"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="27"/>
+      <c r="L30" s="26"/>
       <c r="M30" s="25"/>
       <c r="N30" s="25"/>
     </row>
@@ -3365,19 +3368,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="28"/>
+      <c r="B31" s="27"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="28"/>
+      <c r="G31" s="27"/>
       <c r="H31" s="25"/>
       <c r="I31" s="25"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="28"/>
+      <c r="L31" s="27"/>
       <c r="M31" s="25"/>
       <c r="N31" s="25"/>
     </row>
@@ -3385,19 +3388,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="27"/>
+      <c r="B32" s="26"/>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="27"/>
+      <c r="G32" s="26"/>
       <c r="H32" s="25"/>
       <c r="I32" s="25"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="27"/>
+      <c r="L32" s="26"/>
       <c r="M32" s="25"/>
       <c r="N32" s="25"/>
     </row>
@@ -3405,19 +3408,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="28"/>
+      <c r="B33" s="27"/>
       <c r="C33" s="25"/>
       <c r="D33" s="25"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="28"/>
+      <c r="G33" s="27"/>
       <c r="H33" s="25"/>
       <c r="I33" s="25"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="28"/>
+      <c r="L33" s="27"/>
       <c r="M33" s="25"/>
       <c r="N33" s="25"/>
     </row>
@@ -3425,19 +3428,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="27"/>
+      <c r="B34" s="26"/>
       <c r="C34" s="25"/>
       <c r="D34" s="25"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="27"/>
+      <c r="G34" s="26"/>
       <c r="H34" s="25"/>
       <c r="I34" s="25"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="27"/>
+      <c r="L34" s="26"/>
       <c r="M34" s="25"/>
       <c r="N34" s="25"/>
     </row>
@@ -3445,19 +3448,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="28"/>
+      <c r="B35" s="27"/>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="28"/>
+      <c r="G35" s="27"/>
       <c r="H35" s="25"/>
       <c r="I35" s="25"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="28"/>
+      <c r="L35" s="27"/>
       <c r="M35" s="25"/>
       <c r="N35" s="25"/>
     </row>
@@ -3465,19 +3468,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="27"/>
+      <c r="B36" s="26"/>
       <c r="C36" s="25"/>
       <c r="D36" s="25"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="27"/>
+      <c r="G36" s="26"/>
       <c r="H36" s="25"/>
       <c r="I36" s="25"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="27"/>
+      <c r="L36" s="26"/>
       <c r="M36" s="25"/>
       <c r="N36" s="25"/>
     </row>
@@ -3485,7 +3488,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="30">
+      <c r="B37" s="29">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -3494,7 +3497,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="30">
+      <c r="G37" s="29">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -3503,7 +3506,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="30">
+      <c r="L37" s="29">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -3540,6 +3543,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
     <mergeCell ref="G36:I36"/>
     <mergeCell ref="L32:N32"/>
     <mergeCell ref="L13:N13"/>
@@ -3556,68 +3621,6 @@
     <mergeCell ref="L33:N33"/>
     <mergeCell ref="L35:N35"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="L9:N9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25EA17D5-9DDE-4CD8-A13C-03A64CE64AC0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CE75BEB-D0D0-4C83-8496-73A3051CF8CD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -427,6 +427,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -437,9 +440,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -774,14 +774,14 @@
       </c>
       <c r="G5" s="14">
         <f>SUM(G6:G7)</f>
-        <v>800</v>
+        <v>350</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="L5" s="14">
         <f>SUM(L6:L7)</f>
-        <v>0</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
@@ -795,12 +795,14 @@
         <v>21</v>
       </c>
       <c r="G6" s="14">
-        <v>800</v>
+        <v>350</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="L6" s="14"/>
+      <c r="L6" s="14">
+        <v>1600</v>
+      </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
@@ -838,7 +840,7 @@
       </c>
       <c r="L8" s="15">
         <f>SUM(L9:L10)</f>
-        <v>149</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1">
@@ -854,8 +856,7 @@
         <v>21</v>
       </c>
       <c r="L9" s="15">
-        <f>540-391</f>
-        <v>149</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
@@ -929,21 +930,21 @@
       </c>
       <c r="B14" s="15">
         <f>SUM(B15:B16)</f>
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>25</v>
       </c>
       <c r="G14" s="15">
         <f>SUM(G15:G16)</f>
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="K14" s="9" t="s">
         <v>25</v>
       </c>
       <c r="L14" s="15">
         <f>SUM(L15:L16)</f>
-        <v>220</v>
+        <v>900</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1">
@@ -951,17 +952,19 @@
         <v>21</v>
       </c>
       <c r="B15" s="15">
-        <v>200</v>
+        <v>160</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="15"/>
+      <c r="G15" s="15">
+        <v>44</v>
+      </c>
       <c r="K15" s="9" t="s">
         <v>21</v>
       </c>
       <c r="L15" s="15">
-        <v>220</v>
+        <v>900</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1">
@@ -984,7 +987,7 @@
       </c>
       <c r="B17" s="14">
         <f>SUM(B18:B19)</f>
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>26</v>
@@ -1005,9 +1008,7 @@
       <c r="A18" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="14">
-        <v>80</v>
-      </c>
+      <c r="B18" s="14"/>
       <c r="F18" s="7" t="s">
         <v>21</v>
       </c>
@@ -1088,7 +1089,7 @@
       </c>
       <c r="B23" s="14">
         <f>SUM(B24:B25)</f>
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>28</v>
@@ -1109,7 +1110,9 @@
       <c r="A24" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="14"/>
+      <c r="B24" s="14">
+        <v>130</v>
+      </c>
       <c r="F24" s="7" t="s">
         <v>21</v>
       </c>
@@ -1190,21 +1193,21 @@
       </c>
       <c r="B29" s="14">
         <f>SUM(B30:B31)</f>
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>30</v>
       </c>
       <c r="G29" s="14">
         <f>SUM(G30:G31)</f>
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K29" s="7" t="s">
         <v>30</v>
       </c>
       <c r="L29" s="14">
         <f>SUM(L30:L31)</f>
-        <v>360</v>
+        <v>400</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1">
@@ -1212,19 +1215,19 @@
         <v>21</v>
       </c>
       <c r="B30" s="14">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>21</v>
       </c>
       <c r="G30" s="14">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="K30" s="7" t="s">
         <v>21</v>
       </c>
       <c r="L30" s="14">
-        <v>360</v>
+        <v>400</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1">
@@ -1247,21 +1250,21 @@
       </c>
       <c r="B32" s="15">
         <f>SUM(B33:B34)</f>
-        <v>140</v>
+        <v>45</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>31</v>
       </c>
       <c r="G32" s="15">
         <f>SUM(G33:G34)</f>
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="K32" s="9" t="s">
         <v>31</v>
       </c>
       <c r="L32" s="15">
         <f>SUM(L33:L34)</f>
-        <v>600</v>
+        <v>240</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
@@ -1269,19 +1272,19 @@
         <v>21</v>
       </c>
       <c r="B33" s="15">
-        <v>140</v>
+        <v>45</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>21</v>
       </c>
       <c r="G33" s="15">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="K33" s="9" t="s">
         <v>21</v>
       </c>
       <c r="L33" s="15">
-        <v>600</v>
+        <v>240</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
@@ -1406,21 +1409,21 @@
       </c>
       <c r="B41" s="13">
         <f>SUM(B5,B8,B11,B14,B17,B20,B23,B26,B29,B32,B35,B38)</f>
-        <v>2590</v>
+        <v>2451</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G41" s="13">
         <f>SUM(G5,G8,G11,G14,G17,G20,G23,G26,G29,G32,G35,G38)</f>
-        <v>908</v>
+        <v>440</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="L41" s="13">
         <f>SUM(L5,L8,L11,L14,L17,L20,L23,L26,L29,L32,L35,L38)</f>
-        <v>1329</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1">
@@ -1669,7 +1672,7 @@
       </c>
       <c r="B62" s="15">
         <f>SUM(B63:B64)</f>
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>25</v>
@@ -1691,7 +1694,7 @@
         <v>21</v>
       </c>
       <c r="B63" s="15">
-        <v>3</v>
+        <v>64</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>21</v>
@@ -1928,7 +1931,7 @@
       </c>
       <c r="B77" s="14">
         <f>SUM(B78:B79)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F77" s="7" t="s">
         <v>30</v>
@@ -1949,9 +1952,7 @@
       <c r="A78" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B78" s="14">
-        <v>5</v>
-      </c>
+      <c r="B78" s="14"/>
       <c r="F78" s="7" t="s">
         <v>21</v>
       </c>
@@ -2083,7 +2084,7 @@
       </c>
       <c r="B86" s="15">
         <f>SUM(B87:B88)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F86" s="9" t="s">
         <v>72</v>
@@ -2104,9 +2105,7 @@
       <c r="A87" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B87" s="15">
-        <v>5</v>
-      </c>
+      <c r="B87" s="15"/>
       <c r="F87" s="9" t="s">
         <v>21</v>
       </c>
@@ -2136,7 +2135,7 @@
       </c>
       <c r="B89" s="13">
         <f>SUM(B53,B56,B59,B62,B65,B68,B71,B74,B77,B80,B83,B86)</f>
-        <v>13</v>
+        <v>64</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>34</v>
@@ -2200,19 +2199,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="25"/>
       <c r="H1" s="25"/>
       <c r="I1" s="25"/>
-      <c r="K1" s="30" t="s">
+      <c r="K1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="25"/>
@@ -2220,19 +2219,19 @@
       <c r="N1" s="25"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
-      <c r="F2" s="30" t="s">
+      <c r="F2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
       <c r="I2" s="25"/>
-      <c r="K2" s="30" t="s">
+      <c r="K2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="25"/>
@@ -2254,27 +2253,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="29" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="25"/>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="25"/>
-      <c r="H4" s="28" t="s">
+      <c r="H4" s="29" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="25"/>
-      <c r="K4" s="28" t="s">
+      <c r="K4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="25"/>
-      <c r="M4" s="28" t="s">
+      <c r="M4" s="29" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="25"/>
@@ -2283,7 +2282,7 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="28">
         <v>352</v>
       </c>
       <c r="C5" s="25"/>
@@ -2291,13 +2290,13 @@
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="27"/>
+      <c r="G5" s="28"/>
       <c r="H5" s="25"/>
       <c r="I5" s="25"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="27"/>
+      <c r="L5" s="28"/>
       <c r="M5" s="25"/>
       <c r="N5" s="25"/>
     </row>
@@ -2305,7 +2304,7 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="27">
         <v>376</v>
       </c>
       <c r="C6" s="25"/>
@@ -2313,13 +2312,13 @@
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="26"/>
+      <c r="G6" s="27"/>
       <c r="H6" s="25"/>
       <c r="I6" s="25"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="26"/>
+      <c r="L6" s="27"/>
       <c r="M6" s="25"/>
       <c r="N6" s="25"/>
     </row>
@@ -2327,7 +2326,7 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="28">
         <v>0</v>
       </c>
       <c r="C7" s="25"/>
@@ -2335,13 +2334,13 @@
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="27"/>
+      <c r="G7" s="28"/>
       <c r="H7" s="25"/>
       <c r="I7" s="25"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="27"/>
+      <c r="L7" s="28"/>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
     </row>
@@ -2349,7 +2348,7 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="27">
         <v>724</v>
       </c>
       <c r="C8" s="25"/>
@@ -2357,13 +2356,13 @@
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="26"/>
+      <c r="G8" s="27"/>
       <c r="H8" s="25"/>
       <c r="I8" s="25"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="26"/>
+      <c r="L8" s="27"/>
       <c r="M8" s="25"/>
       <c r="N8" s="25"/>
     </row>
@@ -2371,7 +2370,7 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="27">
+      <c r="B9" s="28">
         <v>411</v>
       </c>
       <c r="C9" s="25"/>
@@ -2379,13 +2378,13 @@
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="27"/>
+      <c r="G9" s="28"/>
       <c r="H9" s="25"/>
       <c r="I9" s="25"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="27"/>
+      <c r="L9" s="28"/>
       <c r="M9" s="25"/>
       <c r="N9" s="25"/>
     </row>
@@ -2393,7 +2392,7 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="27">
         <v>0</v>
       </c>
       <c r="C10" s="25"/>
@@ -2401,13 +2400,13 @@
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="26"/>
+      <c r="G10" s="27"/>
       <c r="H10" s="25"/>
       <c r="I10" s="25"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="26"/>
+      <c r="L10" s="27"/>
       <c r="M10" s="25"/>
       <c r="N10" s="25"/>
     </row>
@@ -2415,7 +2414,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="30">
         <f>SUM(B5:B10)</f>
         <v>1863</v>
       </c>
@@ -2424,7 +2423,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="29">
+      <c r="G11" s="30">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -2433,7 +2432,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="29">
+      <c r="L11" s="30">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -2469,19 +2468,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
-      <c r="F25" s="30" t="s">
+      <c r="F25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
       <c r="I25" s="25"/>
-      <c r="K25" s="30" t="s">
+      <c r="K25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="25"/>
@@ -2489,19 +2488,19 @@
       <c r="N25" s="25"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
-      <c r="F26" s="30" t="s">
+      <c r="F26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="25"/>
       <c r="H26" s="25"/>
       <c r="I26" s="25"/>
-      <c r="K26" s="30" t="s">
+      <c r="K26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="25"/>
@@ -2523,27 +2522,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="25"/>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="29" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="25"/>
-      <c r="F28" s="28" t="s">
+      <c r="F28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="25"/>
-      <c r="H28" s="28" t="s">
+      <c r="H28" s="29" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="25"/>
-      <c r="K28" s="28" t="s">
+      <c r="K28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="25"/>
-      <c r="M28" s="28" t="s">
+      <c r="M28" s="29" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="25"/>
@@ -2552,7 +2551,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="27">
+      <c r="B29" s="28">
         <v>0</v>
       </c>
       <c r="C29" s="25"/>
@@ -2560,13 +2559,13 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="27"/>
+      <c r="G29" s="28"/>
       <c r="H29" s="25"/>
       <c r="I29" s="25"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="27">
+      <c r="L29" s="28">
         <v>14</v>
       </c>
       <c r="M29" s="25"/>
@@ -2576,7 +2575,7 @@
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="26">
+      <c r="B30" s="27">
         <v>0</v>
       </c>
       <c r="C30" s="25"/>
@@ -2584,13 +2583,13 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="26"/>
+      <c r="G30" s="27"/>
       <c r="H30" s="25"/>
       <c r="I30" s="25"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="26">
+      <c r="L30" s="27">
         <v>605</v>
       </c>
       <c r="M30" s="25"/>
@@ -2600,7 +2599,7 @@
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="27">
+      <c r="B31" s="28">
         <v>0</v>
       </c>
       <c r="C31" s="25"/>
@@ -2608,13 +2607,13 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="27"/>
+      <c r="G31" s="28"/>
       <c r="H31" s="25"/>
       <c r="I31" s="25"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="27">
+      <c r="L31" s="28">
         <v>1708</v>
       </c>
       <c r="M31" s="25"/>
@@ -2624,7 +2623,7 @@
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="26">
+      <c r="B32" s="27">
         <v>0</v>
       </c>
       <c r="C32" s="25"/>
@@ -2632,13 +2631,13 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="26"/>
+      <c r="G32" s="27"/>
       <c r="H32" s="25"/>
       <c r="I32" s="25"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="26">
+      <c r="L32" s="27">
         <v>1395</v>
       </c>
       <c r="M32" s="25"/>
@@ -2648,7 +2647,7 @@
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="27">
+      <c r="B33" s="28">
         <v>0</v>
       </c>
       <c r="C33" s="25"/>
@@ -2656,13 +2655,13 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="27"/>
+      <c r="G33" s="28"/>
       <c r="H33" s="25"/>
       <c r="I33" s="25"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="27">
+      <c r="L33" s="28">
         <v>0</v>
       </c>
       <c r="M33" s="25"/>
@@ -2672,7 +2671,7 @@
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="26">
+      <c r="B34" s="27">
         <v>0</v>
       </c>
       <c r="C34" s="25"/>
@@ -2680,13 +2679,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="26"/>
+      <c r="G34" s="27"/>
       <c r="H34" s="25"/>
       <c r="I34" s="25"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="26">
+      <c r="L34" s="27">
         <v>0</v>
       </c>
       <c r="M34" s="25"/>
@@ -2696,7 +2695,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="29">
+      <c r="B35" s="30">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -2705,7 +2704,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="29">
+      <c r="G35" s="30">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -2714,7 +2713,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="29">
+      <c r="L35" s="30">
         <f>SUM(L29:L34)</f>
         <v>3722</v>
       </c>
@@ -2751,13 +2750,49 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="L11:N11"/>
@@ -2774,49 +2809,13 @@
     <mergeCell ref="K2:N2"/>
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2832,7 +2831,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
@@ -2840,7 +2839,7 @@
       <c r="D1" s="25"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
@@ -2854,11 +2853,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="29" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="29" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="25"/>
@@ -2867,7 +2866,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="27"/>
+      <c r="B5" s="28"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
     </row>
@@ -2875,7 +2874,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="26"/>
+      <c r="B6" s="27"/>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
     </row>
@@ -2883,7 +2882,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="27"/>
+      <c r="B7" s="28"/>
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
     </row>
@@ -2891,7 +2890,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="26"/>
+      <c r="B8" s="27"/>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
     </row>
@@ -2899,7 +2898,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="30">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -2948,19 +2947,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="25"/>
       <c r="H1" s="25"/>
       <c r="I1" s="25"/>
-      <c r="K1" s="30" t="s">
+      <c r="K1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="25"/>
@@ -2968,19 +2967,19 @@
       <c r="N1" s="25"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
-      <c r="F2" s="30" t="s">
+      <c r="F2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
       <c r="I2" s="25"/>
-      <c r="K2" s="30" t="s">
+      <c r="K2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="25"/>
@@ -3002,27 +3001,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="29" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="25"/>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="25"/>
-      <c r="H4" s="28" t="s">
+      <c r="H4" s="29" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="25"/>
-      <c r="K4" s="28" t="s">
+      <c r="K4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="25"/>
-      <c r="M4" s="28" t="s">
+      <c r="M4" s="29" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="25"/>
@@ -3031,19 +3030,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="27"/>
+      <c r="B5" s="28"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="27"/>
+      <c r="G5" s="28"/>
       <c r="H5" s="25"/>
       <c r="I5" s="25"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="27"/>
+      <c r="L5" s="28"/>
       <c r="M5" s="25"/>
       <c r="N5" s="25"/>
     </row>
@@ -3051,19 +3050,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="26"/>
+      <c r="B6" s="27"/>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="26"/>
+      <c r="G6" s="27"/>
       <c r="H6" s="25"/>
       <c r="I6" s="25"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="26"/>
+      <c r="L6" s="27"/>
       <c r="M6" s="25"/>
       <c r="N6" s="25"/>
     </row>
@@ -3071,19 +3070,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="27"/>
+      <c r="B7" s="28"/>
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="27"/>
+      <c r="G7" s="28"/>
       <c r="H7" s="25"/>
       <c r="I7" s="25"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="27"/>
+      <c r="L7" s="28"/>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
     </row>
@@ -3091,19 +3090,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="26"/>
+      <c r="B8" s="27"/>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="26"/>
+      <c r="G8" s="27"/>
       <c r="H8" s="25"/>
       <c r="I8" s="25"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="26"/>
+      <c r="L8" s="27"/>
       <c r="M8" s="25"/>
       <c r="N8" s="25"/>
     </row>
@@ -3111,19 +3110,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="27"/>
+      <c r="B9" s="28"/>
       <c r="C9" s="25"/>
       <c r="D9" s="25"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="27"/>
+      <c r="G9" s="28"/>
       <c r="H9" s="25"/>
       <c r="I9" s="25"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="27"/>
+      <c r="L9" s="28"/>
       <c r="M9" s="25"/>
       <c r="N9" s="25"/>
     </row>
@@ -3131,19 +3130,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="26"/>
+      <c r="B10" s="27"/>
       <c r="C10" s="25"/>
       <c r="D10" s="25"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="26"/>
+      <c r="G10" s="27"/>
       <c r="H10" s="25"/>
       <c r="I10" s="25"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="26"/>
+      <c r="L10" s="27"/>
       <c r="M10" s="25"/>
       <c r="N10" s="25"/>
     </row>
@@ -3151,19 +3150,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="27"/>
+      <c r="B11" s="28"/>
       <c r="C11" s="25"/>
       <c r="D11" s="25"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="27"/>
+      <c r="G11" s="28"/>
       <c r="H11" s="25"/>
       <c r="I11" s="25"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="27"/>
+      <c r="L11" s="28"/>
       <c r="M11" s="25"/>
       <c r="N11" s="25"/>
     </row>
@@ -3171,19 +3170,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="26"/>
+      <c r="B12" s="27"/>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="26"/>
+      <c r="G12" s="27"/>
       <c r="H12" s="25"/>
       <c r="I12" s="25"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="26"/>
+      <c r="L12" s="27"/>
       <c r="M12" s="25"/>
       <c r="N12" s="25"/>
     </row>
@@ -3191,7 +3190,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="30">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3200,7 +3199,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="29">
+      <c r="G13" s="30">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3209,7 +3208,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="29">
+      <c r="L13" s="30">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3245,19 +3244,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
-      <c r="F25" s="30" t="s">
+      <c r="F25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
       <c r="I25" s="25"/>
-      <c r="K25" s="30" t="s">
+      <c r="K25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="25"/>
@@ -3265,19 +3264,19 @@
       <c r="N25" s="25"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
-      <c r="F26" s="30" t="s">
+      <c r="F26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="25"/>
       <c r="H26" s="25"/>
       <c r="I26" s="25"/>
-      <c r="K26" s="30" t="s">
+      <c r="K26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="25"/>
@@ -3299,27 +3298,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="25"/>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="29" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="25"/>
-      <c r="F28" s="28" t="s">
+      <c r="F28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="25"/>
-      <c r="H28" s="28" t="s">
+      <c r="H28" s="29" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="25"/>
-      <c r="K28" s="28" t="s">
+      <c r="K28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="25"/>
-      <c r="M28" s="28" t="s">
+      <c r="M28" s="29" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="25"/>
@@ -3328,19 +3327,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="27"/>
+      <c r="B29" s="28"/>
       <c r="C29" s="25"/>
       <c r="D29" s="25"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="27"/>
+      <c r="G29" s="28"/>
       <c r="H29" s="25"/>
       <c r="I29" s="25"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="27"/>
+      <c r="L29" s="28"/>
       <c r="M29" s="25"/>
       <c r="N29" s="25"/>
     </row>
@@ -3348,19 +3347,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="26"/>
+      <c r="B30" s="27"/>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="26"/>
+      <c r="G30" s="27"/>
       <c r="H30" s="25"/>
       <c r="I30" s="25"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="26"/>
+      <c r="L30" s="27"/>
       <c r="M30" s="25"/>
       <c r="N30" s="25"/>
     </row>
@@ -3368,19 +3367,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="27"/>
+      <c r="B31" s="28"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="27"/>
+      <c r="G31" s="28"/>
       <c r="H31" s="25"/>
       <c r="I31" s="25"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="27"/>
+      <c r="L31" s="28"/>
       <c r="M31" s="25"/>
       <c r="N31" s="25"/>
     </row>
@@ -3388,19 +3387,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="26"/>
+      <c r="B32" s="27"/>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="26"/>
+      <c r="G32" s="27"/>
       <c r="H32" s="25"/>
       <c r="I32" s="25"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="26"/>
+      <c r="L32" s="27"/>
       <c r="M32" s="25"/>
       <c r="N32" s="25"/>
     </row>
@@ -3408,19 +3407,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="27"/>
+      <c r="B33" s="28"/>
       <c r="C33" s="25"/>
       <c r="D33" s="25"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="27"/>
+      <c r="G33" s="28"/>
       <c r="H33" s="25"/>
       <c r="I33" s="25"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="27"/>
+      <c r="L33" s="28"/>
       <c r="M33" s="25"/>
       <c r="N33" s="25"/>
     </row>
@@ -3428,19 +3427,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="26"/>
+      <c r="B34" s="27"/>
       <c r="C34" s="25"/>
       <c r="D34" s="25"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="26"/>
+      <c r="G34" s="27"/>
       <c r="H34" s="25"/>
       <c r="I34" s="25"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="26"/>
+      <c r="L34" s="27"/>
       <c r="M34" s="25"/>
       <c r="N34" s="25"/>
     </row>
@@ -3448,19 +3447,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="27"/>
+      <c r="B35" s="28"/>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="27"/>
+      <c r="G35" s="28"/>
       <c r="H35" s="25"/>
       <c r="I35" s="25"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="27"/>
+      <c r="L35" s="28"/>
       <c r="M35" s="25"/>
       <c r="N35" s="25"/>
     </row>
@@ -3468,19 +3467,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="26"/>
+      <c r="B36" s="27"/>
       <c r="C36" s="25"/>
       <c r="D36" s="25"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="26"/>
+      <c r="G36" s="27"/>
       <c r="H36" s="25"/>
       <c r="I36" s="25"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="26"/>
+      <c r="L36" s="27"/>
       <c r="M36" s="25"/>
       <c r="N36" s="25"/>
     </row>
@@ -3488,7 +3487,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="29">
+      <c r="B37" s="30">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -3497,7 +3496,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="29">
+      <c r="G37" s="30">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -3506,7 +3505,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="29">
+      <c r="L37" s="30">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -3543,6 +3542,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
     <mergeCell ref="L34:N34"/>
     <mergeCell ref="L6:N6"/>
     <mergeCell ref="B33:D33"/>
@@ -3559,68 +3620,6 @@
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3668,7 +3667,7 @@
         <v>49</v>
       </c>
       <c r="E2" s="18">
-        <v>110</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3685,7 +3684,7 @@
         <v>68</v>
       </c>
       <c r="E3" s="18">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3702,7 +3701,7 @@
         <v>49</v>
       </c>
       <c r="E4" s="18">
-        <v>110</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3719,7 +3718,7 @@
         <v>68</v>
       </c>
       <c r="E5" s="18">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -3736,7 +3735,7 @@
         <v>49</v>
       </c>
       <c r="E6" s="18">
-        <v>110</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -3753,7 +3752,7 @@
         <v>68</v>
       </c>
       <c r="E7" s="18">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4068,7 +4067,7 @@
         <v>49</v>
       </c>
       <c r="E26" s="18">
-        <v>120</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -4102,7 +4101,7 @@
         <v>49</v>
       </c>
       <c r="E28" s="18">
-        <v>120</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -4136,7 +4135,7 @@
         <v>49</v>
       </c>
       <c r="E30" s="18">
-        <v>120</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31" spans="1:5">

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CE75BEB-D0D0-4C83-8496-73A3051CF8CD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9761C91-DC72-4B15-8BB4-4ACE8DCEF70F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -427,9 +427,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -440,6 +437,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -767,7 +767,7 @@
       </c>
       <c r="B5" s="21">
         <f>SUM(B6:B7)</f>
-        <v>2100</v>
+        <v>200</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>20</v>
@@ -789,7 +789,7 @@
         <v>21</v>
       </c>
       <c r="B6" s="14">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>21</v>
@@ -808,9 +808,7 @@
       <c r="A7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="14">
-        <v>1800</v>
-      </c>
+      <c r="B7" s="14"/>
       <c r="F7" s="7" t="s">
         <v>22</v>
       </c>
@@ -1409,7 +1407,7 @@
       </c>
       <c r="B41" s="13">
         <f>SUM(B5,B8,B11,B14,B17,B20,B23,B26,B29,B32,B35,B38)</f>
-        <v>2451</v>
+        <v>551</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>34</v>
@@ -2199,19 +2197,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="25"/>
       <c r="H1" s="25"/>
       <c r="I1" s="25"/>
-      <c r="K1" s="26" t="s">
+      <c r="K1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="25"/>
@@ -2219,19 +2217,19 @@
       <c r="N1" s="25"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
       <c r="I2" s="25"/>
-      <c r="K2" s="26" t="s">
+      <c r="K2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="25"/>
@@ -2253,27 +2251,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="28" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="25"/>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="25"/>
-      <c r="H4" s="29" t="s">
+      <c r="H4" s="28" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="25"/>
-      <c r="K4" s="29" t="s">
+      <c r="K4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="25"/>
-      <c r="M4" s="29" t="s">
+      <c r="M4" s="28" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="25"/>
@@ -2282,7 +2280,7 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="28">
+      <c r="B5" s="27">
         <v>352</v>
       </c>
       <c r="C5" s="25"/>
@@ -2290,13 +2288,13 @@
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="28"/>
+      <c r="G5" s="27"/>
       <c r="H5" s="25"/>
       <c r="I5" s="25"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="28"/>
+      <c r="L5" s="27"/>
       <c r="M5" s="25"/>
       <c r="N5" s="25"/>
     </row>
@@ -2304,7 +2302,7 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="26">
         <v>376</v>
       </c>
       <c r="C6" s="25"/>
@@ -2312,13 +2310,13 @@
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="27"/>
+      <c r="G6" s="26"/>
       <c r="H6" s="25"/>
       <c r="I6" s="25"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="27"/>
+      <c r="L6" s="26"/>
       <c r="M6" s="25"/>
       <c r="N6" s="25"/>
     </row>
@@ -2326,7 +2324,7 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="27">
         <v>0</v>
       </c>
       <c r="C7" s="25"/>
@@ -2334,13 +2332,13 @@
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="28"/>
+      <c r="G7" s="27"/>
       <c r="H7" s="25"/>
       <c r="I7" s="25"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="28"/>
+      <c r="L7" s="27"/>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
     </row>
@@ -2348,7 +2346,7 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="26">
         <v>724</v>
       </c>
       <c r="C8" s="25"/>
@@ -2356,13 +2354,13 @@
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="27"/>
+      <c r="G8" s="26"/>
       <c r="H8" s="25"/>
       <c r="I8" s="25"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="27"/>
+      <c r="L8" s="26"/>
       <c r="M8" s="25"/>
       <c r="N8" s="25"/>
     </row>
@@ -2370,7 +2368,7 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="28">
+      <c r="B9" s="27">
         <v>411</v>
       </c>
       <c r="C9" s="25"/>
@@ -2378,13 +2376,13 @@
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="28"/>
+      <c r="G9" s="27"/>
       <c r="H9" s="25"/>
       <c r="I9" s="25"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="28"/>
+      <c r="L9" s="27"/>
       <c r="M9" s="25"/>
       <c r="N9" s="25"/>
     </row>
@@ -2392,7 +2390,7 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="27">
+      <c r="B10" s="26">
         <v>0</v>
       </c>
       <c r="C10" s="25"/>
@@ -2400,13 +2398,13 @@
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="27"/>
+      <c r="G10" s="26"/>
       <c r="H10" s="25"/>
       <c r="I10" s="25"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="27"/>
+      <c r="L10" s="26"/>
       <c r="M10" s="25"/>
       <c r="N10" s="25"/>
     </row>
@@ -2414,7 +2412,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="29">
         <f>SUM(B5:B10)</f>
         <v>1863</v>
       </c>
@@ -2423,7 +2421,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="30">
+      <c r="G11" s="29">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -2432,7 +2430,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="30">
+      <c r="L11" s="29">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -2468,19 +2466,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
-      <c r="F25" s="26" t="s">
+      <c r="F25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
       <c r="I25" s="25"/>
-      <c r="K25" s="26" t="s">
+      <c r="K25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="25"/>
@@ -2488,19 +2486,19 @@
       <c r="N25" s="25"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
-      <c r="F26" s="26" t="s">
+      <c r="F26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="25"/>
       <c r="H26" s="25"/>
       <c r="I26" s="25"/>
-      <c r="K26" s="26" t="s">
+      <c r="K26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="25"/>
@@ -2522,27 +2520,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="25"/>
-      <c r="C28" s="29" t="s">
+      <c r="C28" s="28" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="25"/>
-      <c r="F28" s="29" t="s">
+      <c r="F28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="25"/>
-      <c r="H28" s="29" t="s">
+      <c r="H28" s="28" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="25"/>
-      <c r="K28" s="29" t="s">
+      <c r="K28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="25"/>
-      <c r="M28" s="29" t="s">
+      <c r="M28" s="28" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="25"/>
@@ -2551,7 +2549,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="28">
+      <c r="B29" s="27">
         <v>0</v>
       </c>
       <c r="C29" s="25"/>
@@ -2559,13 +2557,13 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="28"/>
+      <c r="G29" s="27"/>
       <c r="H29" s="25"/>
       <c r="I29" s="25"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="28">
+      <c r="L29" s="27">
         <v>14</v>
       </c>
       <c r="M29" s="25"/>
@@ -2575,7 +2573,7 @@
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="27">
+      <c r="B30" s="26">
         <v>0</v>
       </c>
       <c r="C30" s="25"/>
@@ -2583,13 +2581,13 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="27"/>
+      <c r="G30" s="26"/>
       <c r="H30" s="25"/>
       <c r="I30" s="25"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="27">
+      <c r="L30" s="26">
         <v>605</v>
       </c>
       <c r="M30" s="25"/>
@@ -2599,7 +2597,7 @@
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="28">
+      <c r="B31" s="27">
         <v>0</v>
       </c>
       <c r="C31" s="25"/>
@@ -2607,13 +2605,13 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="28"/>
+      <c r="G31" s="27"/>
       <c r="H31" s="25"/>
       <c r="I31" s="25"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="28">
+      <c r="L31" s="27">
         <v>1708</v>
       </c>
       <c r="M31" s="25"/>
@@ -2623,7 +2621,7 @@
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="27">
+      <c r="B32" s="26">
         <v>0</v>
       </c>
       <c r="C32" s="25"/>
@@ -2631,13 +2629,13 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="27"/>
+      <c r="G32" s="26"/>
       <c r="H32" s="25"/>
       <c r="I32" s="25"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="27">
+      <c r="L32" s="26">
         <v>1395</v>
       </c>
       <c r="M32" s="25"/>
@@ -2647,7 +2645,7 @@
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="28">
+      <c r="B33" s="27">
         <v>0</v>
       </c>
       <c r="C33" s="25"/>
@@ -2655,13 +2653,13 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="28"/>
+      <c r="G33" s="27"/>
       <c r="H33" s="25"/>
       <c r="I33" s="25"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="28">
+      <c r="L33" s="27">
         <v>0</v>
       </c>
       <c r="M33" s="25"/>
@@ -2671,7 +2669,7 @@
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="27">
+      <c r="B34" s="26">
         <v>0</v>
       </c>
       <c r="C34" s="25"/>
@@ -2679,13 +2677,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="27"/>
+      <c r="G34" s="26"/>
       <c r="H34" s="25"/>
       <c r="I34" s="25"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="27">
+      <c r="L34" s="26">
         <v>0</v>
       </c>
       <c r="M34" s="25"/>
@@ -2695,7 +2693,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="30">
+      <c r="B35" s="29">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -2704,7 +2702,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="30">
+      <c r="G35" s="29">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -2713,7 +2711,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="30">
+      <c r="L35" s="29">
         <f>SUM(L29:L34)</f>
         <v>3722</v>
       </c>
@@ -2750,6 +2748,56 @@
     </row>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B10:D10"/>
@@ -2766,56 +2814,6 @@
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="H28:I28"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2831,7 +2829,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
@@ -2839,7 +2837,7 @@
       <c r="D1" s="25"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
@@ -2853,11 +2851,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="28" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="28" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="25"/>
@@ -2866,7 +2864,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="28"/>
+      <c r="B5" s="27"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
     </row>
@@ -2874,7 +2872,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="27"/>
+      <c r="B6" s="26"/>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
     </row>
@@ -2882,7 +2880,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="28"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
     </row>
@@ -2890,7 +2888,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="27"/>
+      <c r="B8" s="26"/>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
     </row>
@@ -2898,7 +2896,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="29">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -2947,19 +2945,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="25"/>
       <c r="H1" s="25"/>
       <c r="I1" s="25"/>
-      <c r="K1" s="26" t="s">
+      <c r="K1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="25"/>
@@ -2967,19 +2965,19 @@
       <c r="N1" s="25"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
       <c r="I2" s="25"/>
-      <c r="K2" s="26" t="s">
+      <c r="K2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="25"/>
@@ -3001,27 +2999,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="28" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="25"/>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="25"/>
-      <c r="H4" s="29" t="s">
+      <c r="H4" s="28" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="25"/>
-      <c r="K4" s="29" t="s">
+      <c r="K4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="25"/>
-      <c r="M4" s="29" t="s">
+      <c r="M4" s="28" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="25"/>
@@ -3030,19 +3028,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="28"/>
+      <c r="B5" s="27"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="28"/>
+      <c r="G5" s="27"/>
       <c r="H5" s="25"/>
       <c r="I5" s="25"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="28"/>
+      <c r="L5" s="27"/>
       <c r="M5" s="25"/>
       <c r="N5" s="25"/>
     </row>
@@ -3050,19 +3048,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="27"/>
+      <c r="B6" s="26"/>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="27"/>
+      <c r="G6" s="26"/>
       <c r="H6" s="25"/>
       <c r="I6" s="25"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="27"/>
+      <c r="L6" s="26"/>
       <c r="M6" s="25"/>
       <c r="N6" s="25"/>
     </row>
@@ -3070,19 +3068,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="28"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="28"/>
+      <c r="G7" s="27"/>
       <c r="H7" s="25"/>
       <c r="I7" s="25"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="28"/>
+      <c r="L7" s="27"/>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
     </row>
@@ -3090,19 +3088,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="27"/>
+      <c r="B8" s="26"/>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="27"/>
+      <c r="G8" s="26"/>
       <c r="H8" s="25"/>
       <c r="I8" s="25"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="27"/>
+      <c r="L8" s="26"/>
       <c r="M8" s="25"/>
       <c r="N8" s="25"/>
     </row>
@@ -3110,19 +3108,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="28"/>
+      <c r="B9" s="27"/>
       <c r="C9" s="25"/>
       <c r="D9" s="25"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="28"/>
+      <c r="G9" s="27"/>
       <c r="H9" s="25"/>
       <c r="I9" s="25"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="28"/>
+      <c r="L9" s="27"/>
       <c r="M9" s="25"/>
       <c r="N9" s="25"/>
     </row>
@@ -3130,19 +3128,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="27"/>
+      <c r="B10" s="26"/>
       <c r="C10" s="25"/>
       <c r="D10" s="25"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="27"/>
+      <c r="G10" s="26"/>
       <c r="H10" s="25"/>
       <c r="I10" s="25"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="27"/>
+      <c r="L10" s="26"/>
       <c r="M10" s="25"/>
       <c r="N10" s="25"/>
     </row>
@@ -3150,19 +3148,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="28"/>
+      <c r="B11" s="27"/>
       <c r="C11" s="25"/>
       <c r="D11" s="25"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="28"/>
+      <c r="G11" s="27"/>
       <c r="H11" s="25"/>
       <c r="I11" s="25"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="28"/>
+      <c r="L11" s="27"/>
       <c r="M11" s="25"/>
       <c r="N11" s="25"/>
     </row>
@@ -3170,19 +3168,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="27"/>
+      <c r="B12" s="26"/>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="27"/>
+      <c r="G12" s="26"/>
       <c r="H12" s="25"/>
       <c r="I12" s="25"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="27"/>
+      <c r="L12" s="26"/>
       <c r="M12" s="25"/>
       <c r="N12" s="25"/>
     </row>
@@ -3190,7 +3188,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="29">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3199,7 +3197,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="30">
+      <c r="G13" s="29">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3208,7 +3206,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="30">
+      <c r="L13" s="29">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3244,19 +3242,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
-      <c r="F25" s="26" t="s">
+      <c r="F25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
       <c r="I25" s="25"/>
-      <c r="K25" s="26" t="s">
+      <c r="K25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="25"/>
@@ -3264,19 +3262,19 @@
       <c r="N25" s="25"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
-      <c r="F26" s="26" t="s">
+      <c r="F26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="25"/>
       <c r="H26" s="25"/>
       <c r="I26" s="25"/>
-      <c r="K26" s="26" t="s">
+      <c r="K26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="25"/>
@@ -3298,27 +3296,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="25"/>
-      <c r="C28" s="29" t="s">
+      <c r="C28" s="28" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="25"/>
-      <c r="F28" s="29" t="s">
+      <c r="F28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="25"/>
-      <c r="H28" s="29" t="s">
+      <c r="H28" s="28" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="25"/>
-      <c r="K28" s="29" t="s">
+      <c r="K28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="25"/>
-      <c r="M28" s="29" t="s">
+      <c r="M28" s="28" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="25"/>
@@ -3327,19 +3325,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="28"/>
+      <c r="B29" s="27"/>
       <c r="C29" s="25"/>
       <c r="D29" s="25"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="28"/>
+      <c r="G29" s="27"/>
       <c r="H29" s="25"/>
       <c r="I29" s="25"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="28"/>
+      <c r="L29" s="27"/>
       <c r="M29" s="25"/>
       <c r="N29" s="25"/>
     </row>
@@ -3347,19 +3345,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="27"/>
+      <c r="B30" s="26"/>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="27"/>
+      <c r="G30" s="26"/>
       <c r="H30" s="25"/>
       <c r="I30" s="25"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="27"/>
+      <c r="L30" s="26"/>
       <c r="M30" s="25"/>
       <c r="N30" s="25"/>
     </row>
@@ -3367,19 +3365,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="28"/>
+      <c r="B31" s="27"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="28"/>
+      <c r="G31" s="27"/>
       <c r="H31" s="25"/>
       <c r="I31" s="25"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="28"/>
+      <c r="L31" s="27"/>
       <c r="M31" s="25"/>
       <c r="N31" s="25"/>
     </row>
@@ -3387,19 +3385,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="27"/>
+      <c r="B32" s="26"/>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="27"/>
+      <c r="G32" s="26"/>
       <c r="H32" s="25"/>
       <c r="I32" s="25"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="27"/>
+      <c r="L32" s="26"/>
       <c r="M32" s="25"/>
       <c r="N32" s="25"/>
     </row>
@@ -3407,19 +3405,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="28"/>
+      <c r="B33" s="27"/>
       <c r="C33" s="25"/>
       <c r="D33" s="25"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="28"/>
+      <c r="G33" s="27"/>
       <c r="H33" s="25"/>
       <c r="I33" s="25"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="28"/>
+      <c r="L33" s="27"/>
       <c r="M33" s="25"/>
       <c r="N33" s="25"/>
     </row>
@@ -3427,19 +3425,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="27"/>
+      <c r="B34" s="26"/>
       <c r="C34" s="25"/>
       <c r="D34" s="25"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="27"/>
+      <c r="G34" s="26"/>
       <c r="H34" s="25"/>
       <c r="I34" s="25"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="27"/>
+      <c r="L34" s="26"/>
       <c r="M34" s="25"/>
       <c r="N34" s="25"/>
     </row>
@@ -3447,19 +3445,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="28"/>
+      <c r="B35" s="27"/>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="28"/>
+      <c r="G35" s="27"/>
       <c r="H35" s="25"/>
       <c r="I35" s="25"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="28"/>
+      <c r="L35" s="27"/>
       <c r="M35" s="25"/>
       <c r="N35" s="25"/>
     </row>
@@ -3467,19 +3465,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="27"/>
+      <c r="B36" s="26"/>
       <c r="C36" s="25"/>
       <c r="D36" s="25"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="27"/>
+      <c r="G36" s="26"/>
       <c r="H36" s="25"/>
       <c r="I36" s="25"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="27"/>
+      <c r="L36" s="26"/>
       <c r="M36" s="25"/>
       <c r="N36" s="25"/>
     </row>
@@ -3487,7 +3485,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="30">
+      <c r="B37" s="29">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -3496,7 +3494,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="30">
+      <c r="G37" s="29">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -3505,7 +3503,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="30">
+      <c r="L37" s="29">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -3542,6 +3540,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
     <mergeCell ref="G36:I36"/>
     <mergeCell ref="L32:N32"/>
     <mergeCell ref="L13:N13"/>
@@ -3558,68 +3618,6 @@
     <mergeCell ref="L33:N33"/>
     <mergeCell ref="L35:N35"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="L9:N9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9761C91-DC72-4B15-8BB4-4ACE8DCEF70F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAD7ACD1-A363-4AA7-B037-36CF35058BBD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -427,6 +427,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -437,9 +440,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -767,21 +767,21 @@
       </c>
       <c r="B5" s="21">
         <f>SUM(B6:B7)</f>
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G5" s="14">
         <f>SUM(G6:G7)</f>
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="L5" s="14">
         <f>SUM(L6:L7)</f>
-        <v>1600</v>
+        <v>480</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
@@ -789,19 +789,19 @@
         <v>21</v>
       </c>
       <c r="B6" s="14">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>21</v>
       </c>
       <c r="G6" s="14">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>21</v>
       </c>
       <c r="L6" s="14">
-        <v>1600</v>
+        <v>480</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
@@ -1407,21 +1407,21 @@
       </c>
       <c r="B41" s="13">
         <f>SUM(B5,B8,B11,B14,B17,B20,B23,B26,B29,B32,B35,B38)</f>
-        <v>551</v>
+        <v>951</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G41" s="13">
         <f>SUM(G5,G8,G11,G14,G17,G20,G23,G26,G29,G32,G35,G38)</f>
-        <v>440</v>
+        <v>340</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="L41" s="13">
         <f>SUM(L5,L8,L11,L14,L17,L20,L23,L26,L29,L32,L35,L38)</f>
-        <v>3200</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1">
@@ -2197,19 +2197,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="25"/>
       <c r="H1" s="25"/>
       <c r="I1" s="25"/>
-      <c r="K1" s="30" t="s">
+      <c r="K1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="25"/>
@@ -2217,19 +2217,19 @@
       <c r="N1" s="25"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
-      <c r="F2" s="30" t="s">
+      <c r="F2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
       <c r="I2" s="25"/>
-      <c r="K2" s="30" t="s">
+      <c r="K2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="25"/>
@@ -2251,27 +2251,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="29" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="25"/>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="25"/>
-      <c r="H4" s="28" t="s">
+      <c r="H4" s="29" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="25"/>
-      <c r="K4" s="28" t="s">
+      <c r="K4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="25"/>
-      <c r="M4" s="28" t="s">
+      <c r="M4" s="29" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="25"/>
@@ -2280,7 +2280,7 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="28">
         <v>352</v>
       </c>
       <c r="C5" s="25"/>
@@ -2288,13 +2288,13 @@
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="27"/>
+      <c r="G5" s="28"/>
       <c r="H5" s="25"/>
       <c r="I5" s="25"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="27"/>
+      <c r="L5" s="28"/>
       <c r="M5" s="25"/>
       <c r="N5" s="25"/>
     </row>
@@ -2302,7 +2302,7 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="27">
         <v>376</v>
       </c>
       <c r="C6" s="25"/>
@@ -2310,13 +2310,13 @@
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="26"/>
+      <c r="G6" s="27"/>
       <c r="H6" s="25"/>
       <c r="I6" s="25"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="26"/>
+      <c r="L6" s="27"/>
       <c r="M6" s="25"/>
       <c r="N6" s="25"/>
     </row>
@@ -2324,7 +2324,7 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="28">
         <v>0</v>
       </c>
       <c r="C7" s="25"/>
@@ -2332,13 +2332,13 @@
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="27"/>
+      <c r="G7" s="28"/>
       <c r="H7" s="25"/>
       <c r="I7" s="25"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="27"/>
+      <c r="L7" s="28"/>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
     </row>
@@ -2346,7 +2346,7 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="27">
         <v>724</v>
       </c>
       <c r="C8" s="25"/>
@@ -2354,13 +2354,13 @@
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="26"/>
+      <c r="G8" s="27"/>
       <c r="H8" s="25"/>
       <c r="I8" s="25"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="26"/>
+      <c r="L8" s="27"/>
       <c r="M8" s="25"/>
       <c r="N8" s="25"/>
     </row>
@@ -2368,7 +2368,7 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="27">
+      <c r="B9" s="28">
         <v>411</v>
       </c>
       <c r="C9" s="25"/>
@@ -2376,13 +2376,13 @@
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="27"/>
+      <c r="G9" s="28"/>
       <c r="H9" s="25"/>
       <c r="I9" s="25"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="27"/>
+      <c r="L9" s="28"/>
       <c r="M9" s="25"/>
       <c r="N9" s="25"/>
     </row>
@@ -2390,7 +2390,7 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="27">
         <v>0</v>
       </c>
       <c r="C10" s="25"/>
@@ -2398,13 +2398,13 @@
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="26"/>
+      <c r="G10" s="27"/>
       <c r="H10" s="25"/>
       <c r="I10" s="25"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="26"/>
+      <c r="L10" s="27"/>
       <c r="M10" s="25"/>
       <c r="N10" s="25"/>
     </row>
@@ -2412,7 +2412,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="30">
         <f>SUM(B5:B10)</f>
         <v>1863</v>
       </c>
@@ -2421,7 +2421,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="29">
+      <c r="G11" s="30">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -2430,7 +2430,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="29">
+      <c r="L11" s="30">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -2466,19 +2466,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
-      <c r="F25" s="30" t="s">
+      <c r="F25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
       <c r="I25" s="25"/>
-      <c r="K25" s="30" t="s">
+      <c r="K25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="25"/>
@@ -2486,19 +2486,19 @@
       <c r="N25" s="25"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
-      <c r="F26" s="30" t="s">
+      <c r="F26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="25"/>
       <c r="H26" s="25"/>
       <c r="I26" s="25"/>
-      <c r="K26" s="30" t="s">
+      <c r="K26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="25"/>
@@ -2520,27 +2520,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="25"/>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="29" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="25"/>
-      <c r="F28" s="28" t="s">
+      <c r="F28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="25"/>
-      <c r="H28" s="28" t="s">
+      <c r="H28" s="29" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="25"/>
-      <c r="K28" s="28" t="s">
+      <c r="K28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="25"/>
-      <c r="M28" s="28" t="s">
+      <c r="M28" s="29" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="25"/>
@@ -2549,7 +2549,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="27">
+      <c r="B29" s="28">
         <v>0</v>
       </c>
       <c r="C29" s="25"/>
@@ -2557,13 +2557,13 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="27"/>
+      <c r="G29" s="28"/>
       <c r="H29" s="25"/>
       <c r="I29" s="25"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="27">
+      <c r="L29" s="28">
         <v>14</v>
       </c>
       <c r="M29" s="25"/>
@@ -2573,7 +2573,7 @@
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="26">
+      <c r="B30" s="27">
         <v>0</v>
       </c>
       <c r="C30" s="25"/>
@@ -2581,13 +2581,13 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="26"/>
+      <c r="G30" s="27"/>
       <c r="H30" s="25"/>
       <c r="I30" s="25"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="26">
+      <c r="L30" s="27">
         <v>605</v>
       </c>
       <c r="M30" s="25"/>
@@ -2597,7 +2597,7 @@
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="27">
+      <c r="B31" s="28">
         <v>0</v>
       </c>
       <c r="C31" s="25"/>
@@ -2605,13 +2605,13 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="27"/>
+      <c r="G31" s="28"/>
       <c r="H31" s="25"/>
       <c r="I31" s="25"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="27">
+      <c r="L31" s="28">
         <v>1708</v>
       </c>
       <c r="M31" s="25"/>
@@ -2621,7 +2621,7 @@
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="26">
+      <c r="B32" s="27">
         <v>0</v>
       </c>
       <c r="C32" s="25"/>
@@ -2629,13 +2629,13 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="26"/>
+      <c r="G32" s="27"/>
       <c r="H32" s="25"/>
       <c r="I32" s="25"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="26">
+      <c r="L32" s="27">
         <v>1395</v>
       </c>
       <c r="M32" s="25"/>
@@ -2645,7 +2645,7 @@
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="27">
+      <c r="B33" s="28">
         <v>0</v>
       </c>
       <c r="C33" s="25"/>
@@ -2653,13 +2653,13 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="27"/>
+      <c r="G33" s="28"/>
       <c r="H33" s="25"/>
       <c r="I33" s="25"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="27">
+      <c r="L33" s="28">
         <v>0</v>
       </c>
       <c r="M33" s="25"/>
@@ -2669,7 +2669,7 @@
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="26">
+      <c r="B34" s="27">
         <v>0</v>
       </c>
       <c r="C34" s="25"/>
@@ -2677,13 +2677,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="26"/>
+      <c r="G34" s="27"/>
       <c r="H34" s="25"/>
       <c r="I34" s="25"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="26">
+      <c r="L34" s="27">
         <v>0</v>
       </c>
       <c r="M34" s="25"/>
@@ -2693,7 +2693,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="29">
+      <c r="B35" s="30">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -2702,7 +2702,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="29">
+      <c r="G35" s="30">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -2711,7 +2711,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="29">
+      <c r="L35" s="30">
         <f>SUM(L29:L34)</f>
         <v>3722</v>
       </c>
@@ -2748,13 +2748,49 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="L11:N11"/>
@@ -2771,49 +2807,13 @@
     <mergeCell ref="K2:N2"/>
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2829,7 +2829,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
@@ -2837,7 +2837,7 @@
       <c r="D1" s="25"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
@@ -2851,11 +2851,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="29" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="29" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="25"/>
@@ -2864,7 +2864,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="27"/>
+      <c r="B5" s="28"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
     </row>
@@ -2872,7 +2872,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="26"/>
+      <c r="B6" s="27"/>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
     </row>
@@ -2880,7 +2880,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="27"/>
+      <c r="B7" s="28"/>
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
     </row>
@@ -2888,7 +2888,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="26"/>
+      <c r="B8" s="27"/>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
     </row>
@@ -2896,7 +2896,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="30">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -2945,19 +2945,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="25"/>
       <c r="H1" s="25"/>
       <c r="I1" s="25"/>
-      <c r="K1" s="30" t="s">
+      <c r="K1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="25"/>
@@ -2965,19 +2965,19 @@
       <c r="N1" s="25"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
-      <c r="F2" s="30" t="s">
+      <c r="F2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
       <c r="I2" s="25"/>
-      <c r="K2" s="30" t="s">
+      <c r="K2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="25"/>
@@ -2999,27 +2999,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="29" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="25"/>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="25"/>
-      <c r="H4" s="28" t="s">
+      <c r="H4" s="29" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="25"/>
-      <c r="K4" s="28" t="s">
+      <c r="K4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="25"/>
-      <c r="M4" s="28" t="s">
+      <c r="M4" s="29" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="25"/>
@@ -3028,19 +3028,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="27"/>
+      <c r="B5" s="28"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="27"/>
+      <c r="G5" s="28"/>
       <c r="H5" s="25"/>
       <c r="I5" s="25"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="27"/>
+      <c r="L5" s="28"/>
       <c r="M5" s="25"/>
       <c r="N5" s="25"/>
     </row>
@@ -3048,19 +3048,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="26"/>
+      <c r="B6" s="27"/>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="26"/>
+      <c r="G6" s="27"/>
       <c r="H6" s="25"/>
       <c r="I6" s="25"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="26"/>
+      <c r="L6" s="27"/>
       <c r="M6" s="25"/>
       <c r="N6" s="25"/>
     </row>
@@ -3068,19 +3068,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="27"/>
+      <c r="B7" s="28"/>
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="27"/>
+      <c r="G7" s="28"/>
       <c r="H7" s="25"/>
       <c r="I7" s="25"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="27"/>
+      <c r="L7" s="28"/>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
     </row>
@@ -3088,19 +3088,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="26"/>
+      <c r="B8" s="27"/>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="26"/>
+      <c r="G8" s="27"/>
       <c r="H8" s="25"/>
       <c r="I8" s="25"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="26"/>
+      <c r="L8" s="27"/>
       <c r="M8" s="25"/>
       <c r="N8" s="25"/>
     </row>
@@ -3108,19 +3108,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="27"/>
+      <c r="B9" s="28"/>
       <c r="C9" s="25"/>
       <c r="D9" s="25"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="27"/>
+      <c r="G9" s="28"/>
       <c r="H9" s="25"/>
       <c r="I9" s="25"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="27"/>
+      <c r="L9" s="28"/>
       <c r="M9" s="25"/>
       <c r="N9" s="25"/>
     </row>
@@ -3128,19 +3128,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="26"/>
+      <c r="B10" s="27"/>
       <c r="C10" s="25"/>
       <c r="D10" s="25"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="26"/>
+      <c r="G10" s="27"/>
       <c r="H10" s="25"/>
       <c r="I10" s="25"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="26"/>
+      <c r="L10" s="27"/>
       <c r="M10" s="25"/>
       <c r="N10" s="25"/>
     </row>
@@ -3148,19 +3148,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="27"/>
+      <c r="B11" s="28"/>
       <c r="C11" s="25"/>
       <c r="D11" s="25"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="27"/>
+      <c r="G11" s="28"/>
       <c r="H11" s="25"/>
       <c r="I11" s="25"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="27"/>
+      <c r="L11" s="28"/>
       <c r="M11" s="25"/>
       <c r="N11" s="25"/>
     </row>
@@ -3168,19 +3168,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="26"/>
+      <c r="B12" s="27"/>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="26"/>
+      <c r="G12" s="27"/>
       <c r="H12" s="25"/>
       <c r="I12" s="25"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="26"/>
+      <c r="L12" s="27"/>
       <c r="M12" s="25"/>
       <c r="N12" s="25"/>
     </row>
@@ -3188,7 +3188,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="30">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3197,7 +3197,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="29">
+      <c r="G13" s="30">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3206,7 +3206,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="29">
+      <c r="L13" s="30">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3242,19 +3242,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
-      <c r="F25" s="30" t="s">
+      <c r="F25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
       <c r="I25" s="25"/>
-      <c r="K25" s="30" t="s">
+      <c r="K25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="25"/>
@@ -3262,19 +3262,19 @@
       <c r="N25" s="25"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
-      <c r="F26" s="30" t="s">
+      <c r="F26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="25"/>
       <c r="H26" s="25"/>
       <c r="I26" s="25"/>
-      <c r="K26" s="30" t="s">
+      <c r="K26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="25"/>
@@ -3296,27 +3296,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="25"/>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="29" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="25"/>
-      <c r="F28" s="28" t="s">
+      <c r="F28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="25"/>
-      <c r="H28" s="28" t="s">
+      <c r="H28" s="29" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="25"/>
-      <c r="K28" s="28" t="s">
+      <c r="K28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="25"/>
-      <c r="M28" s="28" t="s">
+      <c r="M28" s="29" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="25"/>
@@ -3325,19 +3325,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="27"/>
+      <c r="B29" s="28"/>
       <c r="C29" s="25"/>
       <c r="D29" s="25"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="27"/>
+      <c r="G29" s="28"/>
       <c r="H29" s="25"/>
       <c r="I29" s="25"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="27"/>
+      <c r="L29" s="28"/>
       <c r="M29" s="25"/>
       <c r="N29" s="25"/>
     </row>
@@ -3345,19 +3345,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="26"/>
+      <c r="B30" s="27"/>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="26"/>
+      <c r="G30" s="27"/>
       <c r="H30" s="25"/>
       <c r="I30" s="25"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="26"/>
+      <c r="L30" s="27"/>
       <c r="M30" s="25"/>
       <c r="N30" s="25"/>
     </row>
@@ -3365,19 +3365,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="27"/>
+      <c r="B31" s="28"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="27"/>
+      <c r="G31" s="28"/>
       <c r="H31" s="25"/>
       <c r="I31" s="25"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="27"/>
+      <c r="L31" s="28"/>
       <c r="M31" s="25"/>
       <c r="N31" s="25"/>
     </row>
@@ -3385,19 +3385,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="26"/>
+      <c r="B32" s="27"/>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="26"/>
+      <c r="G32" s="27"/>
       <c r="H32" s="25"/>
       <c r="I32" s="25"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="26"/>
+      <c r="L32" s="27"/>
       <c r="M32" s="25"/>
       <c r="N32" s="25"/>
     </row>
@@ -3405,19 +3405,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="27"/>
+      <c r="B33" s="28"/>
       <c r="C33" s="25"/>
       <c r="D33" s="25"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="27"/>
+      <c r="G33" s="28"/>
       <c r="H33" s="25"/>
       <c r="I33" s="25"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="27"/>
+      <c r="L33" s="28"/>
       <c r="M33" s="25"/>
       <c r="N33" s="25"/>
     </row>
@@ -3425,19 +3425,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="26"/>
+      <c r="B34" s="27"/>
       <c r="C34" s="25"/>
       <c r="D34" s="25"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="26"/>
+      <c r="G34" s="27"/>
       <c r="H34" s="25"/>
       <c r="I34" s="25"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="26"/>
+      <c r="L34" s="27"/>
       <c r="M34" s="25"/>
       <c r="N34" s="25"/>
     </row>
@@ -3445,19 +3445,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="27"/>
+      <c r="B35" s="28"/>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="27"/>
+      <c r="G35" s="28"/>
       <c r="H35" s="25"/>
       <c r="I35" s="25"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="27"/>
+      <c r="L35" s="28"/>
       <c r="M35" s="25"/>
       <c r="N35" s="25"/>
     </row>
@@ -3465,19 +3465,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="26"/>
+      <c r="B36" s="27"/>
       <c r="C36" s="25"/>
       <c r="D36" s="25"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="26"/>
+      <c r="G36" s="27"/>
       <c r="H36" s="25"/>
       <c r="I36" s="25"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="26"/>
+      <c r="L36" s="27"/>
       <c r="M36" s="25"/>
       <c r="N36" s="25"/>
     </row>
@@ -3485,7 +3485,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="29">
+      <c r="B37" s="30">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -3494,7 +3494,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="29">
+      <c r="G37" s="30">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -3503,7 +3503,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="29">
+      <c r="L37" s="30">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -3540,6 +3540,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
     <mergeCell ref="L34:N34"/>
     <mergeCell ref="L6:N6"/>
     <mergeCell ref="B33:D33"/>
@@ -3556,68 +3618,6 @@
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAD7ACD1-A363-4AA7-B037-36CF35058BBD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2286645-18B3-4159-9E5B-09D4A236DAAD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -427,9 +427,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -440,6 +437,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -767,42 +767,38 @@
       </c>
       <c r="B5" s="21">
         <f>SUM(B6:B7)</f>
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G5" s="14">
         <f>SUM(G6:G7)</f>
-        <v>250</v>
+        <v>277</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="L5" s="14">
         <f>SUM(L6:L7)</f>
-        <v>480</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
       <c r="A6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="14">
-        <v>600</v>
-      </c>
+      <c r="B6" s="14"/>
       <c r="F6" s="7" t="s">
         <v>21</v>
       </c>
       <c r="G6" s="14">
-        <v>250</v>
+        <v>90</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="L6" s="14">
-        <v>480</v>
-      </c>
+      <c r="L6" s="14"/>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
@@ -812,7 +808,9 @@
       <c r="F7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="14"/>
+      <c r="G7" s="14">
+        <v>187</v>
+      </c>
       <c r="K7" s="7" t="s">
         <v>22</v>
       </c>
@@ -838,7 +836,7 @@
       </c>
       <c r="L8" s="15">
         <f>SUM(L9:L10)</f>
-        <v>60</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1">
@@ -853,9 +851,7 @@
       <c r="K9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L9" s="15">
-        <v>60</v>
-      </c>
+      <c r="L9" s="15"/>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
       <c r="A10" s="9" t="s">
@@ -928,21 +924,21 @@
       </c>
       <c r="B14" s="15">
         <f>SUM(B15:B16)</f>
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>25</v>
       </c>
       <c r="G14" s="15">
         <f>SUM(G15:G16)</f>
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="K14" s="9" t="s">
         <v>25</v>
       </c>
       <c r="L14" s="15">
         <f>SUM(L15:L16)</f>
-        <v>900</v>
+        <v>400</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1">
@@ -950,19 +946,19 @@
         <v>21</v>
       </c>
       <c r="B15" s="15">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>21</v>
       </c>
       <c r="G15" s="15">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="K15" s="9" t="s">
         <v>21</v>
       </c>
       <c r="L15" s="15">
-        <v>900</v>
+        <v>400</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1">
@@ -1087,7 +1083,7 @@
       </c>
       <c r="B23" s="14">
         <f>SUM(B24:B25)</f>
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>28</v>
@@ -1108,9 +1104,7 @@
       <c r="A24" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="14">
-        <v>130</v>
-      </c>
+      <c r="B24" s="14"/>
       <c r="F24" s="7" t="s">
         <v>21</v>
       </c>
@@ -1198,14 +1192,14 @@
       </c>
       <c r="G29" s="14">
         <f>SUM(G30:G31)</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K29" s="7" t="s">
         <v>30</v>
       </c>
       <c r="L29" s="14">
         <f>SUM(L30:L31)</f>
-        <v>400</v>
+        <v>150</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1">
@@ -1218,14 +1212,12 @@
       <c r="F30" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G30" s="14">
-        <v>20</v>
-      </c>
+      <c r="G30" s="14"/>
       <c r="K30" s="7" t="s">
         <v>21</v>
       </c>
       <c r="L30" s="14">
-        <v>400</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1">
@@ -1255,14 +1247,14 @@
       </c>
       <c r="G32" s="15">
         <f>SUM(G33:G34)</f>
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K32" s="9" t="s">
         <v>31</v>
       </c>
       <c r="L32" s="15">
         <f>SUM(L33:L34)</f>
-        <v>240</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
@@ -1275,14 +1267,12 @@
       <c r="F33" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G33" s="15">
-        <v>26</v>
-      </c>
+      <c r="G33" s="15"/>
       <c r="K33" s="9" t="s">
         <v>21</v>
       </c>
       <c r="L33" s="15">
-        <v>240</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
@@ -1407,21 +1397,21 @@
       </c>
       <c r="B41" s="13">
         <f>SUM(B5,B8,B11,B14,B17,B20,B23,B26,B29,B32,B35,B38)</f>
-        <v>951</v>
+        <v>191</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G41" s="13">
         <f>SUM(G5,G8,G11,G14,G17,G20,G23,G26,G29,G32,G35,G38)</f>
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="L41" s="13">
         <f>SUM(L5,L8,L11,L14,L17,L20,L23,L26,L29,L32,L35,L38)</f>
-        <v>2080</v>
+        <v>672</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1">
@@ -1531,7 +1521,7 @@
       </c>
       <c r="L53" s="14">
         <f>SUM(L54:L55)</f>
-        <v>0</v>
+        <v>900</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="15" customHeight="1">
@@ -1546,7 +1536,9 @@
       <c r="K54" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="L54" s="14"/>
+      <c r="L54" s="14">
+        <v>900</v>
+      </c>
     </row>
     <row r="55" spans="1:14" ht="15" customHeight="1">
       <c r="A55" s="7" t="s">
@@ -2147,7 +2139,7 @@
       </c>
       <c r="L89" s="13">
         <f>SUM(L53,L56,L59,L62,L65,L68,L71,L74,L77,L80,L83,L86)</f>
-        <v>0</v>
+        <v>900</v>
       </c>
     </row>
     <row r="90" spans="1:14" ht="15" customHeight="1">
@@ -2197,19 +2189,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="25"/>
       <c r="H1" s="25"/>
       <c r="I1" s="25"/>
-      <c r="K1" s="26" t="s">
+      <c r="K1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="25"/>
@@ -2217,19 +2209,19 @@
       <c r="N1" s="25"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
       <c r="I2" s="25"/>
-      <c r="K2" s="26" t="s">
+      <c r="K2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="25"/>
@@ -2251,27 +2243,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="28" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="25"/>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="25"/>
-      <c r="H4" s="29" t="s">
+      <c r="H4" s="28" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="25"/>
-      <c r="K4" s="29" t="s">
+      <c r="K4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="25"/>
-      <c r="M4" s="29" t="s">
+      <c r="M4" s="28" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="25"/>
@@ -2280,7 +2272,7 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="28">
+      <c r="B5" s="27">
         <v>352</v>
       </c>
       <c r="C5" s="25"/>
@@ -2288,13 +2280,13 @@
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="28"/>
+      <c r="G5" s="27"/>
       <c r="H5" s="25"/>
       <c r="I5" s="25"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="28"/>
+      <c r="L5" s="27"/>
       <c r="M5" s="25"/>
       <c r="N5" s="25"/>
     </row>
@@ -2302,7 +2294,7 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="26">
         <v>376</v>
       </c>
       <c r="C6" s="25"/>
@@ -2310,13 +2302,13 @@
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="27"/>
+      <c r="G6" s="26"/>
       <c r="H6" s="25"/>
       <c r="I6" s="25"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="27"/>
+      <c r="L6" s="26"/>
       <c r="M6" s="25"/>
       <c r="N6" s="25"/>
     </row>
@@ -2324,7 +2316,7 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="27">
         <v>0</v>
       </c>
       <c r="C7" s="25"/>
@@ -2332,13 +2324,13 @@
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="28"/>
+      <c r="G7" s="27"/>
       <c r="H7" s="25"/>
       <c r="I7" s="25"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="28"/>
+      <c r="L7" s="27"/>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
     </row>
@@ -2346,7 +2338,7 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="26">
         <v>724</v>
       </c>
       <c r="C8" s="25"/>
@@ -2354,13 +2346,13 @@
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="27"/>
+      <c r="G8" s="26"/>
       <c r="H8" s="25"/>
       <c r="I8" s="25"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="27"/>
+      <c r="L8" s="26"/>
       <c r="M8" s="25"/>
       <c r="N8" s="25"/>
     </row>
@@ -2368,7 +2360,7 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="28">
+      <c r="B9" s="27">
         <v>411</v>
       </c>
       <c r="C9" s="25"/>
@@ -2376,13 +2368,13 @@
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="28"/>
+      <c r="G9" s="27"/>
       <c r="H9" s="25"/>
       <c r="I9" s="25"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="28"/>
+      <c r="L9" s="27"/>
       <c r="M9" s="25"/>
       <c r="N9" s="25"/>
     </row>
@@ -2390,7 +2382,7 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="27">
+      <c r="B10" s="26">
         <v>0</v>
       </c>
       <c r="C10" s="25"/>
@@ -2398,13 +2390,13 @@
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="27"/>
+      <c r="G10" s="26"/>
       <c r="H10" s="25"/>
       <c r="I10" s="25"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="27"/>
+      <c r="L10" s="26"/>
       <c r="M10" s="25"/>
       <c r="N10" s="25"/>
     </row>
@@ -2412,7 +2404,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="29">
         <f>SUM(B5:B10)</f>
         <v>1863</v>
       </c>
@@ -2421,7 +2413,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="30">
+      <c r="G11" s="29">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -2430,7 +2422,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="30">
+      <c r="L11" s="29">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -2466,19 +2458,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
-      <c r="F25" s="26" t="s">
+      <c r="F25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
       <c r="I25" s="25"/>
-      <c r="K25" s="26" t="s">
+      <c r="K25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="25"/>
@@ -2486,19 +2478,19 @@
       <c r="N25" s="25"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
-      <c r="F26" s="26" t="s">
+      <c r="F26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="25"/>
       <c r="H26" s="25"/>
       <c r="I26" s="25"/>
-      <c r="K26" s="26" t="s">
+      <c r="K26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="25"/>
@@ -2520,27 +2512,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="25"/>
-      <c r="C28" s="29" t="s">
+      <c r="C28" s="28" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="25"/>
-      <c r="F28" s="29" t="s">
+      <c r="F28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="25"/>
-      <c r="H28" s="29" t="s">
+      <c r="H28" s="28" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="25"/>
-      <c r="K28" s="29" t="s">
+      <c r="K28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="25"/>
-      <c r="M28" s="29" t="s">
+      <c r="M28" s="28" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="25"/>
@@ -2549,7 +2541,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="28">
+      <c r="B29" s="27">
         <v>0</v>
       </c>
       <c r="C29" s="25"/>
@@ -2557,13 +2549,13 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="28"/>
+      <c r="G29" s="27"/>
       <c r="H29" s="25"/>
       <c r="I29" s="25"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="28">
+      <c r="L29" s="27">
         <v>14</v>
       </c>
       <c r="M29" s="25"/>
@@ -2573,7 +2565,7 @@
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="27">
+      <c r="B30" s="26">
         <v>0</v>
       </c>
       <c r="C30" s="25"/>
@@ -2581,13 +2573,13 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="27"/>
+      <c r="G30" s="26"/>
       <c r="H30" s="25"/>
       <c r="I30" s="25"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="27">
+      <c r="L30" s="26">
         <v>605</v>
       </c>
       <c r="M30" s="25"/>
@@ -2597,7 +2589,7 @@
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="28">
+      <c r="B31" s="27">
         <v>0</v>
       </c>
       <c r="C31" s="25"/>
@@ -2605,13 +2597,13 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="28"/>
+      <c r="G31" s="27"/>
       <c r="H31" s="25"/>
       <c r="I31" s="25"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="28">
+      <c r="L31" s="27">
         <v>1708</v>
       </c>
       <c r="M31" s="25"/>
@@ -2621,7 +2613,7 @@
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="27">
+      <c r="B32" s="26">
         <v>0</v>
       </c>
       <c r="C32" s="25"/>
@@ -2629,13 +2621,13 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="27"/>
+      <c r="G32" s="26"/>
       <c r="H32" s="25"/>
       <c r="I32" s="25"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="27">
+      <c r="L32" s="26">
         <v>1395</v>
       </c>
       <c r="M32" s="25"/>
@@ -2645,7 +2637,7 @@
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="28">
+      <c r="B33" s="27">
         <v>0</v>
       </c>
       <c r="C33" s="25"/>
@@ -2653,13 +2645,13 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="28"/>
+      <c r="G33" s="27"/>
       <c r="H33" s="25"/>
       <c r="I33" s="25"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="28">
+      <c r="L33" s="27">
         <v>0</v>
       </c>
       <c r="M33" s="25"/>
@@ -2669,7 +2661,7 @@
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="27">
+      <c r="B34" s="26">
         <v>0</v>
       </c>
       <c r="C34" s="25"/>
@@ -2677,13 +2669,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="27"/>
+      <c r="G34" s="26"/>
       <c r="H34" s="25"/>
       <c r="I34" s="25"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="27">
+      <c r="L34" s="26">
         <v>0</v>
       </c>
       <c r="M34" s="25"/>
@@ -2693,7 +2685,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="30">
+      <c r="B35" s="29">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -2702,7 +2694,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="30">
+      <c r="G35" s="29">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -2711,7 +2703,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="30">
+      <c r="L35" s="29">
         <f>SUM(L29:L34)</f>
         <v>3722</v>
       </c>
@@ -2748,6 +2740,56 @@
     </row>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B10:D10"/>
@@ -2764,56 +2806,6 @@
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="H28:I28"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2829,7 +2821,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
@@ -2837,7 +2829,7 @@
       <c r="D1" s="25"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
@@ -2851,11 +2843,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="28" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="28" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="25"/>
@@ -2864,7 +2856,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="28"/>
+      <c r="B5" s="27"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
     </row>
@@ -2872,7 +2864,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="27"/>
+      <c r="B6" s="26"/>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
     </row>
@@ -2880,7 +2872,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="28"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
     </row>
@@ -2888,7 +2880,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="27"/>
+      <c r="B8" s="26"/>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
     </row>
@@ -2896,7 +2888,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="29">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -2945,19 +2937,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="25"/>
       <c r="H1" s="25"/>
       <c r="I1" s="25"/>
-      <c r="K1" s="26" t="s">
+      <c r="K1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="25"/>
@@ -2965,19 +2957,19 @@
       <c r="N1" s="25"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
       <c r="I2" s="25"/>
-      <c r="K2" s="26" t="s">
+      <c r="K2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="25"/>
@@ -2999,27 +2991,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="28" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="25"/>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="25"/>
-      <c r="H4" s="29" t="s">
+      <c r="H4" s="28" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="25"/>
-      <c r="K4" s="29" t="s">
+      <c r="K4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="25"/>
-      <c r="M4" s="29" t="s">
+      <c r="M4" s="28" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="25"/>
@@ -3028,19 +3020,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="28"/>
+      <c r="B5" s="27"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="28"/>
+      <c r="G5" s="27"/>
       <c r="H5" s="25"/>
       <c r="I5" s="25"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="28"/>
+      <c r="L5" s="27"/>
       <c r="M5" s="25"/>
       <c r="N5" s="25"/>
     </row>
@@ -3048,19 +3040,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="27"/>
+      <c r="B6" s="26"/>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="27"/>
+      <c r="G6" s="26"/>
       <c r="H6" s="25"/>
       <c r="I6" s="25"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="27"/>
+      <c r="L6" s="26"/>
       <c r="M6" s="25"/>
       <c r="N6" s="25"/>
     </row>
@@ -3068,19 +3060,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="28"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="28"/>
+      <c r="G7" s="27"/>
       <c r="H7" s="25"/>
       <c r="I7" s="25"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="28"/>
+      <c r="L7" s="27"/>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
     </row>
@@ -3088,19 +3080,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="27"/>
+      <c r="B8" s="26"/>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="27"/>
+      <c r="G8" s="26"/>
       <c r="H8" s="25"/>
       <c r="I8" s="25"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="27"/>
+      <c r="L8" s="26"/>
       <c r="M8" s="25"/>
       <c r="N8" s="25"/>
     </row>
@@ -3108,19 +3100,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="28"/>
+      <c r="B9" s="27"/>
       <c r="C9" s="25"/>
       <c r="D9" s="25"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="28"/>
+      <c r="G9" s="27"/>
       <c r="H9" s="25"/>
       <c r="I9" s="25"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="28"/>
+      <c r="L9" s="27"/>
       <c r="M9" s="25"/>
       <c r="N9" s="25"/>
     </row>
@@ -3128,19 +3120,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="27"/>
+      <c r="B10" s="26"/>
       <c r="C10" s="25"/>
       <c r="D10" s="25"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="27"/>
+      <c r="G10" s="26"/>
       <c r="H10" s="25"/>
       <c r="I10" s="25"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="27"/>
+      <c r="L10" s="26"/>
       <c r="M10" s="25"/>
       <c r="N10" s="25"/>
     </row>
@@ -3148,19 +3140,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="28"/>
+      <c r="B11" s="27"/>
       <c r="C11" s="25"/>
       <c r="D11" s="25"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="28"/>
+      <c r="G11" s="27"/>
       <c r="H11" s="25"/>
       <c r="I11" s="25"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="28"/>
+      <c r="L11" s="27"/>
       <c r="M11" s="25"/>
       <c r="N11" s="25"/>
     </row>
@@ -3168,19 +3160,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="27"/>
+      <c r="B12" s="26"/>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="27"/>
+      <c r="G12" s="26"/>
       <c r="H12" s="25"/>
       <c r="I12" s="25"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="27"/>
+      <c r="L12" s="26"/>
       <c r="M12" s="25"/>
       <c r="N12" s="25"/>
     </row>
@@ -3188,7 +3180,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="29">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3197,7 +3189,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="30">
+      <c r="G13" s="29">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3206,7 +3198,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="30">
+      <c r="L13" s="29">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3242,19 +3234,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
-      <c r="F25" s="26" t="s">
+      <c r="F25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
       <c r="I25" s="25"/>
-      <c r="K25" s="26" t="s">
+      <c r="K25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="25"/>
@@ -3262,19 +3254,19 @@
       <c r="N25" s="25"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
-      <c r="F26" s="26" t="s">
+      <c r="F26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="25"/>
       <c r="H26" s="25"/>
       <c r="I26" s="25"/>
-      <c r="K26" s="26" t="s">
+      <c r="K26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="25"/>
@@ -3296,27 +3288,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="25"/>
-      <c r="C28" s="29" t="s">
+      <c r="C28" s="28" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="25"/>
-      <c r="F28" s="29" t="s">
+      <c r="F28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="25"/>
-      <c r="H28" s="29" t="s">
+      <c r="H28" s="28" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="25"/>
-      <c r="K28" s="29" t="s">
+      <c r="K28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="25"/>
-      <c r="M28" s="29" t="s">
+      <c r="M28" s="28" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="25"/>
@@ -3325,19 +3317,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="28"/>
+      <c r="B29" s="27"/>
       <c r="C29" s="25"/>
       <c r="D29" s="25"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="28"/>
+      <c r="G29" s="27"/>
       <c r="H29" s="25"/>
       <c r="I29" s="25"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="28"/>
+      <c r="L29" s="27"/>
       <c r="M29" s="25"/>
       <c r="N29" s="25"/>
     </row>
@@ -3345,19 +3337,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="27"/>
+      <c r="B30" s="26"/>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="27"/>
+      <c r="G30" s="26"/>
       <c r="H30" s="25"/>
       <c r="I30" s="25"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="27"/>
+      <c r="L30" s="26"/>
       <c r="M30" s="25"/>
       <c r="N30" s="25"/>
     </row>
@@ -3365,19 +3357,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="28"/>
+      <c r="B31" s="27"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="28"/>
+      <c r="G31" s="27"/>
       <c r="H31" s="25"/>
       <c r="I31" s="25"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="28"/>
+      <c r="L31" s="27"/>
       <c r="M31" s="25"/>
       <c r="N31" s="25"/>
     </row>
@@ -3385,19 +3377,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="27"/>
+      <c r="B32" s="26"/>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="27"/>
+      <c r="G32" s="26"/>
       <c r="H32" s="25"/>
       <c r="I32" s="25"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="27"/>
+      <c r="L32" s="26"/>
       <c r="M32" s="25"/>
       <c r="N32" s="25"/>
     </row>
@@ -3405,19 +3397,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="28"/>
+      <c r="B33" s="27"/>
       <c r="C33" s="25"/>
       <c r="D33" s="25"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="28"/>
+      <c r="G33" s="27"/>
       <c r="H33" s="25"/>
       <c r="I33" s="25"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="28"/>
+      <c r="L33" s="27"/>
       <c r="M33" s="25"/>
       <c r="N33" s="25"/>
     </row>
@@ -3425,19 +3417,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="27"/>
+      <c r="B34" s="26"/>
       <c r="C34" s="25"/>
       <c r="D34" s="25"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="27"/>
+      <c r="G34" s="26"/>
       <c r="H34" s="25"/>
       <c r="I34" s="25"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="27"/>
+      <c r="L34" s="26"/>
       <c r="M34" s="25"/>
       <c r="N34" s="25"/>
     </row>
@@ -3445,19 +3437,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="28"/>
+      <c r="B35" s="27"/>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="28"/>
+      <c r="G35" s="27"/>
       <c r="H35" s="25"/>
       <c r="I35" s="25"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="28"/>
+      <c r="L35" s="27"/>
       <c r="M35" s="25"/>
       <c r="N35" s="25"/>
     </row>
@@ -3465,19 +3457,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="27"/>
+      <c r="B36" s="26"/>
       <c r="C36" s="25"/>
       <c r="D36" s="25"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="27"/>
+      <c r="G36" s="26"/>
       <c r="H36" s="25"/>
       <c r="I36" s="25"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="27"/>
+      <c r="L36" s="26"/>
       <c r="M36" s="25"/>
       <c r="N36" s="25"/>
     </row>
@@ -3485,7 +3477,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="30">
+      <c r="B37" s="29">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -3494,7 +3486,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="30">
+      <c r="G37" s="29">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -3503,7 +3495,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="30">
+      <c r="L37" s="29">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -3540,6 +3532,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
     <mergeCell ref="G36:I36"/>
     <mergeCell ref="L32:N32"/>
     <mergeCell ref="L13:N13"/>
@@ -3556,68 +3610,6 @@
     <mergeCell ref="L33:N33"/>
     <mergeCell ref="L35:N35"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="L9:N9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4082,7 +4074,7 @@
         <v>68</v>
       </c>
       <c r="E27" s="18">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:5">

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2286645-18B3-4159-9E5B-09D4A236DAAD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EE195B9-0A29-49A5-8552-9DBA9FB5F284}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -427,6 +427,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -437,9 +440,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -767,38 +767,40 @@
       </c>
       <c r="B5" s="21">
         <f>SUM(B6:B7)</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G5" s="14">
         <f>SUM(G6:G7)</f>
-        <v>277</v>
+        <v>0</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="L5" s="14">
         <f>SUM(L6:L7)</f>
-        <v>0</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
       <c r="A6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="14"/>
+      <c r="B6" s="14">
+        <v>800</v>
+      </c>
       <c r="F6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="14">
-        <v>90</v>
-      </c>
+      <c r="G6" s="14"/>
       <c r="K6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="L6" s="14"/>
+      <c r="L6" s="14">
+        <v>2100</v>
+      </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
@@ -808,9 +810,7 @@
       <c r="F7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="14">
-        <v>187</v>
-      </c>
+      <c r="G7" s="14"/>
       <c r="K7" s="7" t="s">
         <v>22</v>
       </c>
@@ -924,41 +924,37 @@
       </c>
       <c r="B14" s="15">
         <f>SUM(B15:B16)</f>
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>25</v>
       </c>
       <c r="G14" s="15">
         <f>SUM(G15:G16)</f>
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="K14" s="9" t="s">
         <v>25</v>
       </c>
       <c r="L14" s="15">
         <f>SUM(L15:L16)</f>
-        <v>400</v>
+        <v>700</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1">
       <c r="A15" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="15">
-        <v>130</v>
-      </c>
+      <c r="B15" s="15"/>
       <c r="F15" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="15">
-        <v>62</v>
-      </c>
+      <c r="G15" s="15"/>
       <c r="K15" s="9" t="s">
         <v>21</v>
       </c>
       <c r="L15" s="15">
-        <v>400</v>
+        <v>700</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1">
@@ -981,7 +977,7 @@
       </c>
       <c r="B17" s="14">
         <f>SUM(B18:B19)</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>26</v>
@@ -1002,7 +998,9 @@
       <c r="A18" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="14"/>
+      <c r="B18" s="14">
+        <v>180</v>
+      </c>
       <c r="F18" s="7" t="s">
         <v>21</v>
       </c>
@@ -1141,7 +1139,7 @@
       </c>
       <c r="G26" s="15">
         <f>SUM(G27:G28)</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K26" s="9" t="s">
         <v>29</v>
@@ -1159,7 +1157,9 @@
       <c r="F27" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G27" s="15"/>
+      <c r="G27" s="15">
+        <v>300</v>
+      </c>
       <c r="K27" s="9" t="s">
         <v>21</v>
       </c>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="B29" s="14">
         <f>SUM(B30:B31)</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>30</v>
@@ -1199,16 +1199,14 @@
       </c>
       <c r="L29" s="14">
         <f>SUM(L30:L31)</f>
-        <v>150</v>
+        <v>320</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1">
       <c r="A30" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B30" s="14">
-        <v>16</v>
-      </c>
+      <c r="B30" s="14"/>
       <c r="F30" s="7" t="s">
         <v>21</v>
       </c>
@@ -1217,7 +1215,7 @@
         <v>21</v>
       </c>
       <c r="L30" s="14">
-        <v>150</v>
+        <v>320</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1">
@@ -1240,7 +1238,7 @@
       </c>
       <c r="B32" s="15">
         <f>SUM(B33:B34)</f>
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>31</v>
@@ -1254,16 +1252,14 @@
       </c>
       <c r="L32" s="15">
         <f>SUM(L33:L34)</f>
-        <v>122</v>
+        <v>80</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="15">
-        <v>45</v>
-      </c>
+      <c r="B33" s="15"/>
       <c r="F33" s="9" t="s">
         <v>21</v>
       </c>
@@ -1272,7 +1268,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="15">
-        <v>122</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
@@ -1360,7 +1356,7 @@
       </c>
       <c r="L38" s="23">
         <f>SUM(L39:L40)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="15" customHeight="1">
@@ -1375,7 +1371,9 @@
       <c r="K39" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L39" s="15"/>
+      <c r="L39" s="15">
+        <v>50</v>
+      </c>
     </row>
     <row r="40" spans="1:14" ht="15" customHeight="1">
       <c r="A40" s="9" t="s">
@@ -1397,21 +1395,21 @@
       </c>
       <c r="B41" s="13">
         <f>SUM(B5,B8,B11,B14,B17,B20,B23,B26,B29,B32,B35,B38)</f>
-        <v>191</v>
+        <v>980</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G41" s="13">
         <f>SUM(G5,G8,G11,G14,G17,G20,G23,G26,G29,G32,G35,G38)</f>
-        <v>339</v>
+        <v>300</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="L41" s="13">
         <f>SUM(L5,L8,L11,L14,L17,L20,L23,L26,L29,L32,L35,L38)</f>
-        <v>672</v>
+        <v>3250</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1">
@@ -1507,7 +1505,7 @@
       </c>
       <c r="B53" s="14">
         <f>SUM(B54:B55)</f>
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F53" s="7" t="s">
         <v>20</v>
@@ -1521,14 +1519,16 @@
       </c>
       <c r="L53" s="14">
         <f>SUM(L54:L55)</f>
-        <v>900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="15" customHeight="1">
       <c r="A54" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B54" s="14"/>
+      <c r="B54" s="14">
+        <v>400</v>
+      </c>
       <c r="F54" s="7" t="s">
         <v>21</v>
       </c>
@@ -1536,9 +1536,7 @@
       <c r="K54" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="L54" s="14">
-        <v>900</v>
-      </c>
+      <c r="L54" s="14"/>
     </row>
     <row r="55" spans="1:14" ht="15" customHeight="1">
       <c r="A55" s="7" t="s">
@@ -1662,7 +1660,7 @@
       </c>
       <c r="B62" s="15">
         <f>SUM(B63:B64)</f>
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>25</v>
@@ -1676,7 +1674,7 @@
       </c>
       <c r="L62" s="15">
         <f>SUM(L63:L64)</f>
-        <v>0</v>
+        <v>53</v>
       </c>
     </row>
     <row r="63" spans="1:14" ht="15" customHeight="1">
@@ -1684,7 +1682,7 @@
         <v>21</v>
       </c>
       <c r="B63" s="15">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>21</v>
@@ -1693,7 +1691,9 @@
       <c r="K63" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L63" s="15"/>
+      <c r="L63" s="15">
+        <v>53</v>
+      </c>
     </row>
     <row r="64" spans="1:14" ht="15" customHeight="1">
       <c r="A64" s="9" t="s">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="B89" s="13">
         <f>SUM(B53,B56,B59,B62,B65,B68,B71,B74,B77,B80,B83,B86)</f>
-        <v>64</v>
+        <v>440</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>34</v>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="L89" s="13">
         <f>SUM(L53,L56,L59,L62,L65,L68,L71,L74,L77,L80,L83,L86)</f>
-        <v>900</v>
+        <v>53</v>
       </c>
     </row>
     <row r="90" spans="1:14" ht="15" customHeight="1">
@@ -2189,19 +2189,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="25"/>
       <c r="H1" s="25"/>
       <c r="I1" s="25"/>
-      <c r="K1" s="30" t="s">
+      <c r="K1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="25"/>
@@ -2209,19 +2209,19 @@
       <c r="N1" s="25"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
-      <c r="F2" s="30" t="s">
+      <c r="F2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
       <c r="I2" s="25"/>
-      <c r="K2" s="30" t="s">
+      <c r="K2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="25"/>
@@ -2243,27 +2243,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="29" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="25"/>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="25"/>
-      <c r="H4" s="28" t="s">
+      <c r="H4" s="29" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="25"/>
-      <c r="K4" s="28" t="s">
+      <c r="K4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="25"/>
-      <c r="M4" s="28" t="s">
+      <c r="M4" s="29" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="25"/>
@@ -2272,7 +2272,7 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="28">
         <v>352</v>
       </c>
       <c r="C5" s="25"/>
@@ -2280,13 +2280,13 @@
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="27"/>
+      <c r="G5" s="28"/>
       <c r="H5" s="25"/>
       <c r="I5" s="25"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="27"/>
+      <c r="L5" s="28"/>
       <c r="M5" s="25"/>
       <c r="N5" s="25"/>
     </row>
@@ -2294,7 +2294,7 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="27">
         <v>376</v>
       </c>
       <c r="C6" s="25"/>
@@ -2302,13 +2302,13 @@
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="26"/>
+      <c r="G6" s="27"/>
       <c r="H6" s="25"/>
       <c r="I6" s="25"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="26"/>
+      <c r="L6" s="27"/>
       <c r="M6" s="25"/>
       <c r="N6" s="25"/>
     </row>
@@ -2316,7 +2316,7 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="28">
         <v>0</v>
       </c>
       <c r="C7" s="25"/>
@@ -2324,13 +2324,13 @@
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="27"/>
+      <c r="G7" s="28"/>
       <c r="H7" s="25"/>
       <c r="I7" s="25"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="27"/>
+      <c r="L7" s="28"/>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
     </row>
@@ -2338,7 +2338,7 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="27">
         <v>724</v>
       </c>
       <c r="C8" s="25"/>
@@ -2346,13 +2346,13 @@
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="26"/>
+      <c r="G8" s="27"/>
       <c r="H8" s="25"/>
       <c r="I8" s="25"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="26"/>
+      <c r="L8" s="27"/>
       <c r="M8" s="25"/>
       <c r="N8" s="25"/>
     </row>
@@ -2360,7 +2360,7 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="27">
+      <c r="B9" s="28">
         <v>411</v>
       </c>
       <c r="C9" s="25"/>
@@ -2368,13 +2368,13 @@
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="27"/>
+      <c r="G9" s="28"/>
       <c r="H9" s="25"/>
       <c r="I9" s="25"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="27"/>
+      <c r="L9" s="28"/>
       <c r="M9" s="25"/>
       <c r="N9" s="25"/>
     </row>
@@ -2382,7 +2382,7 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="26">
+      <c r="B10" s="27">
         <v>0</v>
       </c>
       <c r="C10" s="25"/>
@@ -2390,13 +2390,13 @@
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="26"/>
+      <c r="G10" s="27"/>
       <c r="H10" s="25"/>
       <c r="I10" s="25"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="26"/>
+      <c r="L10" s="27"/>
       <c r="M10" s="25"/>
       <c r="N10" s="25"/>
     </row>
@@ -2404,7 +2404,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="30">
         <f>SUM(B5:B10)</f>
         <v>1863</v>
       </c>
@@ -2413,7 +2413,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="29">
+      <c r="G11" s="30">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -2422,7 +2422,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="29">
+      <c r="L11" s="30">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -2458,19 +2458,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
-      <c r="F25" s="30" t="s">
+      <c r="F25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
       <c r="I25" s="25"/>
-      <c r="K25" s="30" t="s">
+      <c r="K25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="25"/>
@@ -2478,19 +2478,19 @@
       <c r="N25" s="25"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
-      <c r="F26" s="30" t="s">
+      <c r="F26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="25"/>
       <c r="H26" s="25"/>
       <c r="I26" s="25"/>
-      <c r="K26" s="30" t="s">
+      <c r="K26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="25"/>
@@ -2512,27 +2512,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="25"/>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="29" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="25"/>
-      <c r="F28" s="28" t="s">
+      <c r="F28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="25"/>
-      <c r="H28" s="28" t="s">
+      <c r="H28" s="29" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="25"/>
-      <c r="K28" s="28" t="s">
+      <c r="K28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="25"/>
-      <c r="M28" s="28" t="s">
+      <c r="M28" s="29" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="25"/>
@@ -2541,7 +2541,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="27">
+      <c r="B29" s="28">
         <v>0</v>
       </c>
       <c r="C29" s="25"/>
@@ -2549,13 +2549,13 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="27"/>
+      <c r="G29" s="28"/>
       <c r="H29" s="25"/>
       <c r="I29" s="25"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="27">
+      <c r="L29" s="28">
         <v>14</v>
       </c>
       <c r="M29" s="25"/>
@@ -2565,7 +2565,7 @@
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="26">
+      <c r="B30" s="27">
         <v>0</v>
       </c>
       <c r="C30" s="25"/>
@@ -2573,13 +2573,13 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="26"/>
+      <c r="G30" s="27"/>
       <c r="H30" s="25"/>
       <c r="I30" s="25"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="26">
+      <c r="L30" s="27">
         <v>605</v>
       </c>
       <c r="M30" s="25"/>
@@ -2589,7 +2589,7 @@
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="27">
+      <c r="B31" s="28">
         <v>0</v>
       </c>
       <c r="C31" s="25"/>
@@ -2597,13 +2597,13 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="27"/>
+      <c r="G31" s="28"/>
       <c r="H31" s="25"/>
       <c r="I31" s="25"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="27">
+      <c r="L31" s="28">
         <v>1708</v>
       </c>
       <c r="M31" s="25"/>
@@ -2613,7 +2613,7 @@
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="26">
+      <c r="B32" s="27">
         <v>0</v>
       </c>
       <c r="C32" s="25"/>
@@ -2621,13 +2621,13 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="26"/>
+      <c r="G32" s="27"/>
       <c r="H32" s="25"/>
       <c r="I32" s="25"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="26">
+      <c r="L32" s="27">
         <v>1395</v>
       </c>
       <c r="M32" s="25"/>
@@ -2637,7 +2637,7 @@
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="27">
+      <c r="B33" s="28">
         <v>0</v>
       </c>
       <c r="C33" s="25"/>
@@ -2645,13 +2645,13 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="27"/>
+      <c r="G33" s="28"/>
       <c r="H33" s="25"/>
       <c r="I33" s="25"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="27">
+      <c r="L33" s="28">
         <v>0</v>
       </c>
       <c r="M33" s="25"/>
@@ -2661,7 +2661,7 @@
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="26">
+      <c r="B34" s="27">
         <v>0</v>
       </c>
       <c r="C34" s="25"/>
@@ -2669,13 +2669,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="26"/>
+      <c r="G34" s="27"/>
       <c r="H34" s="25"/>
       <c r="I34" s="25"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="26">
+      <c r="L34" s="27">
         <v>0</v>
       </c>
       <c r="M34" s="25"/>
@@ -2685,7 +2685,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="29">
+      <c r="B35" s="30">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -2694,7 +2694,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="29">
+      <c r="G35" s="30">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -2703,7 +2703,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="29">
+      <c r="L35" s="30">
         <f>SUM(L29:L34)</f>
         <v>3722</v>
       </c>
@@ -2740,13 +2740,49 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="L11:N11"/>
@@ -2763,49 +2799,13 @@
     <mergeCell ref="K2:N2"/>
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2821,7 +2821,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
@@ -2829,7 +2829,7 @@
       <c r="D1" s="25"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
@@ -2843,11 +2843,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="29" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="29" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="25"/>
@@ -2856,7 +2856,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="27"/>
+      <c r="B5" s="28"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
     </row>
@@ -2864,7 +2864,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="26"/>
+      <c r="B6" s="27"/>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
     </row>
@@ -2872,7 +2872,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="27"/>
+      <c r="B7" s="28"/>
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
     </row>
@@ -2880,7 +2880,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="26"/>
+      <c r="B8" s="27"/>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
     </row>
@@ -2888,7 +2888,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="30">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -2937,19 +2937,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
-      <c r="F1" s="30" t="s">
+      <c r="F1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="25"/>
       <c r="H1" s="25"/>
       <c r="I1" s="25"/>
-      <c r="K1" s="30" t="s">
+      <c r="K1" s="26" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="25"/>
@@ -2957,19 +2957,19 @@
       <c r="N1" s="25"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
-      <c r="F2" s="30" t="s">
+      <c r="F2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
       <c r="I2" s="25"/>
-      <c r="K2" s="30" t="s">
+      <c r="K2" s="26" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="25"/>
@@ -2991,27 +2991,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="29" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="25"/>
-      <c r="F4" s="28" t="s">
+      <c r="F4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="25"/>
-      <c r="H4" s="28" t="s">
+      <c r="H4" s="29" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="25"/>
-      <c r="K4" s="28" t="s">
+      <c r="K4" s="29" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="25"/>
-      <c r="M4" s="28" t="s">
+      <c r="M4" s="29" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="25"/>
@@ -3020,19 +3020,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="27"/>
+      <c r="B5" s="28"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="27"/>
+      <c r="G5" s="28"/>
       <c r="H5" s="25"/>
       <c r="I5" s="25"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="27"/>
+      <c r="L5" s="28"/>
       <c r="M5" s="25"/>
       <c r="N5" s="25"/>
     </row>
@@ -3040,19 +3040,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="26"/>
+      <c r="B6" s="27"/>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="26"/>
+      <c r="G6" s="27"/>
       <c r="H6" s="25"/>
       <c r="I6" s="25"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="26"/>
+      <c r="L6" s="27"/>
       <c r="M6" s="25"/>
       <c r="N6" s="25"/>
     </row>
@@ -3060,19 +3060,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="27"/>
+      <c r="B7" s="28"/>
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="27"/>
+      <c r="G7" s="28"/>
       <c r="H7" s="25"/>
       <c r="I7" s="25"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="27"/>
+      <c r="L7" s="28"/>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
     </row>
@@ -3080,19 +3080,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="26"/>
+      <c r="B8" s="27"/>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="26"/>
+      <c r="G8" s="27"/>
       <c r="H8" s="25"/>
       <c r="I8" s="25"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="26"/>
+      <c r="L8" s="27"/>
       <c r="M8" s="25"/>
       <c r="N8" s="25"/>
     </row>
@@ -3100,19 +3100,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="27"/>
+      <c r="B9" s="28"/>
       <c r="C9" s="25"/>
       <c r="D9" s="25"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="27"/>
+      <c r="G9" s="28"/>
       <c r="H9" s="25"/>
       <c r="I9" s="25"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="27"/>
+      <c r="L9" s="28"/>
       <c r="M9" s="25"/>
       <c r="N9" s="25"/>
     </row>
@@ -3120,19 +3120,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="26"/>
+      <c r="B10" s="27"/>
       <c r="C10" s="25"/>
       <c r="D10" s="25"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="26"/>
+      <c r="G10" s="27"/>
       <c r="H10" s="25"/>
       <c r="I10" s="25"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="26"/>
+      <c r="L10" s="27"/>
       <c r="M10" s="25"/>
       <c r="N10" s="25"/>
     </row>
@@ -3140,19 +3140,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="27"/>
+      <c r="B11" s="28"/>
       <c r="C11" s="25"/>
       <c r="D11" s="25"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="27"/>
+      <c r="G11" s="28"/>
       <c r="H11" s="25"/>
       <c r="I11" s="25"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="27"/>
+      <c r="L11" s="28"/>
       <c r="M11" s="25"/>
       <c r="N11" s="25"/>
     </row>
@@ -3160,19 +3160,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="26"/>
+      <c r="B12" s="27"/>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="26"/>
+      <c r="G12" s="27"/>
       <c r="H12" s="25"/>
       <c r="I12" s="25"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="26"/>
+      <c r="L12" s="27"/>
       <c r="M12" s="25"/>
       <c r="N12" s="25"/>
     </row>
@@ -3180,7 +3180,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="30">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3189,7 +3189,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="29">
+      <c r="G13" s="30">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3198,7 +3198,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="29">
+      <c r="L13" s="30">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3234,19 +3234,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
-      <c r="F25" s="30" t="s">
+      <c r="F25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
       <c r="I25" s="25"/>
-      <c r="K25" s="30" t="s">
+      <c r="K25" s="26" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="25"/>
@@ -3254,19 +3254,19 @@
       <c r="N25" s="25"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
-      <c r="F26" s="30" t="s">
+      <c r="F26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="25"/>
       <c r="H26" s="25"/>
       <c r="I26" s="25"/>
-      <c r="K26" s="30" t="s">
+      <c r="K26" s="26" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="25"/>
@@ -3288,27 +3288,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="25"/>
-      <c r="C28" s="28" t="s">
+      <c r="C28" s="29" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="25"/>
-      <c r="F28" s="28" t="s">
+      <c r="F28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="25"/>
-      <c r="H28" s="28" t="s">
+      <c r="H28" s="29" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="25"/>
-      <c r="K28" s="28" t="s">
+      <c r="K28" s="29" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="25"/>
-      <c r="M28" s="28" t="s">
+      <c r="M28" s="29" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="25"/>
@@ -3317,19 +3317,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="27"/>
+      <c r="B29" s="28"/>
       <c r="C29" s="25"/>
       <c r="D29" s="25"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="27"/>
+      <c r="G29" s="28"/>
       <c r="H29" s="25"/>
       <c r="I29" s="25"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="27"/>
+      <c r="L29" s="28"/>
       <c r="M29" s="25"/>
       <c r="N29" s="25"/>
     </row>
@@ -3337,19 +3337,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="26"/>
+      <c r="B30" s="27"/>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="26"/>
+      <c r="G30" s="27"/>
       <c r="H30" s="25"/>
       <c r="I30" s="25"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="26"/>
+      <c r="L30" s="27"/>
       <c r="M30" s="25"/>
       <c r="N30" s="25"/>
     </row>
@@ -3357,19 +3357,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="27"/>
+      <c r="B31" s="28"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="27"/>
+      <c r="G31" s="28"/>
       <c r="H31" s="25"/>
       <c r="I31" s="25"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="27"/>
+      <c r="L31" s="28"/>
       <c r="M31" s="25"/>
       <c r="N31" s="25"/>
     </row>
@@ -3377,19 +3377,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="26"/>
+      <c r="B32" s="27"/>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="26"/>
+      <c r="G32" s="27"/>
       <c r="H32" s="25"/>
       <c r="I32" s="25"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="26"/>
+      <c r="L32" s="27"/>
       <c r="M32" s="25"/>
       <c r="N32" s="25"/>
     </row>
@@ -3397,19 +3397,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="27"/>
+      <c r="B33" s="28"/>
       <c r="C33" s="25"/>
       <c r="D33" s="25"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="27"/>
+      <c r="G33" s="28"/>
       <c r="H33" s="25"/>
       <c r="I33" s="25"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="27"/>
+      <c r="L33" s="28"/>
       <c r="M33" s="25"/>
       <c r="N33" s="25"/>
     </row>
@@ -3417,19 +3417,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="26"/>
+      <c r="B34" s="27"/>
       <c r="C34" s="25"/>
       <c r="D34" s="25"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="26"/>
+      <c r="G34" s="27"/>
       <c r="H34" s="25"/>
       <c r="I34" s="25"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="26"/>
+      <c r="L34" s="27"/>
       <c r="M34" s="25"/>
       <c r="N34" s="25"/>
     </row>
@@ -3437,19 +3437,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="27"/>
+      <c r="B35" s="28"/>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="27"/>
+      <c r="G35" s="28"/>
       <c r="H35" s="25"/>
       <c r="I35" s="25"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="27"/>
+      <c r="L35" s="28"/>
       <c r="M35" s="25"/>
       <c r="N35" s="25"/>
     </row>
@@ -3457,19 +3457,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="26"/>
+      <c r="B36" s="27"/>
       <c r="C36" s="25"/>
       <c r="D36" s="25"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="26"/>
+      <c r="G36" s="27"/>
       <c r="H36" s="25"/>
       <c r="I36" s="25"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="26"/>
+      <c r="L36" s="27"/>
       <c r="M36" s="25"/>
       <c r="N36" s="25"/>
     </row>
@@ -3477,7 +3477,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="29">
+      <c r="B37" s="30">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -3486,7 +3486,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="29">
+      <c r="G37" s="30">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -3495,7 +3495,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="29">
+      <c r="L37" s="30">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -3532,6 +3532,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
     <mergeCell ref="L34:N34"/>
     <mergeCell ref="L6:N6"/>
     <mergeCell ref="B33:D33"/>
@@ -3548,68 +3610,6 @@
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3657,7 +3657,7 @@
         <v>49</v>
       </c>
       <c r="E2" s="18">
-        <v>120</v>
+        <v>180</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3674,7 +3674,7 @@
         <v>68</v>
       </c>
       <c r="E3" s="18">
-        <v>90</v>
+        <v>110</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -3691,7 +3691,7 @@
         <v>49</v>
       </c>
       <c r="E4" s="18">
-        <v>120</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3708,7 +3708,7 @@
         <v>68</v>
       </c>
       <c r="E5" s="18">
-        <v>90</v>
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -3725,7 +3725,7 @@
         <v>49</v>
       </c>
       <c r="E6" s="18">
-        <v>120</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -3742,7 +3742,7 @@
         <v>68</v>
       </c>
       <c r="E7" s="18">
-        <v>90</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -3759,7 +3759,7 @@
         <v>49</v>
       </c>
       <c r="E8" s="18">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -3776,7 +3776,7 @@
         <v>68</v>
       </c>
       <c r="E9" s="18">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -3793,7 +3793,7 @@
         <v>49</v>
       </c>
       <c r="E10" s="18">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -3810,7 +3810,7 @@
         <v>68</v>
       </c>
       <c r="E11" s="18">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -3827,7 +3827,7 @@
         <v>49</v>
       </c>
       <c r="E12" s="18">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -3844,7 +3844,7 @@
         <v>68</v>
       </c>
       <c r="E13" s="18">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -3861,7 +3861,7 @@
         <v>49</v>
       </c>
       <c r="E14" s="18">
-        <v>70</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -3878,7 +3878,7 @@
         <v>68</v>
       </c>
       <c r="E15" s="18">
-        <v>70</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -3895,7 +3895,7 @@
         <v>49</v>
       </c>
       <c r="E16" s="18">
-        <v>70</v>
+        <v>110</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -3912,7 +3912,7 @@
         <v>68</v>
       </c>
       <c r="E17" s="18">
-        <v>70</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -3929,7 +3929,7 @@
         <v>49</v>
       </c>
       <c r="E18" s="18">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -3946,7 +3946,7 @@
         <v>68</v>
       </c>
       <c r="E19" s="18">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -3963,7 +3963,7 @@
         <v>49</v>
       </c>
       <c r="E20" s="18">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -3980,7 +3980,7 @@
         <v>68</v>
       </c>
       <c r="E21" s="18">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -4057,7 +4057,7 @@
         <v>49</v>
       </c>
       <c r="E26" s="18">
-        <v>140</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -4074,7 +4074,7 @@
         <v>68</v>
       </c>
       <c r="E27" s="18">
-        <v>100</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -4091,7 +4091,7 @@
         <v>49</v>
       </c>
       <c r="E28" s="18">
-        <v>140</v>
+        <v>180</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -4108,7 +4108,7 @@
         <v>68</v>
       </c>
       <c r="E29" s="18">
-        <v>90</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -4125,7 +4125,7 @@
         <v>49</v>
       </c>
       <c r="E30" s="18">
-        <v>140</v>
+        <v>180</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -4142,7 +4142,7 @@
         <v>68</v>
       </c>
       <c r="E31" s="18">
-        <v>90</v>
+        <v>110</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -4159,7 +4159,7 @@
         <v>49</v>
       </c>
       <c r="E32" s="18">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -4176,7 +4176,7 @@
         <v>68</v>
       </c>
       <c r="E33" s="18">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -4193,7 +4193,7 @@
         <v>49</v>
       </c>
       <c r="E34" s="18">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -4210,7 +4210,7 @@
         <v>68</v>
       </c>
       <c r="E35" s="18">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -4227,7 +4227,7 @@
         <v>49</v>
       </c>
       <c r="E36" s="18">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -4244,7 +4244,7 @@
         <v>68</v>
       </c>
       <c r="E37" s="18">
-        <v>60</v>
+        <v>110</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -4261,7 +4261,7 @@
         <v>49</v>
       </c>
       <c r="E38" s="18">
-        <v>70</v>
+        <v>110</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -4278,7 +4278,7 @@
         <v>68</v>
       </c>
       <c r="E39" s="18">
-        <v>70</v>
+        <v>110</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -4295,7 +4295,7 @@
         <v>49</v>
       </c>
       <c r="E40" s="18">
-        <v>70</v>
+        <v>110</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -4312,7 +4312,7 @@
         <v>68</v>
       </c>
       <c r="E41" s="18">
-        <v>70</v>
+        <v>110</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -4329,7 +4329,7 @@
         <v>49</v>
       </c>
       <c r="E42" s="18">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -4346,7 +4346,7 @@
         <v>68</v>
       </c>
       <c r="E43" s="18">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -4363,7 +4363,7 @@
         <v>49</v>
       </c>
       <c r="E44" s="18">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -4380,7 +4380,7 @@
         <v>68</v>
       </c>
       <c r="E45" s="18">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
     <row r="46" spans="1:5">

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EE195B9-0A29-49A5-8552-9DBA9FB5F284}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88ABF152-E969-480B-9312-E2F32D72928E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -427,9 +427,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -440,6 +437,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -781,7 +781,7 @@
       </c>
       <c r="L5" s="14">
         <f>SUM(L6:L7)</f>
-        <v>2100</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
@@ -799,7 +799,7 @@
         <v>21</v>
       </c>
       <c r="L6" s="14">
-        <v>2100</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
@@ -938,7 +938,7 @@
       </c>
       <c r="L14" s="15">
         <f>SUM(L15:L16)</f>
-        <v>700</v>
+        <v>170</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1">
@@ -954,7 +954,7 @@
         <v>21</v>
       </c>
       <c r="L15" s="15">
-        <v>700</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="G26" s="15">
         <f>SUM(G27:G28)</f>
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="K26" s="9" t="s">
         <v>29</v>
@@ -1158,7 +1158,7 @@
         <v>21</v>
       </c>
       <c r="G27" s="15">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="K27" s="9" t="s">
         <v>21</v>
@@ -1199,7 +1199,7 @@
       </c>
       <c r="L29" s="14">
         <f>SUM(L30:L31)</f>
-        <v>320</v>
+        <v>750</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1">
@@ -1215,7 +1215,7 @@
         <v>21</v>
       </c>
       <c r="L30" s="14">
-        <v>320</v>
+        <v>750</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="L32" s="15">
         <f>SUM(L33:L34)</f>
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
@@ -1268,7 +1268,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="15">
-        <v>80</v>
+        <v>63</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="L38" s="23">
         <f>SUM(L39:L40)</f>
-        <v>50</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="15" customHeight="1">
@@ -1372,7 +1372,7 @@
         <v>21</v>
       </c>
       <c r="L39" s="15">
-        <v>50</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="15" customHeight="1">
@@ -1402,14 +1402,14 @@
       </c>
       <c r="G41" s="13">
         <f>SUM(G5,G8,G11,G14,G17,G20,G23,G26,G29,G32,G35,G38)</f>
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="L41" s="13">
         <f>SUM(L5,L8,L11,L14,L17,L20,L23,L26,L29,L32,L35,L38)</f>
-        <v>3250</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="B53" s="14">
         <f>SUM(B54:B55)</f>
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F53" s="7" t="s">
         <v>20</v>
@@ -1527,7 +1527,7 @@
         <v>21</v>
       </c>
       <c r="B54" s="14">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="F54" s="7" t="s">
         <v>21</v>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B62" s="15">
         <f>SUM(B63:B64)</f>
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>25</v>
@@ -1682,7 +1682,7 @@
         <v>21</v>
       </c>
       <c r="B63" s="15">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>21</v>
@@ -2125,7 +2125,7 @@
       </c>
       <c r="B89" s="13">
         <f>SUM(B53,B56,B59,B62,B65,B68,B71,B74,B77,B80,B83,B86)</f>
-        <v>440</v>
+        <v>370</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>34</v>
@@ -2189,19 +2189,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="25"/>
       <c r="H1" s="25"/>
       <c r="I1" s="25"/>
-      <c r="K1" s="26" t="s">
+      <c r="K1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="25"/>
@@ -2209,19 +2209,19 @@
       <c r="N1" s="25"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
       <c r="I2" s="25"/>
-      <c r="K2" s="26" t="s">
+      <c r="K2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="25"/>
@@ -2243,27 +2243,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="28" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="25"/>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="25"/>
-      <c r="H4" s="29" t="s">
+      <c r="H4" s="28" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="25"/>
-      <c r="K4" s="29" t="s">
+      <c r="K4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="25"/>
-      <c r="M4" s="29" t="s">
+      <c r="M4" s="28" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="25"/>
@@ -2272,7 +2272,7 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="28">
+      <c r="B5" s="27">
         <v>352</v>
       </c>
       <c r="C5" s="25"/>
@@ -2280,13 +2280,13 @@
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="28"/>
+      <c r="G5" s="27"/>
       <c r="H5" s="25"/>
       <c r="I5" s="25"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="28"/>
+      <c r="L5" s="27"/>
       <c r="M5" s="25"/>
       <c r="N5" s="25"/>
     </row>
@@ -2294,7 +2294,7 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="26">
         <v>376</v>
       </c>
       <c r="C6" s="25"/>
@@ -2302,13 +2302,13 @@
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="27"/>
+      <c r="G6" s="26"/>
       <c r="H6" s="25"/>
       <c r="I6" s="25"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="27"/>
+      <c r="L6" s="26"/>
       <c r="M6" s="25"/>
       <c r="N6" s="25"/>
     </row>
@@ -2316,7 +2316,7 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="27">
         <v>0</v>
       </c>
       <c r="C7" s="25"/>
@@ -2324,13 +2324,13 @@
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="28"/>
+      <c r="G7" s="27"/>
       <c r="H7" s="25"/>
       <c r="I7" s="25"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="28"/>
+      <c r="L7" s="27"/>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
     </row>
@@ -2338,7 +2338,7 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="26">
         <v>724</v>
       </c>
       <c r="C8" s="25"/>
@@ -2346,13 +2346,13 @@
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="27"/>
+      <c r="G8" s="26"/>
       <c r="H8" s="25"/>
       <c r="I8" s="25"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="27"/>
+      <c r="L8" s="26"/>
       <c r="M8" s="25"/>
       <c r="N8" s="25"/>
     </row>
@@ -2360,7 +2360,7 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="28">
+      <c r="B9" s="27">
         <v>411</v>
       </c>
       <c r="C9" s="25"/>
@@ -2368,13 +2368,13 @@
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="28"/>
+      <c r="G9" s="27"/>
       <c r="H9" s="25"/>
       <c r="I9" s="25"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="28"/>
+      <c r="L9" s="27"/>
       <c r="M9" s="25"/>
       <c r="N9" s="25"/>
     </row>
@@ -2382,7 +2382,7 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="27">
+      <c r="B10" s="26">
         <v>0</v>
       </c>
       <c r="C10" s="25"/>
@@ -2390,13 +2390,13 @@
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="27"/>
+      <c r="G10" s="26"/>
       <c r="H10" s="25"/>
       <c r="I10" s="25"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="27"/>
+      <c r="L10" s="26"/>
       <c r="M10" s="25"/>
       <c r="N10" s="25"/>
     </row>
@@ -2404,7 +2404,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="29">
         <f>SUM(B5:B10)</f>
         <v>1863</v>
       </c>
@@ -2413,7 +2413,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="30">
+      <c r="G11" s="29">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -2422,7 +2422,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="30">
+      <c r="L11" s="29">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -2458,19 +2458,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
-      <c r="F25" s="26" t="s">
+      <c r="F25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
       <c r="I25" s="25"/>
-      <c r="K25" s="26" t="s">
+      <c r="K25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="25"/>
@@ -2478,19 +2478,19 @@
       <c r="N25" s="25"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
-      <c r="F26" s="26" t="s">
+      <c r="F26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="25"/>
       <c r="H26" s="25"/>
       <c r="I26" s="25"/>
-      <c r="K26" s="26" t="s">
+      <c r="K26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="25"/>
@@ -2512,27 +2512,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="25"/>
-      <c r="C28" s="29" t="s">
+      <c r="C28" s="28" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="25"/>
-      <c r="F28" s="29" t="s">
+      <c r="F28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="25"/>
-      <c r="H28" s="29" t="s">
+      <c r="H28" s="28" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="25"/>
-      <c r="K28" s="29" t="s">
+      <c r="K28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="25"/>
-      <c r="M28" s="29" t="s">
+      <c r="M28" s="28" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="25"/>
@@ -2541,7 +2541,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="28">
+      <c r="B29" s="27">
         <v>0</v>
       </c>
       <c r="C29" s="25"/>
@@ -2549,13 +2549,13 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="28"/>
+      <c r="G29" s="27"/>
       <c r="H29" s="25"/>
       <c r="I29" s="25"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="28">
+      <c r="L29" s="27">
         <v>14</v>
       </c>
       <c r="M29" s="25"/>
@@ -2565,7 +2565,7 @@
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="27">
+      <c r="B30" s="26">
         <v>0</v>
       </c>
       <c r="C30" s="25"/>
@@ -2573,13 +2573,13 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="27"/>
+      <c r="G30" s="26"/>
       <c r="H30" s="25"/>
       <c r="I30" s="25"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="27">
+      <c r="L30" s="26">
         <v>605</v>
       </c>
       <c r="M30" s="25"/>
@@ -2589,7 +2589,7 @@
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="28">
+      <c r="B31" s="27">
         <v>0</v>
       </c>
       <c r="C31" s="25"/>
@@ -2597,13 +2597,13 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="28"/>
+      <c r="G31" s="27"/>
       <c r="H31" s="25"/>
       <c r="I31" s="25"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="28">
+      <c r="L31" s="27">
         <v>1708</v>
       </c>
       <c r="M31" s="25"/>
@@ -2613,7 +2613,7 @@
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="27">
+      <c r="B32" s="26">
         <v>0</v>
       </c>
       <c r="C32" s="25"/>
@@ -2621,13 +2621,13 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="27"/>
+      <c r="G32" s="26"/>
       <c r="H32" s="25"/>
       <c r="I32" s="25"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="27">
+      <c r="L32" s="26">
         <v>1395</v>
       </c>
       <c r="M32" s="25"/>
@@ -2637,7 +2637,7 @@
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="28">
+      <c r="B33" s="27">
         <v>0</v>
       </c>
       <c r="C33" s="25"/>
@@ -2645,13 +2645,13 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="28"/>
+      <c r="G33" s="27"/>
       <c r="H33" s="25"/>
       <c r="I33" s="25"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="28">
+      <c r="L33" s="27">
         <v>0</v>
       </c>
       <c r="M33" s="25"/>
@@ -2661,7 +2661,7 @@
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="27">
+      <c r="B34" s="26">
         <v>0</v>
       </c>
       <c r="C34" s="25"/>
@@ -2669,13 +2669,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="27"/>
+      <c r="G34" s="26"/>
       <c r="H34" s="25"/>
       <c r="I34" s="25"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="27">
+      <c r="L34" s="26">
         <v>0</v>
       </c>
       <c r="M34" s="25"/>
@@ -2685,7 +2685,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="30">
+      <c r="B35" s="29">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -2694,7 +2694,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="30">
+      <c r="G35" s="29">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -2703,7 +2703,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="30">
+      <c r="L35" s="29">
         <f>SUM(L29:L34)</f>
         <v>3722</v>
       </c>
@@ -2740,6 +2740,56 @@
     </row>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B10:D10"/>
@@ -2756,56 +2806,6 @@
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="H28:I28"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2821,7 +2821,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
@@ -2829,7 +2829,7 @@
       <c r="D1" s="25"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
@@ -2843,11 +2843,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="28" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="28" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="25"/>
@@ -2856,7 +2856,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="28"/>
+      <c r="B5" s="27"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
     </row>
@@ -2864,7 +2864,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="27"/>
+      <c r="B6" s="26"/>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
     </row>
@@ -2872,7 +2872,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="28"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
     </row>
@@ -2880,7 +2880,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="27"/>
+      <c r="B8" s="26"/>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
     </row>
@@ -2888,7 +2888,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="29">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -2937,19 +2937,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
       <c r="D1" s="25"/>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="25"/>
       <c r="H1" s="25"/>
       <c r="I1" s="25"/>
-      <c r="K1" s="26" t="s">
+      <c r="K1" s="30" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="25"/>
@@ -2957,19 +2957,19 @@
       <c r="N1" s="25"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
       <c r="D2" s="25"/>
-      <c r="F2" s="26" t="s">
+      <c r="F2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="25"/>
       <c r="H2" s="25"/>
       <c r="I2" s="25"/>
-      <c r="K2" s="26" t="s">
+      <c r="K2" s="30" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="25"/>
@@ -2991,27 +2991,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="25"/>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="28" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="25"/>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="25"/>
-      <c r="H4" s="29" t="s">
+      <c r="H4" s="28" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="25"/>
-      <c r="K4" s="29" t="s">
+      <c r="K4" s="28" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="25"/>
-      <c r="M4" s="29" t="s">
+      <c r="M4" s="28" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="25"/>
@@ -3020,19 +3020,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="28"/>
+      <c r="B5" s="27"/>
       <c r="C5" s="25"/>
       <c r="D5" s="25"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="28"/>
+      <c r="G5" s="27"/>
       <c r="H5" s="25"/>
       <c r="I5" s="25"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="28"/>
+      <c r="L5" s="27"/>
       <c r="M5" s="25"/>
       <c r="N5" s="25"/>
     </row>
@@ -3040,19 +3040,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="27"/>
+      <c r="B6" s="26"/>
       <c r="C6" s="25"/>
       <c r="D6" s="25"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="27"/>
+      <c r="G6" s="26"/>
       <c r="H6" s="25"/>
       <c r="I6" s="25"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="27"/>
+      <c r="L6" s="26"/>
       <c r="M6" s="25"/>
       <c r="N6" s="25"/>
     </row>
@@ -3060,19 +3060,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="28"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="25"/>
       <c r="D7" s="25"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="28"/>
+      <c r="G7" s="27"/>
       <c r="H7" s="25"/>
       <c r="I7" s="25"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="28"/>
+      <c r="L7" s="27"/>
       <c r="M7" s="25"/>
       <c r="N7" s="25"/>
     </row>
@@ -3080,19 +3080,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="27"/>
+      <c r="B8" s="26"/>
       <c r="C8" s="25"/>
       <c r="D8" s="25"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="27"/>
+      <c r="G8" s="26"/>
       <c r="H8" s="25"/>
       <c r="I8" s="25"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="27"/>
+      <c r="L8" s="26"/>
       <c r="M8" s="25"/>
       <c r="N8" s="25"/>
     </row>
@@ -3100,19 +3100,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="28"/>
+      <c r="B9" s="27"/>
       <c r="C9" s="25"/>
       <c r="D9" s="25"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="28"/>
+      <c r="G9" s="27"/>
       <c r="H9" s="25"/>
       <c r="I9" s="25"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="28"/>
+      <c r="L9" s="27"/>
       <c r="M9" s="25"/>
       <c r="N9" s="25"/>
     </row>
@@ -3120,19 +3120,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="27"/>
+      <c r="B10" s="26"/>
       <c r="C10" s="25"/>
       <c r="D10" s="25"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="27"/>
+      <c r="G10" s="26"/>
       <c r="H10" s="25"/>
       <c r="I10" s="25"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="27"/>
+      <c r="L10" s="26"/>
       <c r="M10" s="25"/>
       <c r="N10" s="25"/>
     </row>
@@ -3140,19 +3140,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="28"/>
+      <c r="B11" s="27"/>
       <c r="C11" s="25"/>
       <c r="D11" s="25"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="28"/>
+      <c r="G11" s="27"/>
       <c r="H11" s="25"/>
       <c r="I11" s="25"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="28"/>
+      <c r="L11" s="27"/>
       <c r="M11" s="25"/>
       <c r="N11" s="25"/>
     </row>
@@ -3160,19 +3160,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="27"/>
+      <c r="B12" s="26"/>
       <c r="C12" s="25"/>
       <c r="D12" s="25"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="27"/>
+      <c r="G12" s="26"/>
       <c r="H12" s="25"/>
       <c r="I12" s="25"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="27"/>
+      <c r="L12" s="26"/>
       <c r="M12" s="25"/>
       <c r="N12" s="25"/>
     </row>
@@ -3180,7 +3180,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="29">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3189,7 +3189,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="30">
+      <c r="G13" s="29">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3198,7 +3198,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="30">
+      <c r="L13" s="29">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3234,19 +3234,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="25"/>
       <c r="C25" s="25"/>
       <c r="D25" s="25"/>
-      <c r="F25" s="26" t="s">
+      <c r="F25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="25"/>
       <c r="H25" s="25"/>
       <c r="I25" s="25"/>
-      <c r="K25" s="26" t="s">
+      <c r="K25" s="30" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="25"/>
@@ -3254,19 +3254,19 @@
       <c r="N25" s="25"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="25"/>
       <c r="C26" s="25"/>
       <c r="D26" s="25"/>
-      <c r="F26" s="26" t="s">
+      <c r="F26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="25"/>
       <c r="H26" s="25"/>
       <c r="I26" s="25"/>
-      <c r="K26" s="26" t="s">
+      <c r="K26" s="30" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="25"/>
@@ -3288,27 +3288,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="25"/>
-      <c r="C28" s="29" t="s">
+      <c r="C28" s="28" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="25"/>
-      <c r="F28" s="29" t="s">
+      <c r="F28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="25"/>
-      <c r="H28" s="29" t="s">
+      <c r="H28" s="28" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="25"/>
-      <c r="K28" s="29" t="s">
+      <c r="K28" s="28" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="25"/>
-      <c r="M28" s="29" t="s">
+      <c r="M28" s="28" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="25"/>
@@ -3317,19 +3317,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="28"/>
+      <c r="B29" s="27"/>
       <c r="C29" s="25"/>
       <c r="D29" s="25"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="28"/>
+      <c r="G29" s="27"/>
       <c r="H29" s="25"/>
       <c r="I29" s="25"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="28"/>
+      <c r="L29" s="27"/>
       <c r="M29" s="25"/>
       <c r="N29" s="25"/>
     </row>
@@ -3337,19 +3337,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="27"/>
+      <c r="B30" s="26"/>
       <c r="C30" s="25"/>
       <c r="D30" s="25"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="27"/>
+      <c r="G30" s="26"/>
       <c r="H30" s="25"/>
       <c r="I30" s="25"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="27"/>
+      <c r="L30" s="26"/>
       <c r="M30" s="25"/>
       <c r="N30" s="25"/>
     </row>
@@ -3357,19 +3357,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="28"/>
+      <c r="B31" s="27"/>
       <c r="C31" s="25"/>
       <c r="D31" s="25"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="28"/>
+      <c r="G31" s="27"/>
       <c r="H31" s="25"/>
       <c r="I31" s="25"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="28"/>
+      <c r="L31" s="27"/>
       <c r="M31" s="25"/>
       <c r="N31" s="25"/>
     </row>
@@ -3377,19 +3377,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="27"/>
+      <c r="B32" s="26"/>
       <c r="C32" s="25"/>
       <c r="D32" s="25"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="27"/>
+      <c r="G32" s="26"/>
       <c r="H32" s="25"/>
       <c r="I32" s="25"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="27"/>
+      <c r="L32" s="26"/>
       <c r="M32" s="25"/>
       <c r="N32" s="25"/>
     </row>
@@ -3397,19 +3397,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="28"/>
+      <c r="B33" s="27"/>
       <c r="C33" s="25"/>
       <c r="D33" s="25"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="28"/>
+      <c r="G33" s="27"/>
       <c r="H33" s="25"/>
       <c r="I33" s="25"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="28"/>
+      <c r="L33" s="27"/>
       <c r="M33" s="25"/>
       <c r="N33" s="25"/>
     </row>
@@ -3417,19 +3417,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="27"/>
+      <c r="B34" s="26"/>
       <c r="C34" s="25"/>
       <c r="D34" s="25"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="27"/>
+      <c r="G34" s="26"/>
       <c r="H34" s="25"/>
       <c r="I34" s="25"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="27"/>
+      <c r="L34" s="26"/>
       <c r="M34" s="25"/>
       <c r="N34" s="25"/>
     </row>
@@ -3437,19 +3437,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="28"/>
+      <c r="B35" s="27"/>
       <c r="C35" s="25"/>
       <c r="D35" s="25"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="28"/>
+      <c r="G35" s="27"/>
       <c r="H35" s="25"/>
       <c r="I35" s="25"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="28"/>
+      <c r="L35" s="27"/>
       <c r="M35" s="25"/>
       <c r="N35" s="25"/>
     </row>
@@ -3457,19 +3457,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="27"/>
+      <c r="B36" s="26"/>
       <c r="C36" s="25"/>
       <c r="D36" s="25"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="27"/>
+      <c r="G36" s="26"/>
       <c r="H36" s="25"/>
       <c r="I36" s="25"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="27"/>
+      <c r="L36" s="26"/>
       <c r="M36" s="25"/>
       <c r="N36" s="25"/>
     </row>
@@ -3477,7 +3477,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="30">
+      <c r="B37" s="29">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -3486,7 +3486,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="30">
+      <c r="G37" s="29">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -3495,7 +3495,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="30">
+      <c r="L37" s="29">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -3532,6 +3532,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
     <mergeCell ref="G36:I36"/>
     <mergeCell ref="L32:N32"/>
     <mergeCell ref="L13:N13"/>
@@ -3548,68 +3610,6 @@
     <mergeCell ref="L33:N33"/>
     <mergeCell ref="L35:N35"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="L9:N9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88ABF152-E969-480B-9312-E2F32D72928E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE9C81CD-F619-4710-B189-E0DBDA203255}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -767,39 +767,39 @@
       </c>
       <c r="B5" s="21">
         <f>SUM(B6:B7)</f>
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G5" s="14">
         <f>SUM(G6:G7)</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="L5" s="14">
         <f>SUM(L6:L7)</f>
-        <v>1500</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
       <c r="A6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="14">
-        <v>800</v>
-      </c>
+      <c r="B6" s="14"/>
       <c r="F6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="14"/>
+      <c r="G6" s="14">
+        <v>200</v>
+      </c>
       <c r="K6" s="7" t="s">
         <v>21</v>
       </c>
       <c r="L6" s="14">
-        <v>1500</v>
+        <v>2300</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
@@ -836,7 +836,7 @@
       </c>
       <c r="L8" s="15">
         <f>SUM(L9:L10)</f>
-        <v>0</v>
+        <v>700</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1">
@@ -851,7 +851,9 @@
       <c r="K9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L9" s="15"/>
+      <c r="L9" s="15">
+        <v>700</v>
+      </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
       <c r="A10" s="9" t="s">
@@ -977,7 +979,7 @@
       </c>
       <c r="B17" s="14">
         <f>SUM(B18:B19)</f>
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>26</v>
@@ -998,9 +1000,7 @@
       <c r="A18" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="14">
-        <v>180</v>
-      </c>
+      <c r="B18" s="14"/>
       <c r="F18" s="7" t="s">
         <v>21</v>
       </c>
@@ -1395,21 +1395,21 @@
       </c>
       <c r="B41" s="13">
         <f>SUM(B5,B8,B11,B14,B17,B20,B23,B26,B29,B32,B35,B38)</f>
-        <v>980</v>
+        <v>0</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G41" s="13">
         <f>SUM(G5,G8,G11,G14,G17,G20,G23,G26,G29,G32,G35,G38)</f>
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="L41" s="13">
         <f>SUM(L5,L8,L11,L14,L17,L20,L23,L26,L29,L32,L35,L38)</f>
-        <v>2500</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="B53" s="14">
         <f>SUM(B54:B55)</f>
-        <v>300</v>
+        <v>750</v>
       </c>
       <c r="F53" s="7" t="s">
         <v>20</v>
@@ -1519,7 +1519,7 @@
       </c>
       <c r="L53" s="14">
         <f>SUM(L54:L55)</f>
-        <v>0</v>
+        <v>2700</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="15" customHeight="1">
@@ -1527,7 +1527,7 @@
         <v>21</v>
       </c>
       <c r="B54" s="14">
-        <v>300</v>
+        <v>750</v>
       </c>
       <c r="F54" s="7" t="s">
         <v>21</v>
@@ -1536,7 +1536,9 @@
       <c r="K54" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="L54" s="14"/>
+      <c r="L54" s="14">
+        <v>2700</v>
+      </c>
     </row>
     <row r="55" spans="1:14" ht="15" customHeight="1">
       <c r="A55" s="7" t="s">
@@ -1674,7 +1676,7 @@
       </c>
       <c r="L62" s="15">
         <f>SUM(L63:L64)</f>
-        <v>53</v>
+        <v>350</v>
       </c>
     </row>
     <row r="63" spans="1:14" ht="15" customHeight="1">
@@ -1692,7 +1694,7 @@
         <v>21</v>
       </c>
       <c r="L63" s="15">
-        <v>53</v>
+        <v>350</v>
       </c>
     </row>
     <row r="64" spans="1:14" ht="15" customHeight="1">
@@ -2125,7 +2127,7 @@
       </c>
       <c r="B89" s="13">
         <f>SUM(B53,B56,B59,B62,B65,B68,B71,B74,B77,B80,B83,B86)</f>
-        <v>370</v>
+        <v>820</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>34</v>
@@ -2139,7 +2141,7 @@
       </c>
       <c r="L89" s="13">
         <f>SUM(L53,L56,L59,L62,L65,L68,L71,L74,L77,L80,L83,L86)</f>
-        <v>53</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="90" spans="1:14" ht="15" customHeight="1">

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE9C81CD-F619-4710-B189-E0DBDA203255}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94497724-9416-4A22-BD98-382E2A2D7F9C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="743" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="74">
   <si>
     <t>Modelo de Disponibilidade por Cultura e Packing</t>
   </si>
@@ -247,6 +247,9 @@
   </si>
   <si>
     <t>Extrinha</t>
+  </si>
+  <si>
+    <t>CEAGESP</t>
   </si>
 </sst>
 </file>
@@ -362,7 +365,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -425,7 +428,6 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -440,6 +442,23 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -615,16 +634,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
+      <c r="A1" s="30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
     </row>
     <row r="3" spans="1:8" ht="29.25" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -692,7 +711,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:N91"/>
+  <dimension ref="A1:N133"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="22.25" style="11" customWidth="1"/>
@@ -767,39 +786,41 @@
       </c>
       <c r="B5" s="21">
         <f>SUM(B6:B7)</f>
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G5" s="14">
         <f>SUM(G6:G7)</f>
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="L5" s="14">
         <f>SUM(L6:L7)</f>
-        <v>2300</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
       <c r="A6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="14"/>
+      <c r="B6" s="14">
+        <v>2700</v>
+      </c>
       <c r="F6" s="7" t="s">
         <v>21</v>
       </c>
       <c r="G6" s="14">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>21</v>
       </c>
       <c r="L6" s="14">
-        <v>2300</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
@@ -822,7 +843,7 @@
       </c>
       <c r="B8" s="15">
         <f>SUM(B9:B10)</f>
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>23</v>
@@ -836,14 +857,16 @@
       </c>
       <c r="L8" s="15">
         <f>SUM(L9:L10)</f>
-        <v>700</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1">
       <c r="A9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="15"/>
+      <c r="B9" s="15">
+        <v>340</v>
+      </c>
       <c r="F9" s="9" t="s">
         <v>21</v>
       </c>
@@ -852,7 +875,7 @@
         <v>21</v>
       </c>
       <c r="L9" s="15">
-        <v>700</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
@@ -933,14 +956,14 @@
       </c>
       <c r="G14" s="15">
         <f>SUM(G15:G16)</f>
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="K14" s="9" t="s">
         <v>25</v>
       </c>
       <c r="L14" s="15">
         <f>SUM(L15:L16)</f>
-        <v>170</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1">
@@ -951,13 +974,13 @@
       <c r="F15" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="15"/>
+      <c r="G15" s="15">
+        <v>130</v>
+      </c>
       <c r="K15" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L15" s="15">
-        <v>170</v>
-      </c>
+      <c r="L15" s="15"/>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1">
       <c r="A16" s="9" t="s">
@@ -979,7 +1002,7 @@
       </c>
       <c r="B17" s="14">
         <f>SUM(B18:B19)</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>26</v>
@@ -1000,7 +1023,9 @@
       <c r="A18" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="14"/>
+      <c r="B18" s="14">
+        <v>50</v>
+      </c>
       <c r="F18" s="7" t="s">
         <v>21</v>
       </c>
@@ -1030,7 +1055,7 @@
       </c>
       <c r="B20" s="15">
         <f>SUM(B21:B22)</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>27</v>
@@ -1051,7 +1076,9 @@
       <c r="A21" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="15"/>
+      <c r="B21" s="15">
+        <v>300</v>
+      </c>
       <c r="F21" s="9" t="s">
         <v>21</v>
       </c>
@@ -1139,7 +1166,7 @@
       </c>
       <c r="G26" s="15">
         <f>SUM(G27:G28)</f>
-        <v>500</v>
+        <v>157</v>
       </c>
       <c r="K26" s="9" t="s">
         <v>29</v>
@@ -1158,7 +1185,7 @@
         <v>21</v>
       </c>
       <c r="G27" s="15">
-        <v>500</v>
+        <v>157</v>
       </c>
       <c r="K27" s="9" t="s">
         <v>21</v>
@@ -1199,7 +1226,7 @@
       </c>
       <c r="L29" s="14">
         <f>SUM(L30:L31)</f>
-        <v>750</v>
+        <v>720</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1">
@@ -1215,7 +1242,7 @@
         <v>21</v>
       </c>
       <c r="L30" s="14">
-        <v>750</v>
+        <v>720</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1">
@@ -1252,7 +1279,7 @@
       </c>
       <c r="L32" s="15">
         <f>SUM(L33:L34)</f>
-        <v>63</v>
+        <v>190</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
@@ -1268,7 +1295,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="15">
-        <v>63</v>
+        <v>190</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
@@ -1356,7 +1383,7 @@
       </c>
       <c r="L38" s="23">
         <f>SUM(L39:L40)</f>
-        <v>17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="15" customHeight="1">
@@ -1371,9 +1398,7 @@
       <c r="K39" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L39" s="15">
-        <v>17</v>
-      </c>
+      <c r="L39" s="15"/>
     </row>
     <row r="40" spans="1:14" ht="15" customHeight="1">
       <c r="A40" s="9" t="s">
@@ -1395,21 +1420,21 @@
       </c>
       <c r="B41" s="13">
         <f>SUM(B5,B8,B11,B14,B17,B20,B23,B26,B29,B32,B35,B38)</f>
-        <v>0</v>
+        <v>3390</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G41" s="13">
         <f>SUM(G5,G8,G11,G14,G17,G20,G23,G26,G29,G32,G35,G38)</f>
-        <v>700</v>
+        <v>687</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="L41" s="13">
         <f>SUM(L5,L8,L11,L14,L17,L20,L23,L26,L29,L32,L35,L38)</f>
-        <v>4000</v>
+        <v>6010</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1">
@@ -1505,7 +1530,7 @@
       </c>
       <c r="B53" s="14">
         <f>SUM(B54:B55)</f>
-        <v>750</v>
+        <v>0</v>
       </c>
       <c r="F53" s="7" t="s">
         <v>20</v>
@@ -1519,16 +1544,14 @@
       </c>
       <c r="L53" s="14">
         <f>SUM(L54:L55)</f>
-        <v>2700</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="15" customHeight="1">
       <c r="A54" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B54" s="14">
-        <v>750</v>
-      </c>
+      <c r="B54" s="14"/>
       <c r="F54" s="7" t="s">
         <v>21</v>
       </c>
@@ -1537,7 +1560,7 @@
         <v>21</v>
       </c>
       <c r="L54" s="14">
-        <v>2700</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="55" spans="1:14" ht="15" customHeight="1">
@@ -1662,7 +1685,7 @@
       </c>
       <c r="B62" s="15">
         <f>SUM(B63:B64)</f>
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>25</v>
@@ -1676,7 +1699,7 @@
       </c>
       <c r="L62" s="15">
         <f>SUM(L63:L64)</f>
-        <v>350</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:14" ht="15" customHeight="1">
@@ -1684,7 +1707,7 @@
         <v>21</v>
       </c>
       <c r="B63" s="15">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>21</v>
@@ -1693,9 +1716,7 @@
       <c r="K63" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L63" s="15">
-        <v>350</v>
-      </c>
+      <c r="L63" s="15"/>
     </row>
     <row r="64" spans="1:14" ht="15" customHeight="1">
       <c r="A64" s="9" t="s">
@@ -2127,7 +2148,7 @@
       </c>
       <c r="B89" s="13">
         <f>SUM(B53,B56,B59,B62,B65,B68,B71,B74,B77,B80,B83,B86)</f>
-        <v>820</v>
+        <v>60</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>34</v>
@@ -2141,7 +2162,7 @@
       </c>
       <c r="L89" s="13">
         <f>SUM(L53,L56,L59,L62,L65,L68,L71,L74,L77,L80,L83,L86)</f>
-        <v>3050</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="90" spans="1:14" ht="15" customHeight="1">
@@ -2171,6 +2192,628 @@
       <c r="L91" s="9"/>
       <c r="M91" s="9"/>
       <c r="N91" s="9"/>
+    </row>
+    <row r="93" spans="1:14" ht="15">
+      <c r="A93" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" s="24"/>
+      <c r="C93" s="24"/>
+      <c r="D93" s="24"/>
+      <c r="E93" s="24"/>
+      <c r="F93" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="G93" s="24"/>
+    </row>
+    <row r="94" spans="1:14" ht="15">
+      <c r="A94" s="10">
+        <f>A46</f>
+        <v>0</v>
+      </c>
+      <c r="B94" s="24"/>
+      <c r="C94" s="24"/>
+      <c r="D94" s="24"/>
+      <c r="E94" s="24"/>
+      <c r="F94" s="10">
+        <f>F46</f>
+        <v>0</v>
+      </c>
+      <c r="G94" s="24"/>
+    </row>
+    <row r="95" spans="1:14" ht="15">
+      <c r="A95" s="9"/>
+      <c r="B95" s="9"/>
+      <c r="C95" s="9"/>
+      <c r="D95" s="9"/>
+      <c r="E95" s="24"/>
+      <c r="F95" s="9"/>
+      <c r="G95" s="9"/>
+    </row>
+    <row r="96" spans="1:14" ht="15">
+      <c r="A96" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="B96" s="24"/>
+      <c r="C96" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="D96" s="24"/>
+      <c r="E96" s="24"/>
+      <c r="F96" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="G96" s="24"/>
+      <c r="H96" s="27" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" ht="15">
+      <c r="A97" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B97" s="26">
+        <f>SUM(B98:B99)</f>
+        <v>946</v>
+      </c>
+      <c r="C97" s="24"/>
+      <c r="D97" s="24"/>
+      <c r="E97" s="24"/>
+      <c r="F97" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G97" s="26">
+        <f>SUM(G98:G99)</f>
+        <v>633</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" ht="15">
+      <c r="A98" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B98" s="26">
+        <v>946</v>
+      </c>
+      <c r="C98" s="24"/>
+      <c r="D98" s="24"/>
+      <c r="E98" s="24"/>
+      <c r="F98" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G98" s="26">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" ht="15">
+      <c r="A99" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B99" s="26"/>
+      <c r="C99" s="24"/>
+      <c r="D99" s="24"/>
+      <c r="E99" s="24"/>
+      <c r="F99" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G99" s="26"/>
+    </row>
+    <row r="100" spans="1:7" ht="15">
+      <c r="A100" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B100" s="25">
+        <f>SUM(B101:B102)</f>
+        <v>0</v>
+      </c>
+      <c r="C100" s="24"/>
+      <c r="D100" s="24"/>
+      <c r="E100" s="24"/>
+      <c r="F100" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G100" s="25">
+        <f>SUM(G101:G102)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" ht="15">
+      <c r="A101" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B101" s="25"/>
+      <c r="C101" s="24"/>
+      <c r="D101" s="24"/>
+      <c r="E101" s="24"/>
+      <c r="F101" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G101" s="25"/>
+    </row>
+    <row r="102" spans="1:7" ht="15">
+      <c r="A102" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B102" s="25"/>
+      <c r="C102" s="24"/>
+      <c r="D102" s="24"/>
+      <c r="E102" s="24"/>
+      <c r="F102" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G102" s="25"/>
+    </row>
+    <row r="103" spans="1:7" ht="15">
+      <c r="A103" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B103" s="26">
+        <f>SUM(B104:B105)</f>
+        <v>0</v>
+      </c>
+      <c r="C103" s="24"/>
+      <c r="D103" s="24"/>
+      <c r="E103" s="24"/>
+      <c r="F103" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G103" s="26">
+        <f>SUM(G104:G105)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" ht="15">
+      <c r="A104" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B104" s="26"/>
+      <c r="C104" s="24"/>
+      <c r="D104" s="24"/>
+      <c r="E104" s="24"/>
+      <c r="F104" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G104" s="26"/>
+    </row>
+    <row r="105" spans="1:7" ht="15">
+      <c r="A105" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B105" s="26"/>
+      <c r="C105" s="24"/>
+      <c r="D105" s="24"/>
+      <c r="E105" s="24"/>
+      <c r="F105" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G105" s="26"/>
+    </row>
+    <row r="106" spans="1:7" ht="15">
+      <c r="A106" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B106" s="25">
+        <f>SUM(B107:B108)</f>
+        <v>0</v>
+      </c>
+      <c r="C106" s="24"/>
+      <c r="D106" s="24"/>
+      <c r="E106" s="24"/>
+      <c r="F106" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G106" s="25">
+        <f>SUM(G107:G108)</f>
+        <v>374</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" ht="15">
+      <c r="A107" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B107" s="25"/>
+      <c r="C107" s="24"/>
+      <c r="D107" s="24"/>
+      <c r="E107" s="24"/>
+      <c r="F107" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G107" s="25">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" ht="15">
+      <c r="A108" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B108" s="25"/>
+      <c r="C108" s="24"/>
+      <c r="D108" s="24"/>
+      <c r="E108" s="24"/>
+      <c r="F108" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G108" s="25"/>
+    </row>
+    <row r="109" spans="1:7" ht="15">
+      <c r="A109" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B109" s="26">
+        <f>SUM(B110:B111)</f>
+        <v>0</v>
+      </c>
+      <c r="C109" s="24"/>
+      <c r="D109" s="24"/>
+      <c r="E109" s="24"/>
+      <c r="F109" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G109" s="26">
+        <f>SUM(G110:G111)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" ht="15">
+      <c r="A110" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B110" s="26"/>
+      <c r="C110" s="24"/>
+      <c r="D110" s="24"/>
+      <c r="E110" s="24"/>
+      <c r="F110" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G110" s="26"/>
+    </row>
+    <row r="111" spans="1:7" ht="15">
+      <c r="A111" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B111" s="26"/>
+      <c r="C111" s="24"/>
+      <c r="D111" s="24"/>
+      <c r="E111" s="24"/>
+      <c r="F111" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G111" s="26"/>
+    </row>
+    <row r="112" spans="1:7" ht="15">
+      <c r="A112" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B112" s="25">
+        <f>SUM(B113:B114)</f>
+        <v>0</v>
+      </c>
+      <c r="C112" s="24"/>
+      <c r="D112" s="24"/>
+      <c r="E112" s="24"/>
+      <c r="F112" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G112" s="25">
+        <f>SUM(G113:G114)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" ht="15">
+      <c r="A113" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B113" s="25"/>
+      <c r="C113" s="24"/>
+      <c r="D113" s="24"/>
+      <c r="E113" s="24"/>
+      <c r="F113" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G113" s="25"/>
+    </row>
+    <row r="114" spans="1:7" ht="15">
+      <c r="A114" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B114" s="25"/>
+      <c r="C114" s="24"/>
+      <c r="D114" s="24"/>
+      <c r="E114" s="24"/>
+      <c r="F114" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G114" s="25"/>
+    </row>
+    <row r="115" spans="1:7" ht="15">
+      <c r="A115" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B115" s="26">
+        <f>SUM(B116:B117)</f>
+        <v>0</v>
+      </c>
+      <c r="C115" s="24"/>
+      <c r="D115" s="24"/>
+      <c r="E115" s="24"/>
+      <c r="F115" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G115" s="26">
+        <f>SUM(G116:G117)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" ht="15">
+      <c r="A116" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B116" s="26"/>
+      <c r="C116" s="24"/>
+      <c r="D116" s="24"/>
+      <c r="E116" s="24"/>
+      <c r="F116" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G116" s="26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" ht="15">
+      <c r="A117" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B117" s="26"/>
+      <c r="C117" s="24"/>
+      <c r="D117" s="24"/>
+      <c r="E117" s="24"/>
+      <c r="F117" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G117" s="26"/>
+    </row>
+    <row r="118" spans="1:7" ht="15">
+      <c r="A118" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B118" s="25">
+        <f>SUM(B119:B120)</f>
+        <v>0</v>
+      </c>
+      <c r="C118" s="24"/>
+      <c r="D118" s="24"/>
+      <c r="E118" s="24"/>
+      <c r="F118" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="G118" s="25">
+        <f>SUM(G119:G120)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" ht="15">
+      <c r="A119" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B119" s="25"/>
+      <c r="C119" s="24"/>
+      <c r="D119" s="24"/>
+      <c r="E119" s="24"/>
+      <c r="F119" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G119" s="25"/>
+    </row>
+    <row r="120" spans="1:7" ht="15">
+      <c r="A120" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B120" s="25"/>
+      <c r="C120" s="24"/>
+      <c r="D120" s="24"/>
+      <c r="E120" s="24"/>
+      <c r="F120" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G120" s="25"/>
+    </row>
+    <row r="121" spans="1:7" ht="15">
+      <c r="A121" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B121" s="26">
+        <f>SUM(B122:B123)</f>
+        <v>0</v>
+      </c>
+      <c r="C121" s="24"/>
+      <c r="D121" s="24"/>
+      <c r="E121" s="24"/>
+      <c r="F121" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="G121" s="26">
+        <f>SUM(G122:G123)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" ht="15">
+      <c r="A122" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B122" s="26"/>
+      <c r="C122" s="24"/>
+      <c r="D122" s="24"/>
+      <c r="E122" s="24"/>
+      <c r="F122" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G122" s="26"/>
+    </row>
+    <row r="123" spans="1:7" ht="15">
+      <c r="A123" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B123" s="26"/>
+      <c r="C123" s="24"/>
+      <c r="D123" s="24"/>
+      <c r="E123" s="24"/>
+      <c r="F123" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G123" s="26"/>
+    </row>
+    <row r="124" spans="1:7" ht="15">
+      <c r="A124" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B124" s="25">
+        <f>SUM(B125:B126)</f>
+        <v>0</v>
+      </c>
+      <c r="C124" s="24"/>
+      <c r="D124" s="24"/>
+      <c r="E124" s="24"/>
+      <c r="F124" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="G124" s="25">
+        <f>SUM(G125:G126)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" ht="15">
+      <c r="A125" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B125" s="25"/>
+      <c r="C125" s="24"/>
+      <c r="D125" s="24"/>
+      <c r="E125" s="24"/>
+      <c r="F125" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G125" s="25"/>
+    </row>
+    <row r="126" spans="1:7" ht="15">
+      <c r="A126" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B126" s="25"/>
+      <c r="C126" s="24"/>
+      <c r="D126" s="24"/>
+      <c r="E126" s="24"/>
+      <c r="F126" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G126" s="25"/>
+    </row>
+    <row r="127" spans="1:7" ht="15">
+      <c r="A127" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B127" s="26">
+        <f>SUM(B128:B129)</f>
+        <v>0</v>
+      </c>
+      <c r="C127" s="24"/>
+      <c r="D127" s="24"/>
+      <c r="E127" s="24"/>
+      <c r="F127" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="G127" s="26">
+        <f>SUM(G128:G129)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" ht="15">
+      <c r="A128" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B128" s="26"/>
+      <c r="C128" s="24"/>
+      <c r="D128" s="24"/>
+      <c r="E128" s="24"/>
+      <c r="F128" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G128" s="26"/>
+    </row>
+    <row r="129" spans="1:7" ht="15">
+      <c r="A129" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B129" s="26"/>
+      <c r="C129" s="24"/>
+      <c r="D129" s="24"/>
+      <c r="E129" s="24"/>
+      <c r="F129" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G129" s="26"/>
+    </row>
+    <row r="130" spans="1:7" ht="15">
+      <c r="A130" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="B130" s="25">
+        <f>SUM(B131:B132)</f>
+        <v>0</v>
+      </c>
+      <c r="C130" s="24"/>
+      <c r="D130" s="24"/>
+      <c r="E130" s="24"/>
+      <c r="F130" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="G130" s="25">
+        <f>SUM(G131:G132)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" ht="15">
+      <c r="A131" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B131" s="25"/>
+      <c r="C131" s="24"/>
+      <c r="D131" s="24"/>
+      <c r="E131" s="24"/>
+      <c r="F131" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="G131" s="25"/>
+    </row>
+    <row r="132" spans="1:7" ht="15">
+      <c r="A132" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B132" s="25"/>
+      <c r="C132" s="24"/>
+      <c r="D132" s="24"/>
+      <c r="E132" s="24"/>
+      <c r="F132" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="G132" s="25"/>
+    </row>
+    <row r="133" spans="1:7" ht="15">
+      <c r="A133" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B133" s="28">
+        <f>SUM(B97,B100,B103,B106,B109,B112,B115,B118,B121,B124,B127,B130)</f>
+        <v>946</v>
+      </c>
+      <c r="C133" s="24"/>
+      <c r="D133" s="24"/>
+      <c r="E133" s="24"/>
+      <c r="F133" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="G133" s="28">
+        <f>SUM(G97,G100,G103,G106,G109,G112,G115,G118,G121,G124,G127,G130)</f>
+        <v>1007</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2191,44 +2834,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="F1" s="30" t="s">
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="F1" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="K1" s="30" t="s">
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="K1" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="F2" s="30" t="s">
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="F2" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="K2" s="30" t="s">
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="K2" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
     </row>
     <row r="3" spans="1:14" ht="15" customHeight="1">
       <c r="A3" s="9"/>
@@ -2245,191 +2888,191 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="28" t="s">
+      <c r="B4" s="31"/>
+      <c r="C4" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="25"/>
-      <c r="F4" s="28" t="s">
+      <c r="D4" s="31"/>
+      <c r="F4" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="25"/>
-      <c r="H4" s="28" t="s">
+      <c r="G4" s="31"/>
+      <c r="H4" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="I4" s="25"/>
-      <c r="K4" s="28" t="s">
+      <c r="I4" s="31"/>
+      <c r="K4" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="L4" s="25"/>
-      <c r="M4" s="28" t="s">
+      <c r="L4" s="31"/>
+      <c r="M4" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="N4" s="25"/>
+      <c r="N4" s="31"/>
     </row>
     <row r="5" spans="1:14" ht="15" customHeight="1">
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="34">
         <v>352</v>
       </c>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="27"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="27"/>
-      <c r="M5" s="25"/>
-      <c r="N5" s="25"/>
+      <c r="L5" s="34"/>
+      <c r="M5" s="31"/>
+      <c r="N5" s="31"/>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="26">
+      <c r="B6" s="33">
         <v>376</v>
       </c>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="26"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="26"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
+      <c r="L6" s="33"/>
+      <c r="M6" s="31"/>
+      <c r="N6" s="31"/>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="27">
-        <v>0</v>
-      </c>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
+      <c r="B7" s="34">
+        <v>0</v>
+      </c>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="27"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="25"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="27"/>
-      <c r="M7" s="25"/>
-      <c r="N7" s="25"/>
+      <c r="L7" s="34"/>
+      <c r="M7" s="31"/>
+      <c r="N7" s="31"/>
     </row>
     <row r="8" spans="1:14" ht="15" customHeight="1">
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="26">
+      <c r="B8" s="33">
         <v>724</v>
       </c>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="26"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="25"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="26"/>
-      <c r="M8" s="25"/>
-      <c r="N8" s="25"/>
+      <c r="L8" s="33"/>
+      <c r="M8" s="31"/>
+      <c r="N8" s="31"/>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1">
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="27">
+      <c r="B9" s="34">
         <v>411</v>
       </c>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="27"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="25"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="27"/>
-      <c r="M9" s="25"/>
-      <c r="N9" s="25"/>
+      <c r="L9" s="34"/>
+      <c r="M9" s="31"/>
+      <c r="N9" s="31"/>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="26">
-        <v>0</v>
-      </c>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
+      <c r="B10" s="33">
+        <v>0</v>
+      </c>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="26"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="25"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="26"/>
-      <c r="M10" s="25"/>
-      <c r="N10" s="25"/>
+      <c r="L10" s="33"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="31"/>
     </row>
     <row r="11" spans="1:14" ht="15" customHeight="1">
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="29">
+      <c r="B11" s="36">
         <f>SUM(B5:B10)</f>
         <v>1863</v>
       </c>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="29">
+      <c r="G11" s="36">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="29">
+      <c r="L11" s="36">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
-      <c r="M11" s="25"/>
-      <c r="N11" s="25"/>
+      <c r="M11" s="31"/>
+      <c r="N11" s="31"/>
     </row>
     <row r="12" spans="1:14" ht="15" customHeight="1">
       <c r="A12" s="9"/>
@@ -2460,44 +3103,44 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="B25" s="25"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="25"/>
-      <c r="F25" s="30" t="s">
+      <c r="B25" s="31"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
+      <c r="F25" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="G25" s="25"/>
-      <c r="H25" s="25"/>
-      <c r="I25" s="25"/>
-      <c r="K25" s="30" t="s">
+      <c r="G25" s="31"/>
+      <c r="H25" s="31"/>
+      <c r="I25" s="31"/>
+      <c r="K25" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="L25" s="25"/>
-      <c r="M25" s="25"/>
-      <c r="N25" s="25"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="31"/>
+      <c r="N25" s="31"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="25"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="25"/>
-      <c r="F26" s="30" t="s">
+      <c r="B26" s="31"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="F26" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="G26" s="25"/>
-      <c r="H26" s="25"/>
-      <c r="I26" s="25"/>
-      <c r="K26" s="30" t="s">
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="K26" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="L26" s="25"/>
-      <c r="M26" s="25"/>
-      <c r="N26" s="25"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31"/>
+      <c r="N26" s="31"/>
     </row>
     <row r="27" spans="1:14" ht="15" customHeight="1">
       <c r="A27" s="9"/>
@@ -2514,203 +3157,203 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="B28" s="25"/>
-      <c r="C28" s="28" t="s">
+      <c r="B28" s="31"/>
+      <c r="C28" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="D28" s="25"/>
-      <c r="F28" s="28" t="s">
+      <c r="D28" s="31"/>
+      <c r="F28" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="G28" s="25"/>
-      <c r="H28" s="28" t="s">
+      <c r="G28" s="31"/>
+      <c r="H28" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="I28" s="25"/>
-      <c r="K28" s="28" t="s">
+      <c r="I28" s="31"/>
+      <c r="K28" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="L28" s="25"/>
-      <c r="M28" s="28" t="s">
+      <c r="L28" s="31"/>
+      <c r="M28" s="35" t="s">
         <v>40</v>
       </c>
-      <c r="N28" s="25"/>
+      <c r="N28" s="31"/>
     </row>
     <row r="29" spans="1:14" ht="15" customHeight="1">
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="27">
-        <v>0</v>
-      </c>
-      <c r="C29" s="25"/>
-      <c r="D29" s="25"/>
+      <c r="B29" s="34">
+        <v>0</v>
+      </c>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="27"/>
-      <c r="H29" s="25"/>
-      <c r="I29" s="25"/>
+      <c r="G29" s="34"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="31"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="27">
+      <c r="L29" s="34">
         <v>14</v>
       </c>
-      <c r="M29" s="25"/>
-      <c r="N29" s="25"/>
+      <c r="M29" s="31"/>
+      <c r="N29" s="31"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="26">
-        <v>0</v>
-      </c>
-      <c r="C30" s="25"/>
-      <c r="D30" s="25"/>
+      <c r="B30" s="33">
+        <v>0</v>
+      </c>
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="26"/>
-      <c r="H30" s="25"/>
-      <c r="I30" s="25"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="31"/>
+      <c r="I30" s="31"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="26">
+      <c r="L30" s="33">
         <v>605</v>
       </c>
-      <c r="M30" s="25"/>
-      <c r="N30" s="25"/>
+      <c r="M30" s="31"/>
+      <c r="N30" s="31"/>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1">
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="27">
-        <v>0</v>
-      </c>
-      <c r="C31" s="25"/>
-      <c r="D31" s="25"/>
+      <c r="B31" s="34">
+        <v>0</v>
+      </c>
+      <c r="C31" s="31"/>
+      <c r="D31" s="31"/>
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="27"/>
-      <c r="H31" s="25"/>
-      <c r="I31" s="25"/>
+      <c r="G31" s="34"/>
+      <c r="H31" s="31"/>
+      <c r="I31" s="31"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="27">
+      <c r="L31" s="34">
         <v>1708</v>
       </c>
-      <c r="M31" s="25"/>
-      <c r="N31" s="25"/>
+      <c r="M31" s="31"/>
+      <c r="N31" s="31"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="26">
-        <v>0</v>
-      </c>
-      <c r="C32" s="25"/>
-      <c r="D32" s="25"/>
+      <c r="B32" s="33">
+        <v>0</v>
+      </c>
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="26"/>
-      <c r="H32" s="25"/>
-      <c r="I32" s="25"/>
+      <c r="G32" s="33"/>
+      <c r="H32" s="31"/>
+      <c r="I32" s="31"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="26">
+      <c r="L32" s="33">
         <v>1395</v>
       </c>
-      <c r="M32" s="25"/>
-      <c r="N32" s="25"/>
+      <c r="M32" s="31"/>
+      <c r="N32" s="31"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="27">
-        <v>0</v>
-      </c>
-      <c r="C33" s="25"/>
-      <c r="D33" s="25"/>
+      <c r="B33" s="34">
+        <v>0</v>
+      </c>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="27"/>
-      <c r="H33" s="25"/>
-      <c r="I33" s="25"/>
+      <c r="G33" s="34"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="31"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="27">
-        <v>0</v>
-      </c>
-      <c r="M33" s="25"/>
-      <c r="N33" s="25"/>
+      <c r="L33" s="34">
+        <v>0</v>
+      </c>
+      <c r="M33" s="31"/>
+      <c r="N33" s="31"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="26">
-        <v>0</v>
-      </c>
-      <c r="C34" s="25"/>
-      <c r="D34" s="25"/>
+      <c r="B34" s="33">
+        <v>0</v>
+      </c>
+      <c r="C34" s="31"/>
+      <c r="D34" s="31"/>
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="26"/>
-      <c r="H34" s="25"/>
-      <c r="I34" s="25"/>
+      <c r="G34" s="33"/>
+      <c r="H34" s="31"/>
+      <c r="I34" s="31"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="26">
-        <v>0</v>
-      </c>
-      <c r="M34" s="25"/>
-      <c r="N34" s="25"/>
+      <c r="L34" s="33">
+        <v>0</v>
+      </c>
+      <c r="M34" s="31"/>
+      <c r="N34" s="31"/>
     </row>
     <row r="35" spans="1:14" ht="15" customHeight="1">
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="29">
+      <c r="B35" s="36">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
-      <c r="C35" s="25"/>
-      <c r="D35" s="25"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="29">
+      <c r="G35" s="36">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
-      <c r="H35" s="25"/>
-      <c r="I35" s="25"/>
+      <c r="H35" s="31"/>
+      <c r="I35" s="31"/>
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="29">
+      <c r="L35" s="36">
         <f>SUM(L29:L34)</f>
         <v>3722</v>
       </c>
-      <c r="M35" s="25"/>
-      <c r="N35" s="25"/>
+      <c r="M35" s="31"/>
+      <c r="N35" s="31"/>
     </row>
     <row r="36" spans="1:14" ht="15" customHeight="1">
       <c r="A36" s="9"/>
@@ -2742,13 +3385,49 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="L11:N11"/>
@@ -2765,49 +3444,13 @@
     <mergeCell ref="K2:N2"/>
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2823,20 +3466,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1">
       <c r="A3" s="9"/>
@@ -2845,57 +3488,57 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="28" t="s">
+      <c r="B4" s="31"/>
+      <c r="C4" s="35" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="25"/>
+      <c r="D4" s="31"/>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1">
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="27"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1">
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="26"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
+      <c r="B6" s="33"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="27"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1">
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1">
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="36">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1">
       <c r="A10" s="9"/>
@@ -2939,44 +3582,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="F1" s="30" t="s">
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="F1" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="K1" s="30" t="s">
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="K1" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="F2" s="30" t="s">
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="F2" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="K2" s="30" t="s">
+      <c r="G2" s="31"/>
+      <c r="H2" s="31"/>
+      <c r="I2" s="31"/>
+      <c r="K2" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="31"/>
+      <c r="N2" s="31"/>
     </row>
     <row r="3" spans="1:14" ht="15" customHeight="1">
       <c r="A3" s="9"/>
@@ -2993,219 +3636,219 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="25"/>
-      <c r="C4" s="28" t="s">
+      <c r="B4" s="31"/>
+      <c r="C4" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="D4" s="25"/>
-      <c r="F4" s="28" t="s">
+      <c r="D4" s="31"/>
+      <c r="F4" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="25"/>
-      <c r="H4" s="28" t="s">
+      <c r="G4" s="31"/>
+      <c r="H4" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="I4" s="25"/>
-      <c r="K4" s="28" t="s">
+      <c r="I4" s="31"/>
+      <c r="K4" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="L4" s="25"/>
-      <c r="M4" s="28" t="s">
+      <c r="L4" s="31"/>
+      <c r="M4" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="N4" s="25"/>
+      <c r="N4" s="31"/>
     </row>
     <row r="5" spans="1:14" ht="15" customHeight="1">
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="27"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
+      <c r="B5" s="34"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="31"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="27"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
+      <c r="G5" s="34"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="27"/>
-      <c r="M5" s="25"/>
-      <c r="N5" s="25"/>
+      <c r="L5" s="34"/>
+      <c r="M5" s="31"/>
+      <c r="N5" s="31"/>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="26"/>
-      <c r="C6" s="25"/>
-      <c r="D6" s="25"/>
+      <c r="B6" s="33"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="26"/>
-      <c r="H6" s="25"/>
-      <c r="I6" s="25"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="26"/>
-      <c r="M6" s="25"/>
-      <c r="N6" s="25"/>
+      <c r="L6" s="33"/>
+      <c r="M6" s="31"/>
+      <c r="N6" s="31"/>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="27"/>
-      <c r="C7" s="25"/>
-      <c r="D7" s="25"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="31"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="27"/>
-      <c r="H7" s="25"/>
-      <c r="I7" s="25"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="27"/>
-      <c r="M7" s="25"/>
-      <c r="N7" s="25"/>
+      <c r="L7" s="34"/>
+      <c r="M7" s="31"/>
+      <c r="N7" s="31"/>
     </row>
     <row r="8" spans="1:14" ht="15" customHeight="1">
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="25"/>
-      <c r="D8" s="25"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="31"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="26"/>
-      <c r="H8" s="25"/>
-      <c r="I8" s="25"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="26"/>
-      <c r="M8" s="25"/>
-      <c r="N8" s="25"/>
+      <c r="L8" s="33"/>
+      <c r="M8" s="31"/>
+      <c r="N8" s="31"/>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1">
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="27"/>
-      <c r="C9" s="25"/>
-      <c r="D9" s="25"/>
+      <c r="B9" s="34"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="31"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="27"/>
-      <c r="H9" s="25"/>
-      <c r="I9" s="25"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="27"/>
-      <c r="M9" s="25"/>
-      <c r="N9" s="25"/>
+      <c r="L9" s="34"/>
+      <c r="M9" s="31"/>
+      <c r="N9" s="31"/>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="26"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="31"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="26"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="25"/>
+      <c r="G10" s="33"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="26"/>
-      <c r="M10" s="25"/>
-      <c r="N10" s="25"/>
+      <c r="L10" s="33"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="31"/>
     </row>
     <row r="11" spans="1:14" ht="15" customHeight="1">
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="27"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="31"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="27"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="27"/>
-      <c r="M11" s="25"/>
-      <c r="N11" s="25"/>
+      <c r="L11" s="34"/>
+      <c r="M11" s="31"/>
+      <c r="N11" s="31"/>
     </row>
     <row r="12" spans="1:14" ht="15" customHeight="1">
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="26"/>
-      <c r="C12" s="25"/>
-      <c r="D12" s="25"/>
+      <c r="B12" s="33"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="31"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="26"/>
-      <c r="H12" s="25"/>
-      <c r="I12" s="25"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="26"/>
-      <c r="M12" s="25"/>
-      <c r="N12" s="25"/>
+      <c r="L12" s="33"/>
+      <c r="M12" s="31"/>
+      <c r="N12" s="31"/>
     </row>
     <row r="13" spans="1:14" ht="15" customHeight="1">
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="29">
+      <c r="B13" s="36">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
-      <c r="C13" s="25"/>
-      <c r="D13" s="25"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="29">
+      <c r="G13" s="36">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
-      <c r="H13" s="25"/>
-      <c r="I13" s="25"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="29">
+      <c r="L13" s="36">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
-      <c r="M13" s="25"/>
-      <c r="N13" s="25"/>
+      <c r="M13" s="31"/>
+      <c r="N13" s="31"/>
     </row>
     <row r="14" spans="1:14" ht="15" customHeight="1">
       <c r="A14" s="9"/>
@@ -3236,44 +3879,44 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="B25" s="25"/>
-      <c r="C25" s="25"/>
-      <c r="D25" s="25"/>
-      <c r="F25" s="30" t="s">
+      <c r="B25" s="31"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="31"/>
+      <c r="F25" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="G25" s="25"/>
-      <c r="H25" s="25"/>
-      <c r="I25" s="25"/>
-      <c r="K25" s="30" t="s">
+      <c r="G25" s="31"/>
+      <c r="H25" s="31"/>
+      <c r="I25" s="31"/>
+      <c r="K25" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="L25" s="25"/>
-      <c r="M25" s="25"/>
-      <c r="N25" s="25"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="31"/>
+      <c r="N25" s="31"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="25"/>
-      <c r="C26" s="25"/>
-      <c r="D26" s="25"/>
-      <c r="F26" s="30" t="s">
+      <c r="B26" s="31"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="F26" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="G26" s="25"/>
-      <c r="H26" s="25"/>
-      <c r="I26" s="25"/>
-      <c r="K26" s="30" t="s">
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="K26" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="L26" s="25"/>
-      <c r="M26" s="25"/>
-      <c r="N26" s="25"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31"/>
+      <c r="N26" s="31"/>
     </row>
     <row r="27" spans="1:14" ht="15" customHeight="1">
       <c r="A27" s="9"/>
@@ -3290,219 +3933,219 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="28" t="s">
+      <c r="A28" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="B28" s="25"/>
-      <c r="C28" s="28" t="s">
+      <c r="B28" s="31"/>
+      <c r="C28" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="D28" s="25"/>
-      <c r="F28" s="28" t="s">
+      <c r="D28" s="31"/>
+      <c r="F28" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="G28" s="25"/>
-      <c r="H28" s="28" t="s">
+      <c r="G28" s="31"/>
+      <c r="H28" s="35" t="s">
         <v>54</v>
       </c>
-      <c r="I28" s="25"/>
-      <c r="K28" s="28" t="s">
+      <c r="I28" s="31"/>
+      <c r="K28" s="35" t="s">
         <v>47</v>
       </c>
-      <c r="L28" s="25"/>
-      <c r="M28" s="28" t="s">
+      <c r="L28" s="31"/>
+      <c r="M28" s="35" t="s">
         <v>55</v>
       </c>
-      <c r="N28" s="25"/>
+      <c r="N28" s="31"/>
     </row>
     <row r="29" spans="1:14" ht="15" customHeight="1">
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="27"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="25"/>
+      <c r="B29" s="34"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="27"/>
-      <c r="H29" s="25"/>
-      <c r="I29" s="25"/>
+      <c r="G29" s="34"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="31"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="27"/>
-      <c r="M29" s="25"/>
-      <c r="N29" s="25"/>
+      <c r="L29" s="34"/>
+      <c r="M29" s="31"/>
+      <c r="N29" s="31"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="26"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="25"/>
+      <c r="B30" s="33"/>
+      <c r="C30" s="31"/>
+      <c r="D30" s="31"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="26"/>
-      <c r="H30" s="25"/>
-      <c r="I30" s="25"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="31"/>
+      <c r="I30" s="31"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="26"/>
-      <c r="M30" s="25"/>
-      <c r="N30" s="25"/>
+      <c r="L30" s="33"/>
+      <c r="M30" s="31"/>
+      <c r="N30" s="31"/>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1">
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="27"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="25"/>
+      <c r="B31" s="34"/>
+      <c r="C31" s="31"/>
+      <c r="D31" s="31"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="27"/>
-      <c r="H31" s="25"/>
-      <c r="I31" s="25"/>
+      <c r="G31" s="34"/>
+      <c r="H31" s="31"/>
+      <c r="I31" s="31"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="27"/>
-      <c r="M31" s="25"/>
-      <c r="N31" s="25"/>
+      <c r="L31" s="34"/>
+      <c r="M31" s="31"/>
+      <c r="N31" s="31"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="26"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="25"/>
+      <c r="B32" s="33"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="26"/>
-      <c r="H32" s="25"/>
-      <c r="I32" s="25"/>
+      <c r="G32" s="33"/>
+      <c r="H32" s="31"/>
+      <c r="I32" s="31"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="26"/>
-      <c r="M32" s="25"/>
-      <c r="N32" s="25"/>
+      <c r="L32" s="33"/>
+      <c r="M32" s="31"/>
+      <c r="N32" s="31"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="27"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="25"/>
+      <c r="B33" s="34"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="27"/>
-      <c r="H33" s="25"/>
-      <c r="I33" s="25"/>
+      <c r="G33" s="34"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="31"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="27"/>
-      <c r="M33" s="25"/>
-      <c r="N33" s="25"/>
+      <c r="L33" s="34"/>
+      <c r="M33" s="31"/>
+      <c r="N33" s="31"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="26"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="25"/>
+      <c r="B34" s="33"/>
+      <c r="C34" s="31"/>
+      <c r="D34" s="31"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="26"/>
-      <c r="H34" s="25"/>
-      <c r="I34" s="25"/>
+      <c r="G34" s="33"/>
+      <c r="H34" s="31"/>
+      <c r="I34" s="31"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="26"/>
-      <c r="M34" s="25"/>
-      <c r="N34" s="25"/>
+      <c r="L34" s="33"/>
+      <c r="M34" s="31"/>
+      <c r="N34" s="31"/>
     </row>
     <row r="35" spans="1:14" ht="15" customHeight="1">
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="27"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="25"/>
+      <c r="B35" s="34"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="27"/>
-      <c r="H35" s="25"/>
-      <c r="I35" s="25"/>
+      <c r="G35" s="34"/>
+      <c r="H35" s="31"/>
+      <c r="I35" s="31"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="27"/>
-      <c r="M35" s="25"/>
-      <c r="N35" s="25"/>
+      <c r="L35" s="34"/>
+      <c r="M35" s="31"/>
+      <c r="N35" s="31"/>
     </row>
     <row r="36" spans="1:14" ht="15" customHeight="1">
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="26"/>
-      <c r="C36" s="25"/>
-      <c r="D36" s="25"/>
+      <c r="B36" s="33"/>
+      <c r="C36" s="31"/>
+      <c r="D36" s="31"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="26"/>
-      <c r="H36" s="25"/>
-      <c r="I36" s="25"/>
+      <c r="G36" s="33"/>
+      <c r="H36" s="31"/>
+      <c r="I36" s="31"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="26"/>
-      <c r="M36" s="25"/>
-      <c r="N36" s="25"/>
+      <c r="L36" s="33"/>
+      <c r="M36" s="31"/>
+      <c r="N36" s="31"/>
     </row>
     <row r="37" spans="1:14" ht="15" customHeight="1">
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="29">
+      <c r="B37" s="36">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
-      <c r="C37" s="25"/>
-      <c r="D37" s="25"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="29">
+      <c r="G37" s="36">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
-      <c r="H37" s="25"/>
-      <c r="I37" s="25"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="31"/>
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="29">
+      <c r="L37" s="36">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
-      <c r="M37" s="25"/>
-      <c r="N37" s="25"/>
+      <c r="M37" s="31"/>
+      <c r="N37" s="31"/>
     </row>
     <row r="38" spans="1:14" ht="15" customHeight="1">
       <c r="A38" s="9"/>
@@ -3534,6 +4177,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
     <mergeCell ref="L34:N34"/>
     <mergeCell ref="L6:N6"/>
     <mergeCell ref="B33:D33"/>
@@ -3550,68 +4255,6 @@
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3659,7 +4302,7 @@
         <v>49</v>
       </c>
       <c r="E2" s="18">
-        <v>180</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -3693,7 +4336,7 @@
         <v>49</v>
       </c>
       <c r="E4" s="18">
-        <v>180</v>
+        <v>165</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3727,7 +4370,7 @@
         <v>49</v>
       </c>
       <c r="E6" s="18">
-        <v>180</v>
+        <v>165</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4059,7 +4702,7 @@
         <v>49</v>
       </c>
       <c r="E26" s="18">
-        <v>180</v>
+        <v>165</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -4093,7 +4736,7 @@
         <v>49</v>
       </c>
       <c r="E28" s="18">
-        <v>180</v>
+        <v>165</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -4127,7 +4770,7 @@
         <v>49</v>
       </c>
       <c r="E30" s="18">
-        <v>180</v>
+        <v>165</v>
       </c>
     </row>
     <row r="31" spans="1:5">

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94497724-9416-4A22-BD98-382E2A2D7F9C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C14D998-75FE-4D45-8FA6-D9CA1445E762}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -786,21 +786,21 @@
       </c>
       <c r="B5" s="21">
         <f>SUM(B6:B7)</f>
-        <v>2700</v>
+        <v>2316</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G5" s="14">
         <f>SUM(G6:G7)</f>
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="L5" s="14">
         <f>SUM(L6:L7)</f>
-        <v>4000</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
@@ -808,19 +808,18 @@
         <v>21</v>
       </c>
       <c r="B6" s="14">
-        <v>2700</v>
+        <f>2700-384</f>
+        <v>2316</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="14">
-        <v>400</v>
-      </c>
+      <c r="G6" s="14"/>
       <c r="K6" s="7" t="s">
         <v>21</v>
       </c>
       <c r="L6" s="14">
-        <v>4000</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
@@ -857,7 +856,7 @@
       </c>
       <c r="L8" s="15">
         <f>SUM(L9:L10)</f>
-        <v>1100</v>
+        <v>600</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1">
@@ -875,7 +874,7 @@
         <v>21</v>
       </c>
       <c r="L9" s="15">
-        <v>1100</v>
+        <v>600</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
@@ -1420,21 +1419,21 @@
       </c>
       <c r="B41" s="13">
         <f>SUM(B5,B8,B11,B14,B17,B20,B23,B26,B29,B32,B35,B38)</f>
-        <v>3390</v>
+        <v>3006</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G41" s="13">
         <f>SUM(G5,G8,G11,G14,G17,G20,G23,G26,G29,G32,G35,G38)</f>
-        <v>687</v>
+        <v>287</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="L41" s="13">
         <f>SUM(L5,L8,L11,L14,L17,L20,L23,L26,L29,L32,L35,L38)</f>
-        <v>6010</v>
+        <v>5110</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1">

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C14D998-75FE-4D45-8FA6-D9CA1445E762}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9D18D28-48EB-472A-93A6-9BE6310EEF9B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -446,9 +446,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -459,6 +456,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -786,7 +786,7 @@
       </c>
       <c r="B5" s="21">
         <f>SUM(B6:B7)</f>
-        <v>2316</v>
+        <v>3500</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>20</v>
@@ -800,7 +800,7 @@
       </c>
       <c r="L5" s="14">
         <f>SUM(L6:L7)</f>
-        <v>3600</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
@@ -808,8 +808,7 @@
         <v>21</v>
       </c>
       <c r="B6" s="14">
-        <f>2700-384</f>
-        <v>2316</v>
+        <v>3500</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>21</v>
@@ -819,7 +818,7 @@
         <v>21</v>
       </c>
       <c r="L6" s="14">
-        <v>3600</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
@@ -842,7 +841,7 @@
       </c>
       <c r="B8" s="15">
         <f>SUM(B9:B10)</f>
-        <v>340</v>
+        <v>1000</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>23</v>
@@ -856,7 +855,7 @@
       </c>
       <c r="L8" s="15">
         <f>SUM(L9:L10)</f>
-        <v>600</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1">
@@ -864,7 +863,7 @@
         <v>21</v>
       </c>
       <c r="B9" s="15">
-        <v>340</v>
+        <v>1000</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>21</v>
@@ -874,7 +873,7 @@
         <v>21</v>
       </c>
       <c r="L9" s="15">
-        <v>600</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
@@ -955,14 +954,14 @@
       </c>
       <c r="G14" s="15">
         <f>SUM(G15:G16)</f>
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="K14" s="9" t="s">
         <v>25</v>
       </c>
       <c r="L14" s="15">
         <f>SUM(L15:L16)</f>
-        <v>0</v>
+        <v>250</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1">
@@ -973,13 +972,13 @@
       <c r="F15" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="15">
-        <v>130</v>
-      </c>
+      <c r="G15" s="15"/>
       <c r="K15" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L15" s="15"/>
+      <c r="L15" s="15">
+        <v>250</v>
+      </c>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1">
       <c r="A16" s="9" t="s">
@@ -1001,7 +1000,7 @@
       </c>
       <c r="B17" s="14">
         <f>SUM(B18:B19)</f>
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>26</v>
@@ -1022,9 +1021,7 @@
       <c r="A18" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="14">
-        <v>50</v>
-      </c>
+      <c r="B18" s="14"/>
       <c r="F18" s="7" t="s">
         <v>21</v>
       </c>
@@ -1054,7 +1051,7 @@
       </c>
       <c r="B20" s="15">
         <f>SUM(B21:B22)</f>
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>27</v>
@@ -1076,7 +1073,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="15">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>21</v>
@@ -1114,7 +1111,7 @@
       </c>
       <c r="G23" s="14">
         <f>SUM(G24:G25)</f>
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="K23" s="7" t="s">
         <v>28</v>
@@ -1132,7 +1129,9 @@
       <c r="F24" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G24" s="14"/>
+      <c r="G24" s="14">
+        <v>340</v>
+      </c>
       <c r="K24" s="7" t="s">
         <v>21</v>
       </c>
@@ -1165,7 +1164,7 @@
       </c>
       <c r="G26" s="15">
         <f>SUM(G27:G28)</f>
-        <v>157</v>
+        <v>700</v>
       </c>
       <c r="K26" s="9" t="s">
         <v>29</v>
@@ -1184,7 +1183,7 @@
         <v>21</v>
       </c>
       <c r="G27" s="15">
-        <v>157</v>
+        <v>700</v>
       </c>
       <c r="K27" s="9" t="s">
         <v>21</v>
@@ -1225,7 +1224,7 @@
       </c>
       <c r="L29" s="14">
         <f>SUM(L30:L31)</f>
-        <v>720</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1">
@@ -1241,7 +1240,7 @@
         <v>21</v>
       </c>
       <c r="L30" s="14">
-        <v>720</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1">
@@ -1278,7 +1277,7 @@
       </c>
       <c r="L32" s="15">
         <f>SUM(L33:L34)</f>
-        <v>190</v>
+        <v>150</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
@@ -1294,7 +1293,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="15">
-        <v>190</v>
+        <v>150</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
@@ -1382,7 +1381,7 @@
       </c>
       <c r="L38" s="23">
         <f>SUM(L39:L40)</f>
-        <v>0</v>
+        <v>200</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="15" customHeight="1">
@@ -1397,7 +1396,9 @@
       <c r="K39" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L39" s="15"/>
+      <c r="L39" s="15">
+        <v>200</v>
+      </c>
     </row>
     <row r="40" spans="1:14" ht="15" customHeight="1">
       <c r="A40" s="9" t="s">
@@ -1419,21 +1420,21 @@
       </c>
       <c r="B41" s="13">
         <f>SUM(B5,B8,B11,B14,B17,B20,B23,B26,B29,B32,B35,B38)</f>
-        <v>3006</v>
+        <v>5000</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G41" s="13">
         <f>SUM(G5,G8,G11,G14,G17,G20,G23,G26,G29,G32,G35,G38)</f>
-        <v>287</v>
+        <v>1040</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="L41" s="13">
         <f>SUM(L5,L8,L11,L14,L17,L20,L23,L26,L29,L32,L35,L38)</f>
-        <v>5110</v>
+        <v>6900</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1">
@@ -2833,19 +2834,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="36" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="31"/>
       <c r="C1" s="31"/>
       <c r="D1" s="31"/>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="36" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="31"/>
       <c r="H1" s="31"/>
       <c r="I1" s="31"/>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="36" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="31"/>
@@ -2853,19 +2854,19 @@
       <c r="N1" s="31"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="36" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
       <c r="D2" s="31"/>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="36" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="31"/>
       <c r="H2" s="31"/>
       <c r="I2" s="31"/>
-      <c r="K2" s="32" t="s">
+      <c r="K2" s="36" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="31"/>
@@ -2887,27 +2888,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="34" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="31"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="34" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="31"/>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="34" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="31"/>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="34" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="31"/>
-      <c r="K4" s="35" t="s">
+      <c r="K4" s="34" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="31"/>
-      <c r="M4" s="35" t="s">
+      <c r="M4" s="34" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="31"/>
@@ -2916,7 +2917,7 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="34">
+      <c r="B5" s="33">
         <v>352</v>
       </c>
       <c r="C5" s="31"/>
@@ -2924,13 +2925,13 @@
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="34"/>
+      <c r="G5" s="33"/>
       <c r="H5" s="31"/>
       <c r="I5" s="31"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="34"/>
+      <c r="L5" s="33"/>
       <c r="M5" s="31"/>
       <c r="N5" s="31"/>
     </row>
@@ -2938,7 +2939,7 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="33">
+      <c r="B6" s="32">
         <v>376</v>
       </c>
       <c r="C6" s="31"/>
@@ -2946,13 +2947,13 @@
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="33"/>
+      <c r="G6" s="32"/>
       <c r="H6" s="31"/>
       <c r="I6" s="31"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="33"/>
+      <c r="L6" s="32"/>
       <c r="M6" s="31"/>
       <c r="N6" s="31"/>
     </row>
@@ -2960,7 +2961,7 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="34">
+      <c r="B7" s="33">
         <v>0</v>
       </c>
       <c r="C7" s="31"/>
@@ -2968,13 +2969,13 @@
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="34"/>
+      <c r="G7" s="33"/>
       <c r="H7" s="31"/>
       <c r="I7" s="31"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="34"/>
+      <c r="L7" s="33"/>
       <c r="M7" s="31"/>
       <c r="N7" s="31"/>
     </row>
@@ -2982,7 +2983,7 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="33">
+      <c r="B8" s="32">
         <v>724</v>
       </c>
       <c r="C8" s="31"/>
@@ -2990,13 +2991,13 @@
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="33"/>
+      <c r="G8" s="32"/>
       <c r="H8" s="31"/>
       <c r="I8" s="31"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="33"/>
+      <c r="L8" s="32"/>
       <c r="M8" s="31"/>
       <c r="N8" s="31"/>
     </row>
@@ -3004,7 +3005,7 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="34">
+      <c r="B9" s="33">
         <v>411</v>
       </c>
       <c r="C9" s="31"/>
@@ -3012,13 +3013,13 @@
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="34"/>
+      <c r="G9" s="33"/>
       <c r="H9" s="31"/>
       <c r="I9" s="31"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="34"/>
+      <c r="L9" s="33"/>
       <c r="M9" s="31"/>
       <c r="N9" s="31"/>
     </row>
@@ -3026,7 +3027,7 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="33">
+      <c r="B10" s="32">
         <v>0</v>
       </c>
       <c r="C10" s="31"/>
@@ -3034,13 +3035,13 @@
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="33"/>
+      <c r="G10" s="32"/>
       <c r="H10" s="31"/>
       <c r="I10" s="31"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="33"/>
+      <c r="L10" s="32"/>
       <c r="M10" s="31"/>
       <c r="N10" s="31"/>
     </row>
@@ -3048,7 +3049,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="36">
+      <c r="B11" s="35">
         <f>SUM(B5:B10)</f>
         <v>1863</v>
       </c>
@@ -3057,7 +3058,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="36">
+      <c r="G11" s="35">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -3066,7 +3067,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="36">
+      <c r="L11" s="35">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -3102,19 +3103,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="32" t="s">
+      <c r="A25" s="36" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="31"/>
       <c r="C25" s="31"/>
       <c r="D25" s="31"/>
-      <c r="F25" s="32" t="s">
+      <c r="F25" s="36" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="31"/>
       <c r="H25" s="31"/>
       <c r="I25" s="31"/>
-      <c r="K25" s="32" t="s">
+      <c r="K25" s="36" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="31"/>
@@ -3122,19 +3123,19 @@
       <c r="N25" s="31"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="32" t="s">
+      <c r="A26" s="36" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="31"/>
       <c r="C26" s="31"/>
       <c r="D26" s="31"/>
-      <c r="F26" s="32" t="s">
+      <c r="F26" s="36" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="31"/>
       <c r="H26" s="31"/>
       <c r="I26" s="31"/>
-      <c r="K26" s="32" t="s">
+      <c r="K26" s="36" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="31"/>
@@ -3156,27 +3157,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="35" t="s">
+      <c r="A28" s="34" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="31"/>
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="34" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="31"/>
-      <c r="F28" s="35" t="s">
+      <c r="F28" s="34" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="31"/>
-      <c r="H28" s="35" t="s">
+      <c r="H28" s="34" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="31"/>
-      <c r="K28" s="35" t="s">
+      <c r="K28" s="34" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="31"/>
-      <c r="M28" s="35" t="s">
+      <c r="M28" s="34" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="31"/>
@@ -3185,7 +3186,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="34">
+      <c r="B29" s="33">
         <v>0</v>
       </c>
       <c r="C29" s="31"/>
@@ -3193,13 +3194,13 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="34"/>
+      <c r="G29" s="33"/>
       <c r="H29" s="31"/>
       <c r="I29" s="31"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="34">
+      <c r="L29" s="33">
         <v>14</v>
       </c>
       <c r="M29" s="31"/>
@@ -3209,7 +3210,7 @@
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="33">
+      <c r="B30" s="32">
         <v>0</v>
       </c>
       <c r="C30" s="31"/>
@@ -3217,13 +3218,13 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="33"/>
+      <c r="G30" s="32"/>
       <c r="H30" s="31"/>
       <c r="I30" s="31"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="33">
+      <c r="L30" s="32">
         <v>605</v>
       </c>
       <c r="M30" s="31"/>
@@ -3233,7 +3234,7 @@
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="34">
+      <c r="B31" s="33">
         <v>0</v>
       </c>
       <c r="C31" s="31"/>
@@ -3241,13 +3242,13 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="34"/>
+      <c r="G31" s="33"/>
       <c r="H31" s="31"/>
       <c r="I31" s="31"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="34">
+      <c r="L31" s="33">
         <v>1708</v>
       </c>
       <c r="M31" s="31"/>
@@ -3257,7 +3258,7 @@
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="33">
+      <c r="B32" s="32">
         <v>0</v>
       </c>
       <c r="C32" s="31"/>
@@ -3265,13 +3266,13 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="33"/>
+      <c r="G32" s="32"/>
       <c r="H32" s="31"/>
       <c r="I32" s="31"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="33">
+      <c r="L32" s="32">
         <v>1395</v>
       </c>
       <c r="M32" s="31"/>
@@ -3281,7 +3282,7 @@
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="34">
+      <c r="B33" s="33">
         <v>0</v>
       </c>
       <c r="C33" s="31"/>
@@ -3289,13 +3290,13 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="34"/>
+      <c r="G33" s="33"/>
       <c r="H33" s="31"/>
       <c r="I33" s="31"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="34">
+      <c r="L33" s="33">
         <v>0</v>
       </c>
       <c r="M33" s="31"/>
@@ -3305,7 +3306,7 @@
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="33">
+      <c r="B34" s="32">
         <v>0</v>
       </c>
       <c r="C34" s="31"/>
@@ -3313,13 +3314,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="33"/>
+      <c r="G34" s="32"/>
       <c r="H34" s="31"/>
       <c r="I34" s="31"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="33">
+      <c r="L34" s="32">
         <v>0</v>
       </c>
       <c r="M34" s="31"/>
@@ -3329,7 +3330,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="36">
+      <c r="B35" s="35">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -3338,7 +3339,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="36">
+      <c r="G35" s="35">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -3347,7 +3348,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="36">
+      <c r="L35" s="35">
         <f>SUM(L29:L34)</f>
         <v>3722</v>
       </c>
@@ -3384,6 +3385,56 @@
     </row>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B10:D10"/>
@@ -3400,56 +3451,6 @@
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="H28:I28"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3465,7 +3466,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="36" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="31"/>
@@ -3473,7 +3474,7 @@
       <c r="D1" s="31"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="36" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="31"/>
@@ -3487,11 +3488,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="34" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="31"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="34" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="31"/>
@@ -3500,7 +3501,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="34"/>
+      <c r="B5" s="33"/>
       <c r="C5" s="31"/>
       <c r="D5" s="31"/>
     </row>
@@ -3508,7 +3509,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="33"/>
+      <c r="B6" s="32"/>
       <c r="C6" s="31"/>
       <c r="D6" s="31"/>
     </row>
@@ -3516,7 +3517,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="34"/>
+      <c r="B7" s="33"/>
       <c r="C7" s="31"/>
       <c r="D7" s="31"/>
     </row>
@@ -3524,7 +3525,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="33"/>
+      <c r="B8" s="32"/>
       <c r="C8" s="31"/>
       <c r="D8" s="31"/>
     </row>
@@ -3532,7 +3533,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="36">
+      <c r="B9" s="35">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -3581,19 +3582,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="36" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="31"/>
       <c r="C1" s="31"/>
       <c r="D1" s="31"/>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="36" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="31"/>
       <c r="H1" s="31"/>
       <c r="I1" s="31"/>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="36" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="31"/>
@@ -3601,19 +3602,19 @@
       <c r="N1" s="31"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="36" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
       <c r="D2" s="31"/>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="36" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="31"/>
       <c r="H2" s="31"/>
       <c r="I2" s="31"/>
-      <c r="K2" s="32" t="s">
+      <c r="K2" s="36" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="31"/>
@@ -3635,27 +3636,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="34" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="31"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="34" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="31"/>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="34" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="31"/>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="34" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="31"/>
-      <c r="K4" s="35" t="s">
+      <c r="K4" s="34" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="31"/>
-      <c r="M4" s="35" t="s">
+      <c r="M4" s="34" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="31"/>
@@ -3664,19 +3665,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="34"/>
+      <c r="B5" s="33"/>
       <c r="C5" s="31"/>
       <c r="D5" s="31"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="34"/>
+      <c r="G5" s="33"/>
       <c r="H5" s="31"/>
       <c r="I5" s="31"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="34"/>
+      <c r="L5" s="33"/>
       <c r="M5" s="31"/>
       <c r="N5" s="31"/>
     </row>
@@ -3684,19 +3685,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="33"/>
+      <c r="B6" s="32"/>
       <c r="C6" s="31"/>
       <c r="D6" s="31"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="33"/>
+      <c r="G6" s="32"/>
       <c r="H6" s="31"/>
       <c r="I6" s="31"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="33"/>
+      <c r="L6" s="32"/>
       <c r="M6" s="31"/>
       <c r="N6" s="31"/>
     </row>
@@ -3704,19 +3705,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="34"/>
+      <c r="B7" s="33"/>
       <c r="C7" s="31"/>
       <c r="D7" s="31"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="34"/>
+      <c r="G7" s="33"/>
       <c r="H7" s="31"/>
       <c r="I7" s="31"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="34"/>
+      <c r="L7" s="33"/>
       <c r="M7" s="31"/>
       <c r="N7" s="31"/>
     </row>
@@ -3724,19 +3725,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="33"/>
+      <c r="B8" s="32"/>
       <c r="C8" s="31"/>
       <c r="D8" s="31"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="33"/>
+      <c r="G8" s="32"/>
       <c r="H8" s="31"/>
       <c r="I8" s="31"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="33"/>
+      <c r="L8" s="32"/>
       <c r="M8" s="31"/>
       <c r="N8" s="31"/>
     </row>
@@ -3744,19 +3745,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="34"/>
+      <c r="B9" s="33"/>
       <c r="C9" s="31"/>
       <c r="D9" s="31"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="34"/>
+      <c r="G9" s="33"/>
       <c r="H9" s="31"/>
       <c r="I9" s="31"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="34"/>
+      <c r="L9" s="33"/>
       <c r="M9" s="31"/>
       <c r="N9" s="31"/>
     </row>
@@ -3764,19 +3765,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="33"/>
+      <c r="B10" s="32"/>
       <c r="C10" s="31"/>
       <c r="D10" s="31"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="33"/>
+      <c r="G10" s="32"/>
       <c r="H10" s="31"/>
       <c r="I10" s="31"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="33"/>
+      <c r="L10" s="32"/>
       <c r="M10" s="31"/>
       <c r="N10" s="31"/>
     </row>
@@ -3784,19 +3785,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="34"/>
+      <c r="B11" s="33"/>
       <c r="C11" s="31"/>
       <c r="D11" s="31"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="34"/>
+      <c r="G11" s="33"/>
       <c r="H11" s="31"/>
       <c r="I11" s="31"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="34"/>
+      <c r="L11" s="33"/>
       <c r="M11" s="31"/>
       <c r="N11" s="31"/>
     </row>
@@ -3804,19 +3805,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="33"/>
+      <c r="B12" s="32"/>
       <c r="C12" s="31"/>
       <c r="D12" s="31"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="33"/>
+      <c r="G12" s="32"/>
       <c r="H12" s="31"/>
       <c r="I12" s="31"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="33"/>
+      <c r="L12" s="32"/>
       <c r="M12" s="31"/>
       <c r="N12" s="31"/>
     </row>
@@ -3824,7 +3825,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="36">
+      <c r="B13" s="35">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3833,7 +3834,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="36">
+      <c r="G13" s="35">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3842,7 +3843,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="36">
+      <c r="L13" s="35">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3878,19 +3879,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="32" t="s">
+      <c r="A25" s="36" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="31"/>
       <c r="C25" s="31"/>
       <c r="D25" s="31"/>
-      <c r="F25" s="32" t="s">
+      <c r="F25" s="36" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="31"/>
       <c r="H25" s="31"/>
       <c r="I25" s="31"/>
-      <c r="K25" s="32" t="s">
+      <c r="K25" s="36" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="31"/>
@@ -3898,19 +3899,19 @@
       <c r="N25" s="31"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="32" t="s">
+      <c r="A26" s="36" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="31"/>
       <c r="C26" s="31"/>
       <c r="D26" s="31"/>
-      <c r="F26" s="32" t="s">
+      <c r="F26" s="36" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="31"/>
       <c r="H26" s="31"/>
       <c r="I26" s="31"/>
-      <c r="K26" s="32" t="s">
+      <c r="K26" s="36" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="31"/>
@@ -3932,27 +3933,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="35" t="s">
+      <c r="A28" s="34" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="31"/>
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="34" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="31"/>
-      <c r="F28" s="35" t="s">
+      <c r="F28" s="34" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="31"/>
-      <c r="H28" s="35" t="s">
+      <c r="H28" s="34" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="31"/>
-      <c r="K28" s="35" t="s">
+      <c r="K28" s="34" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="31"/>
-      <c r="M28" s="35" t="s">
+      <c r="M28" s="34" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="31"/>
@@ -3961,19 +3962,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="34"/>
+      <c r="B29" s="33"/>
       <c r="C29" s="31"/>
       <c r="D29" s="31"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="34"/>
+      <c r="G29" s="33"/>
       <c r="H29" s="31"/>
       <c r="I29" s="31"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="34"/>
+      <c r="L29" s="33"/>
       <c r="M29" s="31"/>
       <c r="N29" s="31"/>
     </row>
@@ -3981,19 +3982,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="33"/>
+      <c r="B30" s="32"/>
       <c r="C30" s="31"/>
       <c r="D30" s="31"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="33"/>
+      <c r="G30" s="32"/>
       <c r="H30" s="31"/>
       <c r="I30" s="31"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="33"/>
+      <c r="L30" s="32"/>
       <c r="M30" s="31"/>
       <c r="N30" s="31"/>
     </row>
@@ -4001,19 +4002,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="34"/>
+      <c r="B31" s="33"/>
       <c r="C31" s="31"/>
       <c r="D31" s="31"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="34"/>
+      <c r="G31" s="33"/>
       <c r="H31" s="31"/>
       <c r="I31" s="31"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="34"/>
+      <c r="L31" s="33"/>
       <c r="M31" s="31"/>
       <c r="N31" s="31"/>
     </row>
@@ -4021,19 +4022,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="33"/>
+      <c r="B32" s="32"/>
       <c r="C32" s="31"/>
       <c r="D32" s="31"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="33"/>
+      <c r="G32" s="32"/>
       <c r="H32" s="31"/>
       <c r="I32" s="31"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="33"/>
+      <c r="L32" s="32"/>
       <c r="M32" s="31"/>
       <c r="N32" s="31"/>
     </row>
@@ -4041,19 +4042,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="34"/>
+      <c r="B33" s="33"/>
       <c r="C33" s="31"/>
       <c r="D33" s="31"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="34"/>
+      <c r="G33" s="33"/>
       <c r="H33" s="31"/>
       <c r="I33" s="31"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="34"/>
+      <c r="L33" s="33"/>
       <c r="M33" s="31"/>
       <c r="N33" s="31"/>
     </row>
@@ -4061,19 +4062,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="33"/>
+      <c r="B34" s="32"/>
       <c r="C34" s="31"/>
       <c r="D34" s="31"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="33"/>
+      <c r="G34" s="32"/>
       <c r="H34" s="31"/>
       <c r="I34" s="31"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="33"/>
+      <c r="L34" s="32"/>
       <c r="M34" s="31"/>
       <c r="N34" s="31"/>
     </row>
@@ -4081,19 +4082,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="34"/>
+      <c r="B35" s="33"/>
       <c r="C35" s="31"/>
       <c r="D35" s="31"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="34"/>
+      <c r="G35" s="33"/>
       <c r="H35" s="31"/>
       <c r="I35" s="31"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="34"/>
+      <c r="L35" s="33"/>
       <c r="M35" s="31"/>
       <c r="N35" s="31"/>
     </row>
@@ -4101,19 +4102,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="33"/>
+      <c r="B36" s="32"/>
       <c r="C36" s="31"/>
       <c r="D36" s="31"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="33"/>
+      <c r="G36" s="32"/>
       <c r="H36" s="31"/>
       <c r="I36" s="31"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="33"/>
+      <c r="L36" s="32"/>
       <c r="M36" s="31"/>
       <c r="N36" s="31"/>
     </row>
@@ -4121,7 +4122,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="36">
+      <c r="B37" s="35">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -4130,7 +4131,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="36">
+      <c r="G37" s="35">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -4139,7 +4140,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="36">
+      <c r="L37" s="35">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -4176,6 +4177,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
     <mergeCell ref="G36:I36"/>
     <mergeCell ref="L32:N32"/>
     <mergeCell ref="L13:N13"/>
@@ -4192,68 +4255,6 @@
     <mergeCell ref="L33:N33"/>
     <mergeCell ref="L35:N35"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="L9:N9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9D18D28-48EB-472A-93A6-9BE6310EEF9B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C35D2EA2-685B-401C-B0EB-909BE0457880}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucoes" sheetId="1" r:id="rId1"/>
@@ -786,7 +786,7 @@
       </c>
       <c r="B5" s="21">
         <f>SUM(B6:B7)</f>
-        <v>3500</v>
+        <v>3200</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>20</v>
@@ -800,16 +800,14 @@
       </c>
       <c r="L5" s="14">
         <f>SUM(L6:L7)</f>
-        <v>3800</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
       <c r="A6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="14">
-        <v>3500</v>
-      </c>
+      <c r="B6" s="14"/>
       <c r="F6" s="7" t="s">
         <v>21</v>
       </c>
@@ -818,14 +816,16 @@
         <v>21</v>
       </c>
       <c r="L6" s="14">
-        <v>3800</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="14"/>
+      <c r="B7" s="14">
+        <v>3200</v>
+      </c>
       <c r="F7" s="7" t="s">
         <v>22</v>
       </c>
@@ -841,7 +841,7 @@
       </c>
       <c r="B8" s="15">
         <f>SUM(B9:B10)</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>23</v>
@@ -862,9 +862,7 @@
       <c r="A9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="15">
-        <v>1000</v>
-      </c>
+      <c r="B9" s="15"/>
       <c r="F9" s="9" t="s">
         <v>21</v>
       </c>
@@ -1420,7 +1418,7 @@
       </c>
       <c r="B41" s="13">
         <f>SUM(B5,B8,B11,B14,B17,B20,B23,B26,B29,B32,B35,B38)</f>
-        <v>5000</v>
+        <v>3700</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>34</v>
@@ -1434,7 +1432,7 @@
       </c>
       <c r="L41" s="13">
         <f>SUM(L5,L8,L11,L14,L17,L20,L23,L26,L29,L32,L35,L38)</f>
-        <v>6900</v>
+        <v>5200</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1">
@@ -2254,7 +2252,7 @@
       </c>
       <c r="B97" s="26">
         <f>SUM(B98:B99)</f>
-        <v>946</v>
+        <v>0</v>
       </c>
       <c r="C97" s="24"/>
       <c r="D97" s="24"/>
@@ -2264,25 +2262,21 @@
       </c>
       <c r="G97" s="26">
         <f>SUM(G98:G99)</f>
-        <v>633</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="15">
       <c r="A98" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B98" s="26">
-        <v>946</v>
-      </c>
+      <c r="B98" s="26"/>
       <c r="C98" s="24"/>
       <c r="D98" s="24"/>
       <c r="E98" s="24"/>
       <c r="F98" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G98" s="26">
-        <v>633</v>
-      </c>
+      <c r="G98" s="26"/>
     </row>
     <row r="99" spans="1:7" ht="15">
       <c r="A99" s="7" t="s">
@@ -2802,7 +2796,7 @@
       </c>
       <c r="B133" s="28">
         <f>SUM(B97,B100,B103,B106,B109,B112,B115,B118,B121,B124,B127,B130)</f>
-        <v>946</v>
+        <v>0</v>
       </c>
       <c r="C133" s="24"/>
       <c r="D133" s="24"/>
@@ -2812,7 +2806,7 @@
       </c>
       <c r="G133" s="28">
         <f>SUM(G97,G100,G103,G106,G109,G112,G115,G118,G121,G124,G127,G130)</f>
-        <v>1007</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -2918,10 +2912,10 @@
         <v>41</v>
       </c>
       <c r="B5" s="33">
-        <v>352</v>
-      </c>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
+        <v>0</v>
+      </c>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
@@ -2940,10 +2934,10 @@
         <v>42</v>
       </c>
       <c r="B6" s="32">
-        <v>376</v>
-      </c>
-      <c r="C6" s="31"/>
-      <c r="D6" s="31"/>
+        <v>0</v>
+      </c>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
@@ -2964,8 +2958,8 @@
       <c r="B7" s="33">
         <v>0</v>
       </c>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
@@ -2984,10 +2978,10 @@
         <v>44</v>
       </c>
       <c r="B8" s="32">
-        <v>724</v>
-      </c>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
+        <v>0</v>
+      </c>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
@@ -3006,10 +3000,10 @@
         <v>45</v>
       </c>
       <c r="B9" s="33">
-        <v>411</v>
-      </c>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
+        <v>0</v>
+      </c>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
@@ -3030,8 +3024,8 @@
       <c r="B10" s="32">
         <v>0</v>
       </c>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
+      <c r="C10" s="32"/>
+      <c r="D10" s="32"/>
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
@@ -3051,7 +3045,7 @@
       </c>
       <c r="B11" s="35">
         <f>SUM(B5:B10)</f>
-        <v>1863</v>
+        <v>0</v>
       </c>
       <c r="C11" s="31"/>
       <c r="D11" s="31"/>
@@ -3201,10 +3195,10 @@
         <v>41</v>
       </c>
       <c r="L29" s="33">
-        <v>14</v>
-      </c>
-      <c r="M29" s="31"/>
-      <c r="N29" s="31"/>
+        <v>0</v>
+      </c>
+      <c r="M29" s="33"/>
+      <c r="N29" s="33"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="9" t="s">
@@ -3225,10 +3219,10 @@
         <v>42</v>
       </c>
       <c r="L30" s="32">
-        <v>605</v>
-      </c>
-      <c r="M30" s="31"/>
-      <c r="N30" s="31"/>
+        <v>0</v>
+      </c>
+      <c r="M30" s="32"/>
+      <c r="N30" s="32"/>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1">
       <c r="A31" s="7" t="s">
@@ -3249,10 +3243,10 @@
         <v>43</v>
       </c>
       <c r="L31" s="33">
-        <v>1708</v>
-      </c>
-      <c r="M31" s="31"/>
-      <c r="N31" s="31"/>
+        <v>0</v>
+      </c>
+      <c r="M31" s="33"/>
+      <c r="N31" s="33"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
       <c r="A32" s="9" t="s">
@@ -3273,10 +3267,10 @@
         <v>44</v>
       </c>
       <c r="L32" s="32">
-        <v>1395</v>
-      </c>
-      <c r="M32" s="31"/>
-      <c r="N32" s="31"/>
+        <v>0</v>
+      </c>
+      <c r="M32" s="32"/>
+      <c r="N32" s="32"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="7" t="s">
@@ -3299,8 +3293,8 @@
       <c r="L33" s="33">
         <v>0</v>
       </c>
-      <c r="M33" s="31"/>
-      <c r="N33" s="31"/>
+      <c r="M33" s="33"/>
+      <c r="N33" s="33"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="9" t="s">
@@ -3350,7 +3344,7 @@
       </c>
       <c r="L35" s="35">
         <f>SUM(L29:L34)</f>
-        <v>3722</v>
+        <v>0</v>
       </c>
       <c r="M35" s="31"/>
       <c r="N35" s="31"/>
@@ -4302,7 +4296,7 @@
         <v>49</v>
       </c>
       <c r="E2" s="18">
-        <v>165</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4319,7 +4313,7 @@
         <v>68</v>
       </c>
       <c r="E3" s="18">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -4336,7 +4330,7 @@
         <v>49</v>
       </c>
       <c r="E4" s="18">
-        <v>165</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4353,7 +4347,7 @@
         <v>68</v>
       </c>
       <c r="E5" s="18">
-        <v>110</v>
+        <v>90</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4370,7 +4364,7 @@
         <v>49</v>
       </c>
       <c r="E6" s="18">
-        <v>165</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4387,7 +4381,7 @@
         <v>68</v>
       </c>
       <c r="E7" s="18">
-        <v>110</v>
+        <v>90</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4404,7 +4398,7 @@
         <v>49</v>
       </c>
       <c r="E8" s="18">
-        <v>110</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -4421,7 +4415,7 @@
         <v>68</v>
       </c>
       <c r="E9" s="18">
-        <v>110</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -4438,7 +4432,7 @@
         <v>49</v>
       </c>
       <c r="E10" s="18">
-        <v>110</v>
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -4455,7 +4449,7 @@
         <v>68</v>
       </c>
       <c r="E11" s="18">
-        <v>110</v>
+        <v>70</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -4472,7 +4466,7 @@
         <v>49</v>
       </c>
       <c r="E12" s="18">
-        <v>110</v>
+        <v>70</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -4489,7 +4483,7 @@
         <v>68</v>
       </c>
       <c r="E13" s="18">
-        <v>110</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -4506,7 +4500,7 @@
         <v>49</v>
       </c>
       <c r="E14" s="18">
-        <v>110</v>
+        <v>70</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -4523,7 +4517,7 @@
         <v>68</v>
       </c>
       <c r="E15" s="18">
-        <v>110</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -4540,7 +4534,7 @@
         <v>49</v>
       </c>
       <c r="E16" s="18">
-        <v>110</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -4557,7 +4551,7 @@
         <v>68</v>
       </c>
       <c r="E17" s="18">
-        <v>110</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:5">

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C35D2EA2-685B-401C-B0EB-909BE0457880}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE3EDB9-CBC3-4F02-9895-4CAB2913F641}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucoes" sheetId="1" r:id="rId1"/>
@@ -446,6 +446,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -456,9 +459,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -848,7 +848,7 @@
       </c>
       <c r="G8" s="15">
         <f>SUM(G9:G10)</f>
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="K8" s="9" t="s">
         <v>23</v>
@@ -866,7 +866,9 @@
       <c r="F9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="15"/>
+      <c r="G9" s="15">
+        <v>700</v>
+      </c>
       <c r="K9" s="9" t="s">
         <v>21</v>
       </c>
@@ -1162,7 +1164,7 @@
       </c>
       <c r="G26" s="15">
         <f>SUM(G27:G28)</f>
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="K26" s="9" t="s">
         <v>29</v>
@@ -1180,9 +1182,7 @@
       <c r="F27" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G27" s="15">
-        <v>700</v>
-      </c>
+      <c r="G27" s="15"/>
       <c r="K27" s="9" t="s">
         <v>21</v>
       </c>
@@ -2828,19 +2828,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="32" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="31"/>
       <c r="C1" s="31"/>
       <c r="D1" s="31"/>
-      <c r="F1" s="36" t="s">
+      <c r="F1" s="32" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="31"/>
       <c r="H1" s="31"/>
       <c r="I1" s="31"/>
-      <c r="K1" s="36" t="s">
+      <c r="K1" s="32" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="31"/>
@@ -2848,19 +2848,19 @@
       <c r="N1" s="31"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="32" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
       <c r="D2" s="31"/>
-      <c r="F2" s="36" t="s">
+      <c r="F2" s="32" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="31"/>
       <c r="H2" s="31"/>
       <c r="I2" s="31"/>
-      <c r="K2" s="36" t="s">
+      <c r="K2" s="32" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="31"/>
@@ -2882,27 +2882,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="31"/>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="35" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="31"/>
-      <c r="F4" s="34" t="s">
+      <c r="F4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="31"/>
-      <c r="H4" s="34" t="s">
+      <c r="H4" s="35" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="31"/>
-      <c r="K4" s="34" t="s">
+      <c r="K4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="31"/>
-      <c r="M4" s="34" t="s">
+      <c r="M4" s="35" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="31"/>
@@ -2911,21 +2911,21 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="33">
-        <v>0</v>
-      </c>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
+      <c r="B5" s="34">
+        <v>0</v>
+      </c>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="33"/>
+      <c r="G5" s="34"/>
       <c r="H5" s="31"/>
       <c r="I5" s="31"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="33"/>
+      <c r="L5" s="34"/>
       <c r="M5" s="31"/>
       <c r="N5" s="31"/>
     </row>
@@ -2933,21 +2933,21 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="32">
-        <v>0</v>
-      </c>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
+      <c r="B6" s="33">
+        <v>0</v>
+      </c>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="32"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="31"/>
       <c r="I6" s="31"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="32"/>
+      <c r="L6" s="33"/>
       <c r="M6" s="31"/>
       <c r="N6" s="31"/>
     </row>
@@ -2955,21 +2955,21 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="33">
-        <v>0</v>
-      </c>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
+      <c r="B7" s="34">
+        <v>0</v>
+      </c>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="33"/>
+      <c r="G7" s="34"/>
       <c r="H7" s="31"/>
       <c r="I7" s="31"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="33"/>
+      <c r="L7" s="34"/>
       <c r="M7" s="31"/>
       <c r="N7" s="31"/>
     </row>
@@ -2977,21 +2977,21 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="32">
-        <v>0</v>
-      </c>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
+      <c r="B8" s="33">
+        <v>0</v>
+      </c>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="32"/>
+      <c r="G8" s="33"/>
       <c r="H8" s="31"/>
       <c r="I8" s="31"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="32"/>
+      <c r="L8" s="33"/>
       <c r="M8" s="31"/>
       <c r="N8" s="31"/>
     </row>
@@ -2999,21 +2999,21 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="33">
-        <v>0</v>
-      </c>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
+      <c r="B9" s="34">
+        <v>0</v>
+      </c>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="33"/>
+      <c r="G9" s="34"/>
       <c r="H9" s="31"/>
       <c r="I9" s="31"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="33"/>
+      <c r="L9" s="34"/>
       <c r="M9" s="31"/>
       <c r="N9" s="31"/>
     </row>
@@ -3021,21 +3021,21 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="32">
-        <v>0</v>
-      </c>
-      <c r="C10" s="32"/>
-      <c r="D10" s="32"/>
+      <c r="B10" s="33">
+        <v>0</v>
+      </c>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="32"/>
+      <c r="G10" s="33"/>
       <c r="H10" s="31"/>
       <c r="I10" s="31"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="32"/>
+      <c r="L10" s="33"/>
       <c r="M10" s="31"/>
       <c r="N10" s="31"/>
     </row>
@@ -3043,7 +3043,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="35">
+      <c r="B11" s="36">
         <f>SUM(B5:B10)</f>
         <v>0</v>
       </c>
@@ -3052,7 +3052,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="35">
+      <c r="G11" s="36">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -3061,7 +3061,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="35">
+      <c r="L11" s="36">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -3097,19 +3097,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="36" t="s">
+      <c r="A25" s="32" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="31"/>
       <c r="C25" s="31"/>
       <c r="D25" s="31"/>
-      <c r="F25" s="36" t="s">
+      <c r="F25" s="32" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="31"/>
       <c r="H25" s="31"/>
       <c r="I25" s="31"/>
-      <c r="K25" s="36" t="s">
+      <c r="K25" s="32" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="31"/>
@@ -3117,19 +3117,19 @@
       <c r="N25" s="31"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="36" t="s">
+      <c r="A26" s="32" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="31"/>
       <c r="C26" s="31"/>
       <c r="D26" s="31"/>
-      <c r="F26" s="36" t="s">
+      <c r="F26" s="32" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="31"/>
       <c r="H26" s="31"/>
       <c r="I26" s="31"/>
-      <c r="K26" s="36" t="s">
+      <c r="K26" s="32" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="31"/>
@@ -3151,27 +3151,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="34" t="s">
+      <c r="A28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="31"/>
-      <c r="C28" s="34" t="s">
+      <c r="C28" s="35" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="31"/>
-      <c r="F28" s="34" t="s">
+      <c r="F28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="31"/>
-      <c r="H28" s="34" t="s">
+      <c r="H28" s="35" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="31"/>
-      <c r="K28" s="34" t="s">
+      <c r="K28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="31"/>
-      <c r="M28" s="34" t="s">
+      <c r="M28" s="35" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="31"/>
@@ -3180,7 +3180,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="33">
+      <c r="B29" s="34">
         <v>0</v>
       </c>
       <c r="C29" s="31"/>
@@ -3188,23 +3188,23 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="33"/>
+      <c r="G29" s="34"/>
       <c r="H29" s="31"/>
       <c r="I29" s="31"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="33">
-        <v>0</v>
-      </c>
-      <c r="M29" s="33"/>
-      <c r="N29" s="33"/>
+      <c r="L29" s="34">
+        <v>0</v>
+      </c>
+      <c r="M29" s="34"/>
+      <c r="N29" s="34"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="32">
+      <c r="B30" s="33">
         <v>0</v>
       </c>
       <c r="C30" s="31"/>
@@ -3212,23 +3212,23 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="32"/>
+      <c r="G30" s="33"/>
       <c r="H30" s="31"/>
       <c r="I30" s="31"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="32">
-        <v>0</v>
-      </c>
-      <c r="M30" s="32"/>
-      <c r="N30" s="32"/>
+      <c r="L30" s="33">
+        <v>0</v>
+      </c>
+      <c r="M30" s="33"/>
+      <c r="N30" s="33"/>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1">
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="33">
+      <c r="B31" s="34">
         <v>0</v>
       </c>
       <c r="C31" s="31"/>
@@ -3236,23 +3236,23 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="33"/>
+      <c r="G31" s="34"/>
       <c r="H31" s="31"/>
       <c r="I31" s="31"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="33">
-        <v>0</v>
-      </c>
-      <c r="M31" s="33"/>
-      <c r="N31" s="33"/>
+      <c r="L31" s="34">
+        <v>0</v>
+      </c>
+      <c r="M31" s="34"/>
+      <c r="N31" s="34"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="32">
+      <c r="B32" s="33">
         <v>0</v>
       </c>
       <c r="C32" s="31"/>
@@ -3260,23 +3260,23 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="32"/>
+      <c r="G32" s="33"/>
       <c r="H32" s="31"/>
       <c r="I32" s="31"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="32">
-        <v>0</v>
-      </c>
-      <c r="M32" s="32"/>
-      <c r="N32" s="32"/>
+      <c r="L32" s="33">
+        <v>0</v>
+      </c>
+      <c r="M32" s="33"/>
+      <c r="N32" s="33"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="33">
+      <c r="B33" s="34">
         <v>0</v>
       </c>
       <c r="C33" s="31"/>
@@ -3284,23 +3284,23 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="33"/>
+      <c r="G33" s="34"/>
       <c r="H33" s="31"/>
       <c r="I33" s="31"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="33">
-        <v>0</v>
-      </c>
-      <c r="M33" s="33"/>
-      <c r="N33" s="33"/>
+      <c r="L33" s="34">
+        <v>0</v>
+      </c>
+      <c r="M33" s="34"/>
+      <c r="N33" s="34"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="32">
+      <c r="B34" s="33">
         <v>0</v>
       </c>
       <c r="C34" s="31"/>
@@ -3308,13 +3308,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="32"/>
+      <c r="G34" s="33"/>
       <c r="H34" s="31"/>
       <c r="I34" s="31"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="32">
+      <c r="L34" s="33">
         <v>0</v>
       </c>
       <c r="M34" s="31"/>
@@ -3324,7 +3324,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="35">
+      <c r="B35" s="36">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -3333,7 +3333,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="35">
+      <c r="G35" s="36">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -3342,7 +3342,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="35">
+      <c r="L35" s="36">
         <f>SUM(L29:L34)</f>
         <v>0</v>
       </c>
@@ -3379,13 +3379,49 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="L11:N11"/>
@@ -3402,49 +3438,13 @@
     <mergeCell ref="K2:N2"/>
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3460,7 +3460,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="32" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="31"/>
@@ -3468,7 +3468,7 @@
       <c r="D1" s="31"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="32" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="31"/>
@@ -3482,11 +3482,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="35" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="31"/>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="35" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="31"/>
@@ -3495,7 +3495,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="33"/>
+      <c r="B5" s="34"/>
       <c r="C5" s="31"/>
       <c r="D5" s="31"/>
     </row>
@@ -3503,7 +3503,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="32"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="31"/>
       <c r="D6" s="31"/>
     </row>
@@ -3511,7 +3511,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="33"/>
+      <c r="B7" s="34"/>
       <c r="C7" s="31"/>
       <c r="D7" s="31"/>
     </row>
@@ -3519,7 +3519,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="32"/>
+      <c r="B8" s="33"/>
       <c r="C8" s="31"/>
       <c r="D8" s="31"/>
     </row>
@@ -3527,7 +3527,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="35">
+      <c r="B9" s="36">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -3576,19 +3576,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="32" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="31"/>
       <c r="C1" s="31"/>
       <c r="D1" s="31"/>
-      <c r="F1" s="36" t="s">
+      <c r="F1" s="32" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="31"/>
       <c r="H1" s="31"/>
       <c r="I1" s="31"/>
-      <c r="K1" s="36" t="s">
+      <c r="K1" s="32" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="31"/>
@@ -3596,19 +3596,19 @@
       <c r="N1" s="31"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="32" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
       <c r="D2" s="31"/>
-      <c r="F2" s="36" t="s">
+      <c r="F2" s="32" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="31"/>
       <c r="H2" s="31"/>
       <c r="I2" s="31"/>
-      <c r="K2" s="36" t="s">
+      <c r="K2" s="32" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="31"/>
@@ -3630,27 +3630,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="31"/>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="35" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="31"/>
-      <c r="F4" s="34" t="s">
+      <c r="F4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="31"/>
-      <c r="H4" s="34" t="s">
+      <c r="H4" s="35" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="31"/>
-      <c r="K4" s="34" t="s">
+      <c r="K4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="31"/>
-      <c r="M4" s="34" t="s">
+      <c r="M4" s="35" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="31"/>
@@ -3659,19 +3659,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="33"/>
+      <c r="B5" s="34"/>
       <c r="C5" s="31"/>
       <c r="D5" s="31"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="33"/>
+      <c r="G5" s="34"/>
       <c r="H5" s="31"/>
       <c r="I5" s="31"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="33"/>
+      <c r="L5" s="34"/>
       <c r="M5" s="31"/>
       <c r="N5" s="31"/>
     </row>
@@ -3679,19 +3679,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="32"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="31"/>
       <c r="D6" s="31"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="32"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="31"/>
       <c r="I6" s="31"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="32"/>
+      <c r="L6" s="33"/>
       <c r="M6" s="31"/>
       <c r="N6" s="31"/>
     </row>
@@ -3699,19 +3699,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="33"/>
+      <c r="B7" s="34"/>
       <c r="C7" s="31"/>
       <c r="D7" s="31"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="33"/>
+      <c r="G7" s="34"/>
       <c r="H7" s="31"/>
       <c r="I7" s="31"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="33"/>
+      <c r="L7" s="34"/>
       <c r="M7" s="31"/>
       <c r="N7" s="31"/>
     </row>
@@ -3719,19 +3719,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="32"/>
+      <c r="B8" s="33"/>
       <c r="C8" s="31"/>
       <c r="D8" s="31"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="32"/>
+      <c r="G8" s="33"/>
       <c r="H8" s="31"/>
       <c r="I8" s="31"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="32"/>
+      <c r="L8" s="33"/>
       <c r="M8" s="31"/>
       <c r="N8" s="31"/>
     </row>
@@ -3739,19 +3739,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="33"/>
+      <c r="B9" s="34"/>
       <c r="C9" s="31"/>
       <c r="D9" s="31"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="33"/>
+      <c r="G9" s="34"/>
       <c r="H9" s="31"/>
       <c r="I9" s="31"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="33"/>
+      <c r="L9" s="34"/>
       <c r="M9" s="31"/>
       <c r="N9" s="31"/>
     </row>
@@ -3759,19 +3759,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="32"/>
+      <c r="B10" s="33"/>
       <c r="C10" s="31"/>
       <c r="D10" s="31"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="32"/>
+      <c r="G10" s="33"/>
       <c r="H10" s="31"/>
       <c r="I10" s="31"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="32"/>
+      <c r="L10" s="33"/>
       <c r="M10" s="31"/>
       <c r="N10" s="31"/>
     </row>
@@ -3779,19 +3779,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="33"/>
+      <c r="B11" s="34"/>
       <c r="C11" s="31"/>
       <c r="D11" s="31"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="33"/>
+      <c r="G11" s="34"/>
       <c r="H11" s="31"/>
       <c r="I11" s="31"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="33"/>
+      <c r="L11" s="34"/>
       <c r="M11" s="31"/>
       <c r="N11" s="31"/>
     </row>
@@ -3799,19 +3799,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="32"/>
+      <c r="B12" s="33"/>
       <c r="C12" s="31"/>
       <c r="D12" s="31"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="32"/>
+      <c r="G12" s="33"/>
       <c r="H12" s="31"/>
       <c r="I12" s="31"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="32"/>
+      <c r="L12" s="33"/>
       <c r="M12" s="31"/>
       <c r="N12" s="31"/>
     </row>
@@ -3819,7 +3819,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="35">
+      <c r="B13" s="36">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3828,7 +3828,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="35">
+      <c r="G13" s="36">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3837,7 +3837,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="35">
+      <c r="L13" s="36">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3873,19 +3873,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="36" t="s">
+      <c r="A25" s="32" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="31"/>
       <c r="C25" s="31"/>
       <c r="D25" s="31"/>
-      <c r="F25" s="36" t="s">
+      <c r="F25" s="32" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="31"/>
       <c r="H25" s="31"/>
       <c r="I25" s="31"/>
-      <c r="K25" s="36" t="s">
+      <c r="K25" s="32" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="31"/>
@@ -3893,19 +3893,19 @@
       <c r="N25" s="31"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="36" t="s">
+      <c r="A26" s="32" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="31"/>
       <c r="C26" s="31"/>
       <c r="D26" s="31"/>
-      <c r="F26" s="36" t="s">
+      <c r="F26" s="32" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="31"/>
       <c r="H26" s="31"/>
       <c r="I26" s="31"/>
-      <c r="K26" s="36" t="s">
+      <c r="K26" s="32" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="31"/>
@@ -3927,27 +3927,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="34" t="s">
+      <c r="A28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="31"/>
-      <c r="C28" s="34" t="s">
+      <c r="C28" s="35" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="31"/>
-      <c r="F28" s="34" t="s">
+      <c r="F28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="31"/>
-      <c r="H28" s="34" t="s">
+      <c r="H28" s="35" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="31"/>
-      <c r="K28" s="34" t="s">
+      <c r="K28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="31"/>
-      <c r="M28" s="34" t="s">
+      <c r="M28" s="35" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="31"/>
@@ -3956,19 +3956,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="33"/>
+      <c r="B29" s="34"/>
       <c r="C29" s="31"/>
       <c r="D29" s="31"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="33"/>
+      <c r="G29" s="34"/>
       <c r="H29" s="31"/>
       <c r="I29" s="31"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="33"/>
+      <c r="L29" s="34"/>
       <c r="M29" s="31"/>
       <c r="N29" s="31"/>
     </row>
@@ -3976,19 +3976,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="32"/>
+      <c r="B30" s="33"/>
       <c r="C30" s="31"/>
       <c r="D30" s="31"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="32"/>
+      <c r="G30" s="33"/>
       <c r="H30" s="31"/>
       <c r="I30" s="31"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="32"/>
+      <c r="L30" s="33"/>
       <c r="M30" s="31"/>
       <c r="N30" s="31"/>
     </row>
@@ -3996,19 +3996,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="33"/>
+      <c r="B31" s="34"/>
       <c r="C31" s="31"/>
       <c r="D31" s="31"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="33"/>
+      <c r="G31" s="34"/>
       <c r="H31" s="31"/>
       <c r="I31" s="31"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="33"/>
+      <c r="L31" s="34"/>
       <c r="M31" s="31"/>
       <c r="N31" s="31"/>
     </row>
@@ -4016,19 +4016,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="32"/>
+      <c r="B32" s="33"/>
       <c r="C32" s="31"/>
       <c r="D32" s="31"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="32"/>
+      <c r="G32" s="33"/>
       <c r="H32" s="31"/>
       <c r="I32" s="31"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="32"/>
+      <c r="L32" s="33"/>
       <c r="M32" s="31"/>
       <c r="N32" s="31"/>
     </row>
@@ -4036,19 +4036,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="33"/>
+      <c r="B33" s="34"/>
       <c r="C33" s="31"/>
       <c r="D33" s="31"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="33"/>
+      <c r="G33" s="34"/>
       <c r="H33" s="31"/>
       <c r="I33" s="31"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="33"/>
+      <c r="L33" s="34"/>
       <c r="M33" s="31"/>
       <c r="N33" s="31"/>
     </row>
@@ -4056,19 +4056,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="32"/>
+      <c r="B34" s="33"/>
       <c r="C34" s="31"/>
       <c r="D34" s="31"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="32"/>
+      <c r="G34" s="33"/>
       <c r="H34" s="31"/>
       <c r="I34" s="31"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="32"/>
+      <c r="L34" s="33"/>
       <c r="M34" s="31"/>
       <c r="N34" s="31"/>
     </row>
@@ -4076,19 +4076,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="33"/>
+      <c r="B35" s="34"/>
       <c r="C35" s="31"/>
       <c r="D35" s="31"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="33"/>
+      <c r="G35" s="34"/>
       <c r="H35" s="31"/>
       <c r="I35" s="31"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="33"/>
+      <c r="L35" s="34"/>
       <c r="M35" s="31"/>
       <c r="N35" s="31"/>
     </row>
@@ -4096,19 +4096,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="32"/>
+      <c r="B36" s="33"/>
       <c r="C36" s="31"/>
       <c r="D36" s="31"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="32"/>
+      <c r="G36" s="33"/>
       <c r="H36" s="31"/>
       <c r="I36" s="31"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="32"/>
+      <c r="L36" s="33"/>
       <c r="M36" s="31"/>
       <c r="N36" s="31"/>
     </row>
@@ -4116,7 +4116,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="35">
+      <c r="B37" s="36">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -4125,7 +4125,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="35">
+      <c r="G37" s="36">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -4134,7 +4134,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="35">
+      <c r="L37" s="36">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -4171,6 +4171,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
     <mergeCell ref="L34:N34"/>
     <mergeCell ref="L6:N6"/>
     <mergeCell ref="B33:D33"/>
@@ -4187,68 +4249,6 @@
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EE3EDB9-CBC3-4F02-9895-4CAB2913F641}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F00FBA45-C007-4BE5-86E5-BDCD4DB64E44}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -786,21 +786,21 @@
       </c>
       <c r="B5" s="21">
         <f>SUM(B6:B7)</f>
-        <v>3200</v>
+        <v>0</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="G5" s="14">
         <f>SUM(G6:G7)</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="L5" s="14">
         <f>SUM(L6:L7)</f>
-        <v>2100</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
@@ -811,21 +811,21 @@
       <c r="F6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="14"/>
+      <c r="G6" s="14">
+        <v>800</v>
+      </c>
       <c r="K6" s="7" t="s">
         <v>21</v>
       </c>
       <c r="L6" s="14">
-        <v>2100</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="14">
-        <v>3200</v>
-      </c>
+      <c r="B7" s="14"/>
       <c r="F7" s="7" t="s">
         <v>22</v>
       </c>
@@ -848,14 +848,14 @@
       </c>
       <c r="G8" s="15">
         <f>SUM(G9:G10)</f>
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="K8" s="9" t="s">
         <v>23</v>
       </c>
       <c r="L8" s="15">
         <f>SUM(L9:L10)</f>
-        <v>1500</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1">
@@ -867,13 +867,13 @@
         <v>21</v>
       </c>
       <c r="G9" s="15">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="K9" s="9" t="s">
         <v>21</v>
       </c>
       <c r="L9" s="15">
-        <v>1500</v>
+        <v>500</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
@@ -961,7 +961,7 @@
       </c>
       <c r="L14" s="15">
         <f>SUM(L15:L16)</f>
-        <v>250</v>
+        <v>400</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1">
@@ -977,7 +977,7 @@
         <v>21</v>
       </c>
       <c r="L15" s="15">
-        <v>250</v>
+        <v>400</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="G23" s="14">
         <f>SUM(G24:G25)</f>
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="K23" s="7" t="s">
         <v>28</v>
@@ -1129,9 +1129,7 @@
       <c r="F24" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G24" s="14">
-        <v>340</v>
-      </c>
+      <c r="G24" s="14"/>
       <c r="K24" s="7" t="s">
         <v>21</v>
       </c>
@@ -1157,7 +1155,7 @@
       </c>
       <c r="B26" s="15">
         <f>SUM(B27:B28)</f>
-        <v>0</v>
+        <v>263</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>29</v>
@@ -1178,7 +1176,9 @@
       <c r="A27" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="15"/>
+      <c r="B27" s="15">
+        <v>263</v>
+      </c>
       <c r="F27" s="9" t="s">
         <v>21</v>
       </c>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="L29" s="14">
         <f>SUM(L30:L31)</f>
-        <v>1000</v>
+        <v>800</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1">
@@ -1238,7 +1238,7 @@
         <v>21</v>
       </c>
       <c r="L30" s="14">
-        <v>1000</v>
+        <v>800</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="L32" s="15">
         <f>SUM(L33:L34)</f>
-        <v>150</v>
+        <v>66</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
@@ -1291,7 +1291,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="15">
-        <v>150</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="L38" s="23">
         <f>SUM(L39:L40)</f>
-        <v>200</v>
+        <v>77</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="15" customHeight="1">
@@ -1395,7 +1395,7 @@
         <v>21</v>
       </c>
       <c r="L39" s="15">
-        <v>200</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="15" customHeight="1">
@@ -1418,21 +1418,21 @@
       </c>
       <c r="B41" s="13">
         <f>SUM(B5,B8,B11,B14,B17,B20,B23,B26,B29,B32,B35,B38)</f>
-        <v>3700</v>
+        <v>763</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G41" s="13">
         <f>SUM(G5,G8,G11,G14,G17,G20,G23,G26,G29,G32,G35,G38)</f>
-        <v>1040</v>
+        <v>1800</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="L41" s="13">
         <f>SUM(L5,L8,L11,L14,L17,L20,L23,L26,L29,L32,L35,L38)</f>
-        <v>5200</v>
+        <v>4843</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L53" s="14">
         <f>SUM(L54:L55)</f>
-        <v>1200</v>
+        <v>300</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="15" customHeight="1">
@@ -1558,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="L54" s="14">
-        <v>1200</v>
+        <v>300</v>
       </c>
     </row>
     <row r="55" spans="1:14" ht="15" customHeight="1">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="L62" s="15">
         <f>SUM(L63:L64)</f>
-        <v>0</v>
+        <v>42</v>
       </c>
     </row>
     <row r="63" spans="1:14" ht="15" customHeight="1">
@@ -1714,7 +1714,9 @@
       <c r="K63" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L63" s="15"/>
+      <c r="L63" s="15">
+        <v>42</v>
+      </c>
     </row>
     <row r="64" spans="1:14" ht="15" customHeight="1">
       <c r="A64" s="9" t="s">
@@ -2160,7 +2162,7 @@
       </c>
       <c r="L89" s="13">
         <f>SUM(L53,L56,L59,L62,L65,L68,L71,L74,L77,L80,L83,L86)</f>
-        <v>1200</v>
+        <v>342</v>
       </c>
     </row>
     <row r="90" spans="1:14" ht="15" customHeight="1">
@@ -2252,7 +2254,7 @@
       </c>
       <c r="B97" s="26">
         <f>SUM(B98:B99)</f>
-        <v>0</v>
+        <v>958</v>
       </c>
       <c r="C97" s="24"/>
       <c r="D97" s="24"/>
@@ -2262,21 +2264,25 @@
       </c>
       <c r="G97" s="26">
         <f>SUM(G98:G99)</f>
-        <v>0</v>
+        <v>652</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="15">
       <c r="A98" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B98" s="26"/>
+      <c r="B98" s="26">
+        <v>958</v>
+      </c>
       <c r="C98" s="24"/>
       <c r="D98" s="24"/>
       <c r="E98" s="24"/>
       <c r="F98" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G98" s="26"/>
+      <c r="G98" s="26">
+        <v>652</v>
+      </c>
     </row>
     <row r="99" spans="1:7" ht="15">
       <c r="A99" s="7" t="s">
@@ -2796,7 +2802,7 @@
       </c>
       <c r="B133" s="28">
         <f>SUM(B97,B100,B103,B106,B109,B112,B115,B118,B121,B124,B127,B130)</f>
-        <v>0</v>
+        <v>958</v>
       </c>
       <c r="C133" s="24"/>
       <c r="D133" s="24"/>
@@ -2806,7 +2812,7 @@
       </c>
       <c r="G133" s="28">
         <f>SUM(G97,G100,G103,G106,G109,G112,G115,G118,G121,G124,G127,G130)</f>
-        <v>374</v>
+        <v>1026</v>
       </c>
     </row>
   </sheetData>

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F00FBA45-C007-4BE5-86E5-BDCD4DB64E44}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA255949-2C12-404F-BA4B-126F6B497241}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -446,9 +446,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -459,6 +456,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -800,7 +800,7 @@
       </c>
       <c r="L5" s="14">
         <f>SUM(L6:L7)</f>
-        <v>3000</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
@@ -818,7 +818,7 @@
         <v>21</v>
       </c>
       <c r="L6" s="14">
-        <v>3000</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="L41" s="13">
         <f>SUM(L5,L8,L11,L14,L17,L20,L23,L26,L29,L32,L35,L38)</f>
-        <v>4843</v>
+        <v>3643</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1">
@@ -2834,19 +2834,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="36" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="31"/>
       <c r="C1" s="31"/>
       <c r="D1" s="31"/>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="36" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="31"/>
       <c r="H1" s="31"/>
       <c r="I1" s="31"/>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="36" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="31"/>
@@ -2854,19 +2854,19 @@
       <c r="N1" s="31"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="36" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
       <c r="D2" s="31"/>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="36" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="31"/>
       <c r="H2" s="31"/>
       <c r="I2" s="31"/>
-      <c r="K2" s="32" t="s">
+      <c r="K2" s="36" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="31"/>
@@ -2888,27 +2888,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="34" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="31"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="34" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="31"/>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="34" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="31"/>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="34" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="31"/>
-      <c r="K4" s="35" t="s">
+      <c r="K4" s="34" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="31"/>
-      <c r="M4" s="35" t="s">
+      <c r="M4" s="34" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="31"/>
@@ -2917,21 +2917,21 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="34">
-        <v>0</v>
-      </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
+      <c r="B5" s="33">
+        <v>0</v>
+      </c>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="34"/>
+      <c r="G5" s="33"/>
       <c r="H5" s="31"/>
       <c r="I5" s="31"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="34"/>
+      <c r="L5" s="33"/>
       <c r="M5" s="31"/>
       <c r="N5" s="31"/>
     </row>
@@ -2939,21 +2939,21 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="33">
-        <v>0</v>
-      </c>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
+      <c r="B6" s="32">
+        <v>0</v>
+      </c>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="33"/>
+      <c r="G6" s="32"/>
       <c r="H6" s="31"/>
       <c r="I6" s="31"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="33"/>
+      <c r="L6" s="32"/>
       <c r="M6" s="31"/>
       <c r="N6" s="31"/>
     </row>
@@ -2961,21 +2961,21 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="34">
-        <v>0</v>
-      </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
+      <c r="B7" s="33">
+        <v>0</v>
+      </c>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="34"/>
+      <c r="G7" s="33"/>
       <c r="H7" s="31"/>
       <c r="I7" s="31"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="34"/>
+      <c r="L7" s="33"/>
       <c r="M7" s="31"/>
       <c r="N7" s="31"/>
     </row>
@@ -2983,21 +2983,21 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="33">
-        <v>0</v>
-      </c>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
+      <c r="B8" s="32">
+        <v>0</v>
+      </c>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="33"/>
+      <c r="G8" s="32"/>
       <c r="H8" s="31"/>
       <c r="I8" s="31"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="33"/>
+      <c r="L8" s="32"/>
       <c r="M8" s="31"/>
       <c r="N8" s="31"/>
     </row>
@@ -3005,21 +3005,21 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="34">
-        <v>0</v>
-      </c>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
+      <c r="B9" s="33">
+        <v>0</v>
+      </c>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="34"/>
+      <c r="G9" s="33"/>
       <c r="H9" s="31"/>
       <c r="I9" s="31"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="34"/>
+      <c r="L9" s="33"/>
       <c r="M9" s="31"/>
       <c r="N9" s="31"/>
     </row>
@@ -3027,21 +3027,21 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="33">
-        <v>0</v>
-      </c>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
+      <c r="B10" s="32">
+        <v>0</v>
+      </c>
+      <c r="C10" s="32"/>
+      <c r="D10" s="32"/>
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="33"/>
+      <c r="G10" s="32"/>
       <c r="H10" s="31"/>
       <c r="I10" s="31"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="33"/>
+      <c r="L10" s="32"/>
       <c r="M10" s="31"/>
       <c r="N10" s="31"/>
     </row>
@@ -3049,7 +3049,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="36">
+      <c r="B11" s="35">
         <f>SUM(B5:B10)</f>
         <v>0</v>
       </c>
@@ -3058,7 +3058,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="36">
+      <c r="G11" s="35">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -3067,7 +3067,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="36">
+      <c r="L11" s="35">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -3103,19 +3103,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="32" t="s">
+      <c r="A25" s="36" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="31"/>
       <c r="C25" s="31"/>
       <c r="D25" s="31"/>
-      <c r="F25" s="32" t="s">
+      <c r="F25" s="36" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="31"/>
       <c r="H25" s="31"/>
       <c r="I25" s="31"/>
-      <c r="K25" s="32" t="s">
+      <c r="K25" s="36" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="31"/>
@@ -3123,19 +3123,19 @@
       <c r="N25" s="31"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="32" t="s">
+      <c r="A26" s="36" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="31"/>
       <c r="C26" s="31"/>
       <c r="D26" s="31"/>
-      <c r="F26" s="32" t="s">
+      <c r="F26" s="36" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="31"/>
       <c r="H26" s="31"/>
       <c r="I26" s="31"/>
-      <c r="K26" s="32" t="s">
+      <c r="K26" s="36" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="31"/>
@@ -3157,27 +3157,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="35" t="s">
+      <c r="A28" s="34" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="31"/>
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="34" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="31"/>
-      <c r="F28" s="35" t="s">
+      <c r="F28" s="34" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="31"/>
-      <c r="H28" s="35" t="s">
+      <c r="H28" s="34" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="31"/>
-      <c r="K28" s="35" t="s">
+      <c r="K28" s="34" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="31"/>
-      <c r="M28" s="35" t="s">
+      <c r="M28" s="34" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="31"/>
@@ -3186,7 +3186,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="34">
+      <c r="B29" s="33">
         <v>0</v>
       </c>
       <c r="C29" s="31"/>
@@ -3194,23 +3194,23 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="34"/>
+      <c r="G29" s="33"/>
       <c r="H29" s="31"/>
       <c r="I29" s="31"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="34">
-        <v>0</v>
-      </c>
-      <c r="M29" s="34"/>
-      <c r="N29" s="34"/>
+      <c r="L29" s="33">
+        <v>0</v>
+      </c>
+      <c r="M29" s="33"/>
+      <c r="N29" s="33"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="33">
+      <c r="B30" s="32">
         <v>0</v>
       </c>
       <c r="C30" s="31"/>
@@ -3218,23 +3218,23 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="33"/>
+      <c r="G30" s="32"/>
       <c r="H30" s="31"/>
       <c r="I30" s="31"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="33">
-        <v>0</v>
-      </c>
-      <c r="M30" s="33"/>
-      <c r="N30" s="33"/>
+      <c r="L30" s="32">
+        <v>0</v>
+      </c>
+      <c r="M30" s="32"/>
+      <c r="N30" s="32"/>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1">
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="34">
+      <c r="B31" s="33">
         <v>0</v>
       </c>
       <c r="C31" s="31"/>
@@ -3242,23 +3242,23 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="34"/>
+      <c r="G31" s="33"/>
       <c r="H31" s="31"/>
       <c r="I31" s="31"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="34">
-        <v>0</v>
-      </c>
-      <c r="M31" s="34"/>
-      <c r="N31" s="34"/>
+      <c r="L31" s="33">
+        <v>0</v>
+      </c>
+      <c r="M31" s="33"/>
+      <c r="N31" s="33"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="33">
+      <c r="B32" s="32">
         <v>0</v>
       </c>
       <c r="C32" s="31"/>
@@ -3266,23 +3266,23 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="33"/>
+      <c r="G32" s="32"/>
       <c r="H32" s="31"/>
       <c r="I32" s="31"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="33">
-        <v>0</v>
-      </c>
-      <c r="M32" s="33"/>
-      <c r="N32" s="33"/>
+      <c r="L32" s="32">
+        <v>0</v>
+      </c>
+      <c r="M32" s="32"/>
+      <c r="N32" s="32"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="34">
+      <c r="B33" s="33">
         <v>0</v>
       </c>
       <c r="C33" s="31"/>
@@ -3290,23 +3290,23 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="34"/>
+      <c r="G33" s="33"/>
       <c r="H33" s="31"/>
       <c r="I33" s="31"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="34">
-        <v>0</v>
-      </c>
-      <c r="M33" s="34"/>
-      <c r="N33" s="34"/>
+      <c r="L33" s="33">
+        <v>0</v>
+      </c>
+      <c r="M33" s="33"/>
+      <c r="N33" s="33"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="33">
+      <c r="B34" s="32">
         <v>0</v>
       </c>
       <c r="C34" s="31"/>
@@ -3314,13 +3314,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="33"/>
+      <c r="G34" s="32"/>
       <c r="H34" s="31"/>
       <c r="I34" s="31"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="33">
+      <c r="L34" s="32">
         <v>0</v>
       </c>
       <c r="M34" s="31"/>
@@ -3330,7 +3330,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="36">
+      <c r="B35" s="35">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -3339,7 +3339,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="36">
+      <c r="G35" s="35">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -3348,7 +3348,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="36">
+      <c r="L35" s="35">
         <f>SUM(L29:L34)</f>
         <v>0</v>
       </c>
@@ -3385,6 +3385,56 @@
     </row>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B10:D10"/>
@@ -3401,56 +3451,6 @@
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="H28:I28"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3466,7 +3466,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="36" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="31"/>
@@ -3474,7 +3474,7 @@
       <c r="D1" s="31"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="36" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="31"/>
@@ -3488,11 +3488,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="34" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="31"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="34" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="31"/>
@@ -3501,7 +3501,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="34"/>
+      <c r="B5" s="33"/>
       <c r="C5" s="31"/>
       <c r="D5" s="31"/>
     </row>
@@ -3509,7 +3509,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="33"/>
+      <c r="B6" s="32"/>
       <c r="C6" s="31"/>
       <c r="D6" s="31"/>
     </row>
@@ -3517,7 +3517,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="34"/>
+      <c r="B7" s="33"/>
       <c r="C7" s="31"/>
       <c r="D7" s="31"/>
     </row>
@@ -3525,7 +3525,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="33"/>
+      <c r="B8" s="32"/>
       <c r="C8" s="31"/>
       <c r="D8" s="31"/>
     </row>
@@ -3533,7 +3533,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="36">
+      <c r="B9" s="35">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -3582,19 +3582,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="36" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="31"/>
       <c r="C1" s="31"/>
       <c r="D1" s="31"/>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="36" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="31"/>
       <c r="H1" s="31"/>
       <c r="I1" s="31"/>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="36" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="31"/>
@@ -3602,19 +3602,19 @@
       <c r="N1" s="31"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="36" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
       <c r="D2" s="31"/>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="36" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="31"/>
       <c r="H2" s="31"/>
       <c r="I2" s="31"/>
-      <c r="K2" s="32" t="s">
+      <c r="K2" s="36" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="31"/>
@@ -3636,27 +3636,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="34" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="31"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="34" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="31"/>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="34" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="31"/>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="34" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="31"/>
-      <c r="K4" s="35" t="s">
+      <c r="K4" s="34" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="31"/>
-      <c r="M4" s="35" t="s">
+      <c r="M4" s="34" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="31"/>
@@ -3665,19 +3665,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="34"/>
+      <c r="B5" s="33"/>
       <c r="C5" s="31"/>
       <c r="D5" s="31"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="34"/>
+      <c r="G5" s="33"/>
       <c r="H5" s="31"/>
       <c r="I5" s="31"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="34"/>
+      <c r="L5" s="33"/>
       <c r="M5" s="31"/>
       <c r="N5" s="31"/>
     </row>
@@ -3685,19 +3685,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="33"/>
+      <c r="B6" s="32"/>
       <c r="C6" s="31"/>
       <c r="D6" s="31"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="33"/>
+      <c r="G6" s="32"/>
       <c r="H6" s="31"/>
       <c r="I6" s="31"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="33"/>
+      <c r="L6" s="32"/>
       <c r="M6" s="31"/>
       <c r="N6" s="31"/>
     </row>
@@ -3705,19 +3705,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="34"/>
+      <c r="B7" s="33"/>
       <c r="C7" s="31"/>
       <c r="D7" s="31"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="34"/>
+      <c r="G7" s="33"/>
       <c r="H7" s="31"/>
       <c r="I7" s="31"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="34"/>
+      <c r="L7" s="33"/>
       <c r="M7" s="31"/>
       <c r="N7" s="31"/>
     </row>
@@ -3725,19 +3725,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="33"/>
+      <c r="B8" s="32"/>
       <c r="C8" s="31"/>
       <c r="D8" s="31"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="33"/>
+      <c r="G8" s="32"/>
       <c r="H8" s="31"/>
       <c r="I8" s="31"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="33"/>
+      <c r="L8" s="32"/>
       <c r="M8" s="31"/>
       <c r="N8" s="31"/>
     </row>
@@ -3745,19 +3745,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="34"/>
+      <c r="B9" s="33"/>
       <c r="C9" s="31"/>
       <c r="D9" s="31"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="34"/>
+      <c r="G9" s="33"/>
       <c r="H9" s="31"/>
       <c r="I9" s="31"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="34"/>
+      <c r="L9" s="33"/>
       <c r="M9" s="31"/>
       <c r="N9" s="31"/>
     </row>
@@ -3765,19 +3765,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="33"/>
+      <c r="B10" s="32"/>
       <c r="C10" s="31"/>
       <c r="D10" s="31"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="33"/>
+      <c r="G10" s="32"/>
       <c r="H10" s="31"/>
       <c r="I10" s="31"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="33"/>
+      <c r="L10" s="32"/>
       <c r="M10" s="31"/>
       <c r="N10" s="31"/>
     </row>
@@ -3785,19 +3785,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="34"/>
+      <c r="B11" s="33"/>
       <c r="C11" s="31"/>
       <c r="D11" s="31"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="34"/>
+      <c r="G11" s="33"/>
       <c r="H11" s="31"/>
       <c r="I11" s="31"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="34"/>
+      <c r="L11" s="33"/>
       <c r="M11" s="31"/>
       <c r="N11" s="31"/>
     </row>
@@ -3805,19 +3805,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="33"/>
+      <c r="B12" s="32"/>
       <c r="C12" s="31"/>
       <c r="D12" s="31"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="33"/>
+      <c r="G12" s="32"/>
       <c r="H12" s="31"/>
       <c r="I12" s="31"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="33"/>
+      <c r="L12" s="32"/>
       <c r="M12" s="31"/>
       <c r="N12" s="31"/>
     </row>
@@ -3825,7 +3825,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="36">
+      <c r="B13" s="35">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3834,7 +3834,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="36">
+      <c r="G13" s="35">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3843,7 +3843,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="36">
+      <c r="L13" s="35">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3879,19 +3879,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="32" t="s">
+      <c r="A25" s="36" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="31"/>
       <c r="C25" s="31"/>
       <c r="D25" s="31"/>
-      <c r="F25" s="32" t="s">
+      <c r="F25" s="36" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="31"/>
       <c r="H25" s="31"/>
       <c r="I25" s="31"/>
-      <c r="K25" s="32" t="s">
+      <c r="K25" s="36" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="31"/>
@@ -3899,19 +3899,19 @@
       <c r="N25" s="31"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="32" t="s">
+      <c r="A26" s="36" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="31"/>
       <c r="C26" s="31"/>
       <c r="D26" s="31"/>
-      <c r="F26" s="32" t="s">
+      <c r="F26" s="36" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="31"/>
       <c r="H26" s="31"/>
       <c r="I26" s="31"/>
-      <c r="K26" s="32" t="s">
+      <c r="K26" s="36" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="31"/>
@@ -3933,27 +3933,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="35" t="s">
+      <c r="A28" s="34" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="31"/>
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="34" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="31"/>
-      <c r="F28" s="35" t="s">
+      <c r="F28" s="34" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="31"/>
-      <c r="H28" s="35" t="s">
+      <c r="H28" s="34" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="31"/>
-      <c r="K28" s="35" t="s">
+      <c r="K28" s="34" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="31"/>
-      <c r="M28" s="35" t="s">
+      <c r="M28" s="34" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="31"/>
@@ -3962,19 +3962,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="34"/>
+      <c r="B29" s="33"/>
       <c r="C29" s="31"/>
       <c r="D29" s="31"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="34"/>
+      <c r="G29" s="33"/>
       <c r="H29" s="31"/>
       <c r="I29" s="31"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="34"/>
+      <c r="L29" s="33"/>
       <c r="M29" s="31"/>
       <c r="N29" s="31"/>
     </row>
@@ -3982,19 +3982,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="33"/>
+      <c r="B30" s="32"/>
       <c r="C30" s="31"/>
       <c r="D30" s="31"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="33"/>
+      <c r="G30" s="32"/>
       <c r="H30" s="31"/>
       <c r="I30" s="31"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="33"/>
+      <c r="L30" s="32"/>
       <c r="M30" s="31"/>
       <c r="N30" s="31"/>
     </row>
@@ -4002,19 +4002,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="34"/>
+      <c r="B31" s="33"/>
       <c r="C31" s="31"/>
       <c r="D31" s="31"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="34"/>
+      <c r="G31" s="33"/>
       <c r="H31" s="31"/>
       <c r="I31" s="31"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="34"/>
+      <c r="L31" s="33"/>
       <c r="M31" s="31"/>
       <c r="N31" s="31"/>
     </row>
@@ -4022,19 +4022,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="33"/>
+      <c r="B32" s="32"/>
       <c r="C32" s="31"/>
       <c r="D32" s="31"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="33"/>
+      <c r="G32" s="32"/>
       <c r="H32" s="31"/>
       <c r="I32" s="31"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="33"/>
+      <c r="L32" s="32"/>
       <c r="M32" s="31"/>
       <c r="N32" s="31"/>
     </row>
@@ -4042,19 +4042,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="34"/>
+      <c r="B33" s="33"/>
       <c r="C33" s="31"/>
       <c r="D33" s="31"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="34"/>
+      <c r="G33" s="33"/>
       <c r="H33" s="31"/>
       <c r="I33" s="31"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="34"/>
+      <c r="L33" s="33"/>
       <c r="M33" s="31"/>
       <c r="N33" s="31"/>
     </row>
@@ -4062,19 +4062,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="33"/>
+      <c r="B34" s="32"/>
       <c r="C34" s="31"/>
       <c r="D34" s="31"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="33"/>
+      <c r="G34" s="32"/>
       <c r="H34" s="31"/>
       <c r="I34" s="31"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="33"/>
+      <c r="L34" s="32"/>
       <c r="M34" s="31"/>
       <c r="N34" s="31"/>
     </row>
@@ -4082,19 +4082,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="34"/>
+      <c r="B35" s="33"/>
       <c r="C35" s="31"/>
       <c r="D35" s="31"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="34"/>
+      <c r="G35" s="33"/>
       <c r="H35" s="31"/>
       <c r="I35" s="31"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="34"/>
+      <c r="L35" s="33"/>
       <c r="M35" s="31"/>
       <c r="N35" s="31"/>
     </row>
@@ -4102,19 +4102,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="33"/>
+      <c r="B36" s="32"/>
       <c r="C36" s="31"/>
       <c r="D36" s="31"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="33"/>
+      <c r="G36" s="32"/>
       <c r="H36" s="31"/>
       <c r="I36" s="31"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="33"/>
+      <c r="L36" s="32"/>
       <c r="M36" s="31"/>
       <c r="N36" s="31"/>
     </row>
@@ -4122,7 +4122,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="36">
+      <c r="B37" s="35">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -4131,7 +4131,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="36">
+      <c r="G37" s="35">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -4140,7 +4140,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="36">
+      <c r="L37" s="35">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -4177,6 +4177,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
     <mergeCell ref="G36:I36"/>
     <mergeCell ref="L32:N32"/>
     <mergeCell ref="L13:N13"/>
@@ -4193,68 +4255,6 @@
     <mergeCell ref="L33:N33"/>
     <mergeCell ref="L35:N35"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="L9:N9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA255949-2C12-404F-BA4B-126F6B497241}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82D5B2CE-F80E-4BD8-BD9E-0A6394B89FB7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -446,6 +446,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -456,9 +459,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -793,14 +793,14 @@
       </c>
       <c r="G5" s="14">
         <f>SUM(G6:G7)</f>
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="K5" s="7" t="s">
         <v>20</v>
       </c>
       <c r="L5" s="14">
         <f>SUM(L6:L7)</f>
-        <v>1800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
@@ -811,14 +811,12 @@
       <c r="F6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="14">
-        <v>800</v>
-      </c>
+      <c r="G6" s="14"/>
       <c r="K6" s="7" t="s">
         <v>21</v>
       </c>
       <c r="L6" s="14">
-        <v>1800</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
@@ -848,14 +846,14 @@
       </c>
       <c r="G8" s="15">
         <f>SUM(G9:G10)</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="K8" s="9" t="s">
         <v>23</v>
       </c>
       <c r="L8" s="15">
         <f>SUM(L9:L10)</f>
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1">
@@ -866,14 +864,12 @@
       <c r="F9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="15">
-        <v>1000</v>
-      </c>
+      <c r="G9" s="15"/>
       <c r="K9" s="9" t="s">
         <v>21</v>
       </c>
       <c r="L9" s="15">
-        <v>500</v>
+        <v>300</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
@@ -961,7 +957,7 @@
       </c>
       <c r="L14" s="15">
         <f>SUM(L15:L16)</f>
-        <v>400</v>
+        <v>600</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1">
@@ -977,7 +973,7 @@
         <v>21</v>
       </c>
       <c r="L15" s="15">
-        <v>400</v>
+        <v>600</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1">
@@ -1000,7 +996,7 @@
       </c>
       <c r="B17" s="14">
         <f>SUM(B18:B19)</f>
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>26</v>
@@ -1021,7 +1017,9 @@
       <c r="A18" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="14"/>
+      <c r="B18" s="14">
+        <v>36</v>
+      </c>
       <c r="F18" s="7" t="s">
         <v>21</v>
       </c>
@@ -1051,7 +1049,7 @@
       </c>
       <c r="B20" s="15">
         <f>SUM(B21:B22)</f>
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>27</v>
@@ -1073,7 +1071,7 @@
         <v>21</v>
       </c>
       <c r="B21" s="15">
-        <v>500</v>
+        <v>170</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>21</v>
@@ -1111,7 +1109,7 @@
       </c>
       <c r="G23" s="14">
         <f>SUM(G24:G25)</f>
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="K23" s="7" t="s">
         <v>28</v>
@@ -1143,7 +1141,9 @@
       <c r="F25" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G25" s="14"/>
+      <c r="G25" s="14">
+        <v>650</v>
+      </c>
       <c r="K25" s="7" t="s">
         <v>22</v>
       </c>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="B26" s="15">
         <f>SUM(B27:B28)</f>
-        <v>263</v>
+        <v>200</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>29</v>
@@ -1177,7 +1177,7 @@
         <v>21</v>
       </c>
       <c r="B27" s="15">
-        <v>263</v>
+        <v>200</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>21</v>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="L29" s="14">
         <f>SUM(L30:L31)</f>
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1">
@@ -1238,7 +1238,7 @@
         <v>21</v>
       </c>
       <c r="L30" s="14">
-        <v>800</v>
+        <v>600</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="L32" s="15">
         <f>SUM(L33:L34)</f>
-        <v>66</v>
+        <v>13</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
@@ -1291,7 +1291,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="15">
-        <v>66</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
@@ -1379,7 +1379,7 @@
       </c>
       <c r="L38" s="23">
         <f>SUM(L39:L40)</f>
-        <v>77</v>
+        <v>240</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="15" customHeight="1">
@@ -1395,7 +1395,7 @@
         <v>21</v>
       </c>
       <c r="L39" s="15">
-        <v>77</v>
+        <v>240</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="15" customHeight="1">
@@ -1418,21 +1418,21 @@
       </c>
       <c r="B41" s="13">
         <f>SUM(B5,B8,B11,B14,B17,B20,B23,B26,B29,B32,B35,B38)</f>
-        <v>763</v>
+        <v>406</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G41" s="13">
         <f>SUM(G5,G8,G11,G14,G17,G20,G23,G26,G29,G32,G35,G38)</f>
-        <v>1800</v>
+        <v>650</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="L41" s="13">
         <f>SUM(L5,L8,L11,L14,L17,L20,L23,L26,L29,L32,L35,L38)</f>
-        <v>3643</v>
+        <v>2753</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="L53" s="14">
         <f>SUM(L54:L55)</f>
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="15" customHeight="1">
@@ -1557,9 +1557,7 @@
       <c r="K54" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="L54" s="14">
-        <v>300</v>
-      </c>
+      <c r="L54" s="14"/>
     </row>
     <row r="55" spans="1:14" ht="15" customHeight="1">
       <c r="A55" s="7" t="s">
@@ -1683,7 +1681,7 @@
       </c>
       <c r="B62" s="15">
         <f>SUM(B63:B64)</f>
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>25</v>
@@ -1697,7 +1695,7 @@
       </c>
       <c r="L62" s="15">
         <f>SUM(L63:L64)</f>
-        <v>42</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:14" ht="15" customHeight="1">
@@ -1705,7 +1703,7 @@
         <v>21</v>
       </c>
       <c r="B63" s="15">
-        <v>60</v>
+        <v>23</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>21</v>
@@ -1714,9 +1712,7 @@
       <c r="K63" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L63" s="15">
-        <v>42</v>
-      </c>
+      <c r="L63" s="15"/>
     </row>
     <row r="64" spans="1:14" ht="15" customHeight="1">
       <c r="A64" s="9" t="s">
@@ -1840,7 +1836,7 @@
       </c>
       <c r="B71" s="14">
         <f>SUM(B72:B73)</f>
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="F71" s="7" t="s">
         <v>28</v>
@@ -1861,7 +1857,9 @@
       <c r="A72" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B72" s="14"/>
+      <c r="B72" s="14">
+        <v>250</v>
+      </c>
       <c r="F72" s="7" t="s">
         <v>21</v>
       </c>
@@ -2148,7 +2146,7 @@
       </c>
       <c r="B89" s="13">
         <f>SUM(B53,B56,B59,B62,B65,B68,B71,B74,B77,B80,B83,B86)</f>
-        <v>60</v>
+        <v>273</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>34</v>
@@ -2162,7 +2160,7 @@
       </c>
       <c r="L89" s="13">
         <f>SUM(L53,L56,L59,L62,L65,L68,L71,L74,L77,L80,L83,L86)</f>
-        <v>342</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:14" ht="15" customHeight="1">
@@ -2834,19 +2832,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="32" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="31"/>
       <c r="C1" s="31"/>
       <c r="D1" s="31"/>
-      <c r="F1" s="36" t="s">
+      <c r="F1" s="32" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="31"/>
       <c r="H1" s="31"/>
       <c r="I1" s="31"/>
-      <c r="K1" s="36" t="s">
+      <c r="K1" s="32" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="31"/>
@@ -2854,19 +2852,19 @@
       <c r="N1" s="31"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="32" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
       <c r="D2" s="31"/>
-      <c r="F2" s="36" t="s">
+      <c r="F2" s="32" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="31"/>
       <c r="H2" s="31"/>
       <c r="I2" s="31"/>
-      <c r="K2" s="36" t="s">
+      <c r="K2" s="32" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="31"/>
@@ -2888,27 +2886,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="31"/>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="35" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="31"/>
-      <c r="F4" s="34" t="s">
+      <c r="F4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="31"/>
-      <c r="H4" s="34" t="s">
+      <c r="H4" s="35" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="31"/>
-      <c r="K4" s="34" t="s">
+      <c r="K4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="31"/>
-      <c r="M4" s="34" t="s">
+      <c r="M4" s="35" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="31"/>
@@ -2917,21 +2915,21 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="33">
-        <v>0</v>
-      </c>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
+      <c r="B5" s="34">
+        <v>0</v>
+      </c>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="33"/>
+      <c r="G5" s="34"/>
       <c r="H5" s="31"/>
       <c r="I5" s="31"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="33"/>
+      <c r="L5" s="34"/>
       <c r="M5" s="31"/>
       <c r="N5" s="31"/>
     </row>
@@ -2939,21 +2937,21 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="32">
-        <v>0</v>
-      </c>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
+      <c r="B6" s="33">
+        <v>0</v>
+      </c>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="32"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="31"/>
       <c r="I6" s="31"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="32"/>
+      <c r="L6" s="33"/>
       <c r="M6" s="31"/>
       <c r="N6" s="31"/>
     </row>
@@ -2961,21 +2959,21 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="33">
-        <v>0</v>
-      </c>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
+      <c r="B7" s="34">
+        <v>0</v>
+      </c>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="33"/>
+      <c r="G7" s="34"/>
       <c r="H7" s="31"/>
       <c r="I7" s="31"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="33"/>
+      <c r="L7" s="34"/>
       <c r="M7" s="31"/>
       <c r="N7" s="31"/>
     </row>
@@ -2983,21 +2981,21 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="32">
-        <v>0</v>
-      </c>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
+      <c r="B8" s="33">
+        <v>0</v>
+      </c>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="32"/>
+      <c r="G8" s="33"/>
       <c r="H8" s="31"/>
       <c r="I8" s="31"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="32"/>
+      <c r="L8" s="33"/>
       <c r="M8" s="31"/>
       <c r="N8" s="31"/>
     </row>
@@ -3005,21 +3003,21 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="33">
-        <v>0</v>
-      </c>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
+      <c r="B9" s="34">
+        <v>0</v>
+      </c>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="33"/>
+      <c r="G9" s="34"/>
       <c r="H9" s="31"/>
       <c r="I9" s="31"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="33"/>
+      <c r="L9" s="34"/>
       <c r="M9" s="31"/>
       <c r="N9" s="31"/>
     </row>
@@ -3027,21 +3025,21 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="32">
-        <v>0</v>
-      </c>
-      <c r="C10" s="32"/>
-      <c r="D10" s="32"/>
+      <c r="B10" s="33">
+        <v>0</v>
+      </c>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="32"/>
+      <c r="G10" s="33"/>
       <c r="H10" s="31"/>
       <c r="I10" s="31"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="32"/>
+      <c r="L10" s="33"/>
       <c r="M10" s="31"/>
       <c r="N10" s="31"/>
     </row>
@@ -3049,7 +3047,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="35">
+      <c r="B11" s="36">
         <f>SUM(B5:B10)</f>
         <v>0</v>
       </c>
@@ -3058,7 +3056,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="35">
+      <c r="G11" s="36">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -3067,7 +3065,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="35">
+      <c r="L11" s="36">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -3103,19 +3101,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="36" t="s">
+      <c r="A25" s="32" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="31"/>
       <c r="C25" s="31"/>
       <c r="D25" s="31"/>
-      <c r="F25" s="36" t="s">
+      <c r="F25" s="32" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="31"/>
       <c r="H25" s="31"/>
       <c r="I25" s="31"/>
-      <c r="K25" s="36" t="s">
+      <c r="K25" s="32" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="31"/>
@@ -3123,19 +3121,19 @@
       <c r="N25" s="31"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="36" t="s">
+      <c r="A26" s="32" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="31"/>
       <c r="C26" s="31"/>
       <c r="D26" s="31"/>
-      <c r="F26" s="36" t="s">
+      <c r="F26" s="32" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="31"/>
       <c r="H26" s="31"/>
       <c r="I26" s="31"/>
-      <c r="K26" s="36" t="s">
+      <c r="K26" s="32" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="31"/>
@@ -3157,27 +3155,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="34" t="s">
+      <c r="A28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="31"/>
-      <c r="C28" s="34" t="s">
+      <c r="C28" s="35" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="31"/>
-      <c r="F28" s="34" t="s">
+      <c r="F28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="31"/>
-      <c r="H28" s="34" t="s">
+      <c r="H28" s="35" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="31"/>
-      <c r="K28" s="34" t="s">
+      <c r="K28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="31"/>
-      <c r="M28" s="34" t="s">
+      <c r="M28" s="35" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="31"/>
@@ -3186,7 +3184,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="33">
+      <c r="B29" s="34">
         <v>0</v>
       </c>
       <c r="C29" s="31"/>
@@ -3194,23 +3192,23 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="33"/>
+      <c r="G29" s="34"/>
       <c r="H29" s="31"/>
       <c r="I29" s="31"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="33">
-        <v>0</v>
-      </c>
-      <c r="M29" s="33"/>
-      <c r="N29" s="33"/>
+      <c r="L29" s="34">
+        <v>0</v>
+      </c>
+      <c r="M29" s="34"/>
+      <c r="N29" s="34"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="32">
+      <c r="B30" s="33">
         <v>0</v>
       </c>
       <c r="C30" s="31"/>
@@ -3218,23 +3216,23 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="32"/>
+      <c r="G30" s="33"/>
       <c r="H30" s="31"/>
       <c r="I30" s="31"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="32">
-        <v>0</v>
-      </c>
-      <c r="M30" s="32"/>
-      <c r="N30" s="32"/>
+      <c r="L30" s="33">
+        <v>0</v>
+      </c>
+      <c r="M30" s="33"/>
+      <c r="N30" s="33"/>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1">
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="33">
+      <c r="B31" s="34">
         <v>0</v>
       </c>
       <c r="C31" s="31"/>
@@ -3242,23 +3240,23 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="33"/>
+      <c r="G31" s="34"/>
       <c r="H31" s="31"/>
       <c r="I31" s="31"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="33">
-        <v>0</v>
-      </c>
-      <c r="M31" s="33"/>
-      <c r="N31" s="33"/>
+      <c r="L31" s="34">
+        <v>0</v>
+      </c>
+      <c r="M31" s="34"/>
+      <c r="N31" s="34"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="32">
+      <c r="B32" s="33">
         <v>0</v>
       </c>
       <c r="C32" s="31"/>
@@ -3266,23 +3264,23 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="32"/>
+      <c r="G32" s="33"/>
       <c r="H32" s="31"/>
       <c r="I32" s="31"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="32">
-        <v>0</v>
-      </c>
-      <c r="M32" s="32"/>
-      <c r="N32" s="32"/>
+      <c r="L32" s="33">
+        <v>0</v>
+      </c>
+      <c r="M32" s="33"/>
+      <c r="N32" s="33"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="33">
+      <c r="B33" s="34">
         <v>0</v>
       </c>
       <c r="C33" s="31"/>
@@ -3290,23 +3288,23 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="33"/>
+      <c r="G33" s="34"/>
       <c r="H33" s="31"/>
       <c r="I33" s="31"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="33">
-        <v>0</v>
-      </c>
-      <c r="M33" s="33"/>
-      <c r="N33" s="33"/>
+      <c r="L33" s="34">
+        <v>0</v>
+      </c>
+      <c r="M33" s="34"/>
+      <c r="N33" s="34"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="32">
+      <c r="B34" s="33">
         <v>0</v>
       </c>
       <c r="C34" s="31"/>
@@ -3314,13 +3312,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="32"/>
+      <c r="G34" s="33"/>
       <c r="H34" s="31"/>
       <c r="I34" s="31"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="32">
+      <c r="L34" s="33">
         <v>0</v>
       </c>
       <c r="M34" s="31"/>
@@ -3330,7 +3328,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="35">
+      <c r="B35" s="36">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -3339,7 +3337,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="35">
+      <c r="G35" s="36">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -3348,7 +3346,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="35">
+      <c r="L35" s="36">
         <f>SUM(L29:L34)</f>
         <v>0</v>
       </c>
@@ -3385,13 +3383,49 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="L11:N11"/>
@@ -3408,49 +3442,13 @@
     <mergeCell ref="K2:N2"/>
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3466,7 +3464,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="32" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="31"/>
@@ -3474,7 +3472,7 @@
       <c r="D1" s="31"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="32" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="31"/>
@@ -3488,11 +3486,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="35" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="31"/>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="35" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="31"/>
@@ -3501,7 +3499,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="33"/>
+      <c r="B5" s="34"/>
       <c r="C5" s="31"/>
       <c r="D5" s="31"/>
     </row>
@@ -3509,7 +3507,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="32"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="31"/>
       <c r="D6" s="31"/>
     </row>
@@ -3517,7 +3515,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="33"/>
+      <c r="B7" s="34"/>
       <c r="C7" s="31"/>
       <c r="D7" s="31"/>
     </row>
@@ -3525,7 +3523,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="32"/>
+      <c r="B8" s="33"/>
       <c r="C8" s="31"/>
       <c r="D8" s="31"/>
     </row>
@@ -3533,7 +3531,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="35">
+      <c r="B9" s="36">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -3582,19 +3580,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="32" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="31"/>
       <c r="C1" s="31"/>
       <c r="D1" s="31"/>
-      <c r="F1" s="36" t="s">
+      <c r="F1" s="32" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="31"/>
       <c r="H1" s="31"/>
       <c r="I1" s="31"/>
-      <c r="K1" s="36" t="s">
+      <c r="K1" s="32" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="31"/>
@@ -3602,19 +3600,19 @@
       <c r="N1" s="31"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="32" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
       <c r="D2" s="31"/>
-      <c r="F2" s="36" t="s">
+      <c r="F2" s="32" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="31"/>
       <c r="H2" s="31"/>
       <c r="I2" s="31"/>
-      <c r="K2" s="36" t="s">
+      <c r="K2" s="32" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="31"/>
@@ -3636,27 +3634,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="31"/>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="35" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="31"/>
-      <c r="F4" s="34" t="s">
+      <c r="F4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="31"/>
-      <c r="H4" s="34" t="s">
+      <c r="H4" s="35" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="31"/>
-      <c r="K4" s="34" t="s">
+      <c r="K4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="31"/>
-      <c r="M4" s="34" t="s">
+      <c r="M4" s="35" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="31"/>
@@ -3665,19 +3663,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="33"/>
+      <c r="B5" s="34"/>
       <c r="C5" s="31"/>
       <c r="D5" s="31"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="33"/>
+      <c r="G5" s="34"/>
       <c r="H5" s="31"/>
       <c r="I5" s="31"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="33"/>
+      <c r="L5" s="34"/>
       <c r="M5" s="31"/>
       <c r="N5" s="31"/>
     </row>
@@ -3685,19 +3683,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="32"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="31"/>
       <c r="D6" s="31"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="32"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="31"/>
       <c r="I6" s="31"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="32"/>
+      <c r="L6" s="33"/>
       <c r="M6" s="31"/>
       <c r="N6" s="31"/>
     </row>
@@ -3705,19 +3703,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="33"/>
+      <c r="B7" s="34"/>
       <c r="C7" s="31"/>
       <c r="D7" s="31"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="33"/>
+      <c r="G7" s="34"/>
       <c r="H7" s="31"/>
       <c r="I7" s="31"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="33"/>
+      <c r="L7" s="34"/>
       <c r="M7" s="31"/>
       <c r="N7" s="31"/>
     </row>
@@ -3725,19 +3723,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="32"/>
+      <c r="B8" s="33"/>
       <c r="C8" s="31"/>
       <c r="D8" s="31"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="32"/>
+      <c r="G8" s="33"/>
       <c r="H8" s="31"/>
       <c r="I8" s="31"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="32"/>
+      <c r="L8" s="33"/>
       <c r="M8" s="31"/>
       <c r="N8" s="31"/>
     </row>
@@ -3745,19 +3743,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="33"/>
+      <c r="B9" s="34"/>
       <c r="C9" s="31"/>
       <c r="D9" s="31"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="33"/>
+      <c r="G9" s="34"/>
       <c r="H9" s="31"/>
       <c r="I9" s="31"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="33"/>
+      <c r="L9" s="34"/>
       <c r="M9" s="31"/>
       <c r="N9" s="31"/>
     </row>
@@ -3765,19 +3763,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="32"/>
+      <c r="B10" s="33"/>
       <c r="C10" s="31"/>
       <c r="D10" s="31"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="32"/>
+      <c r="G10" s="33"/>
       <c r="H10" s="31"/>
       <c r="I10" s="31"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="32"/>
+      <c r="L10" s="33"/>
       <c r="M10" s="31"/>
       <c r="N10" s="31"/>
     </row>
@@ -3785,19 +3783,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="33"/>
+      <c r="B11" s="34"/>
       <c r="C11" s="31"/>
       <c r="D11" s="31"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="33"/>
+      <c r="G11" s="34"/>
       <c r="H11" s="31"/>
       <c r="I11" s="31"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="33"/>
+      <c r="L11" s="34"/>
       <c r="M11" s="31"/>
       <c r="N11" s="31"/>
     </row>
@@ -3805,19 +3803,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="32"/>
+      <c r="B12" s="33"/>
       <c r="C12" s="31"/>
       <c r="D12" s="31"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="32"/>
+      <c r="G12" s="33"/>
       <c r="H12" s="31"/>
       <c r="I12" s="31"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="32"/>
+      <c r="L12" s="33"/>
       <c r="M12" s="31"/>
       <c r="N12" s="31"/>
     </row>
@@ -3825,7 +3823,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="35">
+      <c r="B13" s="36">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3834,7 +3832,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="35">
+      <c r="G13" s="36">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3843,7 +3841,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="35">
+      <c r="L13" s="36">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3879,19 +3877,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="36" t="s">
+      <c r="A25" s="32" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="31"/>
       <c r="C25" s="31"/>
       <c r="D25" s="31"/>
-      <c r="F25" s="36" t="s">
+      <c r="F25" s="32" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="31"/>
       <c r="H25" s="31"/>
       <c r="I25" s="31"/>
-      <c r="K25" s="36" t="s">
+      <c r="K25" s="32" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="31"/>
@@ -3899,19 +3897,19 @@
       <c r="N25" s="31"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="36" t="s">
+      <c r="A26" s="32" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="31"/>
       <c r="C26" s="31"/>
       <c r="D26" s="31"/>
-      <c r="F26" s="36" t="s">
+      <c r="F26" s="32" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="31"/>
       <c r="H26" s="31"/>
       <c r="I26" s="31"/>
-      <c r="K26" s="36" t="s">
+      <c r="K26" s="32" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="31"/>
@@ -3933,27 +3931,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="34" t="s">
+      <c r="A28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="31"/>
-      <c r="C28" s="34" t="s">
+      <c r="C28" s="35" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="31"/>
-      <c r="F28" s="34" t="s">
+      <c r="F28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="31"/>
-      <c r="H28" s="34" t="s">
+      <c r="H28" s="35" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="31"/>
-      <c r="K28" s="34" t="s">
+      <c r="K28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="31"/>
-      <c r="M28" s="34" t="s">
+      <c r="M28" s="35" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="31"/>
@@ -3962,19 +3960,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="33"/>
+      <c r="B29" s="34"/>
       <c r="C29" s="31"/>
       <c r="D29" s="31"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="33"/>
+      <c r="G29" s="34"/>
       <c r="H29" s="31"/>
       <c r="I29" s="31"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="33"/>
+      <c r="L29" s="34"/>
       <c r="M29" s="31"/>
       <c r="N29" s="31"/>
     </row>
@@ -3982,19 +3980,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="32"/>
+      <c r="B30" s="33"/>
       <c r="C30" s="31"/>
       <c r="D30" s="31"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="32"/>
+      <c r="G30" s="33"/>
       <c r="H30" s="31"/>
       <c r="I30" s="31"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="32"/>
+      <c r="L30" s="33"/>
       <c r="M30" s="31"/>
       <c r="N30" s="31"/>
     </row>
@@ -4002,19 +4000,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="33"/>
+      <c r="B31" s="34"/>
       <c r="C31" s="31"/>
       <c r="D31" s="31"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="33"/>
+      <c r="G31" s="34"/>
       <c r="H31" s="31"/>
       <c r="I31" s="31"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="33"/>
+      <c r="L31" s="34"/>
       <c r="M31" s="31"/>
       <c r="N31" s="31"/>
     </row>
@@ -4022,19 +4020,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="32"/>
+      <c r="B32" s="33"/>
       <c r="C32" s="31"/>
       <c r="D32" s="31"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="32"/>
+      <c r="G32" s="33"/>
       <c r="H32" s="31"/>
       <c r="I32" s="31"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="32"/>
+      <c r="L32" s="33"/>
       <c r="M32" s="31"/>
       <c r="N32" s="31"/>
     </row>
@@ -4042,19 +4040,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="33"/>
+      <c r="B33" s="34"/>
       <c r="C33" s="31"/>
       <c r="D33" s="31"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="33"/>
+      <c r="G33" s="34"/>
       <c r="H33" s="31"/>
       <c r="I33" s="31"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="33"/>
+      <c r="L33" s="34"/>
       <c r="M33" s="31"/>
       <c r="N33" s="31"/>
     </row>
@@ -4062,19 +4060,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="32"/>
+      <c r="B34" s="33"/>
       <c r="C34" s="31"/>
       <c r="D34" s="31"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="32"/>
+      <c r="G34" s="33"/>
       <c r="H34" s="31"/>
       <c r="I34" s="31"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="32"/>
+      <c r="L34" s="33"/>
       <c r="M34" s="31"/>
       <c r="N34" s="31"/>
     </row>
@@ -4082,19 +4080,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="33"/>
+      <c r="B35" s="34"/>
       <c r="C35" s="31"/>
       <c r="D35" s="31"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="33"/>
+      <c r="G35" s="34"/>
       <c r="H35" s="31"/>
       <c r="I35" s="31"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="33"/>
+      <c r="L35" s="34"/>
       <c r="M35" s="31"/>
       <c r="N35" s="31"/>
     </row>
@@ -4102,19 +4100,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="32"/>
+      <c r="B36" s="33"/>
       <c r="C36" s="31"/>
       <c r="D36" s="31"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="32"/>
+      <c r="G36" s="33"/>
       <c r="H36" s="31"/>
       <c r="I36" s="31"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="32"/>
+      <c r="L36" s="33"/>
       <c r="M36" s="31"/>
       <c r="N36" s="31"/>
     </row>
@@ -4122,7 +4120,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="35">
+      <c r="B37" s="36">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -4131,7 +4129,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="35">
+      <c r="G37" s="36">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -4140,7 +4138,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="35">
+      <c r="L37" s="36">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -4177,6 +4175,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
     <mergeCell ref="L34:N34"/>
     <mergeCell ref="L6:N6"/>
     <mergeCell ref="B33:D33"/>
@@ -4193,68 +4253,6 @@
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82D5B2CE-F80E-4BD8-BD9E-0A6394B89FB7}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2A979E4-0D7C-4301-B687-D2C86E0EE447}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucoes" sheetId="1" r:id="rId1"/>
@@ -446,9 +446,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -459,6 +456,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="B97" s="26">
         <f>SUM(B98:B99)</f>
-        <v>958</v>
+        <v>0</v>
       </c>
       <c r="C97" s="24"/>
       <c r="D97" s="24"/>
@@ -2262,25 +2262,21 @@
       </c>
       <c r="G97" s="26">
         <f>SUM(G98:G99)</f>
-        <v>652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="15">
       <c r="A98" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B98" s="26">
-        <v>958</v>
-      </c>
+      <c r="B98" s="26"/>
       <c r="C98" s="24"/>
       <c r="D98" s="24"/>
       <c r="E98" s="24"/>
       <c r="F98" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G98" s="26">
-        <v>652</v>
-      </c>
+      <c r="G98" s="26"/>
     </row>
     <row r="99" spans="1:7" ht="15">
       <c r="A99" s="7" t="s">
@@ -2401,7 +2397,7 @@
       </c>
       <c r="G106" s="25">
         <f>SUM(G107:G108)</f>
-        <v>374</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="15">
@@ -2415,9 +2411,7 @@
       <c r="F107" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G107" s="25">
-        <v>374</v>
-      </c>
+      <c r="G107" s="25"/>
     </row>
     <row r="108" spans="1:7" ht="15">
       <c r="A108" s="9" t="s">
@@ -2800,7 +2794,7 @@
       </c>
       <c r="B133" s="28">
         <f>SUM(B97,B100,B103,B106,B109,B112,B115,B118,B121,B124,B127,B130)</f>
-        <v>958</v>
+        <v>0</v>
       </c>
       <c r="C133" s="24"/>
       <c r="D133" s="24"/>
@@ -2810,7 +2804,7 @@
       </c>
       <c r="G133" s="28">
         <f>SUM(G97,G100,G103,G106,G109,G112,G115,G118,G121,G124,G127,G130)</f>
-        <v>1026</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2832,19 +2826,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="36" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="31"/>
       <c r="C1" s="31"/>
       <c r="D1" s="31"/>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="36" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="31"/>
       <c r="H1" s="31"/>
       <c r="I1" s="31"/>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="36" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="31"/>
@@ -2852,19 +2846,19 @@
       <c r="N1" s="31"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="36" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
       <c r="D2" s="31"/>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="36" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="31"/>
       <c r="H2" s="31"/>
       <c r="I2" s="31"/>
-      <c r="K2" s="32" t="s">
+      <c r="K2" s="36" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="31"/>
@@ -2886,27 +2880,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="34" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="31"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="34" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="31"/>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="34" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="31"/>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="34" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="31"/>
-      <c r="K4" s="35" t="s">
+      <c r="K4" s="34" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="31"/>
-      <c r="M4" s="35" t="s">
+      <c r="M4" s="34" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="31"/>
@@ -2915,21 +2909,21 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="34">
-        <v>0</v>
-      </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
+      <c r="B5" s="33">
+        <v>0</v>
+      </c>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="34"/>
+      <c r="G5" s="33"/>
       <c r="H5" s="31"/>
       <c r="I5" s="31"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="34"/>
+      <c r="L5" s="33"/>
       <c r="M5" s="31"/>
       <c r="N5" s="31"/>
     </row>
@@ -2937,21 +2931,21 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="33">
-        <v>0</v>
-      </c>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
+      <c r="B6" s="32">
+        <v>0</v>
+      </c>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="33"/>
+      <c r="G6" s="32"/>
       <c r="H6" s="31"/>
       <c r="I6" s="31"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="33"/>
+      <c r="L6" s="32"/>
       <c r="M6" s="31"/>
       <c r="N6" s="31"/>
     </row>
@@ -2959,21 +2953,21 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="34">
-        <v>0</v>
-      </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
+      <c r="B7" s="33">
+        <v>0</v>
+      </c>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="34"/>
+      <c r="G7" s="33"/>
       <c r="H7" s="31"/>
       <c r="I7" s="31"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="34"/>
+      <c r="L7" s="33"/>
       <c r="M7" s="31"/>
       <c r="N7" s="31"/>
     </row>
@@ -2981,21 +2975,21 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="33">
-        <v>0</v>
-      </c>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
+      <c r="B8" s="32">
+        <v>0</v>
+      </c>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="33"/>
+      <c r="G8" s="32"/>
       <c r="H8" s="31"/>
       <c r="I8" s="31"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="33"/>
+      <c r="L8" s="32"/>
       <c r="M8" s="31"/>
       <c r="N8" s="31"/>
     </row>
@@ -3003,21 +2997,21 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="34">
-        <v>0</v>
-      </c>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
+      <c r="B9" s="33">
+        <v>0</v>
+      </c>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="34"/>
+      <c r="G9" s="33"/>
       <c r="H9" s="31"/>
       <c r="I9" s="31"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="34"/>
+      <c r="L9" s="33"/>
       <c r="M9" s="31"/>
       <c r="N9" s="31"/>
     </row>
@@ -3025,21 +3019,21 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="33">
-        <v>0</v>
-      </c>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
+      <c r="B10" s="32">
+        <v>0</v>
+      </c>
+      <c r="C10" s="32"/>
+      <c r="D10" s="32"/>
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="33"/>
+      <c r="G10" s="32"/>
       <c r="H10" s="31"/>
       <c r="I10" s="31"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="33"/>
+      <c r="L10" s="32"/>
       <c r="M10" s="31"/>
       <c r="N10" s="31"/>
     </row>
@@ -3047,7 +3041,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="36">
+      <c r="B11" s="35">
         <f>SUM(B5:B10)</f>
         <v>0</v>
       </c>
@@ -3056,7 +3050,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="36">
+      <c r="G11" s="35">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -3065,7 +3059,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="36">
+      <c r="L11" s="35">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -3101,19 +3095,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="32" t="s">
+      <c r="A25" s="36" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="31"/>
       <c r="C25" s="31"/>
       <c r="D25" s="31"/>
-      <c r="F25" s="32" t="s">
+      <c r="F25" s="36" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="31"/>
       <c r="H25" s="31"/>
       <c r="I25" s="31"/>
-      <c r="K25" s="32" t="s">
+      <c r="K25" s="36" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="31"/>
@@ -3121,19 +3115,19 @@
       <c r="N25" s="31"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="32" t="s">
+      <c r="A26" s="36" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="31"/>
       <c r="C26" s="31"/>
       <c r="D26" s="31"/>
-      <c r="F26" s="32" t="s">
+      <c r="F26" s="36" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="31"/>
       <c r="H26" s="31"/>
       <c r="I26" s="31"/>
-      <c r="K26" s="32" t="s">
+      <c r="K26" s="36" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="31"/>
@@ -3155,27 +3149,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="35" t="s">
+      <c r="A28" s="34" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="31"/>
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="34" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="31"/>
-      <c r="F28" s="35" t="s">
+      <c r="F28" s="34" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="31"/>
-      <c r="H28" s="35" t="s">
+      <c r="H28" s="34" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="31"/>
-      <c r="K28" s="35" t="s">
+      <c r="K28" s="34" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="31"/>
-      <c r="M28" s="35" t="s">
+      <c r="M28" s="34" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="31"/>
@@ -3184,7 +3178,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="34">
+      <c r="B29" s="33">
         <v>0</v>
       </c>
       <c r="C29" s="31"/>
@@ -3192,23 +3186,23 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="34"/>
+      <c r="G29" s="33"/>
       <c r="H29" s="31"/>
       <c r="I29" s="31"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="34">
-        <v>0</v>
-      </c>
-      <c r="M29" s="34"/>
-      <c r="N29" s="34"/>
+      <c r="L29" s="33">
+        <v>0</v>
+      </c>
+      <c r="M29" s="33"/>
+      <c r="N29" s="33"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="33">
+      <c r="B30" s="32">
         <v>0</v>
       </c>
       <c r="C30" s="31"/>
@@ -3216,23 +3210,23 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="33"/>
+      <c r="G30" s="32"/>
       <c r="H30" s="31"/>
       <c r="I30" s="31"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="33">
-        <v>0</v>
-      </c>
-      <c r="M30" s="33"/>
-      <c r="N30" s="33"/>
+      <c r="L30" s="32">
+        <v>0</v>
+      </c>
+      <c r="M30" s="32"/>
+      <c r="N30" s="32"/>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1">
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="34">
+      <c r="B31" s="33">
         <v>0</v>
       </c>
       <c r="C31" s="31"/>
@@ -3240,23 +3234,23 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="34"/>
+      <c r="G31" s="33"/>
       <c r="H31" s="31"/>
       <c r="I31" s="31"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="34">
-        <v>0</v>
-      </c>
-      <c r="M31" s="34"/>
-      <c r="N31" s="34"/>
+      <c r="L31" s="33">
+        <v>0</v>
+      </c>
+      <c r="M31" s="33"/>
+      <c r="N31" s="33"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="33">
+      <c r="B32" s="32">
         <v>0</v>
       </c>
       <c r="C32" s="31"/>
@@ -3264,23 +3258,23 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="33"/>
+      <c r="G32" s="32"/>
       <c r="H32" s="31"/>
       <c r="I32" s="31"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="33">
-        <v>0</v>
-      </c>
-      <c r="M32" s="33"/>
-      <c r="N32" s="33"/>
+      <c r="L32" s="32">
+        <v>0</v>
+      </c>
+      <c r="M32" s="32"/>
+      <c r="N32" s="32"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="34">
+      <c r="B33" s="33">
         <v>0</v>
       </c>
       <c r="C33" s="31"/>
@@ -3288,23 +3282,23 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="34"/>
+      <c r="G33" s="33"/>
       <c r="H33" s="31"/>
       <c r="I33" s="31"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="34">
-        <v>0</v>
-      </c>
-      <c r="M33" s="34"/>
-      <c r="N33" s="34"/>
+      <c r="L33" s="33">
+        <v>0</v>
+      </c>
+      <c r="M33" s="33"/>
+      <c r="N33" s="33"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="33">
+      <c r="B34" s="32">
         <v>0</v>
       </c>
       <c r="C34" s="31"/>
@@ -3312,13 +3306,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="33"/>
+      <c r="G34" s="32"/>
       <c r="H34" s="31"/>
       <c r="I34" s="31"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="33">
+      <c r="L34" s="32">
         <v>0</v>
       </c>
       <c r="M34" s="31"/>
@@ -3328,7 +3322,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="36">
+      <c r="B35" s="35">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -3337,7 +3331,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="36">
+      <c r="G35" s="35">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -3346,7 +3340,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="36">
+      <c r="L35" s="35">
         <f>SUM(L29:L34)</f>
         <v>0</v>
       </c>
@@ -3383,6 +3377,56 @@
     </row>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B10:D10"/>
@@ -3399,56 +3443,6 @@
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="H28:I28"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3464,7 +3458,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="36" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="31"/>
@@ -3472,7 +3466,7 @@
       <c r="D1" s="31"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="36" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="31"/>
@@ -3486,11 +3480,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="34" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="31"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="34" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="31"/>
@@ -3499,7 +3493,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="34"/>
+      <c r="B5" s="33"/>
       <c r="C5" s="31"/>
       <c r="D5" s="31"/>
     </row>
@@ -3507,7 +3501,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="33"/>
+      <c r="B6" s="32"/>
       <c r="C6" s="31"/>
       <c r="D6" s="31"/>
     </row>
@@ -3515,7 +3509,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="34"/>
+      <c r="B7" s="33"/>
       <c r="C7" s="31"/>
       <c r="D7" s="31"/>
     </row>
@@ -3523,7 +3517,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="33"/>
+      <c r="B8" s="32"/>
       <c r="C8" s="31"/>
       <c r="D8" s="31"/>
     </row>
@@ -3531,7 +3525,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="36">
+      <c r="B9" s="35">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -3580,19 +3574,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="36" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="31"/>
       <c r="C1" s="31"/>
       <c r="D1" s="31"/>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="36" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="31"/>
       <c r="H1" s="31"/>
       <c r="I1" s="31"/>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="36" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="31"/>
@@ -3600,19 +3594,19 @@
       <c r="N1" s="31"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="36" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
       <c r="D2" s="31"/>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="36" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="31"/>
       <c r="H2" s="31"/>
       <c r="I2" s="31"/>
-      <c r="K2" s="32" t="s">
+      <c r="K2" s="36" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="31"/>
@@ -3634,27 +3628,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="34" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="31"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="34" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="31"/>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="34" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="31"/>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="34" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="31"/>
-      <c r="K4" s="35" t="s">
+      <c r="K4" s="34" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="31"/>
-      <c r="M4" s="35" t="s">
+      <c r="M4" s="34" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="31"/>
@@ -3663,19 +3657,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="34"/>
+      <c r="B5" s="33"/>
       <c r="C5" s="31"/>
       <c r="D5" s="31"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="34"/>
+      <c r="G5" s="33"/>
       <c r="H5" s="31"/>
       <c r="I5" s="31"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="34"/>
+      <c r="L5" s="33"/>
       <c r="M5" s="31"/>
       <c r="N5" s="31"/>
     </row>
@@ -3683,19 +3677,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="33"/>
+      <c r="B6" s="32"/>
       <c r="C6" s="31"/>
       <c r="D6" s="31"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="33"/>
+      <c r="G6" s="32"/>
       <c r="H6" s="31"/>
       <c r="I6" s="31"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="33"/>
+      <c r="L6" s="32"/>
       <c r="M6" s="31"/>
       <c r="N6" s="31"/>
     </row>
@@ -3703,19 +3697,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="34"/>
+      <c r="B7" s="33"/>
       <c r="C7" s="31"/>
       <c r="D7" s="31"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="34"/>
+      <c r="G7" s="33"/>
       <c r="H7" s="31"/>
       <c r="I7" s="31"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="34"/>
+      <c r="L7" s="33"/>
       <c r="M7" s="31"/>
       <c r="N7" s="31"/>
     </row>
@@ -3723,19 +3717,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="33"/>
+      <c r="B8" s="32"/>
       <c r="C8" s="31"/>
       <c r="D8" s="31"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="33"/>
+      <c r="G8" s="32"/>
       <c r="H8" s="31"/>
       <c r="I8" s="31"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="33"/>
+      <c r="L8" s="32"/>
       <c r="M8" s="31"/>
       <c r="N8" s="31"/>
     </row>
@@ -3743,19 +3737,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="34"/>
+      <c r="B9" s="33"/>
       <c r="C9" s="31"/>
       <c r="D9" s="31"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="34"/>
+      <c r="G9" s="33"/>
       <c r="H9" s="31"/>
       <c r="I9" s="31"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="34"/>
+      <c r="L9" s="33"/>
       <c r="M9" s="31"/>
       <c r="N9" s="31"/>
     </row>
@@ -3763,19 +3757,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="33"/>
+      <c r="B10" s="32"/>
       <c r="C10" s="31"/>
       <c r="D10" s="31"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="33"/>
+      <c r="G10" s="32"/>
       <c r="H10" s="31"/>
       <c r="I10" s="31"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="33"/>
+      <c r="L10" s="32"/>
       <c r="M10" s="31"/>
       <c r="N10" s="31"/>
     </row>
@@ -3783,19 +3777,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="34"/>
+      <c r="B11" s="33"/>
       <c r="C11" s="31"/>
       <c r="D11" s="31"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="34"/>
+      <c r="G11" s="33"/>
       <c r="H11" s="31"/>
       <c r="I11" s="31"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="34"/>
+      <c r="L11" s="33"/>
       <c r="M11" s="31"/>
       <c r="N11" s="31"/>
     </row>
@@ -3803,19 +3797,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="33"/>
+      <c r="B12" s="32"/>
       <c r="C12" s="31"/>
       <c r="D12" s="31"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="33"/>
+      <c r="G12" s="32"/>
       <c r="H12" s="31"/>
       <c r="I12" s="31"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="33"/>
+      <c r="L12" s="32"/>
       <c r="M12" s="31"/>
       <c r="N12" s="31"/>
     </row>
@@ -3823,7 +3817,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="36">
+      <c r="B13" s="35">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3832,7 +3826,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="36">
+      <c r="G13" s="35">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3841,7 +3835,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="36">
+      <c r="L13" s="35">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3877,19 +3871,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="32" t="s">
+      <c r="A25" s="36" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="31"/>
       <c r="C25" s="31"/>
       <c r="D25" s="31"/>
-      <c r="F25" s="32" t="s">
+      <c r="F25" s="36" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="31"/>
       <c r="H25" s="31"/>
       <c r="I25" s="31"/>
-      <c r="K25" s="32" t="s">
+      <c r="K25" s="36" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="31"/>
@@ -3897,19 +3891,19 @@
       <c r="N25" s="31"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="32" t="s">
+      <c r="A26" s="36" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="31"/>
       <c r="C26" s="31"/>
       <c r="D26" s="31"/>
-      <c r="F26" s="32" t="s">
+      <c r="F26" s="36" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="31"/>
       <c r="H26" s="31"/>
       <c r="I26" s="31"/>
-      <c r="K26" s="32" t="s">
+      <c r="K26" s="36" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="31"/>
@@ -3931,27 +3925,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="35" t="s">
+      <c r="A28" s="34" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="31"/>
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="34" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="31"/>
-      <c r="F28" s="35" t="s">
+      <c r="F28" s="34" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="31"/>
-      <c r="H28" s="35" t="s">
+      <c r="H28" s="34" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="31"/>
-      <c r="K28" s="35" t="s">
+      <c r="K28" s="34" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="31"/>
-      <c r="M28" s="35" t="s">
+      <c r="M28" s="34" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="31"/>
@@ -3960,19 +3954,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="34"/>
+      <c r="B29" s="33"/>
       <c r="C29" s="31"/>
       <c r="D29" s="31"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="34"/>
+      <c r="G29" s="33"/>
       <c r="H29" s="31"/>
       <c r="I29" s="31"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="34"/>
+      <c r="L29" s="33"/>
       <c r="M29" s="31"/>
       <c r="N29" s="31"/>
     </row>
@@ -3980,19 +3974,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="33"/>
+      <c r="B30" s="32"/>
       <c r="C30" s="31"/>
       <c r="D30" s="31"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="33"/>
+      <c r="G30" s="32"/>
       <c r="H30" s="31"/>
       <c r="I30" s="31"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="33"/>
+      <c r="L30" s="32"/>
       <c r="M30" s="31"/>
       <c r="N30" s="31"/>
     </row>
@@ -4000,19 +3994,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="34"/>
+      <c r="B31" s="33"/>
       <c r="C31" s="31"/>
       <c r="D31" s="31"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="34"/>
+      <c r="G31" s="33"/>
       <c r="H31" s="31"/>
       <c r="I31" s="31"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="34"/>
+      <c r="L31" s="33"/>
       <c r="M31" s="31"/>
       <c r="N31" s="31"/>
     </row>
@@ -4020,19 +4014,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="33"/>
+      <c r="B32" s="32"/>
       <c r="C32" s="31"/>
       <c r="D32" s="31"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="33"/>
+      <c r="G32" s="32"/>
       <c r="H32" s="31"/>
       <c r="I32" s="31"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="33"/>
+      <c r="L32" s="32"/>
       <c r="M32" s="31"/>
       <c r="N32" s="31"/>
     </row>
@@ -4040,19 +4034,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="34"/>
+      <c r="B33" s="33"/>
       <c r="C33" s="31"/>
       <c r="D33" s="31"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="34"/>
+      <c r="G33" s="33"/>
       <c r="H33" s="31"/>
       <c r="I33" s="31"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="34"/>
+      <c r="L33" s="33"/>
       <c r="M33" s="31"/>
       <c r="N33" s="31"/>
     </row>
@@ -4060,19 +4054,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="33"/>
+      <c r="B34" s="32"/>
       <c r="C34" s="31"/>
       <c r="D34" s="31"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="33"/>
+      <c r="G34" s="32"/>
       <c r="H34" s="31"/>
       <c r="I34" s="31"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="33"/>
+      <c r="L34" s="32"/>
       <c r="M34" s="31"/>
       <c r="N34" s="31"/>
     </row>
@@ -4080,19 +4074,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="34"/>
+      <c r="B35" s="33"/>
       <c r="C35" s="31"/>
       <c r="D35" s="31"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="34"/>
+      <c r="G35" s="33"/>
       <c r="H35" s="31"/>
       <c r="I35" s="31"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="34"/>
+      <c r="L35" s="33"/>
       <c r="M35" s="31"/>
       <c r="N35" s="31"/>
     </row>
@@ -4100,19 +4094,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="33"/>
+      <c r="B36" s="32"/>
       <c r="C36" s="31"/>
       <c r="D36" s="31"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="33"/>
+      <c r="G36" s="32"/>
       <c r="H36" s="31"/>
       <c r="I36" s="31"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="33"/>
+      <c r="L36" s="32"/>
       <c r="M36" s="31"/>
       <c r="N36" s="31"/>
     </row>
@@ -4120,7 +4114,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="36">
+      <c r="B37" s="35">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -4129,7 +4123,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="36">
+      <c r="G37" s="35">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -4138,7 +4132,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="36">
+      <c r="L37" s="35">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -4175,6 +4169,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
     <mergeCell ref="G36:I36"/>
     <mergeCell ref="L32:N32"/>
     <mergeCell ref="L13:N13"/>
@@ -4191,68 +4247,6 @@
     <mergeCell ref="L33:N33"/>
     <mergeCell ref="L35:N35"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="L9:N9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4300,7 +4294,7 @@
         <v>49</v>
       </c>
       <c r="E2" s="18">
-        <v>135</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4334,7 +4328,7 @@
         <v>49</v>
       </c>
       <c r="E4" s="18">
-        <v>135</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4368,7 +4362,7 @@
         <v>49</v>
       </c>
       <c r="E6" s="18">
-        <v>135</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4904,7 +4898,7 @@
         <v>49</v>
       </c>
       <c r="E38" s="18">
-        <v>110</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -4921,7 +4915,7 @@
         <v>68</v>
       </c>
       <c r="E39" s="18">
-        <v>110</v>
+        <v>70</v>
       </c>
     </row>
     <row r="40" spans="1:5">

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2A979E4-0D7C-4301-B687-D2C86E0EE447}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B7FEC42-B334-4821-84A7-A16DE2818772}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucoes" sheetId="1" r:id="rId1"/>
@@ -446,6 +446,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -456,9 +459,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="B62" s="15">
         <f>SUM(B63:B64)</f>
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="F62" s="9" t="s">
         <v>25</v>
@@ -1702,9 +1702,7 @@
       <c r="A63" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B63" s="15">
-        <v>23</v>
-      </c>
+      <c r="B63" s="15"/>
       <c r="F63" s="9" t="s">
         <v>21</v>
       </c>
@@ -1836,7 +1834,7 @@
       </c>
       <c r="B71" s="14">
         <f>SUM(B72:B73)</f>
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="F71" s="7" t="s">
         <v>28</v>
@@ -1857,9 +1855,7 @@
       <c r="A72" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B72" s="14">
-        <v>250</v>
-      </c>
+      <c r="B72" s="14"/>
       <c r="F72" s="7" t="s">
         <v>21</v>
       </c>
@@ -2146,7 +2142,7 @@
       </c>
       <c r="B89" s="13">
         <f>SUM(B53,B56,B59,B62,B65,B68,B71,B74,B77,B80,B83,B86)</f>
-        <v>273</v>
+        <v>0</v>
       </c>
       <c r="F89" s="8" t="s">
         <v>34</v>
@@ -2826,19 +2822,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="32" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="31"/>
       <c r="C1" s="31"/>
       <c r="D1" s="31"/>
-      <c r="F1" s="36" t="s">
+      <c r="F1" s="32" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="31"/>
       <c r="H1" s="31"/>
       <c r="I1" s="31"/>
-      <c r="K1" s="36" t="s">
+      <c r="K1" s="32" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="31"/>
@@ -2846,19 +2842,19 @@
       <c r="N1" s="31"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="32" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
       <c r="D2" s="31"/>
-      <c r="F2" s="36" t="s">
+      <c r="F2" s="32" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="31"/>
       <c r="H2" s="31"/>
       <c r="I2" s="31"/>
-      <c r="K2" s="36" t="s">
+      <c r="K2" s="32" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="31"/>
@@ -2880,27 +2876,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="31"/>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="35" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="31"/>
-      <c r="F4" s="34" t="s">
+      <c r="F4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="31"/>
-      <c r="H4" s="34" t="s">
+      <c r="H4" s="35" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="31"/>
-      <c r="K4" s="34" t="s">
+      <c r="K4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="31"/>
-      <c r="M4" s="34" t="s">
+      <c r="M4" s="35" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="31"/>
@@ -2909,21 +2905,21 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="33">
-        <v>0</v>
-      </c>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
+      <c r="B5" s="34">
+        <v>0</v>
+      </c>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="33"/>
+      <c r="G5" s="34"/>
       <c r="H5" s="31"/>
       <c r="I5" s="31"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="33"/>
+      <c r="L5" s="34"/>
       <c r="M5" s="31"/>
       <c r="N5" s="31"/>
     </row>
@@ -2931,21 +2927,21 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="32">
-        <v>0</v>
-      </c>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
+      <c r="B6" s="33">
+        <v>0</v>
+      </c>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="32"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="31"/>
       <c r="I6" s="31"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="32"/>
+      <c r="L6" s="33"/>
       <c r="M6" s="31"/>
       <c r="N6" s="31"/>
     </row>
@@ -2953,21 +2949,21 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="33">
-        <v>0</v>
-      </c>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
+      <c r="B7" s="34">
+        <v>0</v>
+      </c>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="33"/>
+      <c r="G7" s="34"/>
       <c r="H7" s="31"/>
       <c r="I7" s="31"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="33"/>
+      <c r="L7" s="34"/>
       <c r="M7" s="31"/>
       <c r="N7" s="31"/>
     </row>
@@ -2975,21 +2971,21 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="32">
-        <v>0</v>
-      </c>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
+      <c r="B8" s="33">
+        <v>0</v>
+      </c>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="32"/>
+      <c r="G8" s="33"/>
       <c r="H8" s="31"/>
       <c r="I8" s="31"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="32"/>
+      <c r="L8" s="33"/>
       <c r="M8" s="31"/>
       <c r="N8" s="31"/>
     </row>
@@ -2997,21 +2993,21 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="33">
-        <v>0</v>
-      </c>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
+      <c r="B9" s="34">
+        <v>0</v>
+      </c>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="33"/>
+      <c r="G9" s="34"/>
       <c r="H9" s="31"/>
       <c r="I9" s="31"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="33"/>
+      <c r="L9" s="34"/>
       <c r="M9" s="31"/>
       <c r="N9" s="31"/>
     </row>
@@ -3019,21 +3015,21 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="32">
-        <v>0</v>
-      </c>
-      <c r="C10" s="32"/>
-      <c r="D10" s="32"/>
+      <c r="B10" s="33">
+        <v>0</v>
+      </c>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="32"/>
+      <c r="G10" s="33"/>
       <c r="H10" s="31"/>
       <c r="I10" s="31"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="32"/>
+      <c r="L10" s="33"/>
       <c r="M10" s="31"/>
       <c r="N10" s="31"/>
     </row>
@@ -3041,7 +3037,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="35">
+      <c r="B11" s="36">
         <f>SUM(B5:B10)</f>
         <v>0</v>
       </c>
@@ -3050,7 +3046,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="35">
+      <c r="G11" s="36">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -3059,7 +3055,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="35">
+      <c r="L11" s="36">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -3095,19 +3091,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="36" t="s">
+      <c r="A25" s="32" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="31"/>
       <c r="C25" s="31"/>
       <c r="D25" s="31"/>
-      <c r="F25" s="36" t="s">
+      <c r="F25" s="32" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="31"/>
       <c r="H25" s="31"/>
       <c r="I25" s="31"/>
-      <c r="K25" s="36" t="s">
+      <c r="K25" s="32" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="31"/>
@@ -3115,19 +3111,19 @@
       <c r="N25" s="31"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="36" t="s">
+      <c r="A26" s="32" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="31"/>
       <c r="C26" s="31"/>
       <c r="D26" s="31"/>
-      <c r="F26" s="36" t="s">
+      <c r="F26" s="32" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="31"/>
       <c r="H26" s="31"/>
       <c r="I26" s="31"/>
-      <c r="K26" s="36" t="s">
+      <c r="K26" s="32" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="31"/>
@@ -3149,27 +3145,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="34" t="s">
+      <c r="A28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="31"/>
-      <c r="C28" s="34" t="s">
+      <c r="C28" s="35" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="31"/>
-      <c r="F28" s="34" t="s">
+      <c r="F28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="31"/>
-      <c r="H28" s="34" t="s">
+      <c r="H28" s="35" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="31"/>
-      <c r="K28" s="34" t="s">
+      <c r="K28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="31"/>
-      <c r="M28" s="34" t="s">
+      <c r="M28" s="35" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="31"/>
@@ -3178,7 +3174,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="33">
+      <c r="B29" s="34">
         <v>0</v>
       </c>
       <c r="C29" s="31"/>
@@ -3186,23 +3182,23 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="33"/>
+      <c r="G29" s="34"/>
       <c r="H29" s="31"/>
       <c r="I29" s="31"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="33">
-        <v>0</v>
-      </c>
-      <c r="M29" s="33"/>
-      <c r="N29" s="33"/>
+      <c r="L29" s="34">
+        <v>0</v>
+      </c>
+      <c r="M29" s="34"/>
+      <c r="N29" s="34"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="32">
+      <c r="B30" s="33">
         <v>0</v>
       </c>
       <c r="C30" s="31"/>
@@ -3210,23 +3206,23 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="32"/>
+      <c r="G30" s="33"/>
       <c r="H30" s="31"/>
       <c r="I30" s="31"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="32">
-        <v>0</v>
-      </c>
-      <c r="M30" s="32"/>
-      <c r="N30" s="32"/>
+      <c r="L30" s="33">
+        <v>0</v>
+      </c>
+      <c r="M30" s="33"/>
+      <c r="N30" s="33"/>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1">
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="33">
+      <c r="B31" s="34">
         <v>0</v>
       </c>
       <c r="C31" s="31"/>
@@ -3234,23 +3230,23 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="33"/>
+      <c r="G31" s="34"/>
       <c r="H31" s="31"/>
       <c r="I31" s="31"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="33">
-        <v>0</v>
-      </c>
-      <c r="M31" s="33"/>
-      <c r="N31" s="33"/>
+      <c r="L31" s="34">
+        <v>0</v>
+      </c>
+      <c r="M31" s="34"/>
+      <c r="N31" s="34"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="32">
+      <c r="B32" s="33">
         <v>0</v>
       </c>
       <c r="C32" s="31"/>
@@ -3258,23 +3254,23 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="32"/>
+      <c r="G32" s="33"/>
       <c r="H32" s="31"/>
       <c r="I32" s="31"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="32">
-        <v>0</v>
-      </c>
-      <c r="M32" s="32"/>
-      <c r="N32" s="32"/>
+      <c r="L32" s="33">
+        <v>0</v>
+      </c>
+      <c r="M32" s="33"/>
+      <c r="N32" s="33"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="33">
+      <c r="B33" s="34">
         <v>0</v>
       </c>
       <c r="C33" s="31"/>
@@ -3282,23 +3278,23 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="33"/>
+      <c r="G33" s="34"/>
       <c r="H33" s="31"/>
       <c r="I33" s="31"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="33">
-        <v>0</v>
-      </c>
-      <c r="M33" s="33"/>
-      <c r="N33" s="33"/>
+      <c r="L33" s="34">
+        <v>0</v>
+      </c>
+      <c r="M33" s="34"/>
+      <c r="N33" s="34"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="32">
+      <c r="B34" s="33">
         <v>0</v>
       </c>
       <c r="C34" s="31"/>
@@ -3306,13 +3302,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="32"/>
+      <c r="G34" s="33"/>
       <c r="H34" s="31"/>
       <c r="I34" s="31"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="32">
+      <c r="L34" s="33">
         <v>0</v>
       </c>
       <c r="M34" s="31"/>
@@ -3322,7 +3318,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="35">
+      <c r="B35" s="36">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -3331,7 +3327,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="35">
+      <c r="G35" s="36">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -3340,7 +3336,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="35">
+      <c r="L35" s="36">
         <f>SUM(L29:L34)</f>
         <v>0</v>
       </c>
@@ -3377,13 +3373,49 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="L11:N11"/>
@@ -3400,49 +3432,13 @@
     <mergeCell ref="K2:N2"/>
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3458,7 +3454,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="32" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="31"/>
@@ -3466,7 +3462,7 @@
       <c r="D1" s="31"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="32" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="31"/>
@@ -3480,11 +3476,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="35" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="31"/>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="35" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="31"/>
@@ -3493,7 +3489,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="33"/>
+      <c r="B5" s="34"/>
       <c r="C5" s="31"/>
       <c r="D5" s="31"/>
     </row>
@@ -3501,7 +3497,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="32"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="31"/>
       <c r="D6" s="31"/>
     </row>
@@ -3509,7 +3505,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="33"/>
+      <c r="B7" s="34"/>
       <c r="C7" s="31"/>
       <c r="D7" s="31"/>
     </row>
@@ -3517,7 +3513,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="32"/>
+      <c r="B8" s="33"/>
       <c r="C8" s="31"/>
       <c r="D8" s="31"/>
     </row>
@@ -3525,7 +3521,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="35">
+      <c r="B9" s="36">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -3574,19 +3570,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="32" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="31"/>
       <c r="C1" s="31"/>
       <c r="D1" s="31"/>
-      <c r="F1" s="36" t="s">
+      <c r="F1" s="32" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="31"/>
       <c r="H1" s="31"/>
       <c r="I1" s="31"/>
-      <c r="K1" s="36" t="s">
+      <c r="K1" s="32" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="31"/>
@@ -3594,19 +3590,19 @@
       <c r="N1" s="31"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="32" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
       <c r="D2" s="31"/>
-      <c r="F2" s="36" t="s">
+      <c r="F2" s="32" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="31"/>
       <c r="H2" s="31"/>
       <c r="I2" s="31"/>
-      <c r="K2" s="36" t="s">
+      <c r="K2" s="32" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="31"/>
@@ -3628,27 +3624,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="31"/>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="35" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="31"/>
-      <c r="F4" s="34" t="s">
+      <c r="F4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="31"/>
-      <c r="H4" s="34" t="s">
+      <c r="H4" s="35" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="31"/>
-      <c r="K4" s="34" t="s">
+      <c r="K4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="31"/>
-      <c r="M4" s="34" t="s">
+      <c r="M4" s="35" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="31"/>
@@ -3657,19 +3653,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="33"/>
+      <c r="B5" s="34"/>
       <c r="C5" s="31"/>
       <c r="D5" s="31"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="33"/>
+      <c r="G5" s="34"/>
       <c r="H5" s="31"/>
       <c r="I5" s="31"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="33"/>
+      <c r="L5" s="34"/>
       <c r="M5" s="31"/>
       <c r="N5" s="31"/>
     </row>
@@ -3677,19 +3673,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="32"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="31"/>
       <c r="D6" s="31"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="32"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="31"/>
       <c r="I6" s="31"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="32"/>
+      <c r="L6" s="33"/>
       <c r="M6" s="31"/>
       <c r="N6" s="31"/>
     </row>
@@ -3697,19 +3693,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="33"/>
+      <c r="B7" s="34"/>
       <c r="C7" s="31"/>
       <c r="D7" s="31"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="33"/>
+      <c r="G7" s="34"/>
       <c r="H7" s="31"/>
       <c r="I7" s="31"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="33"/>
+      <c r="L7" s="34"/>
       <c r="M7" s="31"/>
       <c r="N7" s="31"/>
     </row>
@@ -3717,19 +3713,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="32"/>
+      <c r="B8" s="33"/>
       <c r="C8" s="31"/>
       <c r="D8" s="31"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="32"/>
+      <c r="G8" s="33"/>
       <c r="H8" s="31"/>
       <c r="I8" s="31"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="32"/>
+      <c r="L8" s="33"/>
       <c r="M8" s="31"/>
       <c r="N8" s="31"/>
     </row>
@@ -3737,19 +3733,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="33"/>
+      <c r="B9" s="34"/>
       <c r="C9" s="31"/>
       <c r="D9" s="31"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="33"/>
+      <c r="G9" s="34"/>
       <c r="H9" s="31"/>
       <c r="I9" s="31"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="33"/>
+      <c r="L9" s="34"/>
       <c r="M9" s="31"/>
       <c r="N9" s="31"/>
     </row>
@@ -3757,19 +3753,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="32"/>
+      <c r="B10" s="33"/>
       <c r="C10" s="31"/>
       <c r="D10" s="31"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="32"/>
+      <c r="G10" s="33"/>
       <c r="H10" s="31"/>
       <c r="I10" s="31"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="32"/>
+      <c r="L10" s="33"/>
       <c r="M10" s="31"/>
       <c r="N10" s="31"/>
     </row>
@@ -3777,19 +3773,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="33"/>
+      <c r="B11" s="34"/>
       <c r="C11" s="31"/>
       <c r="D11" s="31"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="33"/>
+      <c r="G11" s="34"/>
       <c r="H11" s="31"/>
       <c r="I11" s="31"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="33"/>
+      <c r="L11" s="34"/>
       <c r="M11" s="31"/>
       <c r="N11" s="31"/>
     </row>
@@ -3797,19 +3793,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="32"/>
+      <c r="B12" s="33"/>
       <c r="C12" s="31"/>
       <c r="D12" s="31"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="32"/>
+      <c r="G12" s="33"/>
       <c r="H12" s="31"/>
       <c r="I12" s="31"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="32"/>
+      <c r="L12" s="33"/>
       <c r="M12" s="31"/>
       <c r="N12" s="31"/>
     </row>
@@ -3817,7 +3813,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="35">
+      <c r="B13" s="36">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3826,7 +3822,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="35">
+      <c r="G13" s="36">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3835,7 +3831,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="35">
+      <c r="L13" s="36">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3871,19 +3867,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="36" t="s">
+      <c r="A25" s="32" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="31"/>
       <c r="C25" s="31"/>
       <c r="D25" s="31"/>
-      <c r="F25" s="36" t="s">
+      <c r="F25" s="32" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="31"/>
       <c r="H25" s="31"/>
       <c r="I25" s="31"/>
-      <c r="K25" s="36" t="s">
+      <c r="K25" s="32" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="31"/>
@@ -3891,19 +3887,19 @@
       <c r="N25" s="31"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="36" t="s">
+      <c r="A26" s="32" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="31"/>
       <c r="C26" s="31"/>
       <c r="D26" s="31"/>
-      <c r="F26" s="36" t="s">
+      <c r="F26" s="32" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="31"/>
       <c r="H26" s="31"/>
       <c r="I26" s="31"/>
-      <c r="K26" s="36" t="s">
+      <c r="K26" s="32" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="31"/>
@@ -3925,27 +3921,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="34" t="s">
+      <c r="A28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="31"/>
-      <c r="C28" s="34" t="s">
+      <c r="C28" s="35" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="31"/>
-      <c r="F28" s="34" t="s">
+      <c r="F28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="31"/>
-      <c r="H28" s="34" t="s">
+      <c r="H28" s="35" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="31"/>
-      <c r="K28" s="34" t="s">
+      <c r="K28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="31"/>
-      <c r="M28" s="34" t="s">
+      <c r="M28" s="35" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="31"/>
@@ -3954,19 +3950,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="33"/>
+      <c r="B29" s="34"/>
       <c r="C29" s="31"/>
       <c r="D29" s="31"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="33"/>
+      <c r="G29" s="34"/>
       <c r="H29" s="31"/>
       <c r="I29" s="31"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="33"/>
+      <c r="L29" s="34"/>
       <c r="M29" s="31"/>
       <c r="N29" s="31"/>
     </row>
@@ -3974,19 +3970,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="32"/>
+      <c r="B30" s="33"/>
       <c r="C30" s="31"/>
       <c r="D30" s="31"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="32"/>
+      <c r="G30" s="33"/>
       <c r="H30" s="31"/>
       <c r="I30" s="31"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="32"/>
+      <c r="L30" s="33"/>
       <c r="M30" s="31"/>
       <c r="N30" s="31"/>
     </row>
@@ -3994,19 +3990,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="33"/>
+      <c r="B31" s="34"/>
       <c r="C31" s="31"/>
       <c r="D31" s="31"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="33"/>
+      <c r="G31" s="34"/>
       <c r="H31" s="31"/>
       <c r="I31" s="31"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="33"/>
+      <c r="L31" s="34"/>
       <c r="M31" s="31"/>
       <c r="N31" s="31"/>
     </row>
@@ -4014,19 +4010,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="32"/>
+      <c r="B32" s="33"/>
       <c r="C32" s="31"/>
       <c r="D32" s="31"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="32"/>
+      <c r="G32" s="33"/>
       <c r="H32" s="31"/>
       <c r="I32" s="31"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="32"/>
+      <c r="L32" s="33"/>
       <c r="M32" s="31"/>
       <c r="N32" s="31"/>
     </row>
@@ -4034,19 +4030,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="33"/>
+      <c r="B33" s="34"/>
       <c r="C33" s="31"/>
       <c r="D33" s="31"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="33"/>
+      <c r="G33" s="34"/>
       <c r="H33" s="31"/>
       <c r="I33" s="31"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="33"/>
+      <c r="L33" s="34"/>
       <c r="M33" s="31"/>
       <c r="N33" s="31"/>
     </row>
@@ -4054,19 +4050,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="32"/>
+      <c r="B34" s="33"/>
       <c r="C34" s="31"/>
       <c r="D34" s="31"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="32"/>
+      <c r="G34" s="33"/>
       <c r="H34" s="31"/>
       <c r="I34" s="31"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="32"/>
+      <c r="L34" s="33"/>
       <c r="M34" s="31"/>
       <c r="N34" s="31"/>
     </row>
@@ -4074,19 +4070,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="33"/>
+      <c r="B35" s="34"/>
       <c r="C35" s="31"/>
       <c r="D35" s="31"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="33"/>
+      <c r="G35" s="34"/>
       <c r="H35" s="31"/>
       <c r="I35" s="31"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="33"/>
+      <c r="L35" s="34"/>
       <c r="M35" s="31"/>
       <c r="N35" s="31"/>
     </row>
@@ -4094,19 +4090,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="32"/>
+      <c r="B36" s="33"/>
       <c r="C36" s="31"/>
       <c r="D36" s="31"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="32"/>
+      <c r="G36" s="33"/>
       <c r="H36" s="31"/>
       <c r="I36" s="31"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="32"/>
+      <c r="L36" s="33"/>
       <c r="M36" s="31"/>
       <c r="N36" s="31"/>
     </row>
@@ -4114,7 +4110,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="35">
+      <c r="B37" s="36">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -4123,7 +4119,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="35">
+      <c r="G37" s="36">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -4132,7 +4128,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="35">
+      <c r="L37" s="36">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -4169,6 +4165,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
     <mergeCell ref="L34:N34"/>
     <mergeCell ref="L6:N6"/>
     <mergeCell ref="B33:D33"/>
@@ -4185,68 +4243,6 @@
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B7FEC42-B334-4821-84A7-A16DE2818772}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD49081F-C972-446D-84D8-17333AA4BBBC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -446,9 +446,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -459,6 +456,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -786,7 +786,7 @@
       </c>
       <c r="B5" s="21">
         <f>SUM(B6:B7)</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>20</v>
@@ -800,14 +800,16 @@
       </c>
       <c r="L5" s="14">
         <f>SUM(L6:L7)</f>
-        <v>1000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
       <c r="A6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="14"/>
+      <c r="B6" s="14">
+        <v>800</v>
+      </c>
       <c r="F6" s="7" t="s">
         <v>21</v>
       </c>
@@ -816,7 +818,7 @@
         <v>21</v>
       </c>
       <c r="L6" s="14">
-        <v>1000</v>
+        <v>800</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
@@ -831,7 +833,9 @@
       <c r="K7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="L7" s="14"/>
+      <c r="L7" s="14">
+        <v>1200</v>
+      </c>
     </row>
     <row r="8" spans="1:14" ht="15" customHeight="1">
       <c r="A8" s="9" t="s">
@@ -853,7 +857,7 @@
       </c>
       <c r="L8" s="15">
         <f>SUM(L9:L10)</f>
-        <v>300</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1">
@@ -869,7 +873,7 @@
         <v>21</v>
       </c>
       <c r="L9" s="15">
-        <v>300</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
@@ -943,7 +947,7 @@
       </c>
       <c r="B14" s="15">
         <f>SUM(B15:B16)</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>25</v>
@@ -957,14 +961,16 @@
       </c>
       <c r="L14" s="15">
         <f>SUM(L15:L16)</f>
-        <v>600</v>
+        <v>800</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1">
       <c r="A15" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="15"/>
+      <c r="B15" s="15">
+        <v>300</v>
+      </c>
       <c r="F15" s="9" t="s">
         <v>21</v>
       </c>
@@ -973,7 +979,7 @@
         <v>21</v>
       </c>
       <c r="L15" s="15">
-        <v>600</v>
+        <v>800</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1">
@@ -996,7 +1002,7 @@
       </c>
       <c r="B17" s="14">
         <f>SUM(B18:B19)</f>
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>26</v>
@@ -1017,9 +1023,7 @@
       <c r="A18" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="14">
-        <v>36</v>
-      </c>
+      <c r="B18" s="14"/>
       <c r="F18" s="7" t="s">
         <v>21</v>
       </c>
@@ -1049,7 +1053,7 @@
       </c>
       <c r="B20" s="15">
         <f>SUM(B21:B22)</f>
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="F20" s="9" t="s">
         <v>27</v>
@@ -1070,9 +1074,7 @@
       <c r="A21" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="15">
-        <v>170</v>
-      </c>
+      <c r="B21" s="15"/>
       <c r="F21" s="9" t="s">
         <v>21</v>
       </c>
@@ -1109,7 +1111,7 @@
       </c>
       <c r="G23" s="14">
         <f>SUM(G24:G25)</f>
-        <v>650</v>
+        <v>800</v>
       </c>
       <c r="K23" s="7" t="s">
         <v>28</v>
@@ -1142,7 +1144,7 @@
         <v>22</v>
       </c>
       <c r="G25" s="14">
-        <v>650</v>
+        <v>800</v>
       </c>
       <c r="K25" s="7" t="s">
         <v>22</v>
@@ -1155,7 +1157,7 @@
       </c>
       <c r="B26" s="15">
         <f>SUM(B27:B28)</f>
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>29</v>
@@ -1177,7 +1179,7 @@
         <v>21</v>
       </c>
       <c r="B27" s="15">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>21</v>
@@ -1222,7 +1224,7 @@
       </c>
       <c r="L29" s="14">
         <f>SUM(L30:L31)</f>
-        <v>600</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1">
@@ -1238,7 +1240,7 @@
         <v>21</v>
       </c>
       <c r="L30" s="14">
-        <v>600</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1">
@@ -1379,7 +1381,7 @@
       </c>
       <c r="L38" s="23">
         <f>SUM(L39:L40)</f>
-        <v>240</v>
+        <v>200</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="15" customHeight="1">
@@ -1395,7 +1397,7 @@
         <v>21</v>
       </c>
       <c r="L39" s="15">
-        <v>240</v>
+        <v>200</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="15" customHeight="1">
@@ -1418,21 +1420,21 @@
       </c>
       <c r="B41" s="13">
         <f>SUM(B5,B8,B11,B14,B17,B20,B23,B26,B29,B32,B35,B38)</f>
-        <v>406</v>
+        <v>1360</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G41" s="13">
         <f>SUM(G5,G8,G11,G14,G17,G20,G23,G26,G29,G32,G35,G38)</f>
-        <v>650</v>
+        <v>800</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="L41" s="13">
         <f>SUM(L5,L8,L11,L14,L17,L20,L23,L26,L29,L32,L35,L38)</f>
-        <v>2753</v>
+        <v>5913</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1">
@@ -1542,7 +1544,7 @@
       </c>
       <c r="L53" s="14">
         <f>SUM(L54:L55)</f>
-        <v>0</v>
+        <v>900</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="15" customHeight="1">
@@ -1557,7 +1559,9 @@
       <c r="K54" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="L54" s="14"/>
+      <c r="L54" s="14">
+        <v>900</v>
+      </c>
     </row>
     <row r="55" spans="1:14" ht="15" customHeight="1">
       <c r="A55" s="7" t="s">
@@ -2156,7 +2160,7 @@
       </c>
       <c r="L89" s="13">
         <f>SUM(L53,L56,L59,L62,L65,L68,L71,L74,L77,L80,L83,L86)</f>
-        <v>0</v>
+        <v>900</v>
       </c>
     </row>
     <row r="90" spans="1:14" ht="15" customHeight="1">
@@ -2258,7 +2262,7 @@
       </c>
       <c r="G97" s="26">
         <f>SUM(G98:G99)</f>
-        <v>0</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="15">
@@ -2272,7 +2276,9 @@
       <c r="F98" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G98" s="26"/>
+      <c r="G98" s="26">
+        <v>1200</v>
+      </c>
     </row>
     <row r="99" spans="1:7" ht="15">
       <c r="A99" s="7" t="s">
@@ -2800,7 +2806,7 @@
       </c>
       <c r="G133" s="28">
         <f>SUM(G97,G100,G103,G106,G109,G112,G115,G118,G121,G124,G127,G130)</f>
-        <v>0</v>
+        <v>1200</v>
       </c>
     </row>
   </sheetData>
@@ -2822,19 +2828,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="36" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="31"/>
       <c r="C1" s="31"/>
       <c r="D1" s="31"/>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="36" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="31"/>
       <c r="H1" s="31"/>
       <c r="I1" s="31"/>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="36" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="31"/>
@@ -2842,19 +2848,19 @@
       <c r="N1" s="31"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="36" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
       <c r="D2" s="31"/>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="36" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="31"/>
       <c r="H2" s="31"/>
       <c r="I2" s="31"/>
-      <c r="K2" s="32" t="s">
+      <c r="K2" s="36" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="31"/>
@@ -2876,27 +2882,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="34" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="31"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="34" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="31"/>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="34" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="31"/>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="34" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="31"/>
-      <c r="K4" s="35" t="s">
+      <c r="K4" s="34" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="31"/>
-      <c r="M4" s="35" t="s">
+      <c r="M4" s="34" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="31"/>
@@ -2905,21 +2911,21 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="34">
-        <v>0</v>
-      </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
+      <c r="B5" s="33">
+        <v>0</v>
+      </c>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="34"/>
+      <c r="G5" s="33"/>
       <c r="H5" s="31"/>
       <c r="I5" s="31"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="34"/>
+      <c r="L5" s="33"/>
       <c r="M5" s="31"/>
       <c r="N5" s="31"/>
     </row>
@@ -2927,21 +2933,21 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="33">
-        <v>0</v>
-      </c>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
+      <c r="B6" s="32">
+        <v>0</v>
+      </c>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="33"/>
+      <c r="G6" s="32"/>
       <c r="H6" s="31"/>
       <c r="I6" s="31"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="33"/>
+      <c r="L6" s="32"/>
       <c r="M6" s="31"/>
       <c r="N6" s="31"/>
     </row>
@@ -2949,21 +2955,21 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="34">
-        <v>0</v>
-      </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
+      <c r="B7" s="33">
+        <v>0</v>
+      </c>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="34"/>
+      <c r="G7" s="33"/>
       <c r="H7" s="31"/>
       <c r="I7" s="31"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="34"/>
+      <c r="L7" s="33"/>
       <c r="M7" s="31"/>
       <c r="N7" s="31"/>
     </row>
@@ -2971,21 +2977,21 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="33">
-        <v>0</v>
-      </c>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
+      <c r="B8" s="32">
+        <v>0</v>
+      </c>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="33"/>
+      <c r="G8" s="32"/>
       <c r="H8" s="31"/>
       <c r="I8" s="31"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="33"/>
+      <c r="L8" s="32"/>
       <c r="M8" s="31"/>
       <c r="N8" s="31"/>
     </row>
@@ -2993,21 +2999,21 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="34">
-        <v>0</v>
-      </c>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
+      <c r="B9" s="33">
+        <v>0</v>
+      </c>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="34"/>
+      <c r="G9" s="33"/>
       <c r="H9" s="31"/>
       <c r="I9" s="31"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="34"/>
+      <c r="L9" s="33"/>
       <c r="M9" s="31"/>
       <c r="N9" s="31"/>
     </row>
@@ -3015,21 +3021,21 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="33">
-        <v>0</v>
-      </c>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
+      <c r="B10" s="32">
+        <v>0</v>
+      </c>
+      <c r="C10" s="32"/>
+      <c r="D10" s="32"/>
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="33"/>
+      <c r="G10" s="32"/>
       <c r="H10" s="31"/>
       <c r="I10" s="31"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="33"/>
+      <c r="L10" s="32"/>
       <c r="M10" s="31"/>
       <c r="N10" s="31"/>
     </row>
@@ -3037,7 +3043,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="36">
+      <c r="B11" s="35">
         <f>SUM(B5:B10)</f>
         <v>0</v>
       </c>
@@ -3046,7 +3052,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="36">
+      <c r="G11" s="35">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -3055,7 +3061,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="36">
+      <c r="L11" s="35">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -3091,19 +3097,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="32" t="s">
+      <c r="A25" s="36" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="31"/>
       <c r="C25" s="31"/>
       <c r="D25" s="31"/>
-      <c r="F25" s="32" t="s">
+      <c r="F25" s="36" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="31"/>
       <c r="H25" s="31"/>
       <c r="I25" s="31"/>
-      <c r="K25" s="32" t="s">
+      <c r="K25" s="36" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="31"/>
@@ -3111,19 +3117,19 @@
       <c r="N25" s="31"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="32" t="s">
+      <c r="A26" s="36" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="31"/>
       <c r="C26" s="31"/>
       <c r="D26" s="31"/>
-      <c r="F26" s="32" t="s">
+      <c r="F26" s="36" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="31"/>
       <c r="H26" s="31"/>
       <c r="I26" s="31"/>
-      <c r="K26" s="32" t="s">
+      <c r="K26" s="36" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="31"/>
@@ -3145,27 +3151,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="35" t="s">
+      <c r="A28" s="34" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="31"/>
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="34" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="31"/>
-      <c r="F28" s="35" t="s">
+      <c r="F28" s="34" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="31"/>
-      <c r="H28" s="35" t="s">
+      <c r="H28" s="34" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="31"/>
-      <c r="K28" s="35" t="s">
+      <c r="K28" s="34" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="31"/>
-      <c r="M28" s="35" t="s">
+      <c r="M28" s="34" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="31"/>
@@ -3174,7 +3180,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="34">
+      <c r="B29" s="33">
         <v>0</v>
       </c>
       <c r="C29" s="31"/>
@@ -3182,23 +3188,23 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="34"/>
+      <c r="G29" s="33"/>
       <c r="H29" s="31"/>
       <c r="I29" s="31"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="34">
-        <v>0</v>
-      </c>
-      <c r="M29" s="34"/>
-      <c r="N29" s="34"/>
+      <c r="L29" s="33">
+        <v>0</v>
+      </c>
+      <c r="M29" s="33"/>
+      <c r="N29" s="33"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="33">
+      <c r="B30" s="32">
         <v>0</v>
       </c>
       <c r="C30" s="31"/>
@@ -3206,23 +3212,23 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="33"/>
+      <c r="G30" s="32"/>
       <c r="H30" s="31"/>
       <c r="I30" s="31"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="33">
-        <v>0</v>
-      </c>
-      <c r="M30" s="33"/>
-      <c r="N30" s="33"/>
+      <c r="L30" s="32">
+        <v>0</v>
+      </c>
+      <c r="M30" s="32"/>
+      <c r="N30" s="32"/>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1">
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="34">
+      <c r="B31" s="33">
         <v>0</v>
       </c>
       <c r="C31" s="31"/>
@@ -3230,23 +3236,23 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="34"/>
+      <c r="G31" s="33"/>
       <c r="H31" s="31"/>
       <c r="I31" s="31"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="34">
-        <v>0</v>
-      </c>
-      <c r="M31" s="34"/>
-      <c r="N31" s="34"/>
+      <c r="L31" s="33">
+        <v>0</v>
+      </c>
+      <c r="M31" s="33"/>
+      <c r="N31" s="33"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="33">
+      <c r="B32" s="32">
         <v>0</v>
       </c>
       <c r="C32" s="31"/>
@@ -3254,23 +3260,23 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="33"/>
+      <c r="G32" s="32"/>
       <c r="H32" s="31"/>
       <c r="I32" s="31"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="33">
-        <v>0</v>
-      </c>
-      <c r="M32" s="33"/>
-      <c r="N32" s="33"/>
+      <c r="L32" s="32">
+        <v>0</v>
+      </c>
+      <c r="M32" s="32"/>
+      <c r="N32" s="32"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="34">
+      <c r="B33" s="33">
         <v>0</v>
       </c>
       <c r="C33" s="31"/>
@@ -3278,23 +3284,23 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="34"/>
+      <c r="G33" s="33"/>
       <c r="H33" s="31"/>
       <c r="I33" s="31"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="34">
-        <v>0</v>
-      </c>
-      <c r="M33" s="34"/>
-      <c r="N33" s="34"/>
+      <c r="L33" s="33">
+        <v>0</v>
+      </c>
+      <c r="M33" s="33"/>
+      <c r="N33" s="33"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="33">
+      <c r="B34" s="32">
         <v>0</v>
       </c>
       <c r="C34" s="31"/>
@@ -3302,13 +3308,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="33"/>
+      <c r="G34" s="32"/>
       <c r="H34" s="31"/>
       <c r="I34" s="31"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="33">
+      <c r="L34" s="32">
         <v>0</v>
       </c>
       <c r="M34" s="31"/>
@@ -3318,7 +3324,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="36">
+      <c r="B35" s="35">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -3327,7 +3333,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="36">
+      <c r="G35" s="35">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -3336,7 +3342,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="36">
+      <c r="L35" s="35">
         <f>SUM(L29:L34)</f>
         <v>0</v>
       </c>
@@ -3373,6 +3379,56 @@
     </row>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B10:D10"/>
@@ -3389,56 +3445,6 @@
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="H28:I28"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3454,7 +3460,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="36" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="31"/>
@@ -3462,7 +3468,7 @@
       <c r="D1" s="31"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="36" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="31"/>
@@ -3476,11 +3482,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="34" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="31"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="34" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="31"/>
@@ -3489,7 +3495,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="34"/>
+      <c r="B5" s="33"/>
       <c r="C5" s="31"/>
       <c r="D5" s="31"/>
     </row>
@@ -3497,7 +3503,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="33"/>
+      <c r="B6" s="32"/>
       <c r="C6" s="31"/>
       <c r="D6" s="31"/>
     </row>
@@ -3505,7 +3511,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="34"/>
+      <c r="B7" s="33"/>
       <c r="C7" s="31"/>
       <c r="D7" s="31"/>
     </row>
@@ -3513,7 +3519,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="33"/>
+      <c r="B8" s="32"/>
       <c r="C8" s="31"/>
       <c r="D8" s="31"/>
     </row>
@@ -3521,7 +3527,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="36">
+      <c r="B9" s="35">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -3570,19 +3576,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="36" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="31"/>
       <c r="C1" s="31"/>
       <c r="D1" s="31"/>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="36" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="31"/>
       <c r="H1" s="31"/>
       <c r="I1" s="31"/>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="36" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="31"/>
@@ -3590,19 +3596,19 @@
       <c r="N1" s="31"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="36" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
       <c r="D2" s="31"/>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="36" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="31"/>
       <c r="H2" s="31"/>
       <c r="I2" s="31"/>
-      <c r="K2" s="32" t="s">
+      <c r="K2" s="36" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="31"/>
@@ -3624,27 +3630,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="34" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="31"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="34" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="31"/>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="34" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="31"/>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="34" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="31"/>
-      <c r="K4" s="35" t="s">
+      <c r="K4" s="34" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="31"/>
-      <c r="M4" s="35" t="s">
+      <c r="M4" s="34" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="31"/>
@@ -3653,19 +3659,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="34"/>
+      <c r="B5" s="33"/>
       <c r="C5" s="31"/>
       <c r="D5" s="31"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="34"/>
+      <c r="G5" s="33"/>
       <c r="H5" s="31"/>
       <c r="I5" s="31"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="34"/>
+      <c r="L5" s="33"/>
       <c r="M5" s="31"/>
       <c r="N5" s="31"/>
     </row>
@@ -3673,19 +3679,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="33"/>
+      <c r="B6" s="32"/>
       <c r="C6" s="31"/>
       <c r="D6" s="31"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="33"/>
+      <c r="G6" s="32"/>
       <c r="H6" s="31"/>
       <c r="I6" s="31"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="33"/>
+      <c r="L6" s="32"/>
       <c r="M6" s="31"/>
       <c r="N6" s="31"/>
     </row>
@@ -3693,19 +3699,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="34"/>
+      <c r="B7" s="33"/>
       <c r="C7" s="31"/>
       <c r="D7" s="31"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="34"/>
+      <c r="G7" s="33"/>
       <c r="H7" s="31"/>
       <c r="I7" s="31"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="34"/>
+      <c r="L7" s="33"/>
       <c r="M7" s="31"/>
       <c r="N7" s="31"/>
     </row>
@@ -3713,19 +3719,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="33"/>
+      <c r="B8" s="32"/>
       <c r="C8" s="31"/>
       <c r="D8" s="31"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="33"/>
+      <c r="G8" s="32"/>
       <c r="H8" s="31"/>
       <c r="I8" s="31"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="33"/>
+      <c r="L8" s="32"/>
       <c r="M8" s="31"/>
       <c r="N8" s="31"/>
     </row>
@@ -3733,19 +3739,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="34"/>
+      <c r="B9" s="33"/>
       <c r="C9" s="31"/>
       <c r="D9" s="31"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="34"/>
+      <c r="G9" s="33"/>
       <c r="H9" s="31"/>
       <c r="I9" s="31"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="34"/>
+      <c r="L9" s="33"/>
       <c r="M9" s="31"/>
       <c r="N9" s="31"/>
     </row>
@@ -3753,19 +3759,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="33"/>
+      <c r="B10" s="32"/>
       <c r="C10" s="31"/>
       <c r="D10" s="31"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="33"/>
+      <c r="G10" s="32"/>
       <c r="H10" s="31"/>
       <c r="I10" s="31"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="33"/>
+      <c r="L10" s="32"/>
       <c r="M10" s="31"/>
       <c r="N10" s="31"/>
     </row>
@@ -3773,19 +3779,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="34"/>
+      <c r="B11" s="33"/>
       <c r="C11" s="31"/>
       <c r="D11" s="31"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="34"/>
+      <c r="G11" s="33"/>
       <c r="H11" s="31"/>
       <c r="I11" s="31"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="34"/>
+      <c r="L11" s="33"/>
       <c r="M11" s="31"/>
       <c r="N11" s="31"/>
     </row>
@@ -3793,19 +3799,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="33"/>
+      <c r="B12" s="32"/>
       <c r="C12" s="31"/>
       <c r="D12" s="31"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="33"/>
+      <c r="G12" s="32"/>
       <c r="H12" s="31"/>
       <c r="I12" s="31"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="33"/>
+      <c r="L12" s="32"/>
       <c r="M12" s="31"/>
       <c r="N12" s="31"/>
     </row>
@@ -3813,7 +3819,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="36">
+      <c r="B13" s="35">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3822,7 +3828,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="36">
+      <c r="G13" s="35">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3831,7 +3837,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="36">
+      <c r="L13" s="35">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3867,19 +3873,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="32" t="s">
+      <c r="A25" s="36" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="31"/>
       <c r="C25" s="31"/>
       <c r="D25" s="31"/>
-      <c r="F25" s="32" t="s">
+      <c r="F25" s="36" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="31"/>
       <c r="H25" s="31"/>
       <c r="I25" s="31"/>
-      <c r="K25" s="32" t="s">
+      <c r="K25" s="36" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="31"/>
@@ -3887,19 +3893,19 @@
       <c r="N25" s="31"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="32" t="s">
+      <c r="A26" s="36" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="31"/>
       <c r="C26" s="31"/>
       <c r="D26" s="31"/>
-      <c r="F26" s="32" t="s">
+      <c r="F26" s="36" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="31"/>
       <c r="H26" s="31"/>
       <c r="I26" s="31"/>
-      <c r="K26" s="32" t="s">
+      <c r="K26" s="36" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="31"/>
@@ -3921,27 +3927,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="35" t="s">
+      <c r="A28" s="34" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="31"/>
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="34" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="31"/>
-      <c r="F28" s="35" t="s">
+      <c r="F28" s="34" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="31"/>
-      <c r="H28" s="35" t="s">
+      <c r="H28" s="34" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="31"/>
-      <c r="K28" s="35" t="s">
+      <c r="K28" s="34" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="31"/>
-      <c r="M28" s="35" t="s">
+      <c r="M28" s="34" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="31"/>
@@ -3950,19 +3956,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="34"/>
+      <c r="B29" s="33"/>
       <c r="C29" s="31"/>
       <c r="D29" s="31"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="34"/>
+      <c r="G29" s="33"/>
       <c r="H29" s="31"/>
       <c r="I29" s="31"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="34"/>
+      <c r="L29" s="33"/>
       <c r="M29" s="31"/>
       <c r="N29" s="31"/>
     </row>
@@ -3970,19 +3976,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="33"/>
+      <c r="B30" s="32"/>
       <c r="C30" s="31"/>
       <c r="D30" s="31"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="33"/>
+      <c r="G30" s="32"/>
       <c r="H30" s="31"/>
       <c r="I30" s="31"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="33"/>
+      <c r="L30" s="32"/>
       <c r="M30" s="31"/>
       <c r="N30" s="31"/>
     </row>
@@ -3990,19 +3996,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="34"/>
+      <c r="B31" s="33"/>
       <c r="C31" s="31"/>
       <c r="D31" s="31"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="34"/>
+      <c r="G31" s="33"/>
       <c r="H31" s="31"/>
       <c r="I31" s="31"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="34"/>
+      <c r="L31" s="33"/>
       <c r="M31" s="31"/>
       <c r="N31" s="31"/>
     </row>
@@ -4010,19 +4016,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="33"/>
+      <c r="B32" s="32"/>
       <c r="C32" s="31"/>
       <c r="D32" s="31"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="33"/>
+      <c r="G32" s="32"/>
       <c r="H32" s="31"/>
       <c r="I32" s="31"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="33"/>
+      <c r="L32" s="32"/>
       <c r="M32" s="31"/>
       <c r="N32" s="31"/>
     </row>
@@ -4030,19 +4036,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="34"/>
+      <c r="B33" s="33"/>
       <c r="C33" s="31"/>
       <c r="D33" s="31"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="34"/>
+      <c r="G33" s="33"/>
       <c r="H33" s="31"/>
       <c r="I33" s="31"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="34"/>
+      <c r="L33" s="33"/>
       <c r="M33" s="31"/>
       <c r="N33" s="31"/>
     </row>
@@ -4050,19 +4056,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="33"/>
+      <c r="B34" s="32"/>
       <c r="C34" s="31"/>
       <c r="D34" s="31"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="33"/>
+      <c r="G34" s="32"/>
       <c r="H34" s="31"/>
       <c r="I34" s="31"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="33"/>
+      <c r="L34" s="32"/>
       <c r="M34" s="31"/>
       <c r="N34" s="31"/>
     </row>
@@ -4070,19 +4076,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="34"/>
+      <c r="B35" s="33"/>
       <c r="C35" s="31"/>
       <c r="D35" s="31"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="34"/>
+      <c r="G35" s="33"/>
       <c r="H35" s="31"/>
       <c r="I35" s="31"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="34"/>
+      <c r="L35" s="33"/>
       <c r="M35" s="31"/>
       <c r="N35" s="31"/>
     </row>
@@ -4090,19 +4096,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="33"/>
+      <c r="B36" s="32"/>
       <c r="C36" s="31"/>
       <c r="D36" s="31"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="33"/>
+      <c r="G36" s="32"/>
       <c r="H36" s="31"/>
       <c r="I36" s="31"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="33"/>
+      <c r="L36" s="32"/>
       <c r="M36" s="31"/>
       <c r="N36" s="31"/>
     </row>
@@ -4110,7 +4116,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="36">
+      <c r="B37" s="35">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -4119,7 +4125,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="36">
+      <c r="G37" s="35">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -4128,7 +4134,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="36">
+      <c r="L37" s="35">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -4165,6 +4171,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
     <mergeCell ref="G36:I36"/>
     <mergeCell ref="L32:N32"/>
     <mergeCell ref="L13:N13"/>
@@ -4181,68 +4249,6 @@
     <mergeCell ref="L33:N33"/>
     <mergeCell ref="L35:N35"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="L9:N9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4290,7 +4296,7 @@
         <v>49</v>
       </c>
       <c r="E2" s="18">
-        <v>120</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -4324,7 +4330,7 @@
         <v>49</v>
       </c>
       <c r="E4" s="18">
-        <v>120</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4341,7 +4347,7 @@
         <v>68</v>
       </c>
       <c r="E5" s="18">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -4358,7 +4364,7 @@
         <v>49</v>
       </c>
       <c r="E6" s="18">
-        <v>120</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -4375,7 +4381,7 @@
         <v>68</v>
       </c>
       <c r="E7" s="18">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -4392,7 +4398,7 @@
         <v>49</v>
       </c>
       <c r="E8" s="18">
-        <v>70</v>
+        <v>140</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -4409,7 +4415,7 @@
         <v>68</v>
       </c>
       <c r="E9" s="18">
-        <v>70</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -4690,7 +4696,7 @@
         <v>49</v>
       </c>
       <c r="E26" s="18">
-        <v>165</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -4724,7 +4730,7 @@
         <v>49</v>
       </c>
       <c r="E28" s="18">
-        <v>165</v>
+        <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -4758,7 +4764,7 @@
         <v>49</v>
       </c>
       <c r="E30" s="18">
-        <v>165</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31" spans="1:5">

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD49081F-C972-446D-84D8-17333AA4BBBC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED4930B2-92C6-4D25-AF34-FF3EDFB34978}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -446,6 +446,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -456,9 +459,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -807,9 +807,7 @@
       <c r="A6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="14">
-        <v>800</v>
-      </c>
+      <c r="B6" s="14"/>
       <c r="F6" s="7" t="s">
         <v>21</v>
       </c>
@@ -825,7 +823,9 @@
       <c r="A7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="14"/>
+      <c r="B7" s="14">
+        <v>800</v>
+      </c>
       <c r="F7" s="7" t="s">
         <v>22</v>
       </c>
@@ -2828,19 +2828,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="32" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="31"/>
       <c r="C1" s="31"/>
       <c r="D1" s="31"/>
-      <c r="F1" s="36" t="s">
+      <c r="F1" s="32" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="31"/>
       <c r="H1" s="31"/>
       <c r="I1" s="31"/>
-      <c r="K1" s="36" t="s">
+      <c r="K1" s="32" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="31"/>
@@ -2848,19 +2848,19 @@
       <c r="N1" s="31"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="32" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
       <c r="D2" s="31"/>
-      <c r="F2" s="36" t="s">
+      <c r="F2" s="32" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="31"/>
       <c r="H2" s="31"/>
       <c r="I2" s="31"/>
-      <c r="K2" s="36" t="s">
+      <c r="K2" s="32" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="31"/>
@@ -2882,27 +2882,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="31"/>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="35" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="31"/>
-      <c r="F4" s="34" t="s">
+      <c r="F4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="31"/>
-      <c r="H4" s="34" t="s">
+      <c r="H4" s="35" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="31"/>
-      <c r="K4" s="34" t="s">
+      <c r="K4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="31"/>
-      <c r="M4" s="34" t="s">
+      <c r="M4" s="35" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="31"/>
@@ -2911,21 +2911,21 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="33">
-        <v>0</v>
-      </c>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
+      <c r="B5" s="34">
+        <v>0</v>
+      </c>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="33"/>
+      <c r="G5" s="34"/>
       <c r="H5" s="31"/>
       <c r="I5" s="31"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="33"/>
+      <c r="L5" s="34"/>
       <c r="M5" s="31"/>
       <c r="N5" s="31"/>
     </row>
@@ -2933,21 +2933,21 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="32">
-        <v>0</v>
-      </c>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
+      <c r="B6" s="33">
+        <v>0</v>
+      </c>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="32"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="31"/>
       <c r="I6" s="31"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="32"/>
+      <c r="L6" s="33"/>
       <c r="M6" s="31"/>
       <c r="N6" s="31"/>
     </row>
@@ -2955,21 +2955,21 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="33">
-        <v>0</v>
-      </c>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
+      <c r="B7" s="34">
+        <v>0</v>
+      </c>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="33"/>
+      <c r="G7" s="34"/>
       <c r="H7" s="31"/>
       <c r="I7" s="31"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="33"/>
+      <c r="L7" s="34"/>
       <c r="M7" s="31"/>
       <c r="N7" s="31"/>
     </row>
@@ -2977,21 +2977,21 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="32">
-        <v>0</v>
-      </c>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
+      <c r="B8" s="33">
+        <v>0</v>
+      </c>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="32"/>
+      <c r="G8" s="33"/>
       <c r="H8" s="31"/>
       <c r="I8" s="31"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="32"/>
+      <c r="L8" s="33"/>
       <c r="M8" s="31"/>
       <c r="N8" s="31"/>
     </row>
@@ -2999,21 +2999,21 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="33">
-        <v>0</v>
-      </c>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
+      <c r="B9" s="34">
+        <v>0</v>
+      </c>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="33"/>
+      <c r="G9" s="34"/>
       <c r="H9" s="31"/>
       <c r="I9" s="31"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="33"/>
+      <c r="L9" s="34"/>
       <c r="M9" s="31"/>
       <c r="N9" s="31"/>
     </row>
@@ -3021,21 +3021,21 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="32">
-        <v>0</v>
-      </c>
-      <c r="C10" s="32"/>
-      <c r="D10" s="32"/>
+      <c r="B10" s="33">
+        <v>0</v>
+      </c>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="32"/>
+      <c r="G10" s="33"/>
       <c r="H10" s="31"/>
       <c r="I10" s="31"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="32"/>
+      <c r="L10" s="33"/>
       <c r="M10" s="31"/>
       <c r="N10" s="31"/>
     </row>
@@ -3043,7 +3043,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="35">
+      <c r="B11" s="36">
         <f>SUM(B5:B10)</f>
         <v>0</v>
       </c>
@@ -3052,7 +3052,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="35">
+      <c r="G11" s="36">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -3061,7 +3061,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="35">
+      <c r="L11" s="36">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -3097,19 +3097,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="36" t="s">
+      <c r="A25" s="32" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="31"/>
       <c r="C25" s="31"/>
       <c r="D25" s="31"/>
-      <c r="F25" s="36" t="s">
+      <c r="F25" s="32" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="31"/>
       <c r="H25" s="31"/>
       <c r="I25" s="31"/>
-      <c r="K25" s="36" t="s">
+      <c r="K25" s="32" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="31"/>
@@ -3117,19 +3117,19 @@
       <c r="N25" s="31"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="36" t="s">
+      <c r="A26" s="32" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="31"/>
       <c r="C26" s="31"/>
       <c r="D26" s="31"/>
-      <c r="F26" s="36" t="s">
+      <c r="F26" s="32" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="31"/>
       <c r="H26" s="31"/>
       <c r="I26" s="31"/>
-      <c r="K26" s="36" t="s">
+      <c r="K26" s="32" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="31"/>
@@ -3151,27 +3151,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="34" t="s">
+      <c r="A28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="31"/>
-      <c r="C28" s="34" t="s">
+      <c r="C28" s="35" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="31"/>
-      <c r="F28" s="34" t="s">
+      <c r="F28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="31"/>
-      <c r="H28" s="34" t="s">
+      <c r="H28" s="35" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="31"/>
-      <c r="K28" s="34" t="s">
+      <c r="K28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="31"/>
-      <c r="M28" s="34" t="s">
+      <c r="M28" s="35" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="31"/>
@@ -3180,7 +3180,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="33">
+      <c r="B29" s="34">
         <v>0</v>
       </c>
       <c r="C29" s="31"/>
@@ -3188,23 +3188,23 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="33"/>
+      <c r="G29" s="34"/>
       <c r="H29" s="31"/>
       <c r="I29" s="31"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="33">
-        <v>0</v>
-      </c>
-      <c r="M29" s="33"/>
-      <c r="N29" s="33"/>
+      <c r="L29" s="34">
+        <v>0</v>
+      </c>
+      <c r="M29" s="34"/>
+      <c r="N29" s="34"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="32">
+      <c r="B30" s="33">
         <v>0</v>
       </c>
       <c r="C30" s="31"/>
@@ -3212,23 +3212,23 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="32"/>
+      <c r="G30" s="33"/>
       <c r="H30" s="31"/>
       <c r="I30" s="31"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="32">
-        <v>0</v>
-      </c>
-      <c r="M30" s="32"/>
-      <c r="N30" s="32"/>
+      <c r="L30" s="33">
+        <v>0</v>
+      </c>
+      <c r="M30" s="33"/>
+      <c r="N30" s="33"/>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1">
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="33">
+      <c r="B31" s="34">
         <v>0</v>
       </c>
       <c r="C31" s="31"/>
@@ -3236,23 +3236,23 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="33"/>
+      <c r="G31" s="34"/>
       <c r="H31" s="31"/>
       <c r="I31" s="31"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="33">
-        <v>0</v>
-      </c>
-      <c r="M31" s="33"/>
-      <c r="N31" s="33"/>
+      <c r="L31" s="34">
+        <v>0</v>
+      </c>
+      <c r="M31" s="34"/>
+      <c r="N31" s="34"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="32">
+      <c r="B32" s="33">
         <v>0</v>
       </c>
       <c r="C32" s="31"/>
@@ -3260,23 +3260,23 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="32"/>
+      <c r="G32" s="33"/>
       <c r="H32" s="31"/>
       <c r="I32" s="31"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="32">
-        <v>0</v>
-      </c>
-      <c r="M32" s="32"/>
-      <c r="N32" s="32"/>
+      <c r="L32" s="33">
+        <v>0</v>
+      </c>
+      <c r="M32" s="33"/>
+      <c r="N32" s="33"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="33">
+      <c r="B33" s="34">
         <v>0</v>
       </c>
       <c r="C33" s="31"/>
@@ -3284,23 +3284,23 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="33"/>
+      <c r="G33" s="34"/>
       <c r="H33" s="31"/>
       <c r="I33" s="31"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="33">
-        <v>0</v>
-      </c>
-      <c r="M33" s="33"/>
-      <c r="N33" s="33"/>
+      <c r="L33" s="34">
+        <v>0</v>
+      </c>
+      <c r="M33" s="34"/>
+      <c r="N33" s="34"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="32">
+      <c r="B34" s="33">
         <v>0</v>
       </c>
       <c r="C34" s="31"/>
@@ -3308,13 +3308,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="32"/>
+      <c r="G34" s="33"/>
       <c r="H34" s="31"/>
       <c r="I34" s="31"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="32">
+      <c r="L34" s="33">
         <v>0</v>
       </c>
       <c r="M34" s="31"/>
@@ -3324,7 +3324,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="35">
+      <c r="B35" s="36">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -3333,7 +3333,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="35">
+      <c r="G35" s="36">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -3342,7 +3342,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="35">
+      <c r="L35" s="36">
         <f>SUM(L29:L34)</f>
         <v>0</v>
       </c>
@@ -3379,13 +3379,49 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="L11:N11"/>
@@ -3402,49 +3438,13 @@
     <mergeCell ref="K2:N2"/>
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3460,7 +3460,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="32" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="31"/>
@@ -3468,7 +3468,7 @@
       <c r="D1" s="31"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="32" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="31"/>
@@ -3482,11 +3482,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="35" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="31"/>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="35" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="31"/>
@@ -3495,7 +3495,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="33"/>
+      <c r="B5" s="34"/>
       <c r="C5" s="31"/>
       <c r="D5" s="31"/>
     </row>
@@ -3503,7 +3503,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="32"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="31"/>
       <c r="D6" s="31"/>
     </row>
@@ -3511,7 +3511,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="33"/>
+      <c r="B7" s="34"/>
       <c r="C7" s="31"/>
       <c r="D7" s="31"/>
     </row>
@@ -3519,7 +3519,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="32"/>
+      <c r="B8" s="33"/>
       <c r="C8" s="31"/>
       <c r="D8" s="31"/>
     </row>
@@ -3527,7 +3527,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="35">
+      <c r="B9" s="36">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -3576,19 +3576,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="32" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="31"/>
       <c r="C1" s="31"/>
       <c r="D1" s="31"/>
-      <c r="F1" s="36" t="s">
+      <c r="F1" s="32" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="31"/>
       <c r="H1" s="31"/>
       <c r="I1" s="31"/>
-      <c r="K1" s="36" t="s">
+      <c r="K1" s="32" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="31"/>
@@ -3596,19 +3596,19 @@
       <c r="N1" s="31"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="32" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
       <c r="D2" s="31"/>
-      <c r="F2" s="36" t="s">
+      <c r="F2" s="32" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="31"/>
       <c r="H2" s="31"/>
       <c r="I2" s="31"/>
-      <c r="K2" s="36" t="s">
+      <c r="K2" s="32" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="31"/>
@@ -3630,27 +3630,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="31"/>
-      <c r="C4" s="34" t="s">
+      <c r="C4" s="35" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="31"/>
-      <c r="F4" s="34" t="s">
+      <c r="F4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="31"/>
-      <c r="H4" s="34" t="s">
+      <c r="H4" s="35" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="31"/>
-      <c r="K4" s="34" t="s">
+      <c r="K4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="31"/>
-      <c r="M4" s="34" t="s">
+      <c r="M4" s="35" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="31"/>
@@ -3659,19 +3659,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="33"/>
+      <c r="B5" s="34"/>
       <c r="C5" s="31"/>
       <c r="D5" s="31"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="33"/>
+      <c r="G5" s="34"/>
       <c r="H5" s="31"/>
       <c r="I5" s="31"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="33"/>
+      <c r="L5" s="34"/>
       <c r="M5" s="31"/>
       <c r="N5" s="31"/>
     </row>
@@ -3679,19 +3679,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="32"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="31"/>
       <c r="D6" s="31"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="32"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="31"/>
       <c r="I6" s="31"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="32"/>
+      <c r="L6" s="33"/>
       <c r="M6" s="31"/>
       <c r="N6" s="31"/>
     </row>
@@ -3699,19 +3699,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="33"/>
+      <c r="B7" s="34"/>
       <c r="C7" s="31"/>
       <c r="D7" s="31"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="33"/>
+      <c r="G7" s="34"/>
       <c r="H7" s="31"/>
       <c r="I7" s="31"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="33"/>
+      <c r="L7" s="34"/>
       <c r="M7" s="31"/>
       <c r="N7" s="31"/>
     </row>
@@ -3719,19 +3719,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="32"/>
+      <c r="B8" s="33"/>
       <c r="C8" s="31"/>
       <c r="D8" s="31"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="32"/>
+      <c r="G8" s="33"/>
       <c r="H8" s="31"/>
       <c r="I8" s="31"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="32"/>
+      <c r="L8" s="33"/>
       <c r="M8" s="31"/>
       <c r="N8" s="31"/>
     </row>
@@ -3739,19 +3739,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="33"/>
+      <c r="B9" s="34"/>
       <c r="C9" s="31"/>
       <c r="D9" s="31"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="33"/>
+      <c r="G9" s="34"/>
       <c r="H9" s="31"/>
       <c r="I9" s="31"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="33"/>
+      <c r="L9" s="34"/>
       <c r="M9" s="31"/>
       <c r="N9" s="31"/>
     </row>
@@ -3759,19 +3759,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="32"/>
+      <c r="B10" s="33"/>
       <c r="C10" s="31"/>
       <c r="D10" s="31"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="32"/>
+      <c r="G10" s="33"/>
       <c r="H10" s="31"/>
       <c r="I10" s="31"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="32"/>
+      <c r="L10" s="33"/>
       <c r="M10" s="31"/>
       <c r="N10" s="31"/>
     </row>
@@ -3779,19 +3779,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="33"/>
+      <c r="B11" s="34"/>
       <c r="C11" s="31"/>
       <c r="D11" s="31"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="33"/>
+      <c r="G11" s="34"/>
       <c r="H11" s="31"/>
       <c r="I11" s="31"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="33"/>
+      <c r="L11" s="34"/>
       <c r="M11" s="31"/>
       <c r="N11" s="31"/>
     </row>
@@ -3799,19 +3799,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="32"/>
+      <c r="B12" s="33"/>
       <c r="C12" s="31"/>
       <c r="D12" s="31"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="32"/>
+      <c r="G12" s="33"/>
       <c r="H12" s="31"/>
       <c r="I12" s="31"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="32"/>
+      <c r="L12" s="33"/>
       <c r="M12" s="31"/>
       <c r="N12" s="31"/>
     </row>
@@ -3819,7 +3819,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="35">
+      <c r="B13" s="36">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3828,7 +3828,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="35">
+      <c r="G13" s="36">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3837,7 +3837,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="35">
+      <c r="L13" s="36">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3873,19 +3873,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="36" t="s">
+      <c r="A25" s="32" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="31"/>
       <c r="C25" s="31"/>
       <c r="D25" s="31"/>
-      <c r="F25" s="36" t="s">
+      <c r="F25" s="32" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="31"/>
       <c r="H25" s="31"/>
       <c r="I25" s="31"/>
-      <c r="K25" s="36" t="s">
+      <c r="K25" s="32" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="31"/>
@@ -3893,19 +3893,19 @@
       <c r="N25" s="31"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="36" t="s">
+      <c r="A26" s="32" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="31"/>
       <c r="C26" s="31"/>
       <c r="D26" s="31"/>
-      <c r="F26" s="36" t="s">
+      <c r="F26" s="32" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="31"/>
       <c r="H26" s="31"/>
       <c r="I26" s="31"/>
-      <c r="K26" s="36" t="s">
+      <c r="K26" s="32" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="31"/>
@@ -3927,27 +3927,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="34" t="s">
+      <c r="A28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="31"/>
-      <c r="C28" s="34" t="s">
+      <c r="C28" s="35" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="31"/>
-      <c r="F28" s="34" t="s">
+      <c r="F28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="31"/>
-      <c r="H28" s="34" t="s">
+      <c r="H28" s="35" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="31"/>
-      <c r="K28" s="34" t="s">
+      <c r="K28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="31"/>
-      <c r="M28" s="34" t="s">
+      <c r="M28" s="35" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="31"/>
@@ -3956,19 +3956,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="33"/>
+      <c r="B29" s="34"/>
       <c r="C29" s="31"/>
       <c r="D29" s="31"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="33"/>
+      <c r="G29" s="34"/>
       <c r="H29" s="31"/>
       <c r="I29" s="31"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="33"/>
+      <c r="L29" s="34"/>
       <c r="M29" s="31"/>
       <c r="N29" s="31"/>
     </row>
@@ -3976,19 +3976,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="32"/>
+      <c r="B30" s="33"/>
       <c r="C30" s="31"/>
       <c r="D30" s="31"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="32"/>
+      <c r="G30" s="33"/>
       <c r="H30" s="31"/>
       <c r="I30" s="31"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="32"/>
+      <c r="L30" s="33"/>
       <c r="M30" s="31"/>
       <c r="N30" s="31"/>
     </row>
@@ -3996,19 +3996,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="33"/>
+      <c r="B31" s="34"/>
       <c r="C31" s="31"/>
       <c r="D31" s="31"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="33"/>
+      <c r="G31" s="34"/>
       <c r="H31" s="31"/>
       <c r="I31" s="31"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="33"/>
+      <c r="L31" s="34"/>
       <c r="M31" s="31"/>
       <c r="N31" s="31"/>
     </row>
@@ -4016,19 +4016,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="32"/>
+      <c r="B32" s="33"/>
       <c r="C32" s="31"/>
       <c r="D32" s="31"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="32"/>
+      <c r="G32" s="33"/>
       <c r="H32" s="31"/>
       <c r="I32" s="31"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="32"/>
+      <c r="L32" s="33"/>
       <c r="M32" s="31"/>
       <c r="N32" s="31"/>
     </row>
@@ -4036,19 +4036,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="33"/>
+      <c r="B33" s="34"/>
       <c r="C33" s="31"/>
       <c r="D33" s="31"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="33"/>
+      <c r="G33" s="34"/>
       <c r="H33" s="31"/>
       <c r="I33" s="31"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="33"/>
+      <c r="L33" s="34"/>
       <c r="M33" s="31"/>
       <c r="N33" s="31"/>
     </row>
@@ -4056,19 +4056,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="32"/>
+      <c r="B34" s="33"/>
       <c r="C34" s="31"/>
       <c r="D34" s="31"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="32"/>
+      <c r="G34" s="33"/>
       <c r="H34" s="31"/>
       <c r="I34" s="31"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="32"/>
+      <c r="L34" s="33"/>
       <c r="M34" s="31"/>
       <c r="N34" s="31"/>
     </row>
@@ -4076,19 +4076,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="33"/>
+      <c r="B35" s="34"/>
       <c r="C35" s="31"/>
       <c r="D35" s="31"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="33"/>
+      <c r="G35" s="34"/>
       <c r="H35" s="31"/>
       <c r="I35" s="31"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="33"/>
+      <c r="L35" s="34"/>
       <c r="M35" s="31"/>
       <c r="N35" s="31"/>
     </row>
@@ -4096,19 +4096,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="32"/>
+      <c r="B36" s="33"/>
       <c r="C36" s="31"/>
       <c r="D36" s="31"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="32"/>
+      <c r="G36" s="33"/>
       <c r="H36" s="31"/>
       <c r="I36" s="31"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="32"/>
+      <c r="L36" s="33"/>
       <c r="M36" s="31"/>
       <c r="N36" s="31"/>
     </row>
@@ -4116,7 +4116,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="35">
+      <c r="B37" s="36">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -4125,7 +4125,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="35">
+      <c r="G37" s="36">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -4134,7 +4134,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="35">
+      <c r="L37" s="36">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -4171,6 +4171,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
     <mergeCell ref="L34:N34"/>
     <mergeCell ref="L6:N6"/>
     <mergeCell ref="B33:D33"/>
@@ -4187,68 +4249,6 @@
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED4930B2-92C6-4D25-AF34-FF3EDFB34978}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2CEEA35-9E39-4961-91A9-477ADB31FFE2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucoes" sheetId="1" r:id="rId1"/>
@@ -446,9 +446,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -459,6 +456,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2828,19 +2828,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="36" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="31"/>
       <c r="C1" s="31"/>
       <c r="D1" s="31"/>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="36" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="31"/>
       <c r="H1" s="31"/>
       <c r="I1" s="31"/>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="36" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="31"/>
@@ -2848,19 +2848,19 @@
       <c r="N1" s="31"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="36" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
       <c r="D2" s="31"/>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="36" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="31"/>
       <c r="H2" s="31"/>
       <c r="I2" s="31"/>
-      <c r="K2" s="32" t="s">
+      <c r="K2" s="36" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="31"/>
@@ -2882,27 +2882,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="34" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="31"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="34" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="31"/>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="34" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="31"/>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="34" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="31"/>
-      <c r="K4" s="35" t="s">
+      <c r="K4" s="34" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="31"/>
-      <c r="M4" s="35" t="s">
+      <c r="M4" s="34" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="31"/>
@@ -2911,21 +2911,21 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="34">
-        <v>0</v>
-      </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
+      <c r="B5" s="33">
+        <v>0</v>
+      </c>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="34"/>
+      <c r="G5" s="33"/>
       <c r="H5" s="31"/>
       <c r="I5" s="31"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="34"/>
+      <c r="L5" s="33"/>
       <c r="M5" s="31"/>
       <c r="N5" s="31"/>
     </row>
@@ -2933,21 +2933,21 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="33">
-        <v>0</v>
-      </c>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
+      <c r="B6" s="32">
+        <v>0</v>
+      </c>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="33"/>
+      <c r="G6" s="32"/>
       <c r="H6" s="31"/>
       <c r="I6" s="31"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="33"/>
+      <c r="L6" s="32"/>
       <c r="M6" s="31"/>
       <c r="N6" s="31"/>
     </row>
@@ -2955,21 +2955,21 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="34">
-        <v>0</v>
-      </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
+      <c r="B7" s="33">
+        <v>0</v>
+      </c>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="34"/>
+      <c r="G7" s="33"/>
       <c r="H7" s="31"/>
       <c r="I7" s="31"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="34"/>
+      <c r="L7" s="33"/>
       <c r="M7" s="31"/>
       <c r="N7" s="31"/>
     </row>
@@ -2977,21 +2977,21 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="33">
-        <v>0</v>
-      </c>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
+      <c r="B8" s="32">
+        <v>0</v>
+      </c>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="33"/>
+      <c r="G8" s="32"/>
       <c r="H8" s="31"/>
       <c r="I8" s="31"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="33"/>
+      <c r="L8" s="32"/>
       <c r="M8" s="31"/>
       <c r="N8" s="31"/>
     </row>
@@ -2999,21 +2999,21 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="34">
-        <v>0</v>
-      </c>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
+      <c r="B9" s="33">
+        <v>0</v>
+      </c>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="34"/>
+      <c r="G9" s="33"/>
       <c r="H9" s="31"/>
       <c r="I9" s="31"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="34"/>
+      <c r="L9" s="33"/>
       <c r="M9" s="31"/>
       <c r="N9" s="31"/>
     </row>
@@ -3021,21 +3021,21 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="33">
-        <v>0</v>
-      </c>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
+      <c r="B10" s="32">
+        <v>0</v>
+      </c>
+      <c r="C10" s="32"/>
+      <c r="D10" s="32"/>
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="33"/>
+      <c r="G10" s="32"/>
       <c r="H10" s="31"/>
       <c r="I10" s="31"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="33"/>
+      <c r="L10" s="32"/>
       <c r="M10" s="31"/>
       <c r="N10" s="31"/>
     </row>
@@ -3043,7 +3043,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="36">
+      <c r="B11" s="35">
         <f>SUM(B5:B10)</f>
         <v>0</v>
       </c>
@@ -3052,7 +3052,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="36">
+      <c r="G11" s="35">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -3061,7 +3061,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="36">
+      <c r="L11" s="35">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -3097,19 +3097,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="32" t="s">
+      <c r="A25" s="36" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="31"/>
       <c r="C25" s="31"/>
       <c r="D25" s="31"/>
-      <c r="F25" s="32" t="s">
+      <c r="F25" s="36" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="31"/>
       <c r="H25" s="31"/>
       <c r="I25" s="31"/>
-      <c r="K25" s="32" t="s">
+      <c r="K25" s="36" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="31"/>
@@ -3117,19 +3117,19 @@
       <c r="N25" s="31"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="32" t="s">
+      <c r="A26" s="36" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="31"/>
       <c r="C26" s="31"/>
       <c r="D26" s="31"/>
-      <c r="F26" s="32" t="s">
+      <c r="F26" s="36" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="31"/>
       <c r="H26" s="31"/>
       <c r="I26" s="31"/>
-      <c r="K26" s="32" t="s">
+      <c r="K26" s="36" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="31"/>
@@ -3151,27 +3151,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="35" t="s">
+      <c r="A28" s="34" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="31"/>
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="34" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="31"/>
-      <c r="F28" s="35" t="s">
+      <c r="F28" s="34" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="31"/>
-      <c r="H28" s="35" t="s">
+      <c r="H28" s="34" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="31"/>
-      <c r="K28" s="35" t="s">
+      <c r="K28" s="34" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="31"/>
-      <c r="M28" s="35" t="s">
+      <c r="M28" s="34" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="31"/>
@@ -3180,7 +3180,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="34">
+      <c r="B29" s="33">
         <v>0</v>
       </c>
       <c r="C29" s="31"/>
@@ -3188,23 +3188,23 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="34"/>
+      <c r="G29" s="33"/>
       <c r="H29" s="31"/>
       <c r="I29" s="31"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="34">
-        <v>0</v>
-      </c>
-      <c r="M29" s="34"/>
-      <c r="N29" s="34"/>
+      <c r="L29" s="33">
+        <v>0</v>
+      </c>
+      <c r="M29" s="33"/>
+      <c r="N29" s="33"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="33">
+      <c r="B30" s="32">
         <v>0</v>
       </c>
       <c r="C30" s="31"/>
@@ -3212,23 +3212,23 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="33"/>
+      <c r="G30" s="32"/>
       <c r="H30" s="31"/>
       <c r="I30" s="31"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="33">
-        <v>0</v>
-      </c>
-      <c r="M30" s="33"/>
-      <c r="N30" s="33"/>
+      <c r="L30" s="32">
+        <v>0</v>
+      </c>
+      <c r="M30" s="32"/>
+      <c r="N30" s="32"/>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1">
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="34">
+      <c r="B31" s="33">
         <v>0</v>
       </c>
       <c r="C31" s="31"/>
@@ -3236,23 +3236,23 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="34"/>
+      <c r="G31" s="33"/>
       <c r="H31" s="31"/>
       <c r="I31" s="31"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="34">
-        <v>0</v>
-      </c>
-      <c r="M31" s="34"/>
-      <c r="N31" s="34"/>
+      <c r="L31" s="33">
+        <v>0</v>
+      </c>
+      <c r="M31" s="33"/>
+      <c r="N31" s="33"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="33">
+      <c r="B32" s="32">
         <v>0</v>
       </c>
       <c r="C32" s="31"/>
@@ -3260,23 +3260,23 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="33"/>
+      <c r="G32" s="32"/>
       <c r="H32" s="31"/>
       <c r="I32" s="31"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="33">
-        <v>0</v>
-      </c>
-      <c r="M32" s="33"/>
-      <c r="N32" s="33"/>
+      <c r="L32" s="32">
+        <v>0</v>
+      </c>
+      <c r="M32" s="32"/>
+      <c r="N32" s="32"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="34">
+      <c r="B33" s="33">
         <v>0</v>
       </c>
       <c r="C33" s="31"/>
@@ -3284,23 +3284,23 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="34"/>
+      <c r="G33" s="33"/>
       <c r="H33" s="31"/>
       <c r="I33" s="31"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="34">
-        <v>0</v>
-      </c>
-      <c r="M33" s="34"/>
-      <c r="N33" s="34"/>
+      <c r="L33" s="33">
+        <v>0</v>
+      </c>
+      <c r="M33" s="33"/>
+      <c r="N33" s="33"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="33">
+      <c r="B34" s="32">
         <v>0</v>
       </c>
       <c r="C34" s="31"/>
@@ -3308,13 +3308,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="33"/>
+      <c r="G34" s="32"/>
       <c r="H34" s="31"/>
       <c r="I34" s="31"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="33">
+      <c r="L34" s="32">
         <v>0</v>
       </c>
       <c r="M34" s="31"/>
@@ -3324,7 +3324,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="36">
+      <c r="B35" s="35">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -3333,7 +3333,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="36">
+      <c r="G35" s="35">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -3342,7 +3342,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="36">
+      <c r="L35" s="35">
         <f>SUM(L29:L34)</f>
         <v>0</v>
       </c>
@@ -3379,6 +3379,56 @@
     </row>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B10:D10"/>
@@ -3395,56 +3445,6 @@
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="H28:I28"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3460,7 +3460,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="36" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="31"/>
@@ -3468,7 +3468,7 @@
       <c r="D1" s="31"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="36" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="31"/>
@@ -3482,11 +3482,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="34" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="31"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="34" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="31"/>
@@ -3495,7 +3495,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="34"/>
+      <c r="B5" s="33"/>
       <c r="C5" s="31"/>
       <c r="D5" s="31"/>
     </row>
@@ -3503,7 +3503,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="33"/>
+      <c r="B6" s="32"/>
       <c r="C6" s="31"/>
       <c r="D6" s="31"/>
     </row>
@@ -3511,7 +3511,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="34"/>
+      <c r="B7" s="33"/>
       <c r="C7" s="31"/>
       <c r="D7" s="31"/>
     </row>
@@ -3519,7 +3519,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="33"/>
+      <c r="B8" s="32"/>
       <c r="C8" s="31"/>
       <c r="D8" s="31"/>
     </row>
@@ -3527,7 +3527,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="36">
+      <c r="B9" s="35">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -3576,19 +3576,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="36" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="31"/>
       <c r="C1" s="31"/>
       <c r="D1" s="31"/>
-      <c r="F1" s="32" t="s">
+      <c r="F1" s="36" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="31"/>
       <c r="H1" s="31"/>
       <c r="I1" s="31"/>
-      <c r="K1" s="32" t="s">
+      <c r="K1" s="36" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="31"/>
@@ -3596,19 +3596,19 @@
       <c r="N1" s="31"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="36" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="31"/>
       <c r="D2" s="31"/>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="36" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="31"/>
       <c r="H2" s="31"/>
       <c r="I2" s="31"/>
-      <c r="K2" s="32" t="s">
+      <c r="K2" s="36" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="31"/>
@@ -3630,27 +3630,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="34" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="31"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="34" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="31"/>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="34" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="31"/>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="34" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="31"/>
-      <c r="K4" s="35" t="s">
+      <c r="K4" s="34" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="31"/>
-      <c r="M4" s="35" t="s">
+      <c r="M4" s="34" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="31"/>
@@ -3659,19 +3659,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="34"/>
+      <c r="B5" s="33"/>
       <c r="C5" s="31"/>
       <c r="D5" s="31"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="34"/>
+      <c r="G5" s="33"/>
       <c r="H5" s="31"/>
       <c r="I5" s="31"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="34"/>
+      <c r="L5" s="33"/>
       <c r="M5" s="31"/>
       <c r="N5" s="31"/>
     </row>
@@ -3679,19 +3679,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="33"/>
+      <c r="B6" s="32"/>
       <c r="C6" s="31"/>
       <c r="D6" s="31"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="33"/>
+      <c r="G6" s="32"/>
       <c r="H6" s="31"/>
       <c r="I6" s="31"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="33"/>
+      <c r="L6" s="32"/>
       <c r="M6" s="31"/>
       <c r="N6" s="31"/>
     </row>
@@ -3699,19 +3699,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="34"/>
+      <c r="B7" s="33"/>
       <c r="C7" s="31"/>
       <c r="D7" s="31"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="34"/>
+      <c r="G7" s="33"/>
       <c r="H7" s="31"/>
       <c r="I7" s="31"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="34"/>
+      <c r="L7" s="33"/>
       <c r="M7" s="31"/>
       <c r="N7" s="31"/>
     </row>
@@ -3719,19 +3719,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="33"/>
+      <c r="B8" s="32"/>
       <c r="C8" s="31"/>
       <c r="D8" s="31"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="33"/>
+      <c r="G8" s="32"/>
       <c r="H8" s="31"/>
       <c r="I8" s="31"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="33"/>
+      <c r="L8" s="32"/>
       <c r="M8" s="31"/>
       <c r="N8" s="31"/>
     </row>
@@ -3739,19 +3739,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="34"/>
+      <c r="B9" s="33"/>
       <c r="C9" s="31"/>
       <c r="D9" s="31"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="34"/>
+      <c r="G9" s="33"/>
       <c r="H9" s="31"/>
       <c r="I9" s="31"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="34"/>
+      <c r="L9" s="33"/>
       <c r="M9" s="31"/>
       <c r="N9" s="31"/>
     </row>
@@ -3759,19 +3759,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="33"/>
+      <c r="B10" s="32"/>
       <c r="C10" s="31"/>
       <c r="D10" s="31"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="33"/>
+      <c r="G10" s="32"/>
       <c r="H10" s="31"/>
       <c r="I10" s="31"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="33"/>
+      <c r="L10" s="32"/>
       <c r="M10" s="31"/>
       <c r="N10" s="31"/>
     </row>
@@ -3779,19 +3779,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="34"/>
+      <c r="B11" s="33"/>
       <c r="C11" s="31"/>
       <c r="D11" s="31"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="34"/>
+      <c r="G11" s="33"/>
       <c r="H11" s="31"/>
       <c r="I11" s="31"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="34"/>
+      <c r="L11" s="33"/>
       <c r="M11" s="31"/>
       <c r="N11" s="31"/>
     </row>
@@ -3799,19 +3799,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="33"/>
+      <c r="B12" s="32"/>
       <c r="C12" s="31"/>
       <c r="D12" s="31"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="33"/>
+      <c r="G12" s="32"/>
       <c r="H12" s="31"/>
       <c r="I12" s="31"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="33"/>
+      <c r="L12" s="32"/>
       <c r="M12" s="31"/>
       <c r="N12" s="31"/>
     </row>
@@ -3819,7 +3819,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="36">
+      <c r="B13" s="35">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3828,7 +3828,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="36">
+      <c r="G13" s="35">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3837,7 +3837,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="36">
+      <c r="L13" s="35">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3873,19 +3873,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="32" t="s">
+      <c r="A25" s="36" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="31"/>
       <c r="C25" s="31"/>
       <c r="D25" s="31"/>
-      <c r="F25" s="32" t="s">
+      <c r="F25" s="36" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="31"/>
       <c r="H25" s="31"/>
       <c r="I25" s="31"/>
-      <c r="K25" s="32" t="s">
+      <c r="K25" s="36" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="31"/>
@@ -3893,19 +3893,19 @@
       <c r="N25" s="31"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="32" t="s">
+      <c r="A26" s="36" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="31"/>
       <c r="C26" s="31"/>
       <c r="D26" s="31"/>
-      <c r="F26" s="32" t="s">
+      <c r="F26" s="36" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="31"/>
       <c r="H26" s="31"/>
       <c r="I26" s="31"/>
-      <c r="K26" s="32" t="s">
+      <c r="K26" s="36" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="31"/>
@@ -3927,27 +3927,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="35" t="s">
+      <c r="A28" s="34" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="31"/>
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="34" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="31"/>
-      <c r="F28" s="35" t="s">
+      <c r="F28" s="34" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="31"/>
-      <c r="H28" s="35" t="s">
+      <c r="H28" s="34" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="31"/>
-      <c r="K28" s="35" t="s">
+      <c r="K28" s="34" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="31"/>
-      <c r="M28" s="35" t="s">
+      <c r="M28" s="34" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="31"/>
@@ -3956,19 +3956,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="34"/>
+      <c r="B29" s="33"/>
       <c r="C29" s="31"/>
       <c r="D29" s="31"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="34"/>
+      <c r="G29" s="33"/>
       <c r="H29" s="31"/>
       <c r="I29" s="31"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="34"/>
+      <c r="L29" s="33"/>
       <c r="M29" s="31"/>
       <c r="N29" s="31"/>
     </row>
@@ -3976,19 +3976,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="33"/>
+      <c r="B30" s="32"/>
       <c r="C30" s="31"/>
       <c r="D30" s="31"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="33"/>
+      <c r="G30" s="32"/>
       <c r="H30" s="31"/>
       <c r="I30" s="31"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="33"/>
+      <c r="L30" s="32"/>
       <c r="M30" s="31"/>
       <c r="N30" s="31"/>
     </row>
@@ -3996,19 +3996,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="34"/>
+      <c r="B31" s="33"/>
       <c r="C31" s="31"/>
       <c r="D31" s="31"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="34"/>
+      <c r="G31" s="33"/>
       <c r="H31" s="31"/>
       <c r="I31" s="31"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="34"/>
+      <c r="L31" s="33"/>
       <c r="M31" s="31"/>
       <c r="N31" s="31"/>
     </row>
@@ -4016,19 +4016,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="33"/>
+      <c r="B32" s="32"/>
       <c r="C32" s="31"/>
       <c r="D32" s="31"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="33"/>
+      <c r="G32" s="32"/>
       <c r="H32" s="31"/>
       <c r="I32" s="31"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="33"/>
+      <c r="L32" s="32"/>
       <c r="M32" s="31"/>
       <c r="N32" s="31"/>
     </row>
@@ -4036,19 +4036,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="34"/>
+      <c r="B33" s="33"/>
       <c r="C33" s="31"/>
       <c r="D33" s="31"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="34"/>
+      <c r="G33" s="33"/>
       <c r="H33" s="31"/>
       <c r="I33" s="31"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="34"/>
+      <c r="L33" s="33"/>
       <c r="M33" s="31"/>
       <c r="N33" s="31"/>
     </row>
@@ -4056,19 +4056,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="33"/>
+      <c r="B34" s="32"/>
       <c r="C34" s="31"/>
       <c r="D34" s="31"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="33"/>
+      <c r="G34" s="32"/>
       <c r="H34" s="31"/>
       <c r="I34" s="31"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="33"/>
+      <c r="L34" s="32"/>
       <c r="M34" s="31"/>
       <c r="N34" s="31"/>
     </row>
@@ -4076,19 +4076,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="34"/>
+      <c r="B35" s="33"/>
       <c r="C35" s="31"/>
       <c r="D35" s="31"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="34"/>
+      <c r="G35" s="33"/>
       <c r="H35" s="31"/>
       <c r="I35" s="31"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="34"/>
+      <c r="L35" s="33"/>
       <c r="M35" s="31"/>
       <c r="N35" s="31"/>
     </row>
@@ -4096,19 +4096,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="33"/>
+      <c r="B36" s="32"/>
       <c r="C36" s="31"/>
       <c r="D36" s="31"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="33"/>
+      <c r="G36" s="32"/>
       <c r="H36" s="31"/>
       <c r="I36" s="31"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="33"/>
+      <c r="L36" s="32"/>
       <c r="M36" s="31"/>
       <c r="N36" s="31"/>
     </row>
@@ -4116,7 +4116,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="36">
+      <c r="B37" s="35">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -4125,7 +4125,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="36">
+      <c r="G37" s="35">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -4134,7 +4134,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="36">
+      <c r="L37" s="35">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -4171,6 +4171,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
     <mergeCell ref="G36:I36"/>
     <mergeCell ref="L32:N32"/>
     <mergeCell ref="L13:N13"/>
@@ -4187,68 +4249,6 @@
     <mergeCell ref="L33:N33"/>
     <mergeCell ref="L35:N35"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="L9:N9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4696,7 +4696,7 @@
         <v>49</v>
       </c>
       <c r="E26" s="18">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="27" spans="1:5">

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2CEEA35-9E39-4961-91A9-477ADB31FFE2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E758ED2-A383-414E-9F83-96D476301539}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -365,7 +365,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -444,8 +444,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -456,9 +460,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -634,16 +635,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A1" s="30" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
+      <c r="A1" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
     </row>
     <row r="3" spans="1:8" ht="29.25" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -2828,44 +2829,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="F1" s="36" t="s">
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="F1" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="K1" s="36" t="s">
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="K1" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="F2" s="36" t="s">
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="F2" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="K2" s="36" t="s">
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="K2" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="L2" s="31"/>
-      <c r="M2" s="31"/>
-      <c r="N2" s="31"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
     </row>
     <row r="3" spans="1:14" ht="15" customHeight="1">
       <c r="A3" s="9"/>
@@ -2882,191 +2883,191 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="31"/>
-      <c r="C4" s="34" t="s">
+      <c r="B4" s="32"/>
+      <c r="C4" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="31"/>
-      <c r="F4" s="34" t="s">
+      <c r="D4" s="32"/>
+      <c r="F4" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="31"/>
-      <c r="H4" s="34" t="s">
+      <c r="G4" s="32"/>
+      <c r="H4" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="I4" s="31"/>
-      <c r="K4" s="34" t="s">
+      <c r="I4" s="32"/>
+      <c r="K4" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="L4" s="31"/>
-      <c r="M4" s="34" t="s">
+      <c r="L4" s="32"/>
+      <c r="M4" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="N4" s="31"/>
+      <c r="N4" s="32"/>
     </row>
     <row r="5" spans="1:14" ht="15" customHeight="1">
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="33">
-        <v>0</v>
-      </c>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
+      <c r="B5" s="35">
+        <v>0</v>
+      </c>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="33"/>
-      <c r="H5" s="31"/>
-      <c r="I5" s="31"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="33"/>
-      <c r="M5" s="31"/>
-      <c r="N5" s="31"/>
+      <c r="L5" s="35"/>
+      <c r="M5" s="32"/>
+      <c r="N5" s="32"/>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="32">
-        <v>0</v>
-      </c>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
+      <c r="B6" s="34">
+        <v>0</v>
+      </c>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="32"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="32"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="32"/>
-      <c r="M6" s="31"/>
-      <c r="N6" s="31"/>
+      <c r="L6" s="34"/>
+      <c r="M6" s="32"/>
+      <c r="N6" s="32"/>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="33">
-        <v>0</v>
-      </c>
-      <c r="C7" s="33"/>
-      <c r="D7" s="33"/>
+      <c r="B7" s="35">
+        <v>0</v>
+      </c>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="33"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="32"/>
+      <c r="I7" s="32"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="33"/>
-      <c r="M7" s="31"/>
-      <c r="N7" s="31"/>
+      <c r="L7" s="35"/>
+      <c r="M7" s="32"/>
+      <c r="N7" s="32"/>
     </row>
     <row r="8" spans="1:14" ht="15" customHeight="1">
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="32">
-        <v>0</v>
-      </c>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
+      <c r="B8" s="34">
+        <v>0</v>
+      </c>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="31"/>
-      <c r="I8" s="31"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="32"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="32"/>
-      <c r="M8" s="31"/>
-      <c r="N8" s="31"/>
+      <c r="L8" s="34"/>
+      <c r="M8" s="32"/>
+      <c r="N8" s="32"/>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1">
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="33">
-        <v>0</v>
-      </c>
-      <c r="C9" s="33"/>
-      <c r="D9" s="33"/>
+      <c r="B9" s="35">
+        <v>0</v>
+      </c>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="33"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="33"/>
-      <c r="M9" s="31"/>
-      <c r="N9" s="31"/>
+      <c r="L9" s="35"/>
+      <c r="M9" s="32"/>
+      <c r="N9" s="32"/>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="32">
-        <v>0</v>
-      </c>
-      <c r="C10" s="32"/>
-      <c r="D10" s="32"/>
+      <c r="B10" s="34">
+        <v>0</v>
+      </c>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="31"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="32"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="32"/>
-      <c r="M10" s="31"/>
-      <c r="N10" s="31"/>
+      <c r="L10" s="34"/>
+      <c r="M10" s="32"/>
+      <c r="N10" s="32"/>
     </row>
     <row r="11" spans="1:14" ht="15" customHeight="1">
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="35">
+      <c r="B11" s="37">
         <f>SUM(B5:B10)</f>
         <v>0</v>
       </c>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="32"/>
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="35">
+      <c r="G11" s="37">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="31"/>
-      <c r="I11" s="31"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="35">
+      <c r="L11" s="37">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
-      <c r="M11" s="31"/>
-      <c r="N11" s="31"/>
+      <c r="M11" s="32"/>
+      <c r="N11" s="32"/>
     </row>
     <row r="12" spans="1:14" ht="15" customHeight="1">
       <c r="A12" s="9"/>
@@ -3097,44 +3098,44 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="36" t="s">
+      <c r="A25" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="B25" s="31"/>
-      <c r="C25" s="31"/>
-      <c r="D25" s="31"/>
-      <c r="F25" s="36" t="s">
+      <c r="B25" s="32"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+      <c r="F25" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="G25" s="31"/>
-      <c r="H25" s="31"/>
-      <c r="I25" s="31"/>
-      <c r="K25" s="36" t="s">
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="32"/>
+      <c r="K25" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="L25" s="31"/>
-      <c r="M25" s="31"/>
-      <c r="N25" s="31"/>
+      <c r="L25" s="32"/>
+      <c r="M25" s="32"/>
+      <c r="N25" s="32"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="36" t="s">
+      <c r="A26" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="31"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
-      <c r="F26" s="36" t="s">
+      <c r="B26" s="32"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="F26" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="31"/>
-      <c r="K26" s="36" t="s">
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="32"/>
+      <c r="K26" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="L26" s="31"/>
-      <c r="M26" s="31"/>
-      <c r="N26" s="31"/>
+      <c r="L26" s="32"/>
+      <c r="M26" s="32"/>
+      <c r="N26" s="32"/>
     </row>
     <row r="27" spans="1:14" ht="15" customHeight="1">
       <c r="A27" s="9"/>
@@ -3151,203 +3152,203 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="34" t="s">
+      <c r="A28" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="34" t="s">
+      <c r="B28" s="32"/>
+      <c r="C28" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="D28" s="31"/>
-      <c r="F28" s="34" t="s">
+      <c r="D28" s="32"/>
+      <c r="F28" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="G28" s="31"/>
-      <c r="H28" s="34" t="s">
+      <c r="G28" s="32"/>
+      <c r="H28" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="I28" s="31"/>
-      <c r="K28" s="34" t="s">
+      <c r="I28" s="32"/>
+      <c r="K28" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="L28" s="31"/>
-      <c r="M28" s="34" t="s">
+      <c r="L28" s="32"/>
+      <c r="M28" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="N28" s="31"/>
+      <c r="N28" s="32"/>
     </row>
     <row r="29" spans="1:14" ht="15" customHeight="1">
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="33">
-        <v>0</v>
-      </c>
-      <c r="C29" s="31"/>
-      <c r="D29" s="31"/>
+      <c r="B29" s="35">
+        <v>0</v>
+      </c>
+      <c r="C29" s="32"/>
+      <c r="D29" s="32"/>
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="33"/>
-      <c r="H29" s="31"/>
-      <c r="I29" s="31"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="32"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="33">
-        <v>0</v>
-      </c>
-      <c r="M29" s="33"/>
-      <c r="N29" s="33"/>
+      <c r="L29" s="35">
+        <v>0</v>
+      </c>
+      <c r="M29" s="35"/>
+      <c r="N29" s="35"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="32">
-        <v>0</v>
-      </c>
-      <c r="C30" s="31"/>
-      <c r="D30" s="31"/>
+      <c r="B30" s="34">
+        <v>0</v>
+      </c>
+      <c r="C30" s="32"/>
+      <c r="D30" s="32"/>
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="32"/>
-      <c r="H30" s="31"/>
-      <c r="I30" s="31"/>
+      <c r="G30" s="34"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="32"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="32">
-        <v>0</v>
-      </c>
-      <c r="M30" s="32"/>
-      <c r="N30" s="32"/>
+      <c r="L30" s="34">
+        <v>0</v>
+      </c>
+      <c r="M30" s="34"/>
+      <c r="N30" s="34"/>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1">
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="33">
-        <v>0</v>
-      </c>
-      <c r="C31" s="31"/>
-      <c r="D31" s="31"/>
+      <c r="B31" s="35">
+        <v>0</v>
+      </c>
+      <c r="C31" s="32"/>
+      <c r="D31" s="32"/>
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="33"/>
-      <c r="H31" s="31"/>
-      <c r="I31" s="31"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="32"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="33">
-        <v>0</v>
-      </c>
-      <c r="M31" s="33"/>
-      <c r="N31" s="33"/>
+      <c r="L31" s="35">
+        <v>0</v>
+      </c>
+      <c r="M31" s="35"/>
+      <c r="N31" s="35"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="32">
-        <v>0</v>
-      </c>
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
+      <c r="B32" s="34">
+        <v>0</v>
+      </c>
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="32"/>
-      <c r="H32" s="31"/>
-      <c r="I32" s="31"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="32"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="32">
-        <v>0</v>
-      </c>
-      <c r="M32" s="32"/>
-      <c r="N32" s="32"/>
+      <c r="L32" s="34">
+        <v>0</v>
+      </c>
+      <c r="M32" s="34"/>
+      <c r="N32" s="34"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="33">
-        <v>0</v>
-      </c>
-      <c r="C33" s="31"/>
-      <c r="D33" s="31"/>
+      <c r="B33" s="35">
+        <v>0</v>
+      </c>
+      <c r="C33" s="32"/>
+      <c r="D33" s="32"/>
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="33"/>
-      <c r="H33" s="31"/>
-      <c r="I33" s="31"/>
+      <c r="G33" s="35"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="32"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="33">
-        <v>0</v>
-      </c>
-      <c r="M33" s="33"/>
-      <c r="N33" s="33"/>
+      <c r="L33" s="35">
+        <v>0</v>
+      </c>
+      <c r="M33" s="35"/>
+      <c r="N33" s="35"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="32">
-        <v>0</v>
-      </c>
-      <c r="C34" s="31"/>
-      <c r="D34" s="31"/>
+      <c r="B34" s="34">
+        <v>0</v>
+      </c>
+      <c r="C34" s="32"/>
+      <c r="D34" s="32"/>
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="32"/>
-      <c r="H34" s="31"/>
-      <c r="I34" s="31"/>
+      <c r="G34" s="34"/>
+      <c r="H34" s="32"/>
+      <c r="I34" s="32"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="32">
-        <v>0</v>
-      </c>
-      <c r="M34" s="31"/>
-      <c r="N34" s="31"/>
+      <c r="L34" s="34">
+        <v>0</v>
+      </c>
+      <c r="M34" s="32"/>
+      <c r="N34" s="32"/>
     </row>
     <row r="35" spans="1:14" ht="15" customHeight="1">
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="35">
+      <c r="B35" s="37">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
+      <c r="C35" s="32"/>
+      <c r="D35" s="32"/>
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="35">
+      <c r="G35" s="37">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
-      <c r="H35" s="31"/>
-      <c r="I35" s="31"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="32"/>
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="35">
+      <c r="L35" s="37">
         <f>SUM(L29:L34)</f>
         <v>0</v>
       </c>
-      <c r="M35" s="31"/>
-      <c r="N35" s="31"/>
+      <c r="M35" s="32"/>
+      <c r="N35" s="32"/>
     </row>
     <row r="36" spans="1:14" ht="15" customHeight="1">
       <c r="A36" s="9"/>
@@ -3379,13 +3380,49 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="L11:N11"/>
@@ -3402,49 +3439,13 @@
     <mergeCell ref="K2:N2"/>
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3460,20 +3461,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1">
       <c r="A3" s="9"/>
@@ -3482,57 +3483,57 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="31"/>
-      <c r="C4" s="34" t="s">
+      <c r="B4" s="32"/>
+      <c r="C4" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="31"/>
+      <c r="D4" s="32"/>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1">
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="33"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1">
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="32"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="31"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="33"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1">
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="32"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1">
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="35">
+      <c r="B9" s="37">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="32"/>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1">
       <c r="A10" s="9"/>
@@ -3576,44 +3577,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="36" t="s">
+      <c r="A1" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="F1" s="36" t="s">
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="F1" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="K1" s="36" t="s">
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="K1" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="F2" s="36" t="s">
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="F2" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="G2" s="31"/>
-      <c r="H2" s="31"/>
-      <c r="I2" s="31"/>
-      <c r="K2" s="36" t="s">
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+      <c r="I2" s="32"/>
+      <c r="K2" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="L2" s="31"/>
-      <c r="M2" s="31"/>
-      <c r="N2" s="31"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
     </row>
     <row r="3" spans="1:14" ht="15" customHeight="1">
       <c r="A3" s="9"/>
@@ -3630,219 +3631,219 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="34" t="s">
+      <c r="A4" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="31"/>
-      <c r="C4" s="34" t="s">
+      <c r="B4" s="32"/>
+      <c r="C4" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="D4" s="31"/>
-      <c r="F4" s="34" t="s">
+      <c r="D4" s="32"/>
+      <c r="F4" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="31"/>
-      <c r="H4" s="34" t="s">
+      <c r="G4" s="32"/>
+      <c r="H4" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="I4" s="31"/>
-      <c r="K4" s="34" t="s">
+      <c r="I4" s="32"/>
+      <c r="K4" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="L4" s="31"/>
-      <c r="M4" s="34" t="s">
+      <c r="L4" s="32"/>
+      <c r="M4" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="N4" s="31"/>
+      <c r="N4" s="32"/>
     </row>
     <row r="5" spans="1:14" ht="15" customHeight="1">
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="33"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="31"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="33"/>
-      <c r="H5" s="31"/>
-      <c r="I5" s="31"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="33"/>
-      <c r="M5" s="31"/>
-      <c r="N5" s="31"/>
+      <c r="L5" s="35"/>
+      <c r="M5" s="32"/>
+      <c r="N5" s="32"/>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="32"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="31"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="32"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="32"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="32"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="32"/>
-      <c r="M6" s="31"/>
-      <c r="N6" s="31"/>
+      <c r="L6" s="34"/>
+      <c r="M6" s="32"/>
+      <c r="N6" s="32"/>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="33"/>
-      <c r="C7" s="31"/>
-      <c r="D7" s="31"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="32"/>
+      <c r="D7" s="32"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="33"/>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="32"/>
+      <c r="I7" s="32"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="33"/>
-      <c r="M7" s="31"/>
-      <c r="N7" s="31"/>
+      <c r="L7" s="35"/>
+      <c r="M7" s="32"/>
+      <c r="N7" s="32"/>
     </row>
     <row r="8" spans="1:14" ht="15" customHeight="1">
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="32"/>
-      <c r="C8" s="31"/>
-      <c r="D8" s="31"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="32"/>
-      <c r="H8" s="31"/>
-      <c r="I8" s="31"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="32"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="32"/>
-      <c r="M8" s="31"/>
-      <c r="N8" s="31"/>
+      <c r="L8" s="34"/>
+      <c r="M8" s="32"/>
+      <c r="N8" s="32"/>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1">
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="33"/>
-      <c r="C9" s="31"/>
-      <c r="D9" s="31"/>
+      <c r="B9" s="35"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="32"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="33"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="33"/>
-      <c r="M9" s="31"/>
-      <c r="N9" s="31"/>
+      <c r="L9" s="35"/>
+      <c r="M9" s="32"/>
+      <c r="N9" s="32"/>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="32"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="31"/>
+      <c r="B10" s="34"/>
+      <c r="C10" s="32"/>
+      <c r="D10" s="32"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="31"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="32"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="32"/>
-      <c r="M10" s="31"/>
-      <c r="N10" s="31"/>
+      <c r="L10" s="34"/>
+      <c r="M10" s="32"/>
+      <c r="N10" s="32"/>
     </row>
     <row r="11" spans="1:14" ht="15" customHeight="1">
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="33"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="31"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="32"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="33"/>
-      <c r="H11" s="31"/>
-      <c r="I11" s="31"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="33"/>
-      <c r="M11" s="31"/>
-      <c r="N11" s="31"/>
+      <c r="L11" s="35"/>
+      <c r="M11" s="32"/>
+      <c r="N11" s="32"/>
     </row>
     <row r="12" spans="1:14" ht="15" customHeight="1">
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="32"/>
-      <c r="C12" s="31"/>
-      <c r="D12" s="31"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="32"/>
-      <c r="H12" s="31"/>
-      <c r="I12" s="31"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="32"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="32"/>
-      <c r="M12" s="31"/>
-      <c r="N12" s="31"/>
+      <c r="L12" s="34"/>
+      <c r="M12" s="32"/>
+      <c r="N12" s="32"/>
     </row>
     <row r="13" spans="1:14" ht="15" customHeight="1">
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="35">
+      <c r="B13" s="37">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="31"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="35">
+      <c r="G13" s="37">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
-      <c r="H13" s="31"/>
-      <c r="I13" s="31"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="32"/>
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="35">
+      <c r="L13" s="37">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
-      <c r="M13" s="31"/>
-      <c r="N13" s="31"/>
+      <c r="M13" s="32"/>
+      <c r="N13" s="32"/>
     </row>
     <row r="14" spans="1:14" ht="15" customHeight="1">
       <c r="A14" s="9"/>
@@ -3873,44 +3874,44 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="36" t="s">
+      <c r="A25" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="B25" s="31"/>
-      <c r="C25" s="31"/>
-      <c r="D25" s="31"/>
-      <c r="F25" s="36" t="s">
+      <c r="B25" s="32"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+      <c r="F25" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="G25" s="31"/>
-      <c r="H25" s="31"/>
-      <c r="I25" s="31"/>
-      <c r="K25" s="36" t="s">
+      <c r="G25" s="32"/>
+      <c r="H25" s="32"/>
+      <c r="I25" s="32"/>
+      <c r="K25" s="33" t="s">
         <v>15</v>
       </c>
-      <c r="L25" s="31"/>
-      <c r="M25" s="31"/>
-      <c r="N25" s="31"/>
+      <c r="L25" s="32"/>
+      <c r="M25" s="32"/>
+      <c r="N25" s="32"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="36" t="s">
+      <c r="A26" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="31"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
-      <c r="F26" s="36" t="s">
+      <c r="B26" s="32"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="F26" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
-      <c r="I26" s="31"/>
-      <c r="K26" s="36" t="s">
+      <c r="G26" s="32"/>
+      <c r="H26" s="32"/>
+      <c r="I26" s="32"/>
+      <c r="K26" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="L26" s="31"/>
-      <c r="M26" s="31"/>
-      <c r="N26" s="31"/>
+      <c r="L26" s="32"/>
+      <c r="M26" s="32"/>
+      <c r="N26" s="32"/>
     </row>
     <row r="27" spans="1:14" ht="15" customHeight="1">
       <c r="A27" s="9"/>
@@ -3927,219 +3928,219 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="34" t="s">
+      <c r="A28" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="34" t="s">
+      <c r="B28" s="32"/>
+      <c r="C28" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="D28" s="31"/>
-      <c r="F28" s="34" t="s">
+      <c r="D28" s="32"/>
+      <c r="F28" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="G28" s="31"/>
-      <c r="H28" s="34" t="s">
+      <c r="G28" s="32"/>
+      <c r="H28" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="I28" s="31"/>
-      <c r="K28" s="34" t="s">
+      <c r="I28" s="32"/>
+      <c r="K28" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="L28" s="31"/>
-      <c r="M28" s="34" t="s">
+      <c r="L28" s="32"/>
+      <c r="M28" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="N28" s="31"/>
+      <c r="N28" s="32"/>
     </row>
     <row r="29" spans="1:14" ht="15" customHeight="1">
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="33"/>
-      <c r="C29" s="31"/>
-      <c r="D29" s="31"/>
+      <c r="B29" s="35"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="32"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="33"/>
-      <c r="H29" s="31"/>
-      <c r="I29" s="31"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="32"/>
+      <c r="I29" s="32"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="33"/>
-      <c r="M29" s="31"/>
-      <c r="N29" s="31"/>
+      <c r="L29" s="35"/>
+      <c r="M29" s="32"/>
+      <c r="N29" s="32"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="32"/>
-      <c r="C30" s="31"/>
-      <c r="D30" s="31"/>
+      <c r="B30" s="34"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="32"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="32"/>
-      <c r="H30" s="31"/>
-      <c r="I30" s="31"/>
+      <c r="G30" s="34"/>
+      <c r="H30" s="32"/>
+      <c r="I30" s="32"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="32"/>
-      <c r="M30" s="31"/>
-      <c r="N30" s="31"/>
+      <c r="L30" s="34"/>
+      <c r="M30" s="32"/>
+      <c r="N30" s="32"/>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1">
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="33"/>
-      <c r="C31" s="31"/>
-      <c r="D31" s="31"/>
+      <c r="B31" s="35"/>
+      <c r="C31" s="32"/>
+      <c r="D31" s="32"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="33"/>
-      <c r="H31" s="31"/>
-      <c r="I31" s="31"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="32"/>
+      <c r="I31" s="32"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="33"/>
-      <c r="M31" s="31"/>
-      <c r="N31" s="31"/>
+      <c r="L31" s="35"/>
+      <c r="M31" s="32"/>
+      <c r="N31" s="32"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="32"/>
-      <c r="C32" s="31"/>
-      <c r="D32" s="31"/>
+      <c r="B32" s="34"/>
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="32"/>
-      <c r="H32" s="31"/>
-      <c r="I32" s="31"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="32"/>
+      <c r="I32" s="32"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="32"/>
-      <c r="M32" s="31"/>
-      <c r="N32" s="31"/>
+      <c r="L32" s="34"/>
+      <c r="M32" s="32"/>
+      <c r="N32" s="32"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="33"/>
-      <c r="C33" s="31"/>
-      <c r="D33" s="31"/>
+      <c r="B33" s="35"/>
+      <c r="C33" s="32"/>
+      <c r="D33" s="32"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="33"/>
-      <c r="H33" s="31"/>
-      <c r="I33" s="31"/>
+      <c r="G33" s="35"/>
+      <c r="H33" s="32"/>
+      <c r="I33" s="32"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="33"/>
-      <c r="M33" s="31"/>
-      <c r="N33" s="31"/>
+      <c r="L33" s="35"/>
+      <c r="M33" s="32"/>
+      <c r="N33" s="32"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="32"/>
-      <c r="C34" s="31"/>
-      <c r="D34" s="31"/>
+      <c r="B34" s="34"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="32"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="32"/>
-      <c r="H34" s="31"/>
-      <c r="I34" s="31"/>
+      <c r="G34" s="34"/>
+      <c r="H34" s="32"/>
+      <c r="I34" s="32"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="32"/>
-      <c r="M34" s="31"/>
-      <c r="N34" s="31"/>
+      <c r="L34" s="34"/>
+      <c r="M34" s="32"/>
+      <c r="N34" s="32"/>
     </row>
     <row r="35" spans="1:14" ht="15" customHeight="1">
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="33"/>
-      <c r="C35" s="31"/>
-      <c r="D35" s="31"/>
+      <c r="B35" s="35"/>
+      <c r="C35" s="32"/>
+      <c r="D35" s="32"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="33"/>
-      <c r="H35" s="31"/>
-      <c r="I35" s="31"/>
+      <c r="G35" s="35"/>
+      <c r="H35" s="32"/>
+      <c r="I35" s="32"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="33"/>
-      <c r="M35" s="31"/>
-      <c r="N35" s="31"/>
+      <c r="L35" s="35"/>
+      <c r="M35" s="32"/>
+      <c r="N35" s="32"/>
     </row>
     <row r="36" spans="1:14" ht="15" customHeight="1">
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="32"/>
-      <c r="C36" s="31"/>
-      <c r="D36" s="31"/>
+      <c r="B36" s="34"/>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="32"/>
-      <c r="H36" s="31"/>
-      <c r="I36" s="31"/>
+      <c r="G36" s="34"/>
+      <c r="H36" s="32"/>
+      <c r="I36" s="32"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="32"/>
-      <c r="M36" s="31"/>
-      <c r="N36" s="31"/>
+      <c r="L36" s="34"/>
+      <c r="M36" s="32"/>
+      <c r="N36" s="32"/>
     </row>
     <row r="37" spans="1:14" ht="15" customHeight="1">
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="35">
+      <c r="B37" s="37">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
-      <c r="C37" s="31"/>
-      <c r="D37" s="31"/>
+      <c r="C37" s="32"/>
+      <c r="D37" s="32"/>
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="35">
+      <c r="G37" s="37">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
-      <c r="H37" s="31"/>
-      <c r="I37" s="31"/>
+      <c r="H37" s="32"/>
+      <c r="I37" s="32"/>
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="35">
+      <c r="L37" s="37">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
-      <c r="M37" s="31"/>
-      <c r="N37" s="31"/>
+      <c r="M37" s="32"/>
+      <c r="N37" s="32"/>
     </row>
     <row r="38" spans="1:14" ht="15" customHeight="1">
       <c r="A38" s="9"/>
@@ -4171,6 +4172,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
     <mergeCell ref="L34:N34"/>
     <mergeCell ref="L6:N6"/>
     <mergeCell ref="B33:D33"/>
@@ -4187,68 +4250,6 @@
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4256,7 +4257,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:E96"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="18" style="11" customWidth="1"/>
@@ -4265,7 +4266,7 @@
     <col min="4" max="5" width="14" style="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15">
+    <row r="1" spans="1:6" ht="15">
       <c r="A1" s="17" t="s">
         <v>62</v>
       </c>
@@ -4282,7 +4283,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6">
       <c r="A2" t="s">
         <v>67</v>
       </c>
@@ -4295,11 +4296,12 @@
       <c r="D2" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="18">
+      <c r="E2" s="18"/>
+      <c r="F2" s="18">
         <v>140</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>67</v>
       </c>
@@ -4312,11 +4314,12 @@
       <c r="D3" t="s">
         <v>68</v>
       </c>
-      <c r="E3" s="18">
+      <c r="E3" s="18"/>
+      <c r="F3" s="18">
         <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>67</v>
       </c>
@@ -4329,11 +4332,12 @@
       <c r="D4" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="18">
+      <c r="E4" s="18"/>
+      <c r="F4" s="18">
         <v>140</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>67</v>
       </c>
@@ -4346,11 +4350,12 @@
       <c r="D5" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="18">
+      <c r="E5" s="18"/>
+      <c r="F5" s="18">
         <v>100</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>67</v>
       </c>
@@ -4363,11 +4368,12 @@
       <c r="D6" t="s">
         <v>49</v>
       </c>
-      <c r="E6" s="18">
+      <c r="E6" s="18"/>
+      <c r="F6" s="18">
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>67</v>
       </c>
@@ -4380,11 +4386,12 @@
       <c r="D7" t="s">
         <v>68</v>
       </c>
-      <c r="E7" s="18">
+      <c r="E7" s="18"/>
+      <c r="F7" s="18">
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:6">
       <c r="A8" t="s">
         <v>67</v>
       </c>
@@ -4397,11 +4404,12 @@
       <c r="D8" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="18">
+      <c r="E8" s="18"/>
+      <c r="F8" s="18">
         <v>140</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:6">
       <c r="A9" t="s">
         <v>67</v>
       </c>
@@ -4414,11 +4422,12 @@
       <c r="D9" t="s">
         <v>68</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="18"/>
+      <c r="F9" s="18">
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:6">
       <c r="A10" t="s">
         <v>67</v>
       </c>
@@ -4431,11 +4440,12 @@
       <c r="D10" t="s">
         <v>49</v>
       </c>
-      <c r="E10" s="18">
+      <c r="E10" s="18"/>
+      <c r="F10" s="18">
         <v>70</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>67</v>
       </c>
@@ -4448,11 +4458,12 @@
       <c r="D11" t="s">
         <v>68</v>
       </c>
-      <c r="E11" s="18">
+      <c r="E11" s="18"/>
+      <c r="F11" s="18">
         <v>70</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>67</v>
       </c>
@@ -4465,11 +4476,12 @@
       <c r="D12" t="s">
         <v>49</v>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="18"/>
+      <c r="F12" s="18">
         <v>70</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>67</v>
       </c>
@@ -4482,11 +4494,12 @@
       <c r="D13" t="s">
         <v>68</v>
       </c>
-      <c r="E13" s="18">
+      <c r="E13" s="18"/>
+      <c r="F13" s="18">
         <v>70</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>67</v>
       </c>
@@ -4499,11 +4512,12 @@
       <c r="D14" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="18">
+      <c r="E14" s="18"/>
+      <c r="F14" s="18">
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>67</v>
       </c>
@@ -4516,11 +4530,12 @@
       <c r="D15" t="s">
         <v>68</v>
       </c>
-      <c r="E15" s="18">
+      <c r="E15" s="18"/>
+      <c r="F15" s="18">
         <v>70</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>67</v>
       </c>
@@ -4533,11 +4548,12 @@
       <c r="D16" t="s">
         <v>49</v>
       </c>
-      <c r="E16" s="18">
+      <c r="E16" s="18"/>
+      <c r="F16" s="18">
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:6">
       <c r="A17" t="s">
         <v>67</v>
       </c>
@@ -4550,11 +4566,12 @@
       <c r="D17" t="s">
         <v>68</v>
       </c>
-      <c r="E17" s="18">
+      <c r="E17" s="18"/>
+      <c r="F17" s="18">
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:6">
       <c r="A18" t="s">
         <v>67</v>
       </c>
@@ -4567,11 +4584,12 @@
       <c r="D18" t="s">
         <v>49</v>
       </c>
-      <c r="E18" s="18">
+      <c r="E18" s="18"/>
+      <c r="F18" s="18">
         <v>50</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:6">
       <c r="A19" t="s">
         <v>67</v>
       </c>
@@ -4584,11 +4602,12 @@
       <c r="D19" t="s">
         <v>68</v>
       </c>
-      <c r="E19" s="18">
+      <c r="E19" s="18"/>
+      <c r="F19" s="18">
         <v>50</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:6">
       <c r="A20" t="s">
         <v>67</v>
       </c>
@@ -4601,11 +4620,12 @@
       <c r="D20" t="s">
         <v>49</v>
       </c>
-      <c r="E20" s="18">
+      <c r="E20" s="18"/>
+      <c r="F20" s="18">
         <v>50</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:6">
       <c r="A21" t="s">
         <v>67</v>
       </c>
@@ -4618,11 +4638,12 @@
       <c r="D21" t="s">
         <v>68</v>
       </c>
-      <c r="E21" s="18">
+      <c r="E21" s="18"/>
+      <c r="F21" s="18">
         <v>50</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:6">
       <c r="A22" t="s">
         <v>67</v>
       </c>
@@ -4636,8 +4657,9 @@
         <v>49</v>
       </c>
       <c r="E22" s="18"/>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="F22" s="18"/>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" t="s">
         <v>67</v>
       </c>
@@ -4651,8 +4673,9 @@
         <v>68</v>
       </c>
       <c r="E23" s="18"/>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="F23" s="18"/>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" t="s">
         <v>67</v>
       </c>
@@ -4666,8 +4689,9 @@
         <v>49</v>
       </c>
       <c r="E24" s="18"/>
-    </row>
-    <row r="25" spans="1:5">
+      <c r="F24" s="18"/>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" t="s">
         <v>67</v>
       </c>
@@ -4681,8 +4705,9 @@
         <v>68</v>
       </c>
       <c r="E25" s="18"/>
-    </row>
-    <row r="26" spans="1:5">
+      <c r="F25" s="18"/>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" t="s">
         <v>67</v>
       </c>
@@ -4695,11 +4720,12 @@
       <c r="D26" t="s">
         <v>49</v>
       </c>
-      <c r="E26" s="18">
+      <c r="E26" s="18"/>
+      <c r="F26" s="18">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
         <v>67</v>
       </c>
@@ -4712,11 +4738,12 @@
       <c r="D27" t="s">
         <v>68</v>
       </c>
-      <c r="E27" s="18">
+      <c r="E27" s="18"/>
+      <c r="F27" s="18">
         <v>110</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
         <v>67</v>
       </c>
@@ -4729,11 +4756,12 @@
       <c r="D28" t="s">
         <v>49</v>
       </c>
-      <c r="E28" s="18">
+      <c r="E28" s="18"/>
+      <c r="F28" s="18">
         <v>150</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
         <v>67</v>
       </c>
@@ -4746,11 +4774,12 @@
       <c r="D29" t="s">
         <v>68</v>
       </c>
-      <c r="E29" s="18">
+      <c r="E29" s="18"/>
+      <c r="F29" s="18">
         <v>110</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:6">
       <c r="A30" t="s">
         <v>67</v>
       </c>
@@ -4763,11 +4792,12 @@
       <c r="D30" t="s">
         <v>49</v>
       </c>
-      <c r="E30" s="18">
+      <c r="E30" s="18"/>
+      <c r="F30" s="18">
         <v>150</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:6">
       <c r="A31" t="s">
         <v>67</v>
       </c>
@@ -4780,11 +4810,12 @@
       <c r="D31" t="s">
         <v>68</v>
       </c>
-      <c r="E31" s="18">
+      <c r="E31" s="18"/>
+      <c r="F31" s="18">
         <v>110</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:6">
       <c r="A32" t="s">
         <v>67</v>
       </c>
@@ -4797,11 +4828,12 @@
       <c r="D32" t="s">
         <v>49</v>
       </c>
-      <c r="E32" s="18">
+      <c r="E32" s="18"/>
+      <c r="F32" s="18">
         <v>110</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:6">
       <c r="A33" t="s">
         <v>67</v>
       </c>
@@ -4814,11 +4846,12 @@
       <c r="D33" t="s">
         <v>68</v>
       </c>
-      <c r="E33" s="18">
+      <c r="E33" s="18"/>
+      <c r="F33" s="18">
         <v>110</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:6">
       <c r="A34" t="s">
         <v>67</v>
       </c>
@@ -4831,11 +4864,12 @@
       <c r="D34" t="s">
         <v>49</v>
       </c>
-      <c r="E34" s="18">
+      <c r="E34" s="18"/>
+      <c r="F34" s="18">
         <v>110</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:6">
       <c r="A35" t="s">
         <v>67</v>
       </c>
@@ -4848,11 +4882,12 @@
       <c r="D35" t="s">
         <v>68</v>
       </c>
-      <c r="E35" s="18">
+      <c r="E35" s="18"/>
+      <c r="F35" s="18">
         <v>110</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:6">
       <c r="A36" t="s">
         <v>67</v>
       </c>
@@ -4865,11 +4900,12 @@
       <c r="D36" t="s">
         <v>49</v>
       </c>
-      <c r="E36" s="18">
+      <c r="E36" s="18"/>
+      <c r="F36" s="18">
         <v>110</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:6">
       <c r="A37" t="s">
         <v>67</v>
       </c>
@@ -4882,11 +4918,12 @@
       <c r="D37" t="s">
         <v>68</v>
       </c>
-      <c r="E37" s="18">
+      <c r="E37" s="18"/>
+      <c r="F37" s="18">
         <v>110</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:6">
       <c r="A38" t="s">
         <v>67</v>
       </c>
@@ -4899,11 +4936,12 @@
       <c r="D38" t="s">
         <v>49</v>
       </c>
-      <c r="E38" s="18">
+      <c r="E38" s="18"/>
+      <c r="F38" s="18">
         <v>70</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:6">
       <c r="A39" t="s">
         <v>67</v>
       </c>
@@ -4916,11 +4954,12 @@
       <c r="D39" t="s">
         <v>68</v>
       </c>
-      <c r="E39" s="18">
+      <c r="E39" s="18"/>
+      <c r="F39" s="18">
         <v>70</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:6">
       <c r="A40" t="s">
         <v>67</v>
       </c>
@@ -4933,11 +4972,12 @@
       <c r="D40" t="s">
         <v>49</v>
       </c>
-      <c r="E40" s="18">
+      <c r="E40" s="18"/>
+      <c r="F40" s="18">
         <v>110</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:6">
       <c r="A41" t="s">
         <v>67</v>
       </c>
@@ -4950,11 +4990,12 @@
       <c r="D41" t="s">
         <v>68</v>
       </c>
-      <c r="E41" s="18">
+      <c r="E41" s="18"/>
+      <c r="F41" s="18">
         <v>110</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:6">
       <c r="A42" t="s">
         <v>67</v>
       </c>
@@ -4967,11 +5008,12 @@
       <c r="D42" t="s">
         <v>49</v>
       </c>
-      <c r="E42" s="18">
+      <c r="E42" s="18"/>
+      <c r="F42" s="18">
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:6">
       <c r="A43" t="s">
         <v>67</v>
       </c>
@@ -4984,11 +5026,12 @@
       <c r="D43" t="s">
         <v>68</v>
       </c>
-      <c r="E43" s="18">
+      <c r="E43" s="18"/>
+      <c r="F43" s="18">
         <v>50</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:6">
       <c r="A44" t="s">
         <v>67</v>
       </c>
@@ -5001,11 +5044,12 @@
       <c r="D44" t="s">
         <v>49</v>
       </c>
-      <c r="E44" s="18">
+      <c r="E44" s="18"/>
+      <c r="F44" s="18">
         <v>50</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:6">
       <c r="A45" t="s">
         <v>67</v>
       </c>
@@ -5018,11 +5062,12 @@
       <c r="D45" t="s">
         <v>68</v>
       </c>
-      <c r="E45" s="18">
+      <c r="E45" s="18"/>
+      <c r="F45" s="18">
         <v>50</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:6">
       <c r="A46" t="s">
         <v>67</v>
       </c>
@@ -5036,8 +5081,9 @@
         <v>49</v>
       </c>
       <c r="E46" s="18"/>
-    </row>
-    <row r="47" spans="1:5">
+      <c r="F46" s="18"/>
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47" t="s">
         <v>67</v>
       </c>
@@ -5051,8 +5097,9 @@
         <v>68</v>
       </c>
       <c r="E47" s="18"/>
-    </row>
-    <row r="48" spans="1:5">
+      <c r="F47" s="18"/>
+    </row>
+    <row r="48" spans="1:6">
       <c r="A48" t="s">
         <v>67</v>
       </c>
@@ -5066,8 +5113,9 @@
         <v>49</v>
       </c>
       <c r="E48" s="18"/>
-    </row>
-    <row r="49" spans="1:5">
+      <c r="F48" s="18"/>
+    </row>
+    <row r="49" spans="1:6">
       <c r="A49" t="s">
         <v>67</v>
       </c>
@@ -5081,8 +5129,9 @@
         <v>68</v>
       </c>
       <c r="E49" s="18"/>
-    </row>
-    <row r="50" spans="1:5">
+      <c r="F49" s="18"/>
+    </row>
+    <row r="50" spans="1:6">
       <c r="A50" t="s">
         <v>69</v>
       </c>
@@ -5093,11 +5142,10 @@
         <v>41</v>
       </c>
       <c r="D50"/>
-      <c r="E50" s="19">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5">
+      <c r="E50" s="19"/>
+      <c r="F50" s="30"/>
+    </row>
+    <row r="51" spans="1:6">
       <c r="A51" t="s">
         <v>69</v>
       </c>
@@ -5108,11 +5156,9 @@
         <v>42</v>
       </c>
       <c r="D51"/>
-      <c r="E51" s="19">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5">
+      <c r="E51" s="19"/>
+    </row>
+    <row r="52" spans="1:6">
       <c r="A52" t="s">
         <v>69</v>
       </c>
@@ -5123,11 +5169,9 @@
         <v>43</v>
       </c>
       <c r="D52"/>
-      <c r="E52" s="19">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5">
+      <c r="E52" s="19"/>
+    </row>
+    <row r="53" spans="1:6">
       <c r="A53" t="s">
         <v>69</v>
       </c>
@@ -5138,11 +5182,9 @@
         <v>44</v>
       </c>
       <c r="D53"/>
-      <c r="E53" s="19">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5">
+      <c r="E53" s="19"/>
+    </row>
+    <row r="54" spans="1:6">
       <c r="A54" t="s">
         <v>69</v>
       </c>
@@ -5153,11 +5195,9 @@
         <v>45</v>
       </c>
       <c r="D54"/>
-      <c r="E54" s="19">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5">
+      <c r="E54" s="19"/>
+    </row>
+    <row r="55" spans="1:6">
       <c r="A55" t="s">
         <v>69</v>
       </c>
@@ -5168,11 +5208,9 @@
         <v>46</v>
       </c>
       <c r="D55"/>
-      <c r="E55" s="19">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5">
+      <c r="E55" s="19"/>
+    </row>
+    <row r="56" spans="1:6">
       <c r="A56" t="s">
         <v>69</v>
       </c>
@@ -5185,7 +5223,7 @@
       <c r="D56"/>
       <c r="E56" s="19"/>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:6">
       <c r="A57" t="s">
         <v>69</v>
       </c>
@@ -5198,7 +5236,7 @@
       <c r="D57"/>
       <c r="E57" s="19"/>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:6">
       <c r="A58" t="s">
         <v>69</v>
       </c>
@@ -5211,7 +5249,7 @@
       <c r="D58"/>
       <c r="E58" s="19"/>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:6">
       <c r="A59" t="s">
         <v>69</v>
       </c>
@@ -5224,7 +5262,7 @@
       <c r="D59"/>
       <c r="E59" s="19"/>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:6">
       <c r="A60" t="s">
         <v>69</v>
       </c>
@@ -5237,7 +5275,7 @@
       <c r="D60"/>
       <c r="E60" s="19"/>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:6">
       <c r="A61" t="s">
         <v>69</v>
       </c>
@@ -5250,7 +5288,7 @@
       <c r="D61"/>
       <c r="E61" s="19"/>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:6">
       <c r="A62" t="s">
         <v>69</v>
       </c>
@@ -5261,11 +5299,9 @@
         <v>41</v>
       </c>
       <c r="D62"/>
-      <c r="E62" s="19">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5">
+      <c r="E62" s="19"/>
+    </row>
+    <row r="63" spans="1:6">
       <c r="A63" t="s">
         <v>69</v>
       </c>
@@ -5276,11 +5312,9 @@
         <v>42</v>
       </c>
       <c r="D63"/>
-      <c r="E63" s="19">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5">
+      <c r="E63" s="19"/>
+    </row>
+    <row r="64" spans="1:6">
       <c r="A64" t="s">
         <v>69</v>
       </c>
@@ -5291,9 +5325,7 @@
         <v>43</v>
       </c>
       <c r="D64"/>
-      <c r="E64" s="19">
-        <v>90</v>
-      </c>
+      <c r="E64" s="19"/>
     </row>
     <row r="65" spans="1:5">
       <c r="A65" t="s">
@@ -5306,9 +5338,7 @@
         <v>44</v>
       </c>
       <c r="D65"/>
-      <c r="E65" s="19">
-        <v>90</v>
-      </c>
+      <c r="E65" s="19"/>
     </row>
     <row r="66" spans="1:5">
       <c r="A66" t="s">
@@ -5321,9 +5351,7 @@
         <v>45</v>
       </c>
       <c r="D66"/>
-      <c r="E66" s="20">
-        <v>80</v>
-      </c>
+      <c r="E66" s="20"/>
     </row>
     <row r="67" spans="1:5">
       <c r="A67" t="s">
@@ -5336,9 +5364,7 @@
         <v>46</v>
       </c>
       <c r="D67"/>
-      <c r="E67" s="20">
-        <v>75</v>
-      </c>
+      <c r="E67" s="20"/>
     </row>
     <row r="68" spans="1:5">
       <c r="A68" t="s">

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E758ED2-A383-414E-9F83-96D476301539}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6655F2AE-FF92-4182-91D5-03C15130AED9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -447,9 +447,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -460,6 +457,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2829,19 +2829,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="32"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
-      <c r="K1" s="33" t="s">
+      <c r="K1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="32"/>
@@ -2849,19 +2849,19 @@
       <c r="N1" s="32"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
-      <c r="F2" s="33" t="s">
+      <c r="F2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="32"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="K2" s="33" t="s">
+      <c r="K2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="32"/>
@@ -2883,27 +2883,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="35" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="32"/>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="32"/>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="35" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="32"/>
-      <c r="K4" s="36" t="s">
+      <c r="K4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="32"/>
-      <c r="M4" s="36" t="s">
+      <c r="M4" s="35" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="32"/>
@@ -2912,21 +2912,21 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="35">
-        <v>0</v>
-      </c>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
+      <c r="B5" s="34">
+        <v>0</v>
+      </c>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="35"/>
+      <c r="G5" s="34"/>
       <c r="H5" s="32"/>
       <c r="I5" s="32"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="35"/>
+      <c r="L5" s="34"/>
       <c r="M5" s="32"/>
       <c r="N5" s="32"/>
     </row>
@@ -2934,21 +2934,21 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="34">
-        <v>0</v>
-      </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
+      <c r="B6" s="33">
+        <v>0</v>
+      </c>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="34"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="34"/>
+      <c r="L6" s="33"/>
       <c r="M6" s="32"/>
       <c r="N6" s="32"/>
     </row>
@@ -2956,21 +2956,21 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="35">
-        <v>0</v>
-      </c>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
+      <c r="B7" s="34">
+        <v>0</v>
+      </c>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="35"/>
+      <c r="G7" s="34"/>
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="35"/>
+      <c r="L7" s="34"/>
       <c r="M7" s="32"/>
       <c r="N7" s="32"/>
     </row>
@@ -2978,21 +2978,21 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="34">
-        <v>0</v>
-      </c>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
+      <c r="B8" s="33">
+        <v>0</v>
+      </c>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="34"/>
+      <c r="G8" s="33"/>
       <c r="H8" s="32"/>
       <c r="I8" s="32"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="34"/>
+      <c r="L8" s="33"/>
       <c r="M8" s="32"/>
       <c r="N8" s="32"/>
     </row>
@@ -3000,21 +3000,21 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="35">
-        <v>0</v>
-      </c>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
+      <c r="B9" s="34">
+        <v>0</v>
+      </c>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="35"/>
+      <c r="G9" s="34"/>
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="35"/>
+      <c r="L9" s="34"/>
       <c r="M9" s="32"/>
       <c r="N9" s="32"/>
     </row>
@@ -3022,21 +3022,21 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="34">
-        <v>0</v>
-      </c>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
+      <c r="B10" s="33">
+        <v>0</v>
+      </c>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="34"/>
+      <c r="G10" s="33"/>
       <c r="H10" s="32"/>
       <c r="I10" s="32"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="34"/>
+      <c r="L10" s="33"/>
       <c r="M10" s="32"/>
       <c r="N10" s="32"/>
     </row>
@@ -3044,7 +3044,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="37">
+      <c r="B11" s="36">
         <f>SUM(B5:B10)</f>
         <v>0</v>
       </c>
@@ -3053,7 +3053,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="37">
+      <c r="G11" s="36">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -3062,7 +3062,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="37">
+      <c r="L11" s="36">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -3098,19 +3098,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="33" t="s">
+      <c r="A25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
-      <c r="F25" s="33" t="s">
+      <c r="F25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
       <c r="I25" s="32"/>
-      <c r="K25" s="33" t="s">
+      <c r="K25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="32"/>
@@ -3118,19 +3118,19 @@
       <c r="N25" s="32"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="33" t="s">
+      <c r="A26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
-      <c r="F26" s="33" t="s">
+      <c r="F26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="32"/>
       <c r="H26" s="32"/>
       <c r="I26" s="32"/>
-      <c r="K26" s="33" t="s">
+      <c r="K26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="32"/>
@@ -3152,27 +3152,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="32"/>
-      <c r="C28" s="36" t="s">
+      <c r="C28" s="35" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="32"/>
-      <c r="F28" s="36" t="s">
+      <c r="F28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="32"/>
-      <c r="H28" s="36" t="s">
+      <c r="H28" s="35" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="32"/>
-      <c r="K28" s="36" t="s">
+      <c r="K28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="32"/>
-      <c r="M28" s="36" t="s">
+      <c r="M28" s="35" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="32"/>
@@ -3181,7 +3181,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="35">
+      <c r="B29" s="34">
         <v>0</v>
       </c>
       <c r="C29" s="32"/>
@@ -3189,23 +3189,23 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="35"/>
+      <c r="G29" s="34"/>
       <c r="H29" s="32"/>
       <c r="I29" s="32"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="35">
-        <v>0</v>
-      </c>
-      <c r="M29" s="35"/>
-      <c r="N29" s="35"/>
+      <c r="L29" s="34">
+        <v>0</v>
+      </c>
+      <c r="M29" s="34"/>
+      <c r="N29" s="34"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="34">
+      <c r="B30" s="33">
         <v>0</v>
       </c>
       <c r="C30" s="32"/>
@@ -3213,23 +3213,23 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="34"/>
+      <c r="G30" s="33"/>
       <c r="H30" s="32"/>
       <c r="I30" s="32"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="34">
-        <v>0</v>
-      </c>
-      <c r="M30" s="34"/>
-      <c r="N30" s="34"/>
+      <c r="L30" s="33">
+        <v>0</v>
+      </c>
+      <c r="M30" s="33"/>
+      <c r="N30" s="33"/>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1">
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="35">
+      <c r="B31" s="34">
         <v>0</v>
       </c>
       <c r="C31" s="32"/>
@@ -3237,23 +3237,23 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="35"/>
+      <c r="G31" s="34"/>
       <c r="H31" s="32"/>
       <c r="I31" s="32"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="35">
-        <v>0</v>
-      </c>
-      <c r="M31" s="35"/>
-      <c r="N31" s="35"/>
+      <c r="L31" s="34">
+        <v>0</v>
+      </c>
+      <c r="M31" s="34"/>
+      <c r="N31" s="34"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="34">
+      <c r="B32" s="33">
         <v>0</v>
       </c>
       <c r="C32" s="32"/>
@@ -3261,23 +3261,23 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="34"/>
+      <c r="G32" s="33"/>
       <c r="H32" s="32"/>
       <c r="I32" s="32"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="34">
-        <v>0</v>
-      </c>
-      <c r="M32" s="34"/>
-      <c r="N32" s="34"/>
+      <c r="L32" s="33">
+        <v>0</v>
+      </c>
+      <c r="M32" s="33"/>
+      <c r="N32" s="33"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="35">
+      <c r="B33" s="34">
         <v>0</v>
       </c>
       <c r="C33" s="32"/>
@@ -3285,23 +3285,23 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="35"/>
+      <c r="G33" s="34"/>
       <c r="H33" s="32"/>
       <c r="I33" s="32"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="35">
-        <v>0</v>
-      </c>
-      <c r="M33" s="35"/>
-      <c r="N33" s="35"/>
+      <c r="L33" s="34">
+        <v>0</v>
+      </c>
+      <c r="M33" s="34"/>
+      <c r="N33" s="34"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="34">
+      <c r="B34" s="33">
         <v>0</v>
       </c>
       <c r="C34" s="32"/>
@@ -3309,13 +3309,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="34"/>
+      <c r="G34" s="33"/>
       <c r="H34" s="32"/>
       <c r="I34" s="32"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="34">
+      <c r="L34" s="33">
         <v>0</v>
       </c>
       <c r="M34" s="32"/>
@@ -3325,7 +3325,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="37">
+      <c r="B35" s="36">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -3334,7 +3334,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="37">
+      <c r="G35" s="36">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -3343,7 +3343,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="37">
+      <c r="L35" s="36">
         <f>SUM(L29:L34)</f>
         <v>0</v>
       </c>
@@ -3380,6 +3380,56 @@
     </row>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B10:D10"/>
@@ -3396,56 +3446,6 @@
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="H28:I28"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3461,7 +3461,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
@@ -3469,7 +3469,7 @@
       <c r="D1" s="32"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
@@ -3483,11 +3483,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="35" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="35" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="32"/>
@@ -3496,7 +3496,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="35"/>
+      <c r="B5" s="34"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
     </row>
@@ -3504,7 +3504,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="34"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
     </row>
@@ -3512,7 +3512,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="35"/>
+      <c r="B7" s="34"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
     </row>
@@ -3520,7 +3520,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="34"/>
+      <c r="B8" s="33"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32"/>
     </row>
@@ -3528,7 +3528,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="37">
+      <c r="B9" s="36">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -3577,19 +3577,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="32"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
-      <c r="K1" s="33" t="s">
+      <c r="K1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="32"/>
@@ -3597,19 +3597,19 @@
       <c r="N1" s="32"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
-      <c r="F2" s="33" t="s">
+      <c r="F2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="32"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="K2" s="33" t="s">
+      <c r="K2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="32"/>
@@ -3631,27 +3631,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="35" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="32"/>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="32"/>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="35" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="32"/>
-      <c r="K4" s="36" t="s">
+      <c r="K4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="32"/>
-      <c r="M4" s="36" t="s">
+      <c r="M4" s="35" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="32"/>
@@ -3660,19 +3660,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="35"/>
+      <c r="B5" s="34"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="35"/>
+      <c r="G5" s="34"/>
       <c r="H5" s="32"/>
       <c r="I5" s="32"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="35"/>
+      <c r="L5" s="34"/>
       <c r="M5" s="32"/>
       <c r="N5" s="32"/>
     </row>
@@ -3680,19 +3680,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="34"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="34"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="34"/>
+      <c r="L6" s="33"/>
       <c r="M6" s="32"/>
       <c r="N6" s="32"/>
     </row>
@@ -3700,19 +3700,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="35"/>
+      <c r="B7" s="34"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="35"/>
+      <c r="G7" s="34"/>
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="35"/>
+      <c r="L7" s="34"/>
       <c r="M7" s="32"/>
       <c r="N7" s="32"/>
     </row>
@@ -3720,19 +3720,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="34"/>
+      <c r="B8" s="33"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="34"/>
+      <c r="G8" s="33"/>
       <c r="H8" s="32"/>
       <c r="I8" s="32"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="34"/>
+      <c r="L8" s="33"/>
       <c r="M8" s="32"/>
       <c r="N8" s="32"/>
     </row>
@@ -3740,19 +3740,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="35"/>
+      <c r="B9" s="34"/>
       <c r="C9" s="32"/>
       <c r="D9" s="32"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="35"/>
+      <c r="G9" s="34"/>
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="35"/>
+      <c r="L9" s="34"/>
       <c r="M9" s="32"/>
       <c r="N9" s="32"/>
     </row>
@@ -3760,19 +3760,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="34"/>
+      <c r="B10" s="33"/>
       <c r="C10" s="32"/>
       <c r="D10" s="32"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="34"/>
+      <c r="G10" s="33"/>
       <c r="H10" s="32"/>
       <c r="I10" s="32"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="34"/>
+      <c r="L10" s="33"/>
       <c r="M10" s="32"/>
       <c r="N10" s="32"/>
     </row>
@@ -3780,19 +3780,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="35"/>
+      <c r="B11" s="34"/>
       <c r="C11" s="32"/>
       <c r="D11" s="32"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="35"/>
+      <c r="G11" s="34"/>
       <c r="H11" s="32"/>
       <c r="I11" s="32"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="35"/>
+      <c r="L11" s="34"/>
       <c r="M11" s="32"/>
       <c r="N11" s="32"/>
     </row>
@@ -3800,19 +3800,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="34"/>
+      <c r="B12" s="33"/>
       <c r="C12" s="32"/>
       <c r="D12" s="32"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="34"/>
+      <c r="G12" s="33"/>
       <c r="H12" s="32"/>
       <c r="I12" s="32"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="34"/>
+      <c r="L12" s="33"/>
       <c r="M12" s="32"/>
       <c r="N12" s="32"/>
     </row>
@@ -3820,7 +3820,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="37">
+      <c r="B13" s="36">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3829,7 +3829,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="37">
+      <c r="G13" s="36">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3838,7 +3838,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="37">
+      <c r="L13" s="36">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3874,19 +3874,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="33" t="s">
+      <c r="A25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
-      <c r="F25" s="33" t="s">
+      <c r="F25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
       <c r="I25" s="32"/>
-      <c r="K25" s="33" t="s">
+      <c r="K25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="32"/>
@@ -3894,19 +3894,19 @@
       <c r="N25" s="32"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="33" t="s">
+      <c r="A26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
-      <c r="F26" s="33" t="s">
+      <c r="F26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="32"/>
       <c r="H26" s="32"/>
       <c r="I26" s="32"/>
-      <c r="K26" s="33" t="s">
+      <c r="K26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="32"/>
@@ -3928,27 +3928,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="32"/>
-      <c r="C28" s="36" t="s">
+      <c r="C28" s="35" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="32"/>
-      <c r="F28" s="36" t="s">
+      <c r="F28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="32"/>
-      <c r="H28" s="36" t="s">
+      <c r="H28" s="35" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="32"/>
-      <c r="K28" s="36" t="s">
+      <c r="K28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="32"/>
-      <c r="M28" s="36" t="s">
+      <c r="M28" s="35" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="32"/>
@@ -3957,19 +3957,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="35"/>
+      <c r="B29" s="34"/>
       <c r="C29" s="32"/>
       <c r="D29" s="32"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="35"/>
+      <c r="G29" s="34"/>
       <c r="H29" s="32"/>
       <c r="I29" s="32"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="35"/>
+      <c r="L29" s="34"/>
       <c r="M29" s="32"/>
       <c r="N29" s="32"/>
     </row>
@@ -3977,19 +3977,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="34"/>
+      <c r="B30" s="33"/>
       <c r="C30" s="32"/>
       <c r="D30" s="32"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="34"/>
+      <c r="G30" s="33"/>
       <c r="H30" s="32"/>
       <c r="I30" s="32"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="34"/>
+      <c r="L30" s="33"/>
       <c r="M30" s="32"/>
       <c r="N30" s="32"/>
     </row>
@@ -3997,19 +3997,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="35"/>
+      <c r="B31" s="34"/>
       <c r="C31" s="32"/>
       <c r="D31" s="32"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="35"/>
+      <c r="G31" s="34"/>
       <c r="H31" s="32"/>
       <c r="I31" s="32"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="35"/>
+      <c r="L31" s="34"/>
       <c r="M31" s="32"/>
       <c r="N31" s="32"/>
     </row>
@@ -4017,19 +4017,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="34"/>
+      <c r="B32" s="33"/>
       <c r="C32" s="32"/>
       <c r="D32" s="32"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="34"/>
+      <c r="G32" s="33"/>
       <c r="H32" s="32"/>
       <c r="I32" s="32"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="34"/>
+      <c r="L32" s="33"/>
       <c r="M32" s="32"/>
       <c r="N32" s="32"/>
     </row>
@@ -4037,19 +4037,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="35"/>
+      <c r="B33" s="34"/>
       <c r="C33" s="32"/>
       <c r="D33" s="32"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="35"/>
+      <c r="G33" s="34"/>
       <c r="H33" s="32"/>
       <c r="I33" s="32"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="35"/>
+      <c r="L33" s="34"/>
       <c r="M33" s="32"/>
       <c r="N33" s="32"/>
     </row>
@@ -4057,19 +4057,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="34"/>
+      <c r="B34" s="33"/>
       <c r="C34" s="32"/>
       <c r="D34" s="32"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="34"/>
+      <c r="G34" s="33"/>
       <c r="H34" s="32"/>
       <c r="I34" s="32"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="34"/>
+      <c r="L34" s="33"/>
       <c r="M34" s="32"/>
       <c r="N34" s="32"/>
     </row>
@@ -4077,19 +4077,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="35"/>
+      <c r="B35" s="34"/>
       <c r="C35" s="32"/>
       <c r="D35" s="32"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="35"/>
+      <c r="G35" s="34"/>
       <c r="H35" s="32"/>
       <c r="I35" s="32"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="35"/>
+      <c r="L35" s="34"/>
       <c r="M35" s="32"/>
       <c r="N35" s="32"/>
     </row>
@@ -4097,19 +4097,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="34"/>
+      <c r="B36" s="33"/>
       <c r="C36" s="32"/>
       <c r="D36" s="32"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="34"/>
+      <c r="G36" s="33"/>
       <c r="H36" s="32"/>
       <c r="I36" s="32"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="34"/>
+      <c r="L36" s="33"/>
       <c r="M36" s="32"/>
       <c r="N36" s="32"/>
     </row>
@@ -4117,7 +4117,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="37">
+      <c r="B37" s="36">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -4126,7 +4126,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="37">
+      <c r="G37" s="36">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -4135,7 +4135,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="37">
+      <c r="L37" s="36">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -4172,6 +4172,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
     <mergeCell ref="G36:I36"/>
     <mergeCell ref="L32:N32"/>
     <mergeCell ref="L13:N13"/>
@@ -4188,68 +4250,6 @@
     <mergeCell ref="L33:N33"/>
     <mergeCell ref="L35:N35"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="L9:N9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4296,10 +4296,10 @@
       <c r="D2" t="s">
         <v>49</v>
       </c>
-      <c r="E2" s="18"/>
-      <c r="F2" s="18">
+      <c r="E2" s="18">
         <v>140</v>
       </c>
+      <c r="F2" s="18"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
@@ -4314,10 +4314,10 @@
       <c r="D3" t="s">
         <v>68</v>
       </c>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18">
+      <c r="E3" s="18">
         <v>100</v>
       </c>
+      <c r="F3" s="18"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
@@ -4332,10 +4332,10 @@
       <c r="D4" t="s">
         <v>49</v>
       </c>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18">
+      <c r="E4" s="18">
         <v>140</v>
       </c>
+      <c r="F4" s="18"/>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
@@ -4350,10 +4350,10 @@
       <c r="D5" t="s">
         <v>68</v>
       </c>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18">
+      <c r="E5" s="18">
         <v>100</v>
       </c>
+      <c r="F5" s="18"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
@@ -4368,10 +4368,10 @@
       <c r="D6" t="s">
         <v>49</v>
       </c>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18">
+      <c r="E6" s="18">
         <v>140</v>
       </c>
+      <c r="F6" s="18"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
@@ -4386,10 +4386,10 @@
       <c r="D7" t="s">
         <v>68</v>
       </c>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18">
+      <c r="E7" s="18">
         <v>100</v>
       </c>
+      <c r="F7" s="18"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
@@ -4404,10 +4404,10 @@
       <c r="D8" t="s">
         <v>49</v>
       </c>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18">
+      <c r="E8" s="18">
         <v>140</v>
       </c>
+      <c r="F8" s="18"/>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
@@ -4422,10 +4422,10 @@
       <c r="D9" t="s">
         <v>68</v>
       </c>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18">
+      <c r="E9" s="18">
         <v>100</v>
       </c>
+      <c r="F9" s="18"/>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
@@ -4440,10 +4440,10 @@
       <c r="D10" t="s">
         <v>49</v>
       </c>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18">
+      <c r="E10" s="18">
         <v>70</v>
       </c>
+      <c r="F10" s="18"/>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
@@ -4458,10 +4458,10 @@
       <c r="D11" t="s">
         <v>68</v>
       </c>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18">
+      <c r="E11" s="18">
         <v>70</v>
       </c>
+      <c r="F11" s="18"/>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
@@ -4476,10 +4476,10 @@
       <c r="D12" t="s">
         <v>49</v>
       </c>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18">
+      <c r="E12" s="18">
         <v>70</v>
       </c>
+      <c r="F12" s="18"/>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
@@ -4494,10 +4494,10 @@
       <c r="D13" t="s">
         <v>68</v>
       </c>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18">
+      <c r="E13" s="18">
         <v>70</v>
       </c>
+      <c r="F13" s="18"/>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
@@ -4512,10 +4512,10 @@
       <c r="D14" t="s">
         <v>49</v>
       </c>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18">
+      <c r="E14" s="18">
         <v>70</v>
       </c>
+      <c r="F14" s="18"/>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
@@ -4530,10 +4530,10 @@
       <c r="D15" t="s">
         <v>68</v>
       </c>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18">
+      <c r="E15" s="18">
         <v>70</v>
       </c>
+      <c r="F15" s="18"/>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
@@ -4548,10 +4548,10 @@
       <c r="D16" t="s">
         <v>49</v>
       </c>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18">
+      <c r="E16" s="18">
         <v>70</v>
       </c>
+      <c r="F16" s="18"/>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
@@ -4566,10 +4566,10 @@
       <c r="D17" t="s">
         <v>68</v>
       </c>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18">
+      <c r="E17" s="18">
         <v>70</v>
       </c>
+      <c r="F17" s="18"/>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
@@ -4584,10 +4584,10 @@
       <c r="D18" t="s">
         <v>49</v>
       </c>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18">
+      <c r="E18" s="18">
         <v>50</v>
       </c>
+      <c r="F18" s="18"/>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
@@ -4602,10 +4602,10 @@
       <c r="D19" t="s">
         <v>68</v>
       </c>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18">
+      <c r="E19" s="18">
         <v>50</v>
       </c>
+      <c r="F19" s="18"/>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
@@ -4620,10 +4620,10 @@
       <c r="D20" t="s">
         <v>49</v>
       </c>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18">
+      <c r="E20" s="18">
         <v>50</v>
       </c>
+      <c r="F20" s="18"/>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
@@ -4638,10 +4638,10 @@
       <c r="D21" t="s">
         <v>68</v>
       </c>
-      <c r="E21" s="18"/>
-      <c r="F21" s="18">
+      <c r="E21" s="18">
         <v>50</v>
       </c>
+      <c r="F21" s="18"/>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
@@ -4720,10 +4720,10 @@
       <c r="D26" t="s">
         <v>49</v>
       </c>
-      <c r="E26" s="18"/>
-      <c r="F26" s="18">
-        <v>200</v>
-      </c>
+      <c r="E26" s="18">
+        <v>170</v>
+      </c>
+      <c r="F26" s="18"/>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
@@ -4738,10 +4738,10 @@
       <c r="D27" t="s">
         <v>68</v>
       </c>
-      <c r="E27" s="18"/>
-      <c r="F27" s="18">
+      <c r="E27" s="18">
         <v>110</v>
       </c>
+      <c r="F27" s="18"/>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
@@ -4756,10 +4756,10 @@
       <c r="D28" t="s">
         <v>49</v>
       </c>
-      <c r="E28" s="18"/>
-      <c r="F28" s="18">
+      <c r="E28" s="18">
         <v>150</v>
       </c>
+      <c r="F28" s="18"/>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
@@ -4774,10 +4774,10 @@
       <c r="D29" t="s">
         <v>68</v>
       </c>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18">
+      <c r="E29" s="18">
         <v>110</v>
       </c>
+      <c r="F29" s="18"/>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
@@ -4792,10 +4792,10 @@
       <c r="D30" t="s">
         <v>49</v>
       </c>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18">
+      <c r="E30" s="18">
         <v>150</v>
       </c>
+      <c r="F30" s="18"/>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
@@ -4810,10 +4810,10 @@
       <c r="D31" t="s">
         <v>68</v>
       </c>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18">
+      <c r="E31" s="18">
         <v>110</v>
       </c>
+      <c r="F31" s="18"/>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
@@ -4828,10 +4828,10 @@
       <c r="D32" t="s">
         <v>49</v>
       </c>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18">
+      <c r="E32" s="18">
         <v>110</v>
       </c>
+      <c r="F32" s="18"/>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
@@ -4846,10 +4846,10 @@
       <c r="D33" t="s">
         <v>68</v>
       </c>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18">
+      <c r="E33" s="18">
         <v>110</v>
       </c>
+      <c r="F33" s="18"/>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
@@ -4864,10 +4864,10 @@
       <c r="D34" t="s">
         <v>49</v>
       </c>
-      <c r="E34" s="18"/>
-      <c r="F34" s="18">
+      <c r="E34" s="18">
         <v>110</v>
       </c>
+      <c r="F34" s="18"/>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
@@ -4882,10 +4882,10 @@
       <c r="D35" t="s">
         <v>68</v>
       </c>
-      <c r="E35" s="18"/>
-      <c r="F35" s="18">
+      <c r="E35" s="18">
         <v>110</v>
       </c>
+      <c r="F35" s="18"/>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
@@ -4900,10 +4900,10 @@
       <c r="D36" t="s">
         <v>49</v>
       </c>
-      <c r="E36" s="18"/>
-      <c r="F36" s="18">
+      <c r="E36" s="18">
         <v>110</v>
       </c>
+      <c r="F36" s="18"/>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
@@ -4918,10 +4918,10 @@
       <c r="D37" t="s">
         <v>68</v>
       </c>
-      <c r="E37" s="18"/>
-      <c r="F37" s="18">
+      <c r="E37" s="18">
         <v>110</v>
       </c>
+      <c r="F37" s="18"/>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
@@ -4936,10 +4936,10 @@
       <c r="D38" t="s">
         <v>49</v>
       </c>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18">
+      <c r="E38" s="18">
         <v>70</v>
       </c>
+      <c r="F38" s="18"/>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
@@ -4954,10 +4954,10 @@
       <c r="D39" t="s">
         <v>68</v>
       </c>
-      <c r="E39" s="18"/>
-      <c r="F39" s="18">
+      <c r="E39" s="18">
         <v>70</v>
       </c>
+      <c r="F39" s="18"/>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
@@ -4972,10 +4972,10 @@
       <c r="D40" t="s">
         <v>49</v>
       </c>
-      <c r="E40" s="18"/>
-      <c r="F40" s="18">
+      <c r="E40" s="18">
         <v>110</v>
       </c>
+      <c r="F40" s="18"/>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
@@ -4990,10 +4990,10 @@
       <c r="D41" t="s">
         <v>68</v>
       </c>
-      <c r="E41" s="18"/>
-      <c r="F41" s="18">
+      <c r="E41" s="18">
         <v>110</v>
       </c>
+      <c r="F41" s="18"/>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
@@ -5008,10 +5008,10 @@
       <c r="D42" t="s">
         <v>49</v>
       </c>
-      <c r="E42" s="18"/>
-      <c r="F42" s="18">
+      <c r="E42" s="18">
         <v>50</v>
       </c>
+      <c r="F42" s="18"/>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
@@ -5026,10 +5026,10 @@
       <c r="D43" t="s">
         <v>68</v>
       </c>
-      <c r="E43" s="18"/>
-      <c r="F43" s="18">
+      <c r="E43" s="18">
         <v>50</v>
       </c>
+      <c r="F43" s="18"/>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
@@ -5044,10 +5044,10 @@
       <c r="D44" t="s">
         <v>49</v>
       </c>
-      <c r="E44" s="18"/>
-      <c r="F44" s="18">
+      <c r="E44" s="18">
         <v>50</v>
       </c>
+      <c r="F44" s="18"/>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
@@ -5062,10 +5062,10 @@
       <c r="D45" t="s">
         <v>68</v>
       </c>
-      <c r="E45" s="18"/>
-      <c r="F45" s="18">
+      <c r="E45" s="18">
         <v>50</v>
       </c>
+      <c r="F45" s="18"/>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6655F2AE-FF92-4182-91D5-03C15130AED9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{382A9572-796A-464E-8F48-0064C751F07F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucoes" sheetId="1" r:id="rId1"/>
@@ -447,6 +447,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -457,9 +460,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -801,7 +801,7 @@
       </c>
       <c r="L5" s="14">
         <f>SUM(L6:L7)</f>
-        <v>2000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
@@ -835,7 +835,7 @@
         <v>22</v>
       </c>
       <c r="L7" s="14">
-        <v>1200</v>
+        <v>700</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15" customHeight="1">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="L41" s="13">
         <f>SUM(L5,L8,L11,L14,L17,L20,L23,L26,L29,L32,L35,L38)</f>
-        <v>5913</v>
+        <v>5413</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1">
@@ -2829,19 +2829,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
-      <c r="F1" s="37" t="s">
+      <c r="F1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="32"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
-      <c r="K1" s="37" t="s">
+      <c r="K1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="32"/>
@@ -2849,19 +2849,19 @@
       <c r="N1" s="32"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
-      <c r="F2" s="37" t="s">
+      <c r="F2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="32"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="K2" s="37" t="s">
+      <c r="K2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="32"/>
@@ -2883,27 +2883,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="36" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="32"/>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="32"/>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="36" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="32"/>
-      <c r="K4" s="35" t="s">
+      <c r="K4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="32"/>
-      <c r="M4" s="35" t="s">
+      <c r="M4" s="36" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="32"/>
@@ -2912,21 +2912,21 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="34">
-        <v>0</v>
-      </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
+      <c r="B5" s="35">
+        <v>0</v>
+      </c>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="34"/>
+      <c r="G5" s="35"/>
       <c r="H5" s="32"/>
       <c r="I5" s="32"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="34"/>
+      <c r="L5" s="35"/>
       <c r="M5" s="32"/>
       <c r="N5" s="32"/>
     </row>
@@ -2934,21 +2934,21 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="33">
-        <v>0</v>
-      </c>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
+      <c r="B6" s="34">
+        <v>0</v>
+      </c>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="33"/>
+      <c r="G6" s="34"/>
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="33"/>
+      <c r="L6" s="34"/>
       <c r="M6" s="32"/>
       <c r="N6" s="32"/>
     </row>
@@ -2956,21 +2956,21 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="34">
-        <v>0</v>
-      </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
+      <c r="B7" s="35">
+        <v>0</v>
+      </c>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="34"/>
+      <c r="G7" s="35"/>
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="34"/>
+      <c r="L7" s="35"/>
       <c r="M7" s="32"/>
       <c r="N7" s="32"/>
     </row>
@@ -2978,21 +2978,21 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="33">
-        <v>0</v>
-      </c>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
+      <c r="B8" s="34">
+        <v>0</v>
+      </c>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="33"/>
+      <c r="G8" s="34"/>
       <c r="H8" s="32"/>
       <c r="I8" s="32"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="33"/>
+      <c r="L8" s="34"/>
       <c r="M8" s="32"/>
       <c r="N8" s="32"/>
     </row>
@@ -3000,21 +3000,21 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="34">
-        <v>0</v>
-      </c>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
+      <c r="B9" s="35">
+        <v>0</v>
+      </c>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="34"/>
+      <c r="G9" s="35"/>
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="34"/>
+      <c r="L9" s="35"/>
       <c r="M9" s="32"/>
       <c r="N9" s="32"/>
     </row>
@@ -3022,21 +3022,21 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="33">
-        <v>0</v>
-      </c>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
+      <c r="B10" s="34">
+        <v>0</v>
+      </c>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="33"/>
+      <c r="G10" s="34"/>
       <c r="H10" s="32"/>
       <c r="I10" s="32"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="33"/>
+      <c r="L10" s="34"/>
       <c r="M10" s="32"/>
       <c r="N10" s="32"/>
     </row>
@@ -3044,7 +3044,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="36">
+      <c r="B11" s="37">
         <f>SUM(B5:B10)</f>
         <v>0</v>
       </c>
@@ -3053,7 +3053,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="36">
+      <c r="G11" s="37">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -3062,7 +3062,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="36">
+      <c r="L11" s="37">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -3098,19 +3098,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="37" t="s">
+      <c r="A25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
-      <c r="F25" s="37" t="s">
+      <c r="F25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
       <c r="I25" s="32"/>
-      <c r="K25" s="37" t="s">
+      <c r="K25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="32"/>
@@ -3118,19 +3118,19 @@
       <c r="N25" s="32"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="37" t="s">
+      <c r="A26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
-      <c r="F26" s="37" t="s">
+      <c r="F26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="32"/>
       <c r="H26" s="32"/>
       <c r="I26" s="32"/>
-      <c r="K26" s="37" t="s">
+      <c r="K26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="32"/>
@@ -3152,27 +3152,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="35" t="s">
+      <c r="A28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="32"/>
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="36" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="32"/>
-      <c r="F28" s="35" t="s">
+      <c r="F28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="32"/>
-      <c r="H28" s="35" t="s">
+      <c r="H28" s="36" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="32"/>
-      <c r="K28" s="35" t="s">
+      <c r="K28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="32"/>
-      <c r="M28" s="35" t="s">
+      <c r="M28" s="36" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="32"/>
@@ -3181,7 +3181,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="34">
+      <c r="B29" s="35">
         <v>0</v>
       </c>
       <c r="C29" s="32"/>
@@ -3189,23 +3189,23 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="34"/>
+      <c r="G29" s="35"/>
       <c r="H29" s="32"/>
       <c r="I29" s="32"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="34">
-        <v>0</v>
-      </c>
-      <c r="M29" s="34"/>
-      <c r="N29" s="34"/>
+      <c r="L29" s="35">
+        <v>0</v>
+      </c>
+      <c r="M29" s="35"/>
+      <c r="N29" s="35"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="33">
+      <c r="B30" s="34">
         <v>0</v>
       </c>
       <c r="C30" s="32"/>
@@ -3213,23 +3213,23 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="33"/>
+      <c r="G30" s="34"/>
       <c r="H30" s="32"/>
       <c r="I30" s="32"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="33">
-        <v>0</v>
-      </c>
-      <c r="M30" s="33"/>
-      <c r="N30" s="33"/>
+      <c r="L30" s="34">
+        <v>0</v>
+      </c>
+      <c r="M30" s="34"/>
+      <c r="N30" s="34"/>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1">
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="34">
+      <c r="B31" s="35">
         <v>0</v>
       </c>
       <c r="C31" s="32"/>
@@ -3237,23 +3237,23 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="34"/>
+      <c r="G31" s="35"/>
       <c r="H31" s="32"/>
       <c r="I31" s="32"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="34">
-        <v>0</v>
-      </c>
-      <c r="M31" s="34"/>
-      <c r="N31" s="34"/>
+      <c r="L31" s="35">
+        <v>0</v>
+      </c>
+      <c r="M31" s="35"/>
+      <c r="N31" s="35"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="33">
+      <c r="B32" s="34">
         <v>0</v>
       </c>
       <c r="C32" s="32"/>
@@ -3261,23 +3261,23 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="33"/>
+      <c r="G32" s="34"/>
       <c r="H32" s="32"/>
       <c r="I32" s="32"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="33">
-        <v>0</v>
-      </c>
-      <c r="M32" s="33"/>
-      <c r="N32" s="33"/>
+      <c r="L32" s="34">
+        <v>0</v>
+      </c>
+      <c r="M32" s="34"/>
+      <c r="N32" s="34"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="34">
+      <c r="B33" s="35">
         <v>0</v>
       </c>
       <c r="C33" s="32"/>
@@ -3285,23 +3285,23 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="34"/>
+      <c r="G33" s="35"/>
       <c r="H33" s="32"/>
       <c r="I33" s="32"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="34">
-        <v>0</v>
-      </c>
-      <c r="M33" s="34"/>
-      <c r="N33" s="34"/>
+      <c r="L33" s="35">
+        <v>0</v>
+      </c>
+      <c r="M33" s="35"/>
+      <c r="N33" s="35"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="33">
+      <c r="B34" s="34">
         <v>0</v>
       </c>
       <c r="C34" s="32"/>
@@ -3309,13 +3309,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="33"/>
+      <c r="G34" s="34"/>
       <c r="H34" s="32"/>
       <c r="I34" s="32"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="33">
+      <c r="L34" s="34">
         <v>0</v>
       </c>
       <c r="M34" s="32"/>
@@ -3325,7 +3325,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="36">
+      <c r="B35" s="37">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -3334,7 +3334,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="36">
+      <c r="G35" s="37">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -3343,7 +3343,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="36">
+      <c r="L35" s="37">
         <f>SUM(L29:L34)</f>
         <v>0</v>
       </c>
@@ -3380,13 +3380,49 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="L11:N11"/>
@@ -3403,49 +3439,13 @@
     <mergeCell ref="K2:N2"/>
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3461,7 +3461,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
@@ -3469,7 +3469,7 @@
       <c r="D1" s="32"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
@@ -3483,11 +3483,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="36" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="36" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="32"/>
@@ -3496,7 +3496,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="34"/>
+      <c r="B5" s="35"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
     </row>
@@ -3504,7 +3504,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="33"/>
+      <c r="B6" s="34"/>
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
     </row>
@@ -3512,7 +3512,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="34"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
     </row>
@@ -3520,7 +3520,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="33"/>
+      <c r="B8" s="34"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32"/>
     </row>
@@ -3528,7 +3528,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="36">
+      <c r="B9" s="37">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -3577,19 +3577,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
-      <c r="F1" s="37" t="s">
+      <c r="F1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="32"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
-      <c r="K1" s="37" t="s">
+      <c r="K1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="32"/>
@@ -3597,19 +3597,19 @@
       <c r="N1" s="32"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
-      <c r="F2" s="37" t="s">
+      <c r="F2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="32"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="K2" s="37" t="s">
+      <c r="K2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="32"/>
@@ -3631,27 +3631,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="36" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="32"/>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="32"/>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="36" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="32"/>
-      <c r="K4" s="35" t="s">
+      <c r="K4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="32"/>
-      <c r="M4" s="35" t="s">
+      <c r="M4" s="36" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="32"/>
@@ -3660,19 +3660,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="34"/>
+      <c r="B5" s="35"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="34"/>
+      <c r="G5" s="35"/>
       <c r="H5" s="32"/>
       <c r="I5" s="32"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="34"/>
+      <c r="L5" s="35"/>
       <c r="M5" s="32"/>
       <c r="N5" s="32"/>
     </row>
@@ -3680,19 +3680,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="33"/>
+      <c r="B6" s="34"/>
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="33"/>
+      <c r="G6" s="34"/>
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="33"/>
+      <c r="L6" s="34"/>
       <c r="M6" s="32"/>
       <c r="N6" s="32"/>
     </row>
@@ -3700,19 +3700,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="34"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="34"/>
+      <c r="G7" s="35"/>
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="34"/>
+      <c r="L7" s="35"/>
       <c r="M7" s="32"/>
       <c r="N7" s="32"/>
     </row>
@@ -3720,19 +3720,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="33"/>
+      <c r="B8" s="34"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="33"/>
+      <c r="G8" s="34"/>
       <c r="H8" s="32"/>
       <c r="I8" s="32"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="33"/>
+      <c r="L8" s="34"/>
       <c r="M8" s="32"/>
       <c r="N8" s="32"/>
     </row>
@@ -3740,19 +3740,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="34"/>
+      <c r="B9" s="35"/>
       <c r="C9" s="32"/>
       <c r="D9" s="32"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="34"/>
+      <c r="G9" s="35"/>
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="34"/>
+      <c r="L9" s="35"/>
       <c r="M9" s="32"/>
       <c r="N9" s="32"/>
     </row>
@@ -3760,19 +3760,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="33"/>
+      <c r="B10" s="34"/>
       <c r="C10" s="32"/>
       <c r="D10" s="32"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="33"/>
+      <c r="G10" s="34"/>
       <c r="H10" s="32"/>
       <c r="I10" s="32"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="33"/>
+      <c r="L10" s="34"/>
       <c r="M10" s="32"/>
       <c r="N10" s="32"/>
     </row>
@@ -3780,19 +3780,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="34"/>
+      <c r="B11" s="35"/>
       <c r="C11" s="32"/>
       <c r="D11" s="32"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="34"/>
+      <c r="G11" s="35"/>
       <c r="H11" s="32"/>
       <c r="I11" s="32"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="34"/>
+      <c r="L11" s="35"/>
       <c r="M11" s="32"/>
       <c r="N11" s="32"/>
     </row>
@@ -3800,19 +3800,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="33"/>
+      <c r="B12" s="34"/>
       <c r="C12" s="32"/>
       <c r="D12" s="32"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="33"/>
+      <c r="G12" s="34"/>
       <c r="H12" s="32"/>
       <c r="I12" s="32"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="33"/>
+      <c r="L12" s="34"/>
       <c r="M12" s="32"/>
       <c r="N12" s="32"/>
     </row>
@@ -3820,7 +3820,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="36">
+      <c r="B13" s="37">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3829,7 +3829,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="36">
+      <c r="G13" s="37">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3838,7 +3838,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="36">
+      <c r="L13" s="37">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3874,19 +3874,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="37" t="s">
+      <c r="A25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
-      <c r="F25" s="37" t="s">
+      <c r="F25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
       <c r="I25" s="32"/>
-      <c r="K25" s="37" t="s">
+      <c r="K25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="32"/>
@@ -3894,19 +3894,19 @@
       <c r="N25" s="32"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="37" t="s">
+      <c r="A26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
-      <c r="F26" s="37" t="s">
+      <c r="F26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="32"/>
       <c r="H26" s="32"/>
       <c r="I26" s="32"/>
-      <c r="K26" s="37" t="s">
+      <c r="K26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="32"/>
@@ -3928,27 +3928,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="35" t="s">
+      <c r="A28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="32"/>
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="36" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="32"/>
-      <c r="F28" s="35" t="s">
+      <c r="F28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="32"/>
-      <c r="H28" s="35" t="s">
+      <c r="H28" s="36" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="32"/>
-      <c r="K28" s="35" t="s">
+      <c r="K28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="32"/>
-      <c r="M28" s="35" t="s">
+      <c r="M28" s="36" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="32"/>
@@ -3957,19 +3957,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="34"/>
+      <c r="B29" s="35"/>
       <c r="C29" s="32"/>
       <c r="D29" s="32"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="34"/>
+      <c r="G29" s="35"/>
       <c r="H29" s="32"/>
       <c r="I29" s="32"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="34"/>
+      <c r="L29" s="35"/>
       <c r="M29" s="32"/>
       <c r="N29" s="32"/>
     </row>
@@ -3977,19 +3977,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="33"/>
+      <c r="B30" s="34"/>
       <c r="C30" s="32"/>
       <c r="D30" s="32"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="33"/>
+      <c r="G30" s="34"/>
       <c r="H30" s="32"/>
       <c r="I30" s="32"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="33"/>
+      <c r="L30" s="34"/>
       <c r="M30" s="32"/>
       <c r="N30" s="32"/>
     </row>
@@ -3997,19 +3997,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="34"/>
+      <c r="B31" s="35"/>
       <c r="C31" s="32"/>
       <c r="D31" s="32"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="34"/>
+      <c r="G31" s="35"/>
       <c r="H31" s="32"/>
       <c r="I31" s="32"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="34"/>
+      <c r="L31" s="35"/>
       <c r="M31" s="32"/>
       <c r="N31" s="32"/>
     </row>
@@ -4017,19 +4017,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="33"/>
+      <c r="B32" s="34"/>
       <c r="C32" s="32"/>
       <c r="D32" s="32"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="33"/>
+      <c r="G32" s="34"/>
       <c r="H32" s="32"/>
       <c r="I32" s="32"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="33"/>
+      <c r="L32" s="34"/>
       <c r="M32" s="32"/>
       <c r="N32" s="32"/>
     </row>
@@ -4037,19 +4037,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="34"/>
+      <c r="B33" s="35"/>
       <c r="C33" s="32"/>
       <c r="D33" s="32"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="34"/>
+      <c r="G33" s="35"/>
       <c r="H33" s="32"/>
       <c r="I33" s="32"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="34"/>
+      <c r="L33" s="35"/>
       <c r="M33" s="32"/>
       <c r="N33" s="32"/>
     </row>
@@ -4057,19 +4057,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="33"/>
+      <c r="B34" s="34"/>
       <c r="C34" s="32"/>
       <c r="D34" s="32"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="33"/>
+      <c r="G34" s="34"/>
       <c r="H34" s="32"/>
       <c r="I34" s="32"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="33"/>
+      <c r="L34" s="34"/>
       <c r="M34" s="32"/>
       <c r="N34" s="32"/>
     </row>
@@ -4077,19 +4077,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="34"/>
+      <c r="B35" s="35"/>
       <c r="C35" s="32"/>
       <c r="D35" s="32"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="34"/>
+      <c r="G35" s="35"/>
       <c r="H35" s="32"/>
       <c r="I35" s="32"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="34"/>
+      <c r="L35" s="35"/>
       <c r="M35" s="32"/>
       <c r="N35" s="32"/>
     </row>
@@ -4097,19 +4097,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="33"/>
+      <c r="B36" s="34"/>
       <c r="C36" s="32"/>
       <c r="D36" s="32"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="33"/>
+      <c r="G36" s="34"/>
       <c r="H36" s="32"/>
       <c r="I36" s="32"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="33"/>
+      <c r="L36" s="34"/>
       <c r="M36" s="32"/>
       <c r="N36" s="32"/>
     </row>
@@ -4117,7 +4117,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="36">
+      <c r="B37" s="37">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -4126,7 +4126,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="36">
+      <c r="G37" s="37">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -4135,7 +4135,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="36">
+      <c r="L37" s="37">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -4172,6 +4172,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
     <mergeCell ref="L34:N34"/>
     <mergeCell ref="L6:N6"/>
     <mergeCell ref="B33:D33"/>
@@ -4188,68 +4250,6 @@
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{382A9572-796A-464E-8F48-0064C751F07F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E2DE9BB-4347-41AB-8257-1CF73406444D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -447,9 +447,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -460,6 +457,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -787,7 +787,7 @@
       </c>
       <c r="B5" s="21">
         <f>SUM(B6:B7)</f>
-        <v>800</v>
+        <v>290</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>20</v>
@@ -801,7 +801,7 @@
       </c>
       <c r="L5" s="14">
         <f>SUM(L6:L7)</f>
-        <v>1500</v>
+        <v>630</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
@@ -817,7 +817,7 @@
         <v>21</v>
       </c>
       <c r="L6" s="14">
-        <v>800</v>
+        <v>350</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
@@ -825,7 +825,7 @@
         <v>22</v>
       </c>
       <c r="B7" s="14">
-        <v>800</v>
+        <v>290</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>22</v>
@@ -835,7 +835,7 @@
         <v>22</v>
       </c>
       <c r="L7" s="14">
-        <v>700</v>
+        <v>280</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="15" customHeight="1">
@@ -858,7 +858,7 @@
       </c>
       <c r="L8" s="15">
         <f>SUM(L9:L10)</f>
-        <v>1500</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1">
@@ -874,7 +874,7 @@
         <v>21</v>
       </c>
       <c r="L9" s="15">
-        <v>1500</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
@@ -948,7 +948,7 @@
       </c>
       <c r="B14" s="15">
         <f>SUM(B15:B16)</f>
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>25</v>
@@ -962,7 +962,7 @@
       </c>
       <c r="L14" s="15">
         <f>SUM(L15:L16)</f>
-        <v>800</v>
+        <v>500</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1">
@@ -970,7 +970,7 @@
         <v>21</v>
       </c>
       <c r="B15" s="15">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>21</v>
@@ -980,7 +980,7 @@
         <v>21</v>
       </c>
       <c r="L15" s="15">
-        <v>800</v>
+        <v>500</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="G23" s="14">
         <f>SUM(G24:G25)</f>
-        <v>800</v>
+        <v>0</v>
       </c>
       <c r="K23" s="7" t="s">
         <v>28</v>
@@ -1144,9 +1144,7 @@
       <c r="F25" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G25" s="14">
-        <v>800</v>
-      </c>
+      <c r="G25" s="14"/>
       <c r="K25" s="7" t="s">
         <v>22</v>
       </c>
@@ -1165,7 +1163,7 @@
       </c>
       <c r="G26" s="15">
         <f>SUM(G27:G28)</f>
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="K26" s="9" t="s">
         <v>29</v>
@@ -1185,7 +1183,9 @@
       <c r="F27" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G27" s="15"/>
+      <c r="G27" s="15">
+        <v>73</v>
+      </c>
       <c r="K27" s="9" t="s">
         <v>21</v>
       </c>
@@ -1421,21 +1421,21 @@
       </c>
       <c r="B41" s="13">
         <f>SUM(B5,B8,B11,B14,B17,B20,B23,B26,B29,B32,B35,B38)</f>
-        <v>1360</v>
+        <v>950</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G41" s="13">
         <f>SUM(G5,G8,G11,G14,G17,G20,G23,G26,G29,G32,G35,G38)</f>
-        <v>800</v>
+        <v>73</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="L41" s="13">
         <f>SUM(L5,L8,L11,L14,L17,L20,L23,L26,L29,L32,L35,L38)</f>
-        <v>5413</v>
+        <v>3943</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="L53" s="14">
         <f>SUM(L54:L55)</f>
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="15" customHeight="1">
@@ -1561,7 +1561,7 @@
         <v>21</v>
       </c>
       <c r="L54" s="14">
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="55" spans="1:14" ht="15" customHeight="1">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="L89" s="13">
         <f>SUM(L53,L56,L59,L62,L65,L68,L71,L74,L77,L80,L83,L86)</f>
-        <v>900</v>
+        <v>600</v>
       </c>
     </row>
     <row r="90" spans="1:14" ht="15" customHeight="1">
@@ -2829,19 +2829,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="32"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
-      <c r="K1" s="33" t="s">
+      <c r="K1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="32"/>
@@ -2849,19 +2849,19 @@
       <c r="N1" s="32"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
-      <c r="F2" s="33" t="s">
+      <c r="F2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="32"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="K2" s="33" t="s">
+      <c r="K2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="32"/>
@@ -2883,27 +2883,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="35" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="32"/>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="32"/>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="35" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="32"/>
-      <c r="K4" s="36" t="s">
+      <c r="K4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="32"/>
-      <c r="M4" s="36" t="s">
+      <c r="M4" s="35" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="32"/>
@@ -2912,21 +2912,21 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="35">
-        <v>0</v>
-      </c>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
+      <c r="B5" s="34">
+        <v>0</v>
+      </c>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="35"/>
+      <c r="G5" s="34"/>
       <c r="H5" s="32"/>
       <c r="I5" s="32"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="35"/>
+      <c r="L5" s="34"/>
       <c r="M5" s="32"/>
       <c r="N5" s="32"/>
     </row>
@@ -2934,21 +2934,21 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="34">
-        <v>0</v>
-      </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
+      <c r="B6" s="33">
+        <v>0</v>
+      </c>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="34"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="34"/>
+      <c r="L6" s="33"/>
       <c r="M6" s="32"/>
       <c r="N6" s="32"/>
     </row>
@@ -2956,21 +2956,21 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="35">
-        <v>0</v>
-      </c>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
+      <c r="B7" s="34">
+        <v>0</v>
+      </c>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="35"/>
+      <c r="G7" s="34"/>
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="35"/>
+      <c r="L7" s="34"/>
       <c r="M7" s="32"/>
       <c r="N7" s="32"/>
     </row>
@@ -2978,21 +2978,21 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="34">
-        <v>0</v>
-      </c>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
+      <c r="B8" s="33">
+        <v>0</v>
+      </c>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="34"/>
+      <c r="G8" s="33"/>
       <c r="H8" s="32"/>
       <c r="I8" s="32"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="34"/>
+      <c r="L8" s="33"/>
       <c r="M8" s="32"/>
       <c r="N8" s="32"/>
     </row>
@@ -3000,21 +3000,21 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="35">
-        <v>0</v>
-      </c>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
+      <c r="B9" s="34">
+        <v>0</v>
+      </c>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="35"/>
+      <c r="G9" s="34"/>
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="35"/>
+      <c r="L9" s="34"/>
       <c r="M9" s="32"/>
       <c r="N9" s="32"/>
     </row>
@@ -3022,21 +3022,21 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="34">
-        <v>0</v>
-      </c>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
+      <c r="B10" s="33">
+        <v>0</v>
+      </c>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="34"/>
+      <c r="G10" s="33"/>
       <c r="H10" s="32"/>
       <c r="I10" s="32"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="34"/>
+      <c r="L10" s="33"/>
       <c r="M10" s="32"/>
       <c r="N10" s="32"/>
     </row>
@@ -3044,7 +3044,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="37">
+      <c r="B11" s="36">
         <f>SUM(B5:B10)</f>
         <v>0</v>
       </c>
@@ -3053,7 +3053,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="37">
+      <c r="G11" s="36">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -3062,7 +3062,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="37">
+      <c r="L11" s="36">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -3098,19 +3098,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="33" t="s">
+      <c r="A25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
-      <c r="F25" s="33" t="s">
+      <c r="F25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
       <c r="I25" s="32"/>
-      <c r="K25" s="33" t="s">
+      <c r="K25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="32"/>
@@ -3118,19 +3118,19 @@
       <c r="N25" s="32"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="33" t="s">
+      <c r="A26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
-      <c r="F26" s="33" t="s">
+      <c r="F26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="32"/>
       <c r="H26" s="32"/>
       <c r="I26" s="32"/>
-      <c r="K26" s="33" t="s">
+      <c r="K26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="32"/>
@@ -3152,27 +3152,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="32"/>
-      <c r="C28" s="36" t="s">
+      <c r="C28" s="35" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="32"/>
-      <c r="F28" s="36" t="s">
+      <c r="F28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="32"/>
-      <c r="H28" s="36" t="s">
+      <c r="H28" s="35" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="32"/>
-      <c r="K28" s="36" t="s">
+      <c r="K28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="32"/>
-      <c r="M28" s="36" t="s">
+      <c r="M28" s="35" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="32"/>
@@ -3181,7 +3181,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="35">
+      <c r="B29" s="34">
         <v>0</v>
       </c>
       <c r="C29" s="32"/>
@@ -3189,23 +3189,23 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="35"/>
+      <c r="G29" s="34"/>
       <c r="H29" s="32"/>
       <c r="I29" s="32"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="35">
-        <v>0</v>
-      </c>
-      <c r="M29" s="35"/>
-      <c r="N29" s="35"/>
+      <c r="L29" s="34">
+        <v>0</v>
+      </c>
+      <c r="M29" s="34"/>
+      <c r="N29" s="34"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="34">
+      <c r="B30" s="33">
         <v>0</v>
       </c>
       <c r="C30" s="32"/>
@@ -3213,23 +3213,23 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="34"/>
+      <c r="G30" s="33"/>
       <c r="H30" s="32"/>
       <c r="I30" s="32"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="34">
-        <v>0</v>
-      </c>
-      <c r="M30" s="34"/>
-      <c r="N30" s="34"/>
+      <c r="L30" s="33">
+        <v>0</v>
+      </c>
+      <c r="M30" s="33"/>
+      <c r="N30" s="33"/>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1">
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="35">
+      <c r="B31" s="34">
         <v>0</v>
       </c>
       <c r="C31" s="32"/>
@@ -3237,23 +3237,23 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="35"/>
+      <c r="G31" s="34"/>
       <c r="H31" s="32"/>
       <c r="I31" s="32"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="35">
-        <v>0</v>
-      </c>
-      <c r="M31" s="35"/>
-      <c r="N31" s="35"/>
+      <c r="L31" s="34">
+        <v>0</v>
+      </c>
+      <c r="M31" s="34"/>
+      <c r="N31" s="34"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="34">
+      <c r="B32" s="33">
         <v>0</v>
       </c>
       <c r="C32" s="32"/>
@@ -3261,23 +3261,23 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="34"/>
+      <c r="G32" s="33"/>
       <c r="H32" s="32"/>
       <c r="I32" s="32"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="34">
-        <v>0</v>
-      </c>
-      <c r="M32" s="34"/>
-      <c r="N32" s="34"/>
+      <c r="L32" s="33">
+        <v>0</v>
+      </c>
+      <c r="M32" s="33"/>
+      <c r="N32" s="33"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="35">
+      <c r="B33" s="34">
         <v>0</v>
       </c>
       <c r="C33" s="32"/>
@@ -3285,23 +3285,23 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="35"/>
+      <c r="G33" s="34"/>
       <c r="H33" s="32"/>
       <c r="I33" s="32"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="35">
-        <v>0</v>
-      </c>
-      <c r="M33" s="35"/>
-      <c r="N33" s="35"/>
+      <c r="L33" s="34">
+        <v>0</v>
+      </c>
+      <c r="M33" s="34"/>
+      <c r="N33" s="34"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="34">
+      <c r="B34" s="33">
         <v>0</v>
       </c>
       <c r="C34" s="32"/>
@@ -3309,13 +3309,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="34"/>
+      <c r="G34" s="33"/>
       <c r="H34" s="32"/>
       <c r="I34" s="32"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="34">
+      <c r="L34" s="33">
         <v>0</v>
       </c>
       <c r="M34" s="32"/>
@@ -3325,7 +3325,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="37">
+      <c r="B35" s="36">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -3334,7 +3334,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="37">
+      <c r="G35" s="36">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -3343,7 +3343,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="37">
+      <c r="L35" s="36">
         <f>SUM(L29:L34)</f>
         <v>0</v>
       </c>
@@ -3380,6 +3380,56 @@
     </row>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B10:D10"/>
@@ -3396,56 +3446,6 @@
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="H28:I28"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3461,7 +3461,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
@@ -3469,7 +3469,7 @@
       <c r="D1" s="32"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
@@ -3483,11 +3483,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="35" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="35" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="32"/>
@@ -3496,7 +3496,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="35"/>
+      <c r="B5" s="34"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
     </row>
@@ -3504,7 +3504,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="34"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
     </row>
@@ -3512,7 +3512,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="35"/>
+      <c r="B7" s="34"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
     </row>
@@ -3520,7 +3520,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="34"/>
+      <c r="B8" s="33"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32"/>
     </row>
@@ -3528,7 +3528,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="37">
+      <c r="B9" s="36">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -3577,19 +3577,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="32"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
-      <c r="K1" s="33" t="s">
+      <c r="K1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="32"/>
@@ -3597,19 +3597,19 @@
       <c r="N1" s="32"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
-      <c r="F2" s="33" t="s">
+      <c r="F2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="32"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="K2" s="33" t="s">
+      <c r="K2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="32"/>
@@ -3631,27 +3631,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="35" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="32"/>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="32"/>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="35" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="32"/>
-      <c r="K4" s="36" t="s">
+      <c r="K4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="32"/>
-      <c r="M4" s="36" t="s">
+      <c r="M4" s="35" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="32"/>
@@ -3660,19 +3660,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="35"/>
+      <c r="B5" s="34"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="35"/>
+      <c r="G5" s="34"/>
       <c r="H5" s="32"/>
       <c r="I5" s="32"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="35"/>
+      <c r="L5" s="34"/>
       <c r="M5" s="32"/>
       <c r="N5" s="32"/>
     </row>
@@ -3680,19 +3680,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="34"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="34"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="34"/>
+      <c r="L6" s="33"/>
       <c r="M6" s="32"/>
       <c r="N6" s="32"/>
     </row>
@@ -3700,19 +3700,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="35"/>
+      <c r="B7" s="34"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="35"/>
+      <c r="G7" s="34"/>
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="35"/>
+      <c r="L7" s="34"/>
       <c r="M7" s="32"/>
       <c r="N7" s="32"/>
     </row>
@@ -3720,19 +3720,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="34"/>
+      <c r="B8" s="33"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="34"/>
+      <c r="G8" s="33"/>
       <c r="H8" s="32"/>
       <c r="I8" s="32"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="34"/>
+      <c r="L8" s="33"/>
       <c r="M8" s="32"/>
       <c r="N8" s="32"/>
     </row>
@@ -3740,19 +3740,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="35"/>
+      <c r="B9" s="34"/>
       <c r="C9" s="32"/>
       <c r="D9" s="32"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="35"/>
+      <c r="G9" s="34"/>
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="35"/>
+      <c r="L9" s="34"/>
       <c r="M9" s="32"/>
       <c r="N9" s="32"/>
     </row>
@@ -3760,19 +3760,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="34"/>
+      <c r="B10" s="33"/>
       <c r="C10" s="32"/>
       <c r="D10" s="32"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="34"/>
+      <c r="G10" s="33"/>
       <c r="H10" s="32"/>
       <c r="I10" s="32"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="34"/>
+      <c r="L10" s="33"/>
       <c r="M10" s="32"/>
       <c r="N10" s="32"/>
     </row>
@@ -3780,19 +3780,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="35"/>
+      <c r="B11" s="34"/>
       <c r="C11" s="32"/>
       <c r="D11" s="32"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="35"/>
+      <c r="G11" s="34"/>
       <c r="H11" s="32"/>
       <c r="I11" s="32"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="35"/>
+      <c r="L11" s="34"/>
       <c r="M11" s="32"/>
       <c r="N11" s="32"/>
     </row>
@@ -3800,19 +3800,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="34"/>
+      <c r="B12" s="33"/>
       <c r="C12" s="32"/>
       <c r="D12" s="32"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="34"/>
+      <c r="G12" s="33"/>
       <c r="H12" s="32"/>
       <c r="I12" s="32"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="34"/>
+      <c r="L12" s="33"/>
       <c r="M12" s="32"/>
       <c r="N12" s="32"/>
     </row>
@@ -3820,7 +3820,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="37">
+      <c r="B13" s="36">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3829,7 +3829,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="37">
+      <c r="G13" s="36">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3838,7 +3838,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="37">
+      <c r="L13" s="36">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3874,19 +3874,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="33" t="s">
+      <c r="A25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
-      <c r="F25" s="33" t="s">
+      <c r="F25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
       <c r="I25" s="32"/>
-      <c r="K25" s="33" t="s">
+      <c r="K25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="32"/>
@@ -3894,19 +3894,19 @@
       <c r="N25" s="32"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="33" t="s">
+      <c r="A26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
-      <c r="F26" s="33" t="s">
+      <c r="F26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="32"/>
       <c r="H26" s="32"/>
       <c r="I26" s="32"/>
-      <c r="K26" s="33" t="s">
+      <c r="K26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="32"/>
@@ -3928,27 +3928,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="32"/>
-      <c r="C28" s="36" t="s">
+      <c r="C28" s="35" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="32"/>
-      <c r="F28" s="36" t="s">
+      <c r="F28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="32"/>
-      <c r="H28" s="36" t="s">
+      <c r="H28" s="35" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="32"/>
-      <c r="K28" s="36" t="s">
+      <c r="K28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="32"/>
-      <c r="M28" s="36" t="s">
+      <c r="M28" s="35" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="32"/>
@@ -3957,19 +3957,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="35"/>
+      <c r="B29" s="34"/>
       <c r="C29" s="32"/>
       <c r="D29" s="32"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="35"/>
+      <c r="G29" s="34"/>
       <c r="H29" s="32"/>
       <c r="I29" s="32"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="35"/>
+      <c r="L29" s="34"/>
       <c r="M29" s="32"/>
       <c r="N29" s="32"/>
     </row>
@@ -3977,19 +3977,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="34"/>
+      <c r="B30" s="33"/>
       <c r="C30" s="32"/>
       <c r="D30" s="32"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="34"/>
+      <c r="G30" s="33"/>
       <c r="H30" s="32"/>
       <c r="I30" s="32"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="34"/>
+      <c r="L30" s="33"/>
       <c r="M30" s="32"/>
       <c r="N30" s="32"/>
     </row>
@@ -3997,19 +3997,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="35"/>
+      <c r="B31" s="34"/>
       <c r="C31" s="32"/>
       <c r="D31" s="32"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="35"/>
+      <c r="G31" s="34"/>
       <c r="H31" s="32"/>
       <c r="I31" s="32"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="35"/>
+      <c r="L31" s="34"/>
       <c r="M31" s="32"/>
       <c r="N31" s="32"/>
     </row>
@@ -4017,19 +4017,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="34"/>
+      <c r="B32" s="33"/>
       <c r="C32" s="32"/>
       <c r="D32" s="32"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="34"/>
+      <c r="G32" s="33"/>
       <c r="H32" s="32"/>
       <c r="I32" s="32"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="34"/>
+      <c r="L32" s="33"/>
       <c r="M32" s="32"/>
       <c r="N32" s="32"/>
     </row>
@@ -4037,19 +4037,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="35"/>
+      <c r="B33" s="34"/>
       <c r="C33" s="32"/>
       <c r="D33" s="32"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="35"/>
+      <c r="G33" s="34"/>
       <c r="H33" s="32"/>
       <c r="I33" s="32"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="35"/>
+      <c r="L33" s="34"/>
       <c r="M33" s="32"/>
       <c r="N33" s="32"/>
     </row>
@@ -4057,19 +4057,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="34"/>
+      <c r="B34" s="33"/>
       <c r="C34" s="32"/>
       <c r="D34" s="32"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="34"/>
+      <c r="G34" s="33"/>
       <c r="H34" s="32"/>
       <c r="I34" s="32"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="34"/>
+      <c r="L34" s="33"/>
       <c r="M34" s="32"/>
       <c r="N34" s="32"/>
     </row>
@@ -4077,19 +4077,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="35"/>
+      <c r="B35" s="34"/>
       <c r="C35" s="32"/>
       <c r="D35" s="32"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="35"/>
+      <c r="G35" s="34"/>
       <c r="H35" s="32"/>
       <c r="I35" s="32"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="35"/>
+      <c r="L35" s="34"/>
       <c r="M35" s="32"/>
       <c r="N35" s="32"/>
     </row>
@@ -4097,19 +4097,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="34"/>
+      <c r="B36" s="33"/>
       <c r="C36" s="32"/>
       <c r="D36" s="32"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="34"/>
+      <c r="G36" s="33"/>
       <c r="H36" s="32"/>
       <c r="I36" s="32"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="34"/>
+      <c r="L36" s="33"/>
       <c r="M36" s="32"/>
       <c r="N36" s="32"/>
     </row>
@@ -4117,7 +4117,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="37">
+      <c r="B37" s="36">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -4126,7 +4126,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="37">
+      <c r="G37" s="36">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -4135,7 +4135,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="37">
+      <c r="L37" s="36">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -4172,6 +4172,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
     <mergeCell ref="G36:I36"/>
     <mergeCell ref="L32:N32"/>
     <mergeCell ref="L13:N13"/>
@@ -4188,68 +4250,6 @@
     <mergeCell ref="L33:N33"/>
     <mergeCell ref="L35:N35"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="L9:N9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E2DE9BB-4347-41AB-8257-1CF73406444D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C331591-B1D8-47C8-907D-30D13DEC6F31}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -447,6 +447,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -457,9 +460,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="G97" s="26">
         <f>SUM(G98:G99)</f>
-        <v>1200</v>
+        <v>900</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="15">
@@ -2278,7 +2278,7 @@
         <v>21</v>
       </c>
       <c r="G98" s="26">
-        <v>1200</v>
+        <v>900</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="15">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="G133" s="28">
         <f>SUM(G97,G100,G103,G106,G109,G112,G115,G118,G121,G124,G127,G130)</f>
-        <v>1200</v>
+        <v>900</v>
       </c>
     </row>
   </sheetData>
@@ -2829,19 +2829,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
-      <c r="F1" s="37" t="s">
+      <c r="F1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="32"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
-      <c r="K1" s="37" t="s">
+      <c r="K1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="32"/>
@@ -2849,19 +2849,19 @@
       <c r="N1" s="32"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
-      <c r="F2" s="37" t="s">
+      <c r="F2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="32"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="K2" s="37" t="s">
+      <c r="K2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="32"/>
@@ -2883,27 +2883,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="36" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="32"/>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="32"/>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="36" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="32"/>
-      <c r="K4" s="35" t="s">
+      <c r="K4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="32"/>
-      <c r="M4" s="35" t="s">
+      <c r="M4" s="36" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="32"/>
@@ -2912,21 +2912,21 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="34">
-        <v>0</v>
-      </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
+      <c r="B5" s="35">
+        <v>0</v>
+      </c>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="34"/>
+      <c r="G5" s="35"/>
       <c r="H5" s="32"/>
       <c r="I5" s="32"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="34"/>
+      <c r="L5" s="35"/>
       <c r="M5" s="32"/>
       <c r="N5" s="32"/>
     </row>
@@ -2934,21 +2934,21 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="33">
-        <v>0</v>
-      </c>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
+      <c r="B6" s="34">
+        <v>0</v>
+      </c>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="33"/>
+      <c r="G6" s="34"/>
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="33"/>
+      <c r="L6" s="34"/>
       <c r="M6" s="32"/>
       <c r="N6" s="32"/>
     </row>
@@ -2956,21 +2956,21 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="34">
-        <v>0</v>
-      </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
+      <c r="B7" s="35">
+        <v>0</v>
+      </c>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="34"/>
+      <c r="G7" s="35"/>
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="34"/>
+      <c r="L7" s="35"/>
       <c r="M7" s="32"/>
       <c r="N7" s="32"/>
     </row>
@@ -2978,21 +2978,21 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="33">
-        <v>0</v>
-      </c>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
+      <c r="B8" s="34">
+        <v>0</v>
+      </c>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="33"/>
+      <c r="G8" s="34"/>
       <c r="H8" s="32"/>
       <c r="I8" s="32"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="33"/>
+      <c r="L8" s="34"/>
       <c r="M8" s="32"/>
       <c r="N8" s="32"/>
     </row>
@@ -3000,21 +3000,21 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="34">
-        <v>0</v>
-      </c>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
+      <c r="B9" s="35">
+        <v>0</v>
+      </c>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="34"/>
+      <c r="G9" s="35"/>
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="34"/>
+      <c r="L9" s="35"/>
       <c r="M9" s="32"/>
       <c r="N9" s="32"/>
     </row>
@@ -3022,21 +3022,21 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="33">
-        <v>0</v>
-      </c>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
+      <c r="B10" s="34">
+        <v>0</v>
+      </c>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="33"/>
+      <c r="G10" s="34"/>
       <c r="H10" s="32"/>
       <c r="I10" s="32"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="33"/>
+      <c r="L10" s="34"/>
       <c r="M10" s="32"/>
       <c r="N10" s="32"/>
     </row>
@@ -3044,7 +3044,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="36">
+      <c r="B11" s="37">
         <f>SUM(B5:B10)</f>
         <v>0</v>
       </c>
@@ -3053,7 +3053,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="36">
+      <c r="G11" s="37">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -3062,7 +3062,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="36">
+      <c r="L11" s="37">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -3098,19 +3098,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="37" t="s">
+      <c r="A25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
-      <c r="F25" s="37" t="s">
+      <c r="F25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
       <c r="I25" s="32"/>
-      <c r="K25" s="37" t="s">
+      <c r="K25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="32"/>
@@ -3118,19 +3118,19 @@
       <c r="N25" s="32"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="37" t="s">
+      <c r="A26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
-      <c r="F26" s="37" t="s">
+      <c r="F26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="32"/>
       <c r="H26" s="32"/>
       <c r="I26" s="32"/>
-      <c r="K26" s="37" t="s">
+      <c r="K26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="32"/>
@@ -3152,27 +3152,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="35" t="s">
+      <c r="A28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="32"/>
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="36" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="32"/>
-      <c r="F28" s="35" t="s">
+      <c r="F28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="32"/>
-      <c r="H28" s="35" t="s">
+      <c r="H28" s="36" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="32"/>
-      <c r="K28" s="35" t="s">
+      <c r="K28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="32"/>
-      <c r="M28" s="35" t="s">
+      <c r="M28" s="36" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="32"/>
@@ -3181,7 +3181,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="34">
+      <c r="B29" s="35">
         <v>0</v>
       </c>
       <c r="C29" s="32"/>
@@ -3189,23 +3189,23 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="34"/>
+      <c r="G29" s="35"/>
       <c r="H29" s="32"/>
       <c r="I29" s="32"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="34">
-        <v>0</v>
-      </c>
-      <c r="M29" s="34"/>
-      <c r="N29" s="34"/>
+      <c r="L29" s="35">
+        <v>0</v>
+      </c>
+      <c r="M29" s="35"/>
+      <c r="N29" s="35"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="33">
+      <c r="B30" s="34">
         <v>0</v>
       </c>
       <c r="C30" s="32"/>
@@ -3213,23 +3213,23 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="33"/>
+      <c r="G30" s="34"/>
       <c r="H30" s="32"/>
       <c r="I30" s="32"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="33">
-        <v>0</v>
-      </c>
-      <c r="M30" s="33"/>
-      <c r="N30" s="33"/>
+      <c r="L30" s="34">
+        <v>0</v>
+      </c>
+      <c r="M30" s="34"/>
+      <c r="N30" s="34"/>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1">
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="34">
+      <c r="B31" s="35">
         <v>0</v>
       </c>
       <c r="C31" s="32"/>
@@ -3237,23 +3237,23 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="34"/>
+      <c r="G31" s="35"/>
       <c r="H31" s="32"/>
       <c r="I31" s="32"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="34">
-        <v>0</v>
-      </c>
-      <c r="M31" s="34"/>
-      <c r="N31" s="34"/>
+      <c r="L31" s="35">
+        <v>0</v>
+      </c>
+      <c r="M31" s="35"/>
+      <c r="N31" s="35"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="33">
+      <c r="B32" s="34">
         <v>0</v>
       </c>
       <c r="C32" s="32"/>
@@ -3261,23 +3261,23 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="33"/>
+      <c r="G32" s="34"/>
       <c r="H32" s="32"/>
       <c r="I32" s="32"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="33">
-        <v>0</v>
-      </c>
-      <c r="M32" s="33"/>
-      <c r="N32" s="33"/>
+      <c r="L32" s="34">
+        <v>0</v>
+      </c>
+      <c r="M32" s="34"/>
+      <c r="N32" s="34"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="34">
+      <c r="B33" s="35">
         <v>0</v>
       </c>
       <c r="C33" s="32"/>
@@ -3285,23 +3285,23 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="34"/>
+      <c r="G33" s="35"/>
       <c r="H33" s="32"/>
       <c r="I33" s="32"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="34">
-        <v>0</v>
-      </c>
-      <c r="M33" s="34"/>
-      <c r="N33" s="34"/>
+      <c r="L33" s="35">
+        <v>0</v>
+      </c>
+      <c r="M33" s="35"/>
+      <c r="N33" s="35"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="33">
+      <c r="B34" s="34">
         <v>0</v>
       </c>
       <c r="C34" s="32"/>
@@ -3309,13 +3309,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="33"/>
+      <c r="G34" s="34"/>
       <c r="H34" s="32"/>
       <c r="I34" s="32"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="33">
+      <c r="L34" s="34">
         <v>0</v>
       </c>
       <c r="M34" s="32"/>
@@ -3325,7 +3325,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="36">
+      <c r="B35" s="37">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -3334,7 +3334,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="36">
+      <c r="G35" s="37">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -3343,7 +3343,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="36">
+      <c r="L35" s="37">
         <f>SUM(L29:L34)</f>
         <v>0</v>
       </c>
@@ -3380,13 +3380,49 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="L11:N11"/>
@@ -3403,49 +3439,13 @@
     <mergeCell ref="K2:N2"/>
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3461,7 +3461,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
@@ -3469,7 +3469,7 @@
       <c r="D1" s="32"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
@@ -3483,11 +3483,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="36" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="36" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="32"/>
@@ -3496,7 +3496,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="34"/>
+      <c r="B5" s="35"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
     </row>
@@ -3504,7 +3504,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="33"/>
+      <c r="B6" s="34"/>
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
     </row>
@@ -3512,7 +3512,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="34"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
     </row>
@@ -3520,7 +3520,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="33"/>
+      <c r="B8" s="34"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32"/>
     </row>
@@ -3528,7 +3528,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="36">
+      <c r="B9" s="37">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -3577,19 +3577,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
-      <c r="F1" s="37" t="s">
+      <c r="F1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="32"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
-      <c r="K1" s="37" t="s">
+      <c r="K1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="32"/>
@@ -3597,19 +3597,19 @@
       <c r="N1" s="32"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
-      <c r="F2" s="37" t="s">
+      <c r="F2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="32"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="K2" s="37" t="s">
+      <c r="K2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="32"/>
@@ -3631,27 +3631,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="36" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="32"/>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="32"/>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="36" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="32"/>
-      <c r="K4" s="35" t="s">
+      <c r="K4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="32"/>
-      <c r="M4" s="35" t="s">
+      <c r="M4" s="36" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="32"/>
@@ -3660,19 +3660,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="34"/>
+      <c r="B5" s="35"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="34"/>
+      <c r="G5" s="35"/>
       <c r="H5" s="32"/>
       <c r="I5" s="32"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="34"/>
+      <c r="L5" s="35"/>
       <c r="M5" s="32"/>
       <c r="N5" s="32"/>
     </row>
@@ -3680,19 +3680,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="33"/>
+      <c r="B6" s="34"/>
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="33"/>
+      <c r="G6" s="34"/>
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="33"/>
+      <c r="L6" s="34"/>
       <c r="M6" s="32"/>
       <c r="N6" s="32"/>
     </row>
@@ -3700,19 +3700,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="34"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="34"/>
+      <c r="G7" s="35"/>
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="34"/>
+      <c r="L7" s="35"/>
       <c r="M7" s="32"/>
       <c r="N7" s="32"/>
     </row>
@@ -3720,19 +3720,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="33"/>
+      <c r="B8" s="34"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="33"/>
+      <c r="G8" s="34"/>
       <c r="H8" s="32"/>
       <c r="I8" s="32"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="33"/>
+      <c r="L8" s="34"/>
       <c r="M8" s="32"/>
       <c r="N8" s="32"/>
     </row>
@@ -3740,19 +3740,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="34"/>
+      <c r="B9" s="35"/>
       <c r="C9" s="32"/>
       <c r="D9" s="32"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="34"/>
+      <c r="G9" s="35"/>
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="34"/>
+      <c r="L9" s="35"/>
       <c r="M9" s="32"/>
       <c r="N9" s="32"/>
     </row>
@@ -3760,19 +3760,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="33"/>
+      <c r="B10" s="34"/>
       <c r="C10" s="32"/>
       <c r="D10" s="32"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="33"/>
+      <c r="G10" s="34"/>
       <c r="H10" s="32"/>
       <c r="I10" s="32"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="33"/>
+      <c r="L10" s="34"/>
       <c r="M10" s="32"/>
       <c r="N10" s="32"/>
     </row>
@@ -3780,19 +3780,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="34"/>
+      <c r="B11" s="35"/>
       <c r="C11" s="32"/>
       <c r="D11" s="32"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="34"/>
+      <c r="G11" s="35"/>
       <c r="H11" s="32"/>
       <c r="I11" s="32"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="34"/>
+      <c r="L11" s="35"/>
       <c r="M11" s="32"/>
       <c r="N11" s="32"/>
     </row>
@@ -3800,19 +3800,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="33"/>
+      <c r="B12" s="34"/>
       <c r="C12" s="32"/>
       <c r="D12" s="32"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="33"/>
+      <c r="G12" s="34"/>
       <c r="H12" s="32"/>
       <c r="I12" s="32"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="33"/>
+      <c r="L12" s="34"/>
       <c r="M12" s="32"/>
       <c r="N12" s="32"/>
     </row>
@@ -3820,7 +3820,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="36">
+      <c r="B13" s="37">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3829,7 +3829,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="36">
+      <c r="G13" s="37">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3838,7 +3838,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="36">
+      <c r="L13" s="37">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3874,19 +3874,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="37" t="s">
+      <c r="A25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
-      <c r="F25" s="37" t="s">
+      <c r="F25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
       <c r="I25" s="32"/>
-      <c r="K25" s="37" t="s">
+      <c r="K25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="32"/>
@@ -3894,19 +3894,19 @@
       <c r="N25" s="32"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="37" t="s">
+      <c r="A26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
-      <c r="F26" s="37" t="s">
+      <c r="F26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="32"/>
       <c r="H26" s="32"/>
       <c r="I26" s="32"/>
-      <c r="K26" s="37" t="s">
+      <c r="K26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="32"/>
@@ -3928,27 +3928,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="35" t="s">
+      <c r="A28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="32"/>
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="36" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="32"/>
-      <c r="F28" s="35" t="s">
+      <c r="F28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="32"/>
-      <c r="H28" s="35" t="s">
+      <c r="H28" s="36" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="32"/>
-      <c r="K28" s="35" t="s">
+      <c r="K28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="32"/>
-      <c r="M28" s="35" t="s">
+      <c r="M28" s="36" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="32"/>
@@ -3957,19 +3957,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="34"/>
+      <c r="B29" s="35"/>
       <c r="C29" s="32"/>
       <c r="D29" s="32"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="34"/>
+      <c r="G29" s="35"/>
       <c r="H29" s="32"/>
       <c r="I29" s="32"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="34"/>
+      <c r="L29" s="35"/>
       <c r="M29" s="32"/>
       <c r="N29" s="32"/>
     </row>
@@ -3977,19 +3977,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="33"/>
+      <c r="B30" s="34"/>
       <c r="C30" s="32"/>
       <c r="D30" s="32"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="33"/>
+      <c r="G30" s="34"/>
       <c r="H30" s="32"/>
       <c r="I30" s="32"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="33"/>
+      <c r="L30" s="34"/>
       <c r="M30" s="32"/>
       <c r="N30" s="32"/>
     </row>
@@ -3997,19 +3997,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="34"/>
+      <c r="B31" s="35"/>
       <c r="C31" s="32"/>
       <c r="D31" s="32"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="34"/>
+      <c r="G31" s="35"/>
       <c r="H31" s="32"/>
       <c r="I31" s="32"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="34"/>
+      <c r="L31" s="35"/>
       <c r="M31" s="32"/>
       <c r="N31" s="32"/>
     </row>
@@ -4017,19 +4017,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="33"/>
+      <c r="B32" s="34"/>
       <c r="C32" s="32"/>
       <c r="D32" s="32"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="33"/>
+      <c r="G32" s="34"/>
       <c r="H32" s="32"/>
       <c r="I32" s="32"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="33"/>
+      <c r="L32" s="34"/>
       <c r="M32" s="32"/>
       <c r="N32" s="32"/>
     </row>
@@ -4037,19 +4037,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="34"/>
+      <c r="B33" s="35"/>
       <c r="C33" s="32"/>
       <c r="D33" s="32"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="34"/>
+      <c r="G33" s="35"/>
       <c r="H33" s="32"/>
       <c r="I33" s="32"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="34"/>
+      <c r="L33" s="35"/>
       <c r="M33" s="32"/>
       <c r="N33" s="32"/>
     </row>
@@ -4057,19 +4057,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="33"/>
+      <c r="B34" s="34"/>
       <c r="C34" s="32"/>
       <c r="D34" s="32"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="33"/>
+      <c r="G34" s="34"/>
       <c r="H34" s="32"/>
       <c r="I34" s="32"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="33"/>
+      <c r="L34" s="34"/>
       <c r="M34" s="32"/>
       <c r="N34" s="32"/>
     </row>
@@ -4077,19 +4077,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="34"/>
+      <c r="B35" s="35"/>
       <c r="C35" s="32"/>
       <c r="D35" s="32"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="34"/>
+      <c r="G35" s="35"/>
       <c r="H35" s="32"/>
       <c r="I35" s="32"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="34"/>
+      <c r="L35" s="35"/>
       <c r="M35" s="32"/>
       <c r="N35" s="32"/>
     </row>
@@ -4097,19 +4097,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="33"/>
+      <c r="B36" s="34"/>
       <c r="C36" s="32"/>
       <c r="D36" s="32"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="33"/>
+      <c r="G36" s="34"/>
       <c r="H36" s="32"/>
       <c r="I36" s="32"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="33"/>
+      <c r="L36" s="34"/>
       <c r="M36" s="32"/>
       <c r="N36" s="32"/>
     </row>
@@ -4117,7 +4117,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="36">
+      <c r="B37" s="37">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -4126,7 +4126,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="36">
+      <c r="G37" s="37">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -4135,7 +4135,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="36">
+      <c r="L37" s="37">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -4172,6 +4172,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
     <mergeCell ref="L34:N34"/>
     <mergeCell ref="L6:N6"/>
     <mergeCell ref="B33:D33"/>
@@ -4188,68 +4250,6 @@
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C331591-B1D8-47C8-907D-30D13DEC6F31}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F342E2DB-48CA-4570-8CAB-8C39D7C6893A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -447,9 +447,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -460,6 +457,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="L53" s="14">
         <f>SUM(L54:L55)</f>
-        <v>600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="15" customHeight="1">
@@ -1560,9 +1560,7 @@
       <c r="K54" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="L54" s="14">
-        <v>600</v>
-      </c>
+      <c r="L54" s="14"/>
     </row>
     <row r="55" spans="1:14" ht="15" customHeight="1">
       <c r="A55" s="7" t="s">
@@ -2161,7 +2159,7 @@
       </c>
       <c r="L89" s="13">
         <f>SUM(L53,L56,L59,L62,L65,L68,L71,L74,L77,L80,L83,L86)</f>
-        <v>600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:14" ht="15" customHeight="1">
@@ -2829,19 +2827,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="32"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
-      <c r="K1" s="33" t="s">
+      <c r="K1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="32"/>
@@ -2849,19 +2847,19 @@
       <c r="N1" s="32"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
-      <c r="F2" s="33" t="s">
+      <c r="F2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="32"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="K2" s="33" t="s">
+      <c r="K2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="32"/>
@@ -2883,27 +2881,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="35" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="32"/>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="32"/>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="35" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="32"/>
-      <c r="K4" s="36" t="s">
+      <c r="K4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="32"/>
-      <c r="M4" s="36" t="s">
+      <c r="M4" s="35" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="32"/>
@@ -2912,21 +2910,21 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="35">
-        <v>0</v>
-      </c>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
+      <c r="B5" s="34">
+        <v>0</v>
+      </c>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="35"/>
+      <c r="G5" s="34"/>
       <c r="H5" s="32"/>
       <c r="I5" s="32"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="35"/>
+      <c r="L5" s="34"/>
       <c r="M5" s="32"/>
       <c r="N5" s="32"/>
     </row>
@@ -2934,21 +2932,21 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="34">
-        <v>0</v>
-      </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
+      <c r="B6" s="33">
+        <v>0</v>
+      </c>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="34"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="34"/>
+      <c r="L6" s="33"/>
       <c r="M6" s="32"/>
       <c r="N6" s="32"/>
     </row>
@@ -2956,21 +2954,21 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="35">
-        <v>0</v>
-      </c>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
+      <c r="B7" s="34">
+        <v>0</v>
+      </c>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="35"/>
+      <c r="G7" s="34"/>
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="35"/>
+      <c r="L7" s="34"/>
       <c r="M7" s="32"/>
       <c r="N7" s="32"/>
     </row>
@@ -2978,21 +2976,21 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="34">
-        <v>0</v>
-      </c>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
+      <c r="B8" s="33">
+        <v>0</v>
+      </c>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="34"/>
+      <c r="G8" s="33"/>
       <c r="H8" s="32"/>
       <c r="I8" s="32"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="34"/>
+      <c r="L8" s="33"/>
       <c r="M8" s="32"/>
       <c r="N8" s="32"/>
     </row>
@@ -3000,21 +2998,21 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="35">
-        <v>0</v>
-      </c>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
+      <c r="B9" s="34">
+        <v>0</v>
+      </c>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="35"/>
+      <c r="G9" s="34"/>
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="35"/>
+      <c r="L9" s="34"/>
       <c r="M9" s="32"/>
       <c r="N9" s="32"/>
     </row>
@@ -3022,21 +3020,21 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="34">
-        <v>0</v>
-      </c>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
+      <c r="B10" s="33">
+        <v>0</v>
+      </c>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="34"/>
+      <c r="G10" s="33"/>
       <c r="H10" s="32"/>
       <c r="I10" s="32"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="34"/>
+      <c r="L10" s="33"/>
       <c r="M10" s="32"/>
       <c r="N10" s="32"/>
     </row>
@@ -3044,7 +3042,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="37">
+      <c r="B11" s="36">
         <f>SUM(B5:B10)</f>
         <v>0</v>
       </c>
@@ -3053,7 +3051,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="37">
+      <c r="G11" s="36">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -3062,7 +3060,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="37">
+      <c r="L11" s="36">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -3098,19 +3096,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="33" t="s">
+      <c r="A25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
-      <c r="F25" s="33" t="s">
+      <c r="F25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
       <c r="I25" s="32"/>
-      <c r="K25" s="33" t="s">
+      <c r="K25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="32"/>
@@ -3118,19 +3116,19 @@
       <c r="N25" s="32"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="33" t="s">
+      <c r="A26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
-      <c r="F26" s="33" t="s">
+      <c r="F26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="32"/>
       <c r="H26" s="32"/>
       <c r="I26" s="32"/>
-      <c r="K26" s="33" t="s">
+      <c r="K26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="32"/>
@@ -3152,27 +3150,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="32"/>
-      <c r="C28" s="36" t="s">
+      <c r="C28" s="35" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="32"/>
-      <c r="F28" s="36" t="s">
+      <c r="F28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="32"/>
-      <c r="H28" s="36" t="s">
+      <c r="H28" s="35" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="32"/>
-      <c r="K28" s="36" t="s">
+      <c r="K28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="32"/>
-      <c r="M28" s="36" t="s">
+      <c r="M28" s="35" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="32"/>
@@ -3181,7 +3179,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="35">
+      <c r="B29" s="34">
         <v>0</v>
       </c>
       <c r="C29" s="32"/>
@@ -3189,23 +3187,23 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="35"/>
+      <c r="G29" s="34"/>
       <c r="H29" s="32"/>
       <c r="I29" s="32"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="35">
-        <v>0</v>
-      </c>
-      <c r="M29" s="35"/>
-      <c r="N29" s="35"/>
+      <c r="L29" s="34">
+        <v>0</v>
+      </c>
+      <c r="M29" s="34"/>
+      <c r="N29" s="34"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="34">
+      <c r="B30" s="33">
         <v>0</v>
       </c>
       <c r="C30" s="32"/>
@@ -3213,23 +3211,23 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="34"/>
+      <c r="G30" s="33"/>
       <c r="H30" s="32"/>
       <c r="I30" s="32"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="34">
-        <v>0</v>
-      </c>
-      <c r="M30" s="34"/>
-      <c r="N30" s="34"/>
+      <c r="L30" s="33">
+        <v>0</v>
+      </c>
+      <c r="M30" s="33"/>
+      <c r="N30" s="33"/>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1">
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="35">
+      <c r="B31" s="34">
         <v>0</v>
       </c>
       <c r="C31" s="32"/>
@@ -3237,23 +3235,23 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="35"/>
+      <c r="G31" s="34"/>
       <c r="H31" s="32"/>
       <c r="I31" s="32"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="35">
-        <v>0</v>
-      </c>
-      <c r="M31" s="35"/>
-      <c r="N31" s="35"/>
+      <c r="L31" s="34">
+        <v>0</v>
+      </c>
+      <c r="M31" s="34"/>
+      <c r="N31" s="34"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="34">
+      <c r="B32" s="33">
         <v>0</v>
       </c>
       <c r="C32" s="32"/>
@@ -3261,23 +3259,23 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="34"/>
+      <c r="G32" s="33"/>
       <c r="H32" s="32"/>
       <c r="I32" s="32"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="34">
-        <v>0</v>
-      </c>
-      <c r="M32" s="34"/>
-      <c r="N32" s="34"/>
+      <c r="L32" s="33">
+        <v>0</v>
+      </c>
+      <c r="M32" s="33"/>
+      <c r="N32" s="33"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="35">
+      <c r="B33" s="34">
         <v>0</v>
       </c>
       <c r="C33" s="32"/>
@@ -3285,23 +3283,23 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="35"/>
+      <c r="G33" s="34"/>
       <c r="H33" s="32"/>
       <c r="I33" s="32"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="35">
-        <v>0</v>
-      </c>
-      <c r="M33" s="35"/>
-      <c r="N33" s="35"/>
+      <c r="L33" s="34">
+        <v>0</v>
+      </c>
+      <c r="M33" s="34"/>
+      <c r="N33" s="34"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="34">
+      <c r="B34" s="33">
         <v>0</v>
       </c>
       <c r="C34" s="32"/>
@@ -3309,13 +3307,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="34"/>
+      <c r="G34" s="33"/>
       <c r="H34" s="32"/>
       <c r="I34" s="32"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="34">
+      <c r="L34" s="33">
         <v>0</v>
       </c>
       <c r="M34" s="32"/>
@@ -3325,7 +3323,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="37">
+      <c r="B35" s="36">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -3334,7 +3332,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="37">
+      <c r="G35" s="36">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -3343,7 +3341,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="37">
+      <c r="L35" s="36">
         <f>SUM(L29:L34)</f>
         <v>0</v>
       </c>
@@ -3380,6 +3378,56 @@
     </row>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B10:D10"/>
@@ -3396,56 +3444,6 @@
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="H28:I28"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3461,7 +3459,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
@@ -3469,7 +3467,7 @@
       <c r="D1" s="32"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
@@ -3483,11 +3481,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="35" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="35" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="32"/>
@@ -3496,7 +3494,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="35"/>
+      <c r="B5" s="34"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
     </row>
@@ -3504,7 +3502,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="34"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
     </row>
@@ -3512,7 +3510,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="35"/>
+      <c r="B7" s="34"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
     </row>
@@ -3520,7 +3518,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="34"/>
+      <c r="B8" s="33"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32"/>
     </row>
@@ -3528,7 +3526,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="37">
+      <c r="B9" s="36">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -3577,19 +3575,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="32"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
-      <c r="K1" s="33" t="s">
+      <c r="K1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="32"/>
@@ -3597,19 +3595,19 @@
       <c r="N1" s="32"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
-      <c r="F2" s="33" t="s">
+      <c r="F2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="32"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="K2" s="33" t="s">
+      <c r="K2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="32"/>
@@ -3631,27 +3629,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="35" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="32"/>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="32"/>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="35" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="32"/>
-      <c r="K4" s="36" t="s">
+      <c r="K4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="32"/>
-      <c r="M4" s="36" t="s">
+      <c r="M4" s="35" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="32"/>
@@ -3660,19 +3658,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="35"/>
+      <c r="B5" s="34"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="35"/>
+      <c r="G5" s="34"/>
       <c r="H5" s="32"/>
       <c r="I5" s="32"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="35"/>
+      <c r="L5" s="34"/>
       <c r="M5" s="32"/>
       <c r="N5" s="32"/>
     </row>
@@ -3680,19 +3678,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="34"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="34"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="34"/>
+      <c r="L6" s="33"/>
       <c r="M6" s="32"/>
       <c r="N6" s="32"/>
     </row>
@@ -3700,19 +3698,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="35"/>
+      <c r="B7" s="34"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="35"/>
+      <c r="G7" s="34"/>
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="35"/>
+      <c r="L7" s="34"/>
       <c r="M7" s="32"/>
       <c r="N7" s="32"/>
     </row>
@@ -3720,19 +3718,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="34"/>
+      <c r="B8" s="33"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="34"/>
+      <c r="G8" s="33"/>
       <c r="H8" s="32"/>
       <c r="I8" s="32"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="34"/>
+      <c r="L8" s="33"/>
       <c r="M8" s="32"/>
       <c r="N8" s="32"/>
     </row>
@@ -3740,19 +3738,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="35"/>
+      <c r="B9" s="34"/>
       <c r="C9" s="32"/>
       <c r="D9" s="32"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="35"/>
+      <c r="G9" s="34"/>
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="35"/>
+      <c r="L9" s="34"/>
       <c r="M9" s="32"/>
       <c r="N9" s="32"/>
     </row>
@@ -3760,19 +3758,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="34"/>
+      <c r="B10" s="33"/>
       <c r="C10" s="32"/>
       <c r="D10" s="32"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="34"/>
+      <c r="G10" s="33"/>
       <c r="H10" s="32"/>
       <c r="I10" s="32"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="34"/>
+      <c r="L10" s="33"/>
       <c r="M10" s="32"/>
       <c r="N10" s="32"/>
     </row>
@@ -3780,19 +3778,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="35"/>
+      <c r="B11" s="34"/>
       <c r="C11" s="32"/>
       <c r="D11" s="32"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="35"/>
+      <c r="G11" s="34"/>
       <c r="H11" s="32"/>
       <c r="I11" s="32"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="35"/>
+      <c r="L11" s="34"/>
       <c r="M11" s="32"/>
       <c r="N11" s="32"/>
     </row>
@@ -3800,19 +3798,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="34"/>
+      <c r="B12" s="33"/>
       <c r="C12" s="32"/>
       <c r="D12" s="32"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="34"/>
+      <c r="G12" s="33"/>
       <c r="H12" s="32"/>
       <c r="I12" s="32"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="34"/>
+      <c r="L12" s="33"/>
       <c r="M12" s="32"/>
       <c r="N12" s="32"/>
     </row>
@@ -3820,7 +3818,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="37">
+      <c r="B13" s="36">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3829,7 +3827,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="37">
+      <c r="G13" s="36">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3838,7 +3836,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="37">
+      <c r="L13" s="36">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3874,19 +3872,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="33" t="s">
+      <c r="A25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
-      <c r="F25" s="33" t="s">
+      <c r="F25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
       <c r="I25" s="32"/>
-      <c r="K25" s="33" t="s">
+      <c r="K25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="32"/>
@@ -3894,19 +3892,19 @@
       <c r="N25" s="32"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="33" t="s">
+      <c r="A26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
-      <c r="F26" s="33" t="s">
+      <c r="F26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="32"/>
       <c r="H26" s="32"/>
       <c r="I26" s="32"/>
-      <c r="K26" s="33" t="s">
+      <c r="K26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="32"/>
@@ -3928,27 +3926,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="32"/>
-      <c r="C28" s="36" t="s">
+      <c r="C28" s="35" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="32"/>
-      <c r="F28" s="36" t="s">
+      <c r="F28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="32"/>
-      <c r="H28" s="36" t="s">
+      <c r="H28" s="35" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="32"/>
-      <c r="K28" s="36" t="s">
+      <c r="K28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="32"/>
-      <c r="M28" s="36" t="s">
+      <c r="M28" s="35" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="32"/>
@@ -3957,19 +3955,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="35"/>
+      <c r="B29" s="34"/>
       <c r="C29" s="32"/>
       <c r="D29" s="32"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="35"/>
+      <c r="G29" s="34"/>
       <c r="H29" s="32"/>
       <c r="I29" s="32"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="35"/>
+      <c r="L29" s="34"/>
       <c r="M29" s="32"/>
       <c r="N29" s="32"/>
     </row>
@@ -3977,19 +3975,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="34"/>
+      <c r="B30" s="33"/>
       <c r="C30" s="32"/>
       <c r="D30" s="32"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="34"/>
+      <c r="G30" s="33"/>
       <c r="H30" s="32"/>
       <c r="I30" s="32"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="34"/>
+      <c r="L30" s="33"/>
       <c r="M30" s="32"/>
       <c r="N30" s="32"/>
     </row>
@@ -3997,19 +3995,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="35"/>
+      <c r="B31" s="34"/>
       <c r="C31" s="32"/>
       <c r="D31" s="32"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="35"/>
+      <c r="G31" s="34"/>
       <c r="H31" s="32"/>
       <c r="I31" s="32"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="35"/>
+      <c r="L31" s="34"/>
       <c r="M31" s="32"/>
       <c r="N31" s="32"/>
     </row>
@@ -4017,19 +4015,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="34"/>
+      <c r="B32" s="33"/>
       <c r="C32" s="32"/>
       <c r="D32" s="32"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="34"/>
+      <c r="G32" s="33"/>
       <c r="H32" s="32"/>
       <c r="I32" s="32"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="34"/>
+      <c r="L32" s="33"/>
       <c r="M32" s="32"/>
       <c r="N32" s="32"/>
     </row>
@@ -4037,19 +4035,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="35"/>
+      <c r="B33" s="34"/>
       <c r="C33" s="32"/>
       <c r="D33" s="32"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="35"/>
+      <c r="G33" s="34"/>
       <c r="H33" s="32"/>
       <c r="I33" s="32"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="35"/>
+      <c r="L33" s="34"/>
       <c r="M33" s="32"/>
       <c r="N33" s="32"/>
     </row>
@@ -4057,19 +4055,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="34"/>
+      <c r="B34" s="33"/>
       <c r="C34" s="32"/>
       <c r="D34" s="32"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="34"/>
+      <c r="G34" s="33"/>
       <c r="H34" s="32"/>
       <c r="I34" s="32"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="34"/>
+      <c r="L34" s="33"/>
       <c r="M34" s="32"/>
       <c r="N34" s="32"/>
     </row>
@@ -4077,19 +4075,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="35"/>
+      <c r="B35" s="34"/>
       <c r="C35" s="32"/>
       <c r="D35" s="32"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="35"/>
+      <c r="G35" s="34"/>
       <c r="H35" s="32"/>
       <c r="I35" s="32"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="35"/>
+      <c r="L35" s="34"/>
       <c r="M35" s="32"/>
       <c r="N35" s="32"/>
     </row>
@@ -4097,19 +4095,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="34"/>
+      <c r="B36" s="33"/>
       <c r="C36" s="32"/>
       <c r="D36" s="32"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="34"/>
+      <c r="G36" s="33"/>
       <c r="H36" s="32"/>
       <c r="I36" s="32"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="34"/>
+      <c r="L36" s="33"/>
       <c r="M36" s="32"/>
       <c r="N36" s="32"/>
     </row>
@@ -4117,7 +4115,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="37">
+      <c r="B37" s="36">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -4126,7 +4124,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="37">
+      <c r="G37" s="36">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -4135,7 +4133,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="37">
+      <c r="L37" s="36">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -4172,6 +4170,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
     <mergeCell ref="G36:I36"/>
     <mergeCell ref="L32:N32"/>
     <mergeCell ref="L13:N13"/>
@@ -4188,68 +4248,6 @@
     <mergeCell ref="L33:N33"/>
     <mergeCell ref="L35:N35"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="L9:N9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F342E2DB-48CA-4570-8CAB-8C39D7C6893A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B8C788-A320-40F4-9481-AB09D699CF7E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -447,6 +447,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -457,9 +460,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -787,7 +787,7 @@
       </c>
       <c r="B5" s="21">
         <f>SUM(B6:B7)</f>
-        <v>290</v>
+        <v>670</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>20</v>
@@ -801,7 +801,7 @@
       </c>
       <c r="L5" s="14">
         <f>SUM(L6:L7)</f>
-        <v>630</v>
+        <v>670</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
@@ -817,7 +817,7 @@
         <v>21</v>
       </c>
       <c r="L6" s="14">
-        <v>350</v>
+        <v>670</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
@@ -825,7 +825,7 @@
         <v>22</v>
       </c>
       <c r="B7" s="14">
-        <v>290</v>
+        <v>670</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>22</v>
@@ -834,9 +834,7 @@
       <c r="K7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="L7" s="14">
-        <v>280</v>
-      </c>
+      <c r="L7" s="14"/>
     </row>
     <row r="8" spans="1:14" ht="15" customHeight="1">
       <c r="A8" s="9" t="s">
@@ -858,7 +856,7 @@
       </c>
       <c r="L8" s="15">
         <f>SUM(L9:L10)</f>
-        <v>1200</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1">
@@ -874,7 +872,7 @@
         <v>21</v>
       </c>
       <c r="L9" s="15">
-        <v>1200</v>
+        <v>350</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
@@ -962,7 +960,7 @@
       </c>
       <c r="L14" s="15">
         <f>SUM(L15:L16)</f>
-        <v>500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1">
@@ -979,9 +977,7 @@
       <c r="K15" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L15" s="15">
-        <v>500</v>
-      </c>
+      <c r="L15" s="15"/>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1">
       <c r="A16" s="9" t="s">
@@ -1156,7 +1152,7 @@
       </c>
       <c r="B26" s="15">
         <f>SUM(B27:B28)</f>
-        <v>260</v>
+        <v>0</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>29</v>
@@ -1177,9 +1173,7 @@
       <c r="A27" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B27" s="15">
-        <v>260</v>
-      </c>
+      <c r="B27" s="15"/>
       <c r="F27" s="9" t="s">
         <v>21</v>
       </c>
@@ -1225,7 +1219,7 @@
       </c>
       <c r="L29" s="14">
         <f>SUM(L30:L31)</f>
-        <v>1400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1">
@@ -1241,7 +1235,7 @@
         <v>21</v>
       </c>
       <c r="L30" s="14">
-        <v>1400</v>
+        <v>500</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1">
@@ -1278,7 +1272,7 @@
       </c>
       <c r="L32" s="15">
         <f>SUM(L33:L34)</f>
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
@@ -1294,7 +1288,7 @@
         <v>21</v>
       </c>
       <c r="L33" s="15">
-        <v>13</v>
+        <v>33</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
@@ -1382,7 +1376,7 @@
       </c>
       <c r="L38" s="23">
         <f>SUM(L39:L40)</f>
-        <v>200</v>
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="15" customHeight="1">
@@ -1398,7 +1392,7 @@
         <v>21</v>
       </c>
       <c r="L39" s="15">
-        <v>200</v>
+        <v>30</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="15" customHeight="1">
@@ -1421,7 +1415,7 @@
       </c>
       <c r="B41" s="13">
         <f>SUM(B5,B8,B11,B14,B17,B20,B23,B26,B29,B32,B35,B38)</f>
-        <v>950</v>
+        <v>1070</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>34</v>
@@ -1435,7 +1429,7 @@
       </c>
       <c r="L41" s="13">
         <f>SUM(L5,L8,L11,L14,L17,L20,L23,L26,L29,L32,L35,L38)</f>
-        <v>3943</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1">
@@ -2827,19 +2821,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
-      <c r="F1" s="37" t="s">
+      <c r="F1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="32"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
-      <c r="K1" s="37" t="s">
+      <c r="K1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="32"/>
@@ -2847,19 +2841,19 @@
       <c r="N1" s="32"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
-      <c r="F2" s="37" t="s">
+      <c r="F2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="32"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="K2" s="37" t="s">
+      <c r="K2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="32"/>
@@ -2881,27 +2875,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="36" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="32"/>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="32"/>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="36" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="32"/>
-      <c r="K4" s="35" t="s">
+      <c r="K4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="32"/>
-      <c r="M4" s="35" t="s">
+      <c r="M4" s="36" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="32"/>
@@ -2910,21 +2904,21 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="34">
-        <v>0</v>
-      </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
+      <c r="B5" s="35">
+        <v>0</v>
+      </c>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="34"/>
+      <c r="G5" s="35"/>
       <c r="H5" s="32"/>
       <c r="I5" s="32"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="34"/>
+      <c r="L5" s="35"/>
       <c r="M5" s="32"/>
       <c r="N5" s="32"/>
     </row>
@@ -2932,21 +2926,21 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="33">
-        <v>0</v>
-      </c>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
+      <c r="B6" s="34">
+        <v>0</v>
+      </c>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="33"/>
+      <c r="G6" s="34"/>
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="33"/>
+      <c r="L6" s="34"/>
       <c r="M6" s="32"/>
       <c r="N6" s="32"/>
     </row>
@@ -2954,21 +2948,21 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="34">
-        <v>0</v>
-      </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
+      <c r="B7" s="35">
+        <v>0</v>
+      </c>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="34"/>
+      <c r="G7" s="35"/>
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="34"/>
+      <c r="L7" s="35"/>
       <c r="M7" s="32"/>
       <c r="N7" s="32"/>
     </row>
@@ -2976,21 +2970,21 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="33">
-        <v>0</v>
-      </c>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
+      <c r="B8" s="34">
+        <v>0</v>
+      </c>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="33"/>
+      <c r="G8" s="34"/>
       <c r="H8" s="32"/>
       <c r="I8" s="32"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="33"/>
+      <c r="L8" s="34"/>
       <c r="M8" s="32"/>
       <c r="N8" s="32"/>
     </row>
@@ -2998,21 +2992,21 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="34">
-        <v>0</v>
-      </c>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
+      <c r="B9" s="35">
+        <v>0</v>
+      </c>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="34"/>
+      <c r="G9" s="35"/>
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="34"/>
+      <c r="L9" s="35"/>
       <c r="M9" s="32"/>
       <c r="N9" s="32"/>
     </row>
@@ -3020,21 +3014,21 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="33">
-        <v>0</v>
-      </c>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
+      <c r="B10" s="34">
+        <v>0</v>
+      </c>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="33"/>
+      <c r="G10" s="34"/>
       <c r="H10" s="32"/>
       <c r="I10" s="32"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="33"/>
+      <c r="L10" s="34"/>
       <c r="M10" s="32"/>
       <c r="N10" s="32"/>
     </row>
@@ -3042,7 +3036,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="36">
+      <c r="B11" s="37">
         <f>SUM(B5:B10)</f>
         <v>0</v>
       </c>
@@ -3051,7 +3045,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="36">
+      <c r="G11" s="37">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -3060,7 +3054,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="36">
+      <c r="L11" s="37">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -3096,19 +3090,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="37" t="s">
+      <c r="A25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
-      <c r="F25" s="37" t="s">
+      <c r="F25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
       <c r="I25" s="32"/>
-      <c r="K25" s="37" t="s">
+      <c r="K25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="32"/>
@@ -3116,19 +3110,19 @@
       <c r="N25" s="32"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="37" t="s">
+      <c r="A26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
-      <c r="F26" s="37" t="s">
+      <c r="F26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="32"/>
       <c r="H26" s="32"/>
       <c r="I26" s="32"/>
-      <c r="K26" s="37" t="s">
+      <c r="K26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="32"/>
@@ -3150,27 +3144,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="35" t="s">
+      <c r="A28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="32"/>
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="36" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="32"/>
-      <c r="F28" s="35" t="s">
+      <c r="F28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="32"/>
-      <c r="H28" s="35" t="s">
+      <c r="H28" s="36" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="32"/>
-      <c r="K28" s="35" t="s">
+      <c r="K28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="32"/>
-      <c r="M28" s="35" t="s">
+      <c r="M28" s="36" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="32"/>
@@ -3179,7 +3173,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="34">
+      <c r="B29" s="35">
         <v>0</v>
       </c>
       <c r="C29" s="32"/>
@@ -3187,23 +3181,23 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="34"/>
+      <c r="G29" s="35"/>
       <c r="H29" s="32"/>
       <c r="I29" s="32"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="34">
-        <v>0</v>
-      </c>
-      <c r="M29" s="34"/>
-      <c r="N29" s="34"/>
+      <c r="L29" s="35">
+        <v>0</v>
+      </c>
+      <c r="M29" s="35"/>
+      <c r="N29" s="35"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="33">
+      <c r="B30" s="34">
         <v>0</v>
       </c>
       <c r="C30" s="32"/>
@@ -3211,23 +3205,23 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="33"/>
+      <c r="G30" s="34"/>
       <c r="H30" s="32"/>
       <c r="I30" s="32"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="33">
-        <v>0</v>
-      </c>
-      <c r="M30" s="33"/>
-      <c r="N30" s="33"/>
+      <c r="L30" s="34">
+        <v>0</v>
+      </c>
+      <c r="M30" s="34"/>
+      <c r="N30" s="34"/>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1">
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="34">
+      <c r="B31" s="35">
         <v>0</v>
       </c>
       <c r="C31" s="32"/>
@@ -3235,23 +3229,23 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="34"/>
+      <c r="G31" s="35"/>
       <c r="H31" s="32"/>
       <c r="I31" s="32"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="34">
-        <v>0</v>
-      </c>
-      <c r="M31" s="34"/>
-      <c r="N31" s="34"/>
+      <c r="L31" s="35">
+        <v>0</v>
+      </c>
+      <c r="M31" s="35"/>
+      <c r="N31" s="35"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="33">
+      <c r="B32" s="34">
         <v>0</v>
       </c>
       <c r="C32" s="32"/>
@@ -3259,23 +3253,23 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="33"/>
+      <c r="G32" s="34"/>
       <c r="H32" s="32"/>
       <c r="I32" s="32"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="33">
-        <v>0</v>
-      </c>
-      <c r="M32" s="33"/>
-      <c r="N32" s="33"/>
+      <c r="L32" s="34">
+        <v>0</v>
+      </c>
+      <c r="M32" s="34"/>
+      <c r="N32" s="34"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="34">
+      <c r="B33" s="35">
         <v>0</v>
       </c>
       <c r="C33" s="32"/>
@@ -3283,23 +3277,23 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="34"/>
+      <c r="G33" s="35"/>
       <c r="H33" s="32"/>
       <c r="I33" s="32"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="34">
-        <v>0</v>
-      </c>
-      <c r="M33" s="34"/>
-      <c r="N33" s="34"/>
+      <c r="L33" s="35">
+        <v>0</v>
+      </c>
+      <c r="M33" s="35"/>
+      <c r="N33" s="35"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="33">
+      <c r="B34" s="34">
         <v>0</v>
       </c>
       <c r="C34" s="32"/>
@@ -3307,13 +3301,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="33"/>
+      <c r="G34" s="34"/>
       <c r="H34" s="32"/>
       <c r="I34" s="32"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="33">
+      <c r="L34" s="34">
         <v>0</v>
       </c>
       <c r="M34" s="32"/>
@@ -3323,7 +3317,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="36">
+      <c r="B35" s="37">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -3332,7 +3326,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="36">
+      <c r="G35" s="37">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -3341,7 +3335,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="36">
+      <c r="L35" s="37">
         <f>SUM(L29:L34)</f>
         <v>0</v>
       </c>
@@ -3378,13 +3372,49 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="L11:N11"/>
@@ -3401,49 +3431,13 @@
     <mergeCell ref="K2:N2"/>
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3459,7 +3453,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
@@ -3467,7 +3461,7 @@
       <c r="D1" s="32"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
@@ -3481,11 +3475,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="36" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="36" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="32"/>
@@ -3494,7 +3488,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="34"/>
+      <c r="B5" s="35"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
     </row>
@@ -3502,7 +3496,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="33"/>
+      <c r="B6" s="34"/>
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
     </row>
@@ -3510,7 +3504,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="34"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
     </row>
@@ -3518,7 +3512,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="33"/>
+      <c r="B8" s="34"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32"/>
     </row>
@@ -3526,7 +3520,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="36">
+      <c r="B9" s="37">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -3575,19 +3569,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
-      <c r="F1" s="37" t="s">
+      <c r="F1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="32"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
-      <c r="K1" s="37" t="s">
+      <c r="K1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="32"/>
@@ -3595,19 +3589,19 @@
       <c r="N1" s="32"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
-      <c r="F2" s="37" t="s">
+      <c r="F2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="32"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="K2" s="37" t="s">
+      <c r="K2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="32"/>
@@ -3629,27 +3623,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="36" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="32"/>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="32"/>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="36" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="32"/>
-      <c r="K4" s="35" t="s">
+      <c r="K4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="32"/>
-      <c r="M4" s="35" t="s">
+      <c r="M4" s="36" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="32"/>
@@ -3658,19 +3652,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="34"/>
+      <c r="B5" s="35"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="34"/>
+      <c r="G5" s="35"/>
       <c r="H5" s="32"/>
       <c r="I5" s="32"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="34"/>
+      <c r="L5" s="35"/>
       <c r="M5" s="32"/>
       <c r="N5" s="32"/>
     </row>
@@ -3678,19 +3672,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="33"/>
+      <c r="B6" s="34"/>
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="33"/>
+      <c r="G6" s="34"/>
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="33"/>
+      <c r="L6" s="34"/>
       <c r="M6" s="32"/>
       <c r="N6" s="32"/>
     </row>
@@ -3698,19 +3692,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="34"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="34"/>
+      <c r="G7" s="35"/>
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="34"/>
+      <c r="L7" s="35"/>
       <c r="M7" s="32"/>
       <c r="N7" s="32"/>
     </row>
@@ -3718,19 +3712,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="33"/>
+      <c r="B8" s="34"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="33"/>
+      <c r="G8" s="34"/>
       <c r="H8" s="32"/>
       <c r="I8" s="32"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="33"/>
+      <c r="L8" s="34"/>
       <c r="M8" s="32"/>
       <c r="N8" s="32"/>
     </row>
@@ -3738,19 +3732,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="34"/>
+      <c r="B9" s="35"/>
       <c r="C9" s="32"/>
       <c r="D9" s="32"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="34"/>
+      <c r="G9" s="35"/>
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="34"/>
+      <c r="L9" s="35"/>
       <c r="M9" s="32"/>
       <c r="N9" s="32"/>
     </row>
@@ -3758,19 +3752,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="33"/>
+      <c r="B10" s="34"/>
       <c r="C10" s="32"/>
       <c r="D10" s="32"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="33"/>
+      <c r="G10" s="34"/>
       <c r="H10" s="32"/>
       <c r="I10" s="32"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="33"/>
+      <c r="L10" s="34"/>
       <c r="M10" s="32"/>
       <c r="N10" s="32"/>
     </row>
@@ -3778,19 +3772,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="34"/>
+      <c r="B11" s="35"/>
       <c r="C11" s="32"/>
       <c r="D11" s="32"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="34"/>
+      <c r="G11" s="35"/>
       <c r="H11" s="32"/>
       <c r="I11" s="32"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="34"/>
+      <c r="L11" s="35"/>
       <c r="M11" s="32"/>
       <c r="N11" s="32"/>
     </row>
@@ -3798,19 +3792,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="33"/>
+      <c r="B12" s="34"/>
       <c r="C12" s="32"/>
       <c r="D12" s="32"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="33"/>
+      <c r="G12" s="34"/>
       <c r="H12" s="32"/>
       <c r="I12" s="32"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="33"/>
+      <c r="L12" s="34"/>
       <c r="M12" s="32"/>
       <c r="N12" s="32"/>
     </row>
@@ -3818,7 +3812,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="36">
+      <c r="B13" s="37">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3827,7 +3821,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="36">
+      <c r="G13" s="37">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3836,7 +3830,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="36">
+      <c r="L13" s="37">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3872,19 +3866,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="37" t="s">
+      <c r="A25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
-      <c r="F25" s="37" t="s">
+      <c r="F25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
       <c r="I25" s="32"/>
-      <c r="K25" s="37" t="s">
+      <c r="K25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="32"/>
@@ -3892,19 +3886,19 @@
       <c r="N25" s="32"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="37" t="s">
+      <c r="A26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
-      <c r="F26" s="37" t="s">
+      <c r="F26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="32"/>
       <c r="H26" s="32"/>
       <c r="I26" s="32"/>
-      <c r="K26" s="37" t="s">
+      <c r="K26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="32"/>
@@ -3926,27 +3920,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="35" t="s">
+      <c r="A28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="32"/>
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="36" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="32"/>
-      <c r="F28" s="35" t="s">
+      <c r="F28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="32"/>
-      <c r="H28" s="35" t="s">
+      <c r="H28" s="36" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="32"/>
-      <c r="K28" s="35" t="s">
+      <c r="K28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="32"/>
-      <c r="M28" s="35" t="s">
+      <c r="M28" s="36" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="32"/>
@@ -3955,19 +3949,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="34"/>
+      <c r="B29" s="35"/>
       <c r="C29" s="32"/>
       <c r="D29" s="32"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="34"/>
+      <c r="G29" s="35"/>
       <c r="H29" s="32"/>
       <c r="I29" s="32"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="34"/>
+      <c r="L29" s="35"/>
       <c r="M29" s="32"/>
       <c r="N29" s="32"/>
     </row>
@@ -3975,19 +3969,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="33"/>
+      <c r="B30" s="34"/>
       <c r="C30" s="32"/>
       <c r="D30" s="32"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="33"/>
+      <c r="G30" s="34"/>
       <c r="H30" s="32"/>
       <c r="I30" s="32"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="33"/>
+      <c r="L30" s="34"/>
       <c r="M30" s="32"/>
       <c r="N30" s="32"/>
     </row>
@@ -3995,19 +3989,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="34"/>
+      <c r="B31" s="35"/>
       <c r="C31" s="32"/>
       <c r="D31" s="32"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="34"/>
+      <c r="G31" s="35"/>
       <c r="H31" s="32"/>
       <c r="I31" s="32"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="34"/>
+      <c r="L31" s="35"/>
       <c r="M31" s="32"/>
       <c r="N31" s="32"/>
     </row>
@@ -4015,19 +4009,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="33"/>
+      <c r="B32" s="34"/>
       <c r="C32" s="32"/>
       <c r="D32" s="32"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="33"/>
+      <c r="G32" s="34"/>
       <c r="H32" s="32"/>
       <c r="I32" s="32"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="33"/>
+      <c r="L32" s="34"/>
       <c r="M32" s="32"/>
       <c r="N32" s="32"/>
     </row>
@@ -4035,19 +4029,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="34"/>
+      <c r="B33" s="35"/>
       <c r="C33" s="32"/>
       <c r="D33" s="32"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="34"/>
+      <c r="G33" s="35"/>
       <c r="H33" s="32"/>
       <c r="I33" s="32"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="34"/>
+      <c r="L33" s="35"/>
       <c r="M33" s="32"/>
       <c r="N33" s="32"/>
     </row>
@@ -4055,19 +4049,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="33"/>
+      <c r="B34" s="34"/>
       <c r="C34" s="32"/>
       <c r="D34" s="32"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="33"/>
+      <c r="G34" s="34"/>
       <c r="H34" s="32"/>
       <c r="I34" s="32"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="33"/>
+      <c r="L34" s="34"/>
       <c r="M34" s="32"/>
       <c r="N34" s="32"/>
     </row>
@@ -4075,19 +4069,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="34"/>
+      <c r="B35" s="35"/>
       <c r="C35" s="32"/>
       <c r="D35" s="32"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="34"/>
+      <c r="G35" s="35"/>
       <c r="H35" s="32"/>
       <c r="I35" s="32"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="34"/>
+      <c r="L35" s="35"/>
       <c r="M35" s="32"/>
       <c r="N35" s="32"/>
     </row>
@@ -4095,19 +4089,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="33"/>
+      <c r="B36" s="34"/>
       <c r="C36" s="32"/>
       <c r="D36" s="32"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="33"/>
+      <c r="G36" s="34"/>
       <c r="H36" s="32"/>
       <c r="I36" s="32"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="33"/>
+      <c r="L36" s="34"/>
       <c r="M36" s="32"/>
       <c r="N36" s="32"/>
     </row>
@@ -4115,7 +4109,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="36">
+      <c r="B37" s="37">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -4124,7 +4118,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="36">
+      <c r="G37" s="37">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -4133,7 +4127,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="36">
+      <c r="L37" s="37">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -4170,6 +4164,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
     <mergeCell ref="L34:N34"/>
     <mergeCell ref="L6:N6"/>
     <mergeCell ref="B33:D33"/>
@@ -4186,68 +4242,6 @@
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4295,7 +4289,7 @@
         <v>49</v>
       </c>
       <c r="E2" s="18">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="F2" s="18"/>
     </row>
@@ -4313,7 +4307,7 @@
         <v>68</v>
       </c>
       <c r="E3" s="18">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="F3" s="18"/>
     </row>
@@ -4331,7 +4325,7 @@
         <v>49</v>
       </c>
       <c r="E4" s="18">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="F4" s="18"/>
     </row>
@@ -4349,7 +4343,7 @@
         <v>68</v>
       </c>
       <c r="E5" s="18">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="F5" s="18"/>
     </row>
@@ -4367,7 +4361,7 @@
         <v>49</v>
       </c>
       <c r="E6" s="18">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="F6" s="18"/>
     </row>
@@ -4385,7 +4379,7 @@
         <v>68</v>
       </c>
       <c r="E7" s="18">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="F7" s="18"/>
     </row>
@@ -4403,7 +4397,7 @@
         <v>49</v>
       </c>
       <c r="E8" s="18">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="F8" s="18"/>
     </row>
@@ -4421,7 +4415,7 @@
         <v>68</v>
       </c>
       <c r="E9" s="18">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="F9" s="18"/>
     </row>
@@ -4439,7 +4433,7 @@
         <v>49</v>
       </c>
       <c r="E10" s="18">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F10" s="18"/>
     </row>
@@ -4457,7 +4451,7 @@
         <v>68</v>
       </c>
       <c r="E11" s="18">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F11" s="18"/>
     </row>
@@ -4475,7 +4469,7 @@
         <v>49</v>
       </c>
       <c r="E12" s="18">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F12" s="18"/>
     </row>
@@ -4493,7 +4487,7 @@
         <v>68</v>
       </c>
       <c r="E13" s="18">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F13" s="18"/>
     </row>
@@ -4511,7 +4505,7 @@
         <v>49</v>
       </c>
       <c r="E14" s="18">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F14" s="18"/>
     </row>
@@ -4529,7 +4523,7 @@
         <v>68</v>
       </c>
       <c r="E15" s="18">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F15" s="18"/>
     </row>
@@ -4547,7 +4541,7 @@
         <v>49</v>
       </c>
       <c r="E16" s="18">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F16" s="18"/>
     </row>
@@ -4565,7 +4559,7 @@
         <v>68</v>
       </c>
       <c r="E17" s="18">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="F17" s="18"/>
     </row>
@@ -4719,7 +4713,7 @@
         <v>49</v>
       </c>
       <c r="E26" s="18">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="F26" s="18"/>
     </row>
@@ -4755,7 +4749,7 @@
         <v>49</v>
       </c>
       <c r="E28" s="18">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="F28" s="18"/>
     </row>
@@ -4791,7 +4785,7 @@
         <v>49</v>
       </c>
       <c r="E30" s="18">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="F30" s="18"/>
     </row>
@@ -4809,7 +4803,7 @@
         <v>68</v>
       </c>
       <c r="E31" s="18">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F31" s="18"/>
     </row>
@@ -4827,7 +4821,7 @@
         <v>49</v>
       </c>
       <c r="E32" s="18">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F32" s="18"/>
     </row>
@@ -4845,7 +4839,7 @@
         <v>68</v>
       </c>
       <c r="E33" s="18">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F33" s="18"/>
     </row>
@@ -4863,7 +4857,7 @@
         <v>49</v>
       </c>
       <c r="E34" s="18">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F34" s="18"/>
     </row>
@@ -4881,7 +4875,7 @@
         <v>68</v>
       </c>
       <c r="E35" s="18">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F35" s="18"/>
     </row>
@@ -4899,7 +4893,7 @@
         <v>49</v>
       </c>
       <c r="E36" s="18">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F36" s="18"/>
     </row>
@@ -4917,7 +4911,7 @@
         <v>68</v>
       </c>
       <c r="E37" s="18">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F37" s="18"/>
     </row>
@@ -4935,7 +4929,7 @@
         <v>49</v>
       </c>
       <c r="E38" s="18">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="F38" s="18"/>
     </row>
@@ -4953,7 +4947,7 @@
         <v>68</v>
       </c>
       <c r="E39" s="18">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="F39" s="18"/>
     </row>
@@ -4971,7 +4965,7 @@
         <v>49</v>
       </c>
       <c r="E40" s="18">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F40" s="18"/>
     </row>
@@ -4989,7 +4983,7 @@
         <v>68</v>
       </c>
       <c r="E41" s="18">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F41" s="18"/>
     </row>

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12B8C788-A320-40F4-9481-AB09D699CF7E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{149C4257-E75B-4474-A64C-7904AE4476D3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -447,9 +447,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -460,6 +457,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="G97" s="26">
         <f>SUM(G98:G99)</f>
-        <v>900</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:7" ht="15">
@@ -2269,9 +2269,7 @@
       <c r="F98" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G98" s="26">
-        <v>900</v>
-      </c>
+      <c r="G98" s="26"/>
     </row>
     <row r="99" spans="1:7" ht="15">
       <c r="A99" s="7" t="s">
@@ -2799,7 +2797,7 @@
       </c>
       <c r="G133" s="28">
         <f>SUM(G97,G100,G103,G106,G109,G112,G115,G118,G121,G124,G127,G130)</f>
-        <v>900</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2821,19 +2819,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="32"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
-      <c r="K1" s="33" t="s">
+      <c r="K1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="32"/>
@@ -2841,19 +2839,19 @@
       <c r="N1" s="32"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
-      <c r="F2" s="33" t="s">
+      <c r="F2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="32"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="K2" s="33" t="s">
+      <c r="K2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="32"/>
@@ -2875,27 +2873,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="35" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="32"/>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="32"/>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="35" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="32"/>
-      <c r="K4" s="36" t="s">
+      <c r="K4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="32"/>
-      <c r="M4" s="36" t="s">
+      <c r="M4" s="35" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="32"/>
@@ -2904,21 +2902,21 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="35">
-        <v>0</v>
-      </c>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
+      <c r="B5" s="34">
+        <v>0</v>
+      </c>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="35"/>
+      <c r="G5" s="34"/>
       <c r="H5" s="32"/>
       <c r="I5" s="32"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="35"/>
+      <c r="L5" s="34"/>
       <c r="M5" s="32"/>
       <c r="N5" s="32"/>
     </row>
@@ -2926,21 +2924,21 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="34">
-        <v>0</v>
-      </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
+      <c r="B6" s="33">
+        <v>0</v>
+      </c>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="34"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="34"/>
+      <c r="L6" s="33"/>
       <c r="M6" s="32"/>
       <c r="N6" s="32"/>
     </row>
@@ -2948,21 +2946,21 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="35">
-        <v>0</v>
-      </c>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
+      <c r="B7" s="34">
+        <v>0</v>
+      </c>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="35"/>
+      <c r="G7" s="34"/>
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="35"/>
+      <c r="L7" s="34"/>
       <c r="M7" s="32"/>
       <c r="N7" s="32"/>
     </row>
@@ -2970,21 +2968,21 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="34">
-        <v>0</v>
-      </c>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
+      <c r="B8" s="33">
+        <v>0</v>
+      </c>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="34"/>
+      <c r="G8" s="33"/>
       <c r="H8" s="32"/>
       <c r="I8" s="32"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="34"/>
+      <c r="L8" s="33"/>
       <c r="M8" s="32"/>
       <c r="N8" s="32"/>
     </row>
@@ -2992,21 +2990,21 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="35">
-        <v>0</v>
-      </c>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
+      <c r="B9" s="34">
+        <v>0</v>
+      </c>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="35"/>
+      <c r="G9" s="34"/>
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="35"/>
+      <c r="L9" s="34"/>
       <c r="M9" s="32"/>
       <c r="N9" s="32"/>
     </row>
@@ -3014,21 +3012,21 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="34">
-        <v>0</v>
-      </c>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
+      <c r="B10" s="33">
+        <v>0</v>
+      </c>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="34"/>
+      <c r="G10" s="33"/>
       <c r="H10" s="32"/>
       <c r="I10" s="32"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="34"/>
+      <c r="L10" s="33"/>
       <c r="M10" s="32"/>
       <c r="N10" s="32"/>
     </row>
@@ -3036,7 +3034,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="37">
+      <c r="B11" s="36">
         <f>SUM(B5:B10)</f>
         <v>0</v>
       </c>
@@ -3045,7 +3043,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="37">
+      <c r="G11" s="36">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -3054,7 +3052,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="37">
+      <c r="L11" s="36">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -3090,19 +3088,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="33" t="s">
+      <c r="A25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
-      <c r="F25" s="33" t="s">
+      <c r="F25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
       <c r="I25" s="32"/>
-      <c r="K25" s="33" t="s">
+      <c r="K25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="32"/>
@@ -3110,19 +3108,19 @@
       <c r="N25" s="32"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="33" t="s">
+      <c r="A26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
-      <c r="F26" s="33" t="s">
+      <c r="F26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="32"/>
       <c r="H26" s="32"/>
       <c r="I26" s="32"/>
-      <c r="K26" s="33" t="s">
+      <c r="K26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="32"/>
@@ -3144,27 +3142,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="32"/>
-      <c r="C28" s="36" t="s">
+      <c r="C28" s="35" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="32"/>
-      <c r="F28" s="36" t="s">
+      <c r="F28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="32"/>
-      <c r="H28" s="36" t="s">
+      <c r="H28" s="35" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="32"/>
-      <c r="K28" s="36" t="s">
+      <c r="K28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="32"/>
-      <c r="M28" s="36" t="s">
+      <c r="M28" s="35" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="32"/>
@@ -3173,7 +3171,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="35">
+      <c r="B29" s="34">
         <v>0</v>
       </c>
       <c r="C29" s="32"/>
@@ -3181,23 +3179,23 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="35"/>
+      <c r="G29" s="34"/>
       <c r="H29" s="32"/>
       <c r="I29" s="32"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="35">
-        <v>0</v>
-      </c>
-      <c r="M29" s="35"/>
-      <c r="N29" s="35"/>
+      <c r="L29" s="34">
+        <v>0</v>
+      </c>
+      <c r="M29" s="34"/>
+      <c r="N29" s="34"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="34">
+      <c r="B30" s="33">
         <v>0</v>
       </c>
       <c r="C30" s="32"/>
@@ -3205,23 +3203,23 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="34"/>
+      <c r="G30" s="33"/>
       <c r="H30" s="32"/>
       <c r="I30" s="32"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="34">
-        <v>0</v>
-      </c>
-      <c r="M30" s="34"/>
-      <c r="N30" s="34"/>
+      <c r="L30" s="33">
+        <v>0</v>
+      </c>
+      <c r="M30" s="33"/>
+      <c r="N30" s="33"/>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1">
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="35">
+      <c r="B31" s="34">
         <v>0</v>
       </c>
       <c r="C31" s="32"/>
@@ -3229,23 +3227,23 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="35"/>
+      <c r="G31" s="34"/>
       <c r="H31" s="32"/>
       <c r="I31" s="32"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="35">
-        <v>0</v>
-      </c>
-      <c r="M31" s="35"/>
-      <c r="N31" s="35"/>
+      <c r="L31" s="34">
+        <v>0</v>
+      </c>
+      <c r="M31" s="34"/>
+      <c r="N31" s="34"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="34">
+      <c r="B32" s="33">
         <v>0</v>
       </c>
       <c r="C32" s="32"/>
@@ -3253,23 +3251,23 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="34"/>
+      <c r="G32" s="33"/>
       <c r="H32" s="32"/>
       <c r="I32" s="32"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="34">
-        <v>0</v>
-      </c>
-      <c r="M32" s="34"/>
-      <c r="N32" s="34"/>
+      <c r="L32" s="33">
+        <v>0</v>
+      </c>
+      <c r="M32" s="33"/>
+      <c r="N32" s="33"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="35">
+      <c r="B33" s="34">
         <v>0</v>
       </c>
       <c r="C33" s="32"/>
@@ -3277,23 +3275,23 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="35"/>
+      <c r="G33" s="34"/>
       <c r="H33" s="32"/>
       <c r="I33" s="32"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="35">
-        <v>0</v>
-      </c>
-      <c r="M33" s="35"/>
-      <c r="N33" s="35"/>
+      <c r="L33" s="34">
+        <v>0</v>
+      </c>
+      <c r="M33" s="34"/>
+      <c r="N33" s="34"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="34">
+      <c r="B34" s="33">
         <v>0</v>
       </c>
       <c r="C34" s="32"/>
@@ -3301,13 +3299,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="34"/>
+      <c r="G34" s="33"/>
       <c r="H34" s="32"/>
       <c r="I34" s="32"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="34">
+      <c r="L34" s="33">
         <v>0</v>
       </c>
       <c r="M34" s="32"/>
@@ -3317,7 +3315,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="37">
+      <c r="B35" s="36">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -3326,7 +3324,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="37">
+      <c r="G35" s="36">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -3335,7 +3333,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="37">
+      <c r="L35" s="36">
         <f>SUM(L29:L34)</f>
         <v>0</v>
       </c>
@@ -3372,6 +3370,56 @@
     </row>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B10:D10"/>
@@ -3388,56 +3436,6 @@
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="H28:I28"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3453,7 +3451,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
@@ -3461,7 +3459,7 @@
       <c r="D1" s="32"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
@@ -3475,11 +3473,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="35" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="35" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="32"/>
@@ -3488,7 +3486,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="35"/>
+      <c r="B5" s="34"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
     </row>
@@ -3496,7 +3494,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="34"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
     </row>
@@ -3504,7 +3502,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="35"/>
+      <c r="B7" s="34"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
     </row>
@@ -3512,7 +3510,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="34"/>
+      <c r="B8" s="33"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32"/>
     </row>
@@ -3520,7 +3518,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="37">
+      <c r="B9" s="36">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -3569,19 +3567,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="32"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
-      <c r="K1" s="33" t="s">
+      <c r="K1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="32"/>
@@ -3589,19 +3587,19 @@
       <c r="N1" s="32"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
-      <c r="F2" s="33" t="s">
+      <c r="F2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="32"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="K2" s="33" t="s">
+      <c r="K2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="32"/>
@@ -3623,27 +3621,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="35" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="32"/>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="32"/>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="35" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="32"/>
-      <c r="K4" s="36" t="s">
+      <c r="K4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="32"/>
-      <c r="M4" s="36" t="s">
+      <c r="M4" s="35" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="32"/>
@@ -3652,19 +3650,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="35"/>
+      <c r="B5" s="34"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="35"/>
+      <c r="G5" s="34"/>
       <c r="H5" s="32"/>
       <c r="I5" s="32"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="35"/>
+      <c r="L5" s="34"/>
       <c r="M5" s="32"/>
       <c r="N5" s="32"/>
     </row>
@@ -3672,19 +3670,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="34"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="34"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="34"/>
+      <c r="L6" s="33"/>
       <c r="M6" s="32"/>
       <c r="N6" s="32"/>
     </row>
@@ -3692,19 +3690,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="35"/>
+      <c r="B7" s="34"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="35"/>
+      <c r="G7" s="34"/>
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="35"/>
+      <c r="L7" s="34"/>
       <c r="M7" s="32"/>
       <c r="N7" s="32"/>
     </row>
@@ -3712,19 +3710,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="34"/>
+      <c r="B8" s="33"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="34"/>
+      <c r="G8" s="33"/>
       <c r="H8" s="32"/>
       <c r="I8" s="32"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="34"/>
+      <c r="L8" s="33"/>
       <c r="M8" s="32"/>
       <c r="N8" s="32"/>
     </row>
@@ -3732,19 +3730,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="35"/>
+      <c r="B9" s="34"/>
       <c r="C9" s="32"/>
       <c r="D9" s="32"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="35"/>
+      <c r="G9" s="34"/>
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="35"/>
+      <c r="L9" s="34"/>
       <c r="M9" s="32"/>
       <c r="N9" s="32"/>
     </row>
@@ -3752,19 +3750,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="34"/>
+      <c r="B10" s="33"/>
       <c r="C10" s="32"/>
       <c r="D10" s="32"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="34"/>
+      <c r="G10" s="33"/>
       <c r="H10" s="32"/>
       <c r="I10" s="32"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="34"/>
+      <c r="L10" s="33"/>
       <c r="M10" s="32"/>
       <c r="N10" s="32"/>
     </row>
@@ -3772,19 +3770,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="35"/>
+      <c r="B11" s="34"/>
       <c r="C11" s="32"/>
       <c r="D11" s="32"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="35"/>
+      <c r="G11" s="34"/>
       <c r="H11" s="32"/>
       <c r="I11" s="32"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="35"/>
+      <c r="L11" s="34"/>
       <c r="M11" s="32"/>
       <c r="N11" s="32"/>
     </row>
@@ -3792,19 +3790,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="34"/>
+      <c r="B12" s="33"/>
       <c r="C12" s="32"/>
       <c r="D12" s="32"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="34"/>
+      <c r="G12" s="33"/>
       <c r="H12" s="32"/>
       <c r="I12" s="32"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="34"/>
+      <c r="L12" s="33"/>
       <c r="M12" s="32"/>
       <c r="N12" s="32"/>
     </row>
@@ -3812,7 +3810,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="37">
+      <c r="B13" s="36">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3821,7 +3819,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="37">
+      <c r="G13" s="36">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3830,7 +3828,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="37">
+      <c r="L13" s="36">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3866,19 +3864,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="33" t="s">
+      <c r="A25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
-      <c r="F25" s="33" t="s">
+      <c r="F25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
       <c r="I25" s="32"/>
-      <c r="K25" s="33" t="s">
+      <c r="K25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="32"/>
@@ -3886,19 +3884,19 @@
       <c r="N25" s="32"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="33" t="s">
+      <c r="A26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
-      <c r="F26" s="33" t="s">
+      <c r="F26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="32"/>
       <c r="H26" s="32"/>
       <c r="I26" s="32"/>
-      <c r="K26" s="33" t="s">
+      <c r="K26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="32"/>
@@ -3920,27 +3918,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="32"/>
-      <c r="C28" s="36" t="s">
+      <c r="C28" s="35" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="32"/>
-      <c r="F28" s="36" t="s">
+      <c r="F28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="32"/>
-      <c r="H28" s="36" t="s">
+      <c r="H28" s="35" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="32"/>
-      <c r="K28" s="36" t="s">
+      <c r="K28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="32"/>
-      <c r="M28" s="36" t="s">
+      <c r="M28" s="35" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="32"/>
@@ -3949,19 +3947,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="35"/>
+      <c r="B29" s="34"/>
       <c r="C29" s="32"/>
       <c r="D29" s="32"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="35"/>
+      <c r="G29" s="34"/>
       <c r="H29" s="32"/>
       <c r="I29" s="32"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="35"/>
+      <c r="L29" s="34"/>
       <c r="M29" s="32"/>
       <c r="N29" s="32"/>
     </row>
@@ -3969,19 +3967,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="34"/>
+      <c r="B30" s="33"/>
       <c r="C30" s="32"/>
       <c r="D30" s="32"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="34"/>
+      <c r="G30" s="33"/>
       <c r="H30" s="32"/>
       <c r="I30" s="32"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="34"/>
+      <c r="L30" s="33"/>
       <c r="M30" s="32"/>
       <c r="N30" s="32"/>
     </row>
@@ -3989,19 +3987,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="35"/>
+      <c r="B31" s="34"/>
       <c r="C31" s="32"/>
       <c r="D31" s="32"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="35"/>
+      <c r="G31" s="34"/>
       <c r="H31" s="32"/>
       <c r="I31" s="32"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="35"/>
+      <c r="L31" s="34"/>
       <c r="M31" s="32"/>
       <c r="N31" s="32"/>
     </row>
@@ -4009,19 +4007,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="34"/>
+      <c r="B32" s="33"/>
       <c r="C32" s="32"/>
       <c r="D32" s="32"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="34"/>
+      <c r="G32" s="33"/>
       <c r="H32" s="32"/>
       <c r="I32" s="32"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="34"/>
+      <c r="L32" s="33"/>
       <c r="M32" s="32"/>
       <c r="N32" s="32"/>
     </row>
@@ -4029,19 +4027,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="35"/>
+      <c r="B33" s="34"/>
       <c r="C33" s="32"/>
       <c r="D33" s="32"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="35"/>
+      <c r="G33" s="34"/>
       <c r="H33" s="32"/>
       <c r="I33" s="32"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="35"/>
+      <c r="L33" s="34"/>
       <c r="M33" s="32"/>
       <c r="N33" s="32"/>
     </row>
@@ -4049,19 +4047,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="34"/>
+      <c r="B34" s="33"/>
       <c r="C34" s="32"/>
       <c r="D34" s="32"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="34"/>
+      <c r="G34" s="33"/>
       <c r="H34" s="32"/>
       <c r="I34" s="32"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="34"/>
+      <c r="L34" s="33"/>
       <c r="M34" s="32"/>
       <c r="N34" s="32"/>
     </row>
@@ -4069,19 +4067,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="35"/>
+      <c r="B35" s="34"/>
       <c r="C35" s="32"/>
       <c r="D35" s="32"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="35"/>
+      <c r="G35" s="34"/>
       <c r="H35" s="32"/>
       <c r="I35" s="32"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="35"/>
+      <c r="L35" s="34"/>
       <c r="M35" s="32"/>
       <c r="N35" s="32"/>
     </row>
@@ -4089,19 +4087,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="34"/>
+      <c r="B36" s="33"/>
       <c r="C36" s="32"/>
       <c r="D36" s="32"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="34"/>
+      <c r="G36" s="33"/>
       <c r="H36" s="32"/>
       <c r="I36" s="32"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="34"/>
+      <c r="L36" s="33"/>
       <c r="M36" s="32"/>
       <c r="N36" s="32"/>
     </row>
@@ -4109,7 +4107,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="37">
+      <c r="B37" s="36">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -4118,7 +4116,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="37">
+      <c r="G37" s="36">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -4127,7 +4125,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="37">
+      <c r="L37" s="36">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -4164,6 +4162,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
     <mergeCell ref="G36:I36"/>
     <mergeCell ref="L32:N32"/>
     <mergeCell ref="L13:N13"/>
@@ -4180,68 +4240,6 @@
     <mergeCell ref="L33:N33"/>
     <mergeCell ref="L35:N35"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="L9:N9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{149C4257-E75B-4474-A64C-7904AE4476D3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEB87C96-6194-4692-A133-5D2E7B48E6B3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucoes" sheetId="1" r:id="rId1"/>
@@ -447,6 +447,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -457,9 +460,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -787,7 +787,7 @@
       </c>
       <c r="B5" s="21">
         <f>SUM(B6:B7)</f>
-        <v>670</v>
+        <v>2100</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>20</v>
@@ -801,14 +801,16 @@
       </c>
       <c r="L5" s="14">
         <f>SUM(L6:L7)</f>
-        <v>670</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
       <c r="A6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="14"/>
+      <c r="B6" s="14">
+        <v>900</v>
+      </c>
       <c r="F6" s="7" t="s">
         <v>21</v>
       </c>
@@ -817,7 +819,7 @@
         <v>21</v>
       </c>
       <c r="L6" s="14">
-        <v>670</v>
+        <v>3200</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
@@ -825,7 +827,7 @@
         <v>22</v>
       </c>
       <c r="B7" s="14">
-        <v>670</v>
+        <v>1200</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>22</v>
@@ -842,7 +844,7 @@
       </c>
       <c r="B8" s="15">
         <f>SUM(B9:B10)</f>
-        <v>0</v>
+        <v>280</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>23</v>
@@ -856,14 +858,16 @@
       </c>
       <c r="L8" s="15">
         <f>SUM(L9:L10)</f>
-        <v>350</v>
+        <v>500</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1">
       <c r="A9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="15"/>
+      <c r="B9" s="15">
+        <v>280</v>
+      </c>
       <c r="F9" s="9" t="s">
         <v>21</v>
       </c>
@@ -872,7 +876,7 @@
         <v>21</v>
       </c>
       <c r="L9" s="15">
-        <v>350</v>
+        <v>500</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
@@ -946,7 +950,7 @@
       </c>
       <c r="B14" s="15">
         <f>SUM(B15:B16)</f>
-        <v>400</v>
+        <v>270</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>25</v>
@@ -960,7 +964,7 @@
       </c>
       <c r="L14" s="15">
         <f>SUM(L15:L16)</f>
-        <v>0</v>
+        <v>323</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1">
@@ -968,7 +972,7 @@
         <v>21</v>
       </c>
       <c r="B15" s="15">
-        <v>400</v>
+        <v>270</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>21</v>
@@ -977,7 +981,10 @@
       <c r="K15" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L15" s="15"/>
+      <c r="L15" s="15">
+        <f>194+129</f>
+        <v>323</v>
+      </c>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1">
       <c r="A16" s="9" t="s">
@@ -1108,7 +1115,7 @@
       </c>
       <c r="G23" s="14">
         <f>SUM(G24:G25)</f>
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="K23" s="7" t="s">
         <v>28</v>
@@ -1126,7 +1133,9 @@
       <c r="F24" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G24" s="14"/>
+      <c r="G24" s="14">
+        <v>350</v>
+      </c>
       <c r="K24" s="7" t="s">
         <v>21</v>
       </c>
@@ -1159,7 +1168,7 @@
       </c>
       <c r="G26" s="15">
         <f>SUM(G27:G28)</f>
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="K26" s="9" t="s">
         <v>29</v>
@@ -1177,9 +1186,7 @@
       <c r="F27" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G27" s="15">
-        <v>73</v>
-      </c>
+      <c r="G27" s="15"/>
       <c r="K27" s="9" t="s">
         <v>21</v>
       </c>
@@ -1205,7 +1212,7 @@
       </c>
       <c r="B29" s="14">
         <f>SUM(B30:B31)</f>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>30</v>
@@ -1226,7 +1233,9 @@
       <c r="A30" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B30" s="14"/>
+      <c r="B30" s="14">
+        <v>600</v>
+      </c>
       <c r="F30" s="7" t="s">
         <v>21</v>
       </c>
@@ -1258,7 +1267,7 @@
       </c>
       <c r="B32" s="15">
         <f>SUM(B33:B34)</f>
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>31</v>
@@ -1272,14 +1281,16 @@
       </c>
       <c r="L32" s="15">
         <f>SUM(L33:L34)</f>
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="15"/>
+      <c r="B33" s="15">
+        <v>31</v>
+      </c>
       <c r="F33" s="9" t="s">
         <v>21</v>
       </c>
@@ -1287,9 +1298,7 @@
       <c r="K33" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L33" s="15">
-        <v>33</v>
-      </c>
+      <c r="L33" s="15"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="9" t="s">
@@ -1362,7 +1371,7 @@
       </c>
       <c r="B38" s="22">
         <f>SUM(B39:B40)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>72</v>
@@ -1376,14 +1385,16 @@
       </c>
       <c r="L38" s="23">
         <f>SUM(L39:L40)</f>
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="15" customHeight="1">
       <c r="A39" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B39" s="15"/>
+      <c r="B39" s="15">
+        <v>30</v>
+      </c>
       <c r="F39" s="9" t="s">
         <v>21</v>
       </c>
@@ -1391,9 +1402,7 @@
       <c r="K39" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L39" s="15">
-        <v>30</v>
-      </c>
+      <c r="L39" s="15"/>
     </row>
     <row r="40" spans="1:14" ht="15" customHeight="1">
       <c r="A40" s="9" t="s">
@@ -1415,21 +1424,21 @@
       </c>
       <c r="B41" s="13">
         <f>SUM(B5,B8,B11,B14,B17,B20,B23,B26,B29,B32,B35,B38)</f>
-        <v>1070</v>
+        <v>3311</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G41" s="13">
         <f>SUM(G5,G8,G11,G14,G17,G20,G23,G26,G29,G32,G35,G38)</f>
-        <v>73</v>
+        <v>350</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="L41" s="13">
         <f>SUM(L5,L8,L11,L14,L17,L20,L23,L26,L29,L32,L35,L38)</f>
-        <v>1583</v>
+        <v>4523</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1">
@@ -2819,19 +2828,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
-      <c r="F1" s="37" t="s">
+      <c r="F1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="32"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
-      <c r="K1" s="37" t="s">
+      <c r="K1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="32"/>
@@ -2839,19 +2848,19 @@
       <c r="N1" s="32"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
-      <c r="F2" s="37" t="s">
+      <c r="F2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="32"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="K2" s="37" t="s">
+      <c r="K2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="32"/>
@@ -2873,27 +2882,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="36" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="32"/>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="32"/>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="36" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="32"/>
-      <c r="K4" s="35" t="s">
+      <c r="K4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="32"/>
-      <c r="M4" s="35" t="s">
+      <c r="M4" s="36" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="32"/>
@@ -2902,21 +2911,21 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="34">
-        <v>0</v>
-      </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
+      <c r="B5" s="35">
+        <v>0</v>
+      </c>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="34"/>
+      <c r="G5" s="35"/>
       <c r="H5" s="32"/>
       <c r="I5" s="32"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="34"/>
+      <c r="L5" s="35"/>
       <c r="M5" s="32"/>
       <c r="N5" s="32"/>
     </row>
@@ -2924,21 +2933,21 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="33">
-        <v>0</v>
-      </c>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
+      <c r="B6" s="34">
+        <v>0</v>
+      </c>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="33"/>
+      <c r="G6" s="34"/>
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="33"/>
+      <c r="L6" s="34"/>
       <c r="M6" s="32"/>
       <c r="N6" s="32"/>
     </row>
@@ -2946,21 +2955,21 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="34">
-        <v>0</v>
-      </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
+      <c r="B7" s="35">
+        <v>0</v>
+      </c>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="34"/>
+      <c r="G7" s="35"/>
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="34"/>
+      <c r="L7" s="35"/>
       <c r="M7" s="32"/>
       <c r="N7" s="32"/>
     </row>
@@ -2968,21 +2977,21 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="33">
-        <v>0</v>
-      </c>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
+      <c r="B8" s="34">
+        <v>0</v>
+      </c>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="33"/>
+      <c r="G8" s="34"/>
       <c r="H8" s="32"/>
       <c r="I8" s="32"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="33"/>
+      <c r="L8" s="34"/>
       <c r="M8" s="32"/>
       <c r="N8" s="32"/>
     </row>
@@ -2990,21 +2999,21 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="34">
-        <v>0</v>
-      </c>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
+      <c r="B9" s="35">
+        <v>0</v>
+      </c>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="34"/>
+      <c r="G9" s="35"/>
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="34"/>
+      <c r="L9" s="35"/>
       <c r="M9" s="32"/>
       <c r="N9" s="32"/>
     </row>
@@ -3012,21 +3021,21 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="33">
-        <v>0</v>
-      </c>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
+      <c r="B10" s="34">
+        <v>0</v>
+      </c>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="33"/>
+      <c r="G10" s="34"/>
       <c r="H10" s="32"/>
       <c r="I10" s="32"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="33"/>
+      <c r="L10" s="34"/>
       <c r="M10" s="32"/>
       <c r="N10" s="32"/>
     </row>
@@ -3034,7 +3043,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="36">
+      <c r="B11" s="37">
         <f>SUM(B5:B10)</f>
         <v>0</v>
       </c>
@@ -3043,7 +3052,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="36">
+      <c r="G11" s="37">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -3052,7 +3061,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="36">
+      <c r="L11" s="37">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -3088,19 +3097,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="37" t="s">
+      <c r="A25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
-      <c r="F25" s="37" t="s">
+      <c r="F25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
       <c r="I25" s="32"/>
-      <c r="K25" s="37" t="s">
+      <c r="K25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="32"/>
@@ -3108,19 +3117,19 @@
       <c r="N25" s="32"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="37" t="s">
+      <c r="A26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
-      <c r="F26" s="37" t="s">
+      <c r="F26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="32"/>
       <c r="H26" s="32"/>
       <c r="I26" s="32"/>
-      <c r="K26" s="37" t="s">
+      <c r="K26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="32"/>
@@ -3142,27 +3151,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="35" t="s">
+      <c r="A28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="32"/>
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="36" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="32"/>
-      <c r="F28" s="35" t="s">
+      <c r="F28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="32"/>
-      <c r="H28" s="35" t="s">
+      <c r="H28" s="36" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="32"/>
-      <c r="K28" s="35" t="s">
+      <c r="K28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="32"/>
-      <c r="M28" s="35" t="s">
+      <c r="M28" s="36" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="32"/>
@@ -3171,7 +3180,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="34">
+      <c r="B29" s="35">
         <v>0</v>
       </c>
       <c r="C29" s="32"/>
@@ -3179,23 +3188,23 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="34"/>
+      <c r="G29" s="35"/>
       <c r="H29" s="32"/>
       <c r="I29" s="32"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="34">
-        <v>0</v>
-      </c>
-      <c r="M29" s="34"/>
-      <c r="N29" s="34"/>
+      <c r="L29" s="35">
+        <v>0</v>
+      </c>
+      <c r="M29" s="35"/>
+      <c r="N29" s="35"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="33">
+      <c r="B30" s="34">
         <v>0</v>
       </c>
       <c r="C30" s="32"/>
@@ -3203,23 +3212,23 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="33"/>
+      <c r="G30" s="34"/>
       <c r="H30" s="32"/>
       <c r="I30" s="32"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="33">
-        <v>0</v>
-      </c>
-      <c r="M30" s="33"/>
-      <c r="N30" s="33"/>
+      <c r="L30" s="34">
+        <v>0</v>
+      </c>
+      <c r="M30" s="34"/>
+      <c r="N30" s="34"/>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1">
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="34">
+      <c r="B31" s="35">
         <v>0</v>
       </c>
       <c r="C31" s="32"/>
@@ -3227,23 +3236,23 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="34"/>
+      <c r="G31" s="35"/>
       <c r="H31" s="32"/>
       <c r="I31" s="32"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="34">
-        <v>0</v>
-      </c>
-      <c r="M31" s="34"/>
-      <c r="N31" s="34"/>
+      <c r="L31" s="35">
+        <v>0</v>
+      </c>
+      <c r="M31" s="35"/>
+      <c r="N31" s="35"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="33">
+      <c r="B32" s="34">
         <v>0</v>
       </c>
       <c r="C32" s="32"/>
@@ -3251,23 +3260,23 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="33"/>
+      <c r="G32" s="34"/>
       <c r="H32" s="32"/>
       <c r="I32" s="32"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="33">
-        <v>0</v>
-      </c>
-      <c r="M32" s="33"/>
-      <c r="N32" s="33"/>
+      <c r="L32" s="34">
+        <v>0</v>
+      </c>
+      <c r="M32" s="34"/>
+      <c r="N32" s="34"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="34">
+      <c r="B33" s="35">
         <v>0</v>
       </c>
       <c r="C33" s="32"/>
@@ -3275,23 +3284,23 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="34"/>
+      <c r="G33" s="35"/>
       <c r="H33" s="32"/>
       <c r="I33" s="32"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="34">
-        <v>0</v>
-      </c>
-      <c r="M33" s="34"/>
-      <c r="N33" s="34"/>
+      <c r="L33" s="35">
+        <v>0</v>
+      </c>
+      <c r="M33" s="35"/>
+      <c r="N33" s="35"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="33">
+      <c r="B34" s="34">
         <v>0</v>
       </c>
       <c r="C34" s="32"/>
@@ -3299,13 +3308,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="33"/>
+      <c r="G34" s="34"/>
       <c r="H34" s="32"/>
       <c r="I34" s="32"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="33">
+      <c r="L34" s="34">
         <v>0</v>
       </c>
       <c r="M34" s="32"/>
@@ -3315,7 +3324,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="36">
+      <c r="B35" s="37">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -3324,7 +3333,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="36">
+      <c r="G35" s="37">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -3333,7 +3342,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="36">
+      <c r="L35" s="37">
         <f>SUM(L29:L34)</f>
         <v>0</v>
       </c>
@@ -3370,13 +3379,49 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="L11:N11"/>
@@ -3393,49 +3438,13 @@
     <mergeCell ref="K2:N2"/>
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3451,7 +3460,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
@@ -3459,7 +3468,7 @@
       <c r="D1" s="32"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
@@ -3473,11 +3482,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="36" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="36" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="32"/>
@@ -3486,7 +3495,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="34"/>
+      <c r="B5" s="35"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
     </row>
@@ -3494,7 +3503,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="33"/>
+      <c r="B6" s="34"/>
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
     </row>
@@ -3502,7 +3511,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="34"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
     </row>
@@ -3510,7 +3519,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="33"/>
+      <c r="B8" s="34"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32"/>
     </row>
@@ -3518,7 +3527,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="36">
+      <c r="B9" s="37">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -3567,19 +3576,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
-      <c r="F1" s="37" t="s">
+      <c r="F1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="32"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
-      <c r="K1" s="37" t="s">
+      <c r="K1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="32"/>
@@ -3587,19 +3596,19 @@
       <c r="N1" s="32"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
-      <c r="F2" s="37" t="s">
+      <c r="F2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="32"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="K2" s="37" t="s">
+      <c r="K2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="32"/>
@@ -3621,27 +3630,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="36" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="32"/>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="32"/>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="36" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="32"/>
-      <c r="K4" s="35" t="s">
+      <c r="K4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="32"/>
-      <c r="M4" s="35" t="s">
+      <c r="M4" s="36" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="32"/>
@@ -3650,19 +3659,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="34"/>
+      <c r="B5" s="35"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="34"/>
+      <c r="G5" s="35"/>
       <c r="H5" s="32"/>
       <c r="I5" s="32"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="34"/>
+      <c r="L5" s="35"/>
       <c r="M5" s="32"/>
       <c r="N5" s="32"/>
     </row>
@@ -3670,19 +3679,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="33"/>
+      <c r="B6" s="34"/>
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="33"/>
+      <c r="G6" s="34"/>
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="33"/>
+      <c r="L6" s="34"/>
       <c r="M6" s="32"/>
       <c r="N6" s="32"/>
     </row>
@@ -3690,19 +3699,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="34"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="34"/>
+      <c r="G7" s="35"/>
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="34"/>
+      <c r="L7" s="35"/>
       <c r="M7" s="32"/>
       <c r="N7" s="32"/>
     </row>
@@ -3710,19 +3719,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="33"/>
+      <c r="B8" s="34"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="33"/>
+      <c r="G8" s="34"/>
       <c r="H8" s="32"/>
       <c r="I8" s="32"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="33"/>
+      <c r="L8" s="34"/>
       <c r="M8" s="32"/>
       <c r="N8" s="32"/>
     </row>
@@ -3730,19 +3739,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="34"/>
+      <c r="B9" s="35"/>
       <c r="C9" s="32"/>
       <c r="D9" s="32"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="34"/>
+      <c r="G9" s="35"/>
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="34"/>
+      <c r="L9" s="35"/>
       <c r="M9" s="32"/>
       <c r="N9" s="32"/>
     </row>
@@ -3750,19 +3759,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="33"/>
+      <c r="B10" s="34"/>
       <c r="C10" s="32"/>
       <c r="D10" s="32"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="33"/>
+      <c r="G10" s="34"/>
       <c r="H10" s="32"/>
       <c r="I10" s="32"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="33"/>
+      <c r="L10" s="34"/>
       <c r="M10" s="32"/>
       <c r="N10" s="32"/>
     </row>
@@ -3770,19 +3779,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="34"/>
+      <c r="B11" s="35"/>
       <c r="C11" s="32"/>
       <c r="D11" s="32"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="34"/>
+      <c r="G11" s="35"/>
       <c r="H11" s="32"/>
       <c r="I11" s="32"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="34"/>
+      <c r="L11" s="35"/>
       <c r="M11" s="32"/>
       <c r="N11" s="32"/>
     </row>
@@ -3790,19 +3799,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="33"/>
+      <c r="B12" s="34"/>
       <c r="C12" s="32"/>
       <c r="D12" s="32"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="33"/>
+      <c r="G12" s="34"/>
       <c r="H12" s="32"/>
       <c r="I12" s="32"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="33"/>
+      <c r="L12" s="34"/>
       <c r="M12" s="32"/>
       <c r="N12" s="32"/>
     </row>
@@ -3810,7 +3819,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="36">
+      <c r="B13" s="37">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3819,7 +3828,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="36">
+      <c r="G13" s="37">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3828,7 +3837,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="36">
+      <c r="L13" s="37">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3864,19 +3873,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="37" t="s">
+      <c r="A25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
-      <c r="F25" s="37" t="s">
+      <c r="F25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
       <c r="I25" s="32"/>
-      <c r="K25" s="37" t="s">
+      <c r="K25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="32"/>
@@ -3884,19 +3893,19 @@
       <c r="N25" s="32"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="37" t="s">
+      <c r="A26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
-      <c r="F26" s="37" t="s">
+      <c r="F26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="32"/>
       <c r="H26" s="32"/>
       <c r="I26" s="32"/>
-      <c r="K26" s="37" t="s">
+      <c r="K26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="32"/>
@@ -3918,27 +3927,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="35" t="s">
+      <c r="A28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="32"/>
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="36" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="32"/>
-      <c r="F28" s="35" t="s">
+      <c r="F28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="32"/>
-      <c r="H28" s="35" t="s">
+      <c r="H28" s="36" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="32"/>
-      <c r="K28" s="35" t="s">
+      <c r="K28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="32"/>
-      <c r="M28" s="35" t="s">
+      <c r="M28" s="36" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="32"/>
@@ -3947,19 +3956,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="34"/>
+      <c r="B29" s="35"/>
       <c r="C29" s="32"/>
       <c r="D29" s="32"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="34"/>
+      <c r="G29" s="35"/>
       <c r="H29" s="32"/>
       <c r="I29" s="32"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="34"/>
+      <c r="L29" s="35"/>
       <c r="M29" s="32"/>
       <c r="N29" s="32"/>
     </row>
@@ -3967,19 +3976,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="33"/>
+      <c r="B30" s="34"/>
       <c r="C30" s="32"/>
       <c r="D30" s="32"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="33"/>
+      <c r="G30" s="34"/>
       <c r="H30" s="32"/>
       <c r="I30" s="32"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="33"/>
+      <c r="L30" s="34"/>
       <c r="M30" s="32"/>
       <c r="N30" s="32"/>
     </row>
@@ -3987,19 +3996,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="34"/>
+      <c r="B31" s="35"/>
       <c r="C31" s="32"/>
       <c r="D31" s="32"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="34"/>
+      <c r="G31" s="35"/>
       <c r="H31" s="32"/>
       <c r="I31" s="32"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="34"/>
+      <c r="L31" s="35"/>
       <c r="M31" s="32"/>
       <c r="N31" s="32"/>
     </row>
@@ -4007,19 +4016,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="33"/>
+      <c r="B32" s="34"/>
       <c r="C32" s="32"/>
       <c r="D32" s="32"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="33"/>
+      <c r="G32" s="34"/>
       <c r="H32" s="32"/>
       <c r="I32" s="32"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="33"/>
+      <c r="L32" s="34"/>
       <c r="M32" s="32"/>
       <c r="N32" s="32"/>
     </row>
@@ -4027,19 +4036,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="34"/>
+      <c r="B33" s="35"/>
       <c r="C33" s="32"/>
       <c r="D33" s="32"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="34"/>
+      <c r="G33" s="35"/>
       <c r="H33" s="32"/>
       <c r="I33" s="32"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="34"/>
+      <c r="L33" s="35"/>
       <c r="M33" s="32"/>
       <c r="N33" s="32"/>
     </row>
@@ -4047,19 +4056,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="33"/>
+      <c r="B34" s="34"/>
       <c r="C34" s="32"/>
       <c r="D34" s="32"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="33"/>
+      <c r="G34" s="34"/>
       <c r="H34" s="32"/>
       <c r="I34" s="32"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="33"/>
+      <c r="L34" s="34"/>
       <c r="M34" s="32"/>
       <c r="N34" s="32"/>
     </row>
@@ -4067,19 +4076,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="34"/>
+      <c r="B35" s="35"/>
       <c r="C35" s="32"/>
       <c r="D35" s="32"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="34"/>
+      <c r="G35" s="35"/>
       <c r="H35" s="32"/>
       <c r="I35" s="32"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="34"/>
+      <c r="L35" s="35"/>
       <c r="M35" s="32"/>
       <c r="N35" s="32"/>
     </row>
@@ -4087,19 +4096,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="33"/>
+      <c r="B36" s="34"/>
       <c r="C36" s="32"/>
       <c r="D36" s="32"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="33"/>
+      <c r="G36" s="34"/>
       <c r="H36" s="32"/>
       <c r="I36" s="32"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="33"/>
+      <c r="L36" s="34"/>
       <c r="M36" s="32"/>
       <c r="N36" s="32"/>
     </row>
@@ -4107,7 +4116,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="36">
+      <c r="B37" s="37">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -4116,7 +4125,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="36">
+      <c r="G37" s="37">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -4125,7 +4134,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="36">
+      <c r="L37" s="37">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -4162,6 +4171,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
     <mergeCell ref="L34:N34"/>
     <mergeCell ref="L6:N6"/>
     <mergeCell ref="B33:D33"/>
@@ -4178,68 +4249,6 @@
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4287,7 +4296,7 @@
         <v>49</v>
       </c>
       <c r="E2" s="18">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="F2" s="18"/>
     </row>
@@ -4305,7 +4314,7 @@
         <v>68</v>
       </c>
       <c r="E3" s="18">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="F3" s="18"/>
     </row>
@@ -4323,7 +4332,7 @@
         <v>49</v>
       </c>
       <c r="E4" s="18">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="F4" s="18"/>
     </row>
@@ -4341,7 +4350,7 @@
         <v>68</v>
       </c>
       <c r="E5" s="18">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="F5" s="18"/>
     </row>

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEB87C96-6194-4692-A133-5D2E7B48E6B3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9995AE91-1A46-40BB-9798-6265DDE944BA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucoes" sheetId="1" r:id="rId1"/>
@@ -447,9 +447,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -460,6 +457,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -801,7 +801,7 @@
       </c>
       <c r="L5" s="14">
         <f>SUM(L6:L7)</f>
-        <v>3200</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
@@ -819,7 +819,7 @@
         <v>21</v>
       </c>
       <c r="L6" s="14">
-        <v>3200</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="L41" s="13">
         <f>SUM(L5,L8,L11,L14,L17,L20,L23,L26,L29,L32,L35,L38)</f>
-        <v>4523</v>
+        <v>3823</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1">
@@ -2828,19 +2828,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="32"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
-      <c r="K1" s="33" t="s">
+      <c r="K1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="32"/>
@@ -2848,19 +2848,19 @@
       <c r="N1" s="32"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
-      <c r="F2" s="33" t="s">
+      <c r="F2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="32"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="K2" s="33" t="s">
+      <c r="K2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="32"/>
@@ -2882,27 +2882,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="35" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="32"/>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="32"/>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="35" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="32"/>
-      <c r="K4" s="36" t="s">
+      <c r="K4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="32"/>
-      <c r="M4" s="36" t="s">
+      <c r="M4" s="35" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="32"/>
@@ -2911,21 +2911,21 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="35">
-        <v>0</v>
-      </c>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
+      <c r="B5" s="34">
+        <v>0</v>
+      </c>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="35"/>
+      <c r="G5" s="34"/>
       <c r="H5" s="32"/>
       <c r="I5" s="32"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="35"/>
+      <c r="L5" s="34"/>
       <c r="M5" s="32"/>
       <c r="N5" s="32"/>
     </row>
@@ -2933,21 +2933,21 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="34">
-        <v>0</v>
-      </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
+      <c r="B6" s="33">
+        <v>0</v>
+      </c>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="34"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="34"/>
+      <c r="L6" s="33"/>
       <c r="M6" s="32"/>
       <c r="N6" s="32"/>
     </row>
@@ -2955,21 +2955,21 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="35">
-        <v>0</v>
-      </c>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
+      <c r="B7" s="34">
+        <v>0</v>
+      </c>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="35"/>
+      <c r="G7" s="34"/>
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="35"/>
+      <c r="L7" s="34"/>
       <c r="M7" s="32"/>
       <c r="N7" s="32"/>
     </row>
@@ -2977,21 +2977,21 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="34">
-        <v>0</v>
-      </c>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
+      <c r="B8" s="33">
+        <v>0</v>
+      </c>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="34"/>
+      <c r="G8" s="33"/>
       <c r="H8" s="32"/>
       <c r="I8" s="32"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="34"/>
+      <c r="L8" s="33"/>
       <c r="M8" s="32"/>
       <c r="N8" s="32"/>
     </row>
@@ -2999,21 +2999,21 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="35">
-        <v>0</v>
-      </c>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
+      <c r="B9" s="34">
+        <v>0</v>
+      </c>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="35"/>
+      <c r="G9" s="34"/>
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="35"/>
+      <c r="L9" s="34"/>
       <c r="M9" s="32"/>
       <c r="N9" s="32"/>
     </row>
@@ -3021,21 +3021,21 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="34">
-        <v>0</v>
-      </c>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
+      <c r="B10" s="33">
+        <v>0</v>
+      </c>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="34"/>
+      <c r="G10" s="33"/>
       <c r="H10" s="32"/>
       <c r="I10" s="32"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="34"/>
+      <c r="L10" s="33"/>
       <c r="M10" s="32"/>
       <c r="N10" s="32"/>
     </row>
@@ -3043,7 +3043,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="37">
+      <c r="B11" s="36">
         <f>SUM(B5:B10)</f>
         <v>0</v>
       </c>
@@ -3052,7 +3052,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="37">
+      <c r="G11" s="36">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -3061,7 +3061,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="37">
+      <c r="L11" s="36">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -3097,19 +3097,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="33" t="s">
+      <c r="A25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
-      <c r="F25" s="33" t="s">
+      <c r="F25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
       <c r="I25" s="32"/>
-      <c r="K25" s="33" t="s">
+      <c r="K25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="32"/>
@@ -3117,19 +3117,19 @@
       <c r="N25" s="32"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="33" t="s">
+      <c r="A26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
-      <c r="F26" s="33" t="s">
+      <c r="F26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="32"/>
       <c r="H26" s="32"/>
       <c r="I26" s="32"/>
-      <c r="K26" s="33" t="s">
+      <c r="K26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="32"/>
@@ -3151,27 +3151,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="32"/>
-      <c r="C28" s="36" t="s">
+      <c r="C28" s="35" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="32"/>
-      <c r="F28" s="36" t="s">
+      <c r="F28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="32"/>
-      <c r="H28" s="36" t="s">
+      <c r="H28" s="35" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="32"/>
-      <c r="K28" s="36" t="s">
+      <c r="K28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="32"/>
-      <c r="M28" s="36" t="s">
+      <c r="M28" s="35" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="32"/>
@@ -3180,7 +3180,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="35">
+      <c r="B29" s="34">
         <v>0</v>
       </c>
       <c r="C29" s="32"/>
@@ -3188,23 +3188,23 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="35"/>
+      <c r="G29" s="34"/>
       <c r="H29" s="32"/>
       <c r="I29" s="32"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="35">
-        <v>0</v>
-      </c>
-      <c r="M29" s="35"/>
-      <c r="N29" s="35"/>
+      <c r="L29" s="34">
+        <v>0</v>
+      </c>
+      <c r="M29" s="34"/>
+      <c r="N29" s="34"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="34">
+      <c r="B30" s="33">
         <v>0</v>
       </c>
       <c r="C30" s="32"/>
@@ -3212,23 +3212,23 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="34"/>
+      <c r="G30" s="33"/>
       <c r="H30" s="32"/>
       <c r="I30" s="32"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="34">
-        <v>0</v>
-      </c>
-      <c r="M30" s="34"/>
-      <c r="N30" s="34"/>
+      <c r="L30" s="33">
+        <v>0</v>
+      </c>
+      <c r="M30" s="33"/>
+      <c r="N30" s="33"/>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1">
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="35">
+      <c r="B31" s="34">
         <v>0</v>
       </c>
       <c r="C31" s="32"/>
@@ -3236,23 +3236,23 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="35"/>
+      <c r="G31" s="34"/>
       <c r="H31" s="32"/>
       <c r="I31" s="32"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="35">
-        <v>0</v>
-      </c>
-      <c r="M31" s="35"/>
-      <c r="N31" s="35"/>
+      <c r="L31" s="34">
+        <v>0</v>
+      </c>
+      <c r="M31" s="34"/>
+      <c r="N31" s="34"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="34">
+      <c r="B32" s="33">
         <v>0</v>
       </c>
       <c r="C32" s="32"/>
@@ -3260,23 +3260,23 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="34"/>
+      <c r="G32" s="33"/>
       <c r="H32" s="32"/>
       <c r="I32" s="32"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="34">
-        <v>0</v>
-      </c>
-      <c r="M32" s="34"/>
-      <c r="N32" s="34"/>
+      <c r="L32" s="33">
+        <v>0</v>
+      </c>
+      <c r="M32" s="33"/>
+      <c r="N32" s="33"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="35">
+      <c r="B33" s="34">
         <v>0</v>
       </c>
       <c r="C33" s="32"/>
@@ -3284,23 +3284,23 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="35"/>
+      <c r="G33" s="34"/>
       <c r="H33" s="32"/>
       <c r="I33" s="32"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="35">
-        <v>0</v>
-      </c>
-      <c r="M33" s="35"/>
-      <c r="N33" s="35"/>
+      <c r="L33" s="34">
+        <v>0</v>
+      </c>
+      <c r="M33" s="34"/>
+      <c r="N33" s="34"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="34">
+      <c r="B34" s="33">
         <v>0</v>
       </c>
       <c r="C34" s="32"/>
@@ -3308,13 +3308,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="34"/>
+      <c r="G34" s="33"/>
       <c r="H34" s="32"/>
       <c r="I34" s="32"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="34">
+      <c r="L34" s="33">
         <v>0</v>
       </c>
       <c r="M34" s="32"/>
@@ -3324,7 +3324,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="37">
+      <c r="B35" s="36">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -3333,7 +3333,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="37">
+      <c r="G35" s="36">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -3342,7 +3342,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="37">
+      <c r="L35" s="36">
         <f>SUM(L29:L34)</f>
         <v>0</v>
       </c>
@@ -3379,6 +3379,56 @@
     </row>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B10:D10"/>
@@ -3395,56 +3445,6 @@
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="H28:I28"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3460,7 +3460,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
@@ -3468,7 +3468,7 @@
       <c r="D1" s="32"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
@@ -3482,11 +3482,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="35" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="35" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="32"/>
@@ -3495,7 +3495,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="35"/>
+      <c r="B5" s="34"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
     </row>
@@ -3503,7 +3503,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="34"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
     </row>
@@ -3511,7 +3511,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="35"/>
+      <c r="B7" s="34"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
     </row>
@@ -3519,7 +3519,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="34"/>
+      <c r="B8" s="33"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32"/>
     </row>
@@ -3527,7 +3527,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="37">
+      <c r="B9" s="36">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -3576,19 +3576,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="32"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
-      <c r="K1" s="33" t="s">
+      <c r="K1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="32"/>
@@ -3596,19 +3596,19 @@
       <c r="N1" s="32"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
-      <c r="F2" s="33" t="s">
+      <c r="F2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="32"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="K2" s="33" t="s">
+      <c r="K2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="32"/>
@@ -3630,27 +3630,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="35" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="32"/>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="32"/>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="35" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="32"/>
-      <c r="K4" s="36" t="s">
+      <c r="K4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="32"/>
-      <c r="M4" s="36" t="s">
+      <c r="M4" s="35" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="32"/>
@@ -3659,19 +3659,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="35"/>
+      <c r="B5" s="34"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="35"/>
+      <c r="G5" s="34"/>
       <c r="H5" s="32"/>
       <c r="I5" s="32"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="35"/>
+      <c r="L5" s="34"/>
       <c r="M5" s="32"/>
       <c r="N5" s="32"/>
     </row>
@@ -3679,19 +3679,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="34"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="34"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="34"/>
+      <c r="L6" s="33"/>
       <c r="M6" s="32"/>
       <c r="N6" s="32"/>
     </row>
@@ -3699,19 +3699,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="35"/>
+      <c r="B7" s="34"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="35"/>
+      <c r="G7" s="34"/>
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="35"/>
+      <c r="L7" s="34"/>
       <c r="M7" s="32"/>
       <c r="N7" s="32"/>
     </row>
@@ -3719,19 +3719,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="34"/>
+      <c r="B8" s="33"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="34"/>
+      <c r="G8" s="33"/>
       <c r="H8" s="32"/>
       <c r="I8" s="32"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="34"/>
+      <c r="L8" s="33"/>
       <c r="M8" s="32"/>
       <c r="N8" s="32"/>
     </row>
@@ -3739,19 +3739,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="35"/>
+      <c r="B9" s="34"/>
       <c r="C9" s="32"/>
       <c r="D9" s="32"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="35"/>
+      <c r="G9" s="34"/>
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="35"/>
+      <c r="L9" s="34"/>
       <c r="M9" s="32"/>
       <c r="N9" s="32"/>
     </row>
@@ -3759,19 +3759,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="34"/>
+      <c r="B10" s="33"/>
       <c r="C10" s="32"/>
       <c r="D10" s="32"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="34"/>
+      <c r="G10" s="33"/>
       <c r="H10" s="32"/>
       <c r="I10" s="32"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="34"/>
+      <c r="L10" s="33"/>
       <c r="M10" s="32"/>
       <c r="N10" s="32"/>
     </row>
@@ -3779,19 +3779,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="35"/>
+      <c r="B11" s="34"/>
       <c r="C11" s="32"/>
       <c r="D11" s="32"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="35"/>
+      <c r="G11" s="34"/>
       <c r="H11" s="32"/>
       <c r="I11" s="32"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="35"/>
+      <c r="L11" s="34"/>
       <c r="M11" s="32"/>
       <c r="N11" s="32"/>
     </row>
@@ -3799,19 +3799,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="34"/>
+      <c r="B12" s="33"/>
       <c r="C12" s="32"/>
       <c r="D12" s="32"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="34"/>
+      <c r="G12" s="33"/>
       <c r="H12" s="32"/>
       <c r="I12" s="32"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="34"/>
+      <c r="L12" s="33"/>
       <c r="M12" s="32"/>
       <c r="N12" s="32"/>
     </row>
@@ -3819,7 +3819,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="37">
+      <c r="B13" s="36">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3828,7 +3828,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="37">
+      <c r="G13" s="36">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3837,7 +3837,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="37">
+      <c r="L13" s="36">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3873,19 +3873,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="33" t="s">
+      <c r="A25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
-      <c r="F25" s="33" t="s">
+      <c r="F25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
       <c r="I25" s="32"/>
-      <c r="K25" s="33" t="s">
+      <c r="K25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="32"/>
@@ -3893,19 +3893,19 @@
       <c r="N25" s="32"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="33" t="s">
+      <c r="A26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
-      <c r="F26" s="33" t="s">
+      <c r="F26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="32"/>
       <c r="H26" s="32"/>
       <c r="I26" s="32"/>
-      <c r="K26" s="33" t="s">
+      <c r="K26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="32"/>
@@ -3927,27 +3927,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="32"/>
-      <c r="C28" s="36" t="s">
+      <c r="C28" s="35" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="32"/>
-      <c r="F28" s="36" t="s">
+      <c r="F28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="32"/>
-      <c r="H28" s="36" t="s">
+      <c r="H28" s="35" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="32"/>
-      <c r="K28" s="36" t="s">
+      <c r="K28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="32"/>
-      <c r="M28" s="36" t="s">
+      <c r="M28" s="35" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="32"/>
@@ -3956,19 +3956,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="35"/>
+      <c r="B29" s="34"/>
       <c r="C29" s="32"/>
       <c r="D29" s="32"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="35"/>
+      <c r="G29" s="34"/>
       <c r="H29" s="32"/>
       <c r="I29" s="32"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="35"/>
+      <c r="L29" s="34"/>
       <c r="M29" s="32"/>
       <c r="N29" s="32"/>
     </row>
@@ -3976,19 +3976,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="34"/>
+      <c r="B30" s="33"/>
       <c r="C30" s="32"/>
       <c r="D30" s="32"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="34"/>
+      <c r="G30" s="33"/>
       <c r="H30" s="32"/>
       <c r="I30" s="32"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="34"/>
+      <c r="L30" s="33"/>
       <c r="M30" s="32"/>
       <c r="N30" s="32"/>
     </row>
@@ -3996,19 +3996,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="35"/>
+      <c r="B31" s="34"/>
       <c r="C31" s="32"/>
       <c r="D31" s="32"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="35"/>
+      <c r="G31" s="34"/>
       <c r="H31" s="32"/>
       <c r="I31" s="32"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="35"/>
+      <c r="L31" s="34"/>
       <c r="M31" s="32"/>
       <c r="N31" s="32"/>
     </row>
@@ -4016,19 +4016,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="34"/>
+      <c r="B32" s="33"/>
       <c r="C32" s="32"/>
       <c r="D32" s="32"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="34"/>
+      <c r="G32" s="33"/>
       <c r="H32" s="32"/>
       <c r="I32" s="32"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="34"/>
+      <c r="L32" s="33"/>
       <c r="M32" s="32"/>
       <c r="N32" s="32"/>
     </row>
@@ -4036,19 +4036,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="35"/>
+      <c r="B33" s="34"/>
       <c r="C33" s="32"/>
       <c r="D33" s="32"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="35"/>
+      <c r="G33" s="34"/>
       <c r="H33" s="32"/>
       <c r="I33" s="32"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="35"/>
+      <c r="L33" s="34"/>
       <c r="M33" s="32"/>
       <c r="N33" s="32"/>
     </row>
@@ -4056,19 +4056,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="34"/>
+      <c r="B34" s="33"/>
       <c r="C34" s="32"/>
       <c r="D34" s="32"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="34"/>
+      <c r="G34" s="33"/>
       <c r="H34" s="32"/>
       <c r="I34" s="32"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="34"/>
+      <c r="L34" s="33"/>
       <c r="M34" s="32"/>
       <c r="N34" s="32"/>
     </row>
@@ -4076,19 +4076,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="35"/>
+      <c r="B35" s="34"/>
       <c r="C35" s="32"/>
       <c r="D35" s="32"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="35"/>
+      <c r="G35" s="34"/>
       <c r="H35" s="32"/>
       <c r="I35" s="32"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="35"/>
+      <c r="L35" s="34"/>
       <c r="M35" s="32"/>
       <c r="N35" s="32"/>
     </row>
@@ -4096,19 +4096,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="34"/>
+      <c r="B36" s="33"/>
       <c r="C36" s="32"/>
       <c r="D36" s="32"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="34"/>
+      <c r="G36" s="33"/>
       <c r="H36" s="32"/>
       <c r="I36" s="32"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="34"/>
+      <c r="L36" s="33"/>
       <c r="M36" s="32"/>
       <c r="N36" s="32"/>
     </row>
@@ -4116,7 +4116,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="37">
+      <c r="B37" s="36">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -4125,7 +4125,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="37">
+      <c r="G37" s="36">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -4134,7 +4134,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="37">
+      <c r="L37" s="36">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -4171,6 +4171,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
     <mergeCell ref="G36:I36"/>
     <mergeCell ref="L32:N32"/>
     <mergeCell ref="L13:N13"/>
@@ -4187,68 +4249,6 @@
     <mergeCell ref="L33:N33"/>
     <mergeCell ref="L35:N35"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="L9:N9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9995AE91-1A46-40BB-9798-6265DDE944BA}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F7E81C6-00CF-4F86-A230-16F28674B79B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucoes" sheetId="1" r:id="rId1"/>
@@ -447,6 +447,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -457,9 +460,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2828,19 +2828,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
-      <c r="F1" s="37" t="s">
+      <c r="F1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="32"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
-      <c r="K1" s="37" t="s">
+      <c r="K1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="32"/>
@@ -2848,19 +2848,19 @@
       <c r="N1" s="32"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
-      <c r="F2" s="37" t="s">
+      <c r="F2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="32"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="K2" s="37" t="s">
+      <c r="K2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="32"/>
@@ -2882,27 +2882,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="36" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="32"/>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="32"/>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="36" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="32"/>
-      <c r="K4" s="35" t="s">
+      <c r="K4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="32"/>
-      <c r="M4" s="35" t="s">
+      <c r="M4" s="36" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="32"/>
@@ -2911,21 +2911,21 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="34">
-        <v>0</v>
-      </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
+      <c r="B5" s="35">
+        <v>0</v>
+      </c>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="34"/>
+      <c r="G5" s="35"/>
       <c r="H5" s="32"/>
       <c r="I5" s="32"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="34"/>
+      <c r="L5" s="35"/>
       <c r="M5" s="32"/>
       <c r="N5" s="32"/>
     </row>
@@ -2933,21 +2933,21 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="33">
-        <v>0</v>
-      </c>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
+      <c r="B6" s="34">
+        <v>0</v>
+      </c>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="33"/>
+      <c r="G6" s="34"/>
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="33"/>
+      <c r="L6" s="34"/>
       <c r="M6" s="32"/>
       <c r="N6" s="32"/>
     </row>
@@ -2955,21 +2955,21 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="34">
-        <v>0</v>
-      </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
+      <c r="B7" s="35">
+        <v>0</v>
+      </c>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="34"/>
+      <c r="G7" s="35"/>
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="34"/>
+      <c r="L7" s="35"/>
       <c r="M7" s="32"/>
       <c r="N7" s="32"/>
     </row>
@@ -2977,21 +2977,21 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="33">
-        <v>0</v>
-      </c>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
+      <c r="B8" s="34">
+        <v>0</v>
+      </c>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="33"/>
+      <c r="G8" s="34"/>
       <c r="H8" s="32"/>
       <c r="I8" s="32"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="33"/>
+      <c r="L8" s="34"/>
       <c r="M8" s="32"/>
       <c r="N8" s="32"/>
     </row>
@@ -2999,21 +2999,21 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="34">
-        <v>0</v>
-      </c>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
+      <c r="B9" s="35">
+        <v>0</v>
+      </c>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="34"/>
+      <c r="G9" s="35"/>
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="34"/>
+      <c r="L9" s="35"/>
       <c r="M9" s="32"/>
       <c r="N9" s="32"/>
     </row>
@@ -3021,21 +3021,21 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="33">
-        <v>0</v>
-      </c>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
+      <c r="B10" s="34">
+        <v>0</v>
+      </c>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="33"/>
+      <c r="G10" s="34"/>
       <c r="H10" s="32"/>
       <c r="I10" s="32"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="33"/>
+      <c r="L10" s="34"/>
       <c r="M10" s="32"/>
       <c r="N10" s="32"/>
     </row>
@@ -3043,7 +3043,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="36">
+      <c r="B11" s="37">
         <f>SUM(B5:B10)</f>
         <v>0</v>
       </c>
@@ -3052,7 +3052,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="36">
+      <c r="G11" s="37">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -3061,7 +3061,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="36">
+      <c r="L11" s="37">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -3097,19 +3097,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="37" t="s">
+      <c r="A25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
-      <c r="F25" s="37" t="s">
+      <c r="F25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
       <c r="I25" s="32"/>
-      <c r="K25" s="37" t="s">
+      <c r="K25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="32"/>
@@ -3117,19 +3117,19 @@
       <c r="N25" s="32"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="37" t="s">
+      <c r="A26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
-      <c r="F26" s="37" t="s">
+      <c r="F26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="32"/>
       <c r="H26" s="32"/>
       <c r="I26" s="32"/>
-      <c r="K26" s="37" t="s">
+      <c r="K26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="32"/>
@@ -3151,27 +3151,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="35" t="s">
+      <c r="A28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="32"/>
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="36" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="32"/>
-      <c r="F28" s="35" t="s">
+      <c r="F28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="32"/>
-      <c r="H28" s="35" t="s">
+      <c r="H28" s="36" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="32"/>
-      <c r="K28" s="35" t="s">
+      <c r="K28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="32"/>
-      <c r="M28" s="35" t="s">
+      <c r="M28" s="36" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="32"/>
@@ -3180,7 +3180,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="34">
+      <c r="B29" s="35">
         <v>0</v>
       </c>
       <c r="C29" s="32"/>
@@ -3188,23 +3188,23 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="34"/>
+      <c r="G29" s="35"/>
       <c r="H29" s="32"/>
       <c r="I29" s="32"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="34">
-        <v>0</v>
-      </c>
-      <c r="M29" s="34"/>
-      <c r="N29" s="34"/>
+      <c r="L29" s="35">
+        <v>0</v>
+      </c>
+      <c r="M29" s="35"/>
+      <c r="N29" s="35"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="33">
+      <c r="B30" s="34">
         <v>0</v>
       </c>
       <c r="C30" s="32"/>
@@ -3212,23 +3212,23 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="33"/>
+      <c r="G30" s="34"/>
       <c r="H30" s="32"/>
       <c r="I30" s="32"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="33">
-        <v>0</v>
-      </c>
-      <c r="M30" s="33"/>
-      <c r="N30" s="33"/>
+      <c r="L30" s="34">
+        <v>0</v>
+      </c>
+      <c r="M30" s="34"/>
+      <c r="N30" s="34"/>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1">
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="34">
+      <c r="B31" s="35">
         <v>0</v>
       </c>
       <c r="C31" s="32"/>
@@ -3236,23 +3236,23 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="34"/>
+      <c r="G31" s="35"/>
       <c r="H31" s="32"/>
       <c r="I31" s="32"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="34">
-        <v>0</v>
-      </c>
-      <c r="M31" s="34"/>
-      <c r="N31" s="34"/>
+      <c r="L31" s="35">
+        <v>0</v>
+      </c>
+      <c r="M31" s="35"/>
+      <c r="N31" s="35"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="33">
+      <c r="B32" s="34">
         <v>0</v>
       </c>
       <c r="C32" s="32"/>
@@ -3260,23 +3260,23 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="33"/>
+      <c r="G32" s="34"/>
       <c r="H32" s="32"/>
       <c r="I32" s="32"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="33">
-        <v>0</v>
-      </c>
-      <c r="M32" s="33"/>
-      <c r="N32" s="33"/>
+      <c r="L32" s="34">
+        <v>0</v>
+      </c>
+      <c r="M32" s="34"/>
+      <c r="N32" s="34"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="34">
+      <c r="B33" s="35">
         <v>0</v>
       </c>
       <c r="C33" s="32"/>
@@ -3284,23 +3284,23 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="34"/>
+      <c r="G33" s="35"/>
       <c r="H33" s="32"/>
       <c r="I33" s="32"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="34">
-        <v>0</v>
-      </c>
-      <c r="M33" s="34"/>
-      <c r="N33" s="34"/>
+      <c r="L33" s="35">
+        <v>0</v>
+      </c>
+      <c r="M33" s="35"/>
+      <c r="N33" s="35"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="33">
+      <c r="B34" s="34">
         <v>0</v>
       </c>
       <c r="C34" s="32"/>
@@ -3308,13 +3308,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="33"/>
+      <c r="G34" s="34"/>
       <c r="H34" s="32"/>
       <c r="I34" s="32"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="33">
+      <c r="L34" s="34">
         <v>0</v>
       </c>
       <c r="M34" s="32"/>
@@ -3324,7 +3324,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="36">
+      <c r="B35" s="37">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -3333,7 +3333,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="36">
+      <c r="G35" s="37">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -3342,7 +3342,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="36">
+      <c r="L35" s="37">
         <f>SUM(L29:L34)</f>
         <v>0</v>
       </c>
@@ -3379,13 +3379,49 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="L11:N11"/>
@@ -3402,49 +3438,13 @@
     <mergeCell ref="K2:N2"/>
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3460,7 +3460,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
@@ -3468,7 +3468,7 @@
       <c r="D1" s="32"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
@@ -3482,11 +3482,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="36" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="36" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="32"/>
@@ -3495,7 +3495,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="34"/>
+      <c r="B5" s="35"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
     </row>
@@ -3503,7 +3503,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="33"/>
+      <c r="B6" s="34"/>
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
     </row>
@@ -3511,7 +3511,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="34"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
     </row>
@@ -3519,7 +3519,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="33"/>
+      <c r="B8" s="34"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32"/>
     </row>
@@ -3527,7 +3527,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="36">
+      <c r="B9" s="37">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -3576,19 +3576,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
-      <c r="F1" s="37" t="s">
+      <c r="F1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="32"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
-      <c r="K1" s="37" t="s">
+      <c r="K1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="32"/>
@@ -3596,19 +3596,19 @@
       <c r="N1" s="32"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
-      <c r="F2" s="37" t="s">
+      <c r="F2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="32"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="K2" s="37" t="s">
+      <c r="K2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="32"/>
@@ -3630,27 +3630,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="36" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="32"/>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="32"/>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="36" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="32"/>
-      <c r="K4" s="35" t="s">
+      <c r="K4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="32"/>
-      <c r="M4" s="35" t="s">
+      <c r="M4" s="36" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="32"/>
@@ -3659,19 +3659,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="34"/>
+      <c r="B5" s="35"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="34"/>
+      <c r="G5" s="35"/>
       <c r="H5" s="32"/>
       <c r="I5" s="32"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="34"/>
+      <c r="L5" s="35"/>
       <c r="M5" s="32"/>
       <c r="N5" s="32"/>
     </row>
@@ -3679,19 +3679,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="33"/>
+      <c r="B6" s="34"/>
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="33"/>
+      <c r="G6" s="34"/>
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="33"/>
+      <c r="L6" s="34"/>
       <c r="M6" s="32"/>
       <c r="N6" s="32"/>
     </row>
@@ -3699,19 +3699,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="34"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="34"/>
+      <c r="G7" s="35"/>
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="34"/>
+      <c r="L7" s="35"/>
       <c r="M7" s="32"/>
       <c r="N7" s="32"/>
     </row>
@@ -3719,19 +3719,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="33"/>
+      <c r="B8" s="34"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="33"/>
+      <c r="G8" s="34"/>
       <c r="H8" s="32"/>
       <c r="I8" s="32"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="33"/>
+      <c r="L8" s="34"/>
       <c r="M8" s="32"/>
       <c r="N8" s="32"/>
     </row>
@@ -3739,19 +3739,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="34"/>
+      <c r="B9" s="35"/>
       <c r="C9" s="32"/>
       <c r="D9" s="32"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="34"/>
+      <c r="G9" s="35"/>
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="34"/>
+      <c r="L9" s="35"/>
       <c r="M9" s="32"/>
       <c r="N9" s="32"/>
     </row>
@@ -3759,19 +3759,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="33"/>
+      <c r="B10" s="34"/>
       <c r="C10" s="32"/>
       <c r="D10" s="32"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="33"/>
+      <c r="G10" s="34"/>
       <c r="H10" s="32"/>
       <c r="I10" s="32"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="33"/>
+      <c r="L10" s="34"/>
       <c r="M10" s="32"/>
       <c r="N10" s="32"/>
     </row>
@@ -3779,19 +3779,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="34"/>
+      <c r="B11" s="35"/>
       <c r="C11" s="32"/>
       <c r="D11" s="32"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="34"/>
+      <c r="G11" s="35"/>
       <c r="H11" s="32"/>
       <c r="I11" s="32"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="34"/>
+      <c r="L11" s="35"/>
       <c r="M11" s="32"/>
       <c r="N11" s="32"/>
     </row>
@@ -3799,19 +3799,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="33"/>
+      <c r="B12" s="34"/>
       <c r="C12" s="32"/>
       <c r="D12" s="32"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="33"/>
+      <c r="G12" s="34"/>
       <c r="H12" s="32"/>
       <c r="I12" s="32"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="33"/>
+      <c r="L12" s="34"/>
       <c r="M12" s="32"/>
       <c r="N12" s="32"/>
     </row>
@@ -3819,7 +3819,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="36">
+      <c r="B13" s="37">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3828,7 +3828,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="36">
+      <c r="G13" s="37">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3837,7 +3837,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="36">
+      <c r="L13" s="37">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3873,19 +3873,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="37" t="s">
+      <c r="A25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
-      <c r="F25" s="37" t="s">
+      <c r="F25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
       <c r="I25" s="32"/>
-      <c r="K25" s="37" t="s">
+      <c r="K25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="32"/>
@@ -3893,19 +3893,19 @@
       <c r="N25" s="32"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="37" t="s">
+      <c r="A26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
-      <c r="F26" s="37" t="s">
+      <c r="F26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="32"/>
       <c r="H26" s="32"/>
       <c r="I26" s="32"/>
-      <c r="K26" s="37" t="s">
+      <c r="K26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="32"/>
@@ -3927,27 +3927,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="35" t="s">
+      <c r="A28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="32"/>
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="36" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="32"/>
-      <c r="F28" s="35" t="s">
+      <c r="F28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="32"/>
-      <c r="H28" s="35" t="s">
+      <c r="H28" s="36" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="32"/>
-      <c r="K28" s="35" t="s">
+      <c r="K28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="32"/>
-      <c r="M28" s="35" t="s">
+      <c r="M28" s="36" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="32"/>
@@ -3956,19 +3956,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="34"/>
+      <c r="B29" s="35"/>
       <c r="C29" s="32"/>
       <c r="D29" s="32"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="34"/>
+      <c r="G29" s="35"/>
       <c r="H29" s="32"/>
       <c r="I29" s="32"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="34"/>
+      <c r="L29" s="35"/>
       <c r="M29" s="32"/>
       <c r="N29" s="32"/>
     </row>
@@ -3976,19 +3976,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="33"/>
+      <c r="B30" s="34"/>
       <c r="C30" s="32"/>
       <c r="D30" s="32"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="33"/>
+      <c r="G30" s="34"/>
       <c r="H30" s="32"/>
       <c r="I30" s="32"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="33"/>
+      <c r="L30" s="34"/>
       <c r="M30" s="32"/>
       <c r="N30" s="32"/>
     </row>
@@ -3996,19 +3996,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="34"/>
+      <c r="B31" s="35"/>
       <c r="C31" s="32"/>
       <c r="D31" s="32"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="34"/>
+      <c r="G31" s="35"/>
       <c r="H31" s="32"/>
       <c r="I31" s="32"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="34"/>
+      <c r="L31" s="35"/>
       <c r="M31" s="32"/>
       <c r="N31" s="32"/>
     </row>
@@ -4016,19 +4016,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="33"/>
+      <c r="B32" s="34"/>
       <c r="C32" s="32"/>
       <c r="D32" s="32"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="33"/>
+      <c r="G32" s="34"/>
       <c r="H32" s="32"/>
       <c r="I32" s="32"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="33"/>
+      <c r="L32" s="34"/>
       <c r="M32" s="32"/>
       <c r="N32" s="32"/>
     </row>
@@ -4036,19 +4036,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="34"/>
+      <c r="B33" s="35"/>
       <c r="C33" s="32"/>
       <c r="D33" s="32"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="34"/>
+      <c r="G33" s="35"/>
       <c r="H33" s="32"/>
       <c r="I33" s="32"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="34"/>
+      <c r="L33" s="35"/>
       <c r="M33" s="32"/>
       <c r="N33" s="32"/>
     </row>
@@ -4056,19 +4056,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="33"/>
+      <c r="B34" s="34"/>
       <c r="C34" s="32"/>
       <c r="D34" s="32"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="33"/>
+      <c r="G34" s="34"/>
       <c r="H34" s="32"/>
       <c r="I34" s="32"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="33"/>
+      <c r="L34" s="34"/>
       <c r="M34" s="32"/>
       <c r="N34" s="32"/>
     </row>
@@ -4076,19 +4076,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="34"/>
+      <c r="B35" s="35"/>
       <c r="C35" s="32"/>
       <c r="D35" s="32"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="34"/>
+      <c r="G35" s="35"/>
       <c r="H35" s="32"/>
       <c r="I35" s="32"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="34"/>
+      <c r="L35" s="35"/>
       <c r="M35" s="32"/>
       <c r="N35" s="32"/>
     </row>
@@ -4096,19 +4096,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="33"/>
+      <c r="B36" s="34"/>
       <c r="C36" s="32"/>
       <c r="D36" s="32"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="33"/>
+      <c r="G36" s="34"/>
       <c r="H36" s="32"/>
       <c r="I36" s="32"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="33"/>
+      <c r="L36" s="34"/>
       <c r="M36" s="32"/>
       <c r="N36" s="32"/>
     </row>
@@ -4116,7 +4116,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="36">
+      <c r="B37" s="37">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -4125,7 +4125,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="36">
+      <c r="G37" s="37">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -4134,7 +4134,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="36">
+      <c r="L37" s="37">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -4171,6 +4171,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
     <mergeCell ref="L34:N34"/>
     <mergeCell ref="L6:N6"/>
     <mergeCell ref="B33:D33"/>
@@ -4187,68 +4249,6 @@
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4936,7 +4936,7 @@
         <v>49</v>
       </c>
       <c r="E38" s="18">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F38" s="18"/>
     </row>
@@ -4954,7 +4954,7 @@
         <v>68</v>
       </c>
       <c r="E39" s="18">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F39" s="18"/>
     </row>

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F7E81C6-00CF-4F86-A230-16F28674B79B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BECACB3D-ECF2-45A7-9611-416987491B56}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucoes" sheetId="1" r:id="rId1"/>
@@ -447,9 +447,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -460,6 +457,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -787,7 +787,7 @@
       </c>
       <c r="B5" s="21">
         <f>SUM(B6:B7)</f>
-        <v>2100</v>
+        <v>2800</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>20</v>
@@ -801,7 +801,7 @@
       </c>
       <c r="L5" s="14">
         <f>SUM(L6:L7)</f>
-        <v>2500</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
@@ -809,7 +809,7 @@
         <v>21</v>
       </c>
       <c r="B6" s="14">
-        <v>900</v>
+        <v>1700</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>21</v>
@@ -819,7 +819,7 @@
         <v>21</v>
       </c>
       <c r="L6" s="14">
-        <v>2500</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
@@ -827,7 +827,7 @@
         <v>22</v>
       </c>
       <c r="B7" s="14">
-        <v>1200</v>
+        <v>1100</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>22</v>
@@ -858,7 +858,7 @@
       </c>
       <c r="L8" s="15">
         <f>SUM(L9:L10)</f>
-        <v>500</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1">
@@ -876,7 +876,7 @@
         <v>21</v>
       </c>
       <c r="L9" s="15">
-        <v>500</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
@@ -950,7 +950,7 @@
       </c>
       <c r="B14" s="15">
         <f>SUM(B15:B16)</f>
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>25</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="L14" s="15">
         <f>SUM(L15:L16)</f>
-        <v>323</v>
+        <v>300</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1">
@@ -972,7 +972,7 @@
         <v>21</v>
       </c>
       <c r="B15" s="15">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>21</v>
@@ -982,8 +982,7 @@
         <v>21</v>
       </c>
       <c r="L15" s="15">
-        <f>194+129</f>
-        <v>323</v>
+        <v>300</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1">
@@ -1115,7 +1114,7 @@
       </c>
       <c r="G23" s="14">
         <f>SUM(G24:G25)</f>
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="K23" s="7" t="s">
         <v>28</v>
@@ -1134,7 +1133,7 @@
         <v>21</v>
       </c>
       <c r="G24" s="14">
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="K24" s="7" t="s">
         <v>21</v>
@@ -1212,7 +1211,7 @@
       </c>
       <c r="B29" s="14">
         <f>SUM(B30:B31)</f>
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>30</v>
@@ -1226,16 +1225,14 @@
       </c>
       <c r="L29" s="14">
         <f>SUM(L30:L31)</f>
-        <v>500</v>
+        <v>250</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1">
       <c r="A30" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B30" s="14">
-        <v>600</v>
-      </c>
+      <c r="B30" s="14"/>
       <c r="F30" s="7" t="s">
         <v>21</v>
       </c>
@@ -1244,7 +1241,7 @@
         <v>21</v>
       </c>
       <c r="L30" s="14">
-        <v>500</v>
+        <v>250</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1">
@@ -1267,7 +1264,7 @@
       </c>
       <c r="B32" s="15">
         <f>SUM(B33:B34)</f>
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>31</v>
@@ -1288,9 +1285,7 @@
       <c r="A33" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="15">
-        <v>31</v>
-      </c>
+      <c r="B33" s="15"/>
       <c r="F33" s="9" t="s">
         <v>21</v>
       </c>
@@ -1371,7 +1366,7 @@
       </c>
       <c r="B38" s="22">
         <f>SUM(B39:B40)</f>
-        <v>30</v>
+        <v>140</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>72</v>
@@ -1385,7 +1380,7 @@
       </c>
       <c r="L38" s="23">
         <f>SUM(L39:L40)</f>
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="15" customHeight="1">
@@ -1393,7 +1388,7 @@
         <v>21</v>
       </c>
       <c r="B39" s="15">
-        <v>30</v>
+        <v>140</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>21</v>
@@ -1402,7 +1397,9 @@
       <c r="K39" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L39" s="15"/>
+      <c r="L39" s="15">
+        <v>20</v>
+      </c>
     </row>
     <row r="40" spans="1:14" ht="15" customHeight="1">
       <c r="A40" s="9" t="s">
@@ -1424,21 +1421,21 @@
       </c>
       <c r="B41" s="13">
         <f>SUM(B5,B8,B11,B14,B17,B20,B23,B26,B29,B32,B35,B38)</f>
-        <v>3311</v>
+        <v>4220</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G41" s="13">
         <f>SUM(G5,G8,G11,G14,G17,G20,G23,G26,G29,G32,G35,G38)</f>
-        <v>350</v>
+        <v>500</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="L41" s="13">
         <f>SUM(L5,L8,L11,L14,L17,L20,L23,L26,L29,L32,L35,L38)</f>
-        <v>3823</v>
+        <v>4440</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1">
@@ -1541,14 +1538,14 @@
       </c>
       <c r="G53" s="14">
         <f>SUM(G54:G55)</f>
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="K53" s="7" t="s">
         <v>20</v>
       </c>
       <c r="L53" s="14">
         <f>SUM(L54:L55)</f>
-        <v>0</v>
+        <v>700</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="15" customHeight="1">
@@ -1559,11 +1556,15 @@
       <c r="F54" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G54" s="14"/>
+      <c r="G54" s="14">
+        <v>380</v>
+      </c>
       <c r="K54" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="L54" s="14"/>
+      <c r="L54" s="14">
+        <v>700</v>
+      </c>
     </row>
     <row r="55" spans="1:14" ht="15" customHeight="1">
       <c r="A55" s="7" t="s">
@@ -1694,7 +1695,7 @@
       </c>
       <c r="G62" s="15">
         <f>SUM(G63:G64)</f>
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K62" s="9" t="s">
         <v>25</v>
@@ -1712,7 +1713,9 @@
       <c r="F63" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G63" s="15"/>
+      <c r="G63" s="15">
+        <v>16</v>
+      </c>
       <c r="K63" s="9" t="s">
         <v>21</v>
       </c>
@@ -2155,14 +2158,14 @@
       </c>
       <c r="G89" s="13">
         <f>SUM(G53,G56,G59,G62,G65,G68,G71,G74,G77,G80,G83,G86)</f>
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="K89" s="8" t="s">
         <v>34</v>
       </c>
       <c r="L89" s="13">
         <f>SUM(L53,L56,L59,L62,L65,L68,L71,L74,L77,L80,L83,L86)</f>
-        <v>0</v>
+        <v>700</v>
       </c>
     </row>
     <row r="90" spans="1:14" ht="15" customHeight="1">
@@ -2828,19 +2831,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="32"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
-      <c r="K1" s="33" t="s">
+      <c r="K1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="32"/>
@@ -2848,19 +2851,19 @@
       <c r="N1" s="32"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
-      <c r="F2" s="33" t="s">
+      <c r="F2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="32"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="K2" s="33" t="s">
+      <c r="K2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="32"/>
@@ -2882,27 +2885,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="35" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="32"/>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="32"/>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="35" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="32"/>
-      <c r="K4" s="36" t="s">
+      <c r="K4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="32"/>
-      <c r="M4" s="36" t="s">
+      <c r="M4" s="35" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="32"/>
@@ -2911,21 +2914,21 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="35">
-        <v>0</v>
-      </c>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
+      <c r="B5" s="34">
+        <v>0</v>
+      </c>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="35"/>
+      <c r="G5" s="34"/>
       <c r="H5" s="32"/>
       <c r="I5" s="32"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="35"/>
+      <c r="L5" s="34"/>
       <c r="M5" s="32"/>
       <c r="N5" s="32"/>
     </row>
@@ -2933,21 +2936,21 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="34">
-        <v>0</v>
-      </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
+      <c r="B6" s="33">
+        <v>0</v>
+      </c>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="34"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="34"/>
+      <c r="L6" s="33"/>
       <c r="M6" s="32"/>
       <c r="N6" s="32"/>
     </row>
@@ -2955,21 +2958,21 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="35">
-        <v>0</v>
-      </c>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
+      <c r="B7" s="34">
+        <v>0</v>
+      </c>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="35"/>
+      <c r="G7" s="34"/>
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="35"/>
+      <c r="L7" s="34"/>
       <c r="M7" s="32"/>
       <c r="N7" s="32"/>
     </row>
@@ -2977,21 +2980,21 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="34">
-        <v>0</v>
-      </c>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
+      <c r="B8" s="33">
+        <v>0</v>
+      </c>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="34"/>
+      <c r="G8" s="33"/>
       <c r="H8" s="32"/>
       <c r="I8" s="32"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="34"/>
+      <c r="L8" s="33"/>
       <c r="M8" s="32"/>
       <c r="N8" s="32"/>
     </row>
@@ -2999,21 +3002,21 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="35">
-        <v>0</v>
-      </c>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
+      <c r="B9" s="34">
+        <v>0</v>
+      </c>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="35"/>
+      <c r="G9" s="34"/>
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="35"/>
+      <c r="L9" s="34"/>
       <c r="M9" s="32"/>
       <c r="N9" s="32"/>
     </row>
@@ -3021,21 +3024,21 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="34">
-        <v>0</v>
-      </c>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
+      <c r="B10" s="33">
+        <v>0</v>
+      </c>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="34"/>
+      <c r="G10" s="33"/>
       <c r="H10" s="32"/>
       <c r="I10" s="32"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="34"/>
+      <c r="L10" s="33"/>
       <c r="M10" s="32"/>
       <c r="N10" s="32"/>
     </row>
@@ -3043,7 +3046,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="37">
+      <c r="B11" s="36">
         <f>SUM(B5:B10)</f>
         <v>0</v>
       </c>
@@ -3052,7 +3055,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="37">
+      <c r="G11" s="36">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -3061,7 +3064,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="37">
+      <c r="L11" s="36">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -3097,19 +3100,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="33" t="s">
+      <c r="A25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
-      <c r="F25" s="33" t="s">
+      <c r="F25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
       <c r="I25" s="32"/>
-      <c r="K25" s="33" t="s">
+      <c r="K25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="32"/>
@@ -3117,19 +3120,19 @@
       <c r="N25" s="32"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="33" t="s">
+      <c r="A26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
-      <c r="F26" s="33" t="s">
+      <c r="F26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="32"/>
       <c r="H26" s="32"/>
       <c r="I26" s="32"/>
-      <c r="K26" s="33" t="s">
+      <c r="K26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="32"/>
@@ -3151,27 +3154,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="32"/>
-      <c r="C28" s="36" t="s">
+      <c r="C28" s="35" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="32"/>
-      <c r="F28" s="36" t="s">
+      <c r="F28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="32"/>
-      <c r="H28" s="36" t="s">
+      <c r="H28" s="35" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="32"/>
-      <c r="K28" s="36" t="s">
+      <c r="K28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="32"/>
-      <c r="M28" s="36" t="s">
+      <c r="M28" s="35" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="32"/>
@@ -3180,7 +3183,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="35">
+      <c r="B29" s="34">
         <v>0</v>
       </c>
       <c r="C29" s="32"/>
@@ -3188,23 +3191,23 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="35"/>
+      <c r="G29" s="34"/>
       <c r="H29" s="32"/>
       <c r="I29" s="32"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="35">
-        <v>0</v>
-      </c>
-      <c r="M29" s="35"/>
-      <c r="N29" s="35"/>
+      <c r="L29" s="34">
+        <v>0</v>
+      </c>
+      <c r="M29" s="34"/>
+      <c r="N29" s="34"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="34">
+      <c r="B30" s="33">
         <v>0</v>
       </c>
       <c r="C30" s="32"/>
@@ -3212,23 +3215,23 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="34"/>
+      <c r="G30" s="33"/>
       <c r="H30" s="32"/>
       <c r="I30" s="32"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="34">
-        <v>0</v>
-      </c>
-      <c r="M30" s="34"/>
-      <c r="N30" s="34"/>
+      <c r="L30" s="33">
+        <v>0</v>
+      </c>
+      <c r="M30" s="33"/>
+      <c r="N30" s="33"/>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1">
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="35">
+      <c r="B31" s="34">
         <v>0</v>
       </c>
       <c r="C31" s="32"/>
@@ -3236,23 +3239,23 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="35"/>
+      <c r="G31" s="34"/>
       <c r="H31" s="32"/>
       <c r="I31" s="32"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="35">
-        <v>0</v>
-      </c>
-      <c r="M31" s="35"/>
-      <c r="N31" s="35"/>
+      <c r="L31" s="34">
+        <v>0</v>
+      </c>
+      <c r="M31" s="34"/>
+      <c r="N31" s="34"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="34">
+      <c r="B32" s="33">
         <v>0</v>
       </c>
       <c r="C32" s="32"/>
@@ -3260,23 +3263,23 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="34"/>
+      <c r="G32" s="33"/>
       <c r="H32" s="32"/>
       <c r="I32" s="32"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="34">
-        <v>0</v>
-      </c>
-      <c r="M32" s="34"/>
-      <c r="N32" s="34"/>
+      <c r="L32" s="33">
+        <v>0</v>
+      </c>
+      <c r="M32" s="33"/>
+      <c r="N32" s="33"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="35">
+      <c r="B33" s="34">
         <v>0</v>
       </c>
       <c r="C33" s="32"/>
@@ -3284,23 +3287,23 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="35"/>
+      <c r="G33" s="34"/>
       <c r="H33" s="32"/>
       <c r="I33" s="32"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="35">
-        <v>0</v>
-      </c>
-      <c r="M33" s="35"/>
-      <c r="N33" s="35"/>
+      <c r="L33" s="34">
+        <v>0</v>
+      </c>
+      <c r="M33" s="34"/>
+      <c r="N33" s="34"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="34">
+      <c r="B34" s="33">
         <v>0</v>
       </c>
       <c r="C34" s="32"/>
@@ -3308,13 +3311,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="34"/>
+      <c r="G34" s="33"/>
       <c r="H34" s="32"/>
       <c r="I34" s="32"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="34">
+      <c r="L34" s="33">
         <v>0</v>
       </c>
       <c r="M34" s="32"/>
@@ -3324,7 +3327,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="37">
+      <c r="B35" s="36">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -3333,7 +3336,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="37">
+      <c r="G35" s="36">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -3342,7 +3345,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="37">
+      <c r="L35" s="36">
         <f>SUM(L29:L34)</f>
         <v>0</v>
       </c>
@@ -3379,6 +3382,56 @@
     </row>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B10:D10"/>
@@ -3395,56 +3448,6 @@
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="H28:I28"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3460,7 +3463,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
@@ -3468,7 +3471,7 @@
       <c r="D1" s="32"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
@@ -3482,11 +3485,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="35" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="35" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="32"/>
@@ -3495,7 +3498,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="35"/>
+      <c r="B5" s="34"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
     </row>
@@ -3503,7 +3506,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="34"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
     </row>
@@ -3511,7 +3514,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="35"/>
+      <c r="B7" s="34"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
     </row>
@@ -3519,7 +3522,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="34"/>
+      <c r="B8" s="33"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32"/>
     </row>
@@ -3527,7 +3530,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="37">
+      <c r="B9" s="36">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -3576,19 +3579,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="32"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
-      <c r="K1" s="33" t="s">
+      <c r="K1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="32"/>
@@ -3596,19 +3599,19 @@
       <c r="N1" s="32"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
-      <c r="F2" s="33" t="s">
+      <c r="F2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="32"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="K2" s="33" t="s">
+      <c r="K2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="32"/>
@@ -3630,27 +3633,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="35" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="32"/>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="32"/>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="35" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="32"/>
-      <c r="K4" s="36" t="s">
+      <c r="K4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="32"/>
-      <c r="M4" s="36" t="s">
+      <c r="M4" s="35" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="32"/>
@@ -3659,19 +3662,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="35"/>
+      <c r="B5" s="34"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="35"/>
+      <c r="G5" s="34"/>
       <c r="H5" s="32"/>
       <c r="I5" s="32"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="35"/>
+      <c r="L5" s="34"/>
       <c r="M5" s="32"/>
       <c r="N5" s="32"/>
     </row>
@@ -3679,19 +3682,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="34"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="34"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="34"/>
+      <c r="L6" s="33"/>
       <c r="M6" s="32"/>
       <c r="N6" s="32"/>
     </row>
@@ -3699,19 +3702,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="35"/>
+      <c r="B7" s="34"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="35"/>
+      <c r="G7" s="34"/>
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="35"/>
+      <c r="L7" s="34"/>
       <c r="M7" s="32"/>
       <c r="N7" s="32"/>
     </row>
@@ -3719,19 +3722,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="34"/>
+      <c r="B8" s="33"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="34"/>
+      <c r="G8" s="33"/>
       <c r="H8" s="32"/>
       <c r="I8" s="32"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="34"/>
+      <c r="L8" s="33"/>
       <c r="M8" s="32"/>
       <c r="N8" s="32"/>
     </row>
@@ -3739,19 +3742,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="35"/>
+      <c r="B9" s="34"/>
       <c r="C9" s="32"/>
       <c r="D9" s="32"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="35"/>
+      <c r="G9" s="34"/>
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="35"/>
+      <c r="L9" s="34"/>
       <c r="M9" s="32"/>
       <c r="N9" s="32"/>
     </row>
@@ -3759,19 +3762,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="34"/>
+      <c r="B10" s="33"/>
       <c r="C10" s="32"/>
       <c r="D10" s="32"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="34"/>
+      <c r="G10" s="33"/>
       <c r="H10" s="32"/>
       <c r="I10" s="32"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="34"/>
+      <c r="L10" s="33"/>
       <c r="M10" s="32"/>
       <c r="N10" s="32"/>
     </row>
@@ -3779,19 +3782,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="35"/>
+      <c r="B11" s="34"/>
       <c r="C11" s="32"/>
       <c r="D11" s="32"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="35"/>
+      <c r="G11" s="34"/>
       <c r="H11" s="32"/>
       <c r="I11" s="32"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="35"/>
+      <c r="L11" s="34"/>
       <c r="M11" s="32"/>
       <c r="N11" s="32"/>
     </row>
@@ -3799,19 +3802,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="34"/>
+      <c r="B12" s="33"/>
       <c r="C12" s="32"/>
       <c r="D12" s="32"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="34"/>
+      <c r="G12" s="33"/>
       <c r="H12" s="32"/>
       <c r="I12" s="32"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="34"/>
+      <c r="L12" s="33"/>
       <c r="M12" s="32"/>
       <c r="N12" s="32"/>
     </row>
@@ -3819,7 +3822,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="37">
+      <c r="B13" s="36">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3828,7 +3831,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="37">
+      <c r="G13" s="36">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3837,7 +3840,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="37">
+      <c r="L13" s="36">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3873,19 +3876,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="33" t="s">
+      <c r="A25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
-      <c r="F25" s="33" t="s">
+      <c r="F25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
       <c r="I25" s="32"/>
-      <c r="K25" s="33" t="s">
+      <c r="K25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="32"/>
@@ -3893,19 +3896,19 @@
       <c r="N25" s="32"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="33" t="s">
+      <c r="A26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
-      <c r="F26" s="33" t="s">
+      <c r="F26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="32"/>
       <c r="H26" s="32"/>
       <c r="I26" s="32"/>
-      <c r="K26" s="33" t="s">
+      <c r="K26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="32"/>
@@ -3927,27 +3930,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="32"/>
-      <c r="C28" s="36" t="s">
+      <c r="C28" s="35" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="32"/>
-      <c r="F28" s="36" t="s">
+      <c r="F28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="32"/>
-      <c r="H28" s="36" t="s">
+      <c r="H28" s="35" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="32"/>
-      <c r="K28" s="36" t="s">
+      <c r="K28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="32"/>
-      <c r="M28" s="36" t="s">
+      <c r="M28" s="35" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="32"/>
@@ -3956,19 +3959,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="35"/>
+      <c r="B29" s="34"/>
       <c r="C29" s="32"/>
       <c r="D29" s="32"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="35"/>
+      <c r="G29" s="34"/>
       <c r="H29" s="32"/>
       <c r="I29" s="32"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="35"/>
+      <c r="L29" s="34"/>
       <c r="M29" s="32"/>
       <c r="N29" s="32"/>
     </row>
@@ -3976,19 +3979,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="34"/>
+      <c r="B30" s="33"/>
       <c r="C30" s="32"/>
       <c r="D30" s="32"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="34"/>
+      <c r="G30" s="33"/>
       <c r="H30" s="32"/>
       <c r="I30" s="32"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="34"/>
+      <c r="L30" s="33"/>
       <c r="M30" s="32"/>
       <c r="N30" s="32"/>
     </row>
@@ -3996,19 +3999,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="35"/>
+      <c r="B31" s="34"/>
       <c r="C31" s="32"/>
       <c r="D31" s="32"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="35"/>
+      <c r="G31" s="34"/>
       <c r="H31" s="32"/>
       <c r="I31" s="32"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="35"/>
+      <c r="L31" s="34"/>
       <c r="M31" s="32"/>
       <c r="N31" s="32"/>
     </row>
@@ -4016,19 +4019,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="34"/>
+      <c r="B32" s="33"/>
       <c r="C32" s="32"/>
       <c r="D32" s="32"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="34"/>
+      <c r="G32" s="33"/>
       <c r="H32" s="32"/>
       <c r="I32" s="32"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="34"/>
+      <c r="L32" s="33"/>
       <c r="M32" s="32"/>
       <c r="N32" s="32"/>
     </row>
@@ -4036,19 +4039,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="35"/>
+      <c r="B33" s="34"/>
       <c r="C33" s="32"/>
       <c r="D33" s="32"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="35"/>
+      <c r="G33" s="34"/>
       <c r="H33" s="32"/>
       <c r="I33" s="32"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="35"/>
+      <c r="L33" s="34"/>
       <c r="M33" s="32"/>
       <c r="N33" s="32"/>
     </row>
@@ -4056,19 +4059,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="34"/>
+      <c r="B34" s="33"/>
       <c r="C34" s="32"/>
       <c r="D34" s="32"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="34"/>
+      <c r="G34" s="33"/>
       <c r="H34" s="32"/>
       <c r="I34" s="32"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="34"/>
+      <c r="L34" s="33"/>
       <c r="M34" s="32"/>
       <c r="N34" s="32"/>
     </row>
@@ -4076,19 +4079,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="35"/>
+      <c r="B35" s="34"/>
       <c r="C35" s="32"/>
       <c r="D35" s="32"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="35"/>
+      <c r="G35" s="34"/>
       <c r="H35" s="32"/>
       <c r="I35" s="32"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="35"/>
+      <c r="L35" s="34"/>
       <c r="M35" s="32"/>
       <c r="N35" s="32"/>
     </row>
@@ -4096,19 +4099,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="34"/>
+      <c r="B36" s="33"/>
       <c r="C36" s="32"/>
       <c r="D36" s="32"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="34"/>
+      <c r="G36" s="33"/>
       <c r="H36" s="32"/>
       <c r="I36" s="32"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="34"/>
+      <c r="L36" s="33"/>
       <c r="M36" s="32"/>
       <c r="N36" s="32"/>
     </row>
@@ -4116,7 +4119,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="37">
+      <c r="B37" s="36">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -4125,7 +4128,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="37">
+      <c r="G37" s="36">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -4134,7 +4137,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="37">
+      <c r="L37" s="36">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -4171,6 +4174,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
     <mergeCell ref="G36:I36"/>
     <mergeCell ref="L32:N32"/>
     <mergeCell ref="L13:N13"/>
@@ -4187,68 +4252,6 @@
     <mergeCell ref="L33:N33"/>
     <mergeCell ref="L35:N35"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="L9:N9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BECACB3D-ECF2-45A7-9611-416987491B56}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D1EA637-6613-453B-BF38-EAB6C0F8DCA3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -447,6 +447,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -457,9 +460,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2831,19 +2831,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
-      <c r="F1" s="37" t="s">
+      <c r="F1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="32"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
-      <c r="K1" s="37" t="s">
+      <c r="K1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="32"/>
@@ -2851,19 +2851,19 @@
       <c r="N1" s="32"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
-      <c r="F2" s="37" t="s">
+      <c r="F2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="32"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="K2" s="37" t="s">
+      <c r="K2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="32"/>
@@ -2885,27 +2885,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="36" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="32"/>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="32"/>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="36" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="32"/>
-      <c r="K4" s="35" t="s">
+      <c r="K4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="32"/>
-      <c r="M4" s="35" t="s">
+      <c r="M4" s="36" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="32"/>
@@ -2914,21 +2914,21 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="34">
-        <v>0</v>
-      </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
+      <c r="B5" s="35">
+        <v>0</v>
+      </c>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="34"/>
+      <c r="G5" s="35"/>
       <c r="H5" s="32"/>
       <c r="I5" s="32"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="34"/>
+      <c r="L5" s="35"/>
       <c r="M5" s="32"/>
       <c r="N5" s="32"/>
     </row>
@@ -2936,21 +2936,21 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="33">
-        <v>0</v>
-      </c>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
+      <c r="B6" s="34">
+        <v>0</v>
+      </c>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="33"/>
+      <c r="G6" s="34"/>
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="33"/>
+      <c r="L6" s="34"/>
       <c r="M6" s="32"/>
       <c r="N6" s="32"/>
     </row>
@@ -2958,21 +2958,21 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="34">
-        <v>0</v>
-      </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
+      <c r="B7" s="35">
+        <v>0</v>
+      </c>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="34"/>
+      <c r="G7" s="35"/>
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="34"/>
+      <c r="L7" s="35"/>
       <c r="M7" s="32"/>
       <c r="N7" s="32"/>
     </row>
@@ -2980,21 +2980,21 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="33">
-        <v>0</v>
-      </c>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
+      <c r="B8" s="34">
+        <v>0</v>
+      </c>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="33"/>
+      <c r="G8" s="34"/>
       <c r="H8" s="32"/>
       <c r="I8" s="32"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="33"/>
+      <c r="L8" s="34"/>
       <c r="M8" s="32"/>
       <c r="N8" s="32"/>
     </row>
@@ -3002,21 +3002,21 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="34">
-        <v>0</v>
-      </c>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
+      <c r="B9" s="35">
+        <v>0</v>
+      </c>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="34"/>
+      <c r="G9" s="35"/>
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="34"/>
+      <c r="L9" s="35"/>
       <c r="M9" s="32"/>
       <c r="N9" s="32"/>
     </row>
@@ -3024,21 +3024,21 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="33">
-        <v>0</v>
-      </c>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
+      <c r="B10" s="34">
+        <v>0</v>
+      </c>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="33"/>
+      <c r="G10" s="34"/>
       <c r="H10" s="32"/>
       <c r="I10" s="32"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="33"/>
+      <c r="L10" s="34"/>
       <c r="M10" s="32"/>
       <c r="N10" s="32"/>
     </row>
@@ -3046,7 +3046,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="36">
+      <c r="B11" s="37">
         <f>SUM(B5:B10)</f>
         <v>0</v>
       </c>
@@ -3055,7 +3055,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="36">
+      <c r="G11" s="37">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -3064,7 +3064,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="36">
+      <c r="L11" s="37">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -3100,19 +3100,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="37" t="s">
+      <c r="A25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
-      <c r="F25" s="37" t="s">
+      <c r="F25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
       <c r="I25" s="32"/>
-      <c r="K25" s="37" t="s">
+      <c r="K25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="32"/>
@@ -3120,19 +3120,19 @@
       <c r="N25" s="32"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="37" t="s">
+      <c r="A26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
-      <c r="F26" s="37" t="s">
+      <c r="F26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="32"/>
       <c r="H26" s="32"/>
       <c r="I26" s="32"/>
-      <c r="K26" s="37" t="s">
+      <c r="K26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="32"/>
@@ -3154,27 +3154,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="35" t="s">
+      <c r="A28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="32"/>
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="36" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="32"/>
-      <c r="F28" s="35" t="s">
+      <c r="F28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="32"/>
-      <c r="H28" s="35" t="s">
+      <c r="H28" s="36" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="32"/>
-      <c r="K28" s="35" t="s">
+      <c r="K28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="32"/>
-      <c r="M28" s="35" t="s">
+      <c r="M28" s="36" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="32"/>
@@ -3183,7 +3183,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="34">
+      <c r="B29" s="35">
         <v>0</v>
       </c>
       <c r="C29" s="32"/>
@@ -3191,23 +3191,23 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="34"/>
+      <c r="G29" s="35"/>
       <c r="H29" s="32"/>
       <c r="I29" s="32"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="34">
-        <v>0</v>
-      </c>
-      <c r="M29" s="34"/>
-      <c r="N29" s="34"/>
+      <c r="L29" s="35">
+        <v>0</v>
+      </c>
+      <c r="M29" s="35"/>
+      <c r="N29" s="35"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="33">
+      <c r="B30" s="34">
         <v>0</v>
       </c>
       <c r="C30" s="32"/>
@@ -3215,23 +3215,23 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="33"/>
+      <c r="G30" s="34"/>
       <c r="H30" s="32"/>
       <c r="I30" s="32"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="33">
-        <v>0</v>
-      </c>
-      <c r="M30" s="33"/>
-      <c r="N30" s="33"/>
+      <c r="L30" s="34">
+        <v>0</v>
+      </c>
+      <c r="M30" s="34"/>
+      <c r="N30" s="34"/>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1">
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="34">
+      <c r="B31" s="35">
         <v>0</v>
       </c>
       <c r="C31" s="32"/>
@@ -3239,23 +3239,23 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="34"/>
+      <c r="G31" s="35"/>
       <c r="H31" s="32"/>
       <c r="I31" s="32"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="34">
-        <v>0</v>
-      </c>
-      <c r="M31" s="34"/>
-      <c r="N31" s="34"/>
+      <c r="L31" s="35">
+        <v>0</v>
+      </c>
+      <c r="M31" s="35"/>
+      <c r="N31" s="35"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="33">
+      <c r="B32" s="34">
         <v>0</v>
       </c>
       <c r="C32" s="32"/>
@@ -3263,23 +3263,23 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="33"/>
+      <c r="G32" s="34"/>
       <c r="H32" s="32"/>
       <c r="I32" s="32"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="33">
-        <v>0</v>
-      </c>
-      <c r="M32" s="33"/>
-      <c r="N32" s="33"/>
+      <c r="L32" s="34">
+        <v>0</v>
+      </c>
+      <c r="M32" s="34"/>
+      <c r="N32" s="34"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="34">
+      <c r="B33" s="35">
         <v>0</v>
       </c>
       <c r="C33" s="32"/>
@@ -3287,23 +3287,23 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="34"/>
+      <c r="G33" s="35"/>
       <c r="H33" s="32"/>
       <c r="I33" s="32"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="34">
-        <v>0</v>
-      </c>
-      <c r="M33" s="34"/>
-      <c r="N33" s="34"/>
+      <c r="L33" s="35">
+        <v>0</v>
+      </c>
+      <c r="M33" s="35"/>
+      <c r="N33" s="35"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="33">
+      <c r="B34" s="34">
         <v>0</v>
       </c>
       <c r="C34" s="32"/>
@@ -3311,13 +3311,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="33"/>
+      <c r="G34" s="34"/>
       <c r="H34" s="32"/>
       <c r="I34" s="32"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="33">
+      <c r="L34" s="34">
         <v>0</v>
       </c>
       <c r="M34" s="32"/>
@@ -3327,7 +3327,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="36">
+      <c r="B35" s="37">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -3336,7 +3336,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="36">
+      <c r="G35" s="37">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -3345,7 +3345,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="36">
+      <c r="L35" s="37">
         <f>SUM(L29:L34)</f>
         <v>0</v>
       </c>
@@ -3382,13 +3382,49 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="L11:N11"/>
@@ -3405,49 +3441,13 @@
     <mergeCell ref="K2:N2"/>
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3463,7 +3463,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
@@ -3471,7 +3471,7 @@
       <c r="D1" s="32"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
@@ -3485,11 +3485,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="36" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="36" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="32"/>
@@ -3498,7 +3498,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="34"/>
+      <c r="B5" s="35"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
     </row>
@@ -3506,7 +3506,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="33"/>
+      <c r="B6" s="34"/>
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
     </row>
@@ -3514,7 +3514,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="34"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
     </row>
@@ -3522,7 +3522,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="33"/>
+      <c r="B8" s="34"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32"/>
     </row>
@@ -3530,7 +3530,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="36">
+      <c r="B9" s="37">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -3579,19 +3579,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
-      <c r="F1" s="37" t="s">
+      <c r="F1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="32"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
-      <c r="K1" s="37" t="s">
+      <c r="K1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="32"/>
@@ -3599,19 +3599,19 @@
       <c r="N1" s="32"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
-      <c r="F2" s="37" t="s">
+      <c r="F2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="32"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="K2" s="37" t="s">
+      <c r="K2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="32"/>
@@ -3633,27 +3633,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="36" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="32"/>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="32"/>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="36" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="32"/>
-      <c r="K4" s="35" t="s">
+      <c r="K4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="32"/>
-      <c r="M4" s="35" t="s">
+      <c r="M4" s="36" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="32"/>
@@ -3662,19 +3662,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="34"/>
+      <c r="B5" s="35"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="34"/>
+      <c r="G5" s="35"/>
       <c r="H5" s="32"/>
       <c r="I5" s="32"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="34"/>
+      <c r="L5" s="35"/>
       <c r="M5" s="32"/>
       <c r="N5" s="32"/>
     </row>
@@ -3682,19 +3682,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="33"/>
+      <c r="B6" s="34"/>
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="33"/>
+      <c r="G6" s="34"/>
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="33"/>
+      <c r="L6" s="34"/>
       <c r="M6" s="32"/>
       <c r="N6" s="32"/>
     </row>
@@ -3702,19 +3702,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="34"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="34"/>
+      <c r="G7" s="35"/>
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="34"/>
+      <c r="L7" s="35"/>
       <c r="M7" s="32"/>
       <c r="N7" s="32"/>
     </row>
@@ -3722,19 +3722,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="33"/>
+      <c r="B8" s="34"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="33"/>
+      <c r="G8" s="34"/>
       <c r="H8" s="32"/>
       <c r="I8" s="32"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="33"/>
+      <c r="L8" s="34"/>
       <c r="M8" s="32"/>
       <c r="N8" s="32"/>
     </row>
@@ -3742,19 +3742,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="34"/>
+      <c r="B9" s="35"/>
       <c r="C9" s="32"/>
       <c r="D9" s="32"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="34"/>
+      <c r="G9" s="35"/>
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="34"/>
+      <c r="L9" s="35"/>
       <c r="M9" s="32"/>
       <c r="N9" s="32"/>
     </row>
@@ -3762,19 +3762,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="33"/>
+      <c r="B10" s="34"/>
       <c r="C10" s="32"/>
       <c r="D10" s="32"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="33"/>
+      <c r="G10" s="34"/>
       <c r="H10" s="32"/>
       <c r="I10" s="32"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="33"/>
+      <c r="L10" s="34"/>
       <c r="M10" s="32"/>
       <c r="N10" s="32"/>
     </row>
@@ -3782,19 +3782,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="34"/>
+      <c r="B11" s="35"/>
       <c r="C11" s="32"/>
       <c r="D11" s="32"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="34"/>
+      <c r="G11" s="35"/>
       <c r="H11" s="32"/>
       <c r="I11" s="32"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="34"/>
+      <c r="L11" s="35"/>
       <c r="M11" s="32"/>
       <c r="N11" s="32"/>
     </row>
@@ -3802,19 +3802,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="33"/>
+      <c r="B12" s="34"/>
       <c r="C12" s="32"/>
       <c r="D12" s="32"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="33"/>
+      <c r="G12" s="34"/>
       <c r="H12" s="32"/>
       <c r="I12" s="32"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="33"/>
+      <c r="L12" s="34"/>
       <c r="M12" s="32"/>
       <c r="N12" s="32"/>
     </row>
@@ -3822,7 +3822,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="36">
+      <c r="B13" s="37">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3831,7 +3831,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="36">
+      <c r="G13" s="37">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3840,7 +3840,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="36">
+      <c r="L13" s="37">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3876,19 +3876,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="37" t="s">
+      <c r="A25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
-      <c r="F25" s="37" t="s">
+      <c r="F25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
       <c r="I25" s="32"/>
-      <c r="K25" s="37" t="s">
+      <c r="K25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="32"/>
@@ -3896,19 +3896,19 @@
       <c r="N25" s="32"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="37" t="s">
+      <c r="A26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
-      <c r="F26" s="37" t="s">
+      <c r="F26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="32"/>
       <c r="H26" s="32"/>
       <c r="I26" s="32"/>
-      <c r="K26" s="37" t="s">
+      <c r="K26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="32"/>
@@ -3930,27 +3930,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="35" t="s">
+      <c r="A28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="32"/>
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="36" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="32"/>
-      <c r="F28" s="35" t="s">
+      <c r="F28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="32"/>
-      <c r="H28" s="35" t="s">
+      <c r="H28" s="36" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="32"/>
-      <c r="K28" s="35" t="s">
+      <c r="K28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="32"/>
-      <c r="M28" s="35" t="s">
+      <c r="M28" s="36" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="32"/>
@@ -3959,19 +3959,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="34"/>
+      <c r="B29" s="35"/>
       <c r="C29" s="32"/>
       <c r="D29" s="32"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="34"/>
+      <c r="G29" s="35"/>
       <c r="H29" s="32"/>
       <c r="I29" s="32"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="34"/>
+      <c r="L29" s="35"/>
       <c r="M29" s="32"/>
       <c r="N29" s="32"/>
     </row>
@@ -3979,19 +3979,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="33"/>
+      <c r="B30" s="34"/>
       <c r="C30" s="32"/>
       <c r="D30" s="32"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="33"/>
+      <c r="G30" s="34"/>
       <c r="H30" s="32"/>
       <c r="I30" s="32"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="33"/>
+      <c r="L30" s="34"/>
       <c r="M30" s="32"/>
       <c r="N30" s="32"/>
     </row>
@@ -3999,19 +3999,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="34"/>
+      <c r="B31" s="35"/>
       <c r="C31" s="32"/>
       <c r="D31" s="32"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="34"/>
+      <c r="G31" s="35"/>
       <c r="H31" s="32"/>
       <c r="I31" s="32"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="34"/>
+      <c r="L31" s="35"/>
       <c r="M31" s="32"/>
       <c r="N31" s="32"/>
     </row>
@@ -4019,19 +4019,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="33"/>
+      <c r="B32" s="34"/>
       <c r="C32" s="32"/>
       <c r="D32" s="32"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="33"/>
+      <c r="G32" s="34"/>
       <c r="H32" s="32"/>
       <c r="I32" s="32"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="33"/>
+      <c r="L32" s="34"/>
       <c r="M32" s="32"/>
       <c r="N32" s="32"/>
     </row>
@@ -4039,19 +4039,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="34"/>
+      <c r="B33" s="35"/>
       <c r="C33" s="32"/>
       <c r="D33" s="32"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="34"/>
+      <c r="G33" s="35"/>
       <c r="H33" s="32"/>
       <c r="I33" s="32"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="34"/>
+      <c r="L33" s="35"/>
       <c r="M33" s="32"/>
       <c r="N33" s="32"/>
     </row>
@@ -4059,19 +4059,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="33"/>
+      <c r="B34" s="34"/>
       <c r="C34" s="32"/>
       <c r="D34" s="32"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="33"/>
+      <c r="G34" s="34"/>
       <c r="H34" s="32"/>
       <c r="I34" s="32"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="33"/>
+      <c r="L34" s="34"/>
       <c r="M34" s="32"/>
       <c r="N34" s="32"/>
     </row>
@@ -4079,19 +4079,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="34"/>
+      <c r="B35" s="35"/>
       <c r="C35" s="32"/>
       <c r="D35" s="32"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="34"/>
+      <c r="G35" s="35"/>
       <c r="H35" s="32"/>
       <c r="I35" s="32"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="34"/>
+      <c r="L35" s="35"/>
       <c r="M35" s="32"/>
       <c r="N35" s="32"/>
     </row>
@@ -4099,19 +4099,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="33"/>
+      <c r="B36" s="34"/>
       <c r="C36" s="32"/>
       <c r="D36" s="32"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="33"/>
+      <c r="G36" s="34"/>
       <c r="H36" s="32"/>
       <c r="I36" s="32"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="33"/>
+      <c r="L36" s="34"/>
       <c r="M36" s="32"/>
       <c r="N36" s="32"/>
     </row>
@@ -4119,7 +4119,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="36">
+      <c r="B37" s="37">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -4128,7 +4128,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="36">
+      <c r="G37" s="37">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -4137,7 +4137,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="36">
+      <c r="L37" s="37">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -4174,6 +4174,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
     <mergeCell ref="L34:N34"/>
     <mergeCell ref="L6:N6"/>
     <mergeCell ref="B33:D33"/>
@@ -4190,68 +4252,6 @@
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4299,7 +4299,7 @@
         <v>49</v>
       </c>
       <c r="E2" s="18">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="F2" s="18"/>
     </row>
@@ -4317,7 +4317,7 @@
         <v>68</v>
       </c>
       <c r="E3" s="18">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="F3" s="18"/>
     </row>
@@ -4335,7 +4335,7 @@
         <v>49</v>
       </c>
       <c r="E4" s="18">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="F4" s="18"/>
     </row>
@@ -4353,7 +4353,7 @@
         <v>68</v>
       </c>
       <c r="E5" s="18">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="F5" s="18"/>
     </row>
@@ -4371,7 +4371,7 @@
         <v>49</v>
       </c>
       <c r="E6" s="18">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="F6" s="18"/>
     </row>
@@ -4389,7 +4389,7 @@
         <v>68</v>
       </c>
       <c r="E7" s="18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F7" s="18"/>
     </row>
@@ -4407,7 +4407,7 @@
         <v>49</v>
       </c>
       <c r="E8" s="18">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="F8" s="18"/>
     </row>
@@ -4425,7 +4425,7 @@
         <v>68</v>
       </c>
       <c r="E9" s="18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="F9" s="18"/>
     </row>
@@ -4723,7 +4723,7 @@
         <v>49</v>
       </c>
       <c r="E26" s="18">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="F26" s="18"/>
     </row>
@@ -4939,7 +4939,7 @@
         <v>49</v>
       </c>
       <c r="E38" s="18">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F38" s="18"/>
     </row>

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D1EA637-6613-453B-BF38-EAB6C0F8DCA3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79504FDE-B0E0-4743-9C52-25D1E8437B03}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -447,9 +447,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -460,6 +457,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="L53" s="14">
         <f>SUM(L54:L55)</f>
-        <v>700</v>
+        <v>290</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="15" customHeight="1">
@@ -1563,7 +1563,7 @@
         <v>21</v>
       </c>
       <c r="L54" s="14">
-        <v>700</v>
+        <v>290</v>
       </c>
     </row>
     <row r="55" spans="1:14" ht="15" customHeight="1">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="L89" s="13">
         <f>SUM(L53,L56,L59,L62,L65,L68,L71,L74,L77,L80,L83,L86)</f>
-        <v>700</v>
+        <v>290</v>
       </c>
     </row>
     <row r="90" spans="1:14" ht="15" customHeight="1">
@@ -2831,19 +2831,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="32"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
-      <c r="K1" s="33" t="s">
+      <c r="K1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="32"/>
@@ -2851,19 +2851,19 @@
       <c r="N1" s="32"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
-      <c r="F2" s="33" t="s">
+      <c r="F2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="32"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="K2" s="33" t="s">
+      <c r="K2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="32"/>
@@ -2885,27 +2885,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="35" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="32"/>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="32"/>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="35" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="32"/>
-      <c r="K4" s="36" t="s">
+      <c r="K4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="32"/>
-      <c r="M4" s="36" t="s">
+      <c r="M4" s="35" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="32"/>
@@ -2914,21 +2914,21 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="35">
-        <v>0</v>
-      </c>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
+      <c r="B5" s="34">
+        <v>0</v>
+      </c>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="35"/>
+      <c r="G5" s="34"/>
       <c r="H5" s="32"/>
       <c r="I5" s="32"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="35"/>
+      <c r="L5" s="34"/>
       <c r="M5" s="32"/>
       <c r="N5" s="32"/>
     </row>
@@ -2936,21 +2936,21 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="34">
-        <v>0</v>
-      </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
+      <c r="B6" s="33">
+        <v>0</v>
+      </c>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="34"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="34"/>
+      <c r="L6" s="33"/>
       <c r="M6" s="32"/>
       <c r="N6" s="32"/>
     </row>
@@ -2958,21 +2958,21 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="35">
-        <v>0</v>
-      </c>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
+      <c r="B7" s="34">
+        <v>0</v>
+      </c>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="35"/>
+      <c r="G7" s="34"/>
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="35"/>
+      <c r="L7" s="34"/>
       <c r="M7" s="32"/>
       <c r="N7" s="32"/>
     </row>
@@ -2980,21 +2980,21 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="34">
-        <v>0</v>
-      </c>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
+      <c r="B8" s="33">
+        <v>0</v>
+      </c>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="34"/>
+      <c r="G8" s="33"/>
       <c r="H8" s="32"/>
       <c r="I8" s="32"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="34"/>
+      <c r="L8" s="33"/>
       <c r="M8" s="32"/>
       <c r="N8" s="32"/>
     </row>
@@ -3002,21 +3002,21 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="35">
-        <v>0</v>
-      </c>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
+      <c r="B9" s="34">
+        <v>0</v>
+      </c>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="35"/>
+      <c r="G9" s="34"/>
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="35"/>
+      <c r="L9" s="34"/>
       <c r="M9" s="32"/>
       <c r="N9" s="32"/>
     </row>
@@ -3024,21 +3024,21 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="34">
-        <v>0</v>
-      </c>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
+      <c r="B10" s="33">
+        <v>0</v>
+      </c>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="34"/>
+      <c r="G10" s="33"/>
       <c r="H10" s="32"/>
       <c r="I10" s="32"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="34"/>
+      <c r="L10" s="33"/>
       <c r="M10" s="32"/>
       <c r="N10" s="32"/>
     </row>
@@ -3046,7 +3046,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="37">
+      <c r="B11" s="36">
         <f>SUM(B5:B10)</f>
         <v>0</v>
       </c>
@@ -3055,7 +3055,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="37">
+      <c r="G11" s="36">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -3064,7 +3064,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="37">
+      <c r="L11" s="36">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -3100,19 +3100,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="33" t="s">
+      <c r="A25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
-      <c r="F25" s="33" t="s">
+      <c r="F25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
       <c r="I25" s="32"/>
-      <c r="K25" s="33" t="s">
+      <c r="K25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="32"/>
@@ -3120,19 +3120,19 @@
       <c r="N25" s="32"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="33" t="s">
+      <c r="A26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
-      <c r="F26" s="33" t="s">
+      <c r="F26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="32"/>
       <c r="H26" s="32"/>
       <c r="I26" s="32"/>
-      <c r="K26" s="33" t="s">
+      <c r="K26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="32"/>
@@ -3154,27 +3154,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="32"/>
-      <c r="C28" s="36" t="s">
+      <c r="C28" s="35" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="32"/>
-      <c r="F28" s="36" t="s">
+      <c r="F28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="32"/>
-      <c r="H28" s="36" t="s">
+      <c r="H28" s="35" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="32"/>
-      <c r="K28" s="36" t="s">
+      <c r="K28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="32"/>
-      <c r="M28" s="36" t="s">
+      <c r="M28" s="35" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="32"/>
@@ -3183,7 +3183,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="35">
+      <c r="B29" s="34">
         <v>0</v>
       </c>
       <c r="C29" s="32"/>
@@ -3191,23 +3191,23 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="35"/>
+      <c r="G29" s="34"/>
       <c r="H29" s="32"/>
       <c r="I29" s="32"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="35">
-        <v>0</v>
-      </c>
-      <c r="M29" s="35"/>
-      <c r="N29" s="35"/>
+      <c r="L29" s="34">
+        <v>0</v>
+      </c>
+      <c r="M29" s="34"/>
+      <c r="N29" s="34"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="34">
+      <c r="B30" s="33">
         <v>0</v>
       </c>
       <c r="C30" s="32"/>
@@ -3215,23 +3215,23 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="34"/>
+      <c r="G30" s="33"/>
       <c r="H30" s="32"/>
       <c r="I30" s="32"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="34">
-        <v>0</v>
-      </c>
-      <c r="M30" s="34"/>
-      <c r="N30" s="34"/>
+      <c r="L30" s="33">
+        <v>0</v>
+      </c>
+      <c r="M30" s="33"/>
+      <c r="N30" s="33"/>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1">
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="35">
+      <c r="B31" s="34">
         <v>0</v>
       </c>
       <c r="C31" s="32"/>
@@ -3239,23 +3239,23 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="35"/>
+      <c r="G31" s="34"/>
       <c r="H31" s="32"/>
       <c r="I31" s="32"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="35">
-        <v>0</v>
-      </c>
-      <c r="M31" s="35"/>
-      <c r="N31" s="35"/>
+      <c r="L31" s="34">
+        <v>0</v>
+      </c>
+      <c r="M31" s="34"/>
+      <c r="N31" s="34"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="34">
+      <c r="B32" s="33">
         <v>0</v>
       </c>
       <c r="C32" s="32"/>
@@ -3263,23 +3263,23 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="34"/>
+      <c r="G32" s="33"/>
       <c r="H32" s="32"/>
       <c r="I32" s="32"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="34">
-        <v>0</v>
-      </c>
-      <c r="M32" s="34"/>
-      <c r="N32" s="34"/>
+      <c r="L32" s="33">
+        <v>0</v>
+      </c>
+      <c r="M32" s="33"/>
+      <c r="N32" s="33"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="35">
+      <c r="B33" s="34">
         <v>0</v>
       </c>
       <c r="C33" s="32"/>
@@ -3287,23 +3287,23 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="35"/>
+      <c r="G33" s="34"/>
       <c r="H33" s="32"/>
       <c r="I33" s="32"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="35">
-        <v>0</v>
-      </c>
-      <c r="M33" s="35"/>
-      <c r="N33" s="35"/>
+      <c r="L33" s="34">
+        <v>0</v>
+      </c>
+      <c r="M33" s="34"/>
+      <c r="N33" s="34"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="34">
+      <c r="B34" s="33">
         <v>0</v>
       </c>
       <c r="C34" s="32"/>
@@ -3311,13 +3311,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="34"/>
+      <c r="G34" s="33"/>
       <c r="H34" s="32"/>
       <c r="I34" s="32"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="34">
+      <c r="L34" s="33">
         <v>0</v>
       </c>
       <c r="M34" s="32"/>
@@ -3327,7 +3327,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="37">
+      <c r="B35" s="36">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -3336,7 +3336,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="37">
+      <c r="G35" s="36">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -3345,7 +3345,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="37">
+      <c r="L35" s="36">
         <f>SUM(L29:L34)</f>
         <v>0</v>
       </c>
@@ -3382,6 +3382,56 @@
     </row>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B10:D10"/>
@@ -3398,56 +3448,6 @@
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="H28:I28"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3463,7 +3463,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
@@ -3471,7 +3471,7 @@
       <c r="D1" s="32"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
@@ -3485,11 +3485,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="35" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="35" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="32"/>
@@ -3498,7 +3498,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="35"/>
+      <c r="B5" s="34"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
     </row>
@@ -3506,7 +3506,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="34"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
     </row>
@@ -3514,7 +3514,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="35"/>
+      <c r="B7" s="34"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
     </row>
@@ -3522,7 +3522,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="34"/>
+      <c r="B8" s="33"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32"/>
     </row>
@@ -3530,7 +3530,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="37">
+      <c r="B9" s="36">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -3579,19 +3579,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="32"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
-      <c r="K1" s="33" t="s">
+      <c r="K1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="32"/>
@@ -3599,19 +3599,19 @@
       <c r="N1" s="32"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
-      <c r="F2" s="33" t="s">
+      <c r="F2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="32"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="K2" s="33" t="s">
+      <c r="K2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="32"/>
@@ -3633,27 +3633,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="35" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="32"/>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="32"/>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="35" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="32"/>
-      <c r="K4" s="36" t="s">
+      <c r="K4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="32"/>
-      <c r="M4" s="36" t="s">
+      <c r="M4" s="35" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="32"/>
@@ -3662,19 +3662,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="35"/>
+      <c r="B5" s="34"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="35"/>
+      <c r="G5" s="34"/>
       <c r="H5" s="32"/>
       <c r="I5" s="32"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="35"/>
+      <c r="L5" s="34"/>
       <c r="M5" s="32"/>
       <c r="N5" s="32"/>
     </row>
@@ -3682,19 +3682,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="34"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="34"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="34"/>
+      <c r="L6" s="33"/>
       <c r="M6" s="32"/>
       <c r="N6" s="32"/>
     </row>
@@ -3702,19 +3702,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="35"/>
+      <c r="B7" s="34"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="35"/>
+      <c r="G7" s="34"/>
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="35"/>
+      <c r="L7" s="34"/>
       <c r="M7" s="32"/>
       <c r="N7" s="32"/>
     </row>
@@ -3722,19 +3722,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="34"/>
+      <c r="B8" s="33"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="34"/>
+      <c r="G8" s="33"/>
       <c r="H8" s="32"/>
       <c r="I8" s="32"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="34"/>
+      <c r="L8" s="33"/>
       <c r="M8" s="32"/>
       <c r="N8" s="32"/>
     </row>
@@ -3742,19 +3742,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="35"/>
+      <c r="B9" s="34"/>
       <c r="C9" s="32"/>
       <c r="D9" s="32"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="35"/>
+      <c r="G9" s="34"/>
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="35"/>
+      <c r="L9" s="34"/>
       <c r="M9" s="32"/>
       <c r="N9" s="32"/>
     </row>
@@ -3762,19 +3762,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="34"/>
+      <c r="B10" s="33"/>
       <c r="C10" s="32"/>
       <c r="D10" s="32"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="34"/>
+      <c r="G10" s="33"/>
       <c r="H10" s="32"/>
       <c r="I10" s="32"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="34"/>
+      <c r="L10" s="33"/>
       <c r="M10" s="32"/>
       <c r="N10" s="32"/>
     </row>
@@ -3782,19 +3782,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="35"/>
+      <c r="B11" s="34"/>
       <c r="C11" s="32"/>
       <c r="D11" s="32"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="35"/>
+      <c r="G11" s="34"/>
       <c r="H11" s="32"/>
       <c r="I11" s="32"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="35"/>
+      <c r="L11" s="34"/>
       <c r="M11" s="32"/>
       <c r="N11" s="32"/>
     </row>
@@ -3802,19 +3802,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="34"/>
+      <c r="B12" s="33"/>
       <c r="C12" s="32"/>
       <c r="D12" s="32"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="34"/>
+      <c r="G12" s="33"/>
       <c r="H12" s="32"/>
       <c r="I12" s="32"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="34"/>
+      <c r="L12" s="33"/>
       <c r="M12" s="32"/>
       <c r="N12" s="32"/>
     </row>
@@ -3822,7 +3822,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="37">
+      <c r="B13" s="36">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3831,7 +3831,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="37">
+      <c r="G13" s="36">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3840,7 +3840,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="37">
+      <c r="L13" s="36">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3876,19 +3876,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="33" t="s">
+      <c r="A25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
-      <c r="F25" s="33" t="s">
+      <c r="F25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
       <c r="I25" s="32"/>
-      <c r="K25" s="33" t="s">
+      <c r="K25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="32"/>
@@ -3896,19 +3896,19 @@
       <c r="N25" s="32"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="33" t="s">
+      <c r="A26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
-      <c r="F26" s="33" t="s">
+      <c r="F26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="32"/>
       <c r="H26" s="32"/>
       <c r="I26" s="32"/>
-      <c r="K26" s="33" t="s">
+      <c r="K26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="32"/>
@@ -3930,27 +3930,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="32"/>
-      <c r="C28" s="36" t="s">
+      <c r="C28" s="35" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="32"/>
-      <c r="F28" s="36" t="s">
+      <c r="F28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="32"/>
-      <c r="H28" s="36" t="s">
+      <c r="H28" s="35" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="32"/>
-      <c r="K28" s="36" t="s">
+      <c r="K28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="32"/>
-      <c r="M28" s="36" t="s">
+      <c r="M28" s="35" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="32"/>
@@ -3959,19 +3959,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="35"/>
+      <c r="B29" s="34"/>
       <c r="C29" s="32"/>
       <c r="D29" s="32"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="35"/>
+      <c r="G29" s="34"/>
       <c r="H29" s="32"/>
       <c r="I29" s="32"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="35"/>
+      <c r="L29" s="34"/>
       <c r="M29" s="32"/>
       <c r="N29" s="32"/>
     </row>
@@ -3979,19 +3979,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="34"/>
+      <c r="B30" s="33"/>
       <c r="C30" s="32"/>
       <c r="D30" s="32"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="34"/>
+      <c r="G30" s="33"/>
       <c r="H30" s="32"/>
       <c r="I30" s="32"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="34"/>
+      <c r="L30" s="33"/>
       <c r="M30" s="32"/>
       <c r="N30" s="32"/>
     </row>
@@ -3999,19 +3999,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="35"/>
+      <c r="B31" s="34"/>
       <c r="C31" s="32"/>
       <c r="D31" s="32"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="35"/>
+      <c r="G31" s="34"/>
       <c r="H31" s="32"/>
       <c r="I31" s="32"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="35"/>
+      <c r="L31" s="34"/>
       <c r="M31" s="32"/>
       <c r="N31" s="32"/>
     </row>
@@ -4019,19 +4019,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="34"/>
+      <c r="B32" s="33"/>
       <c r="C32" s="32"/>
       <c r="D32" s="32"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="34"/>
+      <c r="G32" s="33"/>
       <c r="H32" s="32"/>
       <c r="I32" s="32"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="34"/>
+      <c r="L32" s="33"/>
       <c r="M32" s="32"/>
       <c r="N32" s="32"/>
     </row>
@@ -4039,19 +4039,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="35"/>
+      <c r="B33" s="34"/>
       <c r="C33" s="32"/>
       <c r="D33" s="32"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="35"/>
+      <c r="G33" s="34"/>
       <c r="H33" s="32"/>
       <c r="I33" s="32"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="35"/>
+      <c r="L33" s="34"/>
       <c r="M33" s="32"/>
       <c r="N33" s="32"/>
     </row>
@@ -4059,19 +4059,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="34"/>
+      <c r="B34" s="33"/>
       <c r="C34" s="32"/>
       <c r="D34" s="32"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="34"/>
+      <c r="G34" s="33"/>
       <c r="H34" s="32"/>
       <c r="I34" s="32"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="34"/>
+      <c r="L34" s="33"/>
       <c r="M34" s="32"/>
       <c r="N34" s="32"/>
     </row>
@@ -4079,19 +4079,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="35"/>
+      <c r="B35" s="34"/>
       <c r="C35" s="32"/>
       <c r="D35" s="32"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="35"/>
+      <c r="G35" s="34"/>
       <c r="H35" s="32"/>
       <c r="I35" s="32"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="35"/>
+      <c r="L35" s="34"/>
       <c r="M35" s="32"/>
       <c r="N35" s="32"/>
     </row>
@@ -4099,19 +4099,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="34"/>
+      <c r="B36" s="33"/>
       <c r="C36" s="32"/>
       <c r="D36" s="32"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="34"/>
+      <c r="G36" s="33"/>
       <c r="H36" s="32"/>
       <c r="I36" s="32"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="34"/>
+      <c r="L36" s="33"/>
       <c r="M36" s="32"/>
       <c r="N36" s="32"/>
     </row>
@@ -4119,7 +4119,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="37">
+      <c r="B37" s="36">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -4128,7 +4128,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="37">
+      <c r="G37" s="36">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -4137,7 +4137,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="37">
+      <c r="L37" s="36">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -4174,6 +4174,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
     <mergeCell ref="G36:I36"/>
     <mergeCell ref="L32:N32"/>
     <mergeCell ref="L13:N13"/>
@@ -4190,68 +4252,6 @@
     <mergeCell ref="L33:N33"/>
     <mergeCell ref="L35:N35"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="L9:N9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79504FDE-B0E0-4743-9C52-25D1E8437B03}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A85BEE9E-CE9C-462B-B5BB-BBCA78D0D8EF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -447,6 +447,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -457,9 +460,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2831,19 +2831,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
-      <c r="F1" s="37" t="s">
+      <c r="F1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="32"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
-      <c r="K1" s="37" t="s">
+      <c r="K1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="32"/>
@@ -2851,19 +2851,19 @@
       <c r="N1" s="32"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
-      <c r="F2" s="37" t="s">
+      <c r="F2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="32"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="K2" s="37" t="s">
+      <c r="K2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="32"/>
@@ -2885,27 +2885,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="36" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="32"/>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="32"/>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="36" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="32"/>
-      <c r="K4" s="35" t="s">
+      <c r="K4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="32"/>
-      <c r="M4" s="35" t="s">
+      <c r="M4" s="36" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="32"/>
@@ -2914,21 +2914,21 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="34">
-        <v>0</v>
-      </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
+      <c r="B5" s="35">
+        <v>0</v>
+      </c>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="34"/>
+      <c r="G5" s="35"/>
       <c r="H5" s="32"/>
       <c r="I5" s="32"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="34"/>
+      <c r="L5" s="35"/>
       <c r="M5" s="32"/>
       <c r="N5" s="32"/>
     </row>
@@ -2936,21 +2936,21 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="33">
-        <v>0</v>
-      </c>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
+      <c r="B6" s="34">
+        <v>0</v>
+      </c>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="33"/>
+      <c r="G6" s="34"/>
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="33"/>
+      <c r="L6" s="34"/>
       <c r="M6" s="32"/>
       <c r="N6" s="32"/>
     </row>
@@ -2958,21 +2958,21 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="34">
-        <v>0</v>
-      </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
+      <c r="B7" s="35">
+        <v>0</v>
+      </c>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="34"/>
+      <c r="G7" s="35"/>
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="34"/>
+      <c r="L7" s="35"/>
       <c r="M7" s="32"/>
       <c r="N7" s="32"/>
     </row>
@@ -2980,21 +2980,21 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="33">
-        <v>0</v>
-      </c>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
+      <c r="B8" s="34">
+        <v>0</v>
+      </c>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="33"/>
+      <c r="G8" s="34"/>
       <c r="H8" s="32"/>
       <c r="I8" s="32"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="33"/>
+      <c r="L8" s="34"/>
       <c r="M8" s="32"/>
       <c r="N8" s="32"/>
     </row>
@@ -3002,21 +3002,21 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="34">
-        <v>0</v>
-      </c>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
+      <c r="B9" s="35">
+        <v>0</v>
+      </c>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="34"/>
+      <c r="G9" s="35"/>
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="34"/>
+      <c r="L9" s="35"/>
       <c r="M9" s="32"/>
       <c r="N9" s="32"/>
     </row>
@@ -3024,21 +3024,21 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="33">
-        <v>0</v>
-      </c>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
+      <c r="B10" s="34">
+        <v>0</v>
+      </c>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="33"/>
+      <c r="G10" s="34"/>
       <c r="H10" s="32"/>
       <c r="I10" s="32"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="33"/>
+      <c r="L10" s="34"/>
       <c r="M10" s="32"/>
       <c r="N10" s="32"/>
     </row>
@@ -3046,7 +3046,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="36">
+      <c r="B11" s="37">
         <f>SUM(B5:B10)</f>
         <v>0</v>
       </c>
@@ -3055,7 +3055,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="36">
+      <c r="G11" s="37">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -3064,7 +3064,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="36">
+      <c r="L11" s="37">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -3100,19 +3100,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="37" t="s">
+      <c r="A25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
-      <c r="F25" s="37" t="s">
+      <c r="F25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
       <c r="I25" s="32"/>
-      <c r="K25" s="37" t="s">
+      <c r="K25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="32"/>
@@ -3120,19 +3120,19 @@
       <c r="N25" s="32"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="37" t="s">
+      <c r="A26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
-      <c r="F26" s="37" t="s">
+      <c r="F26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="32"/>
       <c r="H26" s="32"/>
       <c r="I26" s="32"/>
-      <c r="K26" s="37" t="s">
+      <c r="K26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="32"/>
@@ -3154,27 +3154,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="35" t="s">
+      <c r="A28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="32"/>
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="36" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="32"/>
-      <c r="F28" s="35" t="s">
+      <c r="F28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="32"/>
-      <c r="H28" s="35" t="s">
+      <c r="H28" s="36" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="32"/>
-      <c r="K28" s="35" t="s">
+      <c r="K28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="32"/>
-      <c r="M28" s="35" t="s">
+      <c r="M28" s="36" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="32"/>
@@ -3183,7 +3183,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="34">
+      <c r="B29" s="35">
         <v>0</v>
       </c>
       <c r="C29" s="32"/>
@@ -3191,23 +3191,23 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="34"/>
+      <c r="G29" s="35"/>
       <c r="H29" s="32"/>
       <c r="I29" s="32"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="34">
-        <v>0</v>
-      </c>
-      <c r="M29" s="34"/>
-      <c r="N29" s="34"/>
+      <c r="L29" s="35">
+        <v>0</v>
+      </c>
+      <c r="M29" s="35"/>
+      <c r="N29" s="35"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="33">
+      <c r="B30" s="34">
         <v>0</v>
       </c>
       <c r="C30" s="32"/>
@@ -3215,23 +3215,23 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="33"/>
+      <c r="G30" s="34"/>
       <c r="H30" s="32"/>
       <c r="I30" s="32"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="33">
-        <v>0</v>
-      </c>
-      <c r="M30" s="33"/>
-      <c r="N30" s="33"/>
+      <c r="L30" s="34">
+        <v>0</v>
+      </c>
+      <c r="M30" s="34"/>
+      <c r="N30" s="34"/>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1">
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="34">
+      <c r="B31" s="35">
         <v>0</v>
       </c>
       <c r="C31" s="32"/>
@@ -3239,23 +3239,23 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="34"/>
+      <c r="G31" s="35"/>
       <c r="H31" s="32"/>
       <c r="I31" s="32"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="34">
-        <v>0</v>
-      </c>
-      <c r="M31" s="34"/>
-      <c r="N31" s="34"/>
+      <c r="L31" s="35">
+        <v>0</v>
+      </c>
+      <c r="M31" s="35"/>
+      <c r="N31" s="35"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="33">
+      <c r="B32" s="34">
         <v>0</v>
       </c>
       <c r="C32" s="32"/>
@@ -3263,23 +3263,23 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="33"/>
+      <c r="G32" s="34"/>
       <c r="H32" s="32"/>
       <c r="I32" s="32"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="33">
-        <v>0</v>
-      </c>
-      <c r="M32" s="33"/>
-      <c r="N32" s="33"/>
+      <c r="L32" s="34">
+        <v>0</v>
+      </c>
+      <c r="M32" s="34"/>
+      <c r="N32" s="34"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="34">
+      <c r="B33" s="35">
         <v>0</v>
       </c>
       <c r="C33" s="32"/>
@@ -3287,23 +3287,23 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="34"/>
+      <c r="G33" s="35"/>
       <c r="H33" s="32"/>
       <c r="I33" s="32"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="34">
-        <v>0</v>
-      </c>
-      <c r="M33" s="34"/>
-      <c r="N33" s="34"/>
+      <c r="L33" s="35">
+        <v>0</v>
+      </c>
+      <c r="M33" s="35"/>
+      <c r="N33" s="35"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="33">
+      <c r="B34" s="34">
         <v>0</v>
       </c>
       <c r="C34" s="32"/>
@@ -3311,13 +3311,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="33"/>
+      <c r="G34" s="34"/>
       <c r="H34" s="32"/>
       <c r="I34" s="32"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="33">
+      <c r="L34" s="34">
         <v>0</v>
       </c>
       <c r="M34" s="32"/>
@@ -3327,7 +3327,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="36">
+      <c r="B35" s="37">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -3336,7 +3336,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="36">
+      <c r="G35" s="37">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -3345,7 +3345,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="36">
+      <c r="L35" s="37">
         <f>SUM(L29:L34)</f>
         <v>0</v>
       </c>
@@ -3382,13 +3382,49 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="L11:N11"/>
@@ -3405,49 +3441,13 @@
     <mergeCell ref="K2:N2"/>
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3463,7 +3463,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
@@ -3471,7 +3471,7 @@
       <c r="D1" s="32"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
@@ -3485,11 +3485,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="36" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="36" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="32"/>
@@ -3498,7 +3498,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="34"/>
+      <c r="B5" s="35"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
     </row>
@@ -3506,7 +3506,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="33"/>
+      <c r="B6" s="34"/>
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
     </row>
@@ -3514,7 +3514,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="34"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
     </row>
@@ -3522,7 +3522,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="33"/>
+      <c r="B8" s="34"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32"/>
     </row>
@@ -3530,7 +3530,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="36">
+      <c r="B9" s="37">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -3579,19 +3579,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
-      <c r="F1" s="37" t="s">
+      <c r="F1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="32"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
-      <c r="K1" s="37" t="s">
+      <c r="K1" s="33" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="32"/>
@@ -3599,19 +3599,19 @@
       <c r="N1" s="32"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
-      <c r="F2" s="37" t="s">
+      <c r="F2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="32"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="K2" s="37" t="s">
+      <c r="K2" s="33" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="32"/>
@@ -3633,27 +3633,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="36" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="32"/>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="32"/>
-      <c r="H4" s="35" t="s">
+      <c r="H4" s="36" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="32"/>
-      <c r="K4" s="35" t="s">
+      <c r="K4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="32"/>
-      <c r="M4" s="35" t="s">
+      <c r="M4" s="36" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="32"/>
@@ -3662,19 +3662,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="34"/>
+      <c r="B5" s="35"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="34"/>
+      <c r="G5" s="35"/>
       <c r="H5" s="32"/>
       <c r="I5" s="32"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="34"/>
+      <c r="L5" s="35"/>
       <c r="M5" s="32"/>
       <c r="N5" s="32"/>
     </row>
@@ -3682,19 +3682,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="33"/>
+      <c r="B6" s="34"/>
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="33"/>
+      <c r="G6" s="34"/>
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="33"/>
+      <c r="L6" s="34"/>
       <c r="M6" s="32"/>
       <c r="N6" s="32"/>
     </row>
@@ -3702,19 +3702,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="34"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="34"/>
+      <c r="G7" s="35"/>
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="34"/>
+      <c r="L7" s="35"/>
       <c r="M7" s="32"/>
       <c r="N7" s="32"/>
     </row>
@@ -3722,19 +3722,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="33"/>
+      <c r="B8" s="34"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="33"/>
+      <c r="G8" s="34"/>
       <c r="H8" s="32"/>
       <c r="I8" s="32"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="33"/>
+      <c r="L8" s="34"/>
       <c r="M8" s="32"/>
       <c r="N8" s="32"/>
     </row>
@@ -3742,19 +3742,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="34"/>
+      <c r="B9" s="35"/>
       <c r="C9" s="32"/>
       <c r="D9" s="32"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="34"/>
+      <c r="G9" s="35"/>
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="34"/>
+      <c r="L9" s="35"/>
       <c r="M9" s="32"/>
       <c r="N9" s="32"/>
     </row>
@@ -3762,19 +3762,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="33"/>
+      <c r="B10" s="34"/>
       <c r="C10" s="32"/>
       <c r="D10" s="32"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="33"/>
+      <c r="G10" s="34"/>
       <c r="H10" s="32"/>
       <c r="I10" s="32"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="33"/>
+      <c r="L10" s="34"/>
       <c r="M10" s="32"/>
       <c r="N10" s="32"/>
     </row>
@@ -3782,19 +3782,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="34"/>
+      <c r="B11" s="35"/>
       <c r="C11" s="32"/>
       <c r="D11" s="32"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="34"/>
+      <c r="G11" s="35"/>
       <c r="H11" s="32"/>
       <c r="I11" s="32"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="34"/>
+      <c r="L11" s="35"/>
       <c r="M11" s="32"/>
       <c r="N11" s="32"/>
     </row>
@@ -3802,19 +3802,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="33"/>
+      <c r="B12" s="34"/>
       <c r="C12" s="32"/>
       <c r="D12" s="32"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="33"/>
+      <c r="G12" s="34"/>
       <c r="H12" s="32"/>
       <c r="I12" s="32"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="33"/>
+      <c r="L12" s="34"/>
       <c r="M12" s="32"/>
       <c r="N12" s="32"/>
     </row>
@@ -3822,7 +3822,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="36">
+      <c r="B13" s="37">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3831,7 +3831,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="36">
+      <c r="G13" s="37">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3840,7 +3840,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="36">
+      <c r="L13" s="37">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3876,19 +3876,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="37" t="s">
+      <c r="A25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
-      <c r="F25" s="37" t="s">
+      <c r="F25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
       <c r="I25" s="32"/>
-      <c r="K25" s="37" t="s">
+      <c r="K25" s="33" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="32"/>
@@ -3896,19 +3896,19 @@
       <c r="N25" s="32"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="37" t="s">
+      <c r="A26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
-      <c r="F26" s="37" t="s">
+      <c r="F26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="32"/>
       <c r="H26" s="32"/>
       <c r="I26" s="32"/>
-      <c r="K26" s="37" t="s">
+      <c r="K26" s="33" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="32"/>
@@ -3930,27 +3930,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="35" t="s">
+      <c r="A28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="32"/>
-      <c r="C28" s="35" t="s">
+      <c r="C28" s="36" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="32"/>
-      <c r="F28" s="35" t="s">
+      <c r="F28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="32"/>
-      <c r="H28" s="35" t="s">
+      <c r="H28" s="36" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="32"/>
-      <c r="K28" s="35" t="s">
+      <c r="K28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="32"/>
-      <c r="M28" s="35" t="s">
+      <c r="M28" s="36" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="32"/>
@@ -3959,19 +3959,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="34"/>
+      <c r="B29" s="35"/>
       <c r="C29" s="32"/>
       <c r="D29" s="32"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="34"/>
+      <c r="G29" s="35"/>
       <c r="H29" s="32"/>
       <c r="I29" s="32"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="34"/>
+      <c r="L29" s="35"/>
       <c r="M29" s="32"/>
       <c r="N29" s="32"/>
     </row>
@@ -3979,19 +3979,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="33"/>
+      <c r="B30" s="34"/>
       <c r="C30" s="32"/>
       <c r="D30" s="32"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="33"/>
+      <c r="G30" s="34"/>
       <c r="H30" s="32"/>
       <c r="I30" s="32"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="33"/>
+      <c r="L30" s="34"/>
       <c r="M30" s="32"/>
       <c r="N30" s="32"/>
     </row>
@@ -3999,19 +3999,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="34"/>
+      <c r="B31" s="35"/>
       <c r="C31" s="32"/>
       <c r="D31" s="32"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="34"/>
+      <c r="G31" s="35"/>
       <c r="H31" s="32"/>
       <c r="I31" s="32"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="34"/>
+      <c r="L31" s="35"/>
       <c r="M31" s="32"/>
       <c r="N31" s="32"/>
     </row>
@@ -4019,19 +4019,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="33"/>
+      <c r="B32" s="34"/>
       <c r="C32" s="32"/>
       <c r="D32" s="32"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="33"/>
+      <c r="G32" s="34"/>
       <c r="H32" s="32"/>
       <c r="I32" s="32"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="33"/>
+      <c r="L32" s="34"/>
       <c r="M32" s="32"/>
       <c r="N32" s="32"/>
     </row>
@@ -4039,19 +4039,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="34"/>
+      <c r="B33" s="35"/>
       <c r="C33" s="32"/>
       <c r="D33" s="32"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="34"/>
+      <c r="G33" s="35"/>
       <c r="H33" s="32"/>
       <c r="I33" s="32"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="34"/>
+      <c r="L33" s="35"/>
       <c r="M33" s="32"/>
       <c r="N33" s="32"/>
     </row>
@@ -4059,19 +4059,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="33"/>
+      <c r="B34" s="34"/>
       <c r="C34" s="32"/>
       <c r="D34" s="32"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="33"/>
+      <c r="G34" s="34"/>
       <c r="H34" s="32"/>
       <c r="I34" s="32"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="33"/>
+      <c r="L34" s="34"/>
       <c r="M34" s="32"/>
       <c r="N34" s="32"/>
     </row>
@@ -4079,19 +4079,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="34"/>
+      <c r="B35" s="35"/>
       <c r="C35" s="32"/>
       <c r="D35" s="32"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="34"/>
+      <c r="G35" s="35"/>
       <c r="H35" s="32"/>
       <c r="I35" s="32"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="34"/>
+      <c r="L35" s="35"/>
       <c r="M35" s="32"/>
       <c r="N35" s="32"/>
     </row>
@@ -4099,19 +4099,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="33"/>
+      <c r="B36" s="34"/>
       <c r="C36" s="32"/>
       <c r="D36" s="32"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="33"/>
+      <c r="G36" s="34"/>
       <c r="H36" s="32"/>
       <c r="I36" s="32"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="33"/>
+      <c r="L36" s="34"/>
       <c r="M36" s="32"/>
       <c r="N36" s="32"/>
     </row>
@@ -4119,7 +4119,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="36">
+      <c r="B37" s="37">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -4128,7 +4128,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="36">
+      <c r="G37" s="37">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -4137,7 +4137,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="36">
+      <c r="L37" s="37">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -4174,6 +4174,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
     <mergeCell ref="L34:N34"/>
     <mergeCell ref="L6:N6"/>
     <mergeCell ref="B33:D33"/>
@@ -4190,68 +4252,6 @@
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4407,7 +4407,7 @@
         <v>49</v>
       </c>
       <c r="E8" s="18">
-        <v>150</v>
+        <v>70</v>
       </c>
       <c r="F8" s="18"/>
     </row>
@@ -4425,7 +4425,7 @@
         <v>68</v>
       </c>
       <c r="E9" s="18">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="F9" s="18"/>
     </row>
@@ -4443,7 +4443,7 @@
         <v>49</v>
       </c>
       <c r="E10" s="18">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F10" s="18"/>
     </row>
@@ -4461,7 +4461,7 @@
         <v>68</v>
       </c>
       <c r="E11" s="18">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F11" s="18"/>
     </row>
@@ -4479,7 +4479,7 @@
         <v>49</v>
       </c>
       <c r="E12" s="18">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F12" s="18"/>
     </row>
@@ -4497,7 +4497,7 @@
         <v>68</v>
       </c>
       <c r="E13" s="18">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F13" s="18"/>
     </row>
@@ -4515,7 +4515,7 @@
         <v>49</v>
       </c>
       <c r="E14" s="18">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F14" s="18"/>
     </row>
@@ -4533,7 +4533,7 @@
         <v>68</v>
       </c>
       <c r="E15" s="18">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F15" s="18"/>
     </row>
@@ -4551,7 +4551,7 @@
         <v>49</v>
       </c>
       <c r="E16" s="18">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F16" s="18"/>
     </row>
@@ -4569,7 +4569,7 @@
         <v>68</v>
       </c>
       <c r="E17" s="18">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F17" s="18"/>
     </row>
@@ -4831,7 +4831,7 @@
         <v>49</v>
       </c>
       <c r="E32" s="18">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F32" s="18"/>
     </row>
@@ -4849,7 +4849,7 @@
         <v>68</v>
       </c>
       <c r="E33" s="18">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F33" s="18"/>
     </row>
@@ -4867,7 +4867,7 @@
         <v>49</v>
       </c>
       <c r="E34" s="18">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F34" s="18"/>
     </row>
@@ -4885,7 +4885,7 @@
         <v>68</v>
       </c>
       <c r="E35" s="18">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F35" s="18"/>
     </row>
@@ -4903,7 +4903,7 @@
         <v>49</v>
       </c>
       <c r="E36" s="18">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F36" s="18"/>
     </row>
@@ -4921,7 +4921,7 @@
         <v>68</v>
       </c>
       <c r="E37" s="18">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F37" s="18"/>
     </row>
@@ -4957,7 +4957,7 @@
         <v>68</v>
       </c>
       <c r="E39" s="18">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F39" s="18"/>
     </row>
@@ -4975,7 +4975,7 @@
         <v>49</v>
       </c>
       <c r="E40" s="18">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F40" s="18"/>
     </row>
@@ -4993,7 +4993,7 @@
         <v>68</v>
       </c>
       <c r="E41" s="18">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="F41" s="18"/>
     </row>

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A85BEE9E-CE9C-462B-B5BB-BBCA78D0D8EF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D84199-42B7-400A-9F0E-58A059A21BB4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -447,9 +447,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -460,6 +457,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -787,7 +787,7 @@
       </c>
       <c r="B5" s="21">
         <f>SUM(B6:B7)</f>
-        <v>2800</v>
+        <v>2600</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>20</v>
@@ -801,7 +801,7 @@
       </c>
       <c r="L5" s="14">
         <f>SUM(L6:L7)</f>
-        <v>3600</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
@@ -809,7 +809,7 @@
         <v>21</v>
       </c>
       <c r="B6" s="14">
-        <v>1700</v>
+        <v>1600</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>21</v>
@@ -819,7 +819,7 @@
         <v>21</v>
       </c>
       <c r="L6" s="14">
-        <v>3600</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
@@ -827,7 +827,7 @@
         <v>22</v>
       </c>
       <c r="B7" s="14">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>22</v>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="B41" s="13">
         <f>SUM(B5,B8,B11,B14,B17,B20,B23,B26,B29,B32,B35,B38)</f>
-        <v>4220</v>
+        <v>4020</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>34</v>
@@ -1435,7 +1435,7 @@
       </c>
       <c r="L41" s="13">
         <f>SUM(L5,L8,L11,L14,L17,L20,L23,L26,L29,L32,L35,L38)</f>
-        <v>4440</v>
+        <v>2940</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="L53" s="14">
         <f>SUM(L54:L55)</f>
-        <v>290</v>
+        <v>168</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="15" customHeight="1">
@@ -1563,7 +1563,7 @@
         <v>21</v>
       </c>
       <c r="L54" s="14">
-        <v>290</v>
+        <v>168</v>
       </c>
     </row>
     <row r="55" spans="1:14" ht="15" customHeight="1">
@@ -2165,7 +2165,7 @@
       </c>
       <c r="L89" s="13">
         <f>SUM(L53,L56,L59,L62,L65,L68,L71,L74,L77,L80,L83,L86)</f>
-        <v>290</v>
+        <v>168</v>
       </c>
     </row>
     <row r="90" spans="1:14" ht="15" customHeight="1">
@@ -2831,19 +2831,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="32"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
-      <c r="K1" s="33" t="s">
+      <c r="K1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="32"/>
@@ -2851,19 +2851,19 @@
       <c r="N1" s="32"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
-      <c r="F2" s="33" t="s">
+      <c r="F2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="32"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="K2" s="33" t="s">
+      <c r="K2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="32"/>
@@ -2885,27 +2885,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="35" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="32"/>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="32"/>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="35" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="32"/>
-      <c r="K4" s="36" t="s">
+      <c r="K4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="32"/>
-      <c r="M4" s="36" t="s">
+      <c r="M4" s="35" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="32"/>
@@ -2914,21 +2914,21 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="35">
-        <v>0</v>
-      </c>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
+      <c r="B5" s="34">
+        <v>0</v>
+      </c>
+      <c r="C5" s="34"/>
+      <c r="D5" s="34"/>
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="35"/>
+      <c r="G5" s="34"/>
       <c r="H5" s="32"/>
       <c r="I5" s="32"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="35"/>
+      <c r="L5" s="34"/>
       <c r="M5" s="32"/>
       <c r="N5" s="32"/>
     </row>
@@ -2936,21 +2936,21 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="34">
-        <v>0</v>
-      </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
+      <c r="B6" s="33">
+        <v>0</v>
+      </c>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="34"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="34"/>
+      <c r="L6" s="33"/>
       <c r="M6" s="32"/>
       <c r="N6" s="32"/>
     </row>
@@ -2958,21 +2958,21 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="35">
-        <v>0</v>
-      </c>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
+      <c r="B7" s="34">
+        <v>0</v>
+      </c>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="35"/>
+      <c r="G7" s="34"/>
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="35"/>
+      <c r="L7" s="34"/>
       <c r="M7" s="32"/>
       <c r="N7" s="32"/>
     </row>
@@ -2980,21 +2980,21 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="34">
-        <v>0</v>
-      </c>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
+      <c r="B8" s="33">
+        <v>0</v>
+      </c>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="34"/>
+      <c r="G8" s="33"/>
       <c r="H8" s="32"/>
       <c r="I8" s="32"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="34"/>
+      <c r="L8" s="33"/>
       <c r="M8" s="32"/>
       <c r="N8" s="32"/>
     </row>
@@ -3002,21 +3002,21 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="35">
-        <v>0</v>
-      </c>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
+      <c r="B9" s="34">
+        <v>0</v>
+      </c>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="35"/>
+      <c r="G9" s="34"/>
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="35"/>
+      <c r="L9" s="34"/>
       <c r="M9" s="32"/>
       <c r="N9" s="32"/>
     </row>
@@ -3024,21 +3024,21 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="34">
-        <v>0</v>
-      </c>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
+      <c r="B10" s="33">
+        <v>0</v>
+      </c>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="34"/>
+      <c r="G10" s="33"/>
       <c r="H10" s="32"/>
       <c r="I10" s="32"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="34"/>
+      <c r="L10" s="33"/>
       <c r="M10" s="32"/>
       <c r="N10" s="32"/>
     </row>
@@ -3046,7 +3046,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="37">
+      <c r="B11" s="36">
         <f>SUM(B5:B10)</f>
         <v>0</v>
       </c>
@@ -3055,7 +3055,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="37">
+      <c r="G11" s="36">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -3064,7 +3064,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="37">
+      <c r="L11" s="36">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -3100,19 +3100,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="33" t="s">
+      <c r="A25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
-      <c r="F25" s="33" t="s">
+      <c r="F25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
       <c r="I25" s="32"/>
-      <c r="K25" s="33" t="s">
+      <c r="K25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="32"/>
@@ -3120,19 +3120,19 @@
       <c r="N25" s="32"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="33" t="s">
+      <c r="A26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
-      <c r="F26" s="33" t="s">
+      <c r="F26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="32"/>
       <c r="H26" s="32"/>
       <c r="I26" s="32"/>
-      <c r="K26" s="33" t="s">
+      <c r="K26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="32"/>
@@ -3154,27 +3154,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="32"/>
-      <c r="C28" s="36" t="s">
+      <c r="C28" s="35" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="32"/>
-      <c r="F28" s="36" t="s">
+      <c r="F28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="32"/>
-      <c r="H28" s="36" t="s">
+      <c r="H28" s="35" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="32"/>
-      <c r="K28" s="36" t="s">
+      <c r="K28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="32"/>
-      <c r="M28" s="36" t="s">
+      <c r="M28" s="35" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="32"/>
@@ -3183,7 +3183,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="35">
+      <c r="B29" s="34">
         <v>0</v>
       </c>
       <c r="C29" s="32"/>
@@ -3191,23 +3191,23 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="35"/>
+      <c r="G29" s="34"/>
       <c r="H29" s="32"/>
       <c r="I29" s="32"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="35">
-        <v>0</v>
-      </c>
-      <c r="M29" s="35"/>
-      <c r="N29" s="35"/>
+      <c r="L29" s="34">
+        <v>0</v>
+      </c>
+      <c r="M29" s="34"/>
+      <c r="N29" s="34"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="34">
+      <c r="B30" s="33">
         <v>0</v>
       </c>
       <c r="C30" s="32"/>
@@ -3215,23 +3215,23 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="34"/>
+      <c r="G30" s="33"/>
       <c r="H30" s="32"/>
       <c r="I30" s="32"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="34">
-        <v>0</v>
-      </c>
-      <c r="M30" s="34"/>
-      <c r="N30" s="34"/>
+      <c r="L30" s="33">
+        <v>0</v>
+      </c>
+      <c r="M30" s="33"/>
+      <c r="N30" s="33"/>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1">
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="35">
+      <c r="B31" s="34">
         <v>0</v>
       </c>
       <c r="C31" s="32"/>
@@ -3239,23 +3239,23 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="35"/>
+      <c r="G31" s="34"/>
       <c r="H31" s="32"/>
       <c r="I31" s="32"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="35">
-        <v>0</v>
-      </c>
-      <c r="M31" s="35"/>
-      <c r="N31" s="35"/>
+      <c r="L31" s="34">
+        <v>0</v>
+      </c>
+      <c r="M31" s="34"/>
+      <c r="N31" s="34"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="34">
+      <c r="B32" s="33">
         <v>0</v>
       </c>
       <c r="C32" s="32"/>
@@ -3263,23 +3263,23 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="34"/>
+      <c r="G32" s="33"/>
       <c r="H32" s="32"/>
       <c r="I32" s="32"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="34">
-        <v>0</v>
-      </c>
-      <c r="M32" s="34"/>
-      <c r="N32" s="34"/>
+      <c r="L32" s="33">
+        <v>0</v>
+      </c>
+      <c r="M32" s="33"/>
+      <c r="N32" s="33"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="35">
+      <c r="B33" s="34">
         <v>0</v>
       </c>
       <c r="C33" s="32"/>
@@ -3287,23 +3287,23 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="35"/>
+      <c r="G33" s="34"/>
       <c r="H33" s="32"/>
       <c r="I33" s="32"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="35">
-        <v>0</v>
-      </c>
-      <c r="M33" s="35"/>
-      <c r="N33" s="35"/>
+      <c r="L33" s="34">
+        <v>0</v>
+      </c>
+      <c r="M33" s="34"/>
+      <c r="N33" s="34"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="34">
+      <c r="B34" s="33">
         <v>0</v>
       </c>
       <c r="C34" s="32"/>
@@ -3311,13 +3311,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="34"/>
+      <c r="G34" s="33"/>
       <c r="H34" s="32"/>
       <c r="I34" s="32"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="34">
+      <c r="L34" s="33">
         <v>0</v>
       </c>
       <c r="M34" s="32"/>
@@ -3327,7 +3327,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="37">
+      <c r="B35" s="36">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -3336,7 +3336,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="37">
+      <c r="G35" s="36">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -3345,7 +3345,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="37">
+      <c r="L35" s="36">
         <f>SUM(L29:L34)</f>
         <v>0</v>
       </c>
@@ -3382,6 +3382,56 @@
     </row>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B10:D10"/>
@@ -3398,56 +3448,6 @@
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="H28:I28"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3463,7 +3463,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
@@ -3471,7 +3471,7 @@
       <c r="D1" s="32"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
@@ -3485,11 +3485,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="35" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="35" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="32"/>
@@ -3498,7 +3498,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="35"/>
+      <c r="B5" s="34"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
     </row>
@@ -3506,7 +3506,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="34"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
     </row>
@@ -3514,7 +3514,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="35"/>
+      <c r="B7" s="34"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
     </row>
@@ -3522,7 +3522,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="34"/>
+      <c r="B8" s="33"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32"/>
     </row>
@@ -3530,7 +3530,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="37">
+      <c r="B9" s="36">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -3579,19 +3579,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
       <c r="D1" s="32"/>
-      <c r="F1" s="33" t="s">
+      <c r="F1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="32"/>
       <c r="H1" s="32"/>
       <c r="I1" s="32"/>
-      <c r="K1" s="33" t="s">
+      <c r="K1" s="37" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="32"/>
@@ -3599,19 +3599,19 @@
       <c r="N1" s="32"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="32"/>
       <c r="C2" s="32"/>
       <c r="D2" s="32"/>
-      <c r="F2" s="33" t="s">
+      <c r="F2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="32"/>
       <c r="H2" s="32"/>
       <c r="I2" s="32"/>
-      <c r="K2" s="33" t="s">
+      <c r="K2" s="37" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="32"/>
@@ -3633,27 +3633,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="32"/>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="35" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="32"/>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="32"/>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="35" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="32"/>
-      <c r="K4" s="36" t="s">
+      <c r="K4" s="35" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="32"/>
-      <c r="M4" s="36" t="s">
+      <c r="M4" s="35" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="32"/>
@@ -3662,19 +3662,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="35"/>
+      <c r="B5" s="34"/>
       <c r="C5" s="32"/>
       <c r="D5" s="32"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="35"/>
+      <c r="G5" s="34"/>
       <c r="H5" s="32"/>
       <c r="I5" s="32"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="35"/>
+      <c r="L5" s="34"/>
       <c r="M5" s="32"/>
       <c r="N5" s="32"/>
     </row>
@@ -3682,19 +3682,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="34"/>
+      <c r="B6" s="33"/>
       <c r="C6" s="32"/>
       <c r="D6" s="32"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="34"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="34"/>
+      <c r="L6" s="33"/>
       <c r="M6" s="32"/>
       <c r="N6" s="32"/>
     </row>
@@ -3702,19 +3702,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="35"/>
+      <c r="B7" s="34"/>
       <c r="C7" s="32"/>
       <c r="D7" s="32"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="35"/>
+      <c r="G7" s="34"/>
       <c r="H7" s="32"/>
       <c r="I7" s="32"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="35"/>
+      <c r="L7" s="34"/>
       <c r="M7" s="32"/>
       <c r="N7" s="32"/>
     </row>
@@ -3722,19 +3722,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="34"/>
+      <c r="B8" s="33"/>
       <c r="C8" s="32"/>
       <c r="D8" s="32"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="34"/>
+      <c r="G8" s="33"/>
       <c r="H8" s="32"/>
       <c r="I8" s="32"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="34"/>
+      <c r="L8" s="33"/>
       <c r="M8" s="32"/>
       <c r="N8" s="32"/>
     </row>
@@ -3742,19 +3742,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="35"/>
+      <c r="B9" s="34"/>
       <c r="C9" s="32"/>
       <c r="D9" s="32"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="35"/>
+      <c r="G9" s="34"/>
       <c r="H9" s="32"/>
       <c r="I9" s="32"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="35"/>
+      <c r="L9" s="34"/>
       <c r="M9" s="32"/>
       <c r="N9" s="32"/>
     </row>
@@ -3762,19 +3762,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="34"/>
+      <c r="B10" s="33"/>
       <c r="C10" s="32"/>
       <c r="D10" s="32"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="34"/>
+      <c r="G10" s="33"/>
       <c r="H10" s="32"/>
       <c r="I10" s="32"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="34"/>
+      <c r="L10" s="33"/>
       <c r="M10" s="32"/>
       <c r="N10" s="32"/>
     </row>
@@ -3782,19 +3782,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="35"/>
+      <c r="B11" s="34"/>
       <c r="C11" s="32"/>
       <c r="D11" s="32"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="35"/>
+      <c r="G11" s="34"/>
       <c r="H11" s="32"/>
       <c r="I11" s="32"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="35"/>
+      <c r="L11" s="34"/>
       <c r="M11" s="32"/>
       <c r="N11" s="32"/>
     </row>
@@ -3802,19 +3802,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="34"/>
+      <c r="B12" s="33"/>
       <c r="C12" s="32"/>
       <c r="D12" s="32"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="34"/>
+      <c r="G12" s="33"/>
       <c r="H12" s="32"/>
       <c r="I12" s="32"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="34"/>
+      <c r="L12" s="33"/>
       <c r="M12" s="32"/>
       <c r="N12" s="32"/>
     </row>
@@ -3822,7 +3822,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="37">
+      <c r="B13" s="36">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3831,7 +3831,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="37">
+      <c r="G13" s="36">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3840,7 +3840,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="37">
+      <c r="L13" s="36">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3876,19 +3876,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="33" t="s">
+      <c r="A25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="32"/>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
-      <c r="F25" s="33" t="s">
+      <c r="F25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="32"/>
       <c r="H25" s="32"/>
       <c r="I25" s="32"/>
-      <c r="K25" s="33" t="s">
+      <c r="K25" s="37" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="32"/>
@@ -3896,19 +3896,19 @@
       <c r="N25" s="32"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="33" t="s">
+      <c r="A26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="32"/>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
-      <c r="F26" s="33" t="s">
+      <c r="F26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="32"/>
       <c r="H26" s="32"/>
       <c r="I26" s="32"/>
-      <c r="K26" s="33" t="s">
+      <c r="K26" s="37" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="32"/>
@@ -3930,27 +3930,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="32"/>
-      <c r="C28" s="36" t="s">
+      <c r="C28" s="35" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="32"/>
-      <c r="F28" s="36" t="s">
+      <c r="F28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="32"/>
-      <c r="H28" s="36" t="s">
+      <c r="H28" s="35" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="32"/>
-      <c r="K28" s="36" t="s">
+      <c r="K28" s="35" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="32"/>
-      <c r="M28" s="36" t="s">
+      <c r="M28" s="35" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="32"/>
@@ -3959,19 +3959,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="35"/>
+      <c r="B29" s="34"/>
       <c r="C29" s="32"/>
       <c r="D29" s="32"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="35"/>
+      <c r="G29" s="34"/>
       <c r="H29" s="32"/>
       <c r="I29" s="32"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="35"/>
+      <c r="L29" s="34"/>
       <c r="M29" s="32"/>
       <c r="N29" s="32"/>
     </row>
@@ -3979,19 +3979,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="34"/>
+      <c r="B30" s="33"/>
       <c r="C30" s="32"/>
       <c r="D30" s="32"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="34"/>
+      <c r="G30" s="33"/>
       <c r="H30" s="32"/>
       <c r="I30" s="32"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="34"/>
+      <c r="L30" s="33"/>
       <c r="M30" s="32"/>
       <c r="N30" s="32"/>
     </row>
@@ -3999,19 +3999,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="35"/>
+      <c r="B31" s="34"/>
       <c r="C31" s="32"/>
       <c r="D31" s="32"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="35"/>
+      <c r="G31" s="34"/>
       <c r="H31" s="32"/>
       <c r="I31" s="32"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="35"/>
+      <c r="L31" s="34"/>
       <c r="M31" s="32"/>
       <c r="N31" s="32"/>
     </row>
@@ -4019,19 +4019,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="34"/>
+      <c r="B32" s="33"/>
       <c r="C32" s="32"/>
       <c r="D32" s="32"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="34"/>
+      <c r="G32" s="33"/>
       <c r="H32" s="32"/>
       <c r="I32" s="32"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="34"/>
+      <c r="L32" s="33"/>
       <c r="M32" s="32"/>
       <c r="N32" s="32"/>
     </row>
@@ -4039,19 +4039,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="35"/>
+      <c r="B33" s="34"/>
       <c r="C33" s="32"/>
       <c r="D33" s="32"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="35"/>
+      <c r="G33" s="34"/>
       <c r="H33" s="32"/>
       <c r="I33" s="32"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="35"/>
+      <c r="L33" s="34"/>
       <c r="M33" s="32"/>
       <c r="N33" s="32"/>
     </row>
@@ -4059,19 +4059,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="34"/>
+      <c r="B34" s="33"/>
       <c r="C34" s="32"/>
       <c r="D34" s="32"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="34"/>
+      <c r="G34" s="33"/>
       <c r="H34" s="32"/>
       <c r="I34" s="32"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="34"/>
+      <c r="L34" s="33"/>
       <c r="M34" s="32"/>
       <c r="N34" s="32"/>
     </row>
@@ -4079,19 +4079,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="35"/>
+      <c r="B35" s="34"/>
       <c r="C35" s="32"/>
       <c r="D35" s="32"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="35"/>
+      <c r="G35" s="34"/>
       <c r="H35" s="32"/>
       <c r="I35" s="32"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="35"/>
+      <c r="L35" s="34"/>
       <c r="M35" s="32"/>
       <c r="N35" s="32"/>
     </row>
@@ -4099,19 +4099,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="34"/>
+      <c r="B36" s="33"/>
       <c r="C36" s="32"/>
       <c r="D36" s="32"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="34"/>
+      <c r="G36" s="33"/>
       <c r="H36" s="32"/>
       <c r="I36" s="32"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="34"/>
+      <c r="L36" s="33"/>
       <c r="M36" s="32"/>
       <c r="N36" s="32"/>
     </row>
@@ -4119,7 +4119,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="37">
+      <c r="B37" s="36">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -4128,7 +4128,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="37">
+      <c r="G37" s="36">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -4137,7 +4137,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="37">
+      <c r="L37" s="36">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -4174,6 +4174,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
     <mergeCell ref="G36:I36"/>
     <mergeCell ref="L32:N32"/>
     <mergeCell ref="L13:N13"/>
@@ -4190,68 +4252,6 @@
     <mergeCell ref="L33:N33"/>
     <mergeCell ref="L35:N35"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="L9:N9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D84199-42B7-400A-9F0E-58A059A21BB4}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45D3833B-30AB-4C6C-B6F5-4D0C536A8C36}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="75">
   <si>
     <t>Modelo de Disponibilidade por Cultura e Packing</t>
   </si>
@@ -250,6 +250,9 @@
   </si>
   <si>
     <t>CEAGESP</t>
+  </si>
+  <si>
+    <t>Corumbá</t>
   </si>
 </sst>
 </file>
@@ -365,7 +368,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -445,6 +448,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -635,16 +641,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A1" s="31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
+      <c r="A1" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
     </row>
     <row r="3" spans="1:8" ht="29.25" customHeight="1">
       <c r="A3" s="1" t="s">
@@ -775,7 +781,7 @@
         <v>18</v>
       </c>
       <c r="K4" s="12" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="M4" s="12" t="s">
         <v>17</v>
@@ -787,7 +793,7 @@
       </c>
       <c r="B5" s="21">
         <f>SUM(B6:B7)</f>
-        <v>2600</v>
+        <v>2200</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>20</v>
@@ -801,7 +807,7 @@
       </c>
       <c r="L5" s="14">
         <f>SUM(L6:L7)</f>
-        <v>2100</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
@@ -819,7 +825,7 @@
         <v>21</v>
       </c>
       <c r="L6" s="14">
-        <v>2100</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
@@ -827,7 +833,7 @@
         <v>22</v>
       </c>
       <c r="B7" s="14">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>22</v>
@@ -844,7 +850,7 @@
       </c>
       <c r="B8" s="15">
         <f>SUM(B9:B10)</f>
-        <v>280</v>
+        <v>500</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>23</v>
@@ -866,7 +872,7 @@
         <v>21</v>
       </c>
       <c r="B9" s="15">
-        <v>280</v>
+        <v>500</v>
       </c>
       <c r="F9" s="9" t="s">
         <v>21</v>
@@ -950,7 +956,7 @@
       </c>
       <c r="B14" s="15">
         <f>SUM(B15:B16)</f>
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>25</v>
@@ -964,16 +970,14 @@
       </c>
       <c r="L14" s="15">
         <f>SUM(L15:L16)</f>
-        <v>300</v>
+        <v>295</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1">
       <c r="A15" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="15">
-        <v>1000</v>
-      </c>
+      <c r="B15" s="15"/>
       <c r="F15" s="9" t="s">
         <v>21</v>
       </c>
@@ -982,7 +986,8 @@
         <v>21</v>
       </c>
       <c r="L15" s="15">
-        <v>300</v>
+        <f>175+120</f>
+        <v>295</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1">
@@ -1114,7 +1119,7 @@
       </c>
       <c r="G23" s="14">
         <f>SUM(G24:G25)</f>
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="K23" s="7" t="s">
         <v>28</v>
@@ -1132,9 +1137,7 @@
       <c r="F24" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G24" s="14">
-        <v>500</v>
-      </c>
+      <c r="G24" s="14"/>
       <c r="K24" s="7" t="s">
         <v>21</v>
       </c>
@@ -1225,7 +1228,7 @@
       </c>
       <c r="L29" s="14">
         <f>SUM(L30:L31)</f>
-        <v>250</v>
+        <v>390</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1">
@@ -1241,7 +1244,7 @@
         <v>21</v>
       </c>
       <c r="L30" s="14">
-        <v>250</v>
+        <v>390</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1">
@@ -1278,7 +1281,7 @@
       </c>
       <c r="L32" s="15">
         <f>SUM(L33:L34)</f>
-        <v>0</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
@@ -1293,7 +1296,9 @@
       <c r="K33" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L33" s="15"/>
+      <c r="L33" s="15">
+        <v>87</v>
+      </c>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="9" t="s">
@@ -1380,7 +1385,7 @@
       </c>
       <c r="L38" s="23">
         <f>SUM(L39:L40)</f>
-        <v>20</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="15" customHeight="1">
@@ -1398,7 +1403,7 @@
         <v>21</v>
       </c>
       <c r="L39" s="15">
-        <v>20</v>
+        <v>33</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="15" customHeight="1">
@@ -1421,21 +1426,21 @@
       </c>
       <c r="B41" s="13">
         <f>SUM(B5,B8,B11,B14,B17,B20,B23,B26,B29,B32,B35,B38)</f>
-        <v>4020</v>
+        <v>2840</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G41" s="13">
         <f>SUM(G5,G8,G11,G14,G17,G20,G23,G26,G29,G32,G35,G38)</f>
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="L41" s="13">
         <f>SUM(L5,L8,L11,L14,L17,L20,L23,L26,L29,L32,L35,L38)</f>
-        <v>2940</v>
+        <v>5275</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1">
@@ -1506,8 +1511,8 @@
       <c r="N51" s="9"/>
     </row>
     <row r="52" spans="1:14" ht="15" customHeight="1">
-      <c r="A52" s="12" t="s">
-        <v>19</v>
+      <c r="A52" s="31" t="s">
+        <v>74</v>
       </c>
       <c r="C52" s="12" t="s">
         <v>18</v>
@@ -1538,14 +1543,14 @@
       </c>
       <c r="G53" s="14">
         <f>SUM(G54:G55)</f>
-        <v>380</v>
+        <v>0</v>
       </c>
       <c r="K53" s="7" t="s">
         <v>20</v>
       </c>
       <c r="L53" s="14">
         <f>SUM(L54:L55)</f>
-        <v>168</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="15" customHeight="1">
@@ -1556,15 +1561,11 @@
       <c r="F54" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G54" s="14">
-        <v>380</v>
-      </c>
+      <c r="G54" s="14"/>
       <c r="K54" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="L54" s="14">
-        <v>168</v>
-      </c>
+      <c r="L54" s="14"/>
     </row>
     <row r="55" spans="1:14" ht="15" customHeight="1">
       <c r="A55" s="7" t="s">
@@ -1702,7 +1703,7 @@
       </c>
       <c r="L62" s="15">
         <f>SUM(L63:L64)</f>
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="63" spans="1:14" ht="15" customHeight="1">
@@ -1719,7 +1720,9 @@
       <c r="K63" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L63" s="15"/>
+      <c r="L63" s="15">
+        <v>13</v>
+      </c>
     </row>
     <row r="64" spans="1:14" ht="15" customHeight="1">
       <c r="A64" s="9" t="s">
@@ -2158,14 +2161,14 @@
       </c>
       <c r="G89" s="13">
         <f>SUM(G53,G56,G59,G62,G65,G68,G71,G74,G77,G80,G83,G86)</f>
-        <v>396</v>
+        <v>16</v>
       </c>
       <c r="K89" s="8" t="s">
         <v>34</v>
       </c>
       <c r="L89" s="13">
         <f>SUM(L53,L56,L59,L62,L65,L68,L71,L74,L77,L80,L83,L86)</f>
-        <v>168</v>
+        <v>13</v>
       </c>
     </row>
     <row r="90" spans="1:14" ht="15" customHeight="1">
@@ -2831,44 +2834,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="F1" s="37" t="s">
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="F1" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="K1" s="37" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="K1" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="F2" s="37" t="s">
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="F2" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="K2" s="37" t="s">
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="K2" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
     </row>
     <row r="3" spans="1:14" ht="15" customHeight="1">
       <c r="A3" s="9"/>
@@ -2885,191 +2888,191 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="32"/>
-      <c r="C4" s="35" t="s">
+      <c r="B4" s="33"/>
+      <c r="C4" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="32"/>
-      <c r="F4" s="35" t="s">
+      <c r="D4" s="33"/>
+      <c r="F4" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="32"/>
-      <c r="H4" s="35" t="s">
+      <c r="G4" s="33"/>
+      <c r="H4" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="I4" s="32"/>
-      <c r="K4" s="35" t="s">
+      <c r="I4" s="33"/>
+      <c r="K4" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="L4" s="32"/>
-      <c r="M4" s="35" t="s">
+      <c r="L4" s="33"/>
+      <c r="M4" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="N4" s="32"/>
+      <c r="N4" s="33"/>
     </row>
     <row r="5" spans="1:14" ht="15" customHeight="1">
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="34">
-        <v>0</v>
-      </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="34"/>
+      <c r="B5" s="35">
+        <v>0</v>
+      </c>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="34"/>
-      <c r="H5" s="32"/>
-      <c r="I5" s="32"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="33"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="34"/>
-      <c r="M5" s="32"/>
-      <c r="N5" s="32"/>
+      <c r="L5" s="35"/>
+      <c r="M5" s="33"/>
+      <c r="N5" s="33"/>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="33">
-        <v>0</v>
-      </c>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
+      <c r="B6" s="34">
+        <v>0</v>
+      </c>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="33"/>
-      <c r="H6" s="32"/>
-      <c r="I6" s="32"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="33"/>
-      <c r="M6" s="32"/>
-      <c r="N6" s="32"/>
+      <c r="L6" s="34"/>
+      <c r="M6" s="33"/>
+      <c r="N6" s="33"/>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="34">
-        <v>0</v>
-      </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
+      <c r="B7" s="35">
+        <v>0</v>
+      </c>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="34"/>
-      <c r="H7" s="32"/>
-      <c r="I7" s="32"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="33"/>
+      <c r="I7" s="33"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="34"/>
-      <c r="M7" s="32"/>
-      <c r="N7" s="32"/>
+      <c r="L7" s="35"/>
+      <c r="M7" s="33"/>
+      <c r="N7" s="33"/>
     </row>
     <row r="8" spans="1:14" ht="15" customHeight="1">
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="33">
-        <v>0</v>
-      </c>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
+      <c r="B8" s="34">
+        <v>0</v>
+      </c>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="33"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="33"/>
-      <c r="M8" s="32"/>
-      <c r="N8" s="32"/>
+      <c r="L8" s="34"/>
+      <c r="M8" s="33"/>
+      <c r="N8" s="33"/>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1">
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="34">
-        <v>0</v>
-      </c>
-      <c r="C9" s="34"/>
-      <c r="D9" s="34"/>
+      <c r="B9" s="35">
+        <v>0</v>
+      </c>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="34"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="33"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="34"/>
-      <c r="M9" s="32"/>
-      <c r="N9" s="32"/>
+      <c r="L9" s="35"/>
+      <c r="M9" s="33"/>
+      <c r="N9" s="33"/>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="33">
-        <v>0</v>
-      </c>
-      <c r="C10" s="33"/>
-      <c r="D10" s="33"/>
+      <c r="B10" s="34">
+        <v>0</v>
+      </c>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="33"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="33"/>
-      <c r="M10" s="32"/>
-      <c r="N10" s="32"/>
+      <c r="L10" s="34"/>
+      <c r="M10" s="33"/>
+      <c r="N10" s="33"/>
     </row>
     <row r="11" spans="1:14" ht="15" customHeight="1">
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="36">
+      <c r="B11" s="37">
         <f>SUM(B5:B10)</f>
         <v>0</v>
       </c>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="36">
+      <c r="G11" s="37">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="33"/>
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="36">
+      <c r="L11" s="37">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
-      <c r="M11" s="32"/>
-      <c r="N11" s="32"/>
+      <c r="M11" s="33"/>
+      <c r="N11" s="33"/>
     </row>
     <row r="12" spans="1:14" ht="15" customHeight="1">
       <c r="A12" s="9"/>
@@ -3100,44 +3103,44 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="37" t="s">
+      <c r="A25" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="B25" s="32"/>
-      <c r="C25" s="32"/>
-      <c r="D25" s="32"/>
-      <c r="F25" s="37" t="s">
+      <c r="B25" s="33"/>
+      <c r="C25" s="33"/>
+      <c r="D25" s="33"/>
+      <c r="F25" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="32"/>
-      <c r="K25" s="37" t="s">
+      <c r="G25" s="33"/>
+      <c r="H25" s="33"/>
+      <c r="I25" s="33"/>
+      <c r="K25" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="L25" s="32"/>
-      <c r="M25" s="32"/>
-      <c r="N25" s="32"/>
+      <c r="L25" s="33"/>
+      <c r="M25" s="33"/>
+      <c r="N25" s="33"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="37" t="s">
+      <c r="A26" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="32"/>
-      <c r="C26" s="32"/>
-      <c r="D26" s="32"/>
-      <c r="F26" s="37" t="s">
+      <c r="B26" s="33"/>
+      <c r="C26" s="33"/>
+      <c r="D26" s="33"/>
+      <c r="F26" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="G26" s="32"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="32"/>
-      <c r="K26" s="37" t="s">
+      <c r="G26" s="33"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="33"/>
+      <c r="K26" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L26" s="32"/>
-      <c r="M26" s="32"/>
-      <c r="N26" s="32"/>
+      <c r="L26" s="33"/>
+      <c r="M26" s="33"/>
+      <c r="N26" s="33"/>
     </row>
     <row r="27" spans="1:14" ht="15" customHeight="1">
       <c r="A27" s="9"/>
@@ -3154,203 +3157,203 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="35" t="s">
+      <c r="A28" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="B28" s="32"/>
-      <c r="C28" s="35" t="s">
+      <c r="B28" s="33"/>
+      <c r="C28" s="36" t="s">
         <v>38</v>
       </c>
-      <c r="D28" s="32"/>
-      <c r="F28" s="35" t="s">
+      <c r="D28" s="33"/>
+      <c r="F28" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="G28" s="32"/>
-      <c r="H28" s="35" t="s">
+      <c r="G28" s="33"/>
+      <c r="H28" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="I28" s="32"/>
-      <c r="K28" s="35" t="s">
+      <c r="I28" s="33"/>
+      <c r="K28" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="L28" s="32"/>
-      <c r="M28" s="35" t="s">
+      <c r="L28" s="33"/>
+      <c r="M28" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="N28" s="32"/>
+      <c r="N28" s="33"/>
     </row>
     <row r="29" spans="1:14" ht="15" customHeight="1">
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="34">
-        <v>0</v>
-      </c>
-      <c r="C29" s="32"/>
-      <c r="D29" s="32"/>
+      <c r="B29" s="35">
+        <v>0</v>
+      </c>
+      <c r="C29" s="33"/>
+      <c r="D29" s="33"/>
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="34"/>
-      <c r="H29" s="32"/>
-      <c r="I29" s="32"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="33"/>
+      <c r="I29" s="33"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="34">
-        <v>0</v>
-      </c>
-      <c r="M29" s="34"/>
-      <c r="N29" s="34"/>
+      <c r="L29" s="35">
+        <v>0</v>
+      </c>
+      <c r="M29" s="35"/>
+      <c r="N29" s="35"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="33">
-        <v>0</v>
-      </c>
-      <c r="C30" s="32"/>
-      <c r="D30" s="32"/>
+      <c r="B30" s="34">
+        <v>0</v>
+      </c>
+      <c r="C30" s="33"/>
+      <c r="D30" s="33"/>
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="33"/>
-      <c r="H30" s="32"/>
-      <c r="I30" s="32"/>
+      <c r="G30" s="34"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="33"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="33">
-        <v>0</v>
-      </c>
-      <c r="M30" s="33"/>
-      <c r="N30" s="33"/>
+      <c r="L30" s="34">
+        <v>0</v>
+      </c>
+      <c r="M30" s="34"/>
+      <c r="N30" s="34"/>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1">
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="34">
-        <v>0</v>
-      </c>
-      <c r="C31" s="32"/>
-      <c r="D31" s="32"/>
+      <c r="B31" s="35">
+        <v>0</v>
+      </c>
+      <c r="C31" s="33"/>
+      <c r="D31" s="33"/>
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="34"/>
-      <c r="H31" s="32"/>
-      <c r="I31" s="32"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="33"/>
+      <c r="I31" s="33"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="34">
-        <v>0</v>
-      </c>
-      <c r="M31" s="34"/>
-      <c r="N31" s="34"/>
+      <c r="L31" s="35">
+        <v>0</v>
+      </c>
+      <c r="M31" s="35"/>
+      <c r="N31" s="35"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="33">
-        <v>0</v>
-      </c>
-      <c r="C32" s="32"/>
-      <c r="D32" s="32"/>
+      <c r="B32" s="34">
+        <v>0</v>
+      </c>
+      <c r="C32" s="33"/>
+      <c r="D32" s="33"/>
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="33"/>
-      <c r="H32" s="32"/>
-      <c r="I32" s="32"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="33"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="33">
-        <v>0</v>
-      </c>
-      <c r="M32" s="33"/>
-      <c r="N32" s="33"/>
+      <c r="L32" s="34">
+        <v>0</v>
+      </c>
+      <c r="M32" s="34"/>
+      <c r="N32" s="34"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="34">
-        <v>0</v>
-      </c>
-      <c r="C33" s="32"/>
-      <c r="D33" s="32"/>
+      <c r="B33" s="35">
+        <v>0</v>
+      </c>
+      <c r="C33" s="33"/>
+      <c r="D33" s="33"/>
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="34"/>
-      <c r="H33" s="32"/>
-      <c r="I33" s="32"/>
+      <c r="G33" s="35"/>
+      <c r="H33" s="33"/>
+      <c r="I33" s="33"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="34">
-        <v>0</v>
-      </c>
-      <c r="M33" s="34"/>
-      <c r="N33" s="34"/>
+      <c r="L33" s="35">
+        <v>0</v>
+      </c>
+      <c r="M33" s="35"/>
+      <c r="N33" s="35"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="33">
-        <v>0</v>
-      </c>
-      <c r="C34" s="32"/>
-      <c r="D34" s="32"/>
+      <c r="B34" s="34">
+        <v>0</v>
+      </c>
+      <c r="C34" s="33"/>
+      <c r="D34" s="33"/>
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="33"/>
-      <c r="H34" s="32"/>
-      <c r="I34" s="32"/>
+      <c r="G34" s="34"/>
+      <c r="H34" s="33"/>
+      <c r="I34" s="33"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="33">
-        <v>0</v>
-      </c>
-      <c r="M34" s="32"/>
-      <c r="N34" s="32"/>
+      <c r="L34" s="34">
+        <v>0</v>
+      </c>
+      <c r="M34" s="33"/>
+      <c r="N34" s="33"/>
     </row>
     <row r="35" spans="1:14" ht="15" customHeight="1">
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="36">
+      <c r="B35" s="37">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
-      <c r="C35" s="32"/>
-      <c r="D35" s="32"/>
+      <c r="C35" s="33"/>
+      <c r="D35" s="33"/>
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="36">
+      <c r="G35" s="37">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
-      <c r="H35" s="32"/>
-      <c r="I35" s="32"/>
+      <c r="H35" s="33"/>
+      <c r="I35" s="33"/>
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="36">
+      <c r="L35" s="37">
         <f>SUM(L29:L34)</f>
         <v>0</v>
       </c>
-      <c r="M35" s="32"/>
-      <c r="N35" s="32"/>
+      <c r="M35" s="33"/>
+      <c r="N35" s="33"/>
     </row>
     <row r="36" spans="1:14" ht="15" customHeight="1">
       <c r="A36" s="9"/>
@@ -3463,20 +3466,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
     </row>
     <row r="3" spans="1:4" ht="15" customHeight="1">
       <c r="A3" s="9"/>
@@ -3485,57 +3488,57 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="32"/>
-      <c r="C4" s="35" t="s">
+      <c r="B4" s="33"/>
+      <c r="C4" s="36" t="s">
         <v>48</v>
       </c>
-      <c r="D4" s="32"/>
+      <c r="D4" s="33"/>
     </row>
     <row r="5" spans="1:4" ht="15" customHeight="1">
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
     </row>
     <row r="6" spans="1:4" ht="15" customHeight="1">
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="33"/>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
     </row>
     <row r="7" spans="1:4" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="34"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
     </row>
     <row r="8" spans="1:4" ht="15" customHeight="1">
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
     </row>
     <row r="9" spans="1:4" ht="15" customHeight="1">
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="36">
+      <c r="B9" s="37">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
     </row>
     <row r="10" spans="1:4" ht="15" customHeight="1">
       <c r="A10" s="9"/>
@@ -3579,44 +3582,44 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="F1" s="37" t="s">
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="F1" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="K1" s="37" t="s">
+      <c r="G1" s="33"/>
+      <c r="H1" s="33"/>
+      <c r="I1" s="33"/>
+      <c r="K1" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="L1" s="32"/>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
+      <c r="N1" s="33"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="F2" s="37" t="s">
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="F2" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
-      <c r="I2" s="32"/>
-      <c r="K2" s="37" t="s">
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
+      <c r="I2" s="33"/>
+      <c r="K2" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L2" s="32"/>
-      <c r="M2" s="32"/>
-      <c r="N2" s="32"/>
+      <c r="L2" s="33"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="33"/>
     </row>
     <row r="3" spans="1:14" ht="15" customHeight="1">
       <c r="A3" s="9"/>
@@ -3633,219 +3636,219 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="35" t="s">
+      <c r="A4" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="32"/>
-      <c r="C4" s="35" t="s">
+      <c r="B4" s="33"/>
+      <c r="C4" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="D4" s="32"/>
-      <c r="F4" s="35" t="s">
+      <c r="D4" s="33"/>
+      <c r="F4" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="32"/>
-      <c r="H4" s="35" t="s">
+      <c r="G4" s="33"/>
+      <c r="H4" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="I4" s="32"/>
-      <c r="K4" s="35" t="s">
+      <c r="I4" s="33"/>
+      <c r="K4" s="36" t="s">
         <v>37</v>
       </c>
-      <c r="L4" s="32"/>
-      <c r="M4" s="35" t="s">
+      <c r="L4" s="33"/>
+      <c r="M4" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="N4" s="32"/>
+      <c r="N4" s="33"/>
     </row>
     <row r="5" spans="1:14" ht="15" customHeight="1">
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32"/>
+      <c r="B5" s="35"/>
+      <c r="C5" s="33"/>
+      <c r="D5" s="33"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="34"/>
-      <c r="H5" s="32"/>
-      <c r="I5" s="32"/>
+      <c r="G5" s="35"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="33"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="34"/>
-      <c r="M5" s="32"/>
-      <c r="N5" s="32"/>
+      <c r="L5" s="35"/>
+      <c r="M5" s="33"/>
+      <c r="N5" s="33"/>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="33"/>
-      <c r="C6" s="32"/>
-      <c r="D6" s="32"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="33"/>
-      <c r="H6" s="32"/>
-      <c r="I6" s="32"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="33"/>
-      <c r="M6" s="32"/>
-      <c r="N6" s="32"/>
+      <c r="L6" s="34"/>
+      <c r="M6" s="33"/>
+      <c r="N6" s="33"/>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="34"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="32"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="33"/>
+      <c r="D7" s="33"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="34"/>
-      <c r="H7" s="32"/>
-      <c r="I7" s="32"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="33"/>
+      <c r="I7" s="33"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="34"/>
-      <c r="M7" s="32"/>
-      <c r="N7" s="32"/>
+      <c r="L7" s="35"/>
+      <c r="M7" s="33"/>
+      <c r="N7" s="33"/>
     </row>
     <row r="8" spans="1:14" ht="15" customHeight="1">
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="33"/>
-      <c r="H8" s="32"/>
-      <c r="I8" s="32"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="33"/>
-      <c r="M8" s="32"/>
-      <c r="N8" s="32"/>
+      <c r="L8" s="34"/>
+      <c r="M8" s="33"/>
+      <c r="N8" s="33"/>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1">
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="34"/>
-      <c r="C9" s="32"/>
-      <c r="D9" s="32"/>
+      <c r="B9" s="35"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="34"/>
-      <c r="H9" s="32"/>
-      <c r="I9" s="32"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="33"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="34"/>
-      <c r="M9" s="32"/>
-      <c r="N9" s="32"/>
+      <c r="L9" s="35"/>
+      <c r="M9" s="33"/>
+      <c r="N9" s="33"/>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="33"/>
-      <c r="C10" s="32"/>
-      <c r="D10" s="32"/>
+      <c r="B10" s="34"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="33"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="32"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="33"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="33"/>
-      <c r="M10" s="32"/>
-      <c r="N10" s="32"/>
+      <c r="L10" s="34"/>
+      <c r="M10" s="33"/>
+      <c r="N10" s="33"/>
     </row>
     <row r="11" spans="1:14" ht="15" customHeight="1">
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="34"/>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="34"/>
-      <c r="H11" s="32"/>
-      <c r="I11" s="32"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="33"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="34"/>
-      <c r="M11" s="32"/>
-      <c r="N11" s="32"/>
+      <c r="L11" s="35"/>
+      <c r="M11" s="33"/>
+      <c r="N11" s="33"/>
     </row>
     <row r="12" spans="1:14" ht="15" customHeight="1">
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="33"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="32"/>
+      <c r="B12" s="34"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="33"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
+      <c r="G12" s="34"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="33"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="33"/>
-      <c r="M12" s="32"/>
-      <c r="N12" s="32"/>
+      <c r="L12" s="34"/>
+      <c r="M12" s="33"/>
+      <c r="N12" s="33"/>
     </row>
     <row r="13" spans="1:14" ht="15" customHeight="1">
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="36">
+      <c r="B13" s="37">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="36">
+      <c r="G13" s="37">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
-      <c r="H13" s="32"/>
-      <c r="I13" s="32"/>
+      <c r="H13" s="33"/>
+      <c r="I13" s="33"/>
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="36">
+      <c r="L13" s="37">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
-      <c r="M13" s="32"/>
-      <c r="N13" s="32"/>
+      <c r="M13" s="33"/>
+      <c r="N13" s="33"/>
     </row>
     <row r="14" spans="1:14" ht="15" customHeight="1">
       <c r="A14" s="9"/>
@@ -3876,44 +3879,44 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="37" t="s">
+      <c r="A25" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="B25" s="32"/>
-      <c r="C25" s="32"/>
-      <c r="D25" s="32"/>
-      <c r="F25" s="37" t="s">
+      <c r="B25" s="33"/>
+      <c r="C25" s="33"/>
+      <c r="D25" s="33"/>
+      <c r="F25" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="32"/>
-      <c r="K25" s="37" t="s">
+      <c r="G25" s="33"/>
+      <c r="H25" s="33"/>
+      <c r="I25" s="33"/>
+      <c r="K25" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="L25" s="32"/>
-      <c r="M25" s="32"/>
-      <c r="N25" s="32"/>
+      <c r="L25" s="33"/>
+      <c r="M25" s="33"/>
+      <c r="N25" s="33"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="37" t="s">
+      <c r="A26" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="B26" s="32"/>
-      <c r="C26" s="32"/>
-      <c r="D26" s="32"/>
-      <c r="F26" s="37" t="s">
+      <c r="B26" s="33"/>
+      <c r="C26" s="33"/>
+      <c r="D26" s="33"/>
+      <c r="F26" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="G26" s="32"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="32"/>
-      <c r="K26" s="37" t="s">
+      <c r="G26" s="33"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="33"/>
+      <c r="K26" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="L26" s="32"/>
-      <c r="M26" s="32"/>
-      <c r="N26" s="32"/>
+      <c r="L26" s="33"/>
+      <c r="M26" s="33"/>
+      <c r="N26" s="33"/>
     </row>
     <row r="27" spans="1:14" ht="15" customHeight="1">
       <c r="A27" s="9"/>
@@ -3930,219 +3933,219 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="35" t="s">
+      <c r="A28" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="B28" s="32"/>
-      <c r="C28" s="35" t="s">
+      <c r="B28" s="33"/>
+      <c r="C28" s="36" t="s">
         <v>53</v>
       </c>
-      <c r="D28" s="32"/>
-      <c r="F28" s="35" t="s">
+      <c r="D28" s="33"/>
+      <c r="F28" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="G28" s="32"/>
-      <c r="H28" s="35" t="s">
+      <c r="G28" s="33"/>
+      <c r="H28" s="36" t="s">
         <v>54</v>
       </c>
-      <c r="I28" s="32"/>
-      <c r="K28" s="35" t="s">
+      <c r="I28" s="33"/>
+      <c r="K28" s="36" t="s">
         <v>47</v>
       </c>
-      <c r="L28" s="32"/>
-      <c r="M28" s="35" t="s">
+      <c r="L28" s="33"/>
+      <c r="M28" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="N28" s="32"/>
+      <c r="N28" s="33"/>
     </row>
     <row r="29" spans="1:14" ht="15" customHeight="1">
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="34"/>
-      <c r="C29" s="32"/>
-      <c r="D29" s="32"/>
+      <c r="B29" s="35"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="33"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="34"/>
-      <c r="H29" s="32"/>
-      <c r="I29" s="32"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="33"/>
+      <c r="I29" s="33"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="34"/>
-      <c r="M29" s="32"/>
-      <c r="N29" s="32"/>
+      <c r="L29" s="35"/>
+      <c r="M29" s="33"/>
+      <c r="N29" s="33"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="33"/>
-      <c r="C30" s="32"/>
-      <c r="D30" s="32"/>
+      <c r="B30" s="34"/>
+      <c r="C30" s="33"/>
+      <c r="D30" s="33"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="33"/>
-      <c r="H30" s="32"/>
-      <c r="I30" s="32"/>
+      <c r="G30" s="34"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="33"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="33"/>
-      <c r="M30" s="32"/>
-      <c r="N30" s="32"/>
+      <c r="L30" s="34"/>
+      <c r="M30" s="33"/>
+      <c r="N30" s="33"/>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1">
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="34"/>
-      <c r="C31" s="32"/>
-      <c r="D31" s="32"/>
+      <c r="B31" s="35"/>
+      <c r="C31" s="33"/>
+      <c r="D31" s="33"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="34"/>
-      <c r="H31" s="32"/>
-      <c r="I31" s="32"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="33"/>
+      <c r="I31" s="33"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="34"/>
-      <c r="M31" s="32"/>
-      <c r="N31" s="32"/>
+      <c r="L31" s="35"/>
+      <c r="M31" s="33"/>
+      <c r="N31" s="33"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="33"/>
-      <c r="C32" s="32"/>
-      <c r="D32" s="32"/>
+      <c r="B32" s="34"/>
+      <c r="C32" s="33"/>
+      <c r="D32" s="33"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="33"/>
-      <c r="H32" s="32"/>
-      <c r="I32" s="32"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="33"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="33"/>
-      <c r="M32" s="32"/>
-      <c r="N32" s="32"/>
+      <c r="L32" s="34"/>
+      <c r="M32" s="33"/>
+      <c r="N32" s="33"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="34"/>
-      <c r="C33" s="32"/>
-      <c r="D33" s="32"/>
+      <c r="B33" s="35"/>
+      <c r="C33" s="33"/>
+      <c r="D33" s="33"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="34"/>
-      <c r="H33" s="32"/>
-      <c r="I33" s="32"/>
+      <c r="G33" s="35"/>
+      <c r="H33" s="33"/>
+      <c r="I33" s="33"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="34"/>
-      <c r="M33" s="32"/>
-      <c r="N33" s="32"/>
+      <c r="L33" s="35"/>
+      <c r="M33" s="33"/>
+      <c r="N33" s="33"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="33"/>
-      <c r="C34" s="32"/>
-      <c r="D34" s="32"/>
+      <c r="B34" s="34"/>
+      <c r="C34" s="33"/>
+      <c r="D34" s="33"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="33"/>
-      <c r="H34" s="32"/>
-      <c r="I34" s="32"/>
+      <c r="G34" s="34"/>
+      <c r="H34" s="33"/>
+      <c r="I34" s="33"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="33"/>
-      <c r="M34" s="32"/>
-      <c r="N34" s="32"/>
+      <c r="L34" s="34"/>
+      <c r="M34" s="33"/>
+      <c r="N34" s="33"/>
     </row>
     <row r="35" spans="1:14" ht="15" customHeight="1">
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="34"/>
-      <c r="C35" s="32"/>
-      <c r="D35" s="32"/>
+      <c r="B35" s="35"/>
+      <c r="C35" s="33"/>
+      <c r="D35" s="33"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="34"/>
-      <c r="H35" s="32"/>
-      <c r="I35" s="32"/>
+      <c r="G35" s="35"/>
+      <c r="H35" s="33"/>
+      <c r="I35" s="33"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="34"/>
-      <c r="M35" s="32"/>
-      <c r="N35" s="32"/>
+      <c r="L35" s="35"/>
+      <c r="M35" s="33"/>
+      <c r="N35" s="33"/>
     </row>
     <row r="36" spans="1:14" ht="15" customHeight="1">
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="33"/>
-      <c r="C36" s="32"/>
-      <c r="D36" s="32"/>
+      <c r="B36" s="34"/>
+      <c r="C36" s="33"/>
+      <c r="D36" s="33"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="33"/>
-      <c r="H36" s="32"/>
-      <c r="I36" s="32"/>
+      <c r="G36" s="34"/>
+      <c r="H36" s="33"/>
+      <c r="I36" s="33"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="33"/>
-      <c r="M36" s="32"/>
-      <c r="N36" s="32"/>
+      <c r="L36" s="34"/>
+      <c r="M36" s="33"/>
+      <c r="N36" s="33"/>
     </row>
     <row r="37" spans="1:14" ht="15" customHeight="1">
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="36">
+      <c r="B37" s="37">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
-      <c r="C37" s="32"/>
-      <c r="D37" s="32"/>
+      <c r="C37" s="33"/>
+      <c r="D37" s="33"/>
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="36">
+      <c r="G37" s="37">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
-      <c r="H37" s="32"/>
-      <c r="I37" s="32"/>
+      <c r="H37" s="33"/>
+      <c r="I37" s="33"/>
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="36">
+      <c r="L37" s="37">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
-      <c r="M37" s="32"/>
-      <c r="N37" s="32"/>
+      <c r="M37" s="33"/>
+      <c r="N37" s="33"/>
     </row>
     <row r="38" spans="1:14" ht="15" customHeight="1">
       <c r="A38" s="9"/>
@@ -4299,7 +4302,7 @@
         <v>49</v>
       </c>
       <c r="E2" s="18">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="F2" s="18"/>
     </row>
@@ -4317,7 +4320,7 @@
         <v>68</v>
       </c>
       <c r="E3" s="18">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F3" s="18"/>
     </row>
@@ -4335,7 +4338,7 @@
         <v>49</v>
       </c>
       <c r="E4" s="18">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="F4" s="18"/>
     </row>
@@ -4353,7 +4356,7 @@
         <v>68</v>
       </c>
       <c r="E5" s="18">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F5" s="18"/>
     </row>
@@ -4371,7 +4374,7 @@
         <v>49</v>
       </c>
       <c r="E6" s="18">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="F6" s="18"/>
     </row>
@@ -4389,7 +4392,7 @@
         <v>68</v>
       </c>
       <c r="E7" s="18">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F7" s="18"/>
     </row>

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45D3833B-30AB-4C6C-B6F5-4D0C536A8C36}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A16D6F6E-1689-4F80-8428-807F669171EC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -453,6 +453,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -463,9 +466,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" s="21">
         <f>SUM(B6:B7)</f>
-        <v>2200</v>
+        <v>2470</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>20</v>
@@ -807,7 +807,7 @@
       </c>
       <c r="L5" s="14">
         <f>SUM(L6:L7)</f>
-        <v>4200</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
@@ -815,7 +815,7 @@
         <v>21</v>
       </c>
       <c r="B6" s="14">
-        <v>1600</v>
+        <v>1400</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>21</v>
@@ -825,7 +825,7 @@
         <v>21</v>
       </c>
       <c r="L6" s="14">
-        <v>4200</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
@@ -833,7 +833,7 @@
         <v>22</v>
       </c>
       <c r="B7" s="14">
-        <v>600</v>
+        <v>1070</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>22</v>
@@ -842,7 +842,9 @@
       <c r="K7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="L7" s="14"/>
+      <c r="L7" s="14">
+        <v>400</v>
+      </c>
     </row>
     <row r="8" spans="1:14" ht="15" customHeight="1">
       <c r="A8" s="9" t="s">
@@ -850,7 +852,7 @@
       </c>
       <c r="B8" s="15">
         <f>SUM(B9:B10)</f>
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>23</v>
@@ -871,9 +873,7 @@
       <c r="A9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="15">
-        <v>500</v>
-      </c>
+      <c r="B9" s="15"/>
       <c r="F9" s="9" t="s">
         <v>21</v>
       </c>
@@ -970,7 +970,7 @@
       </c>
       <c r="L14" s="15">
         <f>SUM(L15:L16)</f>
-        <v>295</v>
+        <v>500</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1">
@@ -986,8 +986,7 @@
         <v>21</v>
       </c>
       <c r="L15" s="15">
-        <f>175+120</f>
-        <v>295</v>
+        <v>500</v>
       </c>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1">
@@ -1228,7 +1227,7 @@
       </c>
       <c r="L29" s="14">
         <f>SUM(L30:L31)</f>
-        <v>390</v>
+        <v>220</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1">
@@ -1244,7 +1243,7 @@
         <v>21</v>
       </c>
       <c r="L30" s="14">
-        <v>390</v>
+        <v>220</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1">
@@ -1281,7 +1280,7 @@
       </c>
       <c r="L32" s="15">
         <f>SUM(L33:L34)</f>
-        <v>87</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
@@ -1296,9 +1295,7 @@
       <c r="K33" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L33" s="15">
-        <v>87</v>
-      </c>
+      <c r="L33" s="15"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="9" t="s">
@@ -1385,7 +1382,7 @@
       </c>
       <c r="L38" s="23">
         <f>SUM(L39:L40)</f>
-        <v>33</v>
+        <v>50</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="15" customHeight="1">
@@ -1403,7 +1400,7 @@
         <v>21</v>
       </c>
       <c r="L39" s="15">
-        <v>33</v>
+        <v>50</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="15" customHeight="1">
@@ -1426,7 +1423,7 @@
       </c>
       <c r="B41" s="13">
         <f>SUM(B5,B8,B11,B14,B17,B20,B23,B26,B29,B32,B35,B38)</f>
-        <v>2840</v>
+        <v>2610</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>34</v>
@@ -1440,7 +1437,7 @@
       </c>
       <c r="L41" s="13">
         <f>SUM(L5,L8,L11,L14,L17,L20,L23,L26,L29,L32,L35,L38)</f>
-        <v>5275</v>
+        <v>2940</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1">
@@ -1550,7 +1547,7 @@
       </c>
       <c r="L53" s="14">
         <f>SUM(L54:L55)</f>
-        <v>0</v>
+        <v>240</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="15" customHeight="1">
@@ -1565,7 +1562,9 @@
       <c r="K54" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="L54" s="14"/>
+      <c r="L54" s="14">
+        <v>240</v>
+      </c>
     </row>
     <row r="55" spans="1:14" ht="15" customHeight="1">
       <c r="A55" s="7" t="s">
@@ -2168,7 +2167,7 @@
       </c>
       <c r="L89" s="13">
         <f>SUM(L53,L56,L59,L62,L65,L68,L71,L74,L77,L80,L83,L86)</f>
-        <v>13</v>
+        <v>253</v>
       </c>
     </row>
     <row r="90" spans="1:14" ht="15" customHeight="1">
@@ -2834,19 +2833,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="34" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="33"/>
       <c r="D1" s="33"/>
-      <c r="F1" s="38" t="s">
+      <c r="F1" s="34" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="33"/>
       <c r="H1" s="33"/>
       <c r="I1" s="33"/>
-      <c r="K1" s="38" t="s">
+      <c r="K1" s="34" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="33"/>
@@ -2854,19 +2853,19 @@
       <c r="N1" s="33"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="34" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="33"/>
       <c r="C2" s="33"/>
       <c r="D2" s="33"/>
-      <c r="F2" s="38" t="s">
+      <c r="F2" s="34" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="33"/>
       <c r="H2" s="33"/>
       <c r="I2" s="33"/>
-      <c r="K2" s="38" t="s">
+      <c r="K2" s="34" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="33"/>
@@ -2888,27 +2887,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="37" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="33"/>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="37" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="33"/>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="37" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="33"/>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="37" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="33"/>
-      <c r="K4" s="36" t="s">
+      <c r="K4" s="37" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="33"/>
-      <c r="M4" s="36" t="s">
+      <c r="M4" s="37" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="33"/>
@@ -2917,21 +2916,21 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="35">
-        <v>0</v>
-      </c>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
+      <c r="B5" s="36">
+        <v>0</v>
+      </c>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="35"/>
+      <c r="G5" s="36"/>
       <c r="H5" s="33"/>
       <c r="I5" s="33"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="35"/>
+      <c r="L5" s="36"/>
       <c r="M5" s="33"/>
       <c r="N5" s="33"/>
     </row>
@@ -2939,21 +2938,21 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="34">
-        <v>0</v>
-      </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
+      <c r="B6" s="35">
+        <v>0</v>
+      </c>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="34"/>
+      <c r="G6" s="35"/>
       <c r="H6" s="33"/>
       <c r="I6" s="33"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="34"/>
+      <c r="L6" s="35"/>
       <c r="M6" s="33"/>
       <c r="N6" s="33"/>
     </row>
@@ -2961,21 +2960,21 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="35">
-        <v>0</v>
-      </c>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
+      <c r="B7" s="36">
+        <v>0</v>
+      </c>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="35"/>
+      <c r="G7" s="36"/>
       <c r="H7" s="33"/>
       <c r="I7" s="33"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="35"/>
+      <c r="L7" s="36"/>
       <c r="M7" s="33"/>
       <c r="N7" s="33"/>
     </row>
@@ -2983,21 +2982,21 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="34">
-        <v>0</v>
-      </c>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
+      <c r="B8" s="35">
+        <v>0</v>
+      </c>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="34"/>
+      <c r="G8" s="35"/>
       <c r="H8" s="33"/>
       <c r="I8" s="33"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="34"/>
+      <c r="L8" s="35"/>
       <c r="M8" s="33"/>
       <c r="N8" s="33"/>
     </row>
@@ -3005,21 +3004,21 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="35">
-        <v>0</v>
-      </c>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
+      <c r="B9" s="36">
+        <v>0</v>
+      </c>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="35"/>
+      <c r="G9" s="36"/>
       <c r="H9" s="33"/>
       <c r="I9" s="33"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="35"/>
+      <c r="L9" s="36"/>
       <c r="M9" s="33"/>
       <c r="N9" s="33"/>
     </row>
@@ -3027,21 +3026,21 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="34">
-        <v>0</v>
-      </c>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
+      <c r="B10" s="35">
+        <v>0</v>
+      </c>
+      <c r="C10" s="35"/>
+      <c r="D10" s="35"/>
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="34"/>
+      <c r="G10" s="35"/>
       <c r="H10" s="33"/>
       <c r="I10" s="33"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="34"/>
+      <c r="L10" s="35"/>
       <c r="M10" s="33"/>
       <c r="N10" s="33"/>
     </row>
@@ -3049,7 +3048,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="37">
+      <c r="B11" s="38">
         <f>SUM(B5:B10)</f>
         <v>0</v>
       </c>
@@ -3058,7 +3057,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="37">
+      <c r="G11" s="38">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -3067,7 +3066,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="37">
+      <c r="L11" s="38">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -3103,19 +3102,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="38" t="s">
+      <c r="A25" s="34" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="33"/>
       <c r="C25" s="33"/>
       <c r="D25" s="33"/>
-      <c r="F25" s="38" t="s">
+      <c r="F25" s="34" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="33"/>
       <c r="H25" s="33"/>
       <c r="I25" s="33"/>
-      <c r="K25" s="38" t="s">
+      <c r="K25" s="34" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="33"/>
@@ -3123,19 +3122,19 @@
       <c r="N25" s="33"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="38" t="s">
+      <c r="A26" s="34" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="33"/>
       <c r="C26" s="33"/>
       <c r="D26" s="33"/>
-      <c r="F26" s="38" t="s">
+      <c r="F26" s="34" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="33"/>
       <c r="H26" s="33"/>
       <c r="I26" s="33"/>
-      <c r="K26" s="38" t="s">
+      <c r="K26" s="34" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="33"/>
@@ -3157,27 +3156,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="37" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="33"/>
-      <c r="C28" s="36" t="s">
+      <c r="C28" s="37" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="33"/>
-      <c r="F28" s="36" t="s">
+      <c r="F28" s="37" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="33"/>
-      <c r="H28" s="36" t="s">
+      <c r="H28" s="37" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="33"/>
-      <c r="K28" s="36" t="s">
+      <c r="K28" s="37" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="33"/>
-      <c r="M28" s="36" t="s">
+      <c r="M28" s="37" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="33"/>
@@ -3186,7 +3185,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="35">
+      <c r="B29" s="36">
         <v>0</v>
       </c>
       <c r="C29" s="33"/>
@@ -3194,23 +3193,23 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="35"/>
+      <c r="G29" s="36"/>
       <c r="H29" s="33"/>
       <c r="I29" s="33"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="35">
-        <v>0</v>
-      </c>
-      <c r="M29" s="35"/>
-      <c r="N29" s="35"/>
+      <c r="L29" s="36">
+        <v>0</v>
+      </c>
+      <c r="M29" s="36"/>
+      <c r="N29" s="36"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="34">
+      <c r="B30" s="35">
         <v>0</v>
       </c>
       <c r="C30" s="33"/>
@@ -3218,23 +3217,23 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="34"/>
+      <c r="G30" s="35"/>
       <c r="H30" s="33"/>
       <c r="I30" s="33"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="34">
-        <v>0</v>
-      </c>
-      <c r="M30" s="34"/>
-      <c r="N30" s="34"/>
+      <c r="L30" s="35">
+        <v>0</v>
+      </c>
+      <c r="M30" s="35"/>
+      <c r="N30" s="35"/>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1">
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="35">
+      <c r="B31" s="36">
         <v>0</v>
       </c>
       <c r="C31" s="33"/>
@@ -3242,23 +3241,23 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="35"/>
+      <c r="G31" s="36"/>
       <c r="H31" s="33"/>
       <c r="I31" s="33"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="35">
-        <v>0</v>
-      </c>
-      <c r="M31" s="35"/>
-      <c r="N31" s="35"/>
+      <c r="L31" s="36">
+        <v>0</v>
+      </c>
+      <c r="M31" s="36"/>
+      <c r="N31" s="36"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="34">
+      <c r="B32" s="35">
         <v>0</v>
       </c>
       <c r="C32" s="33"/>
@@ -3266,23 +3265,23 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="34"/>
+      <c r="G32" s="35"/>
       <c r="H32" s="33"/>
       <c r="I32" s="33"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="34">
-        <v>0</v>
-      </c>
-      <c r="M32" s="34"/>
-      <c r="N32" s="34"/>
+      <c r="L32" s="35">
+        <v>0</v>
+      </c>
+      <c r="M32" s="35"/>
+      <c r="N32" s="35"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="35">
+      <c r="B33" s="36">
         <v>0</v>
       </c>
       <c r="C33" s="33"/>
@@ -3290,23 +3289,23 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="35"/>
+      <c r="G33" s="36"/>
       <c r="H33" s="33"/>
       <c r="I33" s="33"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="35">
-        <v>0</v>
-      </c>
-      <c r="M33" s="35"/>
-      <c r="N33" s="35"/>
+      <c r="L33" s="36">
+        <v>0</v>
+      </c>
+      <c r="M33" s="36"/>
+      <c r="N33" s="36"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="34">
+      <c r="B34" s="35">
         <v>0</v>
       </c>
       <c r="C34" s="33"/>
@@ -3314,13 +3313,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="34"/>
+      <c r="G34" s="35"/>
       <c r="H34" s="33"/>
       <c r="I34" s="33"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="34">
+      <c r="L34" s="35">
         <v>0</v>
       </c>
       <c r="M34" s="33"/>
@@ -3330,7 +3329,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="37">
+      <c r="B35" s="38">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -3339,7 +3338,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="37">
+      <c r="G35" s="38">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -3348,7 +3347,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="37">
+      <c r="L35" s="38">
         <f>SUM(L29:L34)</f>
         <v>0</v>
       </c>
@@ -3385,13 +3384,49 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="L11:N11"/>
@@ -3408,49 +3443,13 @@
     <mergeCell ref="K2:N2"/>
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3466,7 +3465,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="34" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="33"/>
@@ -3474,7 +3473,7 @@
       <c r="D1" s="33"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="34" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="33"/>
@@ -3488,11 +3487,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="37" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="33"/>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="37" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="33"/>
@@ -3501,7 +3500,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="35"/>
+      <c r="B5" s="36"/>
       <c r="C5" s="33"/>
       <c r="D5" s="33"/>
     </row>
@@ -3509,7 +3508,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="34"/>
+      <c r="B6" s="35"/>
       <c r="C6" s="33"/>
       <c r="D6" s="33"/>
     </row>
@@ -3517,7 +3516,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="35"/>
+      <c r="B7" s="36"/>
       <c r="C7" s="33"/>
       <c r="D7" s="33"/>
     </row>
@@ -3525,7 +3524,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="34"/>
+      <c r="B8" s="35"/>
       <c r="C8" s="33"/>
       <c r="D8" s="33"/>
     </row>
@@ -3533,7 +3532,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="37">
+      <c r="B9" s="38">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -3582,19 +3581,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="34" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="33"/>
       <c r="D1" s="33"/>
-      <c r="F1" s="38" t="s">
+      <c r="F1" s="34" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="33"/>
       <c r="H1" s="33"/>
       <c r="I1" s="33"/>
-      <c r="K1" s="38" t="s">
+      <c r="K1" s="34" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="33"/>
@@ -3602,19 +3601,19 @@
       <c r="N1" s="33"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="34" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="33"/>
       <c r="C2" s="33"/>
       <c r="D2" s="33"/>
-      <c r="F2" s="38" t="s">
+      <c r="F2" s="34" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="33"/>
       <c r="H2" s="33"/>
       <c r="I2" s="33"/>
-      <c r="K2" s="38" t="s">
+      <c r="K2" s="34" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="33"/>
@@ -3636,27 +3635,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="37" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="33"/>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="37" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="33"/>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="37" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="33"/>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="37" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="33"/>
-      <c r="K4" s="36" t="s">
+      <c r="K4" s="37" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="33"/>
-      <c r="M4" s="36" t="s">
+      <c r="M4" s="37" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="33"/>
@@ -3665,19 +3664,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="35"/>
+      <c r="B5" s="36"/>
       <c r="C5" s="33"/>
       <c r="D5" s="33"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="35"/>
+      <c r="G5" s="36"/>
       <c r="H5" s="33"/>
       <c r="I5" s="33"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="35"/>
+      <c r="L5" s="36"/>
       <c r="M5" s="33"/>
       <c r="N5" s="33"/>
     </row>
@@ -3685,19 +3684,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="34"/>
+      <c r="B6" s="35"/>
       <c r="C6" s="33"/>
       <c r="D6" s="33"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="34"/>
+      <c r="G6" s="35"/>
       <c r="H6" s="33"/>
       <c r="I6" s="33"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="34"/>
+      <c r="L6" s="35"/>
       <c r="M6" s="33"/>
       <c r="N6" s="33"/>
     </row>
@@ -3705,19 +3704,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="35"/>
+      <c r="B7" s="36"/>
       <c r="C7" s="33"/>
       <c r="D7" s="33"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="35"/>
+      <c r="G7" s="36"/>
       <c r="H7" s="33"/>
       <c r="I7" s="33"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="35"/>
+      <c r="L7" s="36"/>
       <c r="M7" s="33"/>
       <c r="N7" s="33"/>
     </row>
@@ -3725,19 +3724,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="34"/>
+      <c r="B8" s="35"/>
       <c r="C8" s="33"/>
       <c r="D8" s="33"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="34"/>
+      <c r="G8" s="35"/>
       <c r="H8" s="33"/>
       <c r="I8" s="33"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="34"/>
+      <c r="L8" s="35"/>
       <c r="M8" s="33"/>
       <c r="N8" s="33"/>
     </row>
@@ -3745,19 +3744,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="35"/>
+      <c r="B9" s="36"/>
       <c r="C9" s="33"/>
       <c r="D9" s="33"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="35"/>
+      <c r="G9" s="36"/>
       <c r="H9" s="33"/>
       <c r="I9" s="33"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="35"/>
+      <c r="L9" s="36"/>
       <c r="M9" s="33"/>
       <c r="N9" s="33"/>
     </row>
@@ -3765,19 +3764,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="34"/>
+      <c r="B10" s="35"/>
       <c r="C10" s="33"/>
       <c r="D10" s="33"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="34"/>
+      <c r="G10" s="35"/>
       <c r="H10" s="33"/>
       <c r="I10" s="33"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="34"/>
+      <c r="L10" s="35"/>
       <c r="M10" s="33"/>
       <c r="N10" s="33"/>
     </row>
@@ -3785,19 +3784,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="35"/>
+      <c r="B11" s="36"/>
       <c r="C11" s="33"/>
       <c r="D11" s="33"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="35"/>
+      <c r="G11" s="36"/>
       <c r="H11" s="33"/>
       <c r="I11" s="33"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="35"/>
+      <c r="L11" s="36"/>
       <c r="M11" s="33"/>
       <c r="N11" s="33"/>
     </row>
@@ -3805,19 +3804,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="34"/>
+      <c r="B12" s="35"/>
       <c r="C12" s="33"/>
       <c r="D12" s="33"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="34"/>
+      <c r="G12" s="35"/>
       <c r="H12" s="33"/>
       <c r="I12" s="33"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="34"/>
+      <c r="L12" s="35"/>
       <c r="M12" s="33"/>
       <c r="N12" s="33"/>
     </row>
@@ -3825,7 +3824,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="37">
+      <c r="B13" s="38">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3834,7 +3833,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="37">
+      <c r="G13" s="38">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3843,7 +3842,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="37">
+      <c r="L13" s="38">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3879,19 +3878,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="38" t="s">
+      <c r="A25" s="34" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="33"/>
       <c r="C25" s="33"/>
       <c r="D25" s="33"/>
-      <c r="F25" s="38" t="s">
+      <c r="F25" s="34" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="33"/>
       <c r="H25" s="33"/>
       <c r="I25" s="33"/>
-      <c r="K25" s="38" t="s">
+      <c r="K25" s="34" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="33"/>
@@ -3899,19 +3898,19 @@
       <c r="N25" s="33"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="38" t="s">
+      <c r="A26" s="34" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="33"/>
       <c r="C26" s="33"/>
       <c r="D26" s="33"/>
-      <c r="F26" s="38" t="s">
+      <c r="F26" s="34" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="33"/>
       <c r="H26" s="33"/>
       <c r="I26" s="33"/>
-      <c r="K26" s="38" t="s">
+      <c r="K26" s="34" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="33"/>
@@ -3933,27 +3932,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="37" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="33"/>
-      <c r="C28" s="36" t="s">
+      <c r="C28" s="37" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="33"/>
-      <c r="F28" s="36" t="s">
+      <c r="F28" s="37" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="33"/>
-      <c r="H28" s="36" t="s">
+      <c r="H28" s="37" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="33"/>
-      <c r="K28" s="36" t="s">
+      <c r="K28" s="37" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="33"/>
-      <c r="M28" s="36" t="s">
+      <c r="M28" s="37" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="33"/>
@@ -3962,19 +3961,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="35"/>
+      <c r="B29" s="36"/>
       <c r="C29" s="33"/>
       <c r="D29" s="33"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="35"/>
+      <c r="G29" s="36"/>
       <c r="H29" s="33"/>
       <c r="I29" s="33"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="35"/>
+      <c r="L29" s="36"/>
       <c r="M29" s="33"/>
       <c r="N29" s="33"/>
     </row>
@@ -3982,19 +3981,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="34"/>
+      <c r="B30" s="35"/>
       <c r="C30" s="33"/>
       <c r="D30" s="33"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="34"/>
+      <c r="G30" s="35"/>
       <c r="H30" s="33"/>
       <c r="I30" s="33"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="34"/>
+      <c r="L30" s="35"/>
       <c r="M30" s="33"/>
       <c r="N30" s="33"/>
     </row>
@@ -4002,19 +4001,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="35"/>
+      <c r="B31" s="36"/>
       <c r="C31" s="33"/>
       <c r="D31" s="33"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="35"/>
+      <c r="G31" s="36"/>
       <c r="H31" s="33"/>
       <c r="I31" s="33"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="35"/>
+      <c r="L31" s="36"/>
       <c r="M31" s="33"/>
       <c r="N31" s="33"/>
     </row>
@@ -4022,19 +4021,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="34"/>
+      <c r="B32" s="35"/>
       <c r="C32" s="33"/>
       <c r="D32" s="33"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="34"/>
+      <c r="G32" s="35"/>
       <c r="H32" s="33"/>
       <c r="I32" s="33"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="34"/>
+      <c r="L32" s="35"/>
       <c r="M32" s="33"/>
       <c r="N32" s="33"/>
     </row>
@@ -4042,19 +4041,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="35"/>
+      <c r="B33" s="36"/>
       <c r="C33" s="33"/>
       <c r="D33" s="33"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="35"/>
+      <c r="G33" s="36"/>
       <c r="H33" s="33"/>
       <c r="I33" s="33"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="35"/>
+      <c r="L33" s="36"/>
       <c r="M33" s="33"/>
       <c r="N33" s="33"/>
     </row>
@@ -4062,19 +4061,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="34"/>
+      <c r="B34" s="35"/>
       <c r="C34" s="33"/>
       <c r="D34" s="33"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="34"/>
+      <c r="G34" s="35"/>
       <c r="H34" s="33"/>
       <c r="I34" s="33"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="34"/>
+      <c r="L34" s="35"/>
       <c r="M34" s="33"/>
       <c r="N34" s="33"/>
     </row>
@@ -4082,19 +4081,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="35"/>
+      <c r="B35" s="36"/>
       <c r="C35" s="33"/>
       <c r="D35" s="33"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="35"/>
+      <c r="G35" s="36"/>
       <c r="H35" s="33"/>
       <c r="I35" s="33"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="35"/>
+      <c r="L35" s="36"/>
       <c r="M35" s="33"/>
       <c r="N35" s="33"/>
     </row>
@@ -4102,19 +4101,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="34"/>
+      <c r="B36" s="35"/>
       <c r="C36" s="33"/>
       <c r="D36" s="33"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="34"/>
+      <c r="G36" s="35"/>
       <c r="H36" s="33"/>
       <c r="I36" s="33"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="34"/>
+      <c r="L36" s="35"/>
       <c r="M36" s="33"/>
       <c r="N36" s="33"/>
     </row>
@@ -4122,7 +4121,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="37">
+      <c r="B37" s="38">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -4131,7 +4130,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="37">
+      <c r="G37" s="38">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -4140,7 +4139,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="37">
+      <c r="L37" s="38">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -4177,6 +4176,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
     <mergeCell ref="L34:N34"/>
     <mergeCell ref="L6:N6"/>
     <mergeCell ref="B33:D33"/>
@@ -4193,68 +4254,6 @@
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A16D6F6E-1689-4F80-8428-807F669171EC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEDD93C9-25C5-49B2-B65F-12A5CA55550E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -453,9 +453,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -466,6 +463,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" s="21">
         <f>SUM(B6:B7)</f>
-        <v>2470</v>
+        <v>2300</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>20</v>
@@ -807,7 +807,7 @@
       </c>
       <c r="L5" s="14">
         <f>SUM(L6:L7)</f>
-        <v>1900</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
@@ -815,7 +815,7 @@
         <v>21</v>
       </c>
       <c r="B6" s="14">
-        <v>1400</v>
+        <v>1500</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>21</v>
@@ -825,7 +825,7 @@
         <v>21</v>
       </c>
       <c r="L6" s="14">
-        <v>1500</v>
+        <v>2600</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
@@ -833,7 +833,7 @@
         <v>22</v>
       </c>
       <c r="B7" s="14">
-        <v>1070</v>
+        <v>800</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>22</v>
@@ -842,9 +842,7 @@
       <c r="K7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="L7" s="14">
-        <v>400</v>
-      </c>
+      <c r="L7" s="14"/>
     </row>
     <row r="8" spans="1:14" ht="15" customHeight="1">
       <c r="A8" s="9" t="s">
@@ -866,7 +864,7 @@
       </c>
       <c r="L8" s="15">
         <f>SUM(L9:L10)</f>
-        <v>270</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1">
@@ -882,7 +880,7 @@
         <v>21</v>
       </c>
       <c r="L9" s="15">
-        <v>270</v>
+        <v>350</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
@@ -970,7 +968,7 @@
       </c>
       <c r="L14" s="15">
         <f>SUM(L15:L16)</f>
-        <v>500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1">
@@ -985,9 +983,7 @@
       <c r="K15" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L15" s="15">
-        <v>500</v>
-      </c>
+      <c r="L15" s="15"/>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1">
       <c r="A16" s="9" t="s">
@@ -1162,7 +1158,7 @@
       </c>
       <c r="B26" s="15">
         <f>SUM(B27:B28)</f>
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>29</v>
@@ -1197,7 +1193,9 @@
       <c r="A28" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B28" s="15"/>
+      <c r="B28" s="15">
+        <v>1100</v>
+      </c>
       <c r="F28" s="9" t="s">
         <v>22</v>
       </c>
@@ -1227,7 +1225,7 @@
       </c>
       <c r="L29" s="14">
         <f>SUM(L30:L31)</f>
-        <v>220</v>
+        <v>680</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1">
@@ -1243,7 +1241,7 @@
         <v>21</v>
       </c>
       <c r="L30" s="14">
-        <v>220</v>
+        <v>680</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1">
@@ -1423,7 +1421,7 @@
       </c>
       <c r="B41" s="13">
         <f>SUM(B5,B8,B11,B14,B17,B20,B23,B26,B29,B32,B35,B38)</f>
-        <v>2610</v>
+        <v>3540</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>34</v>
@@ -1437,7 +1435,7 @@
       </c>
       <c r="L41" s="13">
         <f>SUM(L5,L8,L11,L14,L17,L20,L23,L26,L29,L32,L35,L38)</f>
-        <v>2940</v>
+        <v>3680</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1">
@@ -1547,7 +1545,7 @@
       </c>
       <c r="L53" s="14">
         <f>SUM(L54:L55)</f>
-        <v>240</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="15" customHeight="1">
@@ -1562,9 +1560,7 @@
       <c r="K54" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="L54" s="14">
-        <v>240</v>
-      </c>
+      <c r="L54" s="14"/>
     </row>
     <row r="55" spans="1:14" ht="15" customHeight="1">
       <c r="A55" s="7" t="s">
@@ -1702,7 +1698,7 @@
       </c>
       <c r="L62" s="15">
         <f>SUM(L63:L64)</f>
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:14" ht="15" customHeight="1">
@@ -1719,9 +1715,7 @@
       <c r="K63" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L63" s="15">
-        <v>13</v>
-      </c>
+      <c r="L63" s="15"/>
     </row>
     <row r="64" spans="1:14" ht="15" customHeight="1">
       <c r="A64" s="9" t="s">
@@ -2167,7 +2161,7 @@
       </c>
       <c r="L89" s="13">
         <f>SUM(L53,L56,L59,L62,L65,L68,L71,L74,L77,L80,L83,L86)</f>
-        <v>253</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:14" ht="15" customHeight="1">
@@ -2833,19 +2827,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="38" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="33"/>
       <c r="D1" s="33"/>
-      <c r="F1" s="34" t="s">
+      <c r="F1" s="38" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="33"/>
       <c r="H1" s="33"/>
       <c r="I1" s="33"/>
-      <c r="K1" s="34" t="s">
+      <c r="K1" s="38" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="33"/>
@@ -2853,19 +2847,19 @@
       <c r="N1" s="33"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="38" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="33"/>
       <c r="C2" s="33"/>
       <c r="D2" s="33"/>
-      <c r="F2" s="34" t="s">
+      <c r="F2" s="38" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="33"/>
       <c r="H2" s="33"/>
       <c r="I2" s="33"/>
-      <c r="K2" s="34" t="s">
+      <c r="K2" s="38" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="33"/>
@@ -2887,27 +2881,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="33"/>
-      <c r="C4" s="37" t="s">
+      <c r="C4" s="36" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="33"/>
-      <c r="F4" s="37" t="s">
+      <c r="F4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="33"/>
-      <c r="H4" s="37" t="s">
+      <c r="H4" s="36" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="33"/>
-      <c r="K4" s="37" t="s">
+      <c r="K4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="33"/>
-      <c r="M4" s="37" t="s">
+      <c r="M4" s="36" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="33"/>
@@ -2916,21 +2910,21 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="36">
-        <v>0</v>
-      </c>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
+      <c r="B5" s="35">
+        <v>0</v>
+      </c>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="36"/>
+      <c r="G5" s="35"/>
       <c r="H5" s="33"/>
       <c r="I5" s="33"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="36"/>
+      <c r="L5" s="35"/>
       <c r="M5" s="33"/>
       <c r="N5" s="33"/>
     </row>
@@ -2938,21 +2932,21 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="35">
-        <v>0</v>
-      </c>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
+      <c r="B6" s="34">
+        <v>0</v>
+      </c>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="35"/>
+      <c r="G6" s="34"/>
       <c r="H6" s="33"/>
       <c r="I6" s="33"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="35"/>
+      <c r="L6" s="34"/>
       <c r="M6" s="33"/>
       <c r="N6" s="33"/>
     </row>
@@ -2960,21 +2954,21 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="36">
-        <v>0</v>
-      </c>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
+      <c r="B7" s="35">
+        <v>0</v>
+      </c>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="36"/>
+      <c r="G7" s="35"/>
       <c r="H7" s="33"/>
       <c r="I7" s="33"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="36"/>
+      <c r="L7" s="35"/>
       <c r="M7" s="33"/>
       <c r="N7" s="33"/>
     </row>
@@ -2982,21 +2976,21 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="35">
-        <v>0</v>
-      </c>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
+      <c r="B8" s="34">
+        <v>0</v>
+      </c>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="35"/>
+      <c r="G8" s="34"/>
       <c r="H8" s="33"/>
       <c r="I8" s="33"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="35"/>
+      <c r="L8" s="34"/>
       <c r="M8" s="33"/>
       <c r="N8" s="33"/>
     </row>
@@ -3004,21 +2998,21 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="36">
-        <v>0</v>
-      </c>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
+      <c r="B9" s="35">
+        <v>0</v>
+      </c>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="36"/>
+      <c r="G9" s="35"/>
       <c r="H9" s="33"/>
       <c r="I9" s="33"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="36"/>
+      <c r="L9" s="35"/>
       <c r="M9" s="33"/>
       <c r="N9" s="33"/>
     </row>
@@ -3026,21 +3020,21 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="35">
-        <v>0</v>
-      </c>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
+      <c r="B10" s="34">
+        <v>0</v>
+      </c>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="35"/>
+      <c r="G10" s="34"/>
       <c r="H10" s="33"/>
       <c r="I10" s="33"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="35"/>
+      <c r="L10" s="34"/>
       <c r="M10" s="33"/>
       <c r="N10" s="33"/>
     </row>
@@ -3048,7 +3042,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="38">
+      <c r="B11" s="37">
         <f>SUM(B5:B10)</f>
         <v>0</v>
       </c>
@@ -3057,7 +3051,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="38">
+      <c r="G11" s="37">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -3066,7 +3060,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="38">
+      <c r="L11" s="37">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -3102,19 +3096,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="34" t="s">
+      <c r="A25" s="38" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="33"/>
       <c r="C25" s="33"/>
       <c r="D25" s="33"/>
-      <c r="F25" s="34" t="s">
+      <c r="F25" s="38" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="33"/>
       <c r="H25" s="33"/>
       <c r="I25" s="33"/>
-      <c r="K25" s="34" t="s">
+      <c r="K25" s="38" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="33"/>
@@ -3122,19 +3116,19 @@
       <c r="N25" s="33"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="34" t="s">
+      <c r="A26" s="38" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="33"/>
       <c r="C26" s="33"/>
       <c r="D26" s="33"/>
-      <c r="F26" s="34" t="s">
+      <c r="F26" s="38" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="33"/>
       <c r="H26" s="33"/>
       <c r="I26" s="33"/>
-      <c r="K26" s="34" t="s">
+      <c r="K26" s="38" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="33"/>
@@ -3156,27 +3150,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="37" t="s">
+      <c r="A28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="33"/>
-      <c r="C28" s="37" t="s">
+      <c r="C28" s="36" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="33"/>
-      <c r="F28" s="37" t="s">
+      <c r="F28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="33"/>
-      <c r="H28" s="37" t="s">
+      <c r="H28" s="36" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="33"/>
-      <c r="K28" s="37" t="s">
+      <c r="K28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="33"/>
-      <c r="M28" s="37" t="s">
+      <c r="M28" s="36" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="33"/>
@@ -3185,7 +3179,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="36">
+      <c r="B29" s="35">
         <v>0</v>
       </c>
       <c r="C29" s="33"/>
@@ -3193,23 +3187,23 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="36"/>
+      <c r="G29" s="35"/>
       <c r="H29" s="33"/>
       <c r="I29" s="33"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="36">
-        <v>0</v>
-      </c>
-      <c r="M29" s="36"/>
-      <c r="N29" s="36"/>
+      <c r="L29" s="35">
+        <v>0</v>
+      </c>
+      <c r="M29" s="35"/>
+      <c r="N29" s="35"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="35">
+      <c r="B30" s="34">
         <v>0</v>
       </c>
       <c r="C30" s="33"/>
@@ -3217,23 +3211,23 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="35"/>
+      <c r="G30" s="34"/>
       <c r="H30" s="33"/>
       <c r="I30" s="33"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="35">
-        <v>0</v>
-      </c>
-      <c r="M30" s="35"/>
-      <c r="N30" s="35"/>
+      <c r="L30" s="34">
+        <v>0</v>
+      </c>
+      <c r="M30" s="34"/>
+      <c r="N30" s="34"/>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1">
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="36">
+      <c r="B31" s="35">
         <v>0</v>
       </c>
       <c r="C31" s="33"/>
@@ -3241,23 +3235,23 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="36"/>
+      <c r="G31" s="35"/>
       <c r="H31" s="33"/>
       <c r="I31" s="33"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="36">
-        <v>0</v>
-      </c>
-      <c r="M31" s="36"/>
-      <c r="N31" s="36"/>
+      <c r="L31" s="35">
+        <v>0</v>
+      </c>
+      <c r="M31" s="35"/>
+      <c r="N31" s="35"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="35">
+      <c r="B32" s="34">
         <v>0</v>
       </c>
       <c r="C32" s="33"/>
@@ -3265,23 +3259,23 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="35"/>
+      <c r="G32" s="34"/>
       <c r="H32" s="33"/>
       <c r="I32" s="33"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="35">
-        <v>0</v>
-      </c>
-      <c r="M32" s="35"/>
-      <c r="N32" s="35"/>
+      <c r="L32" s="34">
+        <v>0</v>
+      </c>
+      <c r="M32" s="34"/>
+      <c r="N32" s="34"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="36">
+      <c r="B33" s="35">
         <v>0</v>
       </c>
       <c r="C33" s="33"/>
@@ -3289,23 +3283,23 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="36"/>
+      <c r="G33" s="35"/>
       <c r="H33" s="33"/>
       <c r="I33" s="33"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="36">
-        <v>0</v>
-      </c>
-      <c r="M33" s="36"/>
-      <c r="N33" s="36"/>
+      <c r="L33" s="35">
+        <v>0</v>
+      </c>
+      <c r="M33" s="35"/>
+      <c r="N33" s="35"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="35">
+      <c r="B34" s="34">
         <v>0</v>
       </c>
       <c r="C34" s="33"/>
@@ -3313,13 +3307,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="35"/>
+      <c r="G34" s="34"/>
       <c r="H34" s="33"/>
       <c r="I34" s="33"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="35">
+      <c r="L34" s="34">
         <v>0</v>
       </c>
       <c r="M34" s="33"/>
@@ -3329,7 +3323,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="38">
+      <c r="B35" s="37">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -3338,7 +3332,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="38">
+      <c r="G35" s="37">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -3347,7 +3341,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="38">
+      <c r="L35" s="37">
         <f>SUM(L29:L34)</f>
         <v>0</v>
       </c>
@@ -3384,6 +3378,56 @@
     </row>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B10:D10"/>
@@ -3400,56 +3444,6 @@
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="H28:I28"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3465,7 +3459,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="38" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="33"/>
@@ -3473,7 +3467,7 @@
       <c r="D1" s="33"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="38" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="33"/>
@@ -3487,11 +3481,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="36" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="33"/>
-      <c r="C4" s="37" t="s">
+      <c r="C4" s="36" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="33"/>
@@ -3500,7 +3494,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="36"/>
+      <c r="B5" s="35"/>
       <c r="C5" s="33"/>
       <c r="D5" s="33"/>
     </row>
@@ -3508,7 +3502,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="35"/>
+      <c r="B6" s="34"/>
       <c r="C6" s="33"/>
       <c r="D6" s="33"/>
     </row>
@@ -3516,7 +3510,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="36"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="33"/>
       <c r="D7" s="33"/>
     </row>
@@ -3524,7 +3518,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="35"/>
+      <c r="B8" s="34"/>
       <c r="C8" s="33"/>
       <c r="D8" s="33"/>
     </row>
@@ -3532,7 +3526,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="38">
+      <c r="B9" s="37">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -3581,19 +3575,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="38" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="33"/>
       <c r="D1" s="33"/>
-      <c r="F1" s="34" t="s">
+      <c r="F1" s="38" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="33"/>
       <c r="H1" s="33"/>
       <c r="I1" s="33"/>
-      <c r="K1" s="34" t="s">
+      <c r="K1" s="38" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="33"/>
@@ -3601,19 +3595,19 @@
       <c r="N1" s="33"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="38" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="33"/>
       <c r="C2" s="33"/>
       <c r="D2" s="33"/>
-      <c r="F2" s="34" t="s">
+      <c r="F2" s="38" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="33"/>
       <c r="H2" s="33"/>
       <c r="I2" s="33"/>
-      <c r="K2" s="34" t="s">
+      <c r="K2" s="38" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="33"/>
@@ -3635,27 +3629,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="33"/>
-      <c r="C4" s="37" t="s">
+      <c r="C4" s="36" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="33"/>
-      <c r="F4" s="37" t="s">
+      <c r="F4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="33"/>
-      <c r="H4" s="37" t="s">
+      <c r="H4" s="36" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="33"/>
-      <c r="K4" s="37" t="s">
+      <c r="K4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="33"/>
-      <c r="M4" s="37" t="s">
+      <c r="M4" s="36" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="33"/>
@@ -3664,19 +3658,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="36"/>
+      <c r="B5" s="35"/>
       <c r="C5" s="33"/>
       <c r="D5" s="33"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="36"/>
+      <c r="G5" s="35"/>
       <c r="H5" s="33"/>
       <c r="I5" s="33"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="36"/>
+      <c r="L5" s="35"/>
       <c r="M5" s="33"/>
       <c r="N5" s="33"/>
     </row>
@@ -3684,19 +3678,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="35"/>
+      <c r="B6" s="34"/>
       <c r="C6" s="33"/>
       <c r="D6" s="33"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="35"/>
+      <c r="G6" s="34"/>
       <c r="H6" s="33"/>
       <c r="I6" s="33"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="35"/>
+      <c r="L6" s="34"/>
       <c r="M6" s="33"/>
       <c r="N6" s="33"/>
     </row>
@@ -3704,19 +3698,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="36"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="33"/>
       <c r="D7" s="33"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="36"/>
+      <c r="G7" s="35"/>
       <c r="H7" s="33"/>
       <c r="I7" s="33"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="36"/>
+      <c r="L7" s="35"/>
       <c r="M7" s="33"/>
       <c r="N7" s="33"/>
     </row>
@@ -3724,19 +3718,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="35"/>
+      <c r="B8" s="34"/>
       <c r="C8" s="33"/>
       <c r="D8" s="33"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="35"/>
+      <c r="G8" s="34"/>
       <c r="H8" s="33"/>
       <c r="I8" s="33"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="35"/>
+      <c r="L8" s="34"/>
       <c r="M8" s="33"/>
       <c r="N8" s="33"/>
     </row>
@@ -3744,19 +3738,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="36"/>
+      <c r="B9" s="35"/>
       <c r="C9" s="33"/>
       <c r="D9" s="33"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="36"/>
+      <c r="G9" s="35"/>
       <c r="H9" s="33"/>
       <c r="I9" s="33"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="36"/>
+      <c r="L9" s="35"/>
       <c r="M9" s="33"/>
       <c r="N9" s="33"/>
     </row>
@@ -3764,19 +3758,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="35"/>
+      <c r="B10" s="34"/>
       <c r="C10" s="33"/>
       <c r="D10" s="33"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="35"/>
+      <c r="G10" s="34"/>
       <c r="H10" s="33"/>
       <c r="I10" s="33"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="35"/>
+      <c r="L10" s="34"/>
       <c r="M10" s="33"/>
       <c r="N10" s="33"/>
     </row>
@@ -3784,19 +3778,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="36"/>
+      <c r="B11" s="35"/>
       <c r="C11" s="33"/>
       <c r="D11" s="33"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="36"/>
+      <c r="G11" s="35"/>
       <c r="H11" s="33"/>
       <c r="I11" s="33"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="36"/>
+      <c r="L11" s="35"/>
       <c r="M11" s="33"/>
       <c r="N11" s="33"/>
     </row>
@@ -3804,19 +3798,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="35"/>
+      <c r="B12" s="34"/>
       <c r="C12" s="33"/>
       <c r="D12" s="33"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="35"/>
+      <c r="G12" s="34"/>
       <c r="H12" s="33"/>
       <c r="I12" s="33"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="35"/>
+      <c r="L12" s="34"/>
       <c r="M12" s="33"/>
       <c r="N12" s="33"/>
     </row>
@@ -3824,7 +3818,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="38">
+      <c r="B13" s="37">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3833,7 +3827,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="38">
+      <c r="G13" s="37">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3842,7 +3836,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="38">
+      <c r="L13" s="37">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3878,19 +3872,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="34" t="s">
+      <c r="A25" s="38" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="33"/>
       <c r="C25" s="33"/>
       <c r="D25" s="33"/>
-      <c r="F25" s="34" t="s">
+      <c r="F25" s="38" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="33"/>
       <c r="H25" s="33"/>
       <c r="I25" s="33"/>
-      <c r="K25" s="34" t="s">
+      <c r="K25" s="38" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="33"/>
@@ -3898,19 +3892,19 @@
       <c r="N25" s="33"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="34" t="s">
+      <c r="A26" s="38" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="33"/>
       <c r="C26" s="33"/>
       <c r="D26" s="33"/>
-      <c r="F26" s="34" t="s">
+      <c r="F26" s="38" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="33"/>
       <c r="H26" s="33"/>
       <c r="I26" s="33"/>
-      <c r="K26" s="34" t="s">
+      <c r="K26" s="38" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="33"/>
@@ -3932,27 +3926,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="37" t="s">
+      <c r="A28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="33"/>
-      <c r="C28" s="37" t="s">
+      <c r="C28" s="36" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="33"/>
-      <c r="F28" s="37" t="s">
+      <c r="F28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="33"/>
-      <c r="H28" s="37" t="s">
+      <c r="H28" s="36" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="33"/>
-      <c r="K28" s="37" t="s">
+      <c r="K28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="33"/>
-      <c r="M28" s="37" t="s">
+      <c r="M28" s="36" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="33"/>
@@ -3961,19 +3955,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="36"/>
+      <c r="B29" s="35"/>
       <c r="C29" s="33"/>
       <c r="D29" s="33"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="36"/>
+      <c r="G29" s="35"/>
       <c r="H29" s="33"/>
       <c r="I29" s="33"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="36"/>
+      <c r="L29" s="35"/>
       <c r="M29" s="33"/>
       <c r="N29" s="33"/>
     </row>
@@ -3981,19 +3975,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="35"/>
+      <c r="B30" s="34"/>
       <c r="C30" s="33"/>
       <c r="D30" s="33"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="35"/>
+      <c r="G30" s="34"/>
       <c r="H30" s="33"/>
       <c r="I30" s="33"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="35"/>
+      <c r="L30" s="34"/>
       <c r="M30" s="33"/>
       <c r="N30" s="33"/>
     </row>
@@ -4001,19 +3995,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="36"/>
+      <c r="B31" s="35"/>
       <c r="C31" s="33"/>
       <c r="D31" s="33"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="36"/>
+      <c r="G31" s="35"/>
       <c r="H31" s="33"/>
       <c r="I31" s="33"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="36"/>
+      <c r="L31" s="35"/>
       <c r="M31" s="33"/>
       <c r="N31" s="33"/>
     </row>
@@ -4021,19 +4015,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="35"/>
+      <c r="B32" s="34"/>
       <c r="C32" s="33"/>
       <c r="D32" s="33"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="35"/>
+      <c r="G32" s="34"/>
       <c r="H32" s="33"/>
       <c r="I32" s="33"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="35"/>
+      <c r="L32" s="34"/>
       <c r="M32" s="33"/>
       <c r="N32" s="33"/>
     </row>
@@ -4041,19 +4035,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="36"/>
+      <c r="B33" s="35"/>
       <c r="C33" s="33"/>
       <c r="D33" s="33"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="36"/>
+      <c r="G33" s="35"/>
       <c r="H33" s="33"/>
       <c r="I33" s="33"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="36"/>
+      <c r="L33" s="35"/>
       <c r="M33" s="33"/>
       <c r="N33" s="33"/>
     </row>
@@ -4061,19 +4055,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="35"/>
+      <c r="B34" s="34"/>
       <c r="C34" s="33"/>
       <c r="D34" s="33"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="35"/>
+      <c r="G34" s="34"/>
       <c r="H34" s="33"/>
       <c r="I34" s="33"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="35"/>
+      <c r="L34" s="34"/>
       <c r="M34" s="33"/>
       <c r="N34" s="33"/>
     </row>
@@ -4081,19 +4075,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="36"/>
+      <c r="B35" s="35"/>
       <c r="C35" s="33"/>
       <c r="D35" s="33"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="36"/>
+      <c r="G35" s="35"/>
       <c r="H35" s="33"/>
       <c r="I35" s="33"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="36"/>
+      <c r="L35" s="35"/>
       <c r="M35" s="33"/>
       <c r="N35" s="33"/>
     </row>
@@ -4101,19 +4095,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="35"/>
+      <c r="B36" s="34"/>
       <c r="C36" s="33"/>
       <c r="D36" s="33"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="35"/>
+      <c r="G36" s="34"/>
       <c r="H36" s="33"/>
       <c r="I36" s="33"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="35"/>
+      <c r="L36" s="34"/>
       <c r="M36" s="33"/>
       <c r="N36" s="33"/>
     </row>
@@ -4121,7 +4115,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="38">
+      <c r="B37" s="37">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -4130,7 +4124,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="38">
+      <c r="G37" s="37">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -4139,7 +4133,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="38">
+      <c r="L37" s="37">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -4176,6 +4170,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
     <mergeCell ref="G36:I36"/>
     <mergeCell ref="L32:N32"/>
     <mergeCell ref="L13:N13"/>
@@ -4192,68 +4248,6 @@
     <mergeCell ref="L33:N33"/>
     <mergeCell ref="L35:N35"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="L9:N9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4301,7 +4295,7 @@
         <v>49</v>
       </c>
       <c r="E2" s="18">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="F2" s="18"/>
     </row>
@@ -4319,7 +4313,7 @@
         <v>68</v>
       </c>
       <c r="E3" s="18">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="F3" s="18"/>
     </row>
@@ -4337,7 +4331,7 @@
         <v>49</v>
       </c>
       <c r="E4" s="18">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="F4" s="18"/>
     </row>
@@ -4355,7 +4349,7 @@
         <v>68</v>
       </c>
       <c r="E5" s="18">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="F5" s="18"/>
     </row>
@@ -4373,7 +4367,7 @@
         <v>49</v>
       </c>
       <c r="E6" s="18">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="F6" s="18"/>
     </row>
@@ -4391,7 +4385,7 @@
         <v>68</v>
       </c>
       <c r="E7" s="18">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="F7" s="18"/>
     </row>

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEDD93C9-25C5-49B2-B65F-12A5CA55550E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8A68365-18B9-4B86-A3DE-0233314273AE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucoes" sheetId="1" r:id="rId1"/>
@@ -453,6 +453,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -463,9 +466,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2827,19 +2827,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="34" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="33"/>
       <c r="D1" s="33"/>
-      <c r="F1" s="38" t="s">
+      <c r="F1" s="34" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="33"/>
       <c r="H1" s="33"/>
       <c r="I1" s="33"/>
-      <c r="K1" s="38" t="s">
+      <c r="K1" s="34" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="33"/>
@@ -2847,19 +2847,19 @@
       <c r="N1" s="33"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="34" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="33"/>
       <c r="C2" s="33"/>
       <c r="D2" s="33"/>
-      <c r="F2" s="38" t="s">
+      <c r="F2" s="34" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="33"/>
       <c r="H2" s="33"/>
       <c r="I2" s="33"/>
-      <c r="K2" s="38" t="s">
+      <c r="K2" s="34" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="33"/>
@@ -2881,27 +2881,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="37" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="33"/>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="37" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="33"/>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="37" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="33"/>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="37" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="33"/>
-      <c r="K4" s="36" t="s">
+      <c r="K4" s="37" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="33"/>
-      <c r="M4" s="36" t="s">
+      <c r="M4" s="37" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="33"/>
@@ -2910,21 +2910,21 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="35">
-        <v>0</v>
-      </c>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
+      <c r="B5" s="36">
+        <v>0</v>
+      </c>
+      <c r="C5" s="36"/>
+      <c r="D5" s="36"/>
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="35"/>
+      <c r="G5" s="36"/>
       <c r="H5" s="33"/>
       <c r="I5" s="33"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="35"/>
+      <c r="L5" s="36"/>
       <c r="M5" s="33"/>
       <c r="N5" s="33"/>
     </row>
@@ -2932,21 +2932,21 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="34">
-        <v>0</v>
-      </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
+      <c r="B6" s="35">
+        <v>0</v>
+      </c>
+      <c r="C6" s="35"/>
+      <c r="D6" s="35"/>
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="34"/>
+      <c r="G6" s="35"/>
       <c r="H6" s="33"/>
       <c r="I6" s="33"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="34"/>
+      <c r="L6" s="35"/>
       <c r="M6" s="33"/>
       <c r="N6" s="33"/>
     </row>
@@ -2954,21 +2954,21 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="35">
-        <v>0</v>
-      </c>
-      <c r="C7" s="35"/>
-      <c r="D7" s="35"/>
+      <c r="B7" s="36">
+        <v>0</v>
+      </c>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="35"/>
+      <c r="G7" s="36"/>
       <c r="H7" s="33"/>
       <c r="I7" s="33"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="35"/>
+      <c r="L7" s="36"/>
       <c r="M7" s="33"/>
       <c r="N7" s="33"/>
     </row>
@@ -2976,21 +2976,21 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="34">
-        <v>0</v>
-      </c>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
+      <c r="B8" s="35">
+        <v>0</v>
+      </c>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="34"/>
+      <c r="G8" s="35"/>
       <c r="H8" s="33"/>
       <c r="I8" s="33"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="34"/>
+      <c r="L8" s="35"/>
       <c r="M8" s="33"/>
       <c r="N8" s="33"/>
     </row>
@@ -2998,21 +2998,21 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="35">
-        <v>0</v>
-      </c>
-      <c r="C9" s="35"/>
-      <c r="D9" s="35"/>
+      <c r="B9" s="36">
+        <v>0</v>
+      </c>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="35"/>
+      <c r="G9" s="36"/>
       <c r="H9" s="33"/>
       <c r="I9" s="33"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="35"/>
+      <c r="L9" s="36"/>
       <c r="M9" s="33"/>
       <c r="N9" s="33"/>
     </row>
@@ -3020,21 +3020,21 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="34">
-        <v>0</v>
-      </c>
-      <c r="C10" s="34"/>
-      <c r="D10" s="34"/>
+      <c r="B10" s="35">
+        <v>0</v>
+      </c>
+      <c r="C10" s="35"/>
+      <c r="D10" s="35"/>
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="34"/>
+      <c r="G10" s="35"/>
       <c r="H10" s="33"/>
       <c r="I10" s="33"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="34"/>
+      <c r="L10" s="35"/>
       <c r="M10" s="33"/>
       <c r="N10" s="33"/>
     </row>
@@ -3042,7 +3042,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="37">
+      <c r="B11" s="38">
         <f>SUM(B5:B10)</f>
         <v>0</v>
       </c>
@@ -3051,7 +3051,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="37">
+      <c r="G11" s="38">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -3060,7 +3060,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="37">
+      <c r="L11" s="38">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -3096,19 +3096,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="38" t="s">
+      <c r="A25" s="34" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="33"/>
       <c r="C25" s="33"/>
       <c r="D25" s="33"/>
-      <c r="F25" s="38" t="s">
+      <c r="F25" s="34" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="33"/>
       <c r="H25" s="33"/>
       <c r="I25" s="33"/>
-      <c r="K25" s="38" t="s">
+      <c r="K25" s="34" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="33"/>
@@ -3116,19 +3116,19 @@
       <c r="N25" s="33"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="38" t="s">
+      <c r="A26" s="34" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="33"/>
       <c r="C26" s="33"/>
       <c r="D26" s="33"/>
-      <c r="F26" s="38" t="s">
+      <c r="F26" s="34" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="33"/>
       <c r="H26" s="33"/>
       <c r="I26" s="33"/>
-      <c r="K26" s="38" t="s">
+      <c r="K26" s="34" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="33"/>
@@ -3150,27 +3150,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="37" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="33"/>
-      <c r="C28" s="36" t="s">
+      <c r="C28" s="37" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="33"/>
-      <c r="F28" s="36" t="s">
+      <c r="F28" s="37" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="33"/>
-      <c r="H28" s="36" t="s">
+      <c r="H28" s="37" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="33"/>
-      <c r="K28" s="36" t="s">
+      <c r="K28" s="37" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="33"/>
-      <c r="M28" s="36" t="s">
+      <c r="M28" s="37" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="33"/>
@@ -3179,7 +3179,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="35">
+      <c r="B29" s="36">
         <v>0</v>
       </c>
       <c r="C29" s="33"/>
@@ -3187,23 +3187,23 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="35"/>
+      <c r="G29" s="36"/>
       <c r="H29" s="33"/>
       <c r="I29" s="33"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="35">
-        <v>0</v>
-      </c>
-      <c r="M29" s="35"/>
-      <c r="N29" s="35"/>
+      <c r="L29" s="36">
+        <v>0</v>
+      </c>
+      <c r="M29" s="36"/>
+      <c r="N29" s="36"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="34">
+      <c r="B30" s="35">
         <v>0</v>
       </c>
       <c r="C30" s="33"/>
@@ -3211,23 +3211,23 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="34"/>
+      <c r="G30" s="35"/>
       <c r="H30" s="33"/>
       <c r="I30" s="33"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="34">
-        <v>0</v>
-      </c>
-      <c r="M30" s="34"/>
-      <c r="N30" s="34"/>
+      <c r="L30" s="35">
+        <v>0</v>
+      </c>
+      <c r="M30" s="35"/>
+      <c r="N30" s="35"/>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1">
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="35">
+      <c r="B31" s="36">
         <v>0</v>
       </c>
       <c r="C31" s="33"/>
@@ -3235,23 +3235,23 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="35"/>
+      <c r="G31" s="36"/>
       <c r="H31" s="33"/>
       <c r="I31" s="33"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="35">
-        <v>0</v>
-      </c>
-      <c r="M31" s="35"/>
-      <c r="N31" s="35"/>
+      <c r="L31" s="36">
+        <v>0</v>
+      </c>
+      <c r="M31" s="36"/>
+      <c r="N31" s="36"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="34">
+      <c r="B32" s="35">
         <v>0</v>
       </c>
       <c r="C32" s="33"/>
@@ -3259,23 +3259,23 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="34"/>
+      <c r="G32" s="35"/>
       <c r="H32" s="33"/>
       <c r="I32" s="33"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="34">
-        <v>0</v>
-      </c>
-      <c r="M32" s="34"/>
-      <c r="N32" s="34"/>
+      <c r="L32" s="35">
+        <v>0</v>
+      </c>
+      <c r="M32" s="35"/>
+      <c r="N32" s="35"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="35">
+      <c r="B33" s="36">
         <v>0</v>
       </c>
       <c r="C33" s="33"/>
@@ -3283,23 +3283,23 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="35"/>
+      <c r="G33" s="36"/>
       <c r="H33" s="33"/>
       <c r="I33" s="33"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="35">
-        <v>0</v>
-      </c>
-      <c r="M33" s="35"/>
-      <c r="N33" s="35"/>
+      <c r="L33" s="36">
+        <v>0</v>
+      </c>
+      <c r="M33" s="36"/>
+      <c r="N33" s="36"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="34">
+      <c r="B34" s="35">
         <v>0</v>
       </c>
       <c r="C34" s="33"/>
@@ -3307,13 +3307,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="34"/>
+      <c r="G34" s="35"/>
       <c r="H34" s="33"/>
       <c r="I34" s="33"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="34">
+      <c r="L34" s="35">
         <v>0</v>
       </c>
       <c r="M34" s="33"/>
@@ -3323,7 +3323,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="37">
+      <c r="B35" s="38">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -3332,7 +3332,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="37">
+      <c r="G35" s="38">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -3341,7 +3341,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="37">
+      <c r="L35" s="38">
         <f>SUM(L29:L34)</f>
         <v>0</v>
       </c>
@@ -3378,13 +3378,49 @@
     </row>
   </sheetData>
   <mergeCells count="66">
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="B5:D5"/>
     <mergeCell ref="L11:N11"/>
@@ -3401,49 +3437,13 @@
     <mergeCell ref="K2:N2"/>
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3459,7 +3459,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="34" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="33"/>
@@ -3467,7 +3467,7 @@
       <c r="D1" s="33"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="34" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="33"/>
@@ -3481,11 +3481,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="37" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="33"/>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="37" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="33"/>
@@ -3494,7 +3494,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="35"/>
+      <c r="B5" s="36"/>
       <c r="C5" s="33"/>
       <c r="D5" s="33"/>
     </row>
@@ -3502,7 +3502,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="34"/>
+      <c r="B6" s="35"/>
       <c r="C6" s="33"/>
       <c r="D6" s="33"/>
     </row>
@@ -3510,7 +3510,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="35"/>
+      <c r="B7" s="36"/>
       <c r="C7" s="33"/>
       <c r="D7" s="33"/>
     </row>
@@ -3518,7 +3518,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="34"/>
+      <c r="B8" s="35"/>
       <c r="C8" s="33"/>
       <c r="D8" s="33"/>
     </row>
@@ -3526,7 +3526,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="37">
+      <c r="B9" s="38">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -3575,19 +3575,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="34" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="33"/>
       <c r="D1" s="33"/>
-      <c r="F1" s="38" t="s">
+      <c r="F1" s="34" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="33"/>
       <c r="H1" s="33"/>
       <c r="I1" s="33"/>
-      <c r="K1" s="38" t="s">
+      <c r="K1" s="34" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="33"/>
@@ -3595,19 +3595,19 @@
       <c r="N1" s="33"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="34" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="33"/>
       <c r="C2" s="33"/>
       <c r="D2" s="33"/>
-      <c r="F2" s="38" t="s">
+      <c r="F2" s="34" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="33"/>
       <c r="H2" s="33"/>
       <c r="I2" s="33"/>
-      <c r="K2" s="38" t="s">
+      <c r="K2" s="34" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="33"/>
@@ -3629,27 +3629,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="37" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="33"/>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="37" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="33"/>
-      <c r="F4" s="36" t="s">
+      <c r="F4" s="37" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="33"/>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="37" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="33"/>
-      <c r="K4" s="36" t="s">
+      <c r="K4" s="37" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="33"/>
-      <c r="M4" s="36" t="s">
+      <c r="M4" s="37" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="33"/>
@@ -3658,19 +3658,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="35"/>
+      <c r="B5" s="36"/>
       <c r="C5" s="33"/>
       <c r="D5" s="33"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="35"/>
+      <c r="G5" s="36"/>
       <c r="H5" s="33"/>
       <c r="I5" s="33"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="35"/>
+      <c r="L5" s="36"/>
       <c r="M5" s="33"/>
       <c r="N5" s="33"/>
     </row>
@@ -3678,19 +3678,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="34"/>
+      <c r="B6" s="35"/>
       <c r="C6" s="33"/>
       <c r="D6" s="33"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="34"/>
+      <c r="G6" s="35"/>
       <c r="H6" s="33"/>
       <c r="I6" s="33"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="34"/>
+      <c r="L6" s="35"/>
       <c r="M6" s="33"/>
       <c r="N6" s="33"/>
     </row>
@@ -3698,19 +3698,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="35"/>
+      <c r="B7" s="36"/>
       <c r="C7" s="33"/>
       <c r="D7" s="33"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="35"/>
+      <c r="G7" s="36"/>
       <c r="H7" s="33"/>
       <c r="I7" s="33"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="35"/>
+      <c r="L7" s="36"/>
       <c r="M7" s="33"/>
       <c r="N7" s="33"/>
     </row>
@@ -3718,19 +3718,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="34"/>
+      <c r="B8" s="35"/>
       <c r="C8" s="33"/>
       <c r="D8" s="33"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="34"/>
+      <c r="G8" s="35"/>
       <c r="H8" s="33"/>
       <c r="I8" s="33"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="34"/>
+      <c r="L8" s="35"/>
       <c r="M8" s="33"/>
       <c r="N8" s="33"/>
     </row>
@@ -3738,19 +3738,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="35"/>
+      <c r="B9" s="36"/>
       <c r="C9" s="33"/>
       <c r="D9" s="33"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="35"/>
+      <c r="G9" s="36"/>
       <c r="H9" s="33"/>
       <c r="I9" s="33"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="35"/>
+      <c r="L9" s="36"/>
       <c r="M9" s="33"/>
       <c r="N9" s="33"/>
     </row>
@@ -3758,19 +3758,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="34"/>
+      <c r="B10" s="35"/>
       <c r="C10" s="33"/>
       <c r="D10" s="33"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="34"/>
+      <c r="G10" s="35"/>
       <c r="H10" s="33"/>
       <c r="I10" s="33"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="34"/>
+      <c r="L10" s="35"/>
       <c r="M10" s="33"/>
       <c r="N10" s="33"/>
     </row>
@@ -3778,19 +3778,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="35"/>
+      <c r="B11" s="36"/>
       <c r="C11" s="33"/>
       <c r="D11" s="33"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="35"/>
+      <c r="G11" s="36"/>
       <c r="H11" s="33"/>
       <c r="I11" s="33"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="35"/>
+      <c r="L11" s="36"/>
       <c r="M11" s="33"/>
       <c r="N11" s="33"/>
     </row>
@@ -3798,19 +3798,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="34"/>
+      <c r="B12" s="35"/>
       <c r="C12" s="33"/>
       <c r="D12" s="33"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="34"/>
+      <c r="G12" s="35"/>
       <c r="H12" s="33"/>
       <c r="I12" s="33"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="34"/>
+      <c r="L12" s="35"/>
       <c r="M12" s="33"/>
       <c r="N12" s="33"/>
     </row>
@@ -3818,7 +3818,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="37">
+      <c r="B13" s="38">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3827,7 +3827,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="37">
+      <c r="G13" s="38">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3836,7 +3836,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="37">
+      <c r="L13" s="38">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3872,19 +3872,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="38" t="s">
+      <c r="A25" s="34" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="33"/>
       <c r="C25" s="33"/>
       <c r="D25" s="33"/>
-      <c r="F25" s="38" t="s">
+      <c r="F25" s="34" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="33"/>
       <c r="H25" s="33"/>
       <c r="I25" s="33"/>
-      <c r="K25" s="38" t="s">
+      <c r="K25" s="34" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="33"/>
@@ -3892,19 +3892,19 @@
       <c r="N25" s="33"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="38" t="s">
+      <c r="A26" s="34" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="33"/>
       <c r="C26" s="33"/>
       <c r="D26" s="33"/>
-      <c r="F26" s="38" t="s">
+      <c r="F26" s="34" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="33"/>
       <c r="H26" s="33"/>
       <c r="I26" s="33"/>
-      <c r="K26" s="38" t="s">
+      <c r="K26" s="34" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="33"/>
@@ -3926,27 +3926,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="37" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="33"/>
-      <c r="C28" s="36" t="s">
+      <c r="C28" s="37" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="33"/>
-      <c r="F28" s="36" t="s">
+      <c r="F28" s="37" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="33"/>
-      <c r="H28" s="36" t="s">
+      <c r="H28" s="37" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="33"/>
-      <c r="K28" s="36" t="s">
+      <c r="K28" s="37" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="33"/>
-      <c r="M28" s="36" t="s">
+      <c r="M28" s="37" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="33"/>
@@ -3955,19 +3955,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="35"/>
+      <c r="B29" s="36"/>
       <c r="C29" s="33"/>
       <c r="D29" s="33"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="35"/>
+      <c r="G29" s="36"/>
       <c r="H29" s="33"/>
       <c r="I29" s="33"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="35"/>
+      <c r="L29" s="36"/>
       <c r="M29" s="33"/>
       <c r="N29" s="33"/>
     </row>
@@ -3975,19 +3975,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="34"/>
+      <c r="B30" s="35"/>
       <c r="C30" s="33"/>
       <c r="D30" s="33"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="34"/>
+      <c r="G30" s="35"/>
       <c r="H30" s="33"/>
       <c r="I30" s="33"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="34"/>
+      <c r="L30" s="35"/>
       <c r="M30" s="33"/>
       <c r="N30" s="33"/>
     </row>
@@ -3995,19 +3995,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="35"/>
+      <c r="B31" s="36"/>
       <c r="C31" s="33"/>
       <c r="D31" s="33"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="35"/>
+      <c r="G31" s="36"/>
       <c r="H31" s="33"/>
       <c r="I31" s="33"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="35"/>
+      <c r="L31" s="36"/>
       <c r="M31" s="33"/>
       <c r="N31" s="33"/>
     </row>
@@ -4015,19 +4015,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="34"/>
+      <c r="B32" s="35"/>
       <c r="C32" s="33"/>
       <c r="D32" s="33"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="34"/>
+      <c r="G32" s="35"/>
       <c r="H32" s="33"/>
       <c r="I32" s="33"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="34"/>
+      <c r="L32" s="35"/>
       <c r="M32" s="33"/>
       <c r="N32" s="33"/>
     </row>
@@ -4035,19 +4035,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="35"/>
+      <c r="B33" s="36"/>
       <c r="C33" s="33"/>
       <c r="D33" s="33"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="35"/>
+      <c r="G33" s="36"/>
       <c r="H33" s="33"/>
       <c r="I33" s="33"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="35"/>
+      <c r="L33" s="36"/>
       <c r="M33" s="33"/>
       <c r="N33" s="33"/>
     </row>
@@ -4055,19 +4055,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="34"/>
+      <c r="B34" s="35"/>
       <c r="C34" s="33"/>
       <c r="D34" s="33"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="34"/>
+      <c r="G34" s="35"/>
       <c r="H34" s="33"/>
       <c r="I34" s="33"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="34"/>
+      <c r="L34" s="35"/>
       <c r="M34" s="33"/>
       <c r="N34" s="33"/>
     </row>
@@ -4075,19 +4075,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="35"/>
+      <c r="B35" s="36"/>
       <c r="C35" s="33"/>
       <c r="D35" s="33"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="35"/>
+      <c r="G35" s="36"/>
       <c r="H35" s="33"/>
       <c r="I35" s="33"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="35"/>
+      <c r="L35" s="36"/>
       <c r="M35" s="33"/>
       <c r="N35" s="33"/>
     </row>
@@ -4095,19 +4095,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="34"/>
+      <c r="B36" s="35"/>
       <c r="C36" s="33"/>
       <c r="D36" s="33"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="34"/>
+      <c r="G36" s="35"/>
       <c r="H36" s="33"/>
       <c r="I36" s="33"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="34"/>
+      <c r="L36" s="35"/>
       <c r="M36" s="33"/>
       <c r="N36" s="33"/>
     </row>
@@ -4115,7 +4115,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="37">
+      <c r="B37" s="38">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -4124,7 +4124,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="37">
+      <c r="G37" s="38">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -4133,7 +4133,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="37">
+      <c r="L37" s="38">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -4170,6 +4170,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="G36:I36"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="L13:N13"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
     <mergeCell ref="L34:N34"/>
     <mergeCell ref="L6:N6"/>
     <mergeCell ref="B33:D33"/>
@@ -4186,68 +4248,6 @@
     <mergeCell ref="B12:D12"/>
     <mergeCell ref="A26:D26"/>
     <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="G36:I36"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="L13:N13"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="F28:G28"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="B36:D36"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="L36:N36"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B34:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4295,7 +4295,7 @@
         <v>49</v>
       </c>
       <c r="E2" s="18">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="F2" s="18"/>
     </row>

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8A68365-18B9-4B86-A3DE-0233314273AE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{089315A4-7ED5-40B3-AD6B-5C63B769879F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instrucoes" sheetId="1" r:id="rId1"/>
@@ -453,9 +453,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -466,6 +463,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" s="21">
         <f>SUM(B6:B7)</f>
-        <v>2300</v>
+        <v>700</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>20</v>
@@ -807,16 +807,14 @@
       </c>
       <c r="L5" s="14">
         <f>SUM(L6:L7)</f>
-        <v>2600</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
       <c r="A6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="14">
-        <v>1500</v>
-      </c>
+      <c r="B6" s="14"/>
       <c r="F6" s="7" t="s">
         <v>21</v>
       </c>
@@ -824,16 +822,14 @@
       <c r="K6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="L6" s="14">
-        <v>2600</v>
-      </c>
+      <c r="L6" s="14"/>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
         <v>22</v>
       </c>
       <c r="B7" s="14">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="F7" s="7" t="s">
         <v>22</v>
@@ -864,7 +860,7 @@
       </c>
       <c r="L8" s="15">
         <f>SUM(L9:L10)</f>
-        <v>350</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1">
@@ -880,7 +876,7 @@
         <v>21</v>
       </c>
       <c r="L9" s="15">
-        <v>350</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
@@ -968,7 +964,7 @@
       </c>
       <c r="L14" s="15">
         <f>SUM(L15:L16)</f>
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1">
@@ -983,7 +979,9 @@
       <c r="K15" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L15" s="15"/>
+      <c r="L15" s="15">
+        <v>40</v>
+      </c>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1">
       <c r="A16" s="9" t="s">
@@ -1158,14 +1156,14 @@
       </c>
       <c r="B26" s="15">
         <f>SUM(B27:B28)</f>
-        <v>1100</v>
+        <v>1400</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>29</v>
       </c>
       <c r="G26" s="15">
         <f>SUM(G27:G28)</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K26" s="9" t="s">
         <v>29</v>
@@ -1183,7 +1181,9 @@
       <c r="F27" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G27" s="15"/>
+      <c r="G27" s="15">
+        <v>300</v>
+      </c>
       <c r="K27" s="9" t="s">
         <v>21</v>
       </c>
@@ -1194,7 +1194,7 @@
         <v>22</v>
       </c>
       <c r="B28" s="15">
-        <v>1100</v>
+        <v>1400</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>22</v>
@@ -1225,7 +1225,7 @@
       </c>
       <c r="L29" s="14">
         <f>SUM(L30:L31)</f>
-        <v>680</v>
+        <v>500</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1">
@@ -1241,7 +1241,7 @@
         <v>21</v>
       </c>
       <c r="L30" s="14">
-        <v>680</v>
+        <v>500</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="L38" s="23">
         <f>SUM(L39:L40)</f>
-        <v>50</v>
+        <v>300</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="15" customHeight="1">
@@ -1398,7 +1398,7 @@
         <v>21</v>
       </c>
       <c r="L39" s="15">
-        <v>50</v>
+        <v>300</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="15" customHeight="1">
@@ -1421,21 +1421,21 @@
       </c>
       <c r="B41" s="13">
         <f>SUM(B5,B8,B11,B14,B17,B20,B23,B26,B29,B32,B35,B38)</f>
-        <v>3540</v>
+        <v>2240</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G41" s="13">
         <f>SUM(G5,G8,G11,G14,G17,G20,G23,G26,G29,G32,G35,G38)</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="L41" s="13">
         <f>SUM(L5,L8,L11,L14,L17,L20,L23,L26,L29,L32,L35,L38)</f>
-        <v>3680</v>
+        <v>940</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="L62" s="15">
         <f>SUM(L63:L64)</f>
-        <v>0</v>
+        <v>190</v>
       </c>
     </row>
     <row r="63" spans="1:14" ht="15" customHeight="1">
@@ -1715,7 +1715,9 @@
       <c r="K63" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L63" s="15"/>
+      <c r="L63" s="15">
+        <v>190</v>
+      </c>
     </row>
     <row r="64" spans="1:14" ht="15" customHeight="1">
       <c r="A64" s="9" t="s">
@@ -2161,7 +2163,7 @@
       </c>
       <c r="L89" s="13">
         <f>SUM(L53,L56,L59,L62,L65,L68,L71,L74,L77,L80,L83,L86)</f>
-        <v>0</v>
+        <v>190</v>
       </c>
     </row>
     <row r="90" spans="1:14" ht="15" customHeight="1">
@@ -2827,19 +2829,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="38" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="33"/>
       <c r="D1" s="33"/>
-      <c r="F1" s="34" t="s">
+      <c r="F1" s="38" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="33"/>
       <c r="H1" s="33"/>
       <c r="I1" s="33"/>
-      <c r="K1" s="34" t="s">
+      <c r="K1" s="38" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="33"/>
@@ -2847,19 +2849,19 @@
       <c r="N1" s="33"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="38" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="33"/>
       <c r="C2" s="33"/>
       <c r="D2" s="33"/>
-      <c r="F2" s="34" t="s">
+      <c r="F2" s="38" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="33"/>
       <c r="H2" s="33"/>
       <c r="I2" s="33"/>
-      <c r="K2" s="34" t="s">
+      <c r="K2" s="38" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="33"/>
@@ -2881,27 +2883,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="33"/>
-      <c r="C4" s="37" t="s">
+      <c r="C4" s="36" t="s">
         <v>38</v>
       </c>
       <c r="D4" s="33"/>
-      <c r="F4" s="37" t="s">
+      <c r="F4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="33"/>
-      <c r="H4" s="37" t="s">
+      <c r="H4" s="36" t="s">
         <v>39</v>
       </c>
       <c r="I4" s="33"/>
-      <c r="K4" s="37" t="s">
+      <c r="K4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="33"/>
-      <c r="M4" s="37" t="s">
+      <c r="M4" s="36" t="s">
         <v>40</v>
       </c>
       <c r="N4" s="33"/>
@@ -2910,21 +2912,21 @@
       <c r="A5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="36">
-        <v>0</v>
-      </c>
-      <c r="C5" s="36"/>
-      <c r="D5" s="36"/>
+      <c r="B5" s="35">
+        <v>0</v>
+      </c>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
       <c r="F5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="36"/>
+      <c r="G5" s="35"/>
       <c r="H5" s="33"/>
       <c r="I5" s="33"/>
       <c r="K5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L5" s="36"/>
+      <c r="L5" s="35"/>
       <c r="M5" s="33"/>
       <c r="N5" s="33"/>
     </row>
@@ -2932,21 +2934,21 @@
       <c r="A6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="35">
-        <v>0</v>
-      </c>
-      <c r="C6" s="35"/>
-      <c r="D6" s="35"/>
+      <c r="B6" s="34">
+        <v>0</v>
+      </c>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
       <c r="F6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G6" s="35"/>
+      <c r="G6" s="34"/>
       <c r="H6" s="33"/>
       <c r="I6" s="33"/>
       <c r="K6" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L6" s="35"/>
+      <c r="L6" s="34"/>
       <c r="M6" s="33"/>
       <c r="N6" s="33"/>
     </row>
@@ -2954,21 +2956,21 @@
       <c r="A7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="36">
-        <v>0</v>
-      </c>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
+      <c r="B7" s="35">
+        <v>0</v>
+      </c>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
       <c r="F7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="36"/>
+      <c r="G7" s="35"/>
       <c r="H7" s="33"/>
       <c r="I7" s="33"/>
       <c r="K7" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L7" s="36"/>
+      <c r="L7" s="35"/>
       <c r="M7" s="33"/>
       <c r="N7" s="33"/>
     </row>
@@ -2976,21 +2978,21 @@
       <c r="A8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B8" s="35">
-        <v>0</v>
-      </c>
-      <c r="C8" s="35"/>
-      <c r="D8" s="35"/>
+      <c r="B8" s="34">
+        <v>0</v>
+      </c>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
       <c r="F8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G8" s="35"/>
+      <c r="G8" s="34"/>
       <c r="H8" s="33"/>
       <c r="I8" s="33"/>
       <c r="K8" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L8" s="35"/>
+      <c r="L8" s="34"/>
       <c r="M8" s="33"/>
       <c r="N8" s="33"/>
     </row>
@@ -2998,21 +3000,21 @@
       <c r="A9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B9" s="36">
-        <v>0</v>
-      </c>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
+      <c r="B9" s="35">
+        <v>0</v>
+      </c>
+      <c r="C9" s="35"/>
+      <c r="D9" s="35"/>
       <c r="F9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G9" s="36"/>
+      <c r="G9" s="35"/>
       <c r="H9" s="33"/>
       <c r="I9" s="33"/>
       <c r="K9" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="36"/>
+      <c r="L9" s="35"/>
       <c r="M9" s="33"/>
       <c r="N9" s="33"/>
     </row>
@@ -3020,21 +3022,21 @@
       <c r="A10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B10" s="35">
-        <v>0</v>
-      </c>
-      <c r="C10" s="35"/>
-      <c r="D10" s="35"/>
+      <c r="B10" s="34">
+        <v>0</v>
+      </c>
+      <c r="C10" s="34"/>
+      <c r="D10" s="34"/>
       <c r="F10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G10" s="35"/>
+      <c r="G10" s="34"/>
       <c r="H10" s="33"/>
       <c r="I10" s="33"/>
       <c r="K10" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L10" s="35"/>
+      <c r="L10" s="34"/>
       <c r="M10" s="33"/>
       <c r="N10" s="33"/>
     </row>
@@ -3042,7 +3044,7 @@
       <c r="A11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="38">
+      <c r="B11" s="37">
         <f>SUM(B5:B10)</f>
         <v>0</v>
       </c>
@@ -3051,7 +3053,7 @@
       <c r="F11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G11" s="38">
+      <c r="G11" s="37">
         <f>SUM(G5:G10)</f>
         <v>0</v>
       </c>
@@ -3060,7 +3062,7 @@
       <c r="K11" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L11" s="38">
+      <c r="L11" s="37">
         <f>SUM(L5:L10)</f>
         <v>0</v>
       </c>
@@ -3096,19 +3098,19 @@
       <c r="N13" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="34" t="s">
+      <c r="A25" s="38" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="33"/>
       <c r="C25" s="33"/>
       <c r="D25" s="33"/>
-      <c r="F25" s="34" t="s">
+      <c r="F25" s="38" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="33"/>
       <c r="H25" s="33"/>
       <c r="I25" s="33"/>
-      <c r="K25" s="34" t="s">
+      <c r="K25" s="38" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="33"/>
@@ -3116,19 +3118,19 @@
       <c r="N25" s="33"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="34" t="s">
+      <c r="A26" s="38" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="33"/>
       <c r="C26" s="33"/>
       <c r="D26" s="33"/>
-      <c r="F26" s="34" t="s">
+      <c r="F26" s="38" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="33"/>
       <c r="H26" s="33"/>
       <c r="I26" s="33"/>
-      <c r="K26" s="34" t="s">
+      <c r="K26" s="38" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="33"/>
@@ -3150,27 +3152,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="37" t="s">
+      <c r="A28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="33"/>
-      <c r="C28" s="37" t="s">
+      <c r="C28" s="36" t="s">
         <v>38</v>
       </c>
       <c r="D28" s="33"/>
-      <c r="F28" s="37" t="s">
+      <c r="F28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="33"/>
-      <c r="H28" s="37" t="s">
+      <c r="H28" s="36" t="s">
         <v>39</v>
       </c>
       <c r="I28" s="33"/>
-      <c r="K28" s="37" t="s">
+      <c r="K28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="33"/>
-      <c r="M28" s="37" t="s">
+      <c r="M28" s="36" t="s">
         <v>40</v>
       </c>
       <c r="N28" s="33"/>
@@ -3179,7 +3181,7 @@
       <c r="A29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="36">
+      <c r="B29" s="35">
         <v>0</v>
       </c>
       <c r="C29" s="33"/>
@@ -3187,23 +3189,23 @@
       <c r="F29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G29" s="36"/>
+      <c r="G29" s="35"/>
       <c r="H29" s="33"/>
       <c r="I29" s="33"/>
       <c r="K29" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="L29" s="36">
-        <v>0</v>
-      </c>
-      <c r="M29" s="36"/>
-      <c r="N29" s="36"/>
+      <c r="L29" s="35">
+        <v>0</v>
+      </c>
+      <c r="M29" s="35"/>
+      <c r="N29" s="35"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B30" s="35">
+      <c r="B30" s="34">
         <v>0</v>
       </c>
       <c r="C30" s="33"/>
@@ -3211,23 +3213,23 @@
       <c r="F30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="G30" s="35"/>
+      <c r="G30" s="34"/>
       <c r="H30" s="33"/>
       <c r="I30" s="33"/>
       <c r="K30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L30" s="35">
-        <v>0</v>
-      </c>
-      <c r="M30" s="35"/>
-      <c r="N30" s="35"/>
+      <c r="L30" s="34">
+        <v>0</v>
+      </c>
+      <c r="M30" s="34"/>
+      <c r="N30" s="34"/>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1">
       <c r="A31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="36">
+      <c r="B31" s="35">
         <v>0</v>
       </c>
       <c r="C31" s="33"/>
@@ -3235,23 +3237,23 @@
       <c r="F31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="G31" s="36"/>
+      <c r="G31" s="35"/>
       <c r="H31" s="33"/>
       <c r="I31" s="33"/>
       <c r="K31" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="L31" s="36">
-        <v>0</v>
-      </c>
-      <c r="M31" s="36"/>
-      <c r="N31" s="36"/>
+      <c r="L31" s="35">
+        <v>0</v>
+      </c>
+      <c r="M31" s="35"/>
+      <c r="N31" s="35"/>
     </row>
     <row r="32" spans="1:14" ht="15" customHeight="1">
       <c r="A32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="35">
+      <c r="B32" s="34">
         <v>0</v>
       </c>
       <c r="C32" s="33"/>
@@ -3259,23 +3261,23 @@
       <c r="F32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="G32" s="35"/>
+      <c r="G32" s="34"/>
       <c r="H32" s="33"/>
       <c r="I32" s="33"/>
       <c r="K32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="L32" s="35">
-        <v>0</v>
-      </c>
-      <c r="M32" s="35"/>
-      <c r="N32" s="35"/>
+      <c r="L32" s="34">
+        <v>0</v>
+      </c>
+      <c r="M32" s="34"/>
+      <c r="N32" s="34"/>
     </row>
     <row r="33" spans="1:14" ht="15" customHeight="1">
       <c r="A33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B33" s="36">
+      <c r="B33" s="35">
         <v>0</v>
       </c>
       <c r="C33" s="33"/>
@@ -3283,23 +3285,23 @@
       <c r="F33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="G33" s="36"/>
+      <c r="G33" s="35"/>
       <c r="H33" s="33"/>
       <c r="I33" s="33"/>
       <c r="K33" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L33" s="36">
-        <v>0</v>
-      </c>
-      <c r="M33" s="36"/>
-      <c r="N33" s="36"/>
+      <c r="L33" s="35">
+        <v>0</v>
+      </c>
+      <c r="M33" s="35"/>
+      <c r="N33" s="35"/>
     </row>
     <row r="34" spans="1:14" ht="15" customHeight="1">
       <c r="A34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B34" s="35">
+      <c r="B34" s="34">
         <v>0</v>
       </c>
       <c r="C34" s="33"/>
@@ -3307,13 +3309,13 @@
       <c r="F34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G34" s="35"/>
+      <c r="G34" s="34"/>
       <c r="H34" s="33"/>
       <c r="I34" s="33"/>
       <c r="K34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="L34" s="35">
+      <c r="L34" s="34">
         <v>0</v>
       </c>
       <c r="M34" s="33"/>
@@ -3323,7 +3325,7 @@
       <c r="A35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B35" s="38">
+      <c r="B35" s="37">
         <f>SUM(B29:B34)</f>
         <v>0</v>
       </c>
@@ -3332,7 +3334,7 @@
       <c r="F35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="38">
+      <c r="G35" s="37">
         <f>SUM(G29:G34)</f>
         <v>0</v>
       </c>
@@ -3341,7 +3343,7 @@
       <c r="K35" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L35" s="38">
+      <c r="L35" s="37">
         <f>SUM(L29:L34)</f>
         <v>0</v>
       </c>
@@ -3378,6 +3380,56 @@
     </row>
   </sheetData>
   <mergeCells count="66">
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="L32:N32"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="K28:L28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="G32:I32"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F25:I25"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="L33:N33"/>
+    <mergeCell ref="L35:N35"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="G34:I34"/>
     <mergeCell ref="B6:D6"/>
     <mergeCell ref="B33:D33"/>
     <mergeCell ref="B10:D10"/>
@@ -3394,56 +3446,6 @@
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="F28:G28"/>
     <mergeCell ref="H28:I28"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="L35:N35"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="B34:D34"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="L9:N9"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="G32:I32"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="L32:N32"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="K28:L28"/>
-    <mergeCell ref="C28:D28"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3459,7 +3461,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15" customHeight="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="38" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="33"/>
@@ -3467,7 +3469,7 @@
       <c r="D1" s="33"/>
     </row>
     <row r="2" spans="1:4" ht="15" customHeight="1">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="38" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="33"/>
@@ -3481,11 +3483,11 @@
       <c r="D3" s="9"/>
     </row>
     <row r="4" spans="1:4" ht="15" customHeight="1">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="36" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="33"/>
-      <c r="C4" s="37" t="s">
+      <c r="C4" s="36" t="s">
         <v>48</v>
       </c>
       <c r="D4" s="33"/>
@@ -3494,7 +3496,7 @@
       <c r="A5" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="36"/>
+      <c r="B5" s="35"/>
       <c r="C5" s="33"/>
       <c r="D5" s="33"/>
     </row>
@@ -3502,7 +3504,7 @@
       <c r="A6" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="35"/>
+      <c r="B6" s="34"/>
       <c r="C6" s="33"/>
       <c r="D6" s="33"/>
     </row>
@@ -3510,7 +3512,7 @@
       <c r="A7" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="36"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="33"/>
       <c r="D7" s="33"/>
     </row>
@@ -3518,7 +3520,7 @@
       <c r="A8" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="B8" s="35"/>
+      <c r="B8" s="34"/>
       <c r="C8" s="33"/>
       <c r="D8" s="33"/>
     </row>
@@ -3526,7 +3528,7 @@
       <c r="A9" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="38">
+      <c r="B9" s="37">
         <f>SUM(B5:B8)</f>
         <v>0</v>
       </c>
@@ -3575,19 +3577,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="38" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="33"/>
       <c r="D1" s="33"/>
-      <c r="F1" s="34" t="s">
+      <c r="F1" s="38" t="s">
         <v>15</v>
       </c>
       <c r="G1" s="33"/>
       <c r="H1" s="33"/>
       <c r="I1" s="33"/>
-      <c r="K1" s="34" t="s">
+      <c r="K1" s="38" t="s">
         <v>15</v>
       </c>
       <c r="L1" s="33"/>
@@ -3595,19 +3597,19 @@
       <c r="N1" s="33"/>
     </row>
     <row r="2" spans="1:14" ht="15" customHeight="1">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="38" t="s">
         <v>36</v>
       </c>
       <c r="B2" s="33"/>
       <c r="C2" s="33"/>
       <c r="D2" s="33"/>
-      <c r="F2" s="34" t="s">
+      <c r="F2" s="38" t="s">
         <v>36</v>
       </c>
       <c r="G2" s="33"/>
       <c r="H2" s="33"/>
       <c r="I2" s="33"/>
-      <c r="K2" s="34" t="s">
+      <c r="K2" s="38" t="s">
         <v>36</v>
       </c>
       <c r="L2" s="33"/>
@@ -3629,27 +3631,27 @@
       <c r="N3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="15" customHeight="1">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="B4" s="33"/>
-      <c r="C4" s="37" t="s">
+      <c r="C4" s="36" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="33"/>
-      <c r="F4" s="37" t="s">
+      <c r="F4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="G4" s="33"/>
-      <c r="H4" s="37" t="s">
+      <c r="H4" s="36" t="s">
         <v>54</v>
       </c>
       <c r="I4" s="33"/>
-      <c r="K4" s="37" t="s">
+      <c r="K4" s="36" t="s">
         <v>37</v>
       </c>
       <c r="L4" s="33"/>
-      <c r="M4" s="37" t="s">
+      <c r="M4" s="36" t="s">
         <v>55</v>
       </c>
       <c r="N4" s="33"/>
@@ -3658,19 +3660,19 @@
       <c r="A5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="36"/>
+      <c r="B5" s="35"/>
       <c r="C5" s="33"/>
       <c r="D5" s="33"/>
       <c r="F5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G5" s="36"/>
+      <c r="G5" s="35"/>
       <c r="H5" s="33"/>
       <c r="I5" s="33"/>
       <c r="K5" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="36"/>
+      <c r="L5" s="35"/>
       <c r="M5" s="33"/>
       <c r="N5" s="33"/>
     </row>
@@ -3678,19 +3680,19 @@
       <c r="A6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B6" s="35"/>
+      <c r="B6" s="34"/>
       <c r="C6" s="33"/>
       <c r="D6" s="33"/>
       <c r="F6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="35"/>
+      <c r="G6" s="34"/>
       <c r="H6" s="33"/>
       <c r="I6" s="33"/>
       <c r="K6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L6" s="35"/>
+      <c r="L6" s="34"/>
       <c r="M6" s="33"/>
       <c r="N6" s="33"/>
     </row>
@@ -3698,19 +3700,19 @@
       <c r="A7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="36"/>
+      <c r="B7" s="35"/>
       <c r="C7" s="33"/>
       <c r="D7" s="33"/>
       <c r="F7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="36"/>
+      <c r="G7" s="35"/>
       <c r="H7" s="33"/>
       <c r="I7" s="33"/>
       <c r="K7" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L7" s="36"/>
+      <c r="L7" s="35"/>
       <c r="M7" s="33"/>
       <c r="N7" s="33"/>
     </row>
@@ -3718,19 +3720,19 @@
       <c r="A8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B8" s="35"/>
+      <c r="B8" s="34"/>
       <c r="C8" s="33"/>
       <c r="D8" s="33"/>
       <c r="F8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G8" s="35"/>
+      <c r="G8" s="34"/>
       <c r="H8" s="33"/>
       <c r="I8" s="33"/>
       <c r="K8" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L8" s="35"/>
+      <c r="L8" s="34"/>
       <c r="M8" s="33"/>
       <c r="N8" s="33"/>
     </row>
@@ -3738,19 +3740,19 @@
       <c r="A9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="36"/>
+      <c r="B9" s="35"/>
       <c r="C9" s="33"/>
       <c r="D9" s="33"/>
       <c r="F9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="36"/>
+      <c r="G9" s="35"/>
       <c r="H9" s="33"/>
       <c r="I9" s="33"/>
       <c r="K9" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L9" s="36"/>
+      <c r="L9" s="35"/>
       <c r="M9" s="33"/>
       <c r="N9" s="33"/>
     </row>
@@ -3758,19 +3760,19 @@
       <c r="A10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="35"/>
+      <c r="B10" s="34"/>
       <c r="C10" s="33"/>
       <c r="D10" s="33"/>
       <c r="F10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G10" s="35"/>
+      <c r="G10" s="34"/>
       <c r="H10" s="33"/>
       <c r="I10" s="33"/>
       <c r="K10" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L10" s="35"/>
+      <c r="L10" s="34"/>
       <c r="M10" s="33"/>
       <c r="N10" s="33"/>
     </row>
@@ -3778,19 +3780,19 @@
       <c r="A11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B11" s="36"/>
+      <c r="B11" s="35"/>
       <c r="C11" s="33"/>
       <c r="D11" s="33"/>
       <c r="F11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G11" s="36"/>
+      <c r="G11" s="35"/>
       <c r="H11" s="33"/>
       <c r="I11" s="33"/>
       <c r="K11" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L11" s="36"/>
+      <c r="L11" s="35"/>
       <c r="M11" s="33"/>
       <c r="N11" s="33"/>
     </row>
@@ -3798,19 +3800,19 @@
       <c r="A12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="35"/>
+      <c r="B12" s="34"/>
       <c r="C12" s="33"/>
       <c r="D12" s="33"/>
       <c r="F12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G12" s="35"/>
+      <c r="G12" s="34"/>
       <c r="H12" s="33"/>
       <c r="I12" s="33"/>
       <c r="K12" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L12" s="35"/>
+      <c r="L12" s="34"/>
       <c r="M12" s="33"/>
       <c r="N12" s="33"/>
     </row>
@@ -3818,7 +3820,7 @@
       <c r="A13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="38">
+      <c r="B13" s="37">
         <f>SUM(B5:B12)</f>
         <v>0</v>
       </c>
@@ -3827,7 +3829,7 @@
       <c r="F13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="38">
+      <c r="G13" s="37">
         <f>SUM(G5:G12)</f>
         <v>0</v>
       </c>
@@ -3836,7 +3838,7 @@
       <c r="K13" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L13" s="38">
+      <c r="L13" s="37">
         <f>SUM(L5:L12)</f>
         <v>0</v>
       </c>
@@ -3872,19 +3874,19 @@
       <c r="N15" s="9"/>
     </row>
     <row r="25" spans="1:14" ht="15" customHeight="1">
-      <c r="A25" s="34" t="s">
+      <c r="A25" s="38" t="s">
         <v>15</v>
       </c>
       <c r="B25" s="33"/>
       <c r="C25" s="33"/>
       <c r="D25" s="33"/>
-      <c r="F25" s="34" t="s">
+      <c r="F25" s="38" t="s">
         <v>15</v>
       </c>
       <c r="G25" s="33"/>
       <c r="H25" s="33"/>
       <c r="I25" s="33"/>
-      <c r="K25" s="34" t="s">
+      <c r="K25" s="38" t="s">
         <v>15</v>
       </c>
       <c r="L25" s="33"/>
@@ -3892,19 +3894,19 @@
       <c r="N25" s="33"/>
     </row>
     <row r="26" spans="1:14" ht="15" customHeight="1">
-      <c r="A26" s="34" t="s">
+      <c r="A26" s="38" t="s">
         <v>36</v>
       </c>
       <c r="B26" s="33"/>
       <c r="C26" s="33"/>
       <c r="D26" s="33"/>
-      <c r="F26" s="34" t="s">
+      <c r="F26" s="38" t="s">
         <v>36</v>
       </c>
       <c r="G26" s="33"/>
       <c r="H26" s="33"/>
       <c r="I26" s="33"/>
-      <c r="K26" s="34" t="s">
+      <c r="K26" s="38" t="s">
         <v>36</v>
       </c>
       <c r="L26" s="33"/>
@@ -3926,27 +3928,27 @@
       <c r="N27" s="9"/>
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
-      <c r="A28" s="37" t="s">
+      <c r="A28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="B28" s="33"/>
-      <c r="C28" s="37" t="s">
+      <c r="C28" s="36" t="s">
         <v>53</v>
       </c>
       <c r="D28" s="33"/>
-      <c r="F28" s="37" t="s">
+      <c r="F28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="G28" s="33"/>
-      <c r="H28" s="37" t="s">
+      <c r="H28" s="36" t="s">
         <v>54</v>
       </c>
       <c r="I28" s="33"/>
-      <c r="K28" s="37" t="s">
+      <c r="K28" s="36" t="s">
         <v>47</v>
       </c>
       <c r="L28" s="33"/>
-      <c r="M28" s="37" t="s">
+      <c r="M28" s="36" t="s">
         <v>55</v>
       </c>
       <c r="N28" s="33"/>
@@ -3955,19 +3957,19 @@
       <c r="A29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="36"/>
+      <c r="B29" s="35"/>
       <c r="C29" s="33"/>
       <c r="D29" s="33"/>
       <c r="F29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="G29" s="36"/>
+      <c r="G29" s="35"/>
       <c r="H29" s="33"/>
       <c r="I29" s="33"/>
       <c r="K29" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="L29" s="36"/>
+      <c r="L29" s="35"/>
       <c r="M29" s="33"/>
       <c r="N29" s="33"/>
     </row>
@@ -3975,19 +3977,19 @@
       <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="35"/>
+      <c r="B30" s="34"/>
       <c r="C30" s="33"/>
       <c r="D30" s="33"/>
       <c r="F30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="G30" s="35"/>
+      <c r="G30" s="34"/>
       <c r="H30" s="33"/>
       <c r="I30" s="33"/>
       <c r="K30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="L30" s="35"/>
+      <c r="L30" s="34"/>
       <c r="M30" s="33"/>
       <c r="N30" s="33"/>
     </row>
@@ -3995,19 +3997,19 @@
       <c r="A31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="B31" s="36"/>
+      <c r="B31" s="35"/>
       <c r="C31" s="33"/>
       <c r="D31" s="33"/>
       <c r="F31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G31" s="36"/>
+      <c r="G31" s="35"/>
       <c r="H31" s="33"/>
       <c r="I31" s="33"/>
       <c r="K31" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L31" s="36"/>
+      <c r="L31" s="35"/>
       <c r="M31" s="33"/>
       <c r="N31" s="33"/>
     </row>
@@ -4015,19 +4017,19 @@
       <c r="A32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B32" s="35"/>
+      <c r="B32" s="34"/>
       <c r="C32" s="33"/>
       <c r="D32" s="33"/>
       <c r="F32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="G32" s="35"/>
+      <c r="G32" s="34"/>
       <c r="H32" s="33"/>
       <c r="I32" s="33"/>
       <c r="K32" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="L32" s="35"/>
+      <c r="L32" s="34"/>
       <c r="M32" s="33"/>
       <c r="N32" s="33"/>
     </row>
@@ -4035,19 +4037,19 @@
       <c r="A33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B33" s="36"/>
+      <c r="B33" s="35"/>
       <c r="C33" s="33"/>
       <c r="D33" s="33"/>
       <c r="F33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="G33" s="36"/>
+      <c r="G33" s="35"/>
       <c r="H33" s="33"/>
       <c r="I33" s="33"/>
       <c r="K33" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L33" s="36"/>
+      <c r="L33" s="35"/>
       <c r="M33" s="33"/>
       <c r="N33" s="33"/>
     </row>
@@ -4055,19 +4057,19 @@
       <c r="A34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B34" s="35"/>
+      <c r="B34" s="34"/>
       <c r="C34" s="33"/>
       <c r="D34" s="33"/>
       <c r="F34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="G34" s="35"/>
+      <c r="G34" s="34"/>
       <c r="H34" s="33"/>
       <c r="I34" s="33"/>
       <c r="K34" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="L34" s="35"/>
+      <c r="L34" s="34"/>
       <c r="M34" s="33"/>
       <c r="N34" s="33"/>
     </row>
@@ -4075,19 +4077,19 @@
       <c r="A35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="B35" s="36"/>
+      <c r="B35" s="35"/>
       <c r="C35" s="33"/>
       <c r="D35" s="33"/>
       <c r="F35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G35" s="36"/>
+      <c r="G35" s="35"/>
       <c r="H35" s="33"/>
       <c r="I35" s="33"/>
       <c r="K35" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L35" s="36"/>
+      <c r="L35" s="35"/>
       <c r="M35" s="33"/>
       <c r="N35" s="33"/>
     </row>
@@ -4095,19 +4097,19 @@
       <c r="A36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="B36" s="35"/>
+      <c r="B36" s="34"/>
       <c r="C36" s="33"/>
       <c r="D36" s="33"/>
       <c r="F36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="G36" s="35"/>
+      <c r="G36" s="34"/>
       <c r="H36" s="33"/>
       <c r="I36" s="33"/>
       <c r="K36" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L36" s="35"/>
+      <c r="L36" s="34"/>
       <c r="M36" s="33"/>
       <c r="N36" s="33"/>
     </row>
@@ -4115,7 +4117,7 @@
       <c r="A37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="38">
+      <c r="B37" s="37">
         <f>SUM(B29:B36)</f>
         <v>0</v>
       </c>
@@ -4124,7 +4126,7 @@
       <c r="F37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="G37" s="38">
+      <c r="G37" s="37">
         <f>SUM(G29:G36)</f>
         <v>0</v>
       </c>
@@ -4133,7 +4135,7 @@
       <c r="K37" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="L37" s="38">
+      <c r="L37" s="37">
         <f>SUM(L29:L36)</f>
         <v>0</v>
       </c>
@@ -4170,6 +4172,68 @@
     </row>
   </sheetData>
   <mergeCells count="78">
+    <mergeCell ref="L34:N34"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="B33:D33"/>
+    <mergeCell ref="B32:D32"/>
+    <mergeCell ref="M28:N28"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="L7:N7"/>
+    <mergeCell ref="F26:I26"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="L9:N9"/>
+    <mergeCell ref="F1:I1"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="F2:I2"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="K2:N2"/>
+    <mergeCell ref="G6:I6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="L37:N37"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="L12:N12"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="G34:I34"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="G37:I37"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="L8:N8"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="G35:I35"/>
+    <mergeCell ref="B37:D37"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="G33:I33"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="B31:D31"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="L11:N11"/>
+    <mergeCell ref="K26:N26"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B11:D11"/>
+    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="G5:I5"/>
     <mergeCell ref="G36:I36"/>
     <mergeCell ref="L32:N32"/>
     <mergeCell ref="L13:N13"/>
@@ -4186,68 +4250,6 @@
     <mergeCell ref="L33:N33"/>
     <mergeCell ref="L35:N35"/>
     <mergeCell ref="B34:D34"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="L11:N11"/>
-    <mergeCell ref="K26:N26"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B11:D11"/>
-    <mergeCell ref="G13:I13"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="G33:I33"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="L37:N37"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="L12:N12"/>
-    <mergeCell ref="G10:I10"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="G34:I34"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="B35:D35"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="G37:I37"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="L8:N8"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="G35:I35"/>
-    <mergeCell ref="B37:D37"/>
-    <mergeCell ref="F1:I1"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="F2:I2"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="K2:N2"/>
-    <mergeCell ref="G6:I6"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="L5:N5"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="L34:N34"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="M28:N28"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="G11:I11"/>
-    <mergeCell ref="L7:N7"/>
-    <mergeCell ref="F26:I26"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="L10:N10"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="L9:N9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/disponibilidade.xlsx
+++ b/disponibilidade.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rafael.germano\Documents\Rafael Germano\Codex\2026-05-19\app disponiblidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{089315A4-7ED5-40B3-AD6B-5C63B769879F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F9056CF-19E1-48E7-9EDE-6309115773D8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12105" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -453,6 +453,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -463,9 +466,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -793,7 +793,7 @@
       </c>
       <c r="B5" s="21">
         <f>SUM(B6:B7)</f>
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>20</v>
@@ -807,7 +807,7 @@
       </c>
       <c r="L5" s="14">
         <f>SUM(L6:L7)</f>
-        <v>0</v>
+        <v>700</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="15" customHeight="1">
@@ -822,15 +822,15 @@
       <c r="K6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="L6" s="14"/>
+      <c r="L6" s="14">
+        <v>700</v>
+      </c>
     </row>
     <row r="7" spans="1:14" ht="15" customHeight="1">
       <c r="A7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="14">
-        <v>700</v>
-      </c>
+      <c r="B7" s="14"/>
       <c r="F7" s="7" t="s">
         <v>22</v>
       </c>
@@ -853,14 +853,14 @@
       </c>
       <c r="G8" s="15">
         <f>SUM(G9:G10)</f>
-        <v>0</v>
+        <v>168.66666666666666</v>
       </c>
       <c r="K8" s="9" t="s">
         <v>23</v>
       </c>
       <c r="L8" s="15">
         <f>SUM(L9:L10)</f>
-        <v>100</v>
+        <v>765</v>
       </c>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1">
@@ -871,12 +871,15 @@
       <c r="F9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="15"/>
+      <c r="G9" s="15">
+        <f>138*22/18</f>
+        <v>168.66666666666666</v>
+      </c>
       <c r="K9" s="9" t="s">
         <v>21</v>
       </c>
       <c r="L9" s="15">
-        <v>100</v>
+        <v>765</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1">
@@ -964,7 +967,7 @@
       </c>
       <c r="L14" s="15">
         <f>SUM(L15:L16)</f>
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:14" ht="15" customHeight="1">
@@ -979,9 +982,7 @@
       <c r="K15" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="L15" s="15">
-        <v>40</v>
-      </c>
+      <c r="L15" s="15"/>
     </row>
     <row r="16" spans="1:14" ht="15" customHeight="1">
       <c r="A16" s="9" t="s">
@@ -1105,14 +1106,14 @@
       </c>
       <c r="B23" s="14">
         <f>SUM(B24:B25)</f>
-        <v>0</v>
+        <v>264</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>28</v>
       </c>
       <c r="G23" s="14">
         <f>SUM(G24:G25)</f>
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="K23" s="7" t="s">
         <v>28</v>
@@ -1140,11 +1141,15 @@
       <c r="A25" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="B25" s="14"/>
+      <c r="B25" s="14">
+        <v>264</v>
+      </c>
       <c r="F25" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G25" s="14"/>
+      <c r="G25" s="14">
+        <v>175</v>
+      </c>
       <c r="K25" s="7" t="s">
         <v>22</v>
       </c>
@@ -1156,14 +1161,14 @@
       </c>
       <c r="B26" s="15">
         <f>SUM(B27:B28)</f>
-        <v>1400</v>
+        <v>1868.5555555555557</v>
       </c>
       <c r="F26" s="9" t="s">
         <v>29</v>
       </c>
       <c r="G26" s="15">
         <f>SUM(G27:G28)</f>
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K26" s="9" t="s">
         <v>29</v>
@@ -1182,7 +1187,7 @@
         <v>21</v>
       </c>
       <c r="G27" s="15">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="K27" s="9" t="s">
         <v>21</v>
@@ -1194,7 +1199,8 @@
         <v>22</v>
       </c>
       <c r="B28" s="15">
-        <v>1400</v>
+        <f>((518*18)+(1105*22))/18</f>
+        <v>1868.5555555555557</v>
       </c>
       <c r="F28" s="9" t="s">
         <v>22</v>
@@ -1211,7 +1217,7 @@
       </c>
       <c r="B29" s="14">
         <f>SUM(B30:B31)</f>
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>30</v>
@@ -1225,14 +1231,16 @@
       </c>
       <c r="L29" s="14">
         <f>SUM(L30:L31)</f>
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="30" spans="1:12" ht="15" customHeight="1">
       <c r="A30" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B30" s="14"/>
+      <c r="B30" s="14">
+        <v>57</v>
+      </c>
       <c r="F30" s="7" t="s">
         <v>21</v>
       </c>
@@ -1241,7 +1249,7 @@
         <v>21</v>
       </c>
       <c r="L30" s="14">
-        <v>500</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="31" spans="1:12" ht="15" customHeight="1">
@@ -1264,7 +1272,7 @@
       </c>
       <c r="B32" s="15">
         <f>SUM(B33:B34)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>31</v>
@@ -1285,7 +1293,9 @@
       <c r="A33" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="15"/>
+      <c r="B33" s="15">
+        <v>30</v>
+      </c>
       <c r="F33" s="9" t="s">
         <v>21</v>
       </c>
@@ -1366,7 +1376,7 @@
       </c>
       <c r="B38" s="22">
         <f>SUM(B39:B40)</f>
-        <v>140</v>
+        <v>92</v>
       </c>
       <c r="F38" s="9" t="s">
         <v>72</v>
@@ -1380,7 +1390,7 @@
       </c>
       <c r="L38" s="23">
         <f>SUM(L39:L40)</f>
-        <v>300</v>
+        <v>340</v>
       </c>
     </row>
     <row r="39" spans="1:14" ht="15" customHeight="1">
@@ -1388,7 +1398,7 @@
         <v>21</v>
       </c>
       <c r="B39" s="15">
-        <v>140</v>
+        <v>92</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>21</v>
@@ -1398,7 +1408,7 @@
         <v>21</v>
       </c>
       <c r="L39" s="15">
-        <v>300</v>
+        <v>340</v>
       </c>
     </row>
     <row r="40" spans="1:14" ht="15" customHeight="1">
@@ -1421,21 +1431,21 @@
       </c>
       <c r="B41" s="13">
         <f>SUM(B5,B8,B11,B14,B17,B20,B23,B26,B29,B32,B35,B38)</f>
-        <v>2240</v>
+        <v>2311.5555555555557</v>
       </c>
       <c r="F41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="G41" s="13">
         <f>SUM(G5,G8,G11,G14,G17,G20,G23,G26,G29,G32,G35,G38)</f>
-        <v>300</v>
+        <v>543.66666666666663</v>
       </c>
       <c r="K41" s="8" t="s">
         <v>34</v>
       </c>
       <c r="L41" s="13">
         <f>SUM(L5,L8,L11,L14,L17,L20,L23,L26,L29,L32,L35,L38)</f>
-        <v>940</v>
+        <v>2805</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="15" customHeight="1">
@@ -1538,7 +1548,7 @@
       </c>
       <c r="G53" s="14">
         <f>SUM(G54:G55)</f>
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="K53" s="7" t="s">
         <v>20</v>
@@ -1556,7 +1566,9 @@
       <c r="F54" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="G54" s="14"/>
+      <c r="G54" s="14">
+        <v>700</v>
+      </c>
       <c r="K54" s="7" t="s">
         <v>21</v>
       </c>
@@ -1589,7 +1601,7 @@
       </c>
       <c r="G56" s="15">
         <f>SUM(G57:G58)</f>
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="K56" s="9" t="s">
         <v>23</v>
@@ -1607,7 +1619,9 @@
       <c r="F57" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G57" s="15"/>
+      <c r="G57" s="15">
+        <v>500</v>
+      </c>
       <c r="K57" s="9" t="s">
         <v>21</v>
       </c>
@@ -1691,14 +1705,14 @@
       </c>
       <c r="G62" s="15">
         <f>SUM(G63:G64)</f>
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="K62" s="9" t="s">
         <v>25</v>
       </c>
       <c r="L62" s="15">
         <f>SUM(L63:L64)</f>
-        <v>190</v>
+        <v>21</v>
       </c>
     </row>
     <row r="63" spans="1:14" ht="15" customHeight="1">
@@ -1709,14 +1723,12 @@
       <c r="F63" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G63" s="15">
-        <v>16</v>
-      </c>
+      <c r="G63" s="15"/>
       <c r="K63" s="9" t="s">
         <v>21</v>
       </c>
       <c r="L63" s="15">
-        <v>190</v>
+        <v>21</v>
       </c>
     </row>
     <row r="64" spans="1:14" ht="15" customHeight="1">
@@ -2156,14 +2168,14 @@
       </c>
       <c r="G89" s="13">
         <f>SUM(G53,G56,G59,G62,G65,G68,G71,G74,G77,G80,G83,G86)</f>
-        <v>16</v>
+        <v>1200</v>
       </c>
       <c r="K89" s="8" t="s">
         <v>34</v>
       </c>
       <c r="L89" s="13">
         <f>SUM(L53,L56,L59,L62,L65,L68,L71,L74,L77,L80,L83,L86)</f>
-        <v>190</v>
+        <v>21</v>
       </c>
     </row>
     <row r="90" spans="1:14" ht="15" customHeight="1">
@@ -2829,19 +2841,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="34" t="s">
         <v>15</v>
       </c>
       <c r="B1" s="33"/>
       <c r="C1" s="33"/>
       <c r="D1" s="33"/>
